--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,15 @@
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,6 +531,51 @@
           <t>rsi</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ah_close</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ah_volume</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ah_pct_move</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pm_open</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pm_volume</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pm_pct_move</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>last_ah_high</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>last_ah_low</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>has_extended_data</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -577,6 +631,33 @@
       <c r="O2" t="n">
         <v>48.2</v>
       </c>
+      <c r="P2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-37.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>16.3997</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="X2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -632,6 +713,33 @@
       <c r="O3" t="n">
         <v>54.8</v>
       </c>
+      <c r="P3" t="n">
+        <v>4.7092</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.7776</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-13.74</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="X3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -687,6 +795,33 @@
       <c r="O4" t="n">
         <v>64.59999999999999</v>
       </c>
+      <c r="P4" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.828</v>
+      </c>
+      <c r="W4" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="X4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -742,6 +877,33 @@
       <c r="O5" t="n">
         <v>73.40000000000001</v>
       </c>
+      <c r="P5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -797,6 +959,33 @@
       <c r="O6" t="n">
         <v>49.5</v>
       </c>
+      <c r="P6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="X6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -852,6 +1041,33 @@
       <c r="O7" t="n">
         <v>66.59999999999999</v>
       </c>
+      <c r="P7" t="n">
+        <v>3.681</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="X7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -907,6 +1123,33 @@
       <c r="O8" t="n">
         <v>58.1</v>
       </c>
+      <c r="P8" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="X8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -962,6 +1205,33 @@
       <c r="O9" t="n">
         <v>52.7</v>
       </c>
+      <c r="P9" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="V9" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1017,6 +1287,33 @@
       <c r="O10" t="n">
         <v>53.7</v>
       </c>
+      <c r="P10" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15.517</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="X10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1072,6 +1369,33 @@
       <c r="O11" t="n">
         <v>52.6</v>
       </c>
+      <c r="P11" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="X11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1127,6 +1451,33 @@
       <c r="O12" t="n">
         <v>58.1</v>
       </c>
+      <c r="P12" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.1196</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.1799</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="X12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1182,6 +1533,33 @@
       <c r="O13" t="n">
         <v>55.3</v>
       </c>
+      <c r="P13" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="V13" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1237,6 +1615,33 @@
       <c r="O14" t="n">
         <v>42.7</v>
       </c>
+      <c r="P14" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1292,6 +1697,33 @@
       <c r="O15" t="n">
         <v>58.2</v>
       </c>
+      <c r="P15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1347,6 +1779,33 @@
       <c r="O16" t="n">
         <v>60.4</v>
       </c>
+      <c r="P16" t="n">
+        <v>5.1599</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.5872</v>
+      </c>
+      <c r="X16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1402,6 +1861,33 @@
       <c r="O17" t="n">
         <v>62.8</v>
       </c>
+      <c r="P17" t="n">
+        <v>1.5983</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.5983</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.4207</v>
+      </c>
+      <c r="X17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1457,6 +1943,33 @@
       <c r="O18" t="n">
         <v>44.7</v>
       </c>
+      <c r="P18" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="X18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1512,6 +2025,33 @@
       <c r="O19" t="n">
         <v>49</v>
       </c>
+      <c r="P19" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="V19" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="W19" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1567,6 +2107,33 @@
       <c r="O20" t="n">
         <v>63.9</v>
       </c>
+      <c r="P20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-9.57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1622,6 +2189,33 @@
       <c r="O21" t="n">
         <v>58.5</v>
       </c>
+      <c r="P21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-7.14</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.3326</v>
+      </c>
+      <c r="X21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1677,6 +2271,33 @@
       <c r="O22" t="n">
         <v>71.90000000000001</v>
       </c>
+      <c r="P22" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>6.451</v>
+      </c>
+      <c r="X22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1732,6 +2353,33 @@
       <c r="O23" t="n">
         <v>61.6</v>
       </c>
+      <c r="P23" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="X23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1787,6 +2435,33 @@
       <c r="O24" t="n">
         <v>46.7</v>
       </c>
+      <c r="P24" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="X24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1842,6 +2517,33 @@
       <c r="O25" t="n">
         <v>69.90000000000001</v>
       </c>
+      <c r="P25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1897,6 +2599,33 @@
       <c r="O26" t="n">
         <v>52.4</v>
       </c>
+      <c r="P26" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="X26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1952,6 +2681,33 @@
       <c r="O27" t="n">
         <v>60.2</v>
       </c>
+      <c r="P27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="X27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2007,6 +2763,33 @@
       <c r="O28" t="n">
         <v>51.2</v>
       </c>
+      <c r="P28" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="S28" t="n">
+        <v>14.0227</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V28" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13.5543</v>
+      </c>
+      <c r="X28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2062,6 +2845,33 @@
       <c r="O29" t="n">
         <v>42.6</v>
       </c>
+      <c r="P29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2117,6 +2927,33 @@
       <c r="O30" t="n">
         <v>70.7</v>
       </c>
+      <c r="P30" t="n">
+        <v>2.8301</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2172,6 +3009,33 @@
       <c r="O31" t="n">
         <v>52.5</v>
       </c>
+      <c r="P31" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="S31" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="V31" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="W31" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="X31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2227,6 +3091,33 @@
       <c r="O32" t="n">
         <v>47.3</v>
       </c>
+      <c r="P32" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="X32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2282,6 +3173,33 @@
       <c r="O33" t="n">
         <v>30.4</v>
       </c>
+      <c r="P33" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="W33" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="X33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2337,6 +3255,33 @@
       <c r="O34" t="n">
         <v>48.2</v>
       </c>
+      <c r="P34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-32.04</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="X34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2392,6 +3337,33 @@
       <c r="O35" t="n">
         <v>54.3</v>
       </c>
+      <c r="P35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.2399</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.9236</v>
+      </c>
+      <c r="X35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2447,6 +3419,33 @@
       <c r="O36" t="n">
         <v>63</v>
       </c>
+      <c r="P36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2502,6 +3501,33 @@
       <c r="O37" t="n">
         <v>37.6</v>
       </c>
+      <c r="P37" t="n">
+        <v>8.321099999999999</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V37" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="W37" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="X37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2557,6 +3583,33 @@
       <c r="O38" t="n">
         <v>65.2</v>
       </c>
+      <c r="P38" t="n">
+        <v>1.6501</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2612,6 +3665,33 @@
       <c r="O39" t="n">
         <v>52.1</v>
       </c>
+      <c r="P39" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="W39" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="X39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2667,6 +3747,33 @@
       <c r="O40" t="n">
         <v>56.4</v>
       </c>
+      <c r="P40" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2722,6 +3829,33 @@
       <c r="O41" t="n">
         <v>40.7</v>
       </c>
+      <c r="P41" t="n">
+        <v>10.3818</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V41" t="n">
+        <v>11.0999</v>
+      </c>
+      <c r="W41" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="X41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2777,6 +3911,33 @@
       <c r="O42" t="n">
         <v>53.5</v>
       </c>
+      <c r="P42" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="X42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2832,6 +3993,33 @@
       <c r="O43" t="n">
         <v>53.3</v>
       </c>
+      <c r="P43" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-11.73</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2887,6 +4075,33 @@
       <c r="O44" t="n">
         <v>59.5</v>
       </c>
+      <c r="P44" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S44" t="n">
+        <v>7.8962</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-7.97</v>
+      </c>
+      <c r="V44" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="W44" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="X44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2942,6 +4157,33 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
+      <c r="P45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2997,6 +4239,33 @@
       <c r="O46" t="n">
         <v>28.1</v>
       </c>
+      <c r="P46" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="W46" t="n">
+        <v>8.5307</v>
+      </c>
+      <c r="X46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3052,6 +4321,33 @@
       <c r="O47" t="n">
         <v>68.3</v>
       </c>
+      <c r="P47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>-11.53</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="X47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3107,6 +4403,33 @@
       <c r="O48" t="n">
         <v>67.8</v>
       </c>
+      <c r="P48" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="V48" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3162,6 +4485,33 @@
       <c r="O49" t="n">
         <v>81.8</v>
       </c>
+      <c r="P49" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="V49" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="W49" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="X49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3217,6 +4567,33 @@
       <c r="O50" t="n">
         <v>42.5</v>
       </c>
+      <c r="P50" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W50" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="X50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3272,6 +4649,33 @@
       <c r="O51" t="n">
         <v>77.8</v>
       </c>
+      <c r="P51" t="n">
+        <v>3.2232</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="V51" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3327,6 +4731,33 @@
       <c r="O52" t="n">
         <v>42.8</v>
       </c>
+      <c r="P52" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="V52" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W52" t="n">
+        <v>2.9101</v>
+      </c>
+      <c r="X52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3382,6 +4813,33 @@
       <c r="O53" t="n">
         <v>41.7</v>
       </c>
+      <c r="P53" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="W53" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="X53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3437,6 +4895,33 @@
       <c r="O54" t="n">
         <v>62.7</v>
       </c>
+      <c r="P54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>-22.36</v>
+      </c>
+      <c r="V54" t="n">
+        <v>2.6884</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3492,6 +4977,33 @@
       <c r="O55" t="n">
         <v>62.2</v>
       </c>
+      <c r="P55" t="n">
+        <v>3.3923</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3547,6 +5059,33 @@
       <c r="O56" t="n">
         <v>67.90000000000001</v>
       </c>
+      <c r="P56" t="n">
+        <v>5.3817</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V56" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W56" t="n">
+        <v>4.1045</v>
+      </c>
+      <c r="X56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3602,6 +5141,33 @@
       <c r="O57" t="n">
         <v>34.1</v>
       </c>
+      <c r="P57" t="n">
+        <v>1.5901</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>-7.01</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.8976</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="V57" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3657,6 +5223,33 @@
       <c r="O58" t="n">
         <v>35</v>
       </c>
+      <c r="P58" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="V58" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W58" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3712,6 +5305,33 @@
       <c r="O59" t="n">
         <v>31.7</v>
       </c>
+      <c r="P59" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.5215</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="V59" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3767,6 +5387,33 @@
       <c r="O60" t="n">
         <v>30.8</v>
       </c>
+      <c r="P60" t="n">
+        <v>9.643700000000001</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="S60" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="V60" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="W60" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="X60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3822,6 +5469,33 @@
       <c r="O61" t="n">
         <v>36.3</v>
       </c>
+      <c r="P61" t="n">
+        <v>3.9999</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V61" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="W61" t="n">
+        <v>3.4575</v>
+      </c>
+      <c r="X61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3877,6 +5551,33 @@
       <c r="O62" t="n">
         <v>30.9</v>
       </c>
+      <c r="P62" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="V62" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W62" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3932,6 +5633,33 @@
       <c r="O63" t="n">
         <v>74.8</v>
       </c>
+      <c r="P63" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V63" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="W63" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="X63" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3987,6 +5715,33 @@
       <c r="O64" t="n">
         <v>34.2</v>
       </c>
+      <c r="P64" t="n">
+        <v>3.7117</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="V64" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="W64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4042,6 +5797,33 @@
       <c r="O65" t="n">
         <v>33.7</v>
       </c>
+      <c r="P65" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1.3797</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4101,6 +5883,33 @@
       <c r="O66" t="n">
         <v>64.3</v>
       </c>
+      <c r="P66" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="V66" t="n">
+        <v>2.2714</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4156,6 +5965,33 @@
       <c r="O67" t="n">
         <v>85.3</v>
       </c>
+      <c r="P67" t="n">
+        <v>1.6208</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="X67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4215,6 +6051,33 @@
       <c r="O68" t="n">
         <v>69.09999999999999</v>
       </c>
+      <c r="P68" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="V68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W68" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4270,6 +6133,33 @@
       <c r="O69" t="n">
         <v>80.90000000000001</v>
       </c>
+      <c r="P69" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>-13.38</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4324,6 +6214,33 @@
       </c>
       <c r="O70" t="n">
         <v>78.40000000000001</v>
+      </c>
+      <c r="P70" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="V70" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="W70" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="X70" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4337,7 +6254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA70"/>
+  <dimension ref="A1:AJ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4354,19 +6271,28 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="45" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="45" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="15" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="45" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="45" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="15" customWidth="1" min="35" max="35"/>
+    <col width="45" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4437,70 +6363,115 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>ah_close</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ah_volume</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ah_pct_move</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>last_ah_high</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>last_ah_low</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pm_open</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pm_volume</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pm_pct_move</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>has_extended_data</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>ps_ratio</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ps_vs_sector</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pb_vs_sector</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ev_ebitda</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>analyst_target</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>graham_number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>fair_value_note</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>vol_3mo_lower</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>vol_3mo_upper</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>annualized_vol</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>atr_3mo_lower</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>atr_3mo_upper</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>vol_range_note</t>
         </is>
@@ -4549,51 +6520,78 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>17.92</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>17.9x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Y2" t="n">
         <v>2.77</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2.8x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="AA2" t="n">
         <v>-3.71</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AB2" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AC2" t="n">
         <v/>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>P/S 17.9x vs 11.4x median — trading at premium | P/B 2.8x vs 1.6x median — trading at premium | EV/EBITDA -3.7x vs -1.5x median — trading at premium | Analyst target $8.22</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AE2" t="n">
         <v>1.45</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AF2" t="n">
         <v>3.23</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AG2" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AH2" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AI2" t="n">
         <v>3.44</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.45–$3.23 (ann. vol 76%) | ATR range: $1.24–$3.44</t>
         </is>
@@ -4642,51 +6640,78 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>57.11</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>57.1x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Y3" t="n">
         <v>1.18</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1.2x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="AA3" t="n">
         <v>-1.52</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AB3" t="n">
         <v/>
       </c>
-      <c r="T3" t="n">
+      <c r="AC3" t="n">
         <v/>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>P/S 57.1x vs 11.4x median — trading at premium | P/B 1.2x vs 1.6x median — trading at discount | EV/EBITDA -1.5x vs -1.5x median — in-line</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="AE3" t="n">
         <v>2.8</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AF3" t="n">
         <v>7.08</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AG3" t="n">
         <v>86.5</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AH3" t="n">
         <v>1.88</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AI3" t="n">
         <v>8</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.80–$7.08 (ann. vol 86%) | ATR range: $1.88–$8.00</t>
         </is>
@@ -4735,51 +6760,78 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
+        <v>4.7092</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.7776</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-13.74</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.05</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>1.0x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="Y4" t="n">
         <v>3.84</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>3.8x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="AA4" t="n">
         <v>-0.58</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AB4" t="n">
         <v/>
       </c>
-      <c r="T4" t="n">
+      <c r="AC4" t="n">
         <v/>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>P/S 1.0x vs 11.4x median — trading at discount | P/B 3.8x vs 1.6x median — trading at premium | EV/EBITDA -0.6x vs -1.5x median — trading at discount</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="AE4" t="n">
         <v>-8.16</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AF4" t="n">
         <v>14.58</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AG4" t="n">
         <v>708.2</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AH4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AI4" t="n">
         <v>6.55</v>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-8.16–$14.58 (ann. vol 708%) | ATR range: $-0.13–$6.55</t>
         </is>
@@ -4828,51 +6880,78 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16.3997</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-37.36</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>43.39</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="Y5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="AA5" t="n">
         <v>-0.62</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AB5" t="n">
         <v/>
       </c>
-      <c r="T5" t="n">
+      <c r="AC5" t="n">
         <v/>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="AE5" t="n">
         <v>-8.65</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AF5" t="n">
         <v>35.01</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AG5" t="n">
         <v>331.3</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AH5" t="n">
         <v>-3.72</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AI5" t="n">
         <v>30.08</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-8.65–$35.01 (ann. vol 331%) | ATR range: $-3.72–$30.08</t>
         </is>
@@ -4921,51 +7000,78 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-32.04</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>139.67</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>139.7x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="Y6" t="n">
         <v>1.71</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1.7x vs 1.6x median — in-line</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AA6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AB6" t="n">
         <v/>
       </c>
-      <c r="T6" t="n">
+      <c r="AC6" t="n">
         <v/>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>P/S 139.7x vs 11.4x median — trading at premium | P/B 1.7x vs 1.6x median — in-line | EV/EBITDA -0.2x vs -1.5x median — trading at discount</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="AE6" t="n">
         <v>0.68</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AF6" t="n">
         <v>2.42</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AG6" t="n">
         <v>111.8</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AH6" t="n">
         <v>0.31</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AI6" t="n">
         <v>2.79</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.68–$2.42 (ann. vol 112%) | ATR range: $0.31–$2.79</t>
         </is>
@@ -5014,51 +7120,78 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9236</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.2399</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>-2.48</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>-2.5x vs 7.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="Y7" t="n">
         <v>0.45</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.5x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AA7" t="n">
         <v/>
       </c>
-      <c r="S7" t="n">
+      <c r="AB7" t="n">
         <v/>
       </c>
-      <c r="T7" t="n">
+      <c r="AC7" t="n">
         <v/>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>P/S -2.5x vs 7.7x median — trading at discount | P/B 0.5x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="AE7" t="n">
         <v>-0.13</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AF7" t="n">
         <v>2.41</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AG7" t="n">
         <v>222.5</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AH7" t="n">
         <v>0.39</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AI7" t="n">
         <v>1.89</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-0.13–$2.41 (ann. vol 222%) | ATR range: $0.39–$1.89</t>
         </is>
@@ -5107,51 +7240,78 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>73.8</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>73.8x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="Y8" t="n">
         <v>-1.08</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>-1.1x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AA8" t="n">
         <v/>
       </c>
-      <c r="S8" t="n">
+      <c r="AB8" t="n">
         <v/>
       </c>
-      <c r="T8" t="n">
+      <c r="AC8" t="n">
         <v/>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>P/S 73.8x vs 11.4x median — trading at premium | P/B -1.1x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="AE8" t="n">
         <v>-23.97</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AF8" t="n">
         <v>36.37</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AG8" t="n">
         <v>973.1</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AH8" t="n">
         <v>-4.49</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AI8" t="n">
         <v>16.89</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-23.97–$36.37 (ann. vol 973%) | ATR range: $-4.49–$16.89</t>
         </is>
@@ -5200,51 +7360,78 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="R9" t="n">
+        <v>13.5543</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14.0227</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.28</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="Y9" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AA9" t="n">
         <v>4.26</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AB9" t="n">
         <v>27.22</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AC9" t="n">
         <v>15.37</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Analyst target $27.22 | Graham # $15.37</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="AE9" t="n">
         <v>10.63</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AF9" t="n">
         <v>17.41</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AG9" t="n">
         <v>48.4</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AH9" t="n">
         <v>9.34</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AI9" t="n">
         <v>18.7</v>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $10.63–$17.41 (ann. vol 48%) | ATR range: $9.34–$18.70</t>
         </is>
@@ -5293,51 +7480,78 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5215</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>62.68</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v/>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>0.0x vs -0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AA10" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AB10" t="n">
         <v/>
       </c>
-      <c r="T10" t="n">
+      <c r="AC10" t="n">
         <v/>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>P/B 0.0x vs -0.7x median — trading at discount | EV/EBITDA -0.1x vs 23.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="AE10" t="n">
         <v>-1.06</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AF10" t="n">
         <v>4.18</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AG10" t="n">
         <v>335.3</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AH10" t="n">
         <v>-1.9</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AI10" t="n">
         <v>5.02</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-1.06–$4.18 (ann. vol 335%) | ATR range: $-1.90–$5.02</t>
         </is>
@@ -5386,51 +7600,78 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10.828</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v/>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="Y11" t="n">
         <v>-16.41</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>-16.4x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="AA11" t="n">
         <v/>
       </c>
-      <c r="S11" t="n">
+      <c r="AB11" t="n">
         <v/>
       </c>
-      <c r="T11" t="n">
+      <c r="AC11" t="n">
         <v/>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>P/B -16.4x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="AE11" t="n">
         <v>9.41</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AF11" t="n">
         <v>12.19</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AG11" t="n">
         <v>25.7</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AH11" t="n">
         <v>10.59</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AI11" t="n">
         <v>11.01</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $9.41–$12.19 (ann. vol 26%) | ATR range: $10.59–$11.01</t>
         </is>
@@ -5479,51 +7720,78 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.6884</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-22.36</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>2.34</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>2.3x vs 7.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="Y12" t="n">
         <v>0.38</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>0.4x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="AA12" t="n">
         <v>-3.47</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AB12" t="n">
         <v/>
       </c>
-      <c r="T12" t="n">
+      <c r="AC12" t="n">
         <v/>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>P/S 2.3x vs 7.7x median — trading at discount | P/B 0.4x vs 0.7x median — trading at discount | EV/EBITDA -3.5x vs -5.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="AE12" t="n">
         <v>0.77</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AF12" t="n">
         <v>4.45</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AG12" t="n">
         <v>140.7</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AH12" t="n">
         <v>0.92</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AI12" t="n">
         <v>4.3</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.77–$4.45 (ann. vol 141%) | ATR range: $0.92–$4.30</t>
         </is>
@@ -5572,51 +7840,78 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.1</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>0.1x vs 0.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="Y13" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>0.1x vs 1.1x median — trading at discount</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="AA13" t="n">
         <v>-941.17</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AB13" t="n">
         <v/>
       </c>
-      <c r="T13" t="n">
+      <c r="AC13" t="n">
         <v/>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.1x vs 1.1x median — trading at discount | EV/EBITDA -941.2x vs -2.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="AE13" t="n">
         <v>1.18</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AF13" t="n">
         <v>2.46</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AG13" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AH13" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AI13" t="n">
         <v>2.56</v>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.18–$2.46 (ann. vol 70%) | ATR range: $1.08–$2.56</t>
         </is>
@@ -5665,51 +7960,78 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
+        <v>1.6208</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v/>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="Y14" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>1.1x vs 0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="AA14" t="n">
         <v/>
       </c>
-      <c r="S14" t="n">
+      <c r="AB14" t="n">
         <v>1.6</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AC14" t="n">
         <v>4.31</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>P/B 1.1x vs 0.7x median — trading at premium | Analyst target $1.60 | Graham # $4.31</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="AE14" t="n">
         <v>-0.25</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AF14" t="n">
         <v>3.09</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AG14" t="n">
         <v>234.8</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AH14" t="n">
         <v>0.53</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AI14" t="n">
         <v>2.31</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-0.25–$3.09 (ann. vol 235%) | ATR range: $0.53–$2.31</t>
         </is>
@@ -5758,51 +8080,78 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v/>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="Y15" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="AA15" t="n">
         <v/>
       </c>
-      <c r="S15" t="n">
+      <c r="AB15" t="n">
         <v>6.33</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AC15" t="n">
         <v/>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Analyst target $6.33</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="AE15" t="n">
         <v>0.82</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AF15" t="n">
         <v>4.12</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AG15" t="n">
         <v>133.9</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AH15" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AI15" t="n">
         <v>3.72</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.82–$4.12 (ann. vol 134%) | ATR range: $1.22–$3.72</t>
         </is>
@@ -5851,51 +8200,78 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
+        <v>9.643700000000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v/>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="Y16" t="n">
         <v/>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="AA16" t="n">
         <v/>
       </c>
-      <c r="S16" t="n">
+      <c r="AB16" t="n">
         <v/>
       </c>
-      <c r="T16" t="n">
+      <c r="AC16" t="n">
         <v/>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="AE16" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AF16" t="n">
         <v>10.66</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AG16" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AH16" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AI16" t="n">
         <v>11.33</v>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $8.72–$10.66 (ann. vol 20%) | ATR range: $8.05–$11.33</t>
         </is>
@@ -5944,51 +8320,78 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
+        <v>5.1599</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.5872</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v/>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="Y17" t="n">
         <v>4.55</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>4.6x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="AA17" t="n">
         <v>-4.32</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AB17" t="n">
         <v>7.67</v>
       </c>
-      <c r="T17" t="n">
+      <c r="AC17" t="n">
         <v/>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>P/B 4.6x vs 1.6x median — trading at premium | EV/EBITDA -4.3x vs -1.5x median — trading at premium | Analyst target $7.67</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="AE17" t="n">
         <v>-0.64</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AF17" t="n">
         <v>10.82</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AG17" t="n">
         <v>225.3</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AH17" t="n">
         <v>2.84</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AI17" t="n">
         <v>7.34</v>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-0.64–$10.82 (ann. vol 225%) | ATR range: $2.84–$7.34</t>
         </is>
@@ -6037,51 +8440,78 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-11.53</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>3.04</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>3.0x vs 0.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="Y18" t="n">
         <v>-1.39</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>-1.4x vs -0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="AA18" t="n">
         <v>-1.45</v>
       </c>
-      <c r="S18" t="n">
+      <c r="AB18" t="n">
         <v>1.3</v>
       </c>
-      <c r="T18" t="n">
+      <c r="AC18" t="n">
         <v/>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>P/S 3.0x vs 0.8x median — trading at premium | P/B -1.4x vs -0.7x median — trading at premium | EV/EBITDA -1.4x vs 23.7x median — trading at discount | Analyst target $1.30</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="AE18" t="n">
         <v>0.42</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AF18" t="n">
         <v>1.74</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AG18" t="n">
         <v>121.4</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AH18" t="n">
         <v>0.51</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AI18" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.42–$1.74 (ann. vol 121%) | ATR range: $0.51–$1.65</t>
         </is>
@@ -6130,51 +8560,78 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
+        <v>3.9999</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.4575</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>78.59</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>78.6x vs 7.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="Y19" t="n">
         <v>-5.06</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>-5.1x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="AA19" t="n">
         <v/>
       </c>
-      <c r="S19" t="n">
+      <c r="AB19" t="n">
         <v/>
       </c>
-      <c r="T19" t="n">
+      <c r="AC19" t="n">
         <v/>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>P/S 78.6x vs 7.7x median — trading at premium | P/B -5.1x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="AE19" t="n">
         <v>1.37</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AF19" t="n">
         <v>6.09</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AG19" t="n">
         <v>126.6</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AH19" t="n">
         <v>-0.24</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AI19" t="n">
         <v>7.7</v>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.37–$6.09 (ann. vol 127%) | ATR range: $-0.24–$7.70</t>
         </is>
@@ -6223,51 +8680,78 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
+        <v>1.5983</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.5983</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4207</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v/>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="Y20" t="n">
         <v>3.71</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>3.7x vs 2.9x median — trading at premium</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="AA20" t="n">
         <v>-16.4</v>
       </c>
-      <c r="S20" t="n">
+      <c r="AB20" t="n">
         <v/>
       </c>
-      <c r="T20" t="n">
+      <c r="AC20" t="n">
         <v/>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>P/B 3.7x vs 2.9x median — trading at premium | EV/EBITDA -16.4x vs -1.1x median — trading at premium</t>
         </is>
       </c>
-      <c r="V20" t="n">
+      <c r="AE20" t="n">
         <v>0.97</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AF20" t="n">
         <v>2.09</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AG20" t="n">
         <v>73.8</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AH20" t="n">
         <v>0.71</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AI20" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.97–$2.09 (ann. vol 74%) | ATR range: $0.71–$2.35</t>
         </is>
@@ -6316,51 +8800,78 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="R21" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="S21" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>2.09</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>2.1x vs 7.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="Y21" t="n">
         <v>1.16</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>1.2x vs 0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="AA21" t="n">
         <v/>
       </c>
-      <c r="S21" t="n">
+      <c r="AB21" t="n">
         <v>23.5</v>
       </c>
-      <c r="T21" t="n">
+      <c r="AC21" t="n">
         <v>26.59</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>P/S 2.1x vs 7.7x median — trading at discount | P/B 1.2x vs 0.7x median — trading at premium | Analyst target $23.50 | Graham # $26.59</t>
         </is>
       </c>
-      <c r="V21" t="n">
+      <c r="AE21" t="n">
         <v>17.17</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AF21" t="n">
         <v>22.61</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AG21" t="n">
         <v>27.3</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AH21" t="n">
         <v>16.01</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AI21" t="n">
         <v>23.77</v>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $17.17–$22.61 (ann. vol 27%) | ATR range: $16.01–$23.77</t>
         </is>
@@ -6409,51 +8920,78 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>4.42</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>4.4x vs 0.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="Y22" t="n">
         <v>0.44</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>0.4x vs 1.3x median — trading at discount</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="AA22" t="n">
         <v>-0.87</v>
       </c>
-      <c r="S22" t="n">
+      <c r="AB22" t="n">
         <v/>
       </c>
-      <c r="T22" t="n">
+      <c r="AC22" t="n">
         <v>255.05</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>P/S 4.4x vs 0.8x median — trading at premium | P/B 0.4x vs 1.3x median — trading at discount | EV/EBITDA -0.9x vs 2.1x median — trading at discount | Graham # $255.05</t>
         </is>
       </c>
-      <c r="V22" t="n">
+      <c r="AE22" t="n">
         <v>1.51</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AF22" t="n">
         <v>4.79</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AG22" t="n">
         <v>104</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AH22" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AI22" t="n">
         <v>4.49</v>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.51–$4.79 (ann. vol 104%) | ATR range: $1.81–$4.49</t>
         </is>
@@ -6502,51 +9040,78 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>0.1x vs 0.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="Y23" t="n">
         <v>0.73</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>0.7x vs -0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="AA23" t="n">
         <v>47.5</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="AB23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC23" t="n">
         <v/>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -0.7x median — trading at discount | EV/EBITDA 47.5x vs 23.7x median — trading at premium | Analyst target $3.64</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -0.7x median — trading at discount | EV/EBITDA 47.5x vs 23.7x median — trading at premium | Analyst target $3.65</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
         <v>1.59</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AF23" t="n">
         <v>2.77</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AG23" t="n">
         <v>54.1</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AH23" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AI23" t="n">
         <v>2.92</v>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.59–$2.77 (ann. vol 54%) | ATR range: $1.44–$2.92</t>
         </is>
@@ -6595,51 +9160,78 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v/>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P24" t="n">
+      <c r="Y24" t="n">
         <v>7.46</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>7.5x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="AA24" t="n">
         <v/>
       </c>
-      <c r="S24" t="n">
+      <c r="AB24" t="n">
         <v/>
       </c>
-      <c r="T24" t="n">
+      <c r="AC24" t="n">
         <v/>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>P/B 7.5x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="V24" t="n">
+      <c r="AE24" t="n">
         <v>1.29</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AF24" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AG24" t="n">
         <v>146.5</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AI24" t="n">
         <v>9.66</v>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.29–$8.39 (ann. vol 146%) | ATR range: $0.02–$9.66</t>
         </is>
@@ -6688,51 +9280,78 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
+        <v>3.681</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.18</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>0.2x vs 0.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="Y25" t="n">
         <v>1.33</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>1.3x vs 1.3x median — in-line</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="AA25" t="n">
         <v>-115.99</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AB25" t="n">
         <v/>
       </c>
-      <c r="T25" t="n">
+      <c r="AC25" t="n">
         <v/>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>P/S 0.2x vs 0.8x median — trading at discount | P/B 1.3x vs 1.3x median — in-line | EV/EBITDA -116.0x vs 2.1x median — trading at discount</t>
         </is>
       </c>
-      <c r="V25" t="n">
+      <c r="AE25" t="n">
         <v>2.36</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AF25" t="n">
         <v>5</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AG25" t="n">
         <v>71.8</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AH25" t="n">
         <v>0.45</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AI25" t="n">
         <v>6.91</v>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.36–$5.00 (ann. vol 72%) | ATR range: $0.45–$6.91</t>
         </is>
@@ -6781,51 +9400,78 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>0.77</v>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0.8x vs 0.8x median — in-line</t>
         </is>
       </c>
-      <c r="P26" t="n">
+      <c r="Y26" t="n">
         <v>-4.1</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>-4.1x vs -0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="AA26" t="n">
         <v>74.33</v>
       </c>
-      <c r="S26" t="n">
+      <c r="AB26" t="n">
         <v>4.75</v>
       </c>
-      <c r="T26" t="n">
+      <c r="AC26" t="n">
         <v/>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>P/S 0.8x vs 0.8x median — in-line | P/B -4.1x vs -0.7x median — trading at premium | EV/EBITDA 74.3x vs 23.7x median — trading at premium | Analyst target $4.75</t>
         </is>
       </c>
-      <c r="V26" t="n">
+      <c r="AE26" t="n">
         <v>2.33</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AF26" t="n">
         <v>6.09</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AG26" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AH26" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AI26" t="n">
         <v>7.21</v>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.33–$6.09 (ann. vol 89%) | ATR range: $1.21–$7.21</t>
         </is>
@@ -6874,51 +9520,78 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>4.45</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>4.4x vs 7.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="Y27" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>0.5x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="AA27" t="n">
         <v>-7.74</v>
       </c>
-      <c r="S27" t="n">
+      <c r="AB27" t="n">
         <v>12</v>
       </c>
-      <c r="T27" t="n">
+      <c r="AC27" t="n">
         <v/>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>P/S 4.4x vs 7.7x median — trading at discount | P/B 0.5x vs 0.7x median — trading at discount | EV/EBITDA -7.7x vs -5.6x median — trading at premium | Analyst target $12.00</t>
         </is>
       </c>
-      <c r="V27" t="n">
+      <c r="AE27" t="n">
         <v>1.24</v>
       </c>
-      <c r="W27" t="n">
+      <c r="AF27" t="n">
         <v>12.88</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AG27" t="n">
         <v>164.7</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AH27" t="n">
         <v>3.65</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AI27" t="n">
         <v>10.47</v>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.24–$12.88 (ann. vol 165%) | ATR range: $3.65–$10.47</t>
         </is>
@@ -6967,51 +9640,78 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>4.04</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>4.0x vs 7.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="P28" t="n">
+      <c r="Y28" t="n">
         <v>0.96</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>1.0x vs 0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="AA28" t="n">
         <v>-17.85</v>
       </c>
-      <c r="S28" t="n">
+      <c r="AB28" t="n">
         <v/>
       </c>
-      <c r="T28" t="n">
+      <c r="AC28" t="n">
         <v/>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>P/S 4.0x vs 7.7x median — trading at discount | P/B 1.0x vs 0.7x median — trading at premium | EV/EBITDA -17.9x vs -5.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="V28" t="n">
+      <c r="AE28" t="n">
         <v>0.79</v>
       </c>
-      <c r="W28" t="n">
+      <c r="AF28" t="n">
         <v>1.91</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AG28" t="n">
         <v>83.2</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AH28" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AI28" t="n">
         <v>2.03</v>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.79–$1.91 (ann. vol 83%) | ATR range: $0.67–$2.03</t>
         </is>
@@ -7060,51 +9760,78 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
+        <v>1.5901</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-7.01</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.8976</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>4.14</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>4.1x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P29" t="n">
+      <c r="Y29" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>0.1x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="AA29" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="S29" t="n">
+      <c r="AB29" t="n">
         <v/>
       </c>
-      <c r="T29" t="n">
+      <c r="AC29" t="n">
         <v/>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>P/S 4.1x vs 11.4x median — trading at discount | P/B 0.1x vs 1.6x median — trading at discount | EV/EBITDA -0.1x vs -1.5x median — trading at discount</t>
         </is>
       </c>
-      <c r="V29" t="n">
+      <c r="AE29" t="n">
         <v>0.29</v>
       </c>
-      <c r="W29" t="n">
+      <c r="AF29" t="n">
         <v>3.09</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AG29" t="n">
         <v>165.7</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AH29" t="n">
         <v>-0.37</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AI29" t="n">
         <v>3.75</v>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.29–$3.09 (ann. vol 166%) | ATR range: $-0.37–$3.75</t>
         </is>
@@ -7153,51 +9880,78 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-13.38</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.31</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>1.3x vs 0.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="P30" t="n">
+      <c r="Y30" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>1.7x vs 1.1x median — trading at premium</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="AA30" t="n">
         <v>-2.62</v>
       </c>
-      <c r="S30" t="n">
+      <c r="AB30" t="n">
         <v>2.5</v>
       </c>
-      <c r="T30" t="n">
+      <c r="AC30" t="n">
         <v/>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>P/S 1.3x vs 0.8x median — trading at premium | P/B 1.7x vs 1.1x median — trading at premium | EV/EBITDA -2.6x vs -2.8x median — in-line | Analyst target $2.50</t>
         </is>
       </c>
-      <c r="V30" t="n">
+      <c r="AE30" t="n">
         <v>0.91</v>
       </c>
-      <c r="W30" t="n">
+      <c r="AF30" t="n">
         <v>2.23</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AG30" t="n">
         <v>83.90000000000001</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AH30" t="n">
         <v>0.84</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AI30" t="n">
         <v>2.3</v>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.91–$2.23 (ann. vol 84%) | ATR range: $0.84–$2.30</t>
         </is>
@@ -7246,51 +10000,78 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.2714</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>2209.24</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>2209.2x vs 7.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="P31" t="n">
+      <c r="Y31" t="n">
         <v>0.57</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>0.6x vs 0.7x median — in-line</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="AA31" t="n">
         <v/>
       </c>
-      <c r="S31" t="n">
+      <c r="AB31" t="n">
         <v/>
       </c>
-      <c r="T31" t="n">
+      <c r="AC31" t="n">
         <v/>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>P/S 2209.2x vs 7.7x median — trading at premium | P/B 0.6x vs 0.7x median — in-line</t>
         </is>
       </c>
-      <c r="V31" t="n">
+      <c r="AE31" t="n">
         <v>1.05</v>
       </c>
-      <c r="W31" t="n">
+      <c r="AF31" t="n">
         <v>3.25</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AG31" t="n">
         <v>102.6</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AH31" t="n">
         <v>0.92</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AI31" t="n">
         <v>3.38</v>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.05–$3.25 (ann. vol 103%) | ATR range: $0.92–$3.38</t>
         </is>
@@ -7339,51 +10120,78 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="R32" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15.517</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.97</v>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="P32" t="n">
+      <c r="Y32" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="AA32" t="n">
         <v>10.52</v>
       </c>
-      <c r="S32" t="n">
+      <c r="AB32" t="n">
         <v>20.3</v>
       </c>
-      <c r="T32" t="n">
+      <c r="AC32" t="n">
         <v>16.56</v>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>Analyst target $20.30 | Graham # $16.56</t>
         </is>
       </c>
-      <c r="V32" t="n">
+      <c r="AE32" t="n">
         <v>13.11</v>
       </c>
-      <c r="W32" t="n">
+      <c r="AF32" t="n">
         <v>18.95</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AG32" t="n">
         <v>36.4</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AH32" t="n">
         <v>10.93</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AI32" t="n">
         <v>21.13</v>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $13.11–$18.95 (ann. vol 36%) | ATR range: $10.93–$21.13</t>
         </is>
@@ -7432,51 +10240,78 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7.8962</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-7.97</v>
+      </c>
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>0.35</v>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>0.3x vs 0.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="P33" t="n">
+      <c r="Y33" t="n">
         <v>1.09</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>1.1x vs 1.1x median — in-line</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="AA33" t="n">
         <v>-2.84</v>
       </c>
-      <c r="S33" t="n">
+      <c r="AB33" t="n">
         <v>12</v>
       </c>
-      <c r="T33" t="n">
+      <c r="AC33" t="n">
         <v/>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>P/S 0.3x vs 0.8x median — trading at discount | P/B 1.1x vs 1.1x median — in-line | EV/EBITDA -2.8x vs -2.8x median — in-line | Analyst target $12.00</t>
         </is>
       </c>
-      <c r="V33" t="n">
+      <c r="AE33" t="n">
         <v>3.06</v>
       </c>
-      <c r="W33" t="n">
+      <c r="AF33" t="n">
         <v>14.12</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AG33" t="n">
         <v>128.8</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AH33" t="n">
         <v>3.6</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AI33" t="n">
         <v>13.58</v>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $3.06–$14.12 (ann. vol 129%) | ATR range: $3.60–$13.58</t>
         </is>
@@ -7525,51 +10360,78 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
+        <v>8.321099999999999</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="R34" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="S34" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>5.64</v>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>5.6x vs 2.1x median — trading at premium</t>
         </is>
       </c>
-      <c r="P34" t="n">
+      <c r="Y34" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>0.8x vs 0.8x median — in-line</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="AA34" t="n">
         <v/>
       </c>
-      <c r="S34" t="n">
+      <c r="AB34" t="n">
         <v>10.55</v>
       </c>
-      <c r="T34" t="n">
+      <c r="AC34" t="n">
         <v>12.99</v>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>P/S 5.6x vs 2.1x median — trading at premium | P/B 0.8x vs 0.8x median — in-line | Analyst target $10.55 | Graham # $12.99</t>
         </is>
       </c>
-      <c r="V34" t="n">
+      <c r="AE34" t="n">
         <v>7.3</v>
       </c>
-      <c r="W34" t="n">
+      <c r="AF34" t="n">
         <v>9.18</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AG34" t="n">
         <v>22.8</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AH34" t="n">
         <v>6.52</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AI34" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $7.30–$9.18 (ann. vol 23%) | ATR range: $6.52–$9.96</t>
         </is>
@@ -7618,51 +10480,78 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>8.09</v>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>8.1x vs 7.7x median — in-line</t>
         </is>
       </c>
-      <c r="P35" t="n">
+      <c r="Y35" t="n">
         <v>-10</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>-10.0x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="AA35" t="n">
         <v>-1.86</v>
       </c>
-      <c r="S35" t="n">
+      <c r="AB35" t="n">
         <v>5.85</v>
       </c>
-      <c r="T35" t="n">
+      <c r="AC35" t="n">
         <v/>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>P/S 8.1x vs 7.7x median — in-line | P/B -10.0x vs 0.7x median — trading at discount | EV/EBITDA -1.9x vs -5.6x median — trading at discount | Analyst target $5.85</t>
         </is>
       </c>
-      <c r="V35" t="n">
+      <c r="AE35" t="n">
         <v>1.77</v>
       </c>
-      <c r="W35" t="n">
+      <c r="AF35" t="n">
         <v>6.11</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AG35" t="n">
         <v>110</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AH35" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AI35" t="n">
         <v>5.98</v>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.77–$6.11 (ann. vol 110%) | ATR range: $1.90–$5.98</t>
         </is>
@@ -7711,51 +10600,78 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="R36" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>7.3</v>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>7.3x vs 7.7x median — in-line</t>
         </is>
       </c>
-      <c r="P36" t="n">
+      <c r="Y36" t="n">
         <v>0.89</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>0.9x vs 0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="AA36" t="n">
         <v/>
       </c>
-      <c r="S36" t="n">
+      <c r="AB36" t="n">
         <v/>
       </c>
-      <c r="T36" t="n">
+      <c r="AC36" t="n">
         <v>11.67</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>P/S 7.3x vs 7.7x median — in-line | P/B 0.9x vs 0.7x median — trading at premium | Graham # $11.67</t>
         </is>
       </c>
-      <c r="V36" t="n">
+      <c r="AE36" t="n">
         <v>10.2</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AF36" t="n">
         <v>11.04</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AG36" t="n">
         <v>7.9</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AH36" t="n">
         <v>9.76</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AI36" t="n">
         <v>11.48</v>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $10.20–$11.04 (ann. vol 8%) | ATR range: $9.76–$11.48</t>
         </is>
@@ -7804,51 +10720,78 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="R37" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v/>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P37" t="n">
+      <c r="Y37" t="n">
         <v>-47.07</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>-47.1x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="AA37" t="n">
         <v/>
       </c>
-      <c r="S37" t="n">
+      <c r="AB37" t="n">
         <v/>
       </c>
-      <c r="T37" t="n">
+      <c r="AC37" t="n">
         <v/>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>P/B -47.1x vs 0.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="V37" t="n">
+      <c r="AE37" t="n">
         <v>10.35</v>
       </c>
-      <c r="W37" t="n">
+      <c r="AF37" t="n">
         <v>11.02</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AG37" t="n">
         <v>6.3</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AH37" t="n">
         <v>10.17</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AI37" t="n">
         <v>11.2</v>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $10.35–$11.02 (ann. vol 6%) | ATR range: $10.17–$11.20</t>
         </is>
@@ -7897,51 +10840,78 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
+        <v>3.3923</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>35.28</v>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>35.3x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P38" t="n">
+      <c r="Y38" t="n">
         <v>0.48</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>0.5x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="AA38" t="n">
         <v/>
       </c>
-      <c r="S38" t="n">
+      <c r="AB38" t="n">
         <v>7.2</v>
       </c>
-      <c r="T38" t="n">
+      <c r="AC38" t="n">
         <v/>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>P/S 35.3x vs 11.4x median — trading at premium | P/B 0.5x vs 1.6x median — trading at discount | Analyst target $7.20</t>
         </is>
       </c>
-      <c r="V38" t="n">
+      <c r="AE38" t="n">
         <v>1.23</v>
       </c>
-      <c r="W38" t="n">
+      <c r="AF38" t="n">
         <v>5.13</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AG38" t="n">
         <v>122.8</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AH38" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AI38" t="n">
         <v>4.97</v>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AJ38" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.23–$5.13 (ann. vol 123%) | ATR range: $1.39–$4.97</t>
         </is>
@@ -7990,51 +10960,78 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="R39" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>2.51</v>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="P39" t="n">
+      <c r="Y39" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="AA39" t="n">
         <v>6.82</v>
       </c>
-      <c r="S39" t="n">
+      <c r="AB39" t="n">
         <v/>
       </c>
-      <c r="T39" t="n">
+      <c r="AC39" t="n">
         <v/>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="V39" t="n">
+      <c r="AE39" t="n">
         <v>4.51</v>
       </c>
-      <c r="W39" t="n">
+      <c r="AF39" t="n">
         <v>6.69</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AG39" t="n">
         <v>39</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AH39" t="n">
         <v>3.81</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AI39" t="n">
         <v>7.39</v>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AJ39" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $4.51–$6.69 (ann. vol 39%) | ATR range: $3.81–$7.39</t>
         </is>
@@ -8083,51 +11080,78 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
+        <v>3.7117</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v/>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P40" t="n">
+      <c r="Y40" t="n">
         <v/>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="AA40" t="n">
         <v>-19.66</v>
       </c>
-      <c r="S40" t="n">
+      <c r="AB40" t="n">
         <v/>
       </c>
-      <c r="T40" t="n">
+      <c r="AC40" t="n">
         <v/>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>EV/EBITDA -19.7x vs -2.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="V40" t="n">
+      <c r="AE40" t="n">
         <v>1.8</v>
       </c>
-      <c r="W40" t="n">
+      <c r="AF40" t="n">
         <v>5.5</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AG40" t="n">
         <v>101.4</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AH40" t="n">
         <v>0.17</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AI40" t="n">
         <v>7.13</v>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.80–$5.50 (ann. vol 101%) | ATR range: $0.17–$7.13</t>
         </is>
@@ -8176,51 +11200,78 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8.5307</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.12</v>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>1.1x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P41" t="n">
+      <c r="Y41" t="n">
         <v>2.34</v>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2.3x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="AA41" t="n">
         <v>6.09</v>
       </c>
-      <c r="S41" t="n">
+      <c r="AB41" t="n">
         <v>11</v>
       </c>
-      <c r="T41" t="n">
+      <c r="AC41" t="n">
         <v>5.53</v>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>P/S 1.1x vs 11.4x median — trading at discount | P/B 2.3x vs 1.6x median — trading at premium | EV/EBITDA 6.1x vs -1.5x median — trading at discount | Analyst target $11.00 | Graham # $5.53</t>
         </is>
       </c>
-      <c r="V41" t="n">
+      <c r="AE41" t="n">
         <v>7.02</v>
       </c>
-      <c r="W41" t="n">
+      <c r="AF41" t="n">
         <v>10.68</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AG41" t="n">
         <v>41.2</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AH41" t="n">
         <v>5.13</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AI41" t="n">
         <v>12.57</v>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AJ41" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $7.02–$10.68 (ann. vol 41%) | ATR range: $5.13–$12.57</t>
         </is>
@@ -8269,51 +11320,78 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.1799</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.1196</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>38.68</v>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>38.7x vs 7.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="P42" t="n">
+      <c r="Y42" t="n">
         <v>1.09</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>1.1x vs 0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="AA42" t="n">
         <v/>
       </c>
-      <c r="S42" t="n">
+      <c r="AB42" t="n">
         <v/>
       </c>
-      <c r="T42" t="n">
+      <c r="AC42" t="n">
         <v>10.33</v>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>P/S 38.7x vs 7.7x median — trading at premium | P/B 1.1x vs 0.7x median — trading at premium | Graham # $10.33</t>
         </is>
       </c>
-      <c r="V42" t="n">
+      <c r="AE42" t="n">
         <v>3.79</v>
       </c>
-      <c r="W42" t="n">
+      <c r="AF42" t="n">
         <v>4.47</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AG42" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AH42" t="n">
         <v>3.75</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AI42" t="n">
         <v>4.51</v>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $3.79–$4.47 (ann. vol 16%) | ATR range: $3.75–$4.51</t>
         </is>
@@ -8362,51 +11440,78 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>8.18</v>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>8.2x vs 7.7x median — in-line</t>
         </is>
       </c>
-      <c r="P43" t="n">
+      <c r="Y43" t="n">
         <v>0.88</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>0.9x vs 0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R43" t="n">
+      <c r="AA43" t="n">
         <v/>
       </c>
-      <c r="S43" t="n">
+      <c r="AB43" t="n">
         <v/>
       </c>
-      <c r="T43" t="n">
+      <c r="AC43" t="n">
         <v>3.2</v>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>P/S 8.2x vs 7.7x median — in-line | P/B 0.9x vs 0.7x median — trading at premium | Graham # $3.20</t>
         </is>
       </c>
-      <c r="V43" t="n">
+      <c r="AE43" t="n">
         <v>2.21</v>
       </c>
-      <c r="W43" t="n">
+      <c r="AF43" t="n">
         <v>2.49</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AG43" t="n">
         <v>12</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AH43" t="n">
         <v>2.14</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AI43" t="n">
         <v>2.56</v>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AJ43" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.21–$2.49 (ann. vol 12%) | ATR range: $2.14–$2.56</t>
         </is>
@@ -8455,51 +11560,78 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>-9.57</v>
+      </c>
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>3.2</v>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>3.2x vs 1.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="P44" t="n">
+      <c r="Y44" t="n">
         <v>14.84</v>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>14.8x vs 2.9x median — trading at premium</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="AA44" t="n">
         <v>19.71</v>
       </c>
-      <c r="S44" t="n">
+      <c r="AB44" t="n">
         <v>6.25</v>
       </c>
-      <c r="T44" t="n">
+      <c r="AC44" t="n">
         <v/>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>P/S 3.2x vs 1.7x median — trading at premium | P/B 14.8x vs 2.9x median — trading at premium | EV/EBITDA 19.7x vs -1.1x median — trading at discount | Analyst target $6.25</t>
         </is>
       </c>
-      <c r="V44" t="n">
+      <c r="AE44" t="n">
         <v>1.46</v>
       </c>
-      <c r="W44" t="n">
+      <c r="AF44" t="n">
         <v>4.18</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AG44" t="n">
         <v>96.7</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AH44" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AI44" t="n">
         <v>4.49</v>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AJ44" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.46–$4.18 (ann. vol 97%) | ATR range: $1.15–$4.49</t>
         </is>
@@ -8548,51 +11680,78 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>3.59</v>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>3.6x vs 0.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="P45" t="n">
+      <c r="Y45" t="n">
         <v>-7.67</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>-7.7x vs 1.1x median — trading at discount</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="AA45" t="n">
         <v>0.42</v>
       </c>
-      <c r="S45" t="n">
+      <c r="AB45" t="n">
         <v/>
       </c>
-      <c r="T45" t="n">
+      <c r="AC45" t="n">
         <v/>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>P/S 3.6x vs 0.8x median — trading at premium | P/B -7.7x vs 1.1x median — trading at discount | EV/EBITDA 0.4x vs -2.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="V45" t="n">
+      <c r="AE45" t="n">
         <v>-0.08</v>
       </c>
-      <c r="W45" t="n">
+      <c r="AF45" t="n">
         <v>8.9</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AG45" t="n">
         <v>203.8</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AH45" t="n">
         <v>-4.07</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AI45" t="n">
         <v>12.89</v>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AJ45" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-0.08–$8.90 (ann. vol 204%) | ATR range: $-4.07–$12.89</t>
         </is>
@@ -8641,51 +11800,78 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
+        <v>2.8301</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="V46" t="b">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>16.47</v>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>16.5x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P46" t="n">
+      <c r="Y46" t="n">
         <v>6.55</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>6.6x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="AA46" t="n">
         <v>-5.11</v>
       </c>
-      <c r="S46" t="n">
+      <c r="AB46" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="T46" t="n">
+      <c r="AC46" t="n">
         <v/>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>P/S 16.5x vs 11.4x median — trading at premium | P/B 6.6x vs 1.6x median — trading at premium | EV/EBITDA -5.1x vs -1.5x median — trading at premium | Analyst target $8.61</t>
         </is>
       </c>
-      <c r="V46" t="n">
+      <c r="AE46" t="n">
         <v>1.81</v>
       </c>
-      <c r="W46" t="n">
+      <c r="AF46" t="n">
         <v>3.99</v>
       </c>
-      <c r="X46" t="n">
+      <c r="AG46" t="n">
         <v>75.5</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AH46" t="n">
         <v>1.76</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AI46" t="n">
         <v>4.04</v>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AJ46" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.81–$3.99 (ann. vol 76%) | ATR range: $1.76–$4.04</t>
         </is>
@@ -8734,51 +11920,78 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
+        <v>5.3817</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4.1045</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V47" t="b">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>7.15</v>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="P47" t="n">
+      <c r="Y47" t="n">
         <v>0.71</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="AA47" t="n">
         <v>47.67</v>
       </c>
-      <c r="S47" t="n">
+      <c r="AB47" t="n">
         <v>7.83</v>
       </c>
-      <c r="T47" t="n">
+      <c r="AC47" t="n">
         <v/>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>Analyst target $7.83</t>
         </is>
       </c>
-      <c r="V47" t="n">
+      <c r="AE47" t="n">
         <v>2.18</v>
       </c>
-      <c r="W47" t="n">
+      <c r="AF47" t="n">
         <v>8.1</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AG47" t="n">
         <v>115</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AH47" t="n">
         <v>2.77</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AI47" t="n">
         <v>7.51</v>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AJ47" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.18–$8.10 (ann. vol 115%) | ATR range: $2.77–$7.51</t>
         </is>
@@ -8827,51 +12040,78 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="R48" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="V48" t="b">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v/>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P48" t="n">
+      <c r="Y48" t="n">
         <v>1.03</v>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>1.0x vs 0.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="AA48" t="n">
         <v/>
       </c>
-      <c r="S48" t="n">
+      <c r="AB48" t="n">
         <v/>
       </c>
-      <c r="T48" t="n">
+      <c r="AC48" t="n">
         <v>15.78</v>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>P/B 1.0x vs 0.7x median — trading at premium | Graham # $15.78</t>
         </is>
       </c>
-      <c r="V48" t="n">
+      <c r="AE48" t="n">
         <v>4.99</v>
       </c>
-      <c r="W48" t="n">
+      <c r="AF48" t="n">
         <v>6.37</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AG48" t="n">
         <v>24.4</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AH48" t="n">
         <v>4.85</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AI48" t="n">
         <v>6.51</v>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AJ48" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $4.99–$6.37 (ann. vol 24%) | ATR range: $4.85–$6.51</t>
         </is>
@@ -8920,51 +12160,78 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
         <v>0.6</v>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="V49" t="b">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X49" t="inlineStr">
         <is>
           <t>0.6x vs 2.1x median — trading at discount</t>
         </is>
       </c>
-      <c r="P49" t="n">
+      <c r="Y49" t="n">
         <v>0.16</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>0.2x vs 0.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="AA49" t="n">
         <v>10.47</v>
       </c>
-      <c r="S49" t="n">
+      <c r="AB49" t="n">
         <v/>
       </c>
-      <c r="T49" t="n">
+      <c r="AC49" t="n">
         <v/>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>P/S 0.6x vs 2.1x median — trading at discount | P/B 0.2x vs 0.8x median — trading at discount | EV/EBITDA 10.5x vs 1.0x median — trading at premium</t>
         </is>
       </c>
-      <c r="V49" t="n">
+      <c r="AE49" t="n">
         <v>1.21</v>
       </c>
-      <c r="W49" t="n">
+      <c r="AF49" t="n">
         <v>2.11</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AG49" t="n">
         <v>54.6</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AH49" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AI49" t="n">
         <v>1.88</v>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AJ49" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.21–$2.11 (ann. vol 55%) | ATR range: $1.44–$1.88</t>
         </is>
@@ -9013,51 +12280,78 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V50" t="b">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>16.76</v>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>16.8x vs 7.7x median — trading at premium</t>
         </is>
       </c>
-      <c r="P50" t="n">
+      <c r="Y50" t="n">
         <v>0.85</v>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>0.9x vs 0.7x median — in-line</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="AA50" t="n">
         <v/>
       </c>
-      <c r="S50" t="n">
+      <c r="AB50" t="n">
         <v/>
       </c>
-      <c r="T50" t="n">
+      <c r="AC50" t="n">
         <v>6.87</v>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>P/S 16.8x vs 7.7x median — trading at premium | P/B 0.9x vs 0.7x median — in-line | Graham # $6.87</t>
         </is>
       </c>
-      <c r="V50" t="n">
+      <c r="AE50" t="n">
         <v>4.17</v>
       </c>
-      <c r="W50" t="n">
+      <c r="AF50" t="n">
         <v>4.55</v>
       </c>
-      <c r="X50" t="n">
+      <c r="AG50" t="n">
         <v>8.5</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AH50" t="n">
         <v>4.13</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AI50" t="n">
         <v>4.59</v>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AJ50" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $4.17–$4.55 (ann. vol 8%) | ATR range: $4.13–$4.59</t>
         </is>
@@ -9106,51 +12400,78 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>8</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="S51" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="V51" t="b">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.36</v>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>0.4x vs 0.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="P51" t="n">
+      <c r="Y51" t="n">
         <v>1.19</v>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>1.2x vs 1.3x median — in-line</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="AA51" t="n">
         <v>5.08</v>
       </c>
-      <c r="S51" t="n">
+      <c r="AB51" t="n">
         <v/>
       </c>
-      <c r="T51" t="n">
+      <c r="AC51" t="n">
         <v>11.88</v>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>P/S 0.4x vs 0.8x median — trading at discount | P/B 1.2x vs 1.3x median — in-line | EV/EBITDA 5.1x vs 2.1x median — trading at premium | Graham # $11.88</t>
         </is>
       </c>
-      <c r="V51" t="n">
+      <c r="AE51" t="n">
         <v>6.1</v>
       </c>
-      <c r="W51" t="n">
+      <c r="AF51" t="n">
         <v>9.84</v>
       </c>
-      <c r="X51" t="n">
+      <c r="AG51" t="n">
         <v>46.8</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="AH51" t="n">
         <v>4.85</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AI51" t="n">
         <v>11.09</v>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AJ51" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $6.10–$9.84 (ann. vol 47%) | ATR range: $4.85–$11.09</t>
         </is>
@@ -9199,51 +12520,78 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="V52" t="b">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>7.02</v>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>7.0x vs 0.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="P52" t="n">
+      <c r="Y52" t="n">
         <v>2.03</v>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>2.0x vs 1.1x median — trading at premium</t>
         </is>
       </c>
-      <c r="R52" t="n">
+      <c r="AA52" t="n">
         <v>-2.85</v>
       </c>
-      <c r="S52" t="n">
+      <c r="AB52" t="n">
         <v/>
       </c>
-      <c r="T52" t="n">
+      <c r="AC52" t="n">
         <v/>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>P/S 7.0x vs 0.8x median — trading at premium | P/B 2.0x vs 1.1x median — trading at premium | EV/EBITDA -2.9x vs -2.8x median — in-line</t>
         </is>
       </c>
-      <c r="V52" t="n">
+      <c r="AE52" t="n">
         <v>0.46</v>
       </c>
-      <c r="W52" t="n">
+      <c r="AF52" t="n">
         <v>1.56</v>
       </c>
-      <c r="X52" t="n">
+      <c r="AG52" t="n">
         <v>109.4</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AH52" t="n">
         <v>0.13</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AI52" t="n">
         <v>1.89</v>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.46–$1.56 (ann. vol 109%) | ATR range: $0.13–$1.89</t>
         </is>
@@ -9292,51 +12640,78 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.3326</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>-7.14</v>
+      </c>
+      <c r="V53" t="b">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v/>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P53" t="n">
+      <c r="Y53" t="n">
         <v>0.66</v>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>0.7x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R53" t="n">
+      <c r="AA53" t="n">
         <v>-0.72</v>
       </c>
-      <c r="S53" t="n">
+      <c r="AB53" t="n">
         <v>10.83</v>
       </c>
-      <c r="T53" t="n">
+      <c r="AC53" t="n">
         <v/>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>P/B 0.7x vs 1.6x median — trading at discount | EV/EBITDA -0.7x vs -1.5x median — trading at discount | Analyst target $10.83</t>
         </is>
       </c>
-      <c r="V53" t="n">
+      <c r="AE53" t="n">
         <v>1.69</v>
       </c>
-      <c r="W53" t="n">
+      <c r="AF53" t="n">
         <v>3.63</v>
       </c>
-      <c r="X53" t="n">
+      <c r="AG53" t="n">
         <v>73.3</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AH53" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AI53" t="n">
         <v>3.92</v>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.69–$3.63 (ann. vol 73%) | ATR range: $1.40–$3.92</t>
         </is>
@@ -9385,51 +12760,78 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
+        <v>3.2232</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="V54" t="b">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v/>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P54" t="n">
+      <c r="Y54" t="n">
         <v>3.99</v>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>4.0x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R54" t="n">
+      <c r="AA54" t="n">
         <v>-1.42</v>
       </c>
-      <c r="S54" t="n">
+      <c r="AB54" t="n">
         <v>7.4</v>
       </c>
-      <c r="T54" t="n">
+      <c r="AC54" t="n">
         <v/>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>P/B 4.0x vs 1.6x median — trading at premium | EV/EBITDA -1.4x vs -1.5x median — in-line | Analyst target $7.40</t>
         </is>
       </c>
-      <c r="V54" t="n">
+      <c r="AE54" t="n">
         <v>1.85</v>
       </c>
-      <c r="W54" t="n">
+      <c r="AF54" t="n">
         <v>4.47</v>
       </c>
-      <c r="X54" t="n">
+      <c r="AG54" t="n">
         <v>82.7</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AH54" t="n">
         <v>1.84</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AI54" t="n">
         <v>4.48</v>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.85–$4.47 (ann. vol 83%) | ATR range: $1.84–$4.48</t>
         </is>
@@ -9478,51 +12880,78 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="R55" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="S55" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="V55" t="b">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>6.01</v>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>6.0x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P55" t="n">
+      <c r="Y55" t="n">
         <v>3.88</v>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>3.9x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R55" t="n">
+      <c r="AA55" t="n">
         <v>-7.15</v>
       </c>
-      <c r="S55" t="n">
+      <c r="AB55" t="n">
         <v>21.17</v>
       </c>
-      <c r="T55" t="n">
+      <c r="AC55" t="n">
         <v/>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>P/S 6.0x vs 11.4x median — trading at discount | P/B 3.9x vs 1.6x median — trading at premium | EV/EBITDA -7.2x vs -1.5x median — trading at premium | Analyst target $21.17</t>
         </is>
       </c>
-      <c r="V55" t="n">
+      <c r="AE55" t="n">
         <v>7.6</v>
       </c>
-      <c r="W55" t="n">
+      <c r="AF55" t="n">
         <v>19.34</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AG55" t="n">
         <v>87.2</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AH55" t="n">
         <v>8.81</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AI55" t="n">
         <v>18.13</v>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $7.60–$19.34 (ann. vol 87%) | ATR range: $8.81–$18.13</t>
         </is>
@@ -9571,51 +13000,78 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>8</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6.451</v>
+      </c>
+      <c r="S56" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="b">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>11.43</v>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>11.4x vs 11.4x median — in-line</t>
         </is>
       </c>
-      <c r="P56" t="n">
+      <c r="Y56" t="n">
         <v>-5.12</v>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>-5.1x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R56" t="n">
+      <c r="AA56" t="n">
         <v>-4.45</v>
       </c>
-      <c r="S56" t="n">
+      <c r="AB56" t="n">
         <v>11.44</v>
       </c>
-      <c r="T56" t="n">
+      <c r="AC56" t="n">
         <v/>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>P/S 11.4x vs 11.4x median — in-line | P/B -5.1x vs 1.6x median — trading at discount | EV/EBITDA -4.5x vs -1.5x median — trading at premium | Analyst target $11.44</t>
         </is>
       </c>
-      <c r="V56" t="n">
+      <c r="AE56" t="n">
         <v>4.42</v>
       </c>
-      <c r="W56" t="n">
+      <c r="AF56" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="X56" t="n">
+      <c r="AG56" t="n">
         <v>74.8</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AH56" t="n">
         <v>3.1</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AI56" t="n">
         <v>11.04</v>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AJ56" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $4.42–$9.72 (ann. vol 75%) | ATR range: $3.10–$11.04</t>
         </is>
@@ -9664,51 +13120,78 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
+        <v>1.6501</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="V57" t="b">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v/>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P57" t="n">
+      <c r="Y57" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>2.9x vs 2.9x median — in-line</t>
         </is>
       </c>
-      <c r="R57" t="n">
+      <c r="AA57" t="n">
         <v>-37.25</v>
       </c>
-      <c r="S57" t="n">
+      <c r="AB57" t="n">
         <v/>
       </c>
-      <c r="T57" t="n">
+      <c r="AC57" t="n">
         <v/>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>P/B 2.9x vs 2.9x median — in-line | EV/EBITDA -37.2x vs -1.1x median — trading at premium</t>
         </is>
       </c>
-      <c r="V57" t="n">
+      <c r="AE57" t="n">
         <v>0.96</v>
       </c>
-      <c r="W57" t="n">
+      <c r="AF57" t="n">
         <v>2.32</v>
       </c>
-      <c r="X57" t="n">
+      <c r="AG57" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AH57" t="n">
         <v>0.86</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AI57" t="n">
         <v>2.42</v>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.96–$2.32 (ann. vol 83%) | ATR range: $0.86–$2.42</t>
         </is>
@@ -9757,51 +13240,78 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2.9101</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="V58" t="b">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>4.07</v>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>4.1x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P58" t="n">
+      <c r="Y58" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>1.3x vs 1.6x median — in-line</t>
         </is>
       </c>
-      <c r="R58" t="n">
+      <c r="AA58" t="n">
         <v>-9.6</v>
       </c>
-      <c r="S58" t="n">
+      <c r="AB58" t="n">
         <v/>
       </c>
-      <c r="T58" t="n">
+      <c r="AC58" t="n">
         <v/>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>P/S 4.1x vs 11.4x median — trading at discount | P/B 1.3x vs 1.6x median — in-line | EV/EBITDA -9.6x vs -1.5x median — trading at premium</t>
         </is>
       </c>
-      <c r="V58" t="n">
+      <c r="AE58" t="n">
         <v>2.33</v>
       </c>
-      <c r="W58" t="n">
+      <c r="AF58" t="n">
         <v>3.75</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AG58" t="n">
         <v>46.7</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AH58" t="n">
         <v>1.99</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AI58" t="n">
         <v>4.09</v>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.33–$3.75 (ann. vol 47%) | ATR range: $1.99–$4.09</t>
         </is>
@@ -9850,51 +13360,78 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="V59" t="b">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>1.28</v>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>1.3x vs 0.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="P59" t="n">
+      <c r="Y59" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>2.1x vs 1.3x median — trading at premium</t>
         </is>
       </c>
-      <c r="R59" t="n">
+      <c r="AA59" t="n">
         <v>11.36</v>
       </c>
-      <c r="S59" t="n">
+      <c r="AB59" t="n">
         <v>18.75</v>
       </c>
-      <c r="T59" t="n">
+      <c r="AC59" t="n">
         <v>9.58</v>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>P/S 1.3x vs 0.8x median — trading at premium | P/B 2.1x vs 1.3x median — trading at premium | EV/EBITDA 11.4x vs 2.1x median — trading at premium | Analyst target $18.75 | Graham # $9.58</t>
         </is>
       </c>
-      <c r="V59" t="n">
+      <c r="AE59" t="n">
         <v>14.08</v>
       </c>
-      <c r="W59" t="n">
+      <c r="AF59" t="n">
         <v>20.32</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AG59" t="n">
         <v>36.3</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AH59" t="n">
         <v>16.83</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AI59" t="n">
         <v>17.57</v>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $14.08–$20.32 (ann. vol 36%) | ATR range: $16.83–$17.57</t>
         </is>
@@ -9943,51 +13480,78 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="V60" t="b">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>2.04</v>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>2.0x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P60" t="n">
+      <c r="Y60" t="n">
         <v>0.99</v>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>1.0x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R60" t="n">
+      <c r="AA60" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S60" t="n">
+      <c r="AB60" t="n">
         <v>7.79</v>
       </c>
-      <c r="T60" t="n">
+      <c r="AC60" t="n">
         <v/>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>P/S 2.0x vs 11.4x median — trading at discount | P/B 1.0x vs 1.6x median — trading at discount | EV/EBITDA -1.2x vs -1.5x median — trading at discount | Analyst target $7.79</t>
         </is>
       </c>
-      <c r="V60" t="n">
+      <c r="AE60" t="n">
         <v>4.25</v>
       </c>
-      <c r="W60" t="n">
+      <c r="AF60" t="n">
         <v>8.25</v>
       </c>
-      <c r="X60" t="n">
+      <c r="AG60" t="n">
         <v>63.8</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="AH60" t="n">
         <v>2.96</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AI60" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $4.25–$8.25 (ann. vol 64%) | ATR range: $2.96–$9.54</t>
         </is>
@@ -10036,51 +13600,78 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="S61" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="V61" t="b">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v/>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P61" t="n">
+      <c r="Y61" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>1.9x vs 1.6x median — in-line</t>
         </is>
       </c>
-      <c r="R61" t="n">
+      <c r="AA61" t="n">
         <v>-0.82</v>
       </c>
-      <c r="S61" t="n">
+      <c r="AB61" t="n">
         <v>34.52</v>
       </c>
-      <c r="T61" t="n">
+      <c r="AC61" t="n">
         <v/>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>P/B 1.9x vs 1.6x median — in-line | EV/EBITDA -0.8x vs -1.5x median — trading at discount | Analyst target $34.52</t>
         </is>
       </c>
-      <c r="V61" t="n">
+      <c r="AE61" t="n">
         <v>6.11</v>
       </c>
-      <c r="W61" t="n">
+      <c r="AF61" t="n">
         <v>14.65</v>
       </c>
-      <c r="X61" t="n">
+      <c r="AG61" t="n">
         <v>82.3</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AH61" t="n">
         <v>6.01</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AI61" t="n">
         <v>14.75</v>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $6.11–$14.65 (ann. vol 82%) | ATR range: $6.01–$14.75</t>
         </is>
@@ -10129,51 +13720,78 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R62" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="V62" t="b">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>25.28</v>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>25.3x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P62" t="n">
+      <c r="Y62" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>2.5x vs 1.6x median — trading at premium</t>
         </is>
       </c>
-      <c r="R62" t="n">
+      <c r="AA62" t="n">
         <v>-3.42</v>
       </c>
-      <c r="S62" t="n">
+      <c r="AB62" t="n">
         <v>11.6</v>
       </c>
-      <c r="T62" t="n">
+      <c r="AC62" t="n">
         <v>7.21</v>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>P/S 25.3x vs 11.4x median — trading at premium | P/B 2.5x vs 1.6x median — trading at premium | EV/EBITDA -3.4x vs -1.5x median — trading at premium | Analyst target $11.60 | Graham # $7.21</t>
         </is>
       </c>
-      <c r="V62" t="n">
+      <c r="AE62" t="n">
         <v>2.44</v>
       </c>
-      <c r="W62" t="n">
+      <c r="AF62" t="n">
         <v>5.64</v>
       </c>
-      <c r="X62" t="n">
+      <c r="AG62" t="n">
         <v>79.3</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="AH62" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="AI62" t="n">
         <v>6.23</v>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.44–$5.64 (ann. vol 79%) | ATR range: $1.85–$6.23</t>
         </is>
@@ -10222,51 +13840,78 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R63" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="V63" t="b">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>2.38</v>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>2.4x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P63" t="n">
+      <c r="Y63" t="n">
         <v>0.86</v>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>0.9x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R63" t="n">
+      <c r="AA63" t="n">
         <v>-1.94</v>
       </c>
-      <c r="S63" t="n">
+      <c r="AB63" t="n">
         <v>4</v>
       </c>
-      <c r="T63" t="n">
+      <c r="AC63" t="n">
         <v/>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>P/S 2.4x vs 11.4x median — trading at discount | P/B 0.9x vs 1.6x median — trading at discount | EV/EBITDA -1.9x vs -1.5x median — trading at premium | Analyst target $4.00</t>
         </is>
       </c>
-      <c r="V63" t="n">
+      <c r="AE63" t="n">
         <v>2.96</v>
       </c>
-      <c r="W63" t="n">
+      <c r="AF63" t="n">
         <v>4.8</v>
       </c>
-      <c r="X63" t="n">
+      <c r="AG63" t="n">
         <v>47.7</v>
       </c>
-      <c r="Y63" t="n">
+      <c r="AH63" t="n">
         <v>2.48</v>
       </c>
-      <c r="Z63" t="n">
+      <c r="AI63" t="n">
         <v>5.28</v>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $2.96–$4.80 (ann. vol 48%) | ATR range: $2.48–$5.28</t>
         </is>
@@ -10315,51 +13960,78 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="V64" t="b">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v/>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="P64" t="n">
+      <c r="Y64" t="n">
         <v>1.39</v>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>1.4x vs 2.9x median — trading at discount</t>
         </is>
       </c>
-      <c r="R64" t="n">
+      <c r="AA64" t="n">
         <v>-1.08</v>
       </c>
-      <c r="S64" t="n">
+      <c r="AB64" t="n">
         <v>4.26</v>
       </c>
-      <c r="T64" t="n">
+      <c r="AC64" t="n">
         <v/>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>P/B 1.4x vs 2.9x median — trading at discount | EV/EBITDA -1.1x vs -1.1x median — in-line | Analyst target $4.26</t>
         </is>
       </c>
-      <c r="V64" t="n">
+      <c r="AE64" t="n">
         <v>0.8</v>
       </c>
-      <c r="W64" t="n">
+      <c r="AF64" t="n">
         <v>2.2</v>
       </c>
-      <c r="X64" t="n">
+      <c r="AG64" t="n">
         <v>93.2</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="AH64" t="n">
         <v>0.92</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="AI64" t="n">
         <v>2.08</v>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.80–$2.20 (ann. vol 93%) | ATR range: $0.92–$2.08</t>
         </is>
@@ -10408,51 +14080,78 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
+        <v>10.3818</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>11.0999</v>
+      </c>
+      <c r="R65" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V65" t="b">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>1.59</v>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>1.6x vs 11.4x median — trading at discount</t>
         </is>
       </c>
-      <c r="P65" t="n">
+      <c r="Y65" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>1.5x vs 1.6x median — in-line</t>
         </is>
       </c>
-      <c r="R65" t="n">
+      <c r="AA65" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="S65" t="n">
+      <c r="AB65" t="n">
         <v>14</v>
       </c>
-      <c r="T65" t="n">
+      <c r="AC65" t="n">
         <v>9.31</v>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>P/S 1.6x vs 11.4x median — trading at discount | P/B 1.5x vs 1.6x median — in-line | EV/EBITDA 9.3x vs -1.5x median — trading at discount | Analyst target $14.00 | Graham # $9.31</t>
         </is>
       </c>
-      <c r="V65" t="n">
+      <c r="AE65" t="n">
         <v>8.75</v>
       </c>
-      <c r="W65" t="n">
+      <c r="AF65" t="n">
         <v>11.87</v>
       </c>
-      <c r="X65" t="n">
+      <c r="AG65" t="n">
         <v>30.3</v>
       </c>
-      <c r="Y65" t="n">
+      <c r="AH65" t="n">
         <v>8.31</v>
       </c>
-      <c r="Z65" t="n">
+      <c r="AI65" t="n">
         <v>12.31</v>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AJ65" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $8.75–$11.87 (ann. vol 30%) | ATR range: $8.31–$12.31</t>
         </is>
@@ -10501,51 +14200,78 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="V66" t="b">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>0.19</v>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>0.2x vs 1.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="P66" t="n">
+      <c r="Y66" t="n">
         <v>0.91</v>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>0.9x vs 2.9x median — trading at discount</t>
         </is>
       </c>
-      <c r="R66" t="n">
+      <c r="AA66" t="n">
         <v>7.04</v>
       </c>
-      <c r="S66" t="n">
+      <c r="AB66" t="n">
         <v>6.69</v>
       </c>
-      <c r="T66" t="n">
+      <c r="AC66" t="n">
         <v/>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>P/S 0.2x vs 1.7x median — trading at discount | P/B 0.9x vs 2.9x median — trading at discount | EV/EBITDA 7.0x vs -1.1x median — trading at discount | Analyst target $6.69</t>
         </is>
       </c>
-      <c r="V66" t="n">
+      <c r="AE66" t="n">
         <v>4.04</v>
       </c>
-      <c r="W66" t="n">
+      <c r="AF66" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="X66" t="n">
+      <c r="AG66" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="AH66" t="n">
         <v>2.41</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="AI66" t="n">
         <v>9.83</v>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AJ66" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $4.04–$8.20 (ann. vol 68%) | ATR range: $2.41–$9.83</t>
         </is>
@@ -10594,51 +14320,78 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R67" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V67" t="b">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>2.14</v>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>2.1x vs 2.1x median — in-line</t>
         </is>
       </c>
-      <c r="P67" t="n">
+      <c r="Y67" t="n">
         <v>1.82</v>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>1.8x vs 0.8x median — trading at premium</t>
         </is>
       </c>
-      <c r="R67" t="n">
+      <c r="AA67" t="n">
         <v>-8.460000000000001</v>
       </c>
-      <c r="S67" t="n">
+      <c r="AB67" t="n">
         <v>9</v>
       </c>
-      <c r="T67" t="n">
+      <c r="AC67" t="n">
         <v/>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>P/S 2.1x vs 2.1x median — in-line | P/B 1.8x vs 0.8x median — trading at premium | EV/EBITDA -8.5x vs 1.0x median — trading at discount | Analyst target $9.00</t>
         </is>
       </c>
-      <c r="V67" t="n">
+      <c r="AE67" t="n">
         <v>1.35</v>
       </c>
-      <c r="W67" t="n">
+      <c r="AF67" t="n">
         <v>7.67</v>
       </c>
-      <c r="X67" t="n">
+      <c r="AG67" t="n">
         <v>140.3</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="AH67" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z67" t="n">
+      <c r="AI67" t="n">
         <v>7.91</v>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $1.35–$7.67 (ann. vol 140%) | ATR range: $1.11–$7.91</t>
         </is>
@@ -10687,51 +14440,78 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>-11.73</v>
+      </c>
+      <c r="V68" t="b">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>785.6799999999999</v>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>785.7x vs 11.4x median — trading at premium</t>
         </is>
       </c>
-      <c r="P68" t="n">
+      <c r="Y68" t="n">
         <v>-0.37</v>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>-0.4x vs 1.6x median — trading at discount</t>
         </is>
       </c>
-      <c r="R68" t="n">
+      <c r="AA68" t="n">
         <v>-7.42</v>
       </c>
-      <c r="S68" t="n">
+      <c r="AB68" t="n">
         <v>6.25</v>
       </c>
-      <c r="T68" t="n">
+      <c r="AC68" t="n">
         <v/>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>P/S 785.7x vs 11.4x median — trading at premium | P/B -0.4x vs 1.6x median — trading at discount | EV/EBITDA -7.4x vs -1.5x median — trading at premium | Analyst target $6.25</t>
         </is>
       </c>
-      <c r="V68" t="n">
+      <c r="AE68" t="n">
         <v>0.96</v>
       </c>
-      <c r="W68" t="n">
+      <c r="AF68" t="n">
         <v>2.26</v>
       </c>
-      <c r="X68" t="n">
+      <c r="AG68" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="AH68" t="n">
         <v>0.73</v>
       </c>
-      <c r="Z68" t="n">
+      <c r="AI68" t="n">
         <v>2.49</v>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.96–$2.26 (ann. vol 81%) | ATR range: $0.73–$2.49</t>
         </is>
@@ -10780,51 +14560,78 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="V69" t="b">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>0.14</v>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>0.1x vs 0.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="P69" t="n">
+      <c r="Y69" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>1.0x vs 1.1x median — in-line</t>
         </is>
       </c>
-      <c r="R69" t="n">
+      <c r="AA69" t="n">
         <v>-0.08</v>
       </c>
-      <c r="S69" t="n">
+      <c r="AB69" t="n">
         <v/>
       </c>
-      <c r="T69" t="n">
+      <c r="AC69" t="n">
         <v/>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 1.0x vs 1.1x median — in-line | EV/EBITDA -0.1x vs -2.8x median — trading at discount</t>
         </is>
       </c>
-      <c r="V69" t="n">
+      <c r="AE69" t="n">
         <v>-0.22</v>
       </c>
-      <c r="W69" t="n">
+      <c r="AF69" t="n">
         <v>5.12</v>
       </c>
-      <c r="X69" t="n">
+      <c r="AG69" t="n">
         <v>218</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="AH69" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z69" t="n">
+      <c r="AI69" t="n">
         <v>3.61</v>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $-0.22–$5.12 (ann. vol 218%) | ATR range: $1.29–$3.61</t>
         </is>
@@ -10873,51 +14680,78 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1.3797</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="V70" t="b">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>0.55</v>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="P70" t="n">
+      <c r="Y70" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>N/A — sector too small</t>
         </is>
       </c>
-      <c r="R70" t="n">
+      <c r="AA70" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="S70" t="n">
+      <c r="AB70" t="n">
         <v>3.96</v>
       </c>
-      <c r="T70" t="n">
+      <c r="AC70" t="n">
         <v/>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="AD70" t="inlineStr">
         <is>
           <t>Analyst target $3.96</t>
         </is>
       </c>
-      <c r="V70" t="n">
+      <c r="AE70" t="n">
         <v>0.84</v>
       </c>
-      <c r="W70" t="n">
+      <c r="AF70" t="n">
         <v>1.74</v>
       </c>
-      <c r="X70" t="n">
+      <c r="AG70" t="n">
         <v>69</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="AH70" t="n">
         <v>0.53</v>
       </c>
-      <c r="Z70" t="n">
+      <c r="AI70" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $0.84–$1.74 (ann. vol 69%) | ATR range: $0.53–$2.05</t>
         </is>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -626,7 +626,7 @@
         <v>10.8</v>
       </c>
       <c r="N2" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="O2" t="n">
         <v>64.59999999999999</v>
@@ -671,13 +671,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D3" t="n">
         <v>2.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-9.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="N3" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="O3" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="P3" t="n">
         <v>13.46</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>19.06</v>
+        <v>18.33</v>
       </c>
       <c r="S3" t="n">
         <v>13.61</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>20.39</v>
+        <v>19.65</v>
       </c>
       <c r="V3" t="n">
         <v>14.6</v>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
@@ -790,10 +790,10 @@
         <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="O4" t="n">
-        <v>68.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="P4" t="n">
         <v>3.9</v>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.39</v>
+        <v>-1.27</v>
       </c>
       <c r="S4" t="n">
         <v>3.98</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="V4" t="n">
         <v>4</v>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7.23</v>
+        <v>7.29</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>62.8</v>
+        <v>63.7</v>
       </c>
       <c r="P6" t="n">
         <v>6.3805</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-11.75</v>
+        <v>-12.48</v>
       </c>
       <c r="S6" t="n">
         <v>6.69</v>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.47</v>
+        <v>-8.23</v>
       </c>
       <c r="V6" t="n">
         <v>7.56</v>
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="D7" t="n">
         <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-14.3</v>
+        <v>-12.8</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="N7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="P7" t="n">
         <v>0.6049</v>
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-13.95</v>
+        <v>-15.37</v>
       </c>
       <c r="S7" t="n">
         <v>0.58</v>
@@ -1057,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-17.5</v>
+        <v>-18.86</v>
       </c>
       <c r="V7" t="n">
         <v>1.1599</v>
@@ -1087,7 +1087,7 @@
         <v>0.6</v>
       </c>
       <c r="E8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N8" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="O8" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
       <c r="P8" t="n">
         <v>3.47</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-12.48</v>
+        <v>-12.15</v>
       </c>
       <c r="S8" t="n">
         <v>3.84</v>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.15</v>
+        <v>-2.78</v>
       </c>
       <c r="V8" t="n">
         <v>3.5609</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>10.79</v>
+        <v>10.77</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>65.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>10.15</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-5.93</v>
+        <v>-5.76</v>
       </c>
       <c r="S10" t="n">
         <v>10.27</v>
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.82</v>
+        <v>-4.64</v>
       </c>
       <c r="V10" t="n">
         <v>10.43</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>45.3</v>
+        <v>46.2</v>
       </c>
       <c r="P11" t="n">
         <v>4</v>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.76</v>
+        <v>0.25</v>
       </c>
       <c r="S11" t="n">
         <v>3.78</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.79</v>
+        <v>-5.26</v>
       </c>
       <c r="V11" t="n">
         <v>4.7</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="N12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O12" t="n">
-        <v>41.3</v>
+        <v>40</v>
       </c>
       <c r="P12" t="n">
         <v>2.35</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="S12" t="n">
         <v>2.35</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="V12" t="n">
         <v>2.39</v>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.71</v>
+        <v>3.81</v>
       </c>
       <c r="D13" t="n">
         <v>1.2</v>
       </c>
       <c r="E13" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Moved</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -1525,13 +1525,13 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
-        <v>74</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>1.53</v>
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>6.99</v>
+        <v>5.88</v>
       </c>
       <c r="S13" t="n">
         <v>1.4297</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.02</v>
+        <v>-1.06</v>
       </c>
       <c r="V13" t="n">
         <v>1.76</v>
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="D14" t="n">
         <v>1.8</v>
       </c>
       <c r="E14" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-15.1</v>
+        <v>-11.5</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -1610,10 +1610,10 @@
         <v>0.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.79</v>
+        <v>3.12</v>
       </c>
       <c r="O14" t="n">
-        <v>31.7</v>
+        <v>33</v>
       </c>
       <c r="P14" t="n">
         <v>0.1182</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-24.47</v>
+        <v>-28.41</v>
       </c>
       <c r="S14" t="n">
         <v>0.1166</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-25.5</v>
+        <v>-29.38</v>
       </c>
       <c r="V14" t="n">
         <v>0.1606</v>
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>7.32</v>
+        <v>7.16</v>
       </c>
       <c r="N15" t="n">
-        <v>16.87</v>
+        <v>16.89</v>
       </c>
       <c r="O15" t="n">
-        <v>75.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="P15" t="n">
         <v>3.4406</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-52.83</v>
+        <v>-51.54</v>
       </c>
       <c r="S15" t="n">
         <v>8.41</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>15.29</v>
+        <v>18.45</v>
       </c>
       <c r="V15" t="n">
         <v>4.15</v>
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="N16" t="n">
-        <v>15.73</v>
+        <v>15.74</v>
       </c>
       <c r="O16" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="P16" t="n">
         <v>4.01</v>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>14.57</v>
+        <v>14.28</v>
       </c>
       <c r="S16" t="n">
         <v>3.98</v>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>13.71</v>
+        <v>13.42</v>
       </c>
       <c r="V16" t="n">
         <v>4.07</v>
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="O17" t="n">
-        <v>52.2</v>
+        <v>50.6</v>
       </c>
       <c r="P17" t="n">
         <v>1.14</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.24</v>
+        <v>4.11</v>
       </c>
       <c r="S17" t="n">
         <v>1.24</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>11.21</v>
+        <v>13.24</v>
       </c>
       <c r="V17" t="n">
         <v>1.52</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -1938,10 +1938,10 @@
         <v>2.02</v>
       </c>
       <c r="N18" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="O18" t="n">
-        <v>67.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="P18" t="n">
         <v>1.68</v>
@@ -2020,7 +2020,7 @@
         <v>1.75</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O19" t="n">
         <v>54.7</v>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O21" t="n">
-        <v>51.7</v>
+        <v>52.1</v>
       </c>
       <c r="P21" t="n">
         <v>0.907</v>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-8.710000000000001</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="S21" t="n">
         <v>0.9301</v>
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.38</v>
+        <v>-6.82</v>
       </c>
       <c r="V21" t="n">
         <v>0.9194</v>
@@ -2220,7 +2220,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>REAX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2229,16 +2229,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2259,41 +2259,41 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="N22" t="n">
-        <v>19.64</v>
+        <v>1.5</v>
       </c>
       <c r="O22" t="n">
-        <v>70.2</v>
+        <v>50.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6845</v>
+        <v>2.6485</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-34.18</v>
+        <v>19.03</v>
       </c>
       <c r="S22" t="n">
-        <v>1.04</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7199</v>
+        <v>2.8492</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6721</v>
+        <v>2.59</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
@@ -2302,7 +2302,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UPXI</t>
+          <t>LUCY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -2348,34 +2348,34 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.57</v>
+        <v>19.64</v>
       </c>
       <c r="O23" t="n">
-        <v>65.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>1.07</v>
+        <v>0.6845</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>-35.41</v>
       </c>
       <c r="S23" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.32</v>
+        <v>-1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>0.7199</v>
       </c>
       <c r="W23" t="n">
-        <v>0.785</v>
+        <v>0.6721</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
@@ -2384,7 +2384,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEFT</t>
+          <t>UPXI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -2427,37 +2427,37 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>2.26</v>
+        <v>2.61</v>
       </c>
       <c r="O24" t="n">
-        <v>67.3</v>
+        <v>66.2</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6156</v>
+        <v>1.07</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.631</v>
+        <v>1.09</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>2.83</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6183</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>0.43</v>
+        <v>0.785</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
@@ -2466,7 +2466,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOVX</t>
+          <t>DEFT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -2505,41 +2505,41 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="N25" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
-        <v>40.4</v>
+        <v>67.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6425</v>
+        <v>0.6156</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-6.75</v>
+        <v>-0.84</v>
       </c>
       <c r="S25" t="n">
-        <v>0.718</v>
+        <v>0.631</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.21</v>
+        <v>1.64</v>
       </c>
       <c r="V25" t="n">
-        <v>0.68</v>
+        <v>0.6183</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5907</v>
+        <v>0.43</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
@@ -2548,7 +2548,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NGEN</t>
+          <t>GOVX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2587,41 +2587,41 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="O26" t="n">
-        <v>65.5</v>
+        <v>40.7</v>
       </c>
       <c r="P26" t="n">
-        <v>1.8896</v>
+        <v>0.6425</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-3.1</v>
+        <v>-7.13</v>
       </c>
       <c r="S26" t="n">
-        <v>1.87</v>
+        <v>0.718</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.1</v>
+        <v>3.79</v>
       </c>
       <c r="V26" t="n">
-        <v>1.8896</v>
+        <v>0.68</v>
       </c>
       <c r="W26" t="n">
-        <v>1.6303</v>
+        <v>0.5907</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
@@ -2630,7 +2630,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>NGEN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2639,71 +2639,71 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F27" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="n">
-        <v>3</v>
-      </c>
       <c r="G27" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>47.8</v>
+        <v/>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.2pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4.48</v>
+        <v>1.97</v>
       </c>
       <c r="N27" t="n">
-        <v>12.78</v>
+        <v>2.01</v>
       </c>
       <c r="O27" t="n">
-        <v>49.1</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>4.7092</v>
+        <v>1.8896</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5.02</v>
+        <v>-4.08</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3402</v>
+        <v>1.87</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.2</v>
+        <v>-5.08</v>
       </c>
       <c r="V27" t="n">
-        <v>5.2</v>
+        <v>1.8896</v>
       </c>
       <c r="W27" t="n">
-        <v>3.03</v>
+        <v>1.6303</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NXGL</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2721,75 +2721,71 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D28" t="n">
         <v>1.2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-0.4</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>49.2</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.4pts) | 2026-08-20 S-1 (dilution_risk, -2.4pts) | 2026-08-17 8-K (material_event, +0.6pts)</t>
+          <t>2026-08-20 8-K (material_event, +1.2pts)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.35</v>
+        <v>4.52</v>
       </c>
       <c r="N28" t="n">
-        <v>14.68</v>
+        <v>12.79</v>
       </c>
       <c r="O28" t="n">
-        <v>42</v>
+        <v>49.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3377</v>
+        <v>4.7092</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.23</v>
+        <v>3.96</v>
       </c>
       <c r="S28" t="n">
-        <v>0.3051</v>
+        <v>4.3402</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>-10.76</v>
+        <v>-4.19</v>
       </c>
       <c r="V28" t="n">
-        <v>0.484</v>
+        <v>5.2</v>
       </c>
       <c r="W28" t="n">
-        <v>0.33</v>
+        <v>3.03</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
@@ -2798,7 +2794,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BMEA</t>
+          <t>NXGL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2807,71 +2803,75 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v/>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>-7.2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 8-K (material_event, +1.4pts) | 2026-08-20 S-1 (dilution_risk, -2.4pts) | 2026-08-17 8-K (material_event, +0.6pts)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1.58</v>
+        <v>0.35</v>
       </c>
       <c r="N29" t="n">
-        <v>9.960000000000001</v>
+        <v>14.68</v>
       </c>
       <c r="O29" t="n">
-        <v>77</v>
+        <v>42.3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.3741</v>
+        <v>0.3377</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-12.98</v>
+        <v>-3.24</v>
       </c>
       <c r="S29" t="n">
-        <v>1.5</v>
+        <v>0.3051</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>-5</v>
+        <v>-12.58</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>0.484</v>
       </c>
       <c r="W29" t="n">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ANY</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2895,65 +2895,65 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Late Entry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>18.1</v>
+        <v/>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-14 8-K (material_event, +0.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2.48</v>
+        <v>1.58</v>
       </c>
       <c r="N30" t="n">
-        <v>1.68</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>58.3</v>
+        <v>76.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>1.3741</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.82</v>
+        <v>-12.76</v>
       </c>
       <c r="S30" t="n">
-        <v>2.68</v>
+        <v>1.5</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>8.06</v>
+        <v>-4.76</v>
       </c>
       <c r="V30" t="n">
-        <v>2.6884</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
@@ -2962,7 +2962,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>ANY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2971,71 +2971,71 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Late Entry</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>32.4</v>
+        <v>18.6</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-17 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts)</t>
+          <t>2026-08-14 8-K (material_event, +0.0pts)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5.66</v>
+        <v>2.49</v>
       </c>
       <c r="N31" t="n">
-        <v>3.11</v>
+        <v>1.7</v>
       </c>
       <c r="O31" t="n">
-        <v>74.40000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="P31" t="n">
-        <v>5.3817</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>-5.08</v>
+        <v>2.62</v>
       </c>
       <c r="S31" t="n">
-        <v>5.52</v>
+        <v>2.68</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>-2.65</v>
+        <v>7.85</v>
       </c>
       <c r="V31" t="n">
-        <v>5.55</v>
+        <v>2.6884</v>
       </c>
       <c r="W31" t="n">
-        <v>4.45</v>
+        <v>1.94</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
@@ -3044,7 +3044,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VMAR</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3059,65 +3059,65 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v/>
+        <v>32.8</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-17 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.65</v>
+        <v>5.68</v>
       </c>
       <c r="N32" t="n">
-        <v>2.72</v>
+        <v>3.14</v>
       </c>
       <c r="O32" t="n">
-        <v>32.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="P32" t="n">
-        <v>0.6989</v>
+        <v>5.3817</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7.09</v>
+        <v>-5.34</v>
       </c>
       <c r="S32" t="n">
-        <v>0.669</v>
+        <v>5.52</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.51</v>
+        <v>-2.9</v>
       </c>
       <c r="V32" t="n">
-        <v>0.7035</v>
+        <v>5.55</v>
       </c>
       <c r="W32" t="n">
-        <v>0.6516999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
@@ -3126,7 +3126,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BTOG</t>
+          <t>VMAR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3141,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3169,37 +3169,37 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>0.66</v>
       </c>
       <c r="N33" t="n">
-        <v>1.99</v>
+        <v>2.73</v>
       </c>
       <c r="O33" t="n">
-        <v>30</v>
+        <v>32.6</v>
       </c>
       <c r="P33" t="n">
-        <v>3.9999</v>
+        <v>0.6989</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>23.45</v>
+        <v>6.04</v>
       </c>
       <c r="S33" t="n">
-        <v>3.63</v>
+        <v>0.669</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>12.04</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>6.85</v>
+        <v>0.7035</v>
       </c>
       <c r="W33" t="n">
-        <v>3.4575</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
@@ -3208,80 +3208,80 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>BTOG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>95.59999999999999</v>
+        <v/>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +0.8pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_overbought -2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1.57</v>
+        <v>3.24</v>
       </c>
       <c r="N34" t="n">
-        <v>7.25</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>87.5</v>
+        <v>30.8</v>
       </c>
       <c r="P34" t="n">
-        <v>1.6208</v>
+        <v>3.9999</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.58</v>
+        <v>23.26</v>
       </c>
       <c r="S34" t="n">
-        <v>1.86</v>
+        <v>3.63</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>17.72</v>
+        <v>11.86</v>
       </c>
       <c r="V34" t="n">
-        <v>1.8</v>
+        <v>6.85</v>
       </c>
       <c r="W34" t="n">
-        <v>0.7705</v>
+        <v>3.4575</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
@@ -3290,7 +3290,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GIPR</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -3319,51 +3319,51 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>57.4</v>
+        <v>97.5</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-17 8-K (material_event, +0.6pts)</t>
+          <t>2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +0.8pts)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.55</v>
+        <v>1.59</v>
       </c>
       <c r="N35" t="n">
-        <v>15.71</v>
+        <v>7.28</v>
       </c>
       <c r="O35" t="n">
-        <v>40.7</v>
+        <v>87.7</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2842</v>
+        <v>1.6208</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>-49.15</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0.29</v>
+        <v>1.86</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>-48.11</v>
+        <v>16.25</v>
       </c>
       <c r="V35" t="n">
-        <v>0.3293</v>
+        <v>1.8</v>
       </c>
       <c r="W35" t="n">
-        <v>0.2624</v>
+        <v>0.7705</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
@@ -3372,7 +3372,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OLOX</t>
+          <t>GIPR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3381,71 +3381,71 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v/>
+        <v>63.1</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-17 8-K (material_event, +0.6pts)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>2.17</v>
+        <v>0.57</v>
       </c>
       <c r="N36" t="n">
-        <v>16.23</v>
+        <v>15.84</v>
       </c>
       <c r="O36" t="n">
-        <v>23.1</v>
+        <v>41.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.24</v>
+        <v>0.2842</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.56</v>
+        <v>-51.13</v>
       </c>
       <c r="S36" t="n">
-        <v>2.39</v>
+        <v>0.29</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>10.49</v>
+        <v>-50.14</v>
       </c>
       <c r="V36" t="n">
-        <v>2.77</v>
+        <v>0.3293</v>
       </c>
       <c r="W36" t="n">
-        <v>2.09</v>
+        <v>0.2624</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HUYA</t>
+          <t>OLOX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
         <v>-1</v>
@@ -3497,37 +3497,37 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="N37" t="n">
-        <v>1.77</v>
+        <v>16.24</v>
       </c>
       <c r="O37" t="n">
-        <v>28.6</v>
+        <v>22</v>
       </c>
       <c r="P37" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.86</v>
+        <v>5.16</v>
       </c>
       <c r="S37" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>12.21</v>
       </c>
       <c r="V37" t="n">
-        <v>2.26</v>
+        <v>2.77</v>
       </c>
       <c r="W37" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
@@ -3536,7 +3536,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>HUYA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3545,71 +3545,71 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-3.4</v>
+        <v>-1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1.19</v>
       </c>
       <c r="F38" t="n">
         <v>-1</v>
       </c>
       <c r="G38" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>331.9</v>
+        <v/>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, +0.8pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>2.76</v>
+        <v>2.15</v>
       </c>
       <c r="N38" t="n">
-        <v>16.22</v>
+        <v>1.78</v>
       </c>
       <c r="O38" t="n">
-        <v>77.40000000000001</v>
+        <v>28.9</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4339</v>
+        <v>2.19</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>-84.28</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.44</v>
+        <v>2.18</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>-84.06</v>
+        <v>1.63</v>
       </c>
       <c r="V38" t="n">
-        <v>0.6679</v>
+        <v>2.26</v>
       </c>
       <c r="W38" t="n">
-        <v>0.3227</v>
+        <v>2.15</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
@@ -3618,7 +3618,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3627,16 +3627,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-4</v>
+        <v>-3.4</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G39" t="n">
         <v>-4</v>
@@ -3647,53 +3647,135 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>30.1</v>
+        <v>313.1</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
+          <t>2026-08-18 8-K (material_event, +0.8pts)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>trend_alignment +1, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N39" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-83.56</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-83.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="X39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DFDV</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>2026-08-21 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts)</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>trend_alignment +2, rsi_overbought -2</t>
         </is>
       </c>
-      <c r="M39" t="n">
+      <c r="M40" t="n">
         <v>4.11</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N40" t="n">
         <v>1.63</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O40" t="n">
         <v>77</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P40" t="n">
         <v>4</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="S40" t="n">
         <v>4.16</v>
       </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V40" t="n">
         <v>4.14</v>
       </c>
-      <c r="W39" t="n">
+      <c r="W40" t="n">
         <v>3.07</v>
       </c>
-      <c r="X39" t="b">
+      <c r="X40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3708,7 +3790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ39"/>
+  <dimension ref="A1:AJ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3941,13 +4023,13 @@
         <v>3.95</v>
       </c>
       <c r="C2" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="D2" t="n">
-        <v>3705298</v>
+        <v>3701765</v>
       </c>
       <c r="E2" t="n">
-        <v>68.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="F2" t="n">
         <v>3.77</v>
@@ -3980,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.39</v>
+        <v>-1.27</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -3995,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -4034,7 +4116,7 @@
         <v>3.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="AG2" t="n">
         <v>25.8</v>
@@ -4043,11 +4125,11 @@
         <v>3.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.73</v>
+        <v>4.72</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.44–$4.47 (ann. vol 26%) | ATR range: $3.18–$4.73</t>
+          <t>1-SD 3mo range: $3.44–$4.46 (ann. vol 26%) | ATR range: $3.18–$4.72</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4140,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="C3" t="n">
         <v>19.64</v>
       </c>
       <c r="D3" t="n">
-        <v>9533339</v>
+        <v>9597832</v>
       </c>
       <c r="E3" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0.76</v>
@@ -4100,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-34.18</v>
+        <v>-35.41</v>
       </c>
       <c r="Q3" t="n">
         <v>0.7199</v>
@@ -4115,21 +4197,21 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1.86</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2.6x vs 2.1x median — trading at premium</t>
+          <t>2.7x vs 2.1x median — trading at premium</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -4147,27 +4229,27 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>P/S 2.6x vs 2.1x median — trading at premium | P/B 1.0x vs 2.0x median — trading at discount | EV/EBITDA -0.3x vs -0.8x median — trading at discount</t>
+          <t>P/S 2.7x vs 2.1x median — trading at premium | P/B 1.0x vs 2.0x median — trading at discount | EV/EBITDA -0.3x vs -0.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AF3" t="n">
         <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>105.5</v>
+        <v>105.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="AI3" t="n">
         <v>1.71</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.49–$1.60 (ann. vol 106%) | ATR range: $0.38–$1.71</t>
+          <t>1-SD 3mo range: $0.50–$1.60 (ann. vol 106%) | ATR range: $0.39–$1.71</t>
         </is>
       </c>
     </row>
@@ -4178,25 +4260,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.32</v>
+        <v>7.16</v>
       </c>
       <c r="C4" t="n">
-        <v>16.87</v>
+        <v>16.89</v>
       </c>
       <c r="D4" t="n">
-        <v>33877372</v>
+        <v>33348617</v>
       </c>
       <c r="E4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="F4" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="G4" t="n">
         <v>4.52</v>
       </c>
       <c r="H4" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="I4" t="n">
         <v>4.38</v>
@@ -4220,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-52.83</v>
+        <v>-51.54</v>
       </c>
       <c r="Q4" t="n">
         <v>4.15</v>
@@ -4235,25 +4317,25 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>15.29</v>
+        <v>18.45</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.8x vs 0.8x median — in-line</t>
+          <t>0.8x vs 0.7x median — in-line</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>10.85</v>
+        <v>10.66</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.9x vs 2.7x median — trading at premium</t>
+          <t>10.7x vs 2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AA4" t="n">
@@ -4267,477 +4349,477 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>P/S 0.8x vs 0.8x median — in-line | P/B 10.9x vs 2.7x median — trading at premium | EV/EBITDA -0.2x vs -1.5x median — trading at discount</t>
+          <t>P/S 0.8x vs 0.7x median — in-line | P/B 10.7x vs 2.7x median — trading at premium | EV/EBITDA -0.2x vs -1.5x median — trading at discount</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.84</v>
+        <v>11.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>123.5</v>
+        <v>122.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" t="n">
-        <v>13.21</v>
+        <v>13.05</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.80–$11.84 (ann. vol 124%) | ATR range: $1.43–$13.21</t>
+          <t>1-SD 3mo range: $2.79–$11.53 (ann. vol 122%) | ATR range: $1.27–$13.05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OLOX</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.17</v>
+        <v>2.64</v>
       </c>
       <c r="C5" t="n">
-        <v>16.23</v>
+        <v>16.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2099491</v>
+        <v>9486421</v>
       </c>
       <c r="E5" t="n">
-        <v>23.1</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>3.28</v>
+        <v>0.92</v>
       </c>
       <c r="G5" t="n">
-        <v>4.49</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>20.37</v>
+        <v>18.19</v>
       </c>
       <c r="I5" t="n">
-        <v>4.67</v>
+        <v>1.29</v>
       </c>
       <c r="J5" t="n">
-        <v>12.37</v>
+        <v>11.79</v>
       </c>
       <c r="K5" t="n">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>0.4339</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.56</v>
+        <v>-83.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.77</v>
+        <v>0.6679</v>
       </c>
       <c r="R5" t="n">
-        <v>2.09</v>
+        <v>0.3227</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>0.44</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>10.49</v>
+        <v>-83.33</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.75</v>
+        <v>14.62</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.8x vs 0.8x median — in-line</t>
+          <t>N/A — sector too small</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>0.19</v>
+        <v>-0.76</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.2x vs 2.7x median — trading at discount</t>
+          <t>N/A — sector too small</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>-2.52</v>
+        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
       </c>
       <c r="AC5" t="n">
-        <v>329.77</v>
+        <v/>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>P/S 0.8x vs 0.8x median — in-line | P/B 0.2x vs 2.7x median — trading at discount | EV/EBITDA -2.5x vs -1.5x median — trading at premium | Graham # $329.77</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01</v>
+        <v>-0.48</v>
       </c>
       <c r="AF5" t="n">
-        <v>4.35</v>
+        <v>5.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>200.6</v>
+        <v>236.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2</v>
+        <v>0.08</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.34</v>
+        <v>5.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.01–$4.35 (ann. vol 201%) | ATR range: $-2.00–$6.34</t>
+          <t>1-SD 3mo range: $-0.48–$5.76 (ann. vol 236%) | ATR range: $0.08–$5.20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>OLOX</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.76</v>
+        <v>2.13</v>
       </c>
       <c r="C6" t="n">
-        <v>16.22</v>
+        <v>16.24</v>
       </c>
       <c r="D6" t="n">
-        <v>9714758</v>
+        <v>2064613</v>
       </c>
       <c r="E6" t="n">
-        <v>77.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>0.93</v>
+        <v>3.28</v>
       </c>
       <c r="G6" t="n">
-        <v>1.57</v>
+        <v>4.49</v>
       </c>
       <c r="H6" t="n">
-        <v>18.19</v>
+        <v>20.37</v>
       </c>
       <c r="I6" t="n">
-        <v>1.29</v>
+        <v>4.67</v>
       </c>
       <c r="J6" t="n">
-        <v>11.79</v>
+        <v>12.37</v>
       </c>
       <c r="K6" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4339</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-84.28</v>
+        <v>5.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6679</v>
+        <v>2.77</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3227</v>
+        <v>2.09</v>
       </c>
       <c r="S6" t="n">
-        <v>0.44</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-84.06</v>
+        <v>12.21</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>15.28</v>
+        <v>0.74</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>0.7x vs 0.7x median — in-line</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>-0.8</v>
+        <v>0.18</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>0.2x vs 2.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v/>
+        <v>-2.52</v>
       </c>
       <c r="AB6" t="n">
         <v/>
       </c>
       <c r="AC6" t="n">
-        <v/>
+        <v>329.77</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>P/S 0.7x vs 0.7x median — in-line | P/B 0.2x vs 2.7x median — trading at discount | EV/EBITDA -2.5x vs -1.5x median — trading at premium | Graham # $329.77</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>-0.55</v>
+        <v>-0.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>6.07</v>
+        <v>4.27</v>
       </c>
       <c r="AG6" t="n">
-        <v>240</v>
+        <v>200.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2</v>
+        <v>-2.04</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.32</v>
+        <v>6.3</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.55–$6.07 (ann. vol 240%) | ATR range: $0.20–$5.32</t>
+          <t>1-SD 3mo range: $-0.01–$4.27 (ann. vol 200%) | ATR range: $-2.04–$6.30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>GIPR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.49</v>
+        <v>0.57</v>
       </c>
       <c r="C7" t="n">
-        <v>15.73</v>
+        <v>15.84</v>
       </c>
       <c r="D7" t="n">
-        <v>1875488</v>
+        <v>5693828</v>
       </c>
       <c r="E7" t="n">
-        <v>47.9</v>
+        <v>41.8</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>0.62</v>
       </c>
       <c r="G7" t="n">
-        <v>3.57</v>
+        <v>1.13</v>
       </c>
       <c r="H7" t="n">
-        <v>4.83</v>
+        <v>3.97</v>
       </c>
       <c r="I7" t="n">
-        <v>3.44</v>
+        <v>1.11</v>
       </c>
       <c r="J7" t="n">
-        <v>5.09</v>
+        <v>4.42</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.01</v>
+        <v>0.2842</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>14.57</v>
+        <v>-51.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.07</v>
+        <v>0.3293</v>
       </c>
       <c r="R7" t="n">
-        <v>3.5</v>
+        <v>0.2624</v>
       </c>
       <c r="S7" t="n">
-        <v>3.98</v>
+        <v>0.29</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>13.71</v>
+        <v>-50.14</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v/>
+        <v>0.12</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>0.1x vs 0.2x median — trading at discount</t>
         </is>
       </c>
       <c r="Y7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.1x vs 0.5x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>P/S 0.1x vs 0.2x median — trading at discount | P/B -0.1x vs 0.5x median — trading at discount | EV/EBITDA 28.3x vs 2.0x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.05</v>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1.1x vs 2.0x median — trading at discount</t>
-        </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>P/B 1.1x vs 2.0x median — trading at discount | EV/EBITDA -0.4x vs -0.8x median — trading at discount</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>5.71</v>
-      </c>
       <c r="AG7" t="n">
-        <v>127</v>
+        <v>164.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>-0.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.52</v>
+        <v>1.76</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.28–$5.71 (ann. vol 127%) | ATR range: $1.47–$5.52</t>
+          <t>1-SD 3mo range: $0.10–$1.05 (ann. vol 164%) | ATR range: $-0.61–$1.76</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GIPR</t>
+          <t>BCTX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.55</v>
+        <v>3.51</v>
       </c>
       <c r="C8" t="n">
-        <v>15.71</v>
+        <v>15.74</v>
       </c>
       <c r="D8" t="n">
-        <v>5334738</v>
+        <v>1884100</v>
       </c>
       <c r="E8" t="n">
-        <v>40.7</v>
+        <v>48.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.62</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.13</v>
+        <v>3.57</v>
       </c>
       <c r="H8" t="n">
-        <v>3.97</v>
+        <v>4.83</v>
       </c>
       <c r="I8" t="n">
-        <v>1.11</v>
+        <v>3.44</v>
       </c>
       <c r="J8" t="n">
-        <v>4.42</v>
+        <v>5.09</v>
       </c>
       <c r="K8" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2842</v>
+        <v>4.01</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-49.15</v>
+        <v>14.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3293</v>
+        <v>4.07</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2624</v>
+        <v>3.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.29</v>
+        <v>3.98</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-48.11</v>
+        <v>13.42</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.11</v>
+        <v/>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>1.1x vs 2.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>28.32</v>
+        <v>-0.38</v>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -4747,27 +4829,27 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>P/B 1.1x vs 2.0x median — trading at discount | EV/EBITDA -0.4x vs -0.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.1</v>
+        <v>1.28</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.01</v>
+        <v>5.74</v>
       </c>
       <c r="AG8" t="n">
-        <v>162.9</v>
+        <v>127</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.63</v>
+        <v>1.48</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.74</v>
+        <v>5.54</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.10–$1.01 (ann. vol 163%) | ATR range: $-0.63–$1.74</t>
+          <t>1-SD 3mo range: $1.28–$5.74 (ann. vol 127%) | ATR range: $1.48–$5.54</t>
         </is>
       </c>
     </row>
@@ -4784,10 +4866,10 @@
         <v>14.68</v>
       </c>
       <c r="D9" t="n">
-        <v>579144</v>
+        <v>583402</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="F9" t="n">
         <v>0.41</v>
@@ -4820,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.23</v>
+        <v>-3.24</v>
       </c>
       <c r="Q9" t="n">
         <v>0.484</v>
@@ -4835,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-10.76</v>
+        <v>-12.58</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
@@ -4849,7 +4931,7 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -4874,7 +4956,7 @@
         <v>0.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="AG9" t="n">
         <v>108.5</v>
@@ -4887,7 +4969,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.16–$0.53 (ann. vol 108%) | ATR range: $-0.29–$0.99</t>
+          <t>1-SD 3mo range: $0.16–$0.54 (ann. vol 108%) | ATR range: $-0.29–$0.99</t>
         </is>
       </c>
     </row>
@@ -5018,16 +5100,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.48</v>
+        <v>4.52</v>
       </c>
       <c r="C11" t="n">
-        <v>12.78</v>
+        <v>12.79</v>
       </c>
       <c r="D11" t="n">
-        <v>6489105</v>
+        <v>6556222</v>
       </c>
       <c r="E11" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="F11" t="n">
         <v>4.07</v>
@@ -5060,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5.02</v>
+        <v>3.96</v>
       </c>
       <c r="Q11" t="n">
         <v>5.2</v>
@@ -5075,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.2</v>
+        <v>-4.19</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -5089,7 +5171,7 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>5.37</v>
+        <v>5.43</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -5114,20 +5196,20 @@
         <v>0.21</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.74</v>
+        <v>8.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>190.4</v>
+        <v>190.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>8.529999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.21–$8.74 (ann. vol 190%) | ATR range: $0.42–$8.53</t>
+          <t>1-SD 3mo range: $0.21–$8.83 (ann. vol 191%) | ATR range: $0.47–$8.57</t>
         </is>
       </c>
     </row>
@@ -5141,13 +5223,13 @@
         <v>1.58</v>
       </c>
       <c r="C12" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1582699</v>
+        <v>1580316</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>76.8</v>
       </c>
       <c r="F12" t="n">
         <v>1.33</v>
@@ -5180,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-12.98</v>
+        <v>-12.76</v>
       </c>
       <c r="Q12" t="n">
         <v>1.4</v>
@@ -5195,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-5</v>
+        <v>-4.76</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -5209,11 +5291,11 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>9.460000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.5x vs 2.0x median — trading at premium</t>
+          <t>9.4x vs 2.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA12" t="n">
@@ -5227,11 +5309,11 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>P/B 9.5x vs 2.0x median — trading at premium | EV/EBITDA -1.2x vs -0.8x median — trading at premium | Analyst target $6.50</t>
+          <t>P/B 9.4x vs 2.0x median — trading at premium | EV/EBITDA -1.2x vs -0.8x median — trading at premium | Analyst target $6.50</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="AF12" t="n">
         <v>2.29</v>
@@ -5247,7 +5329,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.87–$2.29 (ann. vol 90%) | ATR range: $0.85–$2.30</t>
+          <t>1-SD 3mo range: $0.86–$2.29 (ann. vol 90%) | ATR range: $0.85–$2.30</t>
         </is>
       </c>
     </row>
@@ -5378,16 +5460,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="C14" t="n">
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
       <c r="D14" t="n">
-        <v>7327445</v>
+        <v>7421130</v>
       </c>
       <c r="E14" t="n">
-        <v>87.5</v>
+        <v>87.7</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
@@ -5420,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.58</v>
+        <v>1.3</v>
       </c>
       <c r="Q14" t="n">
         <v>1.8</v>
@@ -5435,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>17.72</v>
+        <v>16.25</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -5449,7 +5531,7 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -5474,20 +5556,20 @@
         <v>-0.28</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="AG14" t="n">
-        <v>234.9</v>
+        <v>235</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.28–$3.42 (ann. vol 235%) | ATR range: $0.38–$2.76</t>
+          <t>1-SD 3mo range: $-0.28–$3.46 (ann. vol 235%) | ATR range: $0.40–$2.78</t>
         </is>
       </c>
     </row>
@@ -5501,10 +5583,10 @@
         <v>10.8</v>
       </c>
       <c r="C15" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="D15" t="n">
-        <v>2387395</v>
+        <v>2391372</v>
       </c>
       <c r="E15" t="n">
         <v>64.59999999999999</v>
@@ -5618,16 +5700,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="C16" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="D16" t="n">
-        <v>1076871</v>
+        <v>1058725</v>
       </c>
       <c r="E16" t="n">
-        <v>52.2</v>
+        <v>50.6</v>
       </c>
       <c r="F16" t="n">
         <v>1.07</v>
@@ -5660,7 +5742,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>4.11</v>
       </c>
       <c r="Q16" t="n">
         <v>1.52</v>
@@ -5675,13 +5757,13 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>11.21</v>
+        <v>13.24</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>-2.42</v>
+        <v>-2.38</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -5711,23 +5793,23 @@
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AG16" t="n">
         <v>222.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.13–$2.36 (ann. vol 222%) | ATR range: $0.37–$1.86</t>
+          <t>1-SD 3mo range: $-0.12–$2.31 (ann. vol 222%) | ATR range: $0.34–$1.85</t>
         </is>
       </c>
     </row>
@@ -5741,13 +5823,13 @@
         <v>2.02</v>
       </c>
       <c r="C17" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="D17" t="n">
-        <v>1828752</v>
+        <v>1827308</v>
       </c>
       <c r="E17" t="n">
-        <v>67.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>1.66</v>
@@ -5834,55 +5916,55 @@
         <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AG17" t="n">
         <v>87.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AI17" t="n">
         <v>3.32</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.13–$2.91 (ann. vol 88%) | ATR range: $0.72–$3.32</t>
+          <t>1-SD 3mo range: $1.13–$2.90 (ann. vol 88%) | ATR range: $0.71–$3.32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.66</v>
+        <v>7.29</v>
       </c>
       <c r="C18" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="D18" t="n">
-        <v>6527345</v>
+        <v>2795669</v>
       </c>
       <c r="E18" t="n">
-        <v>74.40000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="F18" t="n">
-        <v>4.57</v>
+        <v>6.71</v>
       </c>
       <c r="G18" t="n">
-        <v>4.42</v>
+        <v>6.64</v>
       </c>
       <c r="H18" t="n">
-        <v>6.3</v>
+        <v>6.72</v>
       </c>
       <c r="I18" t="n">
-        <v>4.33</v>
+        <v>6.51</v>
       </c>
       <c r="J18" t="n">
-        <v>5.54</v>
+        <v>7.09</v>
       </c>
       <c r="K18" t="n">
         <v>0.37</v>
@@ -5894,115 +5976,115 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3817</v>
+        <v>6.3805</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.08</v>
+        <v>-12.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.55</v>
+        <v>7.56</v>
       </c>
       <c r="R18" t="n">
-        <v>4.45</v>
+        <v>6.3805</v>
       </c>
       <c r="S18" t="n">
-        <v>5.52</v>
+        <v>6.69</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.65</v>
+        <v>-8.23</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>7.88</v>
+        <v/>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7.9x vs 7.9x median — in-line</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>0.78</v>
+        <v>4.69</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.8x vs 0.8x median — in-line</t>
+          <t>4.7x vs 2.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>47.67</v>
+        <v>-5.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.83</v>
+        <v>16.35</v>
       </c>
       <c r="AC18" t="n">
         <v/>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/S 7.9x vs 7.9x median — in-line | P/B 0.8x vs 0.8x median — in-line | EV/EBITDA 47.7x vs -1.7x median — trading at discount | Analyst target $7.83</t>
+          <t>P/B 4.7x vs 2.0x median — trading at premium | EV/EBITDA -6.0x vs -0.8x median — trading at premium | Analyst target $16.35</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>2.39</v>
+        <v>5.06</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.94</v>
+        <v>9.52</v>
       </c>
       <c r="AG18" t="n">
-        <v>115.5</v>
+        <v>61.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.94</v>
+        <v>4.85</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.390000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.39–$8.94 (ann. vol 116%) | ATR range: $2.94–$8.39</t>
+          <t>1-SD 3mo range: $5.06–$9.52 (ann. vol 61%) | ATR range: $4.85–$9.73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.23</v>
+        <v>5.68</v>
       </c>
       <c r="C19" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="D19" t="n">
-        <v>2764625</v>
+        <v>6562368</v>
       </c>
       <c r="E19" t="n">
-        <v>62.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>6.7</v>
+        <v>4.57</v>
       </c>
       <c r="G19" t="n">
-        <v>6.63</v>
+        <v>4.43</v>
       </c>
       <c r="H19" t="n">
-        <v>6.72</v>
+        <v>6.3</v>
       </c>
       <c r="I19" t="n">
-        <v>6.51</v>
+        <v>4.33</v>
       </c>
       <c r="J19" t="n">
-        <v>7.09</v>
+        <v>5.54</v>
       </c>
       <c r="K19" t="n">
         <v>0.37</v>
@@ -6014,170 +6096,170 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6.3805</v>
+        <v>5.3817</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-11.75</v>
+        <v>-5.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.56</v>
+        <v>5.55</v>
       </c>
       <c r="R19" t="n">
-        <v>6.3805</v>
+        <v>4.45</v>
       </c>
       <c r="S19" t="n">
-        <v>6.69</v>
+        <v>5.52</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-7.47</v>
+        <v>-2.9</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v/>
+        <v>7.9</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>7.9x vs 7.9x median — in-line</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>4.65</v>
+        <v>0.79</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.7x vs 2.0x median — trading at premium</t>
+          <t>0.8x vs 0.8x median — in-line</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>-5.97</v>
+        <v>47.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>16.35</v>
+        <v>7.83</v>
       </c>
       <c r="AC19" t="n">
         <v/>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>P/B 4.7x vs 2.0x median — trading at premium | EV/EBITDA -6.0x vs -0.8x median — trading at premium | Analyst target $16.35</t>
+          <t>P/S 7.9x vs 7.9x median — in-line | P/B 0.8x vs 0.8x median — in-line | EV/EBITDA 47.7x vs -1.7x median — trading at discount | Analyst target $7.83</t>
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>5.02</v>
+        <v>2.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.44</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>61.2</v>
+        <v>115.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.79</v>
+        <v>2.96</v>
       </c>
       <c r="AI19" t="n">
-        <v>9.67</v>
+        <v>8.41</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $5.02–$9.44 (ann. vol 61%) | ATR range: $4.79–$9.67</t>
+          <t>1-SD 3mo range: $2.40–$8.97 (ann. vol 116%) | ATR range: $2.96–$8.41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>VBIO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.96</v>
+        <v>0.16</v>
       </c>
       <c r="C20" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="D20" t="n">
-        <v>3238630</v>
+        <v>3847033</v>
       </c>
       <c r="E20" t="n">
-        <v>61.9</v>
+        <v>33</v>
       </c>
       <c r="F20" t="n">
-        <v>3.46</v>
+        <v>0.23</v>
       </c>
       <c r="G20" t="n">
-        <v>3.62</v>
+        <v>0.39</v>
       </c>
       <c r="H20" t="n">
-        <v>3.91</v>
+        <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>3.63</v>
+        <v>0.38</v>
       </c>
       <c r="J20" t="n">
-        <v>4.05</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.47</v>
+        <v>0.1182</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-12.48</v>
+        <v>-28.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5609</v>
+        <v>0.1606</v>
       </c>
       <c r="R20" t="n">
-        <v>3.27</v>
+        <v>0.113</v>
       </c>
       <c r="S20" t="n">
-        <v>3.84</v>
+        <v>0.1166</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.15</v>
+        <v>-29.38</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>33.26</v>
+        <v>-8.01</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>33.3x vs 7.9x median — trading at premium</t>
+          <t>-8.0x vs 2.1x median — trading at discount</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>2.29</v>
+        <v>0.16</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.3x vs 0.8x median — trading at premium</t>
+          <t>0.2x vs 2.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>-8</v>
+        <v>-1.09</v>
       </c>
       <c r="AB20" t="n">
         <v/>
@@ -6187,117 +6269,117 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>P/S 33.3x vs 7.9x median — trading at premium | P/B 2.3x vs 0.8x median — trading at premium | EV/EBITDA -8.0x vs -1.7x median — trading at premium</t>
+          <t>P/S -8.0x vs 2.1x median — trading at discount | P/B 0.2x vs 2.0x median — trading at discount | EV/EBITDA -1.1x vs -0.8x median — trading at premium</t>
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>1.18</v>
+        <v>0.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>6.74</v>
+        <v>0.26</v>
       </c>
       <c r="AG20" t="n">
-        <v>140.4</v>
+        <v>122.9</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>-0.89</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.45</v>
+        <v>1.21</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.18–$6.74 (ann. vol 140%) | ATR range: $1.47–$6.45</t>
+          <t>1-SD 3mo range: $0.06–$0.26 (ann. vol 123%) | ATR range: $-0.89–$1.21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VBIO</t>
+          <t>PUSA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.16</v>
+        <v>3.95</v>
       </c>
       <c r="C21" t="n">
-        <v>2.79</v>
+        <v>3.01</v>
       </c>
       <c r="D21" t="n">
-        <v>3620687</v>
+        <v>3232533</v>
       </c>
       <c r="E21" t="n">
-        <v>31.7</v>
+        <v>61.7</v>
       </c>
       <c r="F21" t="n">
-        <v>0.23</v>
+        <v>3.46</v>
       </c>
       <c r="G21" t="n">
-        <v>0.39</v>
+        <v>3.62</v>
       </c>
       <c r="H21" t="n">
-        <v>1.07</v>
+        <v>3.91</v>
       </c>
       <c r="I21" t="n">
-        <v>0.38</v>
+        <v>3.63</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>4.05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1182</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-24.47</v>
+        <v>-12.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1606</v>
+        <v>3.5609</v>
       </c>
       <c r="R21" t="n">
-        <v>0.113</v>
+        <v>3.27</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1166</v>
+        <v>3.84</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-25.5</v>
+        <v>-2.78</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>-7.61</v>
+        <v>33.05</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>-7.6x vs 2.1x median — trading at discount</t>
+          <t>33.1x vs 7.9x median — trading at premium</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>0.15</v>
+        <v>2.28</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.2x vs 2.0x median — trading at discount</t>
+          <t>2.3x vs 0.8x median — trading at premium</t>
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>-1.09</v>
+        <v>-8</v>
       </c>
       <c r="AB21" t="n">
         <v/>
@@ -6307,27 +6389,27 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>P/S -7.6x vs 2.1x median — trading at discount | P/B 0.2x vs 2.0x median — trading at discount | EV/EBITDA -1.1x vs -0.8x median — trading at premium</t>
+          <t>P/S 33.1x vs 7.9x median — trading at premium | P/B 2.3x vs 0.8x median — trading at premium | EV/EBITDA -8.0x vs -1.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>0.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.25</v>
+        <v>6.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>122</v>
+        <v>140.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.89</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.2</v>
+        <v>6.44</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.06–$0.25 (ann. vol 122%) | ATR range: $-0.89–$1.20</t>
+          <t>1-SD 3mo range: $1.18–$6.72 (ann. vol 140%) | ATR range: $1.46–$6.44</t>
         </is>
       </c>
     </row>
@@ -6338,16 +6420,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="C22" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="D22" t="n">
-        <v>2193194</v>
+        <v>2215067</v>
       </c>
       <c r="E22" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="F22" t="n">
         <v>0.77</v>
@@ -6380,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>7.09</v>
+        <v>6.04</v>
       </c>
       <c r="Q22" t="n">
         <v>0.7035</v>
@@ -6395,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.51</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="b">
         <v>1</v>
@@ -6434,20 +6516,20 @@
         <v>0.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AG22" t="n">
         <v>187</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AI22" t="n">
         <v>1.34</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.04–$1.26 (ann. vol 187%) | ATR range: $-0.03–$1.34</t>
+          <t>1-SD 3mo range: $0.04–$1.28 (ann. vol 187%) | ATR range: $-0.02–$1.34</t>
         </is>
       </c>
     </row>
@@ -6458,16 +6540,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="C23" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="D23" t="n">
-        <v>1812107</v>
+        <v>1825471</v>
       </c>
       <c r="E23" t="n">
-        <v>65.7</v>
+        <v>66.2</v>
       </c>
       <c r="F23" t="n">
         <v>0.87</v>
@@ -6500,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>1.12</v>
@@ -6515,13 +6597,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="V23" t="b">
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -6529,7 +6611,7 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>-1.36</v>
+        <v>-1.37</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -6554,20 +6636,20 @@
         <v>0.42</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
         <v>121.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AI23" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.42–$1.69 (ann. vol 121%) | ATR range: $0.44–$1.67</t>
+          <t>1-SD 3mo range: $0.42–$1.70 (ann. vol 121%) | ATR range: $0.45–$1.67</t>
         </is>
       </c>
     </row>
@@ -6578,16 +6660,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.79</v>
+        <v>10.77</v>
       </c>
       <c r="C24" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="D24" t="n">
-        <v>4288757</v>
+        <v>4283893</v>
       </c>
       <c r="E24" t="n">
-        <v>65.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>9.84</v>
@@ -6620,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.93</v>
+        <v>-5.76</v>
       </c>
       <c r="Q24" t="n">
         <v>10.43</v>
@@ -6635,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.82</v>
+        <v>-4.64</v>
       </c>
       <c r="V24" t="b">
         <v>1</v>
@@ -6671,23 +6753,23 @@
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
       <c r="AF24" t="n">
-        <v>15.23</v>
+        <v>15.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.06</v>
+        <v>6.04</v>
       </c>
       <c r="AI24" t="n">
-        <v>15.52</v>
+        <v>15.5</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $6.35–$15.23 (ann. vol 82%) | ATR range: $6.06–$15.52</t>
+          <t>1-SD 3mo range: $6.34–$15.20 (ann. vol 82%) | ATR range: $6.04–$15.50</t>
         </is>
       </c>
     </row>
@@ -6698,16 +6780,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="C25" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="D25" t="n">
-        <v>570383</v>
+        <v>573574</v>
       </c>
       <c r="E25" t="n">
-        <v>45.3</v>
+        <v>46.2</v>
       </c>
       <c r="F25" t="n">
         <v>4.05</v>
@@ -6740,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.76</v>
+        <v>0.25</v>
       </c>
       <c r="Q25" t="n">
         <v>4.7</v>
@@ -6755,7 +6837,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.79</v>
+        <v>-5.26</v>
       </c>
       <c r="V25" t="b">
         <v>1</v>
@@ -6769,7 +6851,7 @@
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -6791,23 +6873,23 @@
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AF25" t="n">
-        <v>5.34</v>
+        <v>5.37</v>
       </c>
       <c r="AG25" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.45</v>
+        <v>6.47</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.60–$5.34 (ann. vol 69%) | ATR range: $1.49–$6.45</t>
+          <t>1-SD 3mo range: $2.61–$5.37 (ann. vol 69%) | ATR range: $1.51–$6.47</t>
         </is>
       </c>
     </row>
@@ -6821,13 +6903,13 @@
         <v>0.62</v>
       </c>
       <c r="C26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="D26" t="n">
-        <v>1566943</v>
+        <v>1574158</v>
       </c>
       <c r="E26" t="n">
-        <v>67.3</v>
+        <v>67.5</v>
       </c>
       <c r="F26" t="n">
         <v>0.49</v>
@@ -6860,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.5</v>
+        <v>-0.84</v>
       </c>
       <c r="Q26" t="n">
         <v>0.6183</v>
@@ -6875,13 +6957,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="b">
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -6889,7 +6971,7 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -6914,7 +6996,7 @@
         <v>0.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AG26" t="n">
         <v>101.9</v>
@@ -6927,7 +7009,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.30–$0.93 (ann. vol 102%) | ATR range: $0.15–$1.09</t>
+          <t>1-SD 3mo range: $0.30–$0.94 (ann. vol 102%) | ATR range: $0.15–$1.09</t>
         </is>
       </c>
     </row>
@@ -6938,16 +7020,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="C27" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="D27" t="n">
-        <v>2443734</v>
+        <v>2477057</v>
       </c>
       <c r="E27" t="n">
-        <v>74</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F27" t="n">
         <v>1.17</v>
@@ -6980,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>6.99</v>
+        <v>5.88</v>
       </c>
       <c r="Q27" t="n">
         <v>1.76</v>
@@ -6995,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.02</v>
+        <v>-1.06</v>
       </c>
       <c r="V27" t="b">
         <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -7009,11 +7091,11 @@
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1.9x vs 0.9x median — trading at premium</t>
+          <t>2.0x vs 0.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -7027,27 +7109,27 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>P/S 4.3x vs 4.2x median — in-line | P/B 1.9x vs 0.9x median — trading at premium | EV/EBITDA -17.9x vs -2.7x median — trading at premium</t>
+          <t>P/S 4.3x vs 4.2x median — in-line | P/B 2.0x vs 0.9x median — trading at premium | EV/EBITDA -17.9x vs -2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AG27" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.84–$2.03 (ann. vol 83%) | ATR range: $0.70–$2.17</t>
+          <t>1-SD 3mo range: $0.85–$2.04 (ann. vol 83%) | ATR range: $0.71–$2.18</t>
         </is>
       </c>
     </row>
@@ -7061,13 +7143,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="D28" t="n">
-        <v>648064</v>
+        <v>650809</v>
       </c>
       <c r="E28" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
       <c r="F28" t="n">
         <v>0.73</v>
@@ -7100,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-6.75</v>
+        <v>-7.13</v>
       </c>
       <c r="Q28" t="n">
         <v>0.68</v>
@@ -7115,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>4.21</v>
+        <v>3.79</v>
       </c>
       <c r="V28" t="b">
         <v>1</v>
@@ -7129,7 +7211,7 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -7154,7 +7236,7 @@
         <v>0.23</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AG28" t="n">
         <v>134.1</v>
@@ -7167,247 +7249,247 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.23–$1.15 (ann. vol 134%) | ATR range: $0.10–$1.28</t>
+          <t>1-SD 3mo range: $0.23–$1.16 (ann. vol 134%) | ATR range: $0.10–$1.28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BTOG</t>
+          <t>NGEN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.16</v>
+        <v>1.97</v>
       </c>
       <c r="C29" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="D29" t="n">
-        <v>1242028</v>
+        <v>799069</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>4.11</v>
+        <v>1.76</v>
       </c>
       <c r="G29" t="n">
-        <v>5.53</v>
+        <v>1.95</v>
       </c>
       <c r="H29" t="n">
-        <v>29.85</v>
+        <v>2.83</v>
       </c>
       <c r="I29" t="n">
-        <v>5.55</v>
+        <v>1.82</v>
       </c>
       <c r="J29" t="n">
-        <v>24.98</v>
+        <v>3.38</v>
       </c>
       <c r="K29" t="n">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9999</v>
+        <v>1.8896</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>23.45</v>
+        <v>-4.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.85</v>
+        <v>1.8896</v>
       </c>
       <c r="R29" t="n">
-        <v>3.4575</v>
+        <v>1.6303</v>
       </c>
       <c r="S29" t="n">
-        <v>3.63</v>
+        <v>1.87</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>12.04</v>
+        <v>-5.08</v>
       </c>
       <c r="V29" t="b">
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>68.27</v>
+        <v/>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>68.3x vs 4.2x median — trading at premium</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>-0.88</v>
+        <v>14.61</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>-0.9x vs 0.9x median — trading at discount</t>
+          <t>14.6x vs 2.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA29" t="n">
-        <v/>
+        <v>-3.51</v>
       </c>
       <c r="AB29" t="n">
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC29" t="n">
         <v/>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>P/S 68.3x vs 4.2x median — trading at premium | P/B -0.9x vs 0.9x median — trading at discount</t>
+          <t>P/B 14.6x vs 2.0x median — trading at premium | EV/EBITDA -3.5x vs -0.8x median — trading at premium | Analyst target $10.00</t>
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF29" t="n">
-        <v>5.17</v>
+        <v>2.87</v>
       </c>
       <c r="AG29" t="n">
-        <v>127.3</v>
+        <v>91.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.53</v>
+        <v>2.71</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.15–$5.17 (ann. vol 127%) | ATR range: $-1.21–$7.53</t>
+          <t>1-SD 3mo range: $1.07–$2.87 (ann. vol 91%) | ATR range: $1.23–$2.71</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NGEN</t>
+          <t>BTOG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.95</v>
+        <v>3.24</v>
       </c>
       <c r="C30" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>788185</v>
+        <v>1275855</v>
       </c>
       <c r="E30" t="n">
-        <v>65.5</v>
+        <v>30.8</v>
       </c>
       <c r="F30" t="n">
-        <v>1.76</v>
+        <v>4.12</v>
       </c>
       <c r="G30" t="n">
-        <v>1.95</v>
+        <v>5.54</v>
       </c>
       <c r="H30" t="n">
-        <v>2.83</v>
+        <v>29.85</v>
       </c>
       <c r="I30" t="n">
-        <v>1.82</v>
+        <v>5.55</v>
       </c>
       <c r="J30" t="n">
-        <v>3.38</v>
+        <v>24.98</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.8896</v>
+        <v>3.9999</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-3.1</v>
+        <v>23.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.8896</v>
+        <v>6.85</v>
       </c>
       <c r="R30" t="n">
-        <v>1.6303</v>
+        <v>3.4575</v>
       </c>
       <c r="S30" t="n">
-        <v>1.87</v>
+        <v>3.63</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>-4.1</v>
+        <v>11.86</v>
       </c>
       <c r="V30" t="b">
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v/>
+        <v>68.37</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>68.4x vs 4.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>14.46</v>
+        <v>-0.88</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14.5x vs 2.0x median — trading at premium</t>
+          <t>-0.9x vs 0.9x median — trading at discount</t>
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>-3.51</v>
+        <v/>
       </c>
       <c r="AB30" t="n">
-        <v>10</v>
+        <v/>
       </c>
       <c r="AC30" t="n">
         <v/>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>P/B 14.5x vs 2.0x median — trading at premium | EV/EBITDA -3.5x vs -0.8x median — trading at premium | Analyst target $10.00</t>
+          <t>P/S 68.4x vs 4.2x median — trading at premium | P/B -0.9x vs 0.9x median — trading at discount</t>
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.84</v>
+        <v>5.31</v>
       </c>
       <c r="AG30" t="n">
-        <v>91.09999999999999</v>
+        <v>127</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.21</v>
+        <v>-1.12</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.69</v>
+        <v>7.61</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.06–$2.84 (ann. vol 91%) | ATR range: $1.21–$2.69</t>
+          <t>1-SD 3mo range: $1.18–$5.31 (ann. vol 127%) | ATR range: $-1.12–$7.61</t>
         </is>
       </c>
     </row>
@@ -7421,10 +7503,10 @@
         <v>1.75</v>
       </c>
       <c r="C31" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="D31" t="n">
-        <v>861907</v>
+        <v>861999</v>
       </c>
       <c r="E31" t="n">
         <v>54.7</v>
@@ -7538,16 +7620,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11.38</v>
+        <v>11.39</v>
       </c>
       <c r="C32" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="D32" t="n">
-        <v>7005794</v>
+        <v>7036902</v>
       </c>
       <c r="E32" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="F32" t="n">
         <v>11.98</v>
@@ -7559,7 +7641,7 @@
         <v>9.25</v>
       </c>
       <c r="I32" t="n">
-        <v>10.75</v>
+        <v>10.76</v>
       </c>
       <c r="J32" t="n">
         <v>8.460000000000001</v>
@@ -7580,7 +7662,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>19.06</v>
+        <v>18.33</v>
       </c>
       <c r="Q32" t="n">
         <v>14.6</v>
@@ -7595,25 +7677,25 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>20.39</v>
+        <v>19.65</v>
       </c>
       <c r="V32" t="b">
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>2.2x vs 0.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>0.5x vs 0.5x median — in-line</t>
         </is>
       </c>
       <c r="AA32" t="n">
@@ -7627,27 +7709,27 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Analyst target $11.40</t>
+          <t>P/S 2.2x vs 0.2x median — trading at premium | P/B 0.5x vs 0.5x median — in-line | EV/EBITDA 2.0x vs 2.0x median — in-line | Analyst target $11.40</t>
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>8.039999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.71</v>
+        <v>14.72</v>
       </c>
       <c r="AG32" t="n">
         <v>58.7</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="AI32" t="n">
-        <v>18.6</v>
+        <v>18.61</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $8.04–$14.71 (ann. vol 59%) | ATR range: $4.15–$18.60</t>
+          <t>1-SD 3mo range: $8.05–$14.72 (ann. vol 59%) | ATR range: $4.16–$18.61</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7746,7 @@
         <v>1.86</v>
       </c>
       <c r="D33" t="n">
-        <v>635948</v>
+        <v>636035</v>
       </c>
       <c r="E33" t="n">
         <v>48.3</v>
@@ -7778,16 +7860,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="D34" t="n">
-        <v>824377</v>
+        <v>829520</v>
       </c>
       <c r="E34" t="n">
-        <v>51.7</v>
+        <v>52.1</v>
       </c>
       <c r="F34" t="n">
         <v>0.95</v>
@@ -7820,7 +7902,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-8.710000000000001</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="Q34" t="n">
         <v>0.9194</v>
@@ -7835,21 +7917,21 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>-6.38</v>
+        <v>-6.82</v>
       </c>
       <c r="V34" t="b">
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>152.14</v>
+        <v>152.86</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>152.1x vs 2.1x median — trading at premium</t>
+          <t>152.9x vs 2.1x median — trading at premium</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -7867,14 +7949,14 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>P/S 152.1x vs 2.1x median — trading at premium | P/B 2.6x vs 2.0x median — trading at premium | EV/EBITDA -0.8x vs -0.8x median — in-line | Analyst target $5.10</t>
+          <t>P/S 152.9x vs 2.1x median — trading at premium | P/B 2.6x vs 2.0x median — trading at premium | EV/EBITDA -0.8x vs -0.8x median — in-line | Analyst target $5.10</t>
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG34" t="n">
         <v>90.7</v>
@@ -7883,11 +7965,11 @@
         <v>0.38</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.54–$1.44 (ann. vol 91%) | ATR range: $0.38–$1.61</t>
+          <t>1-SD 3mo range: $0.55–$1.45 (ann. vol 91%) | ATR range: $0.38–$1.62</t>
         </is>
       </c>
     </row>
@@ -7898,16 +7980,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="C35" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="D35" t="n">
-        <v>2226528</v>
+        <v>2232272</v>
       </c>
       <c r="E35" t="n">
-        <v>28.6</v>
+        <v>28.9</v>
       </c>
       <c r="F35" t="n">
         <v>2.31</v>
@@ -7940,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
         <v>2.26</v>
@@ -7955,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="V35" t="b">
         <v>1</v>
@@ -7969,7 +8051,7 @@
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -7991,7 +8073,7 @@
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
         <v>2.73</v>
@@ -8003,11 +8085,11 @@
         <v>1.4</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.56–$2.73 (ann. vol 54%) | ATR range: $1.40–$2.89</t>
+          <t>1-SD 3mo range: $1.57–$2.73 (ann. vol 54%) | ATR range: $1.40–$2.90</t>
         </is>
       </c>
     </row>
@@ -8018,16 +8100,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="C36" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="D36" t="n">
-        <v>740309</v>
+        <v>738816</v>
       </c>
       <c r="E36" t="n">
-        <v>41.3</v>
+        <v>40</v>
       </c>
       <c r="F36" t="n">
         <v>2.37</v>
@@ -8060,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="Q36" t="n">
         <v>2.39</v>
@@ -8075,17 +8157,17 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="V36" t="b">
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>8.2x vs 4.2x median — trading at premium</t>
+          <t>8.1x vs 4.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -8107,27 +8189,27 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>P/S 8.2x vs 4.2x median — trading at premium | P/B 0.9x vs 0.9x median — in-line | Graham # $3.20</t>
+          <t>P/S 8.1x vs 4.2x median — trading at premium | P/B 0.9x vs 0.9x median — in-line | Graham # $3.20</t>
         </is>
       </c>
       <c r="AE36" t="n">
         <v>2.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AG36" t="n">
         <v>12</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AI36" t="n">
         <v>2.54</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.20–$2.49 (ann. vol 12%) | ATR range: $2.15–$2.54</t>
+          <t>1-SD 3mo range: $2.20–$2.48 (ann. vol 12%) | ATR range: $2.14–$2.54</t>
         </is>
       </c>
     </row>
@@ -8138,16 +8220,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="C37" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="D37" t="n">
-        <v>1362416</v>
+        <v>1369722</v>
       </c>
       <c r="E37" t="n">
-        <v>58.3</v>
+        <v>58.6</v>
       </c>
       <c r="F37" t="n">
         <v>2.19</v>
@@ -8180,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="Q37" t="n">
         <v>2.6884</v>
@@ -8195,13 +8277,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>8.06</v>
+        <v>7.85</v>
       </c>
       <c r="V37" t="b">
         <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -8209,7 +8291,7 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -8231,23 +8313,23 @@
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AF37" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="AG37" t="n">
         <v>140.8</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.73–$4.23 (ann. vol 141%) | ATR range: $0.68–$4.28</t>
+          <t>1-SD 3mo range: $0.74–$4.24 (ann. vol 141%) | ATR range: $0.69–$4.29</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8346,7 @@
         <v>1.63</v>
       </c>
       <c r="D38" t="n">
-        <v>3779700</v>
+        <v>3781150</v>
       </c>
       <c r="E38" t="n">
         <v>77</v>
@@ -8300,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-2.79</v>
+        <v>-2.68</v>
       </c>
       <c r="Q38" t="n">
         <v>4.14</v>
@@ -8315,21 +8397,21 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="b">
         <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>8.5x vs 4.2x median — trading at premium</t>
+          <t>8.4x vs 4.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>-10.44</v>
+        <v>-10.43</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -8347,7 +8429,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>P/S 8.5x vs 4.2x median — trading at premium | P/B -10.4x vs 0.9x median — trading at discount | EV/EBITDA -1.9x vs -2.7x median — trading at discount | Analyst target $5.85</t>
+          <t>P/S 8.4x vs 4.2x median — trading at premium | P/B -10.4x vs 0.9x median — trading at discount | EV/EBITDA -1.9x vs -2.7x median — trading at discount | Analyst target $5.85</t>
         </is>
       </c>
       <c r="AE38" t="n">
@@ -8378,16 +8460,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="C39" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="D39" t="n">
-        <v>693328</v>
+        <v>705709</v>
       </c>
       <c r="E39" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="F39" t="n">
         <v>0.64</v>
@@ -8420,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-13.95</v>
+        <v>-15.37</v>
       </c>
       <c r="Q39" t="n">
         <v>1.1599</v>
@@ -8435,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>-17.5</v>
+        <v>-18.86</v>
       </c>
       <c r="V39" t="b">
         <v>1</v>
@@ -8445,11 +8527,11 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.3x vs 0.8x median — trading at discount</t>
+          <t>0.3x vs 0.7x median — trading at discount</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -8467,27 +8549,147 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>P/S 0.3x vs 0.8x median — trading at discount | P/B 3.3x vs 2.7x median — trading at premium | EV/EBITDA -5.7x vs -1.5x median — trading at premium | Analyst target $4.53</t>
+          <t>P/S 0.3x vs 0.7x median — trading at discount | P/B 3.3x vs 2.7x median — trading at premium | EV/EBITDA -5.7x vs -1.5x median — trading at premium | Analyst target $4.53</t>
         </is>
       </c>
       <c r="AE39" t="n">
         <v>0.24</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AG39" t="n">
-        <v>132.7</v>
+        <v>132.9</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.24–$1.17 (ann. vol 133%) | ATR range: $-0.13–$1.54</t>
+          <t>1-SD 3mo range: $0.24–$1.19 (ann. vol 133%) | ATR range: $-0.12–$1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>REAX</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13089185</v>
+      </c>
+      <c r="E40" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.6485</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.8492</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>0.2x vs 0.2x median — in-line</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>6.2x vs 0.5x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>-387.98</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AC40" t="n">
+        <v/>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>P/S 0.2x vs 0.2x median — in-line | P/B 6.2x vs 0.5x median — trading at premium | EV/EBITDA -388.0x vs 2.0x median — trading at discount | Analyst target $4.95</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $1.47–$2.98 (ann. vol 68%) | ATR range: $0.61–$3.84</t>
         </is>
       </c>
     </row>
@@ -9136,17 +9338,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>VBIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>8-K/A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -9156,12 +9358,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0001493152-26-038731</t>
+          <t>0001683168-26-006632</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>valion_8ka1.htm</t>
         </is>
       </c>
     </row>
@@ -9173,12 +9375,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8-K/A</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9188,19 +9390,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0001683168-26-006632</t>
+          <t>0001683168-26-006501</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>valion_8ka1.htm</t>
+          <t>valion_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VBIO</t>
+          <t>PUSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9220,12 +9422,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0001683168-26-006501</t>
+          <t>0001493152-26-038731</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>valion_8k.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X40"/>
+  <dimension ref="A1:AB43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,10 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,6 +580,26 @@
           <t>has_extended_data</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>first_seen_date</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>consecutive_runs</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>score_trend</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>prev_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -589,10 +613,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -614,7 +638,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.2pts)</t>
+          <t>2026-08-20 8-K (material_event, +6.0pts)   Item 1.01 (entry_agreement, +3) | Item 1.02 (termination_agreement, +1)   Title: &amp;#160;Entry into a Material Definitive Agreement.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -626,7 +650,7 @@
         <v>10.8</v>
       </c>
       <c r="N2" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
         <v>64.59999999999999</v>
@@ -658,11 +682,24 @@
       <c r="X2" t="b">
         <v>1</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RMAX</t>
+          <t>XPON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -671,16 +708,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.359999999999999</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -691,78 +728,91 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.4pts) | 2026-08-20 8-K (material_event, +1.2pts) | 2026-08-14 8-K (material_event, +0.0pts)</t>
+          <t>2026-08-24 8-K (material_event, +8.0pts)   Item 1.01 (entry_agreement, +3) | Item 5.02 (officer_departure, -1)   Title: Entry Into a Material Definitive Agreement.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11.39</v>
+        <v>7.19</v>
       </c>
       <c r="N3" t="n">
-        <v>1.94</v>
+        <v>16.9</v>
       </c>
       <c r="O3" t="n">
-        <v>48</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>13.46</v>
+        <v>3.4406</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>18.33</v>
+        <v>-52.13</v>
       </c>
       <c r="S3" t="n">
-        <v>13.61</v>
+        <v>8.41</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>19.65</v>
+        <v>17</v>
       </c>
       <c r="V3" t="n">
-        <v>14.6</v>
+        <v>4.15</v>
       </c>
       <c r="W3" t="n">
-        <v>13.0381</v>
+        <v>3.41</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRBS</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.3</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -773,60 +823,73 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-1.2</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-17 8-K (material_event, +0.6pts)</t>
+          <t>2026-08-21 8-K (material_event, +1.4pts)   Items: 7.01, 9.01 (routine) | 2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine) | 2026-08-14 8-K (material_event, +0.0pts)   Items: 5.07, 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>trend_alignment +4, golden_cross +2, rsi_mild_high +1</t>
+          <t>trend_alignment +3, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>11.33</v>
       </c>
       <c r="N4" t="n">
-        <v>0.66</v>
+        <v>1.99</v>
       </c>
       <c r="O4" t="n">
-        <v>67.8</v>
+        <v>47.6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>13.46</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.27</v>
+        <v>18.96</v>
       </c>
       <c r="S4" t="n">
-        <v>3.98</v>
+        <v>13.61</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.76</v>
+        <v>20.28</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>14.6</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9</v>
+        <v>13.0381</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FUSB</t>
+          <t>BRBS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -835,80 +898,93 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v/>
+        <v>-1.1</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-17 8-K (material_event, +0.6pts)   Items: 7.01 (routine)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, golden_cross +2, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16.08</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>9.26</v>
+        <v>0.68</v>
       </c>
       <c r="O5" t="n">
-        <v>40.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>16.42</v>
+        <v>3.9</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.11</v>
+        <v>-1.39</v>
       </c>
       <c r="S5" t="n">
-        <v/>
+        <v>3.98</v>
       </c>
       <c r="T5" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v/>
+        <v>0.63</v>
       </c>
       <c r="V5" t="n">
-        <v>16.7243</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>16.24</v>
+        <v>3.9</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>FRMM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -917,13 +993,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -933,16 +1009,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v/>
+        <v>-0.2</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 8-K (material_event, +0.7pts)   Item 5.02 (officer_departure, -1) | 2026-08-19 8-K (material_event, +1.0pts)   Items: 5.07, 9.01 (routine) | 2026-08-14 4 (insider_other, +0.0pts) | 2026-08-14 4 (insider_other, +0.0pts)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -951,46 +1027,59 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7.29</v>
+        <v>6.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>1.54</v>
       </c>
       <c r="O6" t="n">
-        <v>63.7</v>
+        <v>53.9</v>
       </c>
       <c r="P6" t="n">
-        <v>6.3805</v>
+        <v>5.76</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-12.48</v>
+        <v>-5.27</v>
       </c>
       <c r="S6" t="n">
-        <v>6.69</v>
+        <v>5.61</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-8.23</v>
+        <v>-7.74</v>
       </c>
       <c r="V6" t="n">
-        <v>7.56</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>6.3805</v>
+        <v>5.3</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FLUX</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,16 +1088,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.25</v>
+        <v>5.55</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1019,60 +1108,73 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-12.8</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.2pts)</t>
+          <t>2026-08-17 4 (insider_buy, +0.9pts)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.71</v>
+        <v>10.73</v>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>54.6</v>
+        <v>65.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6049</v>
+        <v>10.15</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-15.37</v>
+        <v>-5.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0.58</v>
+        <v>10.27</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-18.86</v>
+        <v>-4.33</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1599</v>
+        <v>10.43</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5800999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1081,80 +1183,93 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>31.7</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-17 8-K (material_event, +0.6pts)</t>
+          <t>2026-08-17 4 (insider_buy, +0.9pts) | 2026-08-17 4 (insider_buy, +0.9pts) | 2026-08-17 4 (insider_buy, +0.9pts)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3.95</v>
+        <v>5.64</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="O8" t="n">
-        <v>61.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>3.47</v>
+        <v>5.3817</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-12.15</v>
+        <v>-4.41</v>
       </c>
       <c r="S8" t="n">
-        <v>3.84</v>
+        <v>5.52</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.78</v>
+        <v>-1.95</v>
       </c>
       <c r="V8" t="n">
-        <v>3.5609</v>
+        <v>5.55</v>
       </c>
       <c r="W8" t="n">
-        <v>3.27</v>
+        <v>4.45</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BACC</t>
+          <t>FUSB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1163,7 +1278,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1172,7 +1287,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1193,26 +1308,26 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>10.46</v>
+        <v>16.08</v>
       </c>
       <c r="N9" t="n">
-        <v>13.33</v>
+        <v>9.26</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>40.6</v>
       </c>
       <c r="P9" t="n">
-        <v>10.48</v>
+        <v>16.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.19</v>
+        <v>2.11</v>
       </c>
       <c r="S9" t="n">
         <v/>
@@ -1224,19 +1339,32 @@
         <v/>
       </c>
       <c r="V9" t="n">
-        <v>10.53</v>
+        <v>16.7243</v>
       </c>
       <c r="W9" t="n">
-        <v>10.48</v>
+        <v>16.24</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1245,80 +1373,93 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v/>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-17 4 (insider_other, +0.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_mild_high +1</t>
+          <t>trend_alignment +3, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>10.77</v>
+        <v>7.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3.17</v>
       </c>
       <c r="O10" t="n">
-        <v>65.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="P10" t="n">
-        <v>10.15</v>
+        <v>6.3805</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-5.76</v>
+        <v>-12.6</v>
       </c>
       <c r="S10" t="n">
-        <v>10.27</v>
+        <v>6.69</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.64</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>10.43</v>
+        <v>7.56</v>
       </c>
       <c r="W10" t="n">
-        <v>9.84</v>
+        <v>6.3805</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OKUR</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1327,80 +1468,93 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v/>
+        <v>48.8</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine)   Title: &gt;pmi20260814_8k.htm</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3.99</v>
+        <v>4.51</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>12.79</v>
       </c>
       <c r="O11" t="n">
-        <v>46.2</v>
+        <v>63.6</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>4.7092</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.25</v>
+        <v>4.65</v>
       </c>
       <c r="S11" t="n">
-        <v>3.78</v>
+        <v>4.3402</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.26</v>
+        <v>-3.55</v>
       </c>
       <c r="V11" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8001</v>
+        <v>3.03</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>FLUX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1409,344 +1563,396 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v/>
+        <v>-12.8</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-20 8-K (material_event, +1.2pts)   Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2.34</v>
+        <v>0.72</v>
       </c>
       <c r="N12" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="O12" t="n">
-        <v>40</v>
+        <v>54.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>0.6049</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.43</v>
+        <v>-14.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.35</v>
+        <v>0.58</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.43</v>
+        <v>-18</v>
       </c>
       <c r="V12" t="n">
-        <v>2.39</v>
+        <v>1.1599</v>
       </c>
       <c r="W12" t="n">
-        <v>2.35</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>PUSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Moved</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>10.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.2pts)</t>
+          <t>2026-08-17 8-K (material_event, +0.6pts)   Items: 8.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.45</v>
+        <v>3.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.26</v>
+        <v>3.01</v>
       </c>
       <c r="O13" t="n">
-        <v>74.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>5.88</v>
+        <v>-12.59</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4297</v>
+        <v>3.84</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.06</v>
+        <v>-3.27</v>
       </c>
       <c r="V13" t="n">
-        <v>1.76</v>
+        <v>3.5609</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>3.27</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VBIO</t>
+          <t>BACC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-11.5</v>
+        <v/>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K/A (material_event, +1.2pts) | 2026-08-17 8-K (material_event, +0.6pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.16</v>
+        <v>10.46</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>13.33</v>
       </c>
       <c r="O14" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1182</v>
+        <v>10.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>-28.41</v>
+        <v>0.19</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1166</v>
+        <v/>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="U14" t="n">
-        <v>-29.38</v>
+        <v/>
       </c>
       <c r="V14" t="n">
-        <v>0.1606</v>
+        <v>10.53</v>
       </c>
       <c r="W14" t="n">
-        <v>0.113</v>
+        <v>10.48</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XPON</t>
+          <t>OKUR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, +2.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>7.16</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>16.89</v>
+        <v>2.49</v>
       </c>
       <c r="O15" t="n">
-        <v>75.3</v>
+        <v>44.6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.4406</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-51.54</v>
+        <v>1.14</v>
       </c>
       <c r="S15" t="n">
-        <v>8.41</v>
+        <v>3.78</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>18.45</v>
+        <v>-4.42</v>
       </c>
       <c r="V15" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="W15" t="n">
-        <v>3.41</v>
+        <v>3.8001</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>DHF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1767,50 +1973,63 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3.51</v>
+        <v>2.34</v>
       </c>
       <c r="N16" t="n">
-        <v>15.74</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>48.3</v>
+        <v>40</v>
       </c>
       <c r="P16" t="n">
-        <v>4.01</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>14.28</v>
+        <v>0.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3.98</v>
+        <v>2.35</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>13.42</v>
+        <v>0.43</v>
       </c>
       <c r="V16" t="n">
-        <v>4.07</v>
+        <v>2.39</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1819,80 +2038,93 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v/>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="N17" t="n">
-        <v>4.36</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
-        <v>50.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.11</v>
+        <v>7.02</v>
       </c>
       <c r="S17" t="n">
-        <v>1.24</v>
+        <v>1.4297</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>13.24</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9236</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>BCTX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1917,64 +2149,77 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v/>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-14 4 (insider_other, +0.0pts) | 2026-08-14 4 (insider_other, +0.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.37</v>
+        <v>15.74</v>
       </c>
       <c r="O18" t="n">
-        <v>67.59999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>4.01</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-16.63</v>
+        <v>14.57</v>
       </c>
       <c r="S18" t="n">
-        <v>1.68</v>
+        <v>4.01</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-16.63</v>
+        <v>14.57</v>
       </c>
       <c r="V18" t="n">
-        <v>1.74</v>
+        <v>4.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5202</v>
+        <v>3.5</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LSTA</t>
+          <t>VBIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,77 +2231,90 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v/>
+        <v>-8.1</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-20 8-K/A (material_event, +1.2pts)   Items: 5.07 (routine)   Title: &gt;Tivic Health Systems, Inc. Form 8-K | 2026-08-17 8-K (material_event, +0.3pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)   Title: &gt;Tivic Health Systems, Inc. Form 8-K</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.75</v>
+        <v>0.17</v>
       </c>
       <c r="N19" t="n">
-        <v>1.94</v>
+        <v>3.52</v>
       </c>
       <c r="O19" t="n">
-        <v>54.7</v>
+        <v>34.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>0.1182</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-5.14</v>
+        <v>-32.73</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6284</v>
+        <v>0.1166</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.95</v>
+        <v>-33.64</v>
       </c>
       <c r="V19" t="n">
-        <v>1.66</v>
+        <v>0.1606</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0.113</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZVIA</t>
+          <t>NPWR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2071,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -2081,64 +2339,77 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v/>
+        <v>2.3</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-14 4 (insider_sell, -0.0pts) | 2026-08-14 4 (insider_sell, -0.0pts)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
-        <v>48.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-8.710000000000001</v>
+        <v>-15.37</v>
       </c>
       <c r="S20" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-7.32</v>
+        <v>-15.37</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="W20" t="n">
-        <v>1.27</v>
+        <v>1.5202</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRDF</t>
+          <t>LSTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2153,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -2181,46 +2452,59 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="N21" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>52.1</v>
+        <v>55</v>
       </c>
       <c r="P21" t="n">
-        <v>0.907</v>
+        <v>1.66</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-9.140000000000001</v>
+        <v>-5.68</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9301</v>
+        <v>1.6284</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.82</v>
+        <v>-7.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9194</v>
+        <v>1.66</v>
       </c>
       <c r="W21" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REAX</t>
+          <t>CRDF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2235,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -2263,46 +2547,59 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2.22</v>
+        <v>0.99</v>
       </c>
       <c r="N22" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="O22" t="n">
-        <v>50.7</v>
+        <v>51.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.6485</v>
+        <v>0.907</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>19.03</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>0.9301</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>18.2</v>
+        <v>-6.39</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8492</v>
+        <v>0.9194</v>
       </c>
       <c r="W22" t="n">
-        <v>2.59</v>
+        <v>0.88</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>PLCE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2311,80 +2608,93 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Moved</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v/>
+        <v>11.9</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-14 8-K (material_event, +0.0pts)   Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>2.73</v>
       </c>
       <c r="N23" t="n">
-        <v>19.64</v>
+        <v>1.66</v>
       </c>
       <c r="O23" t="n">
-        <v>70.40000000000001</v>
+        <v>55.3</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6845</v>
+        <v>2.4622</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-35.41</v>
+        <v>-10.14</v>
       </c>
       <c r="S23" t="n">
-        <v>1.04</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.86</v>
+        <v>-9.85</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7199</v>
+        <v>2.55</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6721</v>
+        <v>2.21</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UPXI</t>
+          <t>REAX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2393,16 +2703,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2423,50 +2733,63 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>2.22</v>
       </c>
       <c r="N24" t="n">
-        <v>2.61</v>
+        <v>1.56</v>
       </c>
       <c r="O24" t="n">
-        <v>66.2</v>
+        <v>50.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>2.6485</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9399999999999999</v>
+        <v>19.79</v>
       </c>
       <c r="S24" t="n">
-        <v>1.09</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.83</v>
+        <v>18.95</v>
       </c>
       <c r="V24" t="n">
-        <v>1.12</v>
+        <v>2.8492</v>
       </c>
       <c r="W24" t="n">
-        <v>0.785</v>
+        <v>2.59</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DEFT</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2475,80 +2798,93 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E25" t="n">
         <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.52</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v/>
+        <v>94.40000000000001</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +2.4pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.62</v>
+        <v>1.57</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>7.31</v>
       </c>
       <c r="O25" t="n">
-        <v>67.5</v>
+        <v>87.3</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6156</v>
+        <v>1.6208</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.84</v>
+        <v>3.9</v>
       </c>
       <c r="S25" t="n">
-        <v>0.631</v>
+        <v>1.86</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.64</v>
+        <v>19.23</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6183</v>
+        <v>1.8</v>
       </c>
       <c r="W25" t="n">
-        <v>0.43</v>
+        <v>0.7705</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOVX</t>
+          <t>CAPR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2557,80 +2893,93 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D26" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-24 8-K (material_event, +2.0pts)   Items: 8.01, 9.01 (routine)   Title: &gt;CAPRICOR THERAPEUTICS, INC._August 24, 2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.6899999999999999</v>
+        <v>7.07</v>
       </c>
       <c r="N26" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="O26" t="n">
-        <v>40.7</v>
+        <v>39.8</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6425</v>
+        <v>6.3796</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-7.13</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>0.718</v>
+        <v>6.81</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.79</v>
+        <v>-3.55</v>
       </c>
       <c r="V26" t="n">
-        <v>0.68</v>
+        <v>8.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5907</v>
+        <v>6.1714</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NGEN</t>
+          <t>LUCY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2645,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -2673,46 +3022,59 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1.97</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.01</v>
+        <v>19.64</v>
       </c>
       <c r="O27" t="n">
-        <v>66.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8896</v>
+        <v>0.6845</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-4.08</v>
+        <v>-36.62</v>
       </c>
       <c r="S27" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.08</v>
+        <v>-3.7</v>
       </c>
       <c r="V27" t="n">
-        <v>1.8896</v>
+        <v>0.7199</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6303</v>
+        <v>0.6721</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>SDEV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2721,80 +3083,93 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>49.2</v>
+        <v/>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.2pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4.52</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>12.79</v>
+        <v>4.42</v>
       </c>
       <c r="O28" t="n">
-        <v>49.5</v>
+        <v>48.1</v>
       </c>
       <c r="P28" t="n">
-        <v>4.7092</v>
+        <v>1.14</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.96</v>
+        <v>6.54</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3402</v>
+        <v>1.24</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.19</v>
+        <v>15.89</v>
       </c>
       <c r="V28" t="n">
-        <v>5.2</v>
+        <v>1.52</v>
       </c>
       <c r="W28" t="n">
-        <v>3.03</v>
+        <v>0.9236</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NXGL</t>
+          <t>UPXI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2803,13 +3178,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
@@ -2819,68 +3194,77 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.4pts) | 2026-08-20 S-1 (dilution_risk, -2.4pts) | 2026-08-17 8-K (material_event, +0.6pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>14.68</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
-        <v>42.3</v>
+        <v>65.7</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3377</v>
+        <v>1.07</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-3.24</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3051</v>
+        <v>1.09</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>-12.58</v>
+        <v>3.32</v>
       </c>
       <c r="V29" t="n">
-        <v>0.484</v>
+        <v>1.12</v>
       </c>
       <c r="W29" t="n">
-        <v>0.33</v>
+        <v>0.785</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BMEA</t>
+          <t>DEFT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2889,16 +3273,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F30" t="n">
         <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2919,50 +3303,63 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>1.58</v>
+        <v>0.63</v>
       </c>
       <c r="N30" t="n">
-        <v>9.970000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="O30" t="n">
-        <v>76.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>1.3741</v>
+        <v>0.6156</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-12.76</v>
+        <v>-1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>1.5</v>
+        <v>0.631</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>-4.76</v>
+        <v>1.06</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>0.6183</v>
       </c>
       <c r="W30" t="n">
-        <v>1.33</v>
+        <v>0.43</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ANY</t>
+          <t>NGEN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2971,80 +3368,93 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Late Entry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>18.6</v>
+        <v/>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-14 8-K (material_event, +0.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="N31" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="O31" t="n">
-        <v>58.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>1.8896</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.62</v>
+        <v>-3.84</v>
       </c>
       <c r="S31" t="n">
-        <v>2.68</v>
+        <v>1.93</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>7.85</v>
+        <v>-1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>2.6884</v>
+        <v>1.8896</v>
       </c>
       <c r="W31" t="n">
-        <v>1.94</v>
+        <v>1.6303</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>ZVIA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3053,80 +3463,93 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" t="n">
-        <v>4</v>
-      </c>
       <c r="G32" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>32.8</v>
+        <v/>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-17 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_mild_high +1</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5.68</v>
+        <v>1.42</v>
       </c>
       <c r="N32" t="n">
-        <v>3.14</v>
+        <v>1.89</v>
       </c>
       <c r="O32" t="n">
-        <v>74.59999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="P32" t="n">
-        <v>5.3817</v>
+        <v>1.31</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>-5.34</v>
+        <v>-8.07</v>
       </c>
       <c r="S32" t="n">
-        <v>5.52</v>
+        <v>1.33</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>-2.9</v>
+        <v>-6.67</v>
       </c>
       <c r="V32" t="n">
-        <v>5.55</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>4.45</v>
+        <v>1.27</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VMAR</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3135,16 +3558,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3165,50 +3588,63 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="N33" t="n">
-        <v>2.73</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
-        <v>32.6</v>
+        <v>76.3</v>
       </c>
       <c r="P33" t="n">
-        <v>0.6989</v>
+        <v>1.3741</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.04</v>
+        <v>-12.13</v>
       </c>
       <c r="S33" t="n">
-        <v>0.669</v>
+        <v>1.5</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>-4.08</v>
       </c>
       <c r="V33" t="n">
-        <v>0.7035</v>
+        <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0.6516999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BTOG</t>
+          <t>ANY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3217,262 +3653,301 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v/>
+        <v>18.1</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-14 8-K (material_event, +0.0pts)   Items: 2.02, 7.01, 9.01 (routine)   Title: &gt;Sphere 3D Corp.: Form 8-K - Filed by newsfilecorp.com</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>30.8</v>
+        <v>58.3</v>
       </c>
       <c r="P34" t="n">
-        <v>3.9999</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>23.26</v>
+        <v>2.82</v>
       </c>
       <c r="S34" t="n">
-        <v>3.63</v>
+        <v>2.69</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>11.86</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="V34" t="n">
-        <v>6.85</v>
+        <v>2.6884</v>
       </c>
       <c r="W34" t="n">
-        <v>3.4575</v>
+        <v>1.94</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>VMAR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>97.5</v>
+        <v/>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +0.8pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_overbought -2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>1.59</v>
+        <v>0.66</v>
       </c>
       <c r="N35" t="n">
-        <v>7.28</v>
+        <v>2.73</v>
       </c>
       <c r="O35" t="n">
-        <v>87.7</v>
+        <v>32.8</v>
       </c>
       <c r="P35" t="n">
-        <v>1.6208</v>
+        <v>0.6989</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="S35" t="n">
-        <v>1.86</v>
+        <v>0.669</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>16.25</v>
+        <v>0.89</v>
       </c>
       <c r="V35" t="n">
-        <v>1.8</v>
+        <v>0.7035</v>
       </c>
       <c r="W35" t="n">
-        <v>0.7705</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GIPR</t>
+          <t>GOVX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>63.1</v>
+        <v/>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-17 8-K (material_event, +0.6pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="N36" t="n">
-        <v>15.84</v>
+        <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>41.8</v>
+        <v>39.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2842</v>
+        <v>0.6425</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>-51.13</v>
+        <v>-5.53</v>
       </c>
       <c r="S36" t="n">
-        <v>0.29</v>
+        <v>0.718</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-50.14</v>
+        <v>5.57</v>
       </c>
       <c r="V36" t="n">
-        <v>0.3293</v>
+        <v>0.68</v>
       </c>
       <c r="W36" t="n">
-        <v>0.2624</v>
+        <v>0.5907</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OLOX</t>
+          <t>BTOG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="F37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3493,50 +3968,63 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>16.24</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>22</v>
+        <v>30.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.24</v>
+        <v>3.9999</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>5.16</v>
+        <v>24.99</v>
       </c>
       <c r="S37" t="n">
-        <v>2.39</v>
+        <v>3.63</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>12.21</v>
+        <v>13.43</v>
       </c>
       <c r="V37" t="n">
-        <v>2.77</v>
+        <v>6.85</v>
       </c>
       <c r="W37" t="n">
-        <v>2.09</v>
+        <v>3.4575</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HUYA</t>
+          <t>NXGL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3545,80 +4033,97 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v/>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>-7.9</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 8-K (material_event, +0.7pts)   Item 5.02 (officer_departure, -1) | 2026-08-20 S-1 (dilution_risk, -2.4pts) | 2026-08-17 8-K (material_event, +0.6pts)   Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>2.15</v>
+        <v>0.35</v>
       </c>
       <c r="N38" t="n">
-        <v>1.78</v>
+        <v>14.68</v>
       </c>
       <c r="O38" t="n">
-        <v>28.9</v>
+        <v>42</v>
       </c>
       <c r="P38" t="n">
-        <v>2.19</v>
+        <v>0.3377</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>-2.51</v>
       </c>
       <c r="S38" t="n">
-        <v>2.18</v>
+        <v>0.3051</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.63</v>
+        <v>-11.92</v>
       </c>
       <c r="V38" t="n">
-        <v>2.26</v>
+        <v>0.484</v>
       </c>
       <c r="W38" t="n">
-        <v>2.15</v>
+        <v>0.33</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3627,16 +4132,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-3.4</v>
+        <v>-0.7</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>-4</v>
@@ -3647,60 +4152,73 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>313.1</v>
+        <v>29.3</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, +0.8pts)</t>
+          <t>2026-08-21 4 (insider_buy, +2.1pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_buy, +0.9pts)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +2, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>2.64</v>
+        <v>4.09</v>
       </c>
       <c r="N39" t="n">
-        <v>16.3</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="P39" t="n">
-        <v>0.4339</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>-83.56</v>
+        <v>-1.96</v>
       </c>
       <c r="S39" t="n">
-        <v>0.44</v>
+        <v>4.16</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>-83.33</v>
+        <v>1.96</v>
       </c>
       <c r="V39" t="n">
-        <v>0.6679</v>
+        <v>4.14</v>
       </c>
       <c r="W39" t="n">
-        <v>0.3227</v>
+        <v>3.07</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>GIPR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3709,16 +4227,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-4</v>
+        <v>-0.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E40" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>-4</v>
@@ -3729,54 +4247,352 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>30.1</v>
+        <v>61.4</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-21 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_other, +0.0pts)</t>
+          <t>2026-08-17 8-K (material_event, +0.6pts)   Items: 2.02, 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>4.11</v>
+        <v>0.57</v>
       </c>
       <c r="N40" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="O40" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-49.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-48.21</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="X40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OLOX</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v/>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N41" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="O41" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="X41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HUYA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v/>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O42" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.63</v>
       </c>
-      <c r="O40" t="n">
-        <v>77</v>
-      </c>
-      <c r="P40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V40" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="W40" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="X40" t="b">
-        <v>1</v>
+      <c r="V42" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>259.9</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-08-18 8-K (material_event, -0.8pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="O43" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>-81.13</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-80.87</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="X43" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3790,7 +4606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4023,13 +4839,13 @@
         <v>3.95</v>
       </c>
       <c r="C2" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="D2" t="n">
-        <v>3701765</v>
+        <v>3710616</v>
       </c>
       <c r="E2" t="n">
-        <v>67.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>3.77</v>
@@ -4062,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.27</v>
+        <v>-1.39</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -4077,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -4116,7 +4932,7 @@
         <v>3.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="AG2" t="n">
         <v>25.8</v>
@@ -4125,11 +4941,11 @@
         <v>3.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.44–$4.46 (ann. vol 26%) | ATR range: $3.18–$4.72</t>
+          <t>1-SD 3mo range: $3.44–$4.47 (ann. vol 26%) | ATR range: $3.18–$4.73</t>
         </is>
       </c>
     </row>
@@ -4140,16 +4956,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="C3" t="n">
         <v>19.64</v>
       </c>
       <c r="D3" t="n">
-        <v>9597832</v>
+        <v>9867949</v>
       </c>
       <c r="E3" t="n">
-        <v>70.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="F3" t="n">
         <v>0.76</v>
@@ -4182,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-35.41</v>
+        <v>-36.62</v>
       </c>
       <c r="Q3" t="n">
         <v>0.7199</v>
@@ -4197,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.86</v>
+        <v>-3.7</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -4211,7 +5027,7 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -4236,20 +5052,20 @@
         <v>0.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>105.7</v>
+        <v>106.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.50–$1.60 (ann. vol 106%) | ATR range: $0.39–$1.71</t>
+          <t>1-SD 3mo range: $0.50–$1.65 (ann. vol 107%) | ATR range: $0.41–$1.74</t>
         </is>
       </c>
     </row>
@@ -4260,19 +5076,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.16</v>
+        <v>7.19</v>
       </c>
       <c r="C4" t="n">
-        <v>16.89</v>
+        <v>16.9</v>
       </c>
       <c r="D4" t="n">
-        <v>33348617</v>
+        <v>33616270</v>
       </c>
       <c r="E4" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="G4" t="n">
         <v>4.52</v>
@@ -4302,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-51.54</v>
+        <v>-52.13</v>
       </c>
       <c r="Q4" t="n">
         <v>4.15</v>
@@ -4317,13 +5133,13 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>18.45</v>
+        <v>17</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -4331,11 +5147,11 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>10.66</v>
+        <v>10.88</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.7x vs 2.7x median — trading at premium</t>
+          <t>10.9x vs 2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AA4" t="n">
@@ -4349,27 +5165,27 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>P/S 0.8x vs 0.7x median — in-line | P/B 10.7x vs 2.7x median — trading at premium | EV/EBITDA -0.2x vs -1.5x median — trading at discount</t>
+          <t>P/S 0.8x vs 0.7x median — in-line | P/B 10.9x vs 2.7x median — trading at premium | EV/EBITDA -0.2x vs -1.5x median — trading at discount</t>
         </is>
       </c>
       <c r="AE4" t="n">
         <v>2.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.53</v>
+        <v>11.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>122.1</v>
+        <v>122.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>13.05</v>
+        <v>13.08</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.79–$11.53 (ann. vol 122%) | ATR range: $1.27–$13.05</t>
+          <t>1-SD 3mo range: $2.79–$11.59 (ann. vol 122%) | ATR range: $1.30–$13.08</t>
         </is>
       </c>
     </row>
@@ -4380,31 +5196,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="C5" t="n">
-        <v>16.3</v>
+        <v>16.33</v>
       </c>
       <c r="D5" t="n">
-        <v>9486421</v>
+        <v>8345548</v>
       </c>
       <c r="E5" t="n">
-        <v>76.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
-        <v>18.19</v>
+        <v>18.18</v>
       </c>
       <c r="I5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J5" t="n">
-        <v>11.79</v>
+        <v>11.78</v>
       </c>
       <c r="K5" t="n">
         <v>0.36</v>
@@ -4422,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-83.56</v>
+        <v>-81.13</v>
       </c>
       <c r="Q5" t="n">
         <v>0.6679</v>
@@ -4437,13 +5253,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-83.33</v>
+        <v>-80.87</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>14.62</v>
+        <v>0.51</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -4451,7 +5267,7 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>-0.76</v>
+        <v>-0.67</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -4473,23 +5289,23 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>-0.48</v>
+        <v>-0.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>5.76</v>
+        <v>4.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>236.5</v>
+        <v>225.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.08</v>
+        <v>-0.26</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.2</v>
+        <v>4.86</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.48–$5.76 (ann. vol 236%) | ATR range: $0.08–$5.20</t>
+          <t>1-SD 3mo range: $-0.30–$4.90 (ann. vol 226%) | ATR range: $-0.26–$4.86</t>
         </is>
       </c>
     </row>
@@ -4500,16 +5316,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="C6" t="n">
-        <v>16.24</v>
+        <v>16.25</v>
       </c>
       <c r="D6" t="n">
-        <v>2064613</v>
+        <v>2059309</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="F6" t="n">
         <v>3.28</v>
@@ -4542,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.16</v>
+        <v>5.41</v>
       </c>
       <c r="Q6" t="n">
         <v>2.77</v>
@@ -4557,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>12.21</v>
+        <v>12.47</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -4596,20 +5412,20 @@
         <v>-0.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="AG6" t="n">
         <v>200.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>-2.04</v>
+        <v>-2.05</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.3</v>
+        <v>6.29</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.01–$4.27 (ann. vol 200%) | ATR range: $-2.04–$6.30</t>
+          <t>1-SD 3mo range: $-0.01–$4.25 (ann. vol 200%) | ATR range: $-2.05–$6.29</t>
         </is>
       </c>
     </row>
@@ -4623,13 +5439,13 @@
         <v>0.57</v>
       </c>
       <c r="C7" t="n">
-        <v>15.84</v>
+        <v>15.96</v>
       </c>
       <c r="D7" t="n">
-        <v>5693828</v>
+        <v>5814236</v>
       </c>
       <c r="E7" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="F7" t="n">
         <v>0.62</v>
@@ -4662,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-51.13</v>
+        <v>-49.25</v>
       </c>
       <c r="Q7" t="n">
         <v>0.3293</v>
@@ -4677,13 +5493,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-50.14</v>
+        <v>-48.21</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -4716,20 +5532,20 @@
         <v>0.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AG7" t="n">
-        <v>164.3</v>
+        <v>163.9</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.10–$1.05 (ann. vol 164%) | ATR range: $-0.61–$1.76</t>
+          <t>1-SD 3mo range: $0.10–$1.03 (ann. vol 164%) | ATR range: $-0.61–$1.75</t>
         </is>
       </c>
     </row>
@@ -4740,16 +5556,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="C8" t="n">
         <v>15.74</v>
       </c>
       <c r="D8" t="n">
-        <v>1884100</v>
+        <v>1882375</v>
       </c>
       <c r="E8" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="F8" t="n">
         <v>3.6</v>
@@ -4782,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>14.28</v>
+        <v>14.57</v>
       </c>
       <c r="Q8" t="n">
         <v>4.07</v>
@@ -4791,13 +5607,13 @@
         <v>3.5</v>
       </c>
       <c r="S8" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>13.42</v>
+        <v>14.57</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -4811,7 +5627,7 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -4836,7 +5652,7 @@
         <v>1.28</v>
       </c>
       <c r="AF8" t="n">
-        <v>5.74</v>
+        <v>5.72</v>
       </c>
       <c r="AG8" t="n">
         <v>127</v>
@@ -4845,11 +5661,11 @@
         <v>1.48</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.28–$5.74 (ann. vol 127%) | ATR range: $1.48–$5.54</t>
+          <t>1-SD 3mo range: $1.28–$5.72 (ann. vol 127%) | ATR range: $1.48–$5.52</t>
         </is>
       </c>
     </row>
@@ -4866,10 +5682,10 @@
         <v>14.68</v>
       </c>
       <c r="D9" t="n">
-        <v>583402</v>
+        <v>579215</v>
       </c>
       <c r="E9" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
         <v>0.41</v>
@@ -4902,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.24</v>
+        <v>-2.51</v>
       </c>
       <c r="Q9" t="n">
         <v>0.484</v>
@@ -4917,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-12.58</v>
+        <v>-11.92</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
@@ -4931,7 +5747,7 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -4956,7 +5772,7 @@
         <v>0.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="AG9" t="n">
         <v>108.5</v>
@@ -4969,7 +5785,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.16–$0.54 (ann. vol 108%) | ATR range: $-0.29–$0.99</t>
+          <t>1-SD 3mo range: $0.16–$0.53 (ann. vol 108%) | ATR range: $-0.29–$0.99</t>
         </is>
       </c>
     </row>
@@ -5100,37 +5916,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="C11" t="n">
         <v>12.79</v>
       </c>
       <c r="D11" t="n">
-        <v>6556222</v>
+        <v>6546071</v>
       </c>
       <c r="E11" t="n">
-        <v>49.5</v>
+        <v>63.6</v>
       </c>
       <c r="F11" t="n">
-        <v>4.07</v>
+        <v>3.11</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>66.01000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="I11" t="n">
-        <v>6.07</v>
+        <v>1.68</v>
       </c>
       <c r="J11" t="n">
-        <v>53.5</v>
+        <v>1.46</v>
       </c>
       <c r="K11" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
@@ -5142,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.96</v>
+        <v>4.65</v>
       </c>
       <c r="Q11" t="n">
         <v>5.2</v>
@@ -5157,13 +5973,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.19</v>
+        <v>-3.55</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -5171,7 +5987,7 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -5193,23 +6009,23 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.21</v>
+        <v>-11.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.83</v>
+        <v>20.46</v>
       </c>
       <c r="AG11" t="n">
-        <v>190.6</v>
+        <v>707.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="AI11" t="n">
-        <v>8.57</v>
+        <v>8.56</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.21–$8.83 (ann. vol 191%) | ATR range: $0.47–$8.57</t>
+          <t>1-SD 3mo range: $-11.44–$20.46 (ann. vol 708%) | ATR range: $0.45–$8.56</t>
         </is>
       </c>
     </row>
@@ -5220,16 +6036,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="C12" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>1580316</v>
+        <v>1574855</v>
       </c>
       <c r="E12" t="n">
-        <v>76.8</v>
+        <v>76.3</v>
       </c>
       <c r="F12" t="n">
         <v>1.33</v>
@@ -5262,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-12.76</v>
+        <v>-12.13</v>
       </c>
       <c r="Q12" t="n">
         <v>1.4</v>
@@ -5277,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.76</v>
+        <v>-4.08</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -5291,7 +6107,7 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>9.43</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -5316,20 +6132,20 @@
         <v>0.86</v>
       </c>
       <c r="AF12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.29</v>
       </c>
-      <c r="AG12" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.86–$2.29 (ann. vol 90%) | ATR range: $0.85–$2.30</t>
+          <t>1-SD 3mo range: $0.86–$2.27 (ann. vol 90%) | ATR range: $0.84–$2.29</t>
         </is>
       </c>
     </row>
@@ -5460,16 +6276,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="C14" t="n">
-        <v>7.28</v>
+        <v>7.31</v>
       </c>
       <c r="D14" t="n">
-        <v>7421130</v>
+        <v>7318948</v>
       </c>
       <c r="E14" t="n">
-        <v>87.7</v>
+        <v>87.3</v>
       </c>
       <c r="F14" t="n">
         <v>0.9</v>
@@ -5502,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q14" t="n">
         <v>1.8</v>
@@ -5517,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>16.25</v>
+        <v>19.23</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -5531,7 +6347,7 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -5553,23 +6369,23 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>235</v>
+        <v>234.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.28–$3.46 (ann. vol 235%) | ATR range: $0.40–$2.78</t>
+          <t>1-SD 3mo range: $-0.27–$3.40 (ann. vol 235%) | ATR range: $0.37–$2.76</t>
         </is>
       </c>
     </row>
@@ -5583,10 +6399,10 @@
         <v>10.8</v>
       </c>
       <c r="C15" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2391372</v>
+        <v>2394631</v>
       </c>
       <c r="E15" t="n">
         <v>64.59999999999999</v>
@@ -5700,16 +6516,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="C16" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="D16" t="n">
-        <v>1058725</v>
+        <v>1028875</v>
       </c>
       <c r="E16" t="n">
-        <v>50.6</v>
+        <v>48.1</v>
       </c>
       <c r="F16" t="n">
         <v>1.07</v>
@@ -5730,7 +6546,7 @@
         <v>0.11</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
@@ -5742,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.11</v>
+        <v>6.54</v>
       </c>
       <c r="Q16" t="n">
         <v>1.52</v>
@@ -5757,21 +6573,21 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>13.24</v>
+        <v>15.89</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>-2.38</v>
+        <v>-2.33</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>-2.4x vs 4.2x median — trading at discount</t>
+          <t>-2.3x vs 4.2x median — trading at discount</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -5789,215 +6605,215 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>P/S -2.4x vs 4.2x median — trading at discount | P/B 0.4x vs 0.9x median — trading at discount</t>
+          <t>P/S -2.3x vs 4.2x median — trading at discount | P/B 0.4x vs 0.9x median — trading at discount</t>
         </is>
       </c>
       <c r="AE16" t="n">
         <v>-0.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="AG16" t="n">
-        <v>222.5</v>
+        <v>222.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.12–$2.31 (ann. vol 222%) | ATR range: $0.34–$1.85</t>
+          <t>1-SD 3mo range: $-0.12–$2.24 (ann. vol 223%) | ATR range: $0.28–$1.84</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>VBIO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.02</v>
+        <v>0.17</v>
       </c>
       <c r="C17" t="n">
-        <v>3.37</v>
+        <v>3.52</v>
       </c>
       <c r="D17" t="n">
-        <v>1827308</v>
+        <v>4089887</v>
       </c>
       <c r="E17" t="n">
-        <v>67.59999999999999</v>
+        <v>34.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1.66</v>
+        <v>0.23</v>
       </c>
       <c r="G17" t="n">
-        <v>1.65</v>
+        <v>0.39</v>
       </c>
       <c r="H17" t="n">
-        <v>1.98</v>
+        <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>1.61</v>
+        <v>0.38</v>
       </c>
       <c r="J17" t="n">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>0.1182</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-16.63</v>
+        <v>-32.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.74</v>
+        <v>0.1606</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5202</v>
+        <v>0.113</v>
       </c>
       <c r="S17" t="n">
-        <v>1.68</v>
+        <v>0.1166</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-16.63</v>
+        <v>-33.64</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
       </c>
       <c r="W17" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-8.5x vs 2.1x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>0.2x vs 2.0x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AB17" t="n">
         <v/>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>N/A — insufficient data</t>
-        </is>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>2.1x vs 2.7x median — trading at discount</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3</v>
       </c>
       <c r="AC17" t="n">
         <v/>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>P/B 2.1x vs 2.7x median — trading at discount | EV/EBITDA -0.4x vs -1.5x median — trading at discount | Analyst target $3.00</t>
+          <t>P/S -8.5x vs 2.1x median — trading at discount | P/B 0.2x vs 2.0x median — trading at discount | EV/EBITDA -1.1x vs -0.8x median — trading at premium</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>0.06</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.9</v>
+        <v>0.27</v>
       </c>
       <c r="AG17" t="n">
-        <v>87.8</v>
+        <v>123.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.71</v>
+        <v>-0.88</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.32</v>
+        <v>1.22</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.13–$2.90 (ann. vol 88%) | ATR range: $0.71–$3.32</t>
+          <t>1-SD 3mo range: $0.06–$0.27 (ann. vol 124%) | ATR range: $-0.88–$1.22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>NPWR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.29</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="D18" t="n">
-        <v>2795669</v>
+        <v>1818824</v>
       </c>
       <c r="E18" t="n">
-        <v>63.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>6.71</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>6.64</v>
+        <v>1.65</v>
       </c>
       <c r="H18" t="n">
-        <v>6.72</v>
+        <v>1.98</v>
       </c>
       <c r="I18" t="n">
-        <v>6.51</v>
+        <v>1.61</v>
       </c>
       <c r="J18" t="n">
-        <v>7.09</v>
+        <v>2.04</v>
       </c>
       <c r="K18" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.3805</v>
+        <v>1.68</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-12.48</v>
+        <v>-15.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.56</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>6.3805</v>
+        <v>1.5202</v>
       </c>
       <c r="S18" t="n">
-        <v>6.69</v>
+        <v>1.68</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-8.23</v>
+        <v>-15.37</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
@@ -6011,45 +6827,45 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>4.69</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.7x vs 2.0x median — trading at premium</t>
+          <t>2.1x vs 2.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>-5.97</v>
+        <v>-0.43</v>
       </c>
       <c r="AB18" t="n">
-        <v>16.35</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="n">
         <v/>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/B 4.7x vs 2.0x median — trading at premium | EV/EBITDA -6.0x vs -0.8x median — trading at premium | Analyst target $16.35</t>
+          <t>P/B 2.1x vs 2.7x median — trading at discount | EV/EBITDA -0.4x vs -1.5x median — trading at discount | Analyst target $3.00</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>5.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.52</v>
+        <v>2.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>61.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>9.73</v>
+        <v>3.3</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $5.06–$9.52 (ann. vol 61%) | ATR range: $4.85–$9.73</t>
+          <t>1-SD 3mo range: $1.12–$2.87 (ann. vol 88%) | ATR range: $0.69–$3.30</t>
         </is>
       </c>
     </row>
@@ -6060,28 +6876,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.68</v>
+        <v>5.64</v>
       </c>
       <c r="C19" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="D19" t="n">
-        <v>6562368</v>
+        <v>6521116</v>
       </c>
       <c r="E19" t="n">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="H19" t="n">
         <v>6.3</v>
       </c>
       <c r="I19" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="J19" t="n">
         <v>5.54</v>
@@ -6102,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.34</v>
+        <v>-4.41</v>
       </c>
       <c r="Q19" t="n">
         <v>5.55</v>
@@ -6117,25 +6933,25 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.9</v>
+        <v>-1.95</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>7.9x vs 7.9x median — in-line</t>
+          <t>7.8x vs 3.9x median — trading at premium</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.8x vs 0.8x median — in-line</t>
+          <t>0.8x vs 0.4x median — trading at premium</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -6149,147 +6965,147 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>P/S 7.9x vs 7.9x median — in-line | P/B 0.8x vs 0.8x median — in-line | EV/EBITDA 47.7x vs -1.7x median — trading at discount | Analyst target $7.83</t>
+          <t>P/S 7.8x vs 3.9x median — trading at premium | P/B 0.8x vs 0.4x median — trading at premium | EV/EBITDA 47.7x vs -4.8x median — trading at discount | Analyst target $7.83</t>
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>8.970000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>115.5</v>
+        <v>115.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.41</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.40–$8.97 (ann. vol 116%) | ATR range: $2.96–$8.41</t>
+          <t>1-SD 3mo range: $2.38–$8.89 (ann. vol 115%) | ATR range: $2.91–$8.36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VBIO</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.16</v>
+        <v>7.3</v>
       </c>
       <c r="C20" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="D20" t="n">
-        <v>3847033</v>
+        <v>2801942</v>
       </c>
       <c r="E20" t="n">
-        <v>33</v>
+        <v>63.8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.23</v>
+        <v>6.71</v>
       </c>
       <c r="G20" t="n">
-        <v>0.39</v>
+        <v>6.64</v>
       </c>
       <c r="H20" t="n">
-        <v>1.07</v>
+        <v>6.72</v>
       </c>
       <c r="I20" t="n">
-        <v>0.38</v>
+        <v>6.51</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>7.09</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1182</v>
+        <v>6.3805</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-28.41</v>
+        <v>-12.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1606</v>
+        <v>7.56</v>
       </c>
       <c r="R20" t="n">
-        <v>0.113</v>
+        <v>6.3805</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1166</v>
+        <v>6.69</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-29.38</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>-8.01</v>
+        <v/>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>-8.0x vs 2.1x median — trading at discount</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>0.16</v>
+        <v>4.7</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.2x vs 2.0x median — trading at discount</t>
+          <t>4.7x vs 2.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>-1.09</v>
+        <v>-5.97</v>
       </c>
       <c r="AB20" t="n">
-        <v/>
+        <v>16.35</v>
       </c>
       <c r="AC20" t="n">
         <v/>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>P/S -8.0x vs 2.1x median — trading at discount | P/B 0.2x vs 2.0x median — trading at discount | EV/EBITDA -1.1x vs -0.8x median — trading at premium</t>
+          <t>P/B 4.7x vs 2.0x median — trading at premium | EV/EBITDA -6.0x vs -0.8x median — trading at premium | Analyst target $16.35</t>
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>0.06</v>
+        <v>5.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.26</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AG20" t="n">
-        <v>122.9</v>
+        <v>61.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.89</v>
+        <v>4.86</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.21</v>
+        <v>9.74</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.06–$0.26 (ann. vol 123%) | ATR range: $-0.89–$1.21</t>
+          <t>1-SD 3mo range: $5.06–$9.54 (ann. vol 61%) | ATR range: $4.86–$9.74</t>
         </is>
       </c>
     </row>
@@ -6300,19 +7116,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="C21" t="n">
         <v>3.01</v>
       </c>
       <c r="D21" t="n">
-        <v>3232533</v>
+        <v>3250696</v>
       </c>
       <c r="E21" t="n">
-        <v>61.7</v>
+        <v>62.1</v>
       </c>
       <c r="F21" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="G21" t="n">
         <v>3.62</v>
@@ -6342,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-12.15</v>
+        <v>-12.59</v>
       </c>
       <c r="Q21" t="n">
         <v>3.5609</v>
@@ -6357,25 +7173,25 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.78</v>
+        <v>-3.27</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>33.05</v>
+        <v>33.31</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>33.1x vs 7.9x median — trading at premium</t>
+          <t>33.3x vs 3.9x median — trading at premium</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.3x vs 0.8x median — trading at premium</t>
+          <t>2.3x vs 0.4x median — trading at premium</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -6389,27 +7205,27 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>P/S 33.1x vs 7.9x median — trading at premium | P/B 2.3x vs 0.8x median — trading at premium | EV/EBITDA -8.0x vs -1.7x median — trading at premium</t>
+          <t>P/S 33.3x vs 3.9x median — trading at premium | P/B 2.3x vs 0.4x median — trading at premium | EV/EBITDA -8.0x vs -4.8x median — trading at premium</t>
         </is>
       </c>
       <c r="AE21" t="n">
         <v>1.18</v>
       </c>
       <c r="AF21" t="n">
-        <v>6.72</v>
+        <v>6.76</v>
       </c>
       <c r="AG21" t="n">
         <v>140.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.44</v>
+        <v>6.46</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.18–$6.72 (ann. vol 140%) | ATR range: $1.46–$6.44</t>
+          <t>1-SD 3mo range: $1.18–$6.76 (ann. vol 140%) | ATR range: $1.48–$6.46</t>
         </is>
       </c>
     </row>
@@ -6426,10 +7242,10 @@
         <v>2.73</v>
       </c>
       <c r="D22" t="n">
-        <v>2215067</v>
+        <v>2228666</v>
       </c>
       <c r="E22" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="F22" t="n">
         <v>0.77</v>
@@ -6462,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6.04</v>
+        <v>5.4</v>
       </c>
       <c r="Q22" t="n">
         <v>0.7035</v>
@@ -6477,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>0.89</v>
       </c>
       <c r="V22" t="b">
         <v>1</v>
@@ -6487,7 +7303,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0.1x vs 7.9x median — trading at discount</t>
+          <t>0.1x vs 3.9x median — trading at discount</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -6495,7 +7311,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.0x vs 0.8x median — trading at discount</t>
+          <t>0.0x vs 0.4x median — trading at discount</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -6509,7 +7325,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 7.9x median — trading at discount | P/B 0.0x vs 0.8x median — trading at discount | EV/EBITDA -1.7x vs -1.7x median — in-line</t>
+          <t>P/S 0.1x vs 3.9x median — trading at discount | P/B 0.0x vs 0.4x median — trading at discount | EV/EBITDA -1.7x vs -4.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AE22" t="n">
@@ -6525,11 +7341,11 @@
         <v>-0.02</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.04–$1.28 (ann. vol 187%) | ATR range: $-0.02–$1.34</t>
+          <t>1-SD 3mo range: $0.04–$1.28 (ann. vol 187%) | ATR range: $-0.02–$1.35</t>
         </is>
       </c>
     </row>
@@ -6540,16 +7356,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="C23" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="D23" t="n">
-        <v>1825471</v>
+        <v>1820360</v>
       </c>
       <c r="E23" t="n">
-        <v>66.2</v>
+        <v>65.7</v>
       </c>
       <c r="F23" t="n">
         <v>0.87</v>
@@ -6582,7 +7398,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="n">
         <v>1.12</v>
@@ -6597,13 +7413,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="V23" t="b">
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -6611,7 +7427,7 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>-1.37</v>
+        <v>-1.36</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -6636,20 +7452,20 @@
         <v>0.42</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG23" t="n">
         <v>121.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AI23" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.42–$1.70 (ann. vol 121%) | ATR range: $0.45–$1.67</t>
+          <t>1-SD 3mo range: $0.42–$1.69 (ann. vol 121%) | ATR range: $0.44–$1.67</t>
         </is>
       </c>
     </row>
@@ -6660,25 +7476,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.77</v>
+        <v>10.73</v>
       </c>
       <c r="C24" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="D24" t="n">
-        <v>4283893</v>
+        <v>4276233</v>
       </c>
       <c r="E24" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="F24" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="G24" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>9.199999999999999</v>
@@ -6702,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.76</v>
+        <v>-5.45</v>
       </c>
       <c r="Q24" t="n">
         <v>10.43</v>
@@ -6717,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.64</v>
+        <v>-4.33</v>
       </c>
       <c r="V24" t="b">
         <v>1</v>
@@ -6731,7 +7547,7 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -6753,23 +7569,23 @@
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>6.34</v>
+        <v>6.31</v>
       </c>
       <c r="AF24" t="n">
-        <v>15.2</v>
+        <v>15.15</v>
       </c>
       <c r="AG24" t="n">
         <v>82.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.04</v>
+        <v>6</v>
       </c>
       <c r="AI24" t="n">
-        <v>15.5</v>
+        <v>15.46</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $6.34–$15.20 (ann. vol 82%) | ATR range: $6.04–$15.50</t>
+          <t>1-SD 3mo range: $6.31–$15.15 (ann. vol 82%) | ATR range: $6.00–$15.46</t>
         </is>
       </c>
     </row>
@@ -6780,16 +7596,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="C25" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="D25" t="n">
-        <v>573574</v>
+        <v>569821</v>
       </c>
       <c r="E25" t="n">
-        <v>46.2</v>
+        <v>44.6</v>
       </c>
       <c r="F25" t="n">
         <v>4.05</v>
@@ -6801,7 +7617,7 @@
         <v>3.76</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="J25" t="n">
         <v>3.64</v>
@@ -6822,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.25</v>
+        <v>1.14</v>
       </c>
       <c r="Q25" t="n">
         <v>4.7</v>
@@ -6837,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.26</v>
+        <v>-4.42</v>
       </c>
       <c r="V25" t="b">
         <v>1</v>
@@ -6851,7 +7667,7 @@
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -6873,61 +7689,61 @@
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="AF25" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="AG25" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.47</v>
+        <v>6.43</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.61–$5.37 (ann. vol 69%) | ATR range: $1.51–$6.47</t>
+          <t>1-SD 3mo range: $2.59–$5.32 (ann. vol 69%) | ATR range: $1.48–$6.43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DEFT</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.62</v>
+        <v>1.42</v>
       </c>
       <c r="C26" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="D26" t="n">
-        <v>1574158</v>
+        <v>2468177</v>
       </c>
       <c r="E26" t="n">
-        <v>67.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.49</v>
+        <v>1.17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.51</v>
+        <v>1.19</v>
       </c>
       <c r="H26" t="n">
-        <v>0.85</v>
+        <v>1.96</v>
       </c>
       <c r="I26" t="n">
-        <v>0.48</v>
+        <v>1.09</v>
       </c>
       <c r="J26" t="n">
-        <v>0.76</v>
+        <v>1.92</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -6936,118 +7752,118 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6156</v>
+        <v>1.53</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.84</v>
+        <v>7.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6183</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="S26" t="n">
-        <v>0.631</v>
+        <v>1.4297</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.64</v>
+        <v>-0</v>
       </c>
       <c r="V26" t="b">
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>3.94</v>
+        <v>4.28</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>3.9x vs 4.2x median — in-line</t>
+          <t>4.3x vs 4.2x median — in-line</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1.7x vs 0.9x median — trading at premium</t>
+          <t>1.9x vs 0.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>8.289999999999999</v>
+        <v>-17.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.39</v>
+        <v/>
       </c>
       <c r="AC26" t="n">
-        <v>0.7</v>
+        <v/>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>P/S 3.9x vs 4.2x median — in-line | P/B 1.7x vs 0.9x median — trading at premium | EV/EBITDA 8.3x vs -2.7x median — trading at discount | Analyst target $2.39 | Graham # $0.70</t>
+          <t>P/S 4.3x vs 4.2x median — in-line | P/B 1.9x vs 0.9x median — trading at premium | EV/EBITDA -17.9x vs -2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AE26" t="n">
-        <v>0.3</v>
+        <v>0.84</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="AG26" t="n">
-        <v>101.9</v>
+        <v>82.8</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.09</v>
+        <v>2.16</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.30–$0.94 (ann. vol 102%) | ATR range: $0.15–$1.09</t>
+          <t>1-SD 3mo range: $0.84–$2.01 (ann. vol 83%) | ATR range: $0.69–$2.16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>DEFT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.45</v>
+        <v>0.63</v>
       </c>
       <c r="C27" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="D27" t="n">
-        <v>2477057</v>
+        <v>1589396</v>
       </c>
       <c r="E27" t="n">
-        <v>74.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>1.17</v>
+        <v>0.49</v>
       </c>
       <c r="G27" t="n">
-        <v>1.19</v>
+        <v>0.51</v>
       </c>
       <c r="H27" t="n">
-        <v>1.96</v>
+        <v>0.85</v>
       </c>
       <c r="I27" t="n">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="J27" t="n">
-        <v>1.92</v>
+        <v>0.76</v>
       </c>
       <c r="K27" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -7056,80 +7872,80 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.53</v>
+        <v>0.6156</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>5.88</v>
+        <v>-1.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>0.6183</v>
       </c>
       <c r="R27" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4297</v>
+        <v>0.631</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.06</v>
+        <v>1.06</v>
       </c>
       <c r="V27" t="b">
         <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>4.33</v>
+        <v>3.99</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>4.3x vs 4.2x median — in-line</t>
+          <t>4.0x vs 4.2x median — in-line</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2.0x vs 0.9x median — trading at premium</t>
+          <t>1.8x vs 0.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>-17.85</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB27" t="n">
-        <v/>
+        <v>2.39</v>
       </c>
       <c r="AC27" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>P/S 4.3x vs 4.2x median — in-line | P/B 2.0x vs 0.9x median — trading at premium | EV/EBITDA -17.9x vs -2.7x median — trading at premium</t>
+          <t>P/S 4.0x vs 4.2x median — in-line | P/B 1.8x vs 0.9x median — trading at premium | EV/EBITDA 8.3x vs -2.7x median — trading at discount | Analyst target $2.39 | Graham # $0.70</t>
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>0.85</v>
+        <v>0.31</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AG27" t="n">
-        <v>82.90000000000001</v>
+        <v>102</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.71</v>
+        <v>0.16</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.85–$2.04 (ann. vol 83%) | ATR range: $0.71–$2.18</t>
+          <t>1-SD 3mo range: $0.31–$0.94 (ann. vol 102%) | ATR range: $0.16–$1.10</t>
         </is>
       </c>
     </row>
@@ -7140,16 +7956,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="C28" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="D28" t="n">
-        <v>650809</v>
+        <v>640326</v>
       </c>
       <c r="E28" t="n">
-        <v>40.7</v>
+        <v>39.4</v>
       </c>
       <c r="F28" t="n">
         <v>0.73</v>
@@ -7182,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.13</v>
+        <v>-5.53</v>
       </c>
       <c r="Q28" t="n">
         <v>0.68</v>
@@ -7197,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.79</v>
+        <v>5.57</v>
       </c>
       <c r="V28" t="b">
         <v>1</v>
@@ -7211,11 +8027,11 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2.9x vs 2.0x median — trading at premium</t>
+          <t>2.8x vs 2.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -7229,27 +8045,27 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>P/B 2.9x vs 2.0x median — trading at premium | EV/EBITDA -0.1x vs -0.8x median — trading at discount | Analyst target $10.00</t>
+          <t>P/B 2.8x vs 2.0x median — trading at premium | EV/EBITDA -0.1x vs -0.8x median — trading at discount | Analyst target $10.00</t>
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AG28" t="n">
-        <v>134.1</v>
+        <v>134</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.23–$1.16 (ann. vol 134%) | ATR range: $0.10–$1.28</t>
+          <t>1-SD 3mo range: $0.22–$1.14 (ann. vol 134%) | ATR range: $0.09–$1.27</t>
         </is>
       </c>
     </row>
@@ -7263,13 +8079,13 @@
         <v>1.97</v>
       </c>
       <c r="C29" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="D29" t="n">
-        <v>799069</v>
+        <v>799497</v>
       </c>
       <c r="E29" t="n">
-        <v>66.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F29" t="n">
         <v>1.76</v>
@@ -7302,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-4.08</v>
+        <v>-3.84</v>
       </c>
       <c r="Q29" t="n">
         <v>1.8896</v>
@@ -7311,13 +8127,13 @@
         <v>1.6303</v>
       </c>
       <c r="S29" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>-5.08</v>
+        <v>-1.78</v>
       </c>
       <c r="V29" t="b">
         <v>1</v>
@@ -7331,7 +8147,7 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>14.61</v>
+        <v>14.58</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -7356,20 +8172,20 @@
         <v>1.07</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AG29" t="n">
         <v>91.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" t="n">
         <v>2.71</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.07–$2.87 (ann. vol 91%) | ATR range: $1.23–$2.71</t>
+          <t>1-SD 3mo range: $1.07–$2.86 (ann. vol 91%) | ATR range: $1.22–$2.71</t>
         </is>
       </c>
     </row>
@@ -7380,22 +8196,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>1275855</v>
+        <v>1258661</v>
       </c>
       <c r="E30" t="n">
-        <v>30.8</v>
+        <v>30.3</v>
       </c>
       <c r="F30" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="G30" t="n">
-        <v>5.54</v>
+        <v>5.53</v>
       </c>
       <c r="H30" t="n">
         <v>29.85</v>
@@ -7422,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>23.26</v>
+        <v>24.99</v>
       </c>
       <c r="Q30" t="n">
         <v>6.85</v>
@@ -7437,21 +8253,21 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>11.86</v>
+        <v>13.43</v>
       </c>
       <c r="V30" t="b">
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>68.37</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>68.4x vs 4.2x median — trading at premium</t>
+          <t>67.4x vs 4.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -7469,267 +8285,267 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>P/S 68.4x vs 4.2x median — trading at premium | P/B -0.9x vs 0.9x median — trading at discount</t>
+          <t>P/S 67.4x vs 4.2x median — trading at premium | P/B -0.9x vs 0.9x median — trading at discount</t>
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF30" t="n">
-        <v>5.31</v>
+        <v>5.23</v>
       </c>
       <c r="AG30" t="n">
-        <v>127</v>
+        <v>127.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>-1.12</v>
+        <v>-1.17</v>
       </c>
       <c r="AI30" t="n">
-        <v>7.61</v>
+        <v>7.57</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.18–$5.31 (ann. vol 127%) | ATR range: $-1.12–$7.61</t>
+          <t>1-SD 3mo range: $1.17–$5.23 (ann. vol 127%) | ATR range: $-1.17–$7.57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LSTA</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.75</v>
+        <v>11.33</v>
       </c>
       <c r="C31" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="D31" t="n">
-        <v>861999</v>
+        <v>7021976</v>
       </c>
       <c r="E31" t="n">
-        <v>54.7</v>
+        <v>47.6</v>
       </c>
       <c r="F31" t="n">
-        <v>1.45</v>
+        <v>11.97</v>
       </c>
       <c r="G31" t="n">
-        <v>2.09</v>
+        <v>10.92</v>
       </c>
       <c r="H31" t="n">
-        <v>2.91</v>
+        <v>9.25</v>
       </c>
       <c r="I31" t="n">
-        <v>2.38</v>
+        <v>10.75</v>
       </c>
       <c r="J31" t="n">
-        <v>3.15</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.66</v>
+        <v>13.46</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-5.14</v>
+        <v>18.96</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.66</v>
+        <v>14.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.11</v>
+        <v>13.0381</v>
       </c>
       <c r="S31" t="n">
-        <v>1.6284</v>
+        <v>13.61</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>-6.95</v>
+        <v>20.28</v>
       </c>
       <c r="V31" t="b">
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>157.69</v>
+        <v>2.2</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>157.7x vs 2.1x median — trading at premium</t>
+          <t>2.2x vs 0.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>1.94</v>
+        <v>0.54</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1.9x vs 2.0x median — in-line</t>
+          <t>0.5x vs 0.5x median — in-line</t>
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>-0.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB31" t="n">
-        <v/>
+        <v>11.4</v>
       </c>
       <c r="AC31" t="n">
         <v/>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>P/S 157.7x vs 2.1x median — trading at premium | P/B 1.9x vs 2.0x median — in-line | EV/EBITDA -0.2x vs -0.8x median — trading at discount</t>
+          <t>P/S 2.2x vs 0.2x median — trading at premium | P/B 0.5x vs 0.5x median — in-line | EV/EBITDA 2.0x vs 2.0x median — in-line | Analyst target $11.40</t>
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>0.77</v>
+        <v>8</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.73</v>
+        <v>14.66</v>
       </c>
       <c r="AG31" t="n">
-        <v>112.4</v>
+        <v>58.8</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.39</v>
+        <v>4.1</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.11</v>
+        <v>18.56</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.77–$2.73 (ann. vol 112%) | ATR range: $0.39–$3.11</t>
+          <t>1-SD 3mo range: $8.00–$14.66 (ann. vol 59%) | ATR range: $4.10–$18.56</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RMAX</t>
+          <t>LSTA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11.39</v>
+        <v>1.76</v>
       </c>
       <c r="C32" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="D32" t="n">
-        <v>7036902</v>
+        <v>867475</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F32" t="n">
-        <v>11.98</v>
+        <v>1.45</v>
       </c>
       <c r="G32" t="n">
-        <v>10.92</v>
+        <v>2.09</v>
       </c>
       <c r="H32" t="n">
-        <v>9.25</v>
+        <v>2.91</v>
       </c>
       <c r="I32" t="n">
-        <v>10.76</v>
+        <v>2.38</v>
       </c>
       <c r="J32" t="n">
-        <v>8.460000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>13.46</v>
+        <v>1.66</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>18.33</v>
+        <v>-5.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>14.6</v>
+        <v>1.66</v>
       </c>
       <c r="R32" t="n">
-        <v>13.0381</v>
+        <v>1.11</v>
       </c>
       <c r="S32" t="n">
-        <v>13.61</v>
+        <v>1.6284</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>19.65</v>
+        <v>-7.48</v>
       </c>
       <c r="V32" t="b">
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>2.21</v>
+        <v>158.59</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2.2x vs 0.2x median — trading at premium</t>
+          <t>158.6x vs 2.1x median — trading at premium</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>0.55</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.5x vs 0.5x median — in-line</t>
+          <t>1.9x vs 2.0x median — in-line</t>
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>2.01</v>
+        <v>-0.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.4</v>
+        <v/>
       </c>
       <c r="AC32" t="n">
         <v/>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>P/S 2.2x vs 0.2x median — trading at premium | P/B 0.5x vs 0.5x median — in-line | EV/EBITDA 2.0x vs 2.0x median — in-line | Analyst target $11.40</t>
+          <t>P/S 158.6x vs 2.1x median — trading at premium | P/B 1.9x vs 2.0x median — in-line | EV/EBITDA -0.2x vs -0.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>8.050000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.72</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>58.7</v>
+        <v>112.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>4.16</v>
+        <v>0.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>18.61</v>
+        <v>3.12</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $8.05–$14.72 (ann. vol 59%) | ATR range: $4.16–$18.61</t>
+          <t>1-SD 3mo range: $0.77–$2.75 (ann. vol 112%) | ATR range: $0.40–$3.12</t>
         </is>
       </c>
     </row>
@@ -7740,16 +8556,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="C33" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="D33" t="n">
-        <v>636035</v>
+        <v>632627</v>
       </c>
       <c r="E33" t="n">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
       <c r="F33" t="n">
         <v>1.43</v>
@@ -7770,7 +8586,7 @@
         <v>0.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -7782,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-8.710000000000001</v>
+        <v>-8.07</v>
       </c>
       <c r="Q33" t="n">
         <v>1.35</v>
@@ -7797,7 +8613,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-7.32</v>
+        <v>-6.67</v>
       </c>
       <c r="V33" t="b">
         <v>1</v>
@@ -7811,7 +8627,7 @@
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -7833,23 +8649,23 @@
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG33" t="n">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.94–$1.93 (ann. vol 70%) | ATR range: $0.65–$2.22</t>
+          <t>1-SD 3mo range: $0.93–$1.92 (ann. vol 70%) | ATR range: $0.64–$2.21</t>
         </is>
       </c>
     </row>
@@ -7860,16 +8676,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C34" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="D34" t="n">
-        <v>829520</v>
+        <v>826351</v>
       </c>
       <c r="E34" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="F34" t="n">
         <v>0.95</v>
@@ -7902,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-9.140000000000001</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="Q34" t="n">
         <v>0.9194</v>
@@ -7917,21 +8733,21 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>-6.82</v>
+        <v>-6.39</v>
       </c>
       <c r="V34" t="b">
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>152.86</v>
+        <v>152.16</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>152.9x vs 2.1x median — trading at premium</t>
+          <t>152.2x vs 2.1x median — trading at premium</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -7949,14 +8765,14 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>P/S 152.9x vs 2.1x median — trading at premium | P/B 2.6x vs 2.0x median — trading at premium | EV/EBITDA -0.8x vs -0.8x median — in-line | Analyst target $5.10</t>
+          <t>P/S 152.2x vs 2.1x median — trading at premium | P/B 2.6x vs 2.0x median — trading at premium | EV/EBITDA -0.8x vs -0.8x median — in-line | Analyst target $5.10</t>
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG34" t="n">
         <v>90.7</v>
@@ -7965,11 +8781,11 @@
         <v>0.38</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.55–$1.45 (ann. vol 91%) | ATR range: $0.38–$1.62</t>
+          <t>1-SD 3mo range: $0.54–$1.44 (ann. vol 91%) | ATR range: $0.38–$1.61</t>
         </is>
       </c>
     </row>
@@ -7980,16 +8796,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="C35" t="n">
         <v>1.78</v>
       </c>
       <c r="D35" t="n">
-        <v>2232272</v>
+        <v>2227971</v>
       </c>
       <c r="E35" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="F35" t="n">
         <v>2.31</v>
@@ -8073,7 +8889,7 @@
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF35" t="n">
         <v>2.73</v>
@@ -8085,529 +8901,529 @@
         <v>1.4</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.57–$2.73 (ann. vol 54%) | ATR range: $1.40–$2.90</t>
+          <t>1-SD 3mo range: $1.56–$2.73 (ann. vol 54%) | ATR range: $1.40–$2.89</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DHF</t>
+          <t>ANY</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="C36" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="D36" t="n">
-        <v>738816</v>
+        <v>1366545</v>
       </c>
       <c r="E36" t="n">
-        <v>40</v>
+        <v>58.3</v>
       </c>
       <c r="F36" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="G36" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="H36" t="n">
-        <v>2.37</v>
+        <v>2.93</v>
       </c>
       <c r="I36" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="J36" t="n">
-        <v>2.36</v>
+        <v>2.61</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.43</v>
+        <v>2.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.39</v>
+        <v>2.6884</v>
       </c>
       <c r="R36" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="S36" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.43</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="V36" t="b">
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>8.15</v>
+        <v>2.22</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>8.1x vs 4.2x median — trading at premium</t>
+          <t>2.2x vs 4.2x median — trading at discount</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>0.9x vs 0.9x median — in-line</t>
+          <t>1.3x vs 0.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AA36" t="n">
-        <v/>
+        <v>-3.47</v>
       </c>
       <c r="AB36" t="n">
         <v/>
       </c>
       <c r="AC36" t="n">
-        <v>3.2</v>
+        <v/>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>P/S 8.1x vs 4.2x median — trading at premium | P/B 0.9x vs 0.9x median — in-line | Graham # $3.20</t>
+          <t>P/S 2.2x vs 4.2x median — trading at discount | P/B 1.3x vs 0.9x median — trading at premium | EV/EBITDA -3.5x vs -2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>2.2</v>
+        <v>0.73</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.48</v>
+        <v>4.23</v>
       </c>
       <c r="AG36" t="n">
-        <v>12</v>
+        <v>140.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.14</v>
+        <v>0.68</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.54</v>
+        <v>4.28</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.20–$2.48 (ann. vol 12%) | ATR range: $2.14–$2.54</t>
+          <t>1-SD 3mo range: $0.73–$4.23 (ann. vol 141%) | ATR range: $0.68–$4.28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ANY</t>
+          <t>DHF</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="C37" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="D37" t="n">
-        <v>1369722</v>
+        <v>739115</v>
       </c>
       <c r="E37" t="n">
-        <v>58.6</v>
+        <v>40</v>
       </c>
       <c r="F37" t="n">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="G37" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="H37" t="n">
-        <v>2.93</v>
+        <v>2.37</v>
       </c>
       <c r="I37" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.35</v>
       </c>
-      <c r="J37" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="b">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.55</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.62</v>
+        <v>0.43</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.6884</v>
+        <v>2.39</v>
       </c>
       <c r="R37" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>7.85</v>
+        <v>0.43</v>
       </c>
       <c r="V37" t="b">
         <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>2.23</v>
+        <v>8.15</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2.2x vs 4.2x median — trading at discount</t>
+          <t>8.1x vs 4.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>1.34</v>
+        <v>0.88</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1.3x vs 0.9x median — trading at premium</t>
+          <t>0.9x vs 0.9x median — in-line</t>
         </is>
       </c>
       <c r="AA37" t="n">
-        <v>-3.47</v>
+        <v/>
       </c>
       <c r="AB37" t="n">
         <v/>
       </c>
       <c r="AC37" t="n">
-        <v/>
+        <v>3.2</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>P/S 2.2x vs 4.2x median — trading at discount | P/B 1.3x vs 0.9x median — trading at premium | EV/EBITDA -3.5x vs -2.7x median — trading at premium</t>
+          <t>P/S 8.1x vs 4.2x median — trading at premium | P/B 0.9x vs 0.9x median — in-line | Graham # $3.20</t>
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>0.74</v>
+        <v>2.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>4.24</v>
+        <v>2.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>140.8</v>
+        <v>12</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.29</v>
+        <v>2.54</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.74–$4.24 (ann. vol 141%) | ATR range: $0.69–$4.29</t>
+          <t>1-SD 3mo range: $2.20–$2.48 (ann. vol 12%) | ATR range: $2.14–$2.54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>PLCE</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4.11</v>
+        <v>2.73</v>
       </c>
       <c r="C38" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="D38" t="n">
-        <v>3781150</v>
+        <v>514169</v>
       </c>
       <c r="E38" t="n">
-        <v>77</v>
+        <v>55.3</v>
       </c>
       <c r="F38" t="n">
-        <v>3.22</v>
+        <v>2.54</v>
       </c>
       <c r="G38" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="H38" t="n">
-        <v>5.42</v>
+        <v>3.76</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="J38" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="K38" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
       </c>
       <c r="N38" t="n">
+        <v>2.4622</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-10.14</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-9.85</v>
+      </c>
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>0.1x vs 3.9x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>-0.6x vs 0.4x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>-18.52</v>
+      </c>
+      <c r="AB38" t="n">
         <v>4</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="R38" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V38" t="b">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>8.4x vs 4.2x median — trading at premium</t>
-        </is>
-      </c>
-      <c r="Y38" t="n">
-        <v>-10.43</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>-10.4x vs 0.9x median — trading at discount</t>
-        </is>
-      </c>
-      <c r="AA38" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>5.85</v>
       </c>
       <c r="AC38" t="n">
         <v/>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>P/S 8.4x vs 4.2x median — trading at premium | P/B -10.4x vs 0.9x median — trading at discount | EV/EBITDA -1.9x vs -2.7x median — trading at discount | Analyst target $5.85</t>
+          <t>P/S 0.1x vs 3.9x median — trading at discount | P/B -0.6x vs 0.4x median — trading at discount | EV/EBITDA -18.5x vs -4.8x median — trading at premium | Analyst target $4.00</t>
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AF38" t="n">
-        <v>6.31</v>
+        <v>4.07</v>
       </c>
       <c r="AG38" t="n">
-        <v>107.2</v>
+        <v>98.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.27</v>
+        <v>4.2</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.91–$6.31 (ann. vol 107%) | ATR range: $1.95–$6.27</t>
+          <t>1-SD 3mo range: $1.39–$4.07 (ann. vol 98%) | ATR range: $1.26–$4.20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FLUX</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.71</v>
+        <v>4.09</v>
       </c>
       <c r="C39" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="D39" t="n">
-        <v>705709</v>
+        <v>3761011</v>
       </c>
       <c r="E39" t="n">
-        <v>54.6</v>
+        <v>76.7</v>
       </c>
       <c r="F39" t="n">
-        <v>0.64</v>
+        <v>3.22</v>
       </c>
       <c r="G39" t="n">
-        <v>0.72</v>
+        <v>3.18</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2</v>
+        <v>5.42</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6049</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-15.37</v>
+        <v>-1.96</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.1599</v>
+        <v>4.14</v>
       </c>
       <c r="R39" t="n">
-        <v>0.5800999999999999</v>
+        <v>3.07</v>
       </c>
       <c r="S39" t="n">
-        <v>0.58</v>
+        <v>4.16</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>-18.86</v>
+        <v>1.96</v>
       </c>
       <c r="V39" t="b">
         <v>1</v>
       </c>
       <c r="W39" t="n">
-        <v>0.3</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.3x vs 0.7x median — trading at discount</t>
+          <t>8.4x vs 4.2x median — trading at premium</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>3.31</v>
+        <v>-10.36</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>3.3x vs 2.7x median — trading at premium</t>
+          <t>-10.4x vs 0.9x median — trading at discount</t>
         </is>
       </c>
       <c r="AA39" t="n">
-        <v>-5.73</v>
+        <v>-1.86</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.53</v>
+        <v>5.85</v>
       </c>
       <c r="AC39" t="n">
         <v/>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>P/S 0.3x vs 0.7x median — trading at discount | P/B 3.3x vs 2.7x median — trading at premium | EV/EBITDA -5.7x vs -1.5x median — trading at premium | Analyst target $4.53</t>
+          <t>P/S 8.4x vs 4.2x median — trading at premium | P/B -10.4x vs 0.9x median — trading at discount | EV/EBITDA -1.9x vs -2.7x median — trading at discount | Analyst target $5.85</t>
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>0.24</v>
+        <v>1.9</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.19</v>
+        <v>6.27</v>
       </c>
       <c r="AG39" t="n">
-        <v>132.9</v>
+        <v>107.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.12</v>
+        <v>1.92</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.55</v>
+        <v>6.25</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.24–$1.19 (ann. vol 133%) | ATR range: $-0.12–$1.55</t>
+          <t>1-SD 3mo range: $1.90–$6.27 (ann. vol 107%) | ATR range: $1.92–$6.25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>REAX</t>
+          <t>FLUX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.22</v>
+        <v>0.72</v>
       </c>
       <c r="C40" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="D40" t="n">
-        <v>13089185</v>
+        <v>706479</v>
       </c>
       <c r="E40" t="n">
-        <v>50.7</v>
+        <v>54.6</v>
       </c>
       <c r="F40" t="n">
-        <v>2.28</v>
+        <v>0.64</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11</v>
+        <v>0.72</v>
       </c>
       <c r="H40" t="n">
-        <v>2.67</v>
+        <v>1.2</v>
       </c>
       <c r="I40" t="n">
-        <v>2.01</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="K40" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -8616,80 +9432,440 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6485</v>
+        <v>0.6049</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>19.03</v>
+        <v>-14.48</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.8492</v>
+        <v>1.1599</v>
       </c>
       <c r="R40" t="n">
-        <v>2.59</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="S40" t="n">
-        <v>2.63</v>
+        <v>0.58</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>18.2</v>
+        <v>-18</v>
       </c>
       <c r="V40" t="b">
         <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>0.2x vs 0.2x median — in-line</t>
+          <t>0.3x vs 0.7x median — trading at discount</t>
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>6.16</v>
+        <v>3.24</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>6.2x vs 0.5x median — trading at premium</t>
+          <t>3.2x vs 2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AA40" t="n">
-        <v>-387.98</v>
+        <v>-5.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.95</v>
+        <v>4.53</v>
       </c>
       <c r="AC40" t="n">
         <v/>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>P/S 0.2x vs 0.2x median — in-line | P/B 6.2x vs 0.5x median — trading at premium | EV/EBITDA -388.0x vs 2.0x median — trading at discount | Analyst target $4.95</t>
+          <t>P/S 0.3x vs 0.7x median — trading at discount | P/B 3.2x vs 2.7x median — trading at premium | EV/EBITDA -5.7x vs -1.5x median — trading at premium | Analyst target $4.53</t>
         </is>
       </c>
       <c r="AE40" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.24–$1.19 (ann. vol 133%) | ATR range: $-0.12–$1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>REAX</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D41" t="n">
+        <v>13100397</v>
+      </c>
+      <c r="E41" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.6485</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.8492</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>0.2x vs 0.2x median — in-line</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>6.1x vs 0.5x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>-387.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AC41" t="n">
+        <v/>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>P/S 0.2x vs 0.2x median — in-line | P/B 6.1x vs 0.5x median — trading at premium | EV/EBITDA -388.0x vs 2.0x median — trading at discount | Analyst target $4.95</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF40" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AG40" t="n">
+      <c r="AF41" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG41" t="n">
         <v>67.5</v>
       </c>
-      <c r="AH40" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AI40" t="n">
+      <c r="AH41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI41" t="n">
         <v>3.84</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>1-SD 3mo range: $1.47–$2.98 (ann. vol 68%) | ATR range: $0.61–$3.84</t>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $1.47–$2.97 (ann. vol 68%) | ATR range: $0.60–$3.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1202297</v>
+      </c>
+      <c r="E42" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="H42" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v/>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Analyst target $9.50</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $2.39–$9.77 (ann. vol 121%) | ATR range: $2.07–$10.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CAPR</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D43" t="n">
+        <v>83193784</v>
+      </c>
+      <c r="E43" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G43" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="H43" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="I43" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="J43" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>6.3796</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6.1714</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v/>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>1.7x vs 2.0x median — in-line</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v/>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>P/B 1.7x vs 2.0x median — in-line | EV/EBITDA -1.6x vs -0.8x median — trading at premium | Analyst target $10.50</t>
+        </is>
+      </c>
+      <c r="AE43" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $-0.54–$14.68 (ann. vol 215%) | ATR range: $-0.88–$15.02</t>
         </is>
       </c>
     </row>
@@ -8704,7 +9880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8712,8 +9888,11 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8744,10 +9923,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>item_bonus</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>item_summary</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>item_title</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>accession_number</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>primary_document</t>
         </is>
@@ -8774,12 +9968,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Items: 7.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>0001193125-26-353285</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>d374220d8k.htm</t>
         </is>
@@ -8806,12 +10009,25 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Item 1.01 (entry_agreement, +3) | Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Entry Into a Material Definitive Agreement.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>0001903596-26-000317</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>xpon_8k.htm</t>
         </is>
@@ -8838,12 +10054,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0001213900-26-091288</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ea0302597-8k_cidhold.htm</t>
         </is>
@@ -8870,12 +10095,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>0001193125-26-353639</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>gipr-20260817.htm</t>
         </is>
@@ -8902,12 +10136,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>0001493152-26-039708</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>form8-k.htm</t>
         </is>
@@ -8934,12 +10177,17 @@
           <t>dilution_risk</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>0001493152-26-039421</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>forms-1.htm</t>
         </is>
@@ -8966,12 +10214,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>0001493152-26-038637</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>form8-k.htm</t>
         </is>
@@ -8998,12 +10255,25 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&gt;pmi20260814_8k.htm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>0001437749-26-028585</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>pmi20260814_8k.htm</t>
         </is>
@@ -9032,15 +10302,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>0002092596-26-000002</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>xslF345X06/form4-08192026_100818.xml</t>
         </is>
@@ -9069,15 +10344,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>0001231919-26-000951</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>xslF345X06/form4-08192026_100822.xml</t>
         </is>
@@ -9107,12 +10387,25 @@
       <c r="E12" t="n">
         <v/>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Entry into a Material Definitive Agreement</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>0001104659-26-098120</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>tm2623453d1_8k.htm</t>
         </is>
@@ -9139,12 +10432,25 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Item 1.01 (entry_agreement, +3) | Item 1.02 (termination_agreement, +1)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&amp;#160;Entry into a Material Definitive Agreement.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>0001213900-26-092163</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>ea0302895-8k_cantor1.htm</t>
         </is>
@@ -9153,81 +10459,97 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>VBIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K/A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0001104659-26-097370</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>xslF345X06/tm2623246-2_4seq1.xml</t>
+          <t>Items: 5.07 (routine)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&gt;Tivic Health Systems, Inc. Form 8-K</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0001683168-26-006632</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>valion_8ka1.htm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>VBIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0001104659-26-097369</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>-1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>xslF345X06/tm2623246-1_4seq1.xml</t>
+          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&gt;Tivic Health Systems, Inc. Form 8-K</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0001683168-26-006501</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>valion_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>NPWR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9237,7 +10559,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9247,24 +10569,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0001683168-26-006540</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0001104659-26-097370</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>xslF345X06/tm2623246-2_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>NPWR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9274,7 +10601,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9284,17 +10611,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0001683168-26-006538</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0001104659-26-097369</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>xslF345X06/tm2623246-1_4seq1.xml</t>
         </is>
       </c>
     </row>
@@ -9321,15 +10653,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0001683168-26-006530</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0001683168-26-006540</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>xslF345X06/ownership.xml</t>
         </is>
@@ -9338,44 +10675,54 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>VBIO</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8-K/A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0001683168-26-006632</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>valion_8ka1.htm</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0001683168-26-006538</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VBIO</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9385,17 +10732,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0001683168-26-006501</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>valion_8k.htm</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0001683168-26-006530</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
@@ -9420,12 +10777,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Items: 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>0001493152-26-038731</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>form8-k.htm</t>
         </is>
@@ -9454,15 +10820,20 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>0001193125-26-354145</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>xslF345X06/ownership.xml</t>
         </is>
@@ -9489,12 +10860,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>0001493152-26-039377</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>form8-k.htm</t>
         </is>
@@ -9521,12 +10901,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>0001104659-26-099714</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>tm2623567d2_8k.htm</t>
         </is>
@@ -9553,12 +10942,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>0001104659-26-099272</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>tm2623567d1_8k.htm</t>
         </is>
@@ -9585,12 +10983,21 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Items: 5.07, 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>0001104659-26-097203</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>tm2623076d1_8k.htm</t>
         </is>
@@ -9617,12 +11024,25 @@
           <t>material_event</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>&gt;Sphere 3D Corp.: Form 8-K - Filed by newsfilecorp.com</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>0001062993-26-004391</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>form8k.htm</t>
         </is>
@@ -9631,37 +11051,41 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>PLCE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0001225208-26-007275</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>-1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>xslF345X06/doc4.xml</t>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0001104659-26-097257</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>tm2623304d1_8k.htm</t>
         </is>
       </c>
     </row>
@@ -9678,7 +11102,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -9688,15 +11112,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0001225208-26-007188</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0001225208-26-007275</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>xslF345X06/doc4.xml</t>
         </is>
@@ -9715,7 +11144,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -9725,15 +11154,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0001225208-26-007140</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0001225208-26-007188</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>xslF345X06/doc4.xml</t>
         </is>
@@ -9742,32 +11176,300 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>DFDV</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0001225208-26-007140</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>FLUX</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>8-K</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>material_event</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>0001493152-26-039473</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>form8-k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v/>
+      </c>
+      <c r="F33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0001213900-26-092591</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ea0303021-8k_forum.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v/>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Items: 5.07, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0001213900-26-091693</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ea0302772-8k_forum.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0001213900-26-090114</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0001213900-26-090081</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CAPR</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Items: 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>&gt;CAPRICOR THERAPEUTICS, INC._August 24, 2026</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0001104659-26-100071</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>capr-20260824x8k.htm</t>
         </is>
       </c>
     </row>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -656,13 +656,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0901</v>
+        <v>1.1385</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.57</v>
+        <v>3.84</v>
       </c>
       <c r="S2" t="n">
         <v>1.04</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XPON</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>19.2</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -731,51 +731,51 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, +8.0pts)   Item 1.01 (entry_agreement, +3) | Item 5.02 (officer_departure, -1)   Title: Entry Into a Material Definitive Agreement.</t>
+          <t>2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_buy, +3.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_buy, +3.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 4 (insider_other, +0.0pts) | 2026-08-24 8-K (material_event, -2.0pts)   Item 2.01 (acquisition, +4) | Item 1.02 (termination_agreement, +1) | Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3) | Item 3.03 (rights_modification, -1) | Item 5.01 (control_change, +2) | Item 5.02 (officer_departure, -1)   Title: &amp;#160; | 2026-08-21 8-K (material_event, +1.4pts)   Items: 7.01, 9.01 (routine) | 2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine) | 2026-08-14 8-K (material_event, +0.0pts)   Items: 5.07, 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +4, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>6.2</v>
+        <v>12.36</v>
       </c>
       <c r="N3" t="n">
-        <v>17.1</v>
+        <v>3.74</v>
       </c>
       <c r="O3" t="n">
-        <v>71</v>
+        <v>55.6</v>
       </c>
       <c r="P3" t="n">
-        <v>5.42</v>
+        <v>13.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>211582</v>
       </c>
       <c r="R3" t="n">
-        <v>-10.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>8.41</v>
+        <v>13.61</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>39.52</v>
+        <v>9.85</v>
       </c>
       <c r="V3" t="n">
-        <v>6.39</v>
+        <v>14.6</v>
       </c>
       <c r="W3" t="n">
-        <v>3.41</v>
+        <v>12.35</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
@@ -786,21 +786,21 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CEPO</t>
+          <t>XPON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -812,13 +812,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -829,51 +829,51 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +6.0pts)   Item 1.01 (entry_agreement, +3) | Item 1.02 (termination_agreement, +1)   Title: &amp;#160;Entry into a Material Definitive Agreement.</t>
+          <t>2026-08-24 8-K (material_event, +8.0pts)   Item 1.01 (entry_agreement, +3) | Item 5.02 (officer_departure, -1)   Title: Entry Into a Material Definitive Agreement.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>10.8</v>
+        <v>6.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6.36</v>
+        <v>17.1</v>
       </c>
       <c r="O4" t="n">
-        <v>64.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="P4" t="n">
-        <v>10.8</v>
+        <v>5.55</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>-7.93</v>
       </c>
       <c r="S4" t="n">
-        <v>10.79</v>
+        <v>8.41</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09</v>
+        <v>39.52</v>
       </c>
       <c r="V4" t="n">
-        <v>10.828</v>
+        <v>6.39</v>
       </c>
       <c r="W4" t="n">
-        <v>10.68</v>
+        <v>3.41</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>CEPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -907,16 +907,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -927,51 +927,51 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K/A (material_event, +2.0pts)   Items: 2.02, 8.01, 9.01 (routine) | 2026-08-24 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)</t>
+          <t>2026-08-20 8-K (material_event, +6.0pts)   Item 1.01 (entry_agreement, +3) | Item 1.02 (termination_agreement, +1)   Title: &amp;#160;Entry into a Material Definitive Agreement.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +4, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.92</v>
+        <v>10.8</v>
       </c>
       <c r="N5" t="n">
-        <v>4.63</v>
+        <v>6.36</v>
       </c>
       <c r="O5" t="n">
-        <v>81</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>2.818</v>
+        <v>10.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.66</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>10.79</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-7.43</v>
+        <v>-0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>2.92</v>
+        <v>10.828</v>
       </c>
       <c r="W5" t="n">
-        <v>1.93</v>
+        <v>10.68</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1005,71 +1005,71 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>108.7</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-24 4 (insider_buy, +3.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +2.4pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement</t>
+          <t>2026-08-24 8-K/A (material_event, +2.0pts)   Items: 2.02, 8.01, 9.01 (routine) | 2026-08-24 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_overbought -2</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1.68</v>
+        <v>2.92</v>
       </c>
       <c r="N6" t="n">
-        <v>7.79</v>
+        <v>4.63</v>
       </c>
       <c r="O6" t="n">
-        <v>88.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>2.82</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>-2.59</v>
       </c>
       <c r="S6" t="n">
-        <v>1.86</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>11.38</v>
+        <v>-7.43</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7705</v>
+        <v>1.93</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
@@ -1088,86 +1088,86 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRBS</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.41</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.68</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-1.7</v>
+        <v>108.7</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-17 8-K (material_event, +0.6pts)   Items: 7.01 (routine)</t>
+          <t>2026-08-24 4 (insider_buy, +3.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +2.4pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>trend_alignment +4, golden_cross +2, rsi_mild_high +1</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3.93</v>
+        <v>1.68</v>
       </c>
       <c r="N7" t="n">
-        <v>1.02</v>
+        <v>7.79</v>
       </c>
       <c r="O7" t="n">
-        <v>66.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>1.721</v>
       </c>
       <c r="Q7" t="n">
-        <v>65522</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.27</v>
+        <v>3.05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.76</v>
+        <v>11.38</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="W7" t="n">
-        <v>3.9</v>
+        <v>0.7705</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>7.41</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RMAX</t>
+          <t>BRBS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1201,16 +1201,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.2</v>
+        <v>7.41</v>
       </c>
       <c r="D8" t="n">
         <v>0.6</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0.68</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1221,51 +1221,51 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, -2.0pts)   Item 2.01 (acquisition, +4) | Item 1.02 (termination_agreement, +1) | Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3) | Item 3.03 (rights_modification, -1) | Item 5.01 (control_change, +2) | Item 5.02 (officer_departure, -1)   Title: &amp;#160; | 2026-08-21 8-K (material_event, +1.4pts)   Items: 7.01, 9.01 (routine) | 2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine) | 2026-08-14 8-K (material_event, +0.0pts)   Items: 5.07, 7.01, 9.01 (routine)</t>
+          <t>2026-08-17 8-K (material_event, +0.6pts)   Items: 7.01 (routine)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, golden_cross +2, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12.36</v>
+        <v>3.93</v>
       </c>
       <c r="N8" t="n">
-        <v>3.74</v>
+        <v>1.02</v>
       </c>
       <c r="O8" t="n">
-        <v>55.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>13.21</v>
+        <v>3.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>211582</v>
+        <v>65522</v>
       </c>
       <c r="R8" t="n">
-        <v>6.62</v>
+        <v>-1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>13.61</v>
+        <v>3.98</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>9.85</v>
+        <v>0.76</v>
       </c>
       <c r="V8" t="n">
-        <v>14.6</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>12.35</v>
+        <v>3.89</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>7.2</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="9">
@@ -1374,15 +1374,15 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>7.12</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="10">
@@ -1440,13 +1440,13 @@
         <v>64.90000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>10.69</v>
+        <v>10.77</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="S10" t="n">
         <v>10.27</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>62</v>
       </c>
       <c r="P15" t="n">
-        <v>6.63</v>
+        <v>6.48</v>
       </c>
       <c r="Q15" t="n">
         <v>3136</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.15</v>
+        <v>-2.41</v>
       </c>
       <c r="S15" t="n">
         <v>6.51</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         <v>57.4</v>
       </c>
       <c r="P17" t="n">
-        <v>16.18</v>
+        <v>16.55</v>
       </c>
       <c r="Q17" t="n">
         <v>12447</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.92</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
         <v>16.65</v>
@@ -2144,7 +2144,7 @@
         <v>1.96</v>
       </c>
       <c r="V17" t="n">
-        <v>16.36</v>
+        <v>16.55</v>
       </c>
       <c r="W17" t="n">
         <v>15.29</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2224,13 +2224,13 @@
         <v>75</v>
       </c>
       <c r="P18" t="n">
-        <v>5.8085</v>
+        <v>5.75</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>0.17</v>
       </c>
       <c r="S18" t="n">
         <v>5.52</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2322,13 +2322,13 @@
         <v>63.5</v>
       </c>
       <c r="P19" t="n">
-        <v>7.28</v>
+        <v>7.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="S19" t="n">
         <v>6.69</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4696</v>
+        <v>1.4699</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="S20" t="n">
         <v>1.5</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         <v>53.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6994</v>
+        <v>0.6827</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.63</v>
+        <v>-1.77</v>
       </c>
       <c r="S21" t="n">
         <v>0.58</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>58.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.79</v>
+        <v>3.8139</v>
       </c>
       <c r="Q23" t="n">
         <v>221</v>
       </c>
       <c r="R23" t="n">
-        <v>0.53</v>
+        <v>1.16</v>
       </c>
       <c r="S23" t="n">
         <v>3.84</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>68.09999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>2.86</v>
+        <v>2.7003</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.35</v>
+        <v>-5.25</v>
       </c>
       <c r="S26" t="n">
         <v>2.91</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>ANY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3063,71 +3063,71 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.64</v>
+        <v>3.92</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Late Entry</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>29.4</v>
+        <v>15.7</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 4 (insider_buy, +3.0pts) | 2026-08-21 4 (insider_buy, +2.1pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_buy, +0.9pts)</t>
+          <t>2026-08-24 8-K (material_event, +2.0pts)   Items: 5.07, 7.01, 8.01, 9.01 (routine)   Title: &gt;DarkHorse Technologies Inc.: Form 8-K - Filed by newsfilecorp.com | 2026-08-14 8-K (material_event, +0.0pts)   Items: 2.02, 7.01, 9.01 (routine)   Title: &gt;Sphere 3D Corp.: Form 8-K - Filed by newsfilecorp.com</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_overbought -2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4.09</v>
+        <v>2.43</v>
       </c>
       <c r="N27" t="n">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="O27" t="n">
-        <v>76.8</v>
+        <v>56.7</v>
       </c>
       <c r="P27" t="n">
-        <v>4.08</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.49</v>
+        <v>-1.65</v>
       </c>
       <c r="S27" t="n">
-        <v>4.16</v>
+        <v>2.69</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.46</v>
+        <v>11.16</v>
       </c>
       <c r="V27" t="n">
-        <v>4.15</v>
+        <v>2.6884</v>
       </c>
       <c r="W27" t="n">
-        <v>3.07</v>
+        <v>1.94</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>3.64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>-4</v>
@@ -3181,51 +3181,51 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>69.3</v>
+        <v>29.4</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine)   Title: &gt;pmi20260814_8k.htm</t>
+          <t>2026-08-24 4 (insider_buy, +3.0pts) | 2026-08-21 4 (insider_buy, +2.1pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-17 4 (insider_buy, +0.9pts)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_mild_high +1</t>
+          <t>trend_alignment +2, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>5.13</v>
+        <v>4.09</v>
       </c>
       <c r="N28" t="n">
-        <v>13.65</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>66.8</v>
+        <v>76.8</v>
       </c>
       <c r="P28" t="n">
-        <v>5.5571</v>
+        <v>4.1073</v>
       </c>
       <c r="Q28" t="n">
-        <v>1962</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>6.72</v>
+        <v>0.18</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3402</v>
+        <v>4.16</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>-16.65</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>4.15</v>
       </c>
       <c r="W28" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VITL</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3259,74 +3259,74 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="D29" t="n">
         <v>1.2</v>
       </c>
       <c r="E29" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>-0.7</v>
+        <v>69.3</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-17 8-K/A (material_event, +0.6pts)   Items: 5.03, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.6pts)   Items: 5.03, 9.01 (routine)</t>
+          <t>2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine)   Title: &gt;pmi20260814_8k.htm</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>11.08</v>
+        <v>5.13</v>
       </c>
       <c r="N29" t="n">
-        <v>1.51</v>
+        <v>13.65</v>
       </c>
       <c r="O29" t="n">
-        <v>42.3</v>
+        <v>66.8</v>
       </c>
       <c r="P29" t="n">
-        <v/>
+        <v>5.48</v>
       </c>
       <c r="Q29" t="n">
-        <v/>
+        <v>1962</v>
       </c>
       <c r="R29" t="n">
-        <v/>
+        <v>5.23</v>
       </c>
       <c r="S29" t="n">
-        <v/>
+        <v>4.3402</v>
       </c>
       <c r="T29" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v/>
+        <v>-16.65</v>
       </c>
       <c r="V29" t="n">
-        <v/>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v/>
+        <v>3.03</v>
       </c>
       <c r="X29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB29" t="n">
-        <v/>
+        <v>3.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>VITL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,74 +3357,74 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F30" t="n">
         <v>2</v>
       </c>
-      <c r="F30" t="n">
-        <v>3</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v/>
+        <v>-0.7</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-17 8-K/A (material_event, +0.6pts)   Items: 5.03, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.6pts)   Items: 5.03, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3.46</v>
+        <v>11.08</v>
       </c>
       <c r="N30" t="n">
-        <v>15.83</v>
+        <v>1.51</v>
       </c>
       <c r="O30" t="n">
-        <v>47.2</v>
+        <v>42.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.7</v>
+        <v/>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="R30" t="n">
-        <v>6.63</v>
+        <v/>
       </c>
       <c r="S30" t="n">
-        <v>4.01</v>
+        <v/>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="U30" t="n">
-        <v>15.56</v>
+        <v/>
       </c>
       <c r="V30" t="n">
-        <v>4.07</v>
+        <v/>
       </c>
       <c r="W30" t="n">
-        <v>3.4</v>
+        <v/>
       </c>
       <c r="X30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>BCTX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3489,37 +3489,37 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>1.12</v>
+        <v>3.46</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7</v>
+        <v>15.83</v>
       </c>
       <c r="O31" t="n">
-        <v>52.6</v>
+        <v>47.2</v>
       </c>
       <c r="P31" t="n">
-        <v>1.1097</v>
+        <v>3.62</v>
       </c>
       <c r="Q31" t="n">
-        <v>7057</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.03</v>
+        <v>4.32</v>
       </c>
       <c r="S31" t="n">
-        <v>1.24</v>
+        <v>4.01</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>11.71</v>
+        <v>15.56</v>
       </c>
       <c r="V31" t="n">
-        <v>1.52</v>
+        <v>4.07</v>
       </c>
       <c r="W31" t="n">
-        <v>0.9236</v>
+        <v>3.4</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VBIO</t>
+          <t>SDEV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3556,68 +3556,68 @@
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>-9.300000000000001</v>
+        <v/>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K/A (material_event, +1.2pts)   Items: 5.07 (routine)   Title: &gt;Tivic Health Systems, Inc. Form 8-K | 2026-08-17 8-K (material_event, +0.3pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)   Title: &gt;Tivic Health Systems, Inc. Form 8-K</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.17</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>4.26</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
-        <v>33.8</v>
+        <v>52.6</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1496</v>
+        <v>1.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>7057</v>
       </c>
       <c r="R32" t="n">
-        <v>-7.6</v>
+        <v>4.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1166</v>
+        <v>1.24</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>-27.98</v>
+        <v>11.71</v>
       </c>
       <c r="V32" t="n">
-        <v>0.166</v>
+        <v>1.52</v>
       </c>
       <c r="W32" t="n">
-        <v>0.113</v>
+        <v>0.9236</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>VBIO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3654,13 +3654,13 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3671,51 +3671,51 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-14 4 (insider_sell, -0.0pts) | 2026-08-14 4 (insider_sell, -0.0pts)</t>
+          <t>2026-08-20 8-K/A (material_event, +1.2pts)   Items: 5.07 (routine)   Title: &gt;Tivic Health Systems, Inc. Form 8-K | 2026-08-17 8-K (material_event, +0.3pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)   Title: &gt;Tivic Health Systems, Inc. Form 8-K</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_mild_high +1</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1.99</v>
+        <v>0.17</v>
       </c>
       <c r="N33" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="O33" t="n">
-        <v>66.90000000000001</v>
+        <v>33.8</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>0.143</v>
       </c>
       <c r="Q33" t="n">
-        <v>69400</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.51</v>
+        <v>-11.67</v>
       </c>
       <c r="S33" t="n">
-        <v>1.68</v>
+        <v>0.1166</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-15.15</v>
+        <v>-27.98</v>
       </c>
       <c r="V33" t="n">
-        <v>2.02</v>
+        <v>0.166</v>
       </c>
       <c r="W33" t="n">
-        <v>1.5202</v>
+        <v>0.113</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UPXI</t>
+          <t>NPWR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3765,55 +3765,55 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v/>
+        <v>2.1</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-14 4 (insider_sell, -0.0pts) | 2026-08-14 4 (insider_sell, -0.0pts)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="N34" t="n">
-        <v>3.04</v>
+        <v>4.17</v>
       </c>
       <c r="O34" t="n">
-        <v>63.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="P34" t="n">
-        <v>1.0403</v>
+        <v>1.9503</v>
       </c>
       <c r="Q34" t="n">
-        <v>7998</v>
+        <v>69400</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>5.83</v>
+        <v>-15.15</v>
       </c>
       <c r="V34" t="n">
-        <v>1.12</v>
+        <v>2.0397</v>
       </c>
       <c r="W34" t="n">
-        <v>0.785</v>
+        <v>1.5202</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LSTA</t>
+          <t>UPXI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -3881,37 +3881,37 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="N35" t="n">
-        <v>2.17</v>
+        <v>3.04</v>
       </c>
       <c r="O35" t="n">
-        <v>55</v>
+        <v>63.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>7998</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.15</v>
+        <v>0.97</v>
       </c>
       <c r="S35" t="n">
-        <v>1.6284</v>
+        <v>1.09</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>-6.41</v>
+        <v>5.83</v>
       </c>
       <c r="V35" t="n">
-        <v>1.7692</v>
+        <v>1.12</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>0.785</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CRDF</t>
+          <t>LSTA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3951,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -3979,37 +3979,37 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="O36" t="n">
-        <v>52.1</v>
+        <v>55</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9996</v>
+        <v>1.75</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.31</v>
+        <v>0.57</v>
       </c>
       <c r="S36" t="n">
-        <v>0.9301</v>
+        <v>1.6284</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-6.66</v>
+        <v>-6.41</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.7692</v>
       </c>
       <c r="W36" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GORO</t>
+          <t>CRDF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4049,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -4077,37 +4077,37 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>3.53</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>63.4</v>
+        <v>52.1</v>
       </c>
       <c r="P37" t="n">
-        <v>3.56</v>
+        <v>0.9996</v>
       </c>
       <c r="Q37" t="n">
-        <v>29096</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.14</v>
+        <v>0.31</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>0.9301</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>-7.67</v>
+        <v>-6.66</v>
       </c>
       <c r="V37" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>2.69</v>
+        <v>0.88</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAPR</t>
+          <t>GORO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4141,71 +4141,71 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>1.13</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, +2.0pts)   Items: 8.01, 9.01 (routine)   Title: &gt;CAPRICOR THERAPEUTICS, INC._August 24, 2026</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>6.8</v>
+        <v>3.53</v>
       </c>
       <c r="N38" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O38" t="n">
-        <v>38.4</v>
+        <v>63.4</v>
       </c>
       <c r="P38" t="n">
-        <v>6.8186</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>29096</v>
       </c>
       <c r="R38" t="n">
-        <v>0.5</v>
+        <v>2.27</v>
       </c>
       <c r="S38" t="n">
-        <v>6.81</v>
+        <v>3.25</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.37</v>
+        <v>-7.67</v>
       </c>
       <c r="V38" t="n">
-        <v>8.01</v>
+        <v>3.6</v>
       </c>
       <c r="W38" t="n">
-        <v>6.1714</v>
+        <v>2.69</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
@@ -4216,21 +4216,21 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MCRP</t>
+          <t>CAPR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4239,71 +4239,71 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D39" t="n">
         <v>2</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-24 8-K (material_event, +2.0pts)   Items: 8.01, 9.01 (routine)   Title: &gt;CAPRICOR THERAPEUTICS, INC._August 24, 2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>1.16</v>
+        <v>6.8</v>
       </c>
       <c r="N39" t="n">
-        <v>10.33</v>
+        <v>1.69</v>
       </c>
       <c r="O39" t="n">
-        <v>41.8</v>
+        <v>38.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.36</v>
+        <v>6.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>2116</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>17.24</v>
+        <v>0.37</v>
       </c>
       <c r="S39" t="n">
-        <v>1.24</v>
+        <v>6.81</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>6.9</v>
+        <v>0.37</v>
       </c>
       <c r="V39" t="n">
-        <v>1.55</v>
+        <v>8.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.16</v>
+        <v>6.1714</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v/>
+        <v>2.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEFT</t>
+          <t>MCRP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
@@ -4367,41 +4367,41 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.62</v>
+        <v>1.16</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>10.33</v>
       </c>
       <c r="O40" t="n">
-        <v>67.40000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6361</v>
+        <v>1.3498</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2116</v>
       </c>
       <c r="R40" t="n">
-        <v>3.01</v>
+        <v>16.36</v>
       </c>
       <c r="S40" t="n">
-        <v>0.631</v>
+        <v>1.24</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.19</v>
+        <v>6.9</v>
       </c>
       <c r="V40" t="n">
-        <v>0.6361</v>
+        <v>1.55</v>
       </c>
       <c r="W40" t="n">
-        <v>0.43</v>
+        <v>1.16</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NGEN</t>
+          <t>DEFT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -4469,37 +4469,37 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>0.62</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>68.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>2.01</v>
+        <v>0.633</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.75</v>
+        <v>2.51</v>
       </c>
       <c r="S41" t="n">
-        <v>1.93</v>
+        <v>0.631</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>-3.26</v>
+        <v>2.19</v>
       </c>
       <c r="V41" t="n">
-        <v>2.083</v>
+        <v>0.6361</v>
       </c>
       <c r="W41" t="n">
-        <v>1.6303</v>
+        <v>0.43</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOVX</t>
+          <t>NGEN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -4563,41 +4563,41 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.6899999999999999</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
-        <v>40.1</v>
+        <v>68.2</v>
       </c>
       <c r="P42" t="n">
-        <v>0.6902</v>
+        <v>1.97</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.07</v>
+        <v>-1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>0.718</v>
+        <v>1.93</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>6.18</v>
+        <v>-3.26</v>
       </c>
       <c r="V42" t="n">
-        <v>0.7</v>
+        <v>2.0899</v>
       </c>
       <c r="W42" t="n">
-        <v>0.5907</v>
+        <v>1.6303</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZVIA</t>
+          <t>GOVX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4637,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
@@ -4665,37 +4665,37 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>45.4</v>
+        <v>40.1</v>
       </c>
       <c r="P43" t="n">
-        <v>1.42</v>
+        <v>0.6896</v>
       </c>
       <c r="Q43" t="n">
-        <v>10065</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="S43" t="n">
-        <v>1.33</v>
+        <v>0.718</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>-5.34</v>
+        <v>6.18</v>
       </c>
       <c r="V43" t="n">
-        <v>1.4395</v>
+        <v>0.7</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>0.5907</v>
       </c>
       <c r="X43" t="b">
         <v>1</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VVR</t>
+          <t>ZVIA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4735,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -4763,37 +4763,37 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2.93</v>
+        <v>1.4</v>
       </c>
       <c r="N44" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="O44" t="n">
-        <v>46.6</v>
+        <v>45.4</v>
       </c>
       <c r="P44" t="n">
-        <v>2.93</v>
+        <v>1.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>9895</v>
+        <v>10065</v>
       </c>
       <c r="R44" t="n">
-        <v>-0</v>
+        <v>-0.36</v>
       </c>
       <c r="S44" t="n">
-        <v>2.9339</v>
+        <v>1.33</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0.13</v>
+        <v>-5.34</v>
       </c>
       <c r="V44" t="n">
-        <v>2.9591</v>
+        <v>1.4395</v>
       </c>
       <c r="W44" t="n">
-        <v>2.925</v>
+        <v>1.27</v>
       </c>
       <c r="X44" t="b">
         <v>1</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>VVR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
@@ -4861,37 +4861,37 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>4.85</v>
+        <v>2.93</v>
       </c>
       <c r="N45" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="O45" t="n">
-        <v>49.2</v>
+        <v>46.6</v>
       </c>
       <c r="P45" t="n">
-        <v>4.85</v>
+        <v>2.93</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>9895</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.41</v>
+        <v>-0</v>
       </c>
       <c r="S45" t="n">
-        <v>4.7005</v>
+        <v>2.9339</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>-3.48</v>
+        <v>0.13</v>
       </c>
       <c r="V45" t="n">
-        <v>5.23</v>
+        <v>2.9591</v>
       </c>
       <c r="W45" t="n">
-        <v>4.78</v>
+        <v>2.925</v>
       </c>
       <c r="X45" t="b">
         <v>1</v>
@@ -4916,7 +4916,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GGN</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
@@ -4955,41 +4955,41 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>5.68</v>
+        <v>4.85</v>
       </c>
       <c r="N46" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O46" t="n">
-        <v>81.8</v>
+        <v>49.2</v>
       </c>
       <c r="P46" t="n">
-        <v>5.68</v>
+        <v>4.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>5498</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.18</v>
+        <v>-0.41</v>
       </c>
       <c r="S46" t="n">
-        <v>5.7</v>
+        <v>4.7005</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0.18</v>
+        <v>-3.48</v>
       </c>
       <c r="V46" t="n">
-        <v>5.69</v>
+        <v>5.23</v>
       </c>
       <c r="W46" t="n">
-        <v>5.33</v>
+        <v>4.78</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BRR</t>
+          <t>GGN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5023,75 +5023,71 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-19 424B3 (dilution_risk, -2.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>2.15</v>
+        <v>5.68</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="O47" t="n">
-        <v>64.3</v>
+        <v>81.8</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1203</v>
+        <v>5.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>5498</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.46</v>
+        <v>0.18</v>
       </c>
       <c r="S47" t="n">
-        <v>2.15</v>
+        <v>5.7</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="V47" t="n">
-        <v>2.2714</v>
+        <v>5.7</v>
       </c>
       <c r="W47" t="n">
-        <v>1.88</v>
+        <v>5.33</v>
       </c>
       <c r="X47" t="b">
         <v>1</v>
@@ -5102,7 +5098,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5110,13 +5106,13 @@
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>BRR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5125,16 +5121,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4</v>
+        <v>-2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -5145,7 +5141,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>-10.2</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -5154,46 +5150,46 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-21 424B3 (dilution_risk, -2.8pts) | 2026-08-21 8-K (material_event, +4.2pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement. | 2026-08-20 424B3 (dilution_risk, -2.4pts) | 2026-08-17 8-K (material_event, +0.6pts)   Items: 2.02, 9.01 (routine)</t>
+          <t>2026-08-19 424B3 (dilution_risk, -2.0pts)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>4.83</v>
+        <v>2.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="O48" t="n">
-        <v>48.5</v>
+        <v>64.3</v>
       </c>
       <c r="P48" t="n">
-        <v>4.7</v>
+        <v>2.1203</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-2.69</v>
+        <v>-0.46</v>
       </c>
       <c r="S48" t="n">
-        <v>5.48</v>
+        <v>2.15</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>13.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="V48" t="n">
-        <v>6.5</v>
+        <v>2.2714</v>
       </c>
       <c r="W48" t="n">
-        <v>4.7</v>
+        <v>1.88</v>
       </c>
       <c r="X48" t="b">
         <v>1</v>
@@ -5212,13 +5208,13 @@
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NFE</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5227,16 +5223,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="E49" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -5247,51 +5243,55 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>-10.2</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +0.7pts)   Item 5.02 (officer_departure, -1)   Title: &gt;nfe-20260817</t>
+          <t>2026-08-21 424B3 (dilution_risk, -2.8pts) | 2026-08-21 8-K (material_event, +4.2pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement. | 2026-08-20 424B3 (dilution_risk, -2.4pts) | 2026-08-17 8-K (material_event, +0.6pts)   Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.28</v>
+        <v>4.83</v>
       </c>
       <c r="N49" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="O49" t="n">
-        <v>31.2</v>
+        <v>48.5</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2891</v>
+        <v>4.7</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.22</v>
+        <v>-2.69</v>
       </c>
       <c r="S49" t="n">
-        <v>0.2804</v>
+        <v>5.48</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.08</v>
+        <v>13.46</v>
       </c>
       <c r="V49" t="n">
-        <v>0.2999</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>0.275</v>
+        <v>4.7</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
@@ -5310,13 +5310,13 @@
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5325,71 +5325,71 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="D50" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E50" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="F50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Moved</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine)</t>
+          <t>2026-08-21 8-K (material_event, +0.7pts)   Item 5.02 (officer_departure, -1)   Title: &gt;nfe-20260817</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1.47</v>
+        <v>0.28</v>
       </c>
       <c r="N50" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O50" t="n">
-        <v>75.3</v>
+        <v>31.2</v>
       </c>
       <c r="P50" t="n">
-        <v>1.4891</v>
+        <v>0.287</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.34</v>
+        <v>3.46</v>
       </c>
       <c r="S50" t="n">
-        <v>1.4297</v>
+        <v>0.2804</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>-1.74</v>
+        <v>1.08</v>
       </c>
       <c r="V50" t="n">
-        <v>1.76</v>
+        <v>0.2999</v>
       </c>
       <c r="W50" t="n">
-        <v>1.08</v>
+        <v>0.275</v>
       </c>
       <c r="X50" t="b">
         <v>1</v>
@@ -5404,17 +5404,17 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SABS</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5423,75 +5423,71 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Moved</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>12.2</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-21 424B3 (dilution_risk, -2.8pts)</t>
+          <t>2026-08-20 8-K (material_event, +1.2pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>3.62</v>
+        <v>1.47</v>
       </c>
       <c r="N51" t="n">
-        <v>1.55</v>
+        <v>2.94</v>
       </c>
       <c r="O51" t="n">
-        <v>44.6</v>
+        <v>75.3</v>
       </c>
       <c r="P51" t="n">
-        <v>3.68</v>
+        <v>1.46</v>
       </c>
       <c r="Q51" t="n">
-        <v>34954</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.66</v>
+        <v>0.34</v>
       </c>
       <c r="S51" t="n">
-        <v>3.7</v>
+        <v>1.4297</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>2.21</v>
+        <v>-1.74</v>
       </c>
       <c r="V51" t="n">
-        <v>3.97</v>
+        <v>1.76</v>
       </c>
       <c r="W51" t="n">
-        <v>3.62</v>
+        <v>1.08</v>
       </c>
       <c r="X51" t="b">
         <v>1</v>
@@ -5502,21 +5498,21 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BMEA</t>
+          <t>SABS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5525,71 +5521,75 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v/>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>-4.2</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 424B3 (dilution_risk, -2.8pts)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1.59</v>
+        <v>3.62</v>
       </c>
       <c r="N52" t="n">
-        <v>10.62</v>
+        <v>1.55</v>
       </c>
       <c r="O52" t="n">
-        <v>77.5</v>
+        <v>44.6</v>
       </c>
       <c r="P52" t="n">
-        <v>1.68</v>
+        <v>3.68</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>34954</v>
       </c>
       <c r="R52" t="n">
-        <v>7.01</v>
+        <v>1.66</v>
       </c>
       <c r="S52" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>-4.46</v>
+        <v>2.21</v>
       </c>
       <c r="V52" t="n">
-        <v>1.68</v>
+        <v>3.97</v>
       </c>
       <c r="W52" t="n">
-        <v>1.33</v>
+        <v>3.62</v>
       </c>
       <c r="X52" t="b">
         <v>1</v>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ANY</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5629,65 +5629,65 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Late Entry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>15.7</v>
+        <v/>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-14 8-K (material_event, +0.0pts)   Items: 2.02, 7.01, 9.01 (routine)   Title: &gt;Sphere 3D Corp.: Form 8-K - Filed by newsfilecorp.com</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>2.43</v>
+        <v>1.59</v>
       </c>
       <c r="N53" t="n">
-        <v>2.19</v>
+        <v>10.62</v>
       </c>
       <c r="O53" t="n">
-        <v>56.7</v>
+        <v>77.5</v>
       </c>
       <c r="P53" t="n">
-        <v>2.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.41</v>
+        <v>3.82</v>
       </c>
       <c r="S53" t="n">
-        <v>2.69</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>11.16</v>
+        <v>-4.46</v>
       </c>
       <c r="V53" t="n">
-        <v>2.6884</v>
+        <v>1.68</v>
       </c>
       <c r="W53" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="X53" t="b">
         <v>1</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5764,13 +5764,13 @@
         <v>50.4</v>
       </c>
       <c r="P54" t="n">
-        <v>0.6353</v>
+        <v>0.654</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-15.32</v>
+        <v>-12.82</v>
       </c>
       <c r="S54" t="n">
         <v>0.29</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5862,13 +5862,13 @@
         <v>35.8</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6992</v>
+        <v>0.6837</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.82</v>
+        <v>-3.02</v>
       </c>
       <c r="S55" t="n">
         <v>0.669</v>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5960,13 +5960,13 @@
         <v>31.5</v>
       </c>
       <c r="P56" t="n">
-        <v>3.36</v>
+        <v>3.19</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.2</v>
+        <v>-3.92</v>
       </c>
       <c r="S56" t="n">
         <v>3.63</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6062,13 +6062,13 @@
         <v>45.6</v>
       </c>
       <c r="P57" t="n">
-        <v>0.365</v>
+        <v>0.3607</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.4</v>
+        <v>-2.57</v>
       </c>
       <c r="S57" t="n">
         <v>0.3051</v>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6160,13 +6160,13 @@
         <v>36.4</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6782</v>
+        <v>0.678</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="S58" t="n">
         <v>0.72</v>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6258,13 +6258,13 @@
         <v>20.6</v>
       </c>
       <c r="P59" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="S59" t="n">
         <v>2.39</v>
@@ -6279,7 +6279,7 @@
         <v>2.77</v>
       </c>
       <c r="W59" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="X59" t="b">
         <v>1</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6454,13 +6454,13 @@
         <v>67.59999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>144.44</v>
+        <v>122.33</v>
       </c>
       <c r="S61" t="n">
         <v>0.44</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6556,13 +6556,13 @@
         <v>32.7</v>
       </c>
       <c r="P62" t="n">
-        <v>0.355</v>
+        <v>0.349</v>
       </c>
       <c r="Q62" t="n">
         <v>868</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.87</v>
+        <v>-4.51</v>
       </c>
       <c r="S62" t="n">
         <v>0.348</v>
@@ -6577,7 +6577,7 @@
         <v>0.4621</v>
       </c>
       <c r="W62" t="n">
-        <v>0.3347</v>
+        <v>0.3251</v>
       </c>
       <c r="X62" t="b">
         <v>1</v>
@@ -6588,15 +6588,15 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB62" t="n">
-        <v/>
+        <v>-38.2</v>
       </c>
     </row>
   </sheetData>
@@ -6876,19 +6876,19 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="O2" t="n">
         <v>65522</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.27</v>
+        <v>-1.52</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="S2" t="n">
         <v>3.98</v>
@@ -6996,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0901</v>
+        <v>1.1385</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.57</v>
+        <v>3.84</v>
       </c>
       <c r="Q3" t="n">
         <v>1.33</v>
@@ -7116,13 +7116,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6353</v>
+        <v>0.654</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-15.32</v>
+        <v>-12.82</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -7236,13 +7236,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>144.44</v>
+        <v>122.33</v>
       </c>
       <c r="Q5" t="n">
         <v>6.26</v>
@@ -7356,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.42</v>
+        <v>5.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-10.08</v>
+        <v>-7.93</v>
       </c>
       <c r="Q6" t="n">
         <v>6.39</v>
@@ -7476,19 +7476,19 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="Q7" t="n">
         <v>2.77</v>
       </c>
       <c r="R7" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
         <v>2.39</v>
@@ -7716,13 +7716,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6.63</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>4.07</v>
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.365</v>
+        <v>0.3607</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4</v>
+        <v>-2.57</v>
       </c>
       <c r="Q10" t="n">
         <v>0.484</v>
@@ -7956,13 +7956,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5571</v>
+        <v>5.48</v>
       </c>
       <c r="O11" t="n">
         <v>1962</v>
       </c>
       <c r="P11" t="n">
-        <v>6.72</v>
+        <v>5.23</v>
       </c>
       <c r="Q11" t="n">
         <v>7.5</v>
@@ -8076,13 +8076,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7.01</v>
+        <v>3.82</v>
       </c>
       <c r="Q12" t="n">
         <v>1.68</v>
@@ -8196,13 +8196,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.3498</v>
       </c>
       <c r="O13" t="n">
         <v>2116</v>
       </c>
       <c r="P13" t="n">
-        <v>17.24</v>
+        <v>16.36</v>
       </c>
       <c r="Q13" t="n">
         <v>1.55</v>
@@ -8436,13 +8436,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.69</v>
+        <v>1.721</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
         <v>1.8</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1097</v>
+        <v>1.16</v>
       </c>
       <c r="O17" t="n">
         <v>7057</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.03</v>
+        <v>4.5</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.818</v>
+        <v>2.82</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.66</v>
+        <v>-2.59</v>
       </c>
       <c r="Q18" t="n">
         <v>2.92</v>
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1496</v>
+        <v>0.143</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.6</v>
+        <v>-11.67</v>
       </c>
       <c r="Q19" t="n">
         <v>0.166</v>
@@ -9036,16 +9036,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.99</v>
+        <v>1.9503</v>
       </c>
       <c r="O20" t="n">
         <v>69400</v>
       </c>
       <c r="P20" t="n">
-        <v>0.51</v>
+        <v>-1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.02</v>
+        <v>2.0397</v>
       </c>
       <c r="R20" t="n">
         <v>1.5202</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8085</v>
+        <v>5.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.19</v>
+        <v>0.17</v>
       </c>
       <c r="Q21" t="n">
         <v>5.88</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>13.21</v>
+        <v>13.53</v>
       </c>
       <c r="O22" t="n">
         <v>211582</v>
       </c>
       <c r="P22" t="n">
-        <v>6.62</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>14.6</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>7.28</v>
+        <v>7.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="Q23" t="n">
         <v>7.56</v>
@@ -9516,13 +9516,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.79</v>
+        <v>3.8139</v>
       </c>
       <c r="O24" t="n">
         <v>221</v>
       </c>
       <c r="P24" t="n">
-        <v>0.53</v>
+        <v>1.16</v>
       </c>
       <c r="Q24" t="n">
         <v>3.89</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.69</v>
+        <v>10.77</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Q25" t="n">
         <v>10.7899</v>
@@ -9756,13 +9756,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.0403</v>
+        <v>1.04</v>
       </c>
       <c r="O26" t="n">
         <v>7998</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q26" t="n">
         <v>1.12</v>
@@ -9876,19 +9876,19 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.355</v>
+        <v>0.349</v>
       </c>
       <c r="O27" t="n">
         <v>868</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.87</v>
+        <v>-4.51</v>
       </c>
       <c r="Q27" t="n">
         <v>0.4621</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3347</v>
+        <v>0.3251</v>
       </c>
       <c r="S27" t="n">
         <v>0.348</v>
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2891</v>
+        <v>0.287</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.22</v>
+        <v>3.46</v>
       </c>
       <c r="Q28" t="n">
         <v>0.2999</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4891</v>
+        <v>1.46</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.34</v>
+        <v>0.34</v>
       </c>
       <c r="Q29" t="n">
         <v>1.76</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6992</v>
+        <v>0.6837</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.82</v>
+        <v>-3.02</v>
       </c>
       <c r="Q31" t="n">
         <v>0.7333</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6361</v>
+        <v>0.633</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.01</v>
+        <v>2.51</v>
       </c>
       <c r="Q32" t="n">
         <v>0.6361</v>
@@ -10596,16 +10596,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.75</v>
+        <v>-1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.083</v>
+        <v>2.0899</v>
       </c>
       <c r="R33" t="n">
         <v>1.6303</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6902</v>
+        <v>0.6896</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
@@ -10836,13 +10836,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.41</v>
+        <v>-1.65</v>
       </c>
       <c r="Q35" t="n">
         <v>2.6884</v>
@@ -10956,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-1.15</v>
+        <v>0.57</v>
       </c>
       <c r="Q36" t="n">
         <v>1.7692</v>
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.36</v>
+        <v>3.19</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.2</v>
+        <v>-3.92</v>
       </c>
       <c r="Q37" t="n">
         <v>6.85</v>
@@ -11242,14 +11242,14 @@
         <v>47.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AC38" t="n">
         <v/>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -1.3x median — trading at discount | EV/EBITDA 47.5x vs 47.5x median — in-line | Analyst target $3.64</t>
+          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -1.3x median — trading at discount | EV/EBITDA 47.5x vs 47.5x median — in-line | Analyst target $3.65</t>
         </is>
       </c>
       <c r="AE38" t="n">
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O39" t="n">
         <v>10065</v>
       </c>
       <c r="P39" t="n">
-        <v>1.07</v>
+        <v>-0.36</v>
       </c>
       <c r="Q39" t="n">
         <v>1.4395</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.08</v>
+        <v>4.1073</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="Q43" t="n">
         <v>4.15</v>
@@ -12156,13 +12156,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.6782</v>
+        <v>0.678</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Q46" t="n">
         <v>0.719</v>
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.6994</v>
+        <v>0.6827</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.63</v>
+        <v>-1.77</v>
       </c>
       <c r="Q47" t="n">
         <v>1.1599</v>
@@ -12516,13 +12516,13 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.63</v>
+        <v>6.48</v>
       </c>
       <c r="O49" t="n">
         <v>3136</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.15</v>
+        <v>-2.41</v>
       </c>
       <c r="Q49" t="n">
         <v>6.63</v>
@@ -12636,13 +12636,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="O50" t="n">
         <v>29096</v>
       </c>
       <c r="P50" t="n">
-        <v>1.14</v>
+        <v>2.27</v>
       </c>
       <c r="Q50" t="n">
         <v>3.6</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.8186</v>
+        <v>6.81</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="Q51" t="n">
         <v>8.01</v>
@@ -12996,13 +12996,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.4696</v>
+        <v>1.4699</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="Q53" t="n">
         <v>1.49</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.86</v>
+        <v>2.7003</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.35</v>
+        <v>-5.25</v>
       </c>
       <c r="Q55" t="n">
         <v>2.95</v>
@@ -13476,16 +13476,16 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="O57" t="n">
         <v>5498</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.18</v>
+        <v>0.18</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="R57" t="n">
         <v>5.33</v>
@@ -13956,16 +13956,16 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>16.18</v>
+        <v>16.55</v>
       </c>
       <c r="O61" t="n">
         <v>12447</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.92</v>
+        <v>1.35</v>
       </c>
       <c r="Q61" t="n">
-        <v>16.36</v>
+        <v>16.55</v>
       </c>
       <c r="R61" t="n">
         <v>15.29</v>
@@ -14164,7 +14164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15392,30 +15392,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Item 2.01 (acquisition, +4) | Item 1.02 (termination_agreement, +1) | Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3) | Item 3.03 (rights_modification, -1) | Item 5.01 (control_change, +2) | Item 5.02 (officer_departure, -1)</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>&amp;#160;</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0001104659-26-100331</t>
+          <t>0001104659-26-100402</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>tm2623567d10_8k.htm</t>
+          <t>xslF345X06/tm2623813-15_4seq1.xml</t>
         </is>
       </c>
     </row>
@@ -15427,36 +15424,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0001104659-26-099714</t>
+          <t>0001104659-26-100400</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>tm2623567d2_8k.htm</t>
+          <t>xslF345X06/tm2623813-14_4seq1.xml</t>
         </is>
       </c>
     </row>
@@ -15468,36 +15466,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0001104659-26-099272</t>
+          <t>0001104659-26-100399</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>tm2623567d1_8k.htm</t>
+          <t>xslF345X06/tm2623813-13_4seq1.xml</t>
         </is>
       </c>
     </row>
@@ -15509,84 +15508,86 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Items: 5.07, 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0001104659-26-097203</t>
+          <t>0001104659-26-100398</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>tm2623076d1_8k.htm</t>
+          <t>xslF345X06/tm2623813-12_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Items: 8.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0001493152-26-038731</t>
+          <t>0001104659-26-100396</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>xslF345X06/tm2623813-11_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15596,7 +15597,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -15606,7 +15607,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>insider_buy</t>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -15616,34 +15617,39 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0001193125-26-354145</t>
+          <t>0001104659-26-100393</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>xslF345X06/tm2623813-10_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -15653,34 +15659,39 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0001527541-26-000320</t>
+          <t>0001104659-26-100392</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>areversestocksplitaugust20.htm</t>
+          <t>xslF345X06/tm2623813-9_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -15690,34 +15701,39 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0001527541-26-000318</t>
+          <t>0001104659-26-100390</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>areversestocksplitaugust20.htm</t>
+          <t>xslF345X06/tm2623813-8_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -15727,79 +15743,81 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0001527541-26-000316</t>
+          <t>0001104659-26-100389</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>areversestocksplitaugust20.htm</t>
+          <t>xslF345X06/tm2623813-7_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Item 3.03 (rights_modification, -1)</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>&gt;whlr-20260821</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0001527541-26-000314</t>
+          <t>0001104659-26-100388</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>whlr-20260821.htm</t>
+          <t>xslF345X06/tm2623813-6_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -15809,34 +15827,39 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0001527541-26-000310</t>
+          <t>0001104659-26-100385</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>astilwellagreementaugust20.htm</t>
+          <t>xslF345X06/tm2623813-5_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -15846,34 +15869,39 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0001527541-26-000307</t>
+          <t>0001104659-26-100382</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>astilwellagreementaugust20.htm</t>
+          <t>xslF345X06/tm2623813-4_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -15883,79 +15911,81 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0001527541-26-000305</t>
+          <t>0001104659-26-100379</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>astilwellagreementaugust20.htm</t>
+          <t>xslF345X06/tm2623813-3_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Item 1.01 (entry_agreement, +3)</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>&gt;whlr-20260817</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0001527541-26-000303</t>
+          <t>0001104659-26-100378</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>whlr-20260817.htm</t>
+          <t>xslF345X06/tm2623813-2_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -15965,93 +15995,111 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0001527541-26-000298</t>
+          <t>0001104659-26-100376</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>a8-kexchangeaugust132026.htm</t>
+          <t>xslF345X06/tm2623813-1_4seq1.xml</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v/>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Item 2.01 (acquisition, +4) | Item 1.02 (termination_agreement, +1) | Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3) | Item 3.03 (rights_modification, -1) | Item 5.01 (control_change, +2) | Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&amp;#160;</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0001527541-26-000296</t>
+          <t>0001104659-26-100331</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>a8-kexchangeaugust132026.htm</t>
+          <t>tm2623567d10_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v/>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0001527541-26-000294</t>
+          <t>0001104659-26-099714</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>a8-kexchangeaugust132026.htm</t>
+          <t>tm2623567d2_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -16061,7 +16109,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -16069,39 +16117,38 @@
           <t>material_event</t>
         </is>
       </c>
+      <c r="E46" t="n">
+        <v/>
+      </c>
       <c r="F46" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Item 3.02 (unregistered_equity, -3)</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&gt;whlr-20260813</t>
-        </is>
-      </c>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0001527541-26-000292</t>
+          <t>0001104659-26-099272</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>whlr-20260813.htm</t>
+          <t>tm2623567d1_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>RMAX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -16111,81 +16158,97 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v/>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Items: 5.07, 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0001527541-26-000287</t>
+          <t>0001104659-26-097203</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>aappointmentofofficerxcfo.htm</t>
+          <t>tm2623076d1_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>PUSA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Items: 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0001527541-26-000285</t>
+          <t>0001493152-26-038731</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>aappointmentofofficerxcfo.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WHLR</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -16195,12 +16258,12 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0001527541-26-000283</t>
+          <t>0001193125-26-354145</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>aappointmentofofficerxcfo.htm</t>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
@@ -16212,52 +16275,44 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>&gt;whlr-20260810</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0001527541-26-000281</t>
+          <t>0001527541-26-000320</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>whlr-20260810.htm</t>
+          <t>areversestocksplitaugust20.htm</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NFE</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -16267,78 +16322,66 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>&gt;nfe-20260817</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0001749723-26-000110</t>
+          <t>0001527541-26-000318</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>nfe-20260817.htm</t>
+          <t>areversestocksplitaugust20.htm</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0001493152-26-039377</t>
+          <t>0001527541-26-000316</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>areversestocksplitaugust20.htm</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ANY</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -16348,7 +16391,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -16357,33 +16400,33 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
+          <t>Item 3.03 (rights_modification, -1)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>&gt;Sphere 3D Corp.: Form 8-K - Filed by newsfilecorp.com</t>
+          <t>&gt;whlr-20260821</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0001062993-26-004391</t>
+          <t>0001527541-26-000314</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>form8k.htm</t>
+          <t>whlr-20260821.htm</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -16408,24 +16451,24 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0001493152-26-039581</t>
+          <t>0001527541-26-000310</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>form424b3.htm</t>
+          <t>astilwellagreementaugust20.htm</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16435,37 +16478,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Entry into a Material Definitive Agreement.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0001493152-26-039579</t>
+          <t>0001527541-26-000307</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>astilwellagreementaugust20.htm</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -16475,7 +16510,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -16490,19 +16525,19 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0001493152-26-039468</t>
+          <t>0001527541-26-000305</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>form424b3.htm</t>
+          <t>astilwellagreementaugust20.htm</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -16512,7 +16547,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -16521,49 +16556,48 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Item 1.01 (entry_agreement, +3)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&gt;whlr-20260817</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0001493152-26-038656</t>
+          <t>0001527541-26-000303</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>whlr-20260817.htm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -16573,39 +16607,34 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0002061848-26-000003</t>
+          <t>0001527541-26-000298</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787602480.xml</t>
+          <t>a8-kexchangeaugust132026.htm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -16615,39 +16644,34 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0001225208-26-007275</t>
+          <t>0001527541-26-000296</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>xslF345X06/doc4.xml</t>
+          <t>a8-kexchangeaugust132026.htm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>insider_other</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -16657,154 +16681,143 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0001225208-26-007188</t>
+          <t>0001527541-26-000294</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>xslF345X06/doc4.xml</t>
+          <t>a8-kexchangeaugust132026.htm</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&gt;whlr-20260813</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0001225208-26-007140</t>
+          <t>0001527541-26-000292</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>xslF345X06/doc4.xml</t>
+          <t>whlr-20260813.htm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FRMM</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v/>
+          <t>dilution_risk</t>
+        </is>
       </c>
       <c r="F62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0001213900-26-092591</t>
+          <t>0001527541-26-000287</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ea0303021-8k_forum.htm</t>
+          <t>aappointmentofofficerxcfo.htm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FRMM</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v/>
+          <t>dilution_risk</t>
+        </is>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Items: 5.07, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0001213900-26-091693</t>
+          <t>0001527541-26-000285</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ea0302772-8k_forum.htm</t>
+          <t>aappointmentofofficerxcfo.htm</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FRMM</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16814,12 +16827,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>insider_other</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -16829,24 +16837,24 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0001213900-26-090114</t>
+          <t>0001527541-26-000283</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>aappointmentofofficerxcfo.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FRMM</t>
+          <t>WHLR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16856,118 +16864,123 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>insider_other</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>&gt;whlr-20260810</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0001213900-26-090081</t>
+          <t>0001527541-26-000281</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>whlr-20260810.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TNYA</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>insider_sell</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&gt;nfe-20260817</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0001193125-26-354518</t>
+          <t>0001749723-26-000110</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>nfe-20260817.htm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TNYA</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>insider_sell</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0001193125-26-354517</t>
+          <t>0001493152-26-039377</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FLUX</t>
+          <t>ANY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -16977,7 +16990,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -16990,25 +17003,29 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Items: 5.07, 7.01, 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&gt;DarkHorse Technologies Inc.: Form 8-K - Filed by newsfilecorp.com</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0001493152-26-039473</t>
+          <t>0001062993-26-004571</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>form8k.htm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAPR</t>
+          <t>ANY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -17018,7 +17035,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -17031,34 +17048,34 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Items: 8.01, 9.01 (routine)</t>
+          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>&gt;CAPRICOR THERAPEUTICS, INC._August 24, 2026</t>
+          <t>&gt;Sphere 3D Corp.: Form 8-K - Filed by newsfilecorp.com</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0001104659-26-100071</t>
+          <t>0001062993-26-004391</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>capr-20260824x8k.htm</t>
+          <t>form8k.htm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17068,12 +17085,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>insider_sell</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -17083,24 +17095,24 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0001861460-26-000007</t>
+          <t>0001493152-26-039581</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787352406.xml</t>
+          <t>form424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SABS</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17110,29 +17122,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Entry into a Material Definitive Agreement.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0001193125-26-361180</t>
+          <t>0001493152-26-039579</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>sabs_424b3_s-3_prospp_2.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BRR</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -17142,7 +17162,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -17157,7 +17177,7 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0001493152-26-039145</t>
+          <t>0001493152-26-039468</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -17169,12 +17189,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VITL</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8-K/A</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17192,57 +17212,724 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Items: 5.03, 9.01 (routine)</t>
+          <t>Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0001193125-26-353479</t>
+          <t>0001493152-26-038656</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>vitl-20260811.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VITL</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Items: 5.03, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
+          <t>0002061848-26-000003</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>xslF345X06/wk-form4_1787602480.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DFDV</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0001225208-26-007275</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DFDV</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0001225208-26-007188</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DFDV</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0001225208-26-007140</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v/>
+      </c>
+      <c r="F78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0001213900-26-092591</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ea0303021-8k_forum.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v/>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Items: 5.07, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0001213900-26-091693</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ea0302772-8k_forum.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0001213900-26-090114</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FRMM</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>insider_other</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0001213900-26-090081</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TNYA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0001193125-26-354518</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TNYA</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0001193125-26-354517</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FLUX</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0001493152-26-039473</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>form8-k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CAPR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Items: 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>&gt;CAPRICOR THERAPEUTICS, INC._August 24, 2026</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0001104659-26-100071</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>capr-20260824x8k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ZIP</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0001861460-26-000007</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>xslF345X06/wk-form4_1787352406.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SABS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>424B3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0001193125-26-361180</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>sabs_424b3_s-3_prospp_2.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BRR</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>424B3</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0001493152-26-039145</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>form424b3.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>8-K/A</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Items: 5.03, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>0001193125-26-353479</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>vitl-20260811.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Items: 5.03, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
           <t>0001193125-26-353246</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>vitl-20260811.htm</t>
         </is>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -656,13 +656,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1385</v>
+        <v>1.1598</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.84</v>
+        <v>5.78</v>
       </c>
       <c r="S2" t="n">
         <v>1.04</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -786,15 +786,15 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="4">
@@ -852,13 +852,13 @@
         <v>71</v>
       </c>
       <c r="P4" t="n">
-        <v>5.55</v>
+        <v>5.28</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-7.93</v>
+        <v>-12.41</v>
       </c>
       <c r="S4" t="n">
         <v>8.41</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         <v>81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>2.8209</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.59</v>
+        <v>-2.56</v>
       </c>
       <c r="S6" t="n">
         <v>2.68</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.721</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.05</v>
+        <v>4.19</v>
       </c>
       <c r="S7" t="n">
         <v>1.86</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1342,13 +1342,13 @@
         <v>53.3</v>
       </c>
       <c r="P9" t="n">
-        <v>6.13</v>
+        <v>5.94</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>-1.82</v>
       </c>
       <c r="S9" t="n">
         <v>5.61</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1440,13 +1440,13 @@
         <v>64.90000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>10.77</v>
+        <v>10.71</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.75</v>
+        <v>0.19</v>
       </c>
       <c r="S10" t="n">
         <v>10.27</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>62</v>
       </c>
       <c r="P15" t="n">
-        <v>6.48</v>
+        <v>6.6346</v>
       </c>
       <c r="Q15" t="n">
         <v>3136</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.41</v>
+        <v>-0.08</v>
       </c>
       <c r="S15" t="n">
         <v>6.51</v>
@@ -1948,7 +1948,7 @@
         <v>-1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>6.63</v>
+        <v>6.6346</v>
       </c>
       <c r="W15" t="n">
         <v>6.44</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2224,13 +2224,13 @@
         <v>75</v>
       </c>
       <c r="P18" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.17</v>
+        <v>1.05</v>
       </c>
       <c r="S18" t="n">
         <v>5.52</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4699</v>
+        <v>1.46</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>-0</v>
       </c>
       <c r="S20" t="n">
         <v>1.5</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>58.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8139</v>
+        <v>3.85</v>
       </c>
       <c r="Q23" t="n">
         <v>221</v>
       </c>
       <c r="R23" t="n">
-        <v>1.16</v>
+        <v>2.12</v>
       </c>
       <c r="S23" t="n">
         <v>3.84</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3106,13 +3106,13 @@
         <v>56.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>2.3503</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.65</v>
+        <v>-2.88</v>
       </c>
       <c r="S27" t="n">
         <v>2.69</v>
@@ -3138,15 +3138,15 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="28">
@@ -3204,13 +3204,13 @@
         <v>76.8</v>
       </c>
       <c r="P28" t="n">
-        <v>4.1073</v>
+        <v>4.1</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>4.16</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3302,13 +3302,13 @@
         <v>66.8</v>
       </c>
       <c r="P29" t="n">
-        <v>5.48</v>
+        <v>5.65</v>
       </c>
       <c r="Q29" t="n">
         <v>1962</v>
       </c>
       <c r="R29" t="n">
-        <v>5.23</v>
+        <v>8.5</v>
       </c>
       <c r="S29" t="n">
         <v>4.3402</v>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3498,13 +3498,13 @@
         <v>47.2</v>
       </c>
       <c r="P31" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.32</v>
+        <v>5.19</v>
       </c>
       <c r="S31" t="n">
         <v>4.01</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3596,13 +3596,13 @@
         <v>52.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1.16</v>
+        <v>1.1001</v>
       </c>
       <c r="Q32" t="n">
         <v>7057</v>
       </c>
       <c r="R32" t="n">
-        <v>4.5</v>
+        <v>-0.89</v>
       </c>
       <c r="S32" t="n">
         <v>1.24</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3694,13 +3694,13 @@
         <v>33.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0.143</v>
+        <v>0.1497</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-11.67</v>
+        <v>-7.54</v>
       </c>
       <c r="S33" t="n">
         <v>0.1166</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3792,13 +3792,13 @@
         <v>66.90000000000001</v>
       </c>
       <c r="P34" t="n">
-        <v>1.9503</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
         <v>69400</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.5</v>
+        <v>-1.52</v>
       </c>
       <c r="S34" t="n">
         <v>1.68</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3988,13 +3988,13 @@
         <v>55</v>
       </c>
       <c r="P36" t="n">
-        <v>1.75</v>
+        <v>1.7697</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.57</v>
+        <v>1.71</v>
       </c>
       <c r="S36" t="n">
         <v>1.6284</v>
@@ -4006,7 +4006,7 @@
         <v>-6.41</v>
       </c>
       <c r="V36" t="n">
-        <v>1.7692</v>
+        <v>1.7845</v>
       </c>
       <c r="W36" t="n">
         <v>1.11</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4086,13 +4086,13 @@
         <v>52.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9996</v>
+        <v>1.01</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.31</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
         <v>0.9301</v>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4184,13 +4184,13 @@
         <v>63.4</v>
       </c>
       <c r="P38" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="Q38" t="n">
         <v>29096</v>
       </c>
       <c r="R38" t="n">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="S38" t="n">
         <v>3.25</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>38.4</v>
       </c>
       <c r="P39" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.37</v>
+        <v>0.52</v>
       </c>
       <c r="S39" t="n">
         <v>6.81</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>41.8</v>
       </c>
       <c r="P40" t="n">
-        <v>1.3498</v>
+        <v>1.3669</v>
       </c>
       <c r="Q40" t="n">
         <v>2116</v>
       </c>
       <c r="R40" t="n">
-        <v>16.36</v>
+        <v>17.84</v>
       </c>
       <c r="S40" t="n">
         <v>1.24</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
         <v>67.40000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>0.633</v>
+        <v>0.6319</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="S41" t="n">
         <v>0.631</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>40.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.6896</v>
+        <v>0.68</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S43" t="n">
         <v>0.718</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4772,13 +4772,13 @@
         <v>45.4</v>
       </c>
       <c r="P44" t="n">
-        <v>1.4</v>
+        <v>1.401</v>
       </c>
       <c r="Q44" t="n">
         <v>10065</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.36</v>
+        <v>-0.28</v>
       </c>
       <c r="S44" t="n">
         <v>1.33</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5066,13 +5066,13 @@
         <v>81.8</v>
       </c>
       <c r="P47" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="Q47" t="n">
         <v>5498</v>
       </c>
       <c r="R47" t="n">
-        <v>0.18</v>
+        <v>0.7</v>
       </c>
       <c r="S47" t="n">
         <v>5.7</v>
@@ -5084,7 +5084,7 @@
         <v>0.18</v>
       </c>
       <c r="V47" t="n">
-        <v>5.7</v>
+        <v>5.74</v>
       </c>
       <c r="W47" t="n">
         <v>5.33</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5270,13 +5270,13 @@
         <v>48.5</v>
       </c>
       <c r="P49" t="n">
-        <v>4.7</v>
+        <v>4.86</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>-2.69</v>
+        <v>0.62</v>
       </c>
       <c r="S49" t="n">
         <v>5.48</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5368,13 +5368,13 @@
         <v>31.2</v>
       </c>
       <c r="P50" t="n">
-        <v>0.287</v>
+        <v>0.2875</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="S50" t="n">
         <v>0.2804</v>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5466,13 +5466,13 @@
         <v>75.3</v>
       </c>
       <c r="P51" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.34</v>
+        <v>1.03</v>
       </c>
       <c r="S51" t="n">
         <v>1.4297</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5666,13 +5666,13 @@
         <v>77.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.63</v>
+        <v>1.6208</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.82</v>
+        <v>3.24</v>
       </c>
       <c r="S53" t="n">
         <v>1.5</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5764,13 +5764,13 @@
         <v>50.4</v>
       </c>
       <c r="P54" t="n">
-        <v>0.654</v>
+        <v>0.6194</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-12.82</v>
+        <v>-17.44</v>
       </c>
       <c r="S54" t="n">
         <v>0.29</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5862,13 +5862,13 @@
         <v>35.8</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6837</v>
+        <v>0.6898</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-3.02</v>
+        <v>-2.16</v>
       </c>
       <c r="S55" t="n">
         <v>0.669</v>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5960,13 +5960,13 @@
         <v>31.5</v>
       </c>
       <c r="P56" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-3.92</v>
+        <v>-5.12</v>
       </c>
       <c r="S56" t="n">
         <v>3.63</v>
@@ -5981,7 +5981,7 @@
         <v>6.85</v>
       </c>
       <c r="W56" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="X56" t="b">
         <v>1</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6062,13 +6062,13 @@
         <v>45.6</v>
       </c>
       <c r="P57" t="n">
-        <v>0.3607</v>
+        <v>0.3556</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-2.57</v>
+        <v>-3.94</v>
       </c>
       <c r="S57" t="n">
         <v>0.3051</v>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6258,13 +6258,13 @@
         <v>20.6</v>
       </c>
       <c r="P59" t="n">
-        <v>1.91</v>
+        <v>1.8198</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-4.5</v>
+        <v>-9.01</v>
       </c>
       <c r="S59" t="n">
         <v>2.39</v>
@@ -6279,7 +6279,7 @@
         <v>2.77</v>
       </c>
       <c r="W59" t="n">
-        <v>1.85</v>
+        <v>1.7597</v>
       </c>
       <c r="X59" t="b">
         <v>1</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6454,13 +6454,13 @@
         <v>67.59999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>122.33</v>
+        <v>156.08</v>
       </c>
       <c r="S61" t="n">
         <v>0.44</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6556,13 +6556,13 @@
         <v>32.7</v>
       </c>
       <c r="P62" t="n">
-        <v>0.349</v>
+        <v>0.3206</v>
       </c>
       <c r="Q62" t="n">
         <v>868</v>
       </c>
       <c r="R62" t="n">
-        <v>-4.51</v>
+        <v>-12.28</v>
       </c>
       <c r="S62" t="n">
         <v>0.348</v>
@@ -6577,7 +6577,7 @@
         <v>0.4621</v>
       </c>
       <c r="W62" t="n">
-        <v>0.3251</v>
+        <v>0.3205</v>
       </c>
       <c r="X62" t="b">
         <v>1</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6996,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1385</v>
+        <v>1.1598</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.84</v>
+        <v>5.78</v>
       </c>
       <c r="Q3" t="n">
         <v>1.33</v>
@@ -7116,13 +7116,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.654</v>
+        <v>0.6194</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-12.82</v>
+        <v>-17.44</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -7236,13 +7236,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>122.33</v>
+        <v>156.08</v>
       </c>
       <c r="Q5" t="n">
         <v>6.26</v>
@@ -7356,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.55</v>
+        <v>5.28</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.93</v>
+        <v>-12.41</v>
       </c>
       <c r="Q6" t="n">
         <v>6.39</v>
@@ -7476,19 +7476,19 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>1.8198</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.5</v>
+        <v>-9.01</v>
       </c>
       <c r="Q7" t="n">
         <v>2.77</v>
       </c>
       <c r="R7" t="n">
-        <v>1.85</v>
+        <v>1.7597</v>
       </c>
       <c r="S7" t="n">
         <v>2.39</v>
@@ -7716,13 +7716,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>5.19</v>
       </c>
       <c r="Q9" t="n">
         <v>4.07</v>
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3607</v>
+        <v>0.3556</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.57</v>
+        <v>-3.94</v>
       </c>
       <c r="Q10" t="n">
         <v>0.484</v>
@@ -7956,13 +7956,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.48</v>
+        <v>5.65</v>
       </c>
       <c r="O11" t="n">
         <v>1962</v>
       </c>
       <c r="P11" t="n">
-        <v>5.23</v>
+        <v>8.5</v>
       </c>
       <c r="Q11" t="n">
         <v>7.5</v>
@@ -8076,13 +8076,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>1.6208</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.82</v>
+        <v>3.24</v>
       </c>
       <c r="Q12" t="n">
         <v>1.68</v>
@@ -8196,13 +8196,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3498</v>
+        <v>1.3669</v>
       </c>
       <c r="O13" t="n">
         <v>2116</v>
       </c>
       <c r="P13" t="n">
-        <v>16.36</v>
+        <v>17.84</v>
       </c>
       <c r="Q13" t="n">
         <v>1.55</v>
@@ -8436,13 +8436,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.721</v>
+        <v>1.74</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>4.19</v>
       </c>
       <c r="Q15" t="n">
         <v>1.8</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.16</v>
+        <v>1.1001</v>
       </c>
       <c r="O17" t="n">
         <v>7057</v>
       </c>
       <c r="P17" t="n">
-        <v>4.5</v>
+        <v>-0.89</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.82</v>
+        <v>2.8209</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.59</v>
+        <v>-2.56</v>
       </c>
       <c r="Q18" t="n">
         <v>2.92</v>
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.143</v>
+        <v>0.1497</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-11.67</v>
+        <v>-7.54</v>
       </c>
       <c r="Q19" t="n">
         <v>0.166</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9503</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
         <v>69400</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5</v>
+        <v>-1.52</v>
       </c>
       <c r="Q20" t="n">
         <v>2.0397</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.17</v>
+        <v>1.05</v>
       </c>
       <c r="Q21" t="n">
         <v>5.88</v>
@@ -9516,13 +9516,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8139</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>221</v>
       </c>
       <c r="P24" t="n">
-        <v>1.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
         <v>3.89</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.77</v>
+        <v>10.71</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.75</v>
+        <v>0.19</v>
       </c>
       <c r="Q25" t="n">
         <v>10.7899</v>
@@ -9876,19 +9876,19 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.349</v>
+        <v>0.3206</v>
       </c>
       <c r="O27" t="n">
         <v>868</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.51</v>
+        <v>-12.28</v>
       </c>
       <c r="Q27" t="n">
         <v>0.4621</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3251</v>
+        <v>0.3205</v>
       </c>
       <c r="S27" t="n">
         <v>0.348</v>
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.287</v>
+        <v>0.2875</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="Q28" t="n">
         <v>0.2999</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.34</v>
+        <v>1.03</v>
       </c>
       <c r="Q29" t="n">
         <v>1.76</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6837</v>
+        <v>0.6898</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-3.02</v>
+        <v>-2.16</v>
       </c>
       <c r="Q31" t="n">
         <v>0.7333</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.633</v>
+        <v>0.6319</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="Q32" t="n">
         <v>0.6361</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6896</v>
+        <v>0.68</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
@@ -10836,13 +10836,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.38</v>
+        <v>2.3503</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-1.65</v>
+        <v>-2.88</v>
       </c>
       <c r="Q35" t="n">
         <v>2.6884</v>
@@ -10956,16 +10956,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.75</v>
+        <v>1.7697</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.57</v>
+        <v>1.71</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.7692</v>
+        <v>1.7845</v>
       </c>
       <c r="R36" t="n">
         <v>1.11</v>
@@ -11076,19 +11076,19 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-3.92</v>
+        <v>-5.12</v>
       </c>
       <c r="Q37" t="n">
         <v>6.85</v>
       </c>
       <c r="R37" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="S37" t="n">
         <v>3.63</v>
@@ -11242,14 +11242,14 @@
         <v>47.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="AC38" t="n">
         <v/>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -1.3x median — trading at discount | EV/EBITDA 47.5x vs 47.5x median — in-line | Analyst target $3.65</t>
+          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -1.3x median — trading at discount | EV/EBITDA 47.5x vs 47.5x median — in-line | Analyst target $3.64</t>
         </is>
       </c>
       <c r="AE38" t="n">
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.4</v>
+        <v>1.401</v>
       </c>
       <c r="O39" t="n">
         <v>10065</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.36</v>
+        <v>-0.28</v>
       </c>
       <c r="Q39" t="n">
         <v>1.4395</v>
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.7</v>
+        <v>4.86</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-2.69</v>
+        <v>0.62</v>
       </c>
       <c r="Q40" t="n">
         <v>6.5</v>
@@ -11556,13 +11556,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0.9996</v>
+        <v>1.01</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.31</v>
+        <v>1.35</v>
       </c>
       <c r="Q41" t="n">
         <v>1.02</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1073</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>4.15</v>
@@ -11916,13 +11916,13 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>6.13</v>
+        <v>5.94</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>-1.82</v>
       </c>
       <c r="Q44" t="n">
         <v>6.13</v>
@@ -12516,16 +12516,16 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.48</v>
+        <v>6.6346</v>
       </c>
       <c r="O49" t="n">
         <v>3136</v>
       </c>
       <c r="P49" t="n">
-        <v>-2.41</v>
+        <v>-0.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.63</v>
+        <v>6.6346</v>
       </c>
       <c r="R49" t="n">
         <v>6.44</v>
@@ -12636,13 +12636,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="O50" t="n">
         <v>29096</v>
       </c>
       <c r="P50" t="n">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="Q50" t="n">
         <v>3.6</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.37</v>
+        <v>0.52</v>
       </c>
       <c r="Q51" t="n">
         <v>8.01</v>
@@ -12996,13 +12996,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.4699</v>
+        <v>1.46</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.68</v>
+        <v>-0</v>
       </c>
       <c r="Q53" t="n">
         <v>1.49</v>
@@ -13476,16 +13476,16 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="O57" t="n">
         <v>5498</v>
       </c>
       <c r="P57" t="n">
-        <v>0.18</v>
+        <v>0.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.7</v>
+        <v>5.74</v>
       </c>
       <c r="R57" t="n">
         <v>5.33</v>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -656,13 +656,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1598</v>
+        <v>1.1401</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.78</v>
+        <v>3.99</v>
       </c>
       <c r="S2" t="n">
         <v>1.04</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>55.6</v>
       </c>
       <c r="P3" t="n">
-        <v>13.53</v>
+        <v>13.39</v>
       </c>
       <c r="Q3" t="n">
         <v>211582</v>
       </c>
       <c r="R3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="S3" t="n">
         <v>13.61</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>71</v>
       </c>
       <c r="P4" t="n">
-        <v>5.28</v>
+        <v>5.39</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-12.41</v>
+        <v>-10.58</v>
       </c>
       <c r="S4" t="n">
         <v>8.41</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         <v>81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8209</v>
+        <v>2.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.56</v>
+        <v>-2.55</v>
       </c>
       <c r="S6" t="n">
         <v>2.68</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.7103</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.19</v>
+        <v>2.41</v>
       </c>
       <c r="S7" t="n">
         <v>1.86</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1440,13 +1440,13 @@
         <v>64.90000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>10.71</v>
+        <v>10.9</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.19</v>
+        <v>1.96</v>
       </c>
       <c r="S10" t="n">
         <v>10.27</v>
@@ -1458,7 +1458,7 @@
         <v>-3.93</v>
       </c>
       <c r="V10" t="n">
-        <v>10.7899</v>
+        <v>10.9</v>
       </c>
       <c r="W10" t="n">
         <v>9.84</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         <v>57.4</v>
       </c>
       <c r="P17" t="n">
-        <v>16.55</v>
+        <v>16.42</v>
       </c>
       <c r="Q17" t="n">
         <v>12447</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0.55</v>
       </c>
       <c r="S17" t="n">
         <v>16.65</v>
@@ -2144,7 +2144,7 @@
         <v>1.96</v>
       </c>
       <c r="V17" t="n">
-        <v>16.55</v>
+        <v>16.74</v>
       </c>
       <c r="W17" t="n">
         <v>15.29</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2224,13 +2224,13 @@
         <v>75</v>
       </c>
       <c r="P18" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
         <v>5.52</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>72.09999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.46</v>
+        <v>1.4692</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0</v>
+        <v>0.63</v>
       </c>
       <c r="S20" t="n">
         <v>1.5</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         <v>53.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6827</v>
+        <v>0.7</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.77</v>
+        <v>0.72</v>
       </c>
       <c r="S21" t="n">
         <v>0.58</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2616,13 +2616,13 @@
         <v>50.9</v>
       </c>
       <c r="P22" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="Q22" t="n">
         <v>93688</v>
       </c>
       <c r="R22" t="n">
-        <v>0.22</v>
+        <v>0.66</v>
       </c>
       <c r="S22" t="n">
         <v>4.23</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>58.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.85</v>
+        <v>3.8037</v>
       </c>
       <c r="Q23" t="n">
         <v>221</v>
       </c>
       <c r="R23" t="n">
-        <v>2.12</v>
+        <v>0.89</v>
       </c>
       <c r="S23" t="n">
         <v>3.84</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3302,13 +3302,13 @@
         <v>66.8</v>
       </c>
       <c r="P29" t="n">
-        <v>5.65</v>
+        <v>5.97</v>
       </c>
       <c r="Q29" t="n">
         <v>1962</v>
       </c>
       <c r="R29" t="n">
-        <v>8.5</v>
+        <v>14.64</v>
       </c>
       <c r="S29" t="n">
         <v>4.3402</v>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3498,13 +3498,13 @@
         <v>47.2</v>
       </c>
       <c r="P31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>5.19</v>
+        <v>6.63</v>
       </c>
       <c r="S31" t="n">
         <v>4.01</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3596,13 +3596,13 @@
         <v>52.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1.1001</v>
+        <v>1.0902</v>
       </c>
       <c r="Q32" t="n">
         <v>7057</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.89</v>
+        <v>-1.78</v>
       </c>
       <c r="S32" t="n">
         <v>1.24</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3694,13 +3694,13 @@
         <v>33.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1497</v>
+        <v>0.1423</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-7.54</v>
+        <v>-12.11</v>
       </c>
       <c r="S33" t="n">
         <v>0.1166</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3792,13 +3792,13 @@
         <v>66.90000000000001</v>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>1.9838</v>
       </c>
       <c r="Q34" t="n">
         <v>69400</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.52</v>
+        <v>0.19</v>
       </c>
       <c r="S34" t="n">
         <v>1.68</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         <v>63.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.04</v>
+        <v>1.0469</v>
       </c>
       <c r="Q35" t="n">
         <v>7998</v>
       </c>
       <c r="R35" t="n">
-        <v>0.97</v>
+        <v>1.64</v>
       </c>
       <c r="S35" t="n">
         <v>1.09</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3988,13 +3988,13 @@
         <v>55</v>
       </c>
       <c r="P36" t="n">
-        <v>1.7697</v>
+        <v>1.75</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.71</v>
+        <v>0.57</v>
       </c>
       <c r="S36" t="n">
         <v>1.6284</v>
@@ -4006,7 +4006,7 @@
         <v>-6.41</v>
       </c>
       <c r="V36" t="n">
-        <v>1.7845</v>
+        <v>1.8</v>
       </c>
       <c r="W36" t="n">
         <v>1.11</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>38.4</v>
       </c>
       <c r="P39" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="S39" t="n">
         <v>6.81</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>41.8</v>
       </c>
       <c r="P40" t="n">
-        <v>1.3669</v>
+        <v>1.3607</v>
       </c>
       <c r="Q40" t="n">
         <v>2116</v>
       </c>
       <c r="R40" t="n">
-        <v>17.84</v>
+        <v>17.3</v>
       </c>
       <c r="S40" t="n">
         <v>1.24</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
         <v>67.40000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>0.6319</v>
+        <v>0.6311</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
         <v>0.631</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4576,13 +4576,13 @@
         <v>68.2</v>
       </c>
       <c r="P42" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.25</v>
+        <v>0.25</v>
       </c>
       <c r="S42" t="n">
         <v>1.93</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>40.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.68</v>
+        <v>0.6711</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.75</v>
       </c>
       <c r="S43" t="n">
         <v>0.718</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5066,13 +5066,13 @@
         <v>81.8</v>
       </c>
       <c r="P47" t="n">
-        <v>5.73</v>
+        <v>5.6984</v>
       </c>
       <c r="Q47" t="n">
         <v>5498</v>
       </c>
       <c r="R47" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="S47" t="n">
         <v>5.7</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5666,13 +5666,13 @@
         <v>77.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.6208</v>
+        <v>1.62</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="S53" t="n">
         <v>1.5</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5764,13 +5764,13 @@
         <v>50.4</v>
       </c>
       <c r="P54" t="n">
-        <v>0.6194</v>
+        <v>0.6288</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-17.44</v>
+        <v>-16.18</v>
       </c>
       <c r="S54" t="n">
         <v>0.29</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5862,13 +5862,13 @@
         <v>35.8</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6898</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-2.16</v>
+        <v>-4.55</v>
       </c>
       <c r="S55" t="n">
         <v>0.669</v>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5960,13 +5960,13 @@
         <v>31.5</v>
       </c>
       <c r="P56" t="n">
-        <v>3.15</v>
+        <v>3.2169</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-5.12</v>
+        <v>-3.11</v>
       </c>
       <c r="S56" t="n">
         <v>3.63</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6062,13 +6062,13 @@
         <v>45.6</v>
       </c>
       <c r="P57" t="n">
-        <v>0.3556</v>
+        <v>0.3568</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.94</v>
+        <v>-3.62</v>
       </c>
       <c r="S57" t="n">
         <v>0.3051</v>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6160,13 +6160,13 @@
         <v>36.4</v>
       </c>
       <c r="P58" t="n">
-        <v>0.678</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
         <v>0.72</v>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6258,13 +6258,13 @@
         <v>20.6</v>
       </c>
       <c r="P59" t="n">
-        <v>1.8198</v>
+        <v>1.8849</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-9.01</v>
+        <v>-5.75</v>
       </c>
       <c r="S59" t="n">
         <v>2.39</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6454,13 +6454,13 @@
         <v>67.59999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>4.4</v>
+        <v>3.9102</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>156.08</v>
+        <v>127.58</v>
       </c>
       <c r="S61" t="n">
         <v>0.44</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6556,13 +6556,13 @@
         <v>32.7</v>
       </c>
       <c r="P62" t="n">
-        <v>0.3206</v>
+        <v>0.3344</v>
       </c>
       <c r="Q62" t="n">
         <v>868</v>
       </c>
       <c r="R62" t="n">
-        <v>-12.28</v>
+        <v>-8.51</v>
       </c>
       <c r="S62" t="n">
         <v>0.348</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6996,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1598</v>
+        <v>1.1401</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5.78</v>
+        <v>3.99</v>
       </c>
       <c r="Q3" t="n">
         <v>1.33</v>
@@ -7116,13 +7116,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6194</v>
+        <v>0.6288</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-17.44</v>
+        <v>-16.18</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -7236,13 +7236,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>3.9102</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>156.08</v>
+        <v>127.58</v>
       </c>
       <c r="Q5" t="n">
         <v>6.26</v>
@@ -7356,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.28</v>
+        <v>5.39</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-12.41</v>
+        <v>-10.58</v>
       </c>
       <c r="Q6" t="n">
         <v>6.39</v>
@@ -7476,13 +7476,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.8198</v>
+        <v>1.8849</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-9.01</v>
+        <v>-5.75</v>
       </c>
       <c r="Q7" t="n">
         <v>2.77</v>
@@ -7716,13 +7716,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5.19</v>
+        <v>6.63</v>
       </c>
       <c r="Q9" t="n">
         <v>4.07</v>
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3556</v>
+        <v>0.3568</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.94</v>
+        <v>-3.62</v>
       </c>
       <c r="Q10" t="n">
         <v>0.484</v>
@@ -7956,13 +7956,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.65</v>
+        <v>5.97</v>
       </c>
       <c r="O11" t="n">
         <v>1962</v>
       </c>
       <c r="P11" t="n">
-        <v>8.5</v>
+        <v>14.64</v>
       </c>
       <c r="Q11" t="n">
         <v>7.5</v>
@@ -8076,13 +8076,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.6208</v>
+        <v>1.62</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="Q12" t="n">
         <v>1.68</v>
@@ -8196,13 +8196,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3669</v>
+        <v>1.3607</v>
       </c>
       <c r="O13" t="n">
         <v>2116</v>
       </c>
       <c r="P13" t="n">
-        <v>17.84</v>
+        <v>17.3</v>
       </c>
       <c r="Q13" t="n">
         <v>1.55</v>
@@ -8436,13 +8436,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.74</v>
+        <v>1.7103</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.19</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
         <v>1.8</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1001</v>
+        <v>1.0902</v>
       </c>
       <c r="O17" t="n">
         <v>7057</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.89</v>
+        <v>-1.78</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8209</v>
+        <v>2.8211</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.56</v>
+        <v>-2.55</v>
       </c>
       <c r="Q18" t="n">
         <v>2.92</v>
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1497</v>
+        <v>0.1423</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.54</v>
+        <v>-12.11</v>
       </c>
       <c r="Q19" t="n">
         <v>0.166</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>1.9838</v>
       </c>
       <c r="O20" t="n">
         <v>69400</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.52</v>
+        <v>0.19</v>
       </c>
       <c r="Q20" t="n">
         <v>2.0397</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="Q21" t="n">
         <v>5.88</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>13.53</v>
+        <v>13.39</v>
       </c>
       <c r="O22" t="n">
         <v>211582</v>
       </c>
       <c r="P22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="Q22" t="n">
         <v>14.6</v>
@@ -9516,13 +9516,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.8037</v>
       </c>
       <c r="O24" t="n">
         <v>221</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0.89</v>
       </c>
       <c r="Q24" t="n">
         <v>3.89</v>
@@ -9636,16 +9636,16 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.71</v>
+        <v>10.9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.19</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.7899</v>
+        <v>10.9</v>
       </c>
       <c r="R25" t="n">
         <v>9.84</v>
@@ -9756,13 +9756,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.04</v>
+        <v>1.0469</v>
       </c>
       <c r="O26" t="n">
         <v>7998</v>
       </c>
       <c r="P26" t="n">
-        <v>0.97</v>
+        <v>1.64</v>
       </c>
       <c r="Q26" t="n">
         <v>1.12</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3206</v>
+        <v>0.3344</v>
       </c>
       <c r="O27" t="n">
         <v>868</v>
       </c>
       <c r="P27" t="n">
-        <v>-12.28</v>
+        <v>-8.51</v>
       </c>
       <c r="Q27" t="n">
         <v>0.4621</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6898</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-2.16</v>
+        <v>-4.55</v>
       </c>
       <c r="Q31" t="n">
         <v>0.7333</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6319</v>
+        <v>0.6311</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
         <v>0.6361</v>
@@ -10596,13 +10596,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-1.25</v>
+        <v>0.25</v>
       </c>
       <c r="Q33" t="n">
         <v>2.0899</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.68</v>
+        <v>0.6711</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.75</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
@@ -10956,16 +10956,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.7697</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.71</v>
+        <v>0.57</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.7845</v>
+        <v>1.8</v>
       </c>
       <c r="R36" t="n">
         <v>1.11</v>
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>3.2169</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-5.12</v>
+        <v>-3.11</v>
       </c>
       <c r="Q37" t="n">
         <v>6.85</v>
@@ -11242,14 +11242,14 @@
         <v>47.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AC38" t="n">
         <v/>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -1.3x median — trading at discount | EV/EBITDA 47.5x vs 47.5x median — in-line | Analyst target $3.64</t>
+          <t>P/S 0.1x vs 0.8x median — trading at discount | P/B 0.7x vs -1.3x median — trading at discount | EV/EBITDA 47.5x vs 47.5x median — in-line | Analyst target $3.65</t>
         </is>
       </c>
       <c r="AE38" t="n">
@@ -12156,13 +12156,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.678</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>0.719</v>
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.6827</v>
+        <v>0.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-1.77</v>
+        <v>0.72</v>
       </c>
       <c r="Q47" t="n">
         <v>1.1599</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="Q51" t="n">
         <v>8.01</v>
@@ -12996,13 +12996,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.46</v>
+        <v>1.4692</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0</v>
+        <v>0.63</v>
       </c>
       <c r="Q53" t="n">
         <v>1.49</v>
@@ -13356,13 +13356,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="O56" t="n">
         <v>93688</v>
       </c>
       <c r="P56" t="n">
-        <v>0.22</v>
+        <v>0.66</v>
       </c>
       <c r="Q56" t="n">
         <v>5.28</v>
@@ -13476,13 +13476,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.73</v>
+        <v>5.6984</v>
       </c>
       <c r="O57" t="n">
         <v>5498</v>
       </c>
       <c r="P57" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="Q57" t="n">
         <v>5.74</v>
@@ -13956,16 +13956,16 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>16.55</v>
+        <v>16.42</v>
       </c>
       <c r="O61" t="n">
         <v>12447</v>
       </c>
       <c r="P61" t="n">
-        <v>1.35</v>
+        <v>0.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>16.55</v>
+        <v>16.74</v>
       </c>
       <c r="R61" t="n">
         <v>15.29</v>
@@ -14002,14 +14002,14 @@
         <v>17.16</v>
       </c>
       <c r="AB61" t="n">
-        <v>42.75</v>
+        <v>41</v>
       </c>
       <c r="AC61" t="n">
         <v>17.76</v>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>P/S 9.1x vs 6.3x median — trading at premium | P/B 3.7x vs 2.3x median — trading at premium | EV/EBITDA 17.2x vs -1.1x median — trading at discount | Analyst target $42.75 | Graham # $17.76</t>
+          <t>P/S 9.1x vs 6.3x median — trading at premium | P/B 3.7x vs 2.3x median — trading at premium | EV/EBITDA 17.2x vs -1.1x median — trading at discount | Analyst target $41.00 | Graham # $17.76</t>
         </is>
       </c>
       <c r="AE61" t="n">

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -656,13 +656,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1401</v>
+        <v>1.14</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="S2" t="n">
         <v>1.04</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>71</v>
       </c>
       <c r="P4" t="n">
-        <v>5.39</v>
+        <v>5.1015</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-10.58</v>
+        <v>-15.37</v>
       </c>
       <c r="S4" t="n">
         <v>8.41</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -950,13 +950,13 @@
         <v>64.59999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>10.8</v>
+        <v>10.805</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="S5" t="n">
         <v>10.79</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7103</v>
+        <v>1.6501</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.41</v>
+        <v>-1.19</v>
       </c>
       <c r="S7" t="n">
         <v>1.86</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2224,13 +2224,13 @@
         <v>75</v>
       </c>
       <c r="P18" t="n">
-        <v>5.81</v>
+        <v>5.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="S18" t="n">
         <v>5.52</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         <v>53.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7</v>
+        <v>0.6975</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="S21" t="n">
         <v>0.58</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2616,13 +2616,13 @@
         <v>50.9</v>
       </c>
       <c r="P22" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="Q22" t="n">
         <v>93688</v>
       </c>
       <c r="R22" t="n">
-        <v>0.66</v>
+        <v>-0.66</v>
       </c>
       <c r="S22" t="n">
         <v>4.23</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>58.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8037</v>
+        <v>3.81</v>
       </c>
       <c r="Q23" t="n">
         <v>221</v>
       </c>
       <c r="R23" t="n">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="S23" t="n">
         <v>3.84</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>68.09999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>2.7003</v>
+        <v>2.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-5.25</v>
+        <v>-5.26</v>
       </c>
       <c r="S26" t="n">
         <v>2.91</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3106,13 +3106,13 @@
         <v>56.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3503</v>
+        <v>2.3598</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.88</v>
+        <v>-2.49</v>
       </c>
       <c r="S27" t="n">
         <v>2.69</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3204,13 +3204,13 @@
         <v>76.8</v>
       </c>
       <c r="P28" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="S28" t="n">
         <v>4.16</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3302,13 +3302,13 @@
         <v>66.8</v>
       </c>
       <c r="P29" t="n">
-        <v>5.97</v>
+        <v>5.8892</v>
       </c>
       <c r="Q29" t="n">
         <v>1962</v>
       </c>
       <c r="R29" t="n">
-        <v>14.64</v>
+        <v>13.09</v>
       </c>
       <c r="S29" t="n">
         <v>4.3402</v>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3498,22 +3498,22 @@
         <v>47.2</v>
       </c>
       <c r="P31" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>6.63</v>
+        <v>5.48</v>
       </c>
       <c r="S31" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>15.56</v>
+        <v>14.7</v>
       </c>
       <c r="V31" t="n">
         <v>4.07</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3596,13 +3596,13 @@
         <v>52.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1.0902</v>
+        <v>1.0808</v>
       </c>
       <c r="Q32" t="n">
         <v>7057</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.78</v>
+        <v>-2.63</v>
       </c>
       <c r="S32" t="n">
         <v>1.24</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3694,13 +3694,13 @@
         <v>33.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1423</v>
+        <v>0.1451</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-12.11</v>
+        <v>-10.38</v>
       </c>
       <c r="S33" t="n">
         <v>0.1166</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3792,13 +3792,13 @@
         <v>66.90000000000001</v>
       </c>
       <c r="P34" t="n">
-        <v>1.9838</v>
+        <v>1.951</v>
       </c>
       <c r="Q34" t="n">
         <v>69400</v>
       </c>
       <c r="R34" t="n">
-        <v>0.19</v>
+        <v>-1.46</v>
       </c>
       <c r="S34" t="n">
         <v>1.68</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         <v>63.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.0469</v>
+        <v>1.0492</v>
       </c>
       <c r="Q35" t="n">
         <v>7998</v>
       </c>
       <c r="R35" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="S35" t="n">
         <v>1.09</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>38.4</v>
       </c>
       <c r="P39" t="n">
-        <v>6.83</v>
+        <v>6.78</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.66</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="S39" t="n">
         <v>6.81</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>41.8</v>
       </c>
       <c r="P40" t="n">
-        <v>1.3607</v>
+        <v>1.3802</v>
       </c>
       <c r="Q40" t="n">
         <v>2116</v>
       </c>
       <c r="R40" t="n">
-        <v>17.3</v>
+        <v>18.98</v>
       </c>
       <c r="S40" t="n">
         <v>1.24</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
         <v>67.40000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>0.6311</v>
+        <v>0.631</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S41" t="n">
         <v>0.631</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>40.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.6711</v>
+        <v>0.6896</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.75</v>
+        <v>1.98</v>
       </c>
       <c r="S43" t="n">
         <v>0.718</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4968,13 +4968,13 @@
         <v>49.2</v>
       </c>
       <c r="P46" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.41</v>
+        <v>2.67</v>
       </c>
       <c r="S46" t="n">
         <v>4.7005</v>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5066,13 +5066,13 @@
         <v>81.8</v>
       </c>
       <c r="P47" t="n">
-        <v>5.6984</v>
+        <v>5.6923</v>
       </c>
       <c r="Q47" t="n">
         <v>5498</v>
       </c>
       <c r="R47" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="S47" t="n">
         <v>5.7</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5368,13 +5368,13 @@
         <v>31.2</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2875</v>
+        <v>0.2907</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.64</v>
+        <v>4.79</v>
       </c>
       <c r="S50" t="n">
         <v>0.2804</v>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5466,13 +5466,13 @@
         <v>75.3</v>
       </c>
       <c r="P51" t="n">
-        <v>1.47</v>
+        <v>1.4615</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.03</v>
+        <v>0.45</v>
       </c>
       <c r="S51" t="n">
         <v>1.4297</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5666,13 +5666,13 @@
         <v>77.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.18</v>
+        <v>3.82</v>
       </c>
       <c r="S53" t="n">
         <v>1.5</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5764,13 +5764,13 @@
         <v>50.4</v>
       </c>
       <c r="P54" t="n">
-        <v>0.6288</v>
+        <v>0.6011</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-16.18</v>
+        <v>-19.87</v>
       </c>
       <c r="S54" t="n">
         <v>0.29</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5862,13 +5862,13 @@
         <v>35.8</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-4.55</v>
+        <v>-2.13</v>
       </c>
       <c r="S55" t="n">
         <v>0.669</v>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5960,13 +5960,13 @@
         <v>31.5</v>
       </c>
       <c r="P56" t="n">
-        <v>3.2169</v>
+        <v>3.2008</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-3.11</v>
+        <v>-3.59</v>
       </c>
       <c r="S56" t="n">
         <v>3.63</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6062,13 +6062,13 @@
         <v>45.6</v>
       </c>
       <c r="P57" t="n">
-        <v>0.3568</v>
+        <v>0.3541</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.62</v>
+        <v>-4.35</v>
       </c>
       <c r="S57" t="n">
         <v>0.3051</v>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6160,13 +6160,13 @@
         <v>36.4</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6731</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
       <c r="S58" t="n">
         <v>0.72</v>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6258,13 +6258,13 @@
         <v>20.6</v>
       </c>
       <c r="P59" t="n">
-        <v>1.8849</v>
+        <v>1.88</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-5.75</v>
+        <v>-6</v>
       </c>
       <c r="S59" t="n">
         <v>2.39</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6454,13 +6454,13 @@
         <v>67.59999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>3.9102</v>
+        <v>3.75</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>127.58</v>
+        <v>118.25</v>
       </c>
       <c r="S61" t="n">
         <v>0.44</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6556,13 +6556,13 @@
         <v>32.7</v>
       </c>
       <c r="P62" t="n">
-        <v>0.3344</v>
+        <v>0.3254</v>
       </c>
       <c r="Q62" t="n">
         <v>868</v>
       </c>
       <c r="R62" t="n">
-        <v>-8.51</v>
+        <v>-10.97</v>
       </c>
       <c r="S62" t="n">
         <v>0.348</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4.2x vs 6.9x median — trading at discount</t>
+          <t>4.2x vs 8.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>P/S 4.2x vs 6.9x median — trading at discount | P/B 1.3x vs 1.0x median — trading at premium | Graham # $2.51</t>
+          <t>P/S 4.2x vs 8.3x median — trading at discount | P/B 1.3x vs 1.0x median — trading at premium | Graham # $2.51</t>
         </is>
       </c>
       <c r="AE2" t="n">
@@ -6996,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1401</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="Q3" t="n">
         <v>1.33</v>
@@ -7116,13 +7116,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6288</v>
+        <v>0.6011</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-16.18</v>
+        <v>-19.87</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -7236,13 +7236,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9102</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>127.58</v>
+        <v>118.25</v>
       </c>
       <c r="Q5" t="n">
         <v>6.26</v>
@@ -7263,11 +7263,11 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.38</v>
+        <v>9.58</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.4x vs 14.8x median — trading at discount</t>
+          <t>9.6x vs 15.9x median — trading at discount</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 14.8x median — trading at discount | P/B -0.5x vs 5.6x median — trading at discount</t>
+          <t>P/S 9.6x vs 15.9x median — trading at discount | P/B -0.5x vs 5.6x median — trading at discount</t>
         </is>
       </c>
       <c r="AE5" t="n">
@@ -7356,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.39</v>
+        <v>5.1015</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-10.58</v>
+        <v>-15.37</v>
       </c>
       <c r="Q6" t="n">
         <v>6.39</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>-0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>P/S 0.7x vs 0.7x median — in-line | P/B 9.3x vs 2.1x median — trading at premium | EV/EBITDA -0.2x vs -2.5x median — trading at discount</t>
+          <t>P/S 0.7x vs 0.7x median — in-line | P/B 9.3x vs 2.1x median — trading at premium | EV/EBITDA -0.4x vs -2.5x median — trading at discount</t>
         </is>
       </c>
       <c r="AE6" t="n">
@@ -7476,13 +7476,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.8849</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.75</v>
+        <v>-6</v>
       </c>
       <c r="Q7" t="n">
         <v>2.77</v>
@@ -7716,13 +7716,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6.63</v>
+        <v>5.48</v>
       </c>
       <c r="Q9" t="n">
         <v>4.07</v>
@@ -7731,13 +7731,13 @@
         <v>3.4</v>
       </c>
       <c r="S9" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>15.56</v>
+        <v>14.7</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>-0.38</v>
+        <v>-0.21</v>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>P/B 1.0x vs 2.3x median — trading at discount | EV/EBITDA -0.4x vs -1.1x median — trading at discount</t>
+          <t>P/B 1.0x vs 2.3x median — trading at discount | EV/EBITDA -0.2x vs -1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AE9" t="n">
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3568</v>
+        <v>0.3541</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.62</v>
+        <v>-4.35</v>
       </c>
       <c r="Q10" t="n">
         <v>0.484</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>-2.52</v>
+        <v>-2.63</v>
       </c>
       <c r="AB10" t="n">
         <v/>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>P/S 0.3x vs 6.3x median — trading at discount | P/B 0.7x vs 2.3x median — trading at discount | EV/EBITDA -2.5x vs -1.1x median — trading at premium</t>
+          <t>P/S 0.3x vs 6.3x median — trading at discount | P/B 0.7x vs 2.3x median — trading at discount | EV/EBITDA -2.6x vs -1.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AE10" t="n">
@@ -7956,13 +7956,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.97</v>
+        <v>5.8892</v>
       </c>
       <c r="O11" t="n">
         <v>1962</v>
       </c>
       <c r="P11" t="n">
-        <v>14.64</v>
+        <v>13.09</v>
       </c>
       <c r="Q11" t="n">
         <v>7.5</v>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>-0.58</v>
+        <v>-0.88</v>
       </c>
       <c r="AB11" t="n">
         <v/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>P/S 1.7x vs 6.3x median — trading at discount | P/B 6.1x vs 2.3x median — trading at premium | EV/EBITDA -0.6x vs -1.1x median — trading at discount</t>
+          <t>P/S 1.7x vs 6.3x median — trading at discount | P/B 6.1x vs 2.3x median — trading at premium | EV/EBITDA -0.9x vs -1.1x median — in-line</t>
         </is>
       </c>
       <c r="AE11" t="n">
@@ -8076,13 +8076,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.18</v>
+        <v>3.82</v>
       </c>
       <c r="Q12" t="n">
         <v>1.68</v>
@@ -8196,13 +8196,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3607</v>
+        <v>1.3802</v>
       </c>
       <c r="O13" t="n">
         <v>2116</v>
       </c>
       <c r="P13" t="n">
-        <v>17.3</v>
+        <v>18.98</v>
       </c>
       <c r="Q13" t="n">
         <v>1.55</v>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>258.9x vs 14.8x median — trading at premium</t>
+          <t>258.9x vs 15.9x median — trading at premium</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P/S 258.9x vs 14.8x median — trading at premium | P/B 18.6x vs 5.6x median — trading at premium | EV/EBITDA -1.4x vs -0.9x median — trading at premium | Analyst target $8.00</t>
+          <t>P/S 258.9x vs 15.9x median — trading at premium | P/B 18.6x vs 5.6x median — trading at premium | EV/EBITDA -1.4x vs -0.9x median — trading at premium | Analyst target $8.00</t>
         </is>
       </c>
       <c r="AE13" t="n">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2.3x vs 6.9x median — trading at discount</t>
+          <t>2.3x vs 8.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P/S 2.3x vs 6.9x median — trading at discount | P/B 0.9x vs 1.0x median — in-line | Graham # $23.68</t>
+          <t>P/S 2.3x vs 8.3x median — trading at discount | P/B 0.9x vs 1.0x median — in-line | Graham # $23.68</t>
         </is>
       </c>
       <c r="AE14" t="n">
@@ -8436,13 +8436,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.7103</v>
+        <v>1.6501</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>-1.19</v>
       </c>
       <c r="Q15" t="n">
         <v>1.8</v>
@@ -8556,13 +8556,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>10.8</v>
+        <v>10.805</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="Q16" t="n">
         <v>10.828</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0902</v>
+        <v>1.0808</v>
       </c>
       <c r="O17" t="n">
         <v>7057</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.78</v>
+        <v>-2.63</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>-2.4x vs 6.9x median — trading at discount</t>
+          <t>-2.4x vs 8.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>P/S -2.4x vs 6.9x median — trading at discount | P/B 0.4x vs 1.0x median — trading at discount</t>
+          <t>P/S -2.4x vs 8.3x median — trading at discount | P/B 0.4x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AE17" t="n">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>13.1x vs 6.9x median — trading at premium</t>
+          <t>13.1x vs 8.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/S 13.1x vs 6.9x median — trading at premium | P/B 1.6x vs 1.0x median — trading at premium | EV/EBITDA -12.3x vs -3.5x median — trading at premium</t>
+          <t>P/S 13.1x vs 8.3x median — trading at premium | P/B 1.6x vs 1.0x median — trading at premium | EV/EBITDA -12.3x vs -3.5x median — trading at premium</t>
         </is>
       </c>
       <c r="AE18" t="n">
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1423</v>
+        <v>0.1451</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-12.11</v>
+        <v>-10.38</v>
       </c>
       <c r="Q19" t="n">
         <v>0.166</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>-1.09</v>
+        <v>-1.15</v>
       </c>
       <c r="AB19" t="n">
         <v/>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9838</v>
+        <v>1.951</v>
       </c>
       <c r="O20" t="n">
         <v>69400</v>
       </c>
       <c r="P20" t="n">
-        <v>0.19</v>
+        <v>-1.46</v>
       </c>
       <c r="Q20" t="n">
         <v>2.0397</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.81</v>
+        <v>5.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Q21" t="n">
         <v>5.88</v>
@@ -9516,13 +9516,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8037</v>
+        <v>3.81</v>
       </c>
       <c r="O24" t="n">
         <v>221</v>
       </c>
       <c r="P24" t="n">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="Q24" t="n">
         <v>3.89</v>
@@ -9756,13 +9756,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.0469</v>
+        <v>1.0492</v>
       </c>
       <c r="O26" t="n">
         <v>7998</v>
       </c>
       <c r="P26" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
         <v>1.12</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3344</v>
+        <v>0.3254</v>
       </c>
       <c r="O27" t="n">
         <v>868</v>
       </c>
       <c r="P27" t="n">
-        <v>-8.51</v>
+        <v>-10.97</v>
       </c>
       <c r="Q27" t="n">
         <v>0.4621</v>
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2875</v>
+        <v>0.2907</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.64</v>
+        <v>4.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0.2999</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.47</v>
+        <v>1.4615</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.03</v>
+        <v>0.45</v>
       </c>
       <c r="Q29" t="n">
         <v>1.76</v>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>4.4x vs 6.9x median — trading at discount</t>
+          <t>4.4x vs 8.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y29" t="n">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>P/S 4.4x vs 6.9x median — trading at discount | P/B 2.0x vs 1.0x median — trading at premium | EV/EBITDA -17.9x vs -3.5x median — trading at premium</t>
+          <t>P/S 4.4x vs 8.3x median — trading at discount | P/B 2.0x vs 1.0x median — trading at premium | EV/EBITDA -17.9x vs -3.5x median — trading at premium</t>
         </is>
       </c>
       <c r="AE29" t="n">
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-4.55</v>
+        <v>-2.13</v>
       </c>
       <c r="Q31" t="n">
         <v>0.7333</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6311</v>
+        <v>0.631</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
         <v>0.6361</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>3.9x vs 6.9x median — trading at discount</t>
+          <t>3.9x vs 8.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y32" t="n">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>P/S 3.9x vs 6.9x median — trading at discount | P/B 1.7x vs 1.0x median — trading at premium | EV/EBITDA 8.3x vs -3.5x median — trading at discount | Analyst target $2.40 | Graham # $0.70</t>
+          <t>P/S 3.9x vs 8.3x median — trading at discount | P/B 1.7x vs 1.0x median — trading at premium | EV/EBITDA 8.3x vs -3.5x median — trading at discount | Analyst target $2.40 | Graham # $0.70</t>
         </is>
       </c>
       <c r="AE32" t="n">
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6711</v>
+        <v>0.6896</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
@@ -10836,13 +10836,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3503</v>
+        <v>2.3598</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-2.88</v>
+        <v>-2.49</v>
       </c>
       <c r="Q35" t="n">
         <v>2.6884</v>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2.2x vs 6.9x median — trading at discount</t>
+          <t>2.2x vs 8.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>P/S 2.2x vs 6.9x median — trading at discount | P/B 1.3x vs 1.0x median — trading at premium | EV/EBITDA -3.5x vs -3.5x median — in-line</t>
+          <t>P/S 2.2x vs 8.3x median — trading at discount | P/B 1.3x vs 1.0x median — trading at premium | EV/EBITDA -3.5x vs -3.5x median — in-line</t>
         </is>
       </c>
       <c r="AE35" t="n">
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2169</v>
+        <v>3.2008</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-3.11</v>
+        <v>-3.59</v>
       </c>
       <c r="Q37" t="n">
         <v>6.85</v>
@@ -11107,7 +11107,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>70.0x vs 6.9x median — trading at premium</t>
+          <t>70.0x vs 8.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y37" t="n">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>P/S 70.0x vs 6.9x median — trading at premium | P/B -0.9x vs 1.0x median — trading at discount</t>
+          <t>P/S 70.0x vs 8.3x median — trading at premium | P/B -0.9x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AE37" t="n">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>22.2x vs 14.8x median — trading at premium</t>
+          <t>22.2x vs 15.9x median — trading at premium</t>
         </is>
       </c>
       <c r="Y40" t="n">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>P/S 22.2x vs 14.8x median — trading at premium | P/B 10.6x vs 5.6x median — trading at premium</t>
+          <t>P/S 22.2x vs 15.9x median — trading at premium | P/B 10.6x vs 5.6x median — trading at premium</t>
         </is>
       </c>
       <c r="AE40" t="n">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>38.8x vs 6.9x median — trading at premium</t>
+          <t>38.8x vs 8.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y42" t="n">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>P/S 38.8x vs 6.9x median — trading at premium | P/B 1.1x vs 1.0x median — in-line | Graham # $10.33</t>
+          <t>P/S 38.8x vs 8.3x median — trading at premium | P/B 1.1x vs 1.0x median — in-line | Graham # $10.33</t>
         </is>
       </c>
       <c r="AE42" t="n">
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="Q43" t="n">
         <v>4.15</v>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>8.4x vs 6.9x median — trading at premium</t>
+          <t>8.4x vs 8.3x median — in-line</t>
         </is>
       </c>
       <c r="Y43" t="n">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="AA43" t="n">
-        <v>-1.86</v>
+        <v>-1.89</v>
       </c>
       <c r="AB43" t="n">
         <v>5.85</v>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>P/S 8.4x vs 6.9x median — trading at premium | P/B -10.4x vs 1.0x median — trading at discount | EV/EBITDA -1.9x vs -3.5x median — trading at discount | Analyst target $5.85</t>
+          <t>P/S 8.4x vs 8.3x median — in-line | P/B -10.4x vs 1.0x median — trading at discount | EV/EBITDA -1.9x vs -3.5x median — trading at discount | Analyst target $5.85</t>
         </is>
       </c>
       <c r="AE43" t="n">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>7.4x vs 14.8x median — trading at discount</t>
+          <t>7.4x vs 15.9x median — trading at discount</t>
         </is>
       </c>
       <c r="Y44" t="n">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>P/S 7.4x vs 14.8x median — trading at discount | P/B 0.6x vs 5.6x median — trading at discount | EV/EBITDA -0.4x vs -0.9x median — trading at discount | Analyst target $9.50</t>
+          <t>P/S 7.4x vs 15.9x median — trading at discount | P/B 0.6x vs 5.6x median — trading at discount | EV/EBITDA -0.4x vs -0.9x median — trading at discount | Analyst target $9.50</t>
         </is>
       </c>
       <c r="AE44" t="n">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>8.1x vs 6.9x median — in-line</t>
+          <t>8.1x vs 8.3x median — in-line</t>
         </is>
       </c>
       <c r="Y45" t="n">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>P/S 8.1x vs 6.9x median — in-line | P/B 0.9x vs 1.0x median — in-line | Graham # $3.20</t>
+          <t>P/S 8.1x vs 8.3x median — in-line | P/B 0.9x vs 1.0x median — in-line | Graham # $3.20</t>
         </is>
       </c>
       <c r="AE45" t="n">
@@ -12156,13 +12156,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6731</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
       <c r="Q46" t="n">
         <v>0.719</v>
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="AA46" t="n">
-        <v>-1.09</v>
+        <v>-1.02</v>
       </c>
       <c r="AB46" t="n">
         <v>3.2</v>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>P/S 113.3x vs 6.3x median — trading at premium | P/B 1.4x vs 2.3x median — trading at discount | EV/EBITDA -1.1x vs -1.1x median — in-line | Analyst target $3.20</t>
+          <t>P/S 113.3x vs 6.3x median — trading at premium | P/B 1.4x vs 2.3x median — trading at discount | EV/EBITDA -1.0x vs -1.1x median — in-line | Analyst target $3.20</t>
         </is>
       </c>
       <c r="AE46" t="n">
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.7</v>
+        <v>0.6975</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="Q47" t="n">
         <v>1.1599</v>
@@ -12543,11 +12543,11 @@
         <v>1</v>
       </c>
       <c r="W49" t="n">
-        <v/>
+        <v>52.25</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>52.3x vs 8.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y49" t="n">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>P/B 2.2x vs 1.0x median — trading at premium | Graham # $6.08</t>
+          <t>P/S 52.3x vs 8.3x median — trading at premium | P/B 2.2x vs 1.0x median — trading at premium | Graham # $6.08</t>
         </is>
       </c>
       <c r="AE49" t="n">
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.83</v>
+        <v>6.78</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.66</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q51" t="n">
         <v>8.01</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>5.6x vs 6.9x median — in-line</t>
+          <t>5.6x vs 8.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y52" t="n">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>P/S 5.6x vs 6.9x median — in-line | P/B 0.8x vs 1.0x median — trading at discount | Graham # $2.75</t>
+          <t>P/S 5.6x vs 8.3x median — trading at discount | P/B 0.8x vs 1.0x median — trading at discount | Graham # $2.75</t>
         </is>
       </c>
       <c r="AE52" t="n">
@@ -13116,13 +13116,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-0.41</v>
+        <v>2.67</v>
       </c>
       <c r="Q54" t="n">
         <v>5.23</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7003</v>
+        <v>2.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>-5.25</v>
+        <v>-5.26</v>
       </c>
       <c r="Q55" t="n">
         <v>2.95</v>
@@ -13356,13 +13356,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="O56" t="n">
         <v>93688</v>
       </c>
       <c r="P56" t="n">
-        <v>0.66</v>
+        <v>-0.66</v>
       </c>
       <c r="Q56" t="n">
         <v>5.28</v>
@@ -13476,13 +13476,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.6984</v>
+        <v>5.6923</v>
       </c>
       <c r="O57" t="n">
         <v>5498</v>
       </c>
       <c r="P57" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="Q57" t="n">
         <v>5.74</v>
@@ -13503,11 +13503,11 @@
         <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v/>
+        <v>38.62</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>38.6x vs 8.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y57" t="n">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>P/B 1.0x vs 1.0x median — in-line | Graham # $15.78</t>
+          <t>P/S 38.6x vs 8.3x median — trading at premium | P/B 1.0x vs 1.0x median — in-line | Graham # $15.78</t>
         </is>
       </c>
       <c r="AE57" t="n">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>85.6x vs 6.9x median — trading at premium</t>
+          <t>85.6x vs 8.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y58" t="n">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>P/S 85.6x vs 6.9x median — trading at premium | P/B 1.0x vs 1.0x median — in-line | Graham # $31.14</t>
+          <t>P/S 85.6x vs 8.3x median — trading at premium | P/B 1.0x vs 1.0x median — in-line | Graham # $31.14</t>
         </is>
       </c>
       <c r="AE58" t="n">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2209.2x vs 6.9x median — trading at premium</t>
+          <t>2209.2x vs 8.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y60" t="n">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>P/S 2209.2x vs 6.9x median — trading at premium | P/B 0.6x vs 1.0x median — trading at discount</t>
+          <t>P/S 2209.2x vs 8.3x median — trading at premium | P/B 0.6x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AE60" t="n">

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -656,13 +656,13 @@
         <v>72.90000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.14</v>
+        <v>1.1201</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="S2" t="n">
         <v>1.04</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>55.6</v>
       </c>
       <c r="P3" t="n">
-        <v>13.39</v>
+        <v>13.4</v>
       </c>
       <c r="Q3" t="n">
         <v>211582</v>
       </c>
       <c r="R3" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="S3" t="n">
         <v>13.61</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>71</v>
       </c>
       <c r="P4" t="n">
-        <v>5.1015</v>
+        <v>5.1311</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-15.37</v>
+        <v>-14.88</v>
       </c>
       <c r="S4" t="n">
         <v>8.41</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         <v>81</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8211</v>
+        <v>2.8201</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.55</v>
+        <v>-2.59</v>
       </c>
       <c r="S6" t="n">
         <v>2.68</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6501</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.19</v>
+        <v>-3.59</v>
       </c>
       <c r="S7" t="n">
         <v>1.86</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1244,13 +1244,13 @@
         <v>66.90000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="Q8" t="n">
         <v>65522</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.52</v>
+        <v>1.01</v>
       </c>
       <c r="S8" t="n">
         <v>3.98</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1440,13 +1440,13 @@
         <v>64.90000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>10.9</v>
+        <v>10.8806</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="S10" t="n">
         <v>10.27</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         <v>57.4</v>
       </c>
       <c r="P17" t="n">
-        <v>16.42</v>
+        <v>16.291</v>
       </c>
       <c r="Q17" t="n">
         <v>12447</v>
       </c>
       <c r="R17" t="n">
-        <v>0.55</v>
+        <v>-0.24</v>
       </c>
       <c r="S17" t="n">
         <v>16.65</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2224,13 +2224,13 @@
         <v>75</v>
       </c>
       <c r="P18" t="n">
-        <v>5.8</v>
+        <v>5.7677</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.05</v>
+        <v>0.48</v>
       </c>
       <c r="S18" t="n">
         <v>5.52</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2322,13 +2322,13 @@
         <v>63.5</v>
       </c>
       <c r="P19" t="n">
-        <v>7.3</v>
+        <v>7.1745</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.55</v>
+        <v>-1.18</v>
       </c>
       <c r="S19" t="n">
         <v>6.69</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         <v>53.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6975</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.36</v>
+        <v>-0.72</v>
       </c>
       <c r="S21" t="n">
         <v>0.58</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>58.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.81</v>
+        <v>3.8155</v>
       </c>
       <c r="Q23" t="n">
         <v>221</v>
       </c>
       <c r="R23" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
         <v>3.84</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3106,13 +3106,13 @@
         <v>56.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3598</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.49</v>
+        <v>-2.48</v>
       </c>
       <c r="S27" t="n">
         <v>2.69</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3204,13 +3204,13 @@
         <v>76.8</v>
       </c>
       <c r="P28" t="n">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
         <v>4.16</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3302,13 +3302,13 @@
         <v>66.8</v>
       </c>
       <c r="P29" t="n">
-        <v>5.8892</v>
+        <v>5.88</v>
       </c>
       <c r="Q29" t="n">
         <v>1962</v>
       </c>
       <c r="R29" t="n">
-        <v>13.09</v>
+        <v>12.92</v>
       </c>
       <c r="S29" t="n">
         <v>4.3402</v>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3498,22 +3498,22 @@
         <v>47.2</v>
       </c>
       <c r="P31" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>5.48</v>
+        <v>6.05</v>
       </c>
       <c r="S31" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>14.7</v>
+        <v>15.56</v>
       </c>
       <c r="V31" t="n">
         <v>4.07</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3596,13 +3596,13 @@
         <v>52.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1.0808</v>
+        <v>1.0797</v>
       </c>
       <c r="Q32" t="n">
         <v>7057</v>
       </c>
       <c r="R32" t="n">
-        <v>-2.63</v>
+        <v>-2.73</v>
       </c>
       <c r="S32" t="n">
         <v>1.24</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3694,13 +3694,13 @@
         <v>33.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1451</v>
+        <v>0.142</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-10.38</v>
+        <v>-12.29</v>
       </c>
       <c r="S33" t="n">
         <v>0.1166</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         <v>63.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.0492</v>
+        <v>1.06</v>
       </c>
       <c r="Q35" t="n">
         <v>7998</v>
       </c>
       <c r="R35" t="n">
-        <v>1.86</v>
+        <v>2.91</v>
       </c>
       <c r="S35" t="n">
         <v>1.09</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3988,13 +3988,13 @@
         <v>55</v>
       </c>
       <c r="P36" t="n">
-        <v>1.75</v>
+        <v>1.7997</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.57</v>
+        <v>3.43</v>
       </c>
       <c r="S36" t="n">
         <v>1.6284</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4086,13 +4086,13 @@
         <v>52.1</v>
       </c>
       <c r="P37" t="n">
-        <v>1.01</v>
+        <v>0.9898</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>-0.67</v>
       </c>
       <c r="S37" t="n">
         <v>0.9301</v>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4184,13 +4184,13 @@
         <v>63.4</v>
       </c>
       <c r="P38" t="n">
-        <v>3.58</v>
+        <v>3.5938</v>
       </c>
       <c r="Q38" t="n">
         <v>29096</v>
       </c>
       <c r="R38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
         <v>3.25</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>38.4</v>
       </c>
       <c r="P39" t="n">
-        <v>6.78</v>
+        <v>6.8006</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="S39" t="n">
         <v>6.81</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>41.8</v>
       </c>
       <c r="P40" t="n">
-        <v>1.3802</v>
+        <v>1.36</v>
       </c>
       <c r="Q40" t="n">
         <v>2116</v>
       </c>
       <c r="R40" t="n">
-        <v>18.98</v>
+        <v>17.24</v>
       </c>
       <c r="S40" t="n">
         <v>1.24</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
         <v>67.40000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>0.631</v>
+        <v>0.632</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S41" t="n">
         <v>0.631</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4576,13 +4576,13 @@
         <v>68.2</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>1.9988</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="S42" t="n">
         <v>1.93</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>40.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.6896</v>
+        <v>0.6711</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.98</v>
+        <v>-0.75</v>
       </c>
       <c r="S43" t="n">
         <v>0.718</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4772,13 +4772,13 @@
         <v>45.4</v>
       </c>
       <c r="P44" t="n">
-        <v>1.401</v>
+        <v>1.4699</v>
       </c>
       <c r="Q44" t="n">
         <v>10065</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.28</v>
+        <v>4.62</v>
       </c>
       <c r="S44" t="n">
         <v>1.33</v>
@@ -4790,7 +4790,7 @@
         <v>-5.34</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4395</v>
+        <v>1.4699</v>
       </c>
       <c r="W44" t="n">
         <v>1.27</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5270,13 +5270,13 @@
         <v>48.5</v>
       </c>
       <c r="P49" t="n">
-        <v>4.86</v>
+        <v>4.99</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.62</v>
+        <v>3.31</v>
       </c>
       <c r="S49" t="n">
         <v>5.48</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5368,13 +5368,13 @@
         <v>31.2</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2907</v>
+        <v>0.282</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.79</v>
+        <v>1.66</v>
       </c>
       <c r="S50" t="n">
         <v>0.2804</v>
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5466,13 +5466,13 @@
         <v>75.3</v>
       </c>
       <c r="P51" t="n">
-        <v>1.4615</v>
+        <v>1.4785</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.45</v>
+        <v>1.62</v>
       </c>
       <c r="S51" t="n">
         <v>1.4297</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5764,13 +5764,13 @@
         <v>50.4</v>
       </c>
       <c r="P54" t="n">
-        <v>0.6011</v>
+        <v>0.6218</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-19.87</v>
+        <v>-17.12</v>
       </c>
       <c r="S54" t="n">
         <v>0.29</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5960,13 +5960,13 @@
         <v>31.5</v>
       </c>
       <c r="P56" t="n">
-        <v>3.2008</v>
+        <v>3.31</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-3.59</v>
+        <v>-0.3</v>
       </c>
       <c r="S56" t="n">
         <v>3.63</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6062,13 +6062,13 @@
         <v>45.6</v>
       </c>
       <c r="P57" t="n">
-        <v>0.3541</v>
+        <v>0.376</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.35</v>
+        <v>1.57</v>
       </c>
       <c r="S57" t="n">
         <v>0.3051</v>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6160,13 +6160,13 @@
         <v>36.4</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6731</v>
+        <v>0.675</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
       </c>
       <c r="S58" t="n">
         <v>0.72</v>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6454,13 +6454,13 @@
         <v>67.59999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>118.25</v>
+        <v>124.07</v>
       </c>
       <c r="S61" t="n">
         <v>0.44</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6556,13 +6556,13 @@
         <v>32.7</v>
       </c>
       <c r="P62" t="n">
-        <v>0.3254</v>
+        <v>0.333</v>
       </c>
       <c r="Q62" t="n">
         <v>868</v>
       </c>
       <c r="R62" t="n">
-        <v>-10.97</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="S62" t="n">
         <v>0.348</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6876,13 +6876,13 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="O2" t="n">
         <v>65522</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.52</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -6996,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.14</v>
+        <v>1.1201</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
         <v>1.33</v>
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>-0.26</v>
+        <v>-0.7</v>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>P/S 2.8x vs 6.3x median — trading at discount | P/B 1.0x vs 2.3x median — trading at discount | EV/EBITDA -0.3x vs -1.1x median — trading at discount</t>
+          <t>P/S 2.8x vs 6.3x median — trading at discount | P/B 1.0x vs 2.3x median — trading at discount | EV/EBITDA -0.7x vs -1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AE3" t="n">
@@ -7116,13 +7116,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6011</v>
+        <v>0.6218</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-19.87</v>
+        <v>-17.12</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -7236,13 +7236,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>118.25</v>
+        <v>124.07</v>
       </c>
       <c r="Q5" t="n">
         <v>6.26</v>
@@ -7356,13 +7356,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1015</v>
+        <v>5.1311</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-15.37</v>
+        <v>-14.88</v>
       </c>
       <c r="Q6" t="n">
         <v>6.39</v>
@@ -7525,11 +7525,11 @@
         <v/>
       </c>
       <c r="AC7" t="n">
-        <v>329.77</v>
+        <v>328.17</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>P/S 0.7x vs 0.7x median — in-line | P/B 0.2x vs 2.1x median — trading at discount | EV/EBITDA -2.5x vs -2.5x median — in-line | Graham # $329.77</t>
+          <t>P/S 0.7x vs 0.7x median — in-line | P/B 0.2x vs 2.1x median — trading at discount | EV/EBITDA -2.5x vs -2.5x median — in-line | Graham # $328.17</t>
         </is>
       </c>
       <c r="AE7" t="n">
@@ -7716,13 +7716,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5.48</v>
+        <v>6.05</v>
       </c>
       <c r="Q9" t="n">
         <v>4.07</v>
@@ -7731,13 +7731,13 @@
         <v>3.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>14.7</v>
+        <v>15.56</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3541</v>
+        <v>0.376</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.35</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
         <v>0.484</v>
@@ -7956,13 +7956,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8892</v>
+        <v>5.88</v>
       </c>
       <c r="O11" t="n">
         <v>1962</v>
       </c>
       <c r="P11" t="n">
-        <v>13.09</v>
+        <v>12.92</v>
       </c>
       <c r="Q11" t="n">
         <v>7.5</v>
@@ -8196,13 +8196,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3802</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
         <v>2116</v>
       </c>
       <c r="P13" t="n">
-        <v>18.98</v>
+        <v>17.24</v>
       </c>
       <c r="Q13" t="n">
         <v>1.55</v>
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>-1.42</v>
+        <v>-1.28</v>
       </c>
       <c r="AB13" t="n">
         <v>8</v>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P/S 258.9x vs 15.9x median — trading at premium | P/B 18.6x vs 5.6x median — trading at premium | EV/EBITDA -1.4x vs -0.9x median — trading at premium | Analyst target $8.00</t>
+          <t>P/S 258.9x vs 15.9x median — trading at premium | P/B 18.6x vs 5.6x median — trading at premium | EV/EBITDA -1.3x vs -0.8x median — trading at premium | Analyst target $8.00</t>
         </is>
       </c>
       <c r="AE13" t="n">
@@ -8436,13 +8436,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6501</v>
+        <v>1.61</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.19</v>
+        <v>-3.59</v>
       </c>
       <c r="Q15" t="n">
         <v>1.8</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0808</v>
+        <v>1.0797</v>
       </c>
       <c r="O17" t="n">
         <v>7057</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.63</v>
+        <v>-2.73</v>
       </c>
       <c r="Q17" t="n">
         <v>1.52</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8211</v>
+        <v>2.8201</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.55</v>
+        <v>-2.59</v>
       </c>
       <c r="Q18" t="n">
         <v>2.92</v>
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1451</v>
+        <v>0.142</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-10.38</v>
+        <v>-12.29</v>
       </c>
       <c r="Q19" t="n">
         <v>0.166</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8</v>
+        <v>5.7677</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.05</v>
+        <v>0.48</v>
       </c>
       <c r="Q21" t="n">
         <v>5.88</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>13.39</v>
+        <v>13.4</v>
       </c>
       <c r="O22" t="n">
         <v>211582</v>
       </c>
       <c r="P22" t="n">
-        <v>8.07</v>
+        <v>8.15</v>
       </c>
       <c r="Q22" t="n">
         <v>14.6</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>7.3</v>
+        <v>7.1745</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.55</v>
+        <v>-1.18</v>
       </c>
       <c r="Q23" t="n">
         <v>7.56</v>
@@ -9516,13 +9516,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.81</v>
+        <v>3.8155</v>
       </c>
       <c r="O24" t="n">
         <v>221</v>
       </c>
       <c r="P24" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Q24" t="n">
         <v>3.89</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.9</v>
+        <v>10.8806</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Q25" t="n">
         <v>10.9</v>
@@ -9756,13 +9756,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.0492</v>
+        <v>1.06</v>
       </c>
       <c r="O26" t="n">
         <v>7998</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>2.91</v>
       </c>
       <c r="Q26" t="n">
         <v>1.12</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3254</v>
+        <v>0.333</v>
       </c>
       <c r="O27" t="n">
         <v>868</v>
       </c>
       <c r="P27" t="n">
-        <v>-10.97</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>0.4621</v>
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2907</v>
+        <v>0.282</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.79</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
         <v>0.2999</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.4615</v>
+        <v>1.4785</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.45</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
         <v>1.76</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.631</v>
+        <v>0.632</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
         <v>0.6361</v>
@@ -10596,13 +10596,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1.9988</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="Q33" t="n">
         <v>2.0899</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6896</v>
+        <v>0.6711</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.98</v>
+        <v>-0.75</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
@@ -10836,13 +10836,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3598</v>
+        <v>2.36</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-2.49</v>
+        <v>-2.48</v>
       </c>
       <c r="Q35" t="n">
         <v>2.6884</v>
@@ -10956,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.75</v>
+        <v>1.7997</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.57</v>
+        <v>3.43</v>
       </c>
       <c r="Q36" t="n">
         <v>1.8</v>
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2008</v>
+        <v>3.31</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-3.59</v>
+        <v>-0.3</v>
       </c>
       <c r="Q37" t="n">
         <v>6.85</v>
@@ -11316,16 +11316,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.401</v>
+        <v>1.4699</v>
       </c>
       <c r="O39" t="n">
         <v>10065</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.28</v>
+        <v>4.62</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.4395</v>
+        <v>1.4699</v>
       </c>
       <c r="R39" t="n">
         <v>1.27</v>
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.86</v>
+        <v>4.99</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.62</v>
+        <v>3.31</v>
       </c>
       <c r="Q40" t="n">
         <v>6.5</v>
@@ -11556,13 +11556,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.01</v>
+        <v>0.9898</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.35</v>
+        <v>-0.67</v>
       </c>
       <c r="Q41" t="n">
         <v>1.02</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="Q43" t="n">
         <v>4.15</v>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>P/S 7.4x vs 15.9x median — trading at discount | P/B 0.6x vs 5.6x median — trading at discount | EV/EBITDA -0.4x vs -0.9x median — trading at discount | Analyst target $9.50</t>
+          <t>P/S 7.4x vs 15.9x median — trading at discount | P/B 0.6x vs 5.6x median — trading at discount | EV/EBITDA -0.4x vs -0.8x median — trading at discount | Analyst target $9.50</t>
         </is>
       </c>
       <c r="AE44" t="n">
@@ -12156,13 +12156,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.6731</v>
+        <v>0.675</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
       </c>
       <c r="Q46" t="n">
         <v>0.719</v>
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.6975</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.36</v>
+        <v>-0.72</v>
       </c>
       <c r="Q47" t="n">
         <v>1.1599</v>
@@ -12636,13 +12636,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.58</v>
+        <v>3.5938</v>
       </c>
       <c r="O50" t="n">
         <v>29096</v>
       </c>
       <c r="P50" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
         <v>3.6</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.78</v>
+        <v>6.8006</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="Q51" t="n">
         <v>8.01</v>
@@ -13956,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>16.42</v>
+        <v>16.291</v>
       </c>
       <c r="O61" t="n">
         <v>12447</v>
       </c>
       <c r="P61" t="n">
-        <v>0.55</v>
+        <v>-0.24</v>
       </c>
       <c r="Q61" t="n">
         <v>16.74</v>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -604,25 +604,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FNGR</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1.19</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -633,51 +633,51 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-41.6</v>
+        <v>-4.5</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 8.01, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.8pts)   Item 1.01 (entry_agreement, +3) | Item 2.03 (direct_obligation, -1) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)   Title: Entry into a Material Definitive Agreement.</t>
+          <t>2026-08-24 8-K/A (material_event, +1.8pts)   Items: 2.02, 8.01, 9.01 (routine) | 2026-08-24 8-K (material_event, +1.8pts)   Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.18</v>
+        <v>2.79</v>
       </c>
       <c r="N2" t="n">
-        <v>11.49</v>
+        <v>1.79</v>
       </c>
       <c r="O2" t="n">
-        <v>31.5</v>
+        <v>74</v>
       </c>
       <c r="P2" t="n">
-        <v>0.196</v>
+        <v>2.8201</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>10.92</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2037</v>
+        <v>2.91</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>15.28</v>
+        <v>4.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2349</v>
+        <v>2.92</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1951</v>
+        <v>1.99</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
@@ -702,7 +702,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GPUS</t>
+          <t>TNXP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.42</v>
+        <v>7.16</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1.95</v>
+        <v>1.05</v>
       </c>
       <c r="F3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -731,51 +731,51 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-19.6</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-20 4/A (insider_buy, +1.5pts) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 7.01 (routine)</t>
+          <t>2026-08-24 4 (insider_buy, +2.7pts) | 2026-08-18 8-K (material_event, +0.3pts)   Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.38</v>
+        <v>13.52</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>1.58</v>
       </c>
       <c r="O3" t="n">
-        <v>24.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v/>
+        <v>12.75</v>
       </c>
       <c r="Q3" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v/>
+        <v>-5.76</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4813</v>
+        <v>12.44</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>26.82</v>
+        <v>-8.06</v>
       </c>
       <c r="V3" t="n">
-        <v/>
+        <v>12.9</v>
       </c>
       <c r="W3" t="n">
-        <v/>
+        <v>12.2</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
@@ -800,7 +800,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRML</t>
+          <t>AVXL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.6</v>
+        <v>6.45</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -825,59 +825,55 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Moved</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>11.5</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-25 4 (insider_buy, +3.0pts) | 2026-08-24 8-K (material_event, +1.8pts)   Items: 9.01 (routine) | 2026-08-24 424B5 (dilution_risk, -3.6pts)</t>
+          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.4pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>trend_alignment +4, golden_cross +2, rsi_overbought -2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>10.75</v>
+        <v>3.58</v>
       </c>
       <c r="N4" t="n">
-        <v>0.26</v>
+        <v>1.53</v>
       </c>
       <c r="O4" t="n">
-        <v>99.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="P4" t="n">
-        <v>8.619999999999999</v>
+        <v>3.1564</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-19.81</v>
+        <v>-11.59</v>
       </c>
       <c r="S4" t="n">
-        <v>10.17</v>
+        <v>3.33</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.4</v>
+        <v>-6.72</v>
       </c>
       <c r="V4" t="n">
-        <v>10.41</v>
+        <v>3.42</v>
       </c>
       <c r="W4" t="n">
-        <v>8.119999999999999</v>
+        <v>3.07</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
@@ -902,7 +898,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLQT</t>
+          <t>FNGR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -911,10 +907,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -931,12 +927,12 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-41.6</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)   Title: &gt;slqt-20260825</t>
+          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 8.01, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.8pts)   Item 1.01 (entry_agreement, +3) | Item 2.03 (direct_obligation, -1) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)   Title: Entry into a Material Definitive Agreement.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -945,37 +941,37 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="N5" t="n">
-        <v>6.54</v>
+        <v>11.56</v>
       </c>
       <c r="O5" t="n">
         <v>31.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8279</v>
+        <v>0.196</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>53.26</v>
+        <v>9.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.643</v>
+        <v>0.2037</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>19.03</v>
+        <v>13.55</v>
       </c>
       <c r="V5" t="n">
-        <v>0.86</v>
+        <v>0.2349</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7403</v>
+        <v>0.1951</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
@@ -986,36 +982,36 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v/>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HVII</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.29</v>
+        <v>5.6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>-1</v>
@@ -1029,12 +1025,12 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-7.6</v>
+        <v>-17.7</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, +1.8pts)   Items: 5.07, 8.01 (routine) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
+          <t>2026-08-20 4/A (insider_buy, +1.5pts) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 7.01 (routine)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1043,37 +1039,37 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7.56</v>
+        <v>0.38</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="O6" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="P6" t="n">
-        <v>9.300000000000001</v>
+        <v/>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="R6" t="n">
-        <v>23.02</v>
+        <v/>
       </c>
       <c r="S6" t="n">
-        <v>7.68</v>
+        <v>0.4813</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.59</v>
+        <v>24.98</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v/>
       </c>
       <c r="W6" t="n">
-        <v>6.09</v>
+        <v/>
       </c>
       <c r="X6" t="b">
         <v>1</v>
@@ -1084,39 +1080,39 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v/>
+        <v>5.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>GRML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1127,51 +1123,55 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 8.01, 9.01 (routine)</t>
+          <t>2026-08-25 4 (insider_buy, +3.0pts) | 2026-08-24 8-K (material_event, +1.8pts)   Items: 9.01 (routine) | 2026-08-24 424B5 (dilution_risk, -3.6pts)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +4, golden_cross +2, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3.51</v>
+        <v>10.41</v>
       </c>
       <c r="N7" t="n">
-        <v>4.35</v>
+        <v>0.28</v>
       </c>
       <c r="O7" t="n">
-        <v>27.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>3.835</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>9.27</v>
+        <v>-17.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7902</v>
+        <v>10.17</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>-2.49</v>
       </c>
       <c r="V7" t="n">
-        <v>5.15</v>
+        <v>10.41</v>
       </c>
       <c r="W7" t="n">
-        <v>3.7</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
@@ -1182,36 +1182,36 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v/>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMIX</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4.09</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1221,16 +1221,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-25 8-K (material_event, +1.0pts)   Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1239,37 +1239,37 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>8.119999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="O8" t="n">
-        <v>54.4</v>
+        <v>59.5</v>
       </c>
       <c r="P8" t="n">
-        <v>11.65</v>
+        <v>1.6297</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>44.36</v>
+        <v>-14</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>1.6781</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.87</v>
+        <v>-11.45</v>
       </c>
       <c r="V8" t="n">
-        <v>16.41</v>
+        <v>1.7254</v>
       </c>
       <c r="W8" t="n">
-        <v>5.17</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
@@ -1294,80 +1294,80 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>SLQT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Moved</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-21 4 (insider_buy, +1.8pts)</t>
+          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)   Title: &gt;slqt-20260825</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="N9" t="n">
-        <v>8.58</v>
+        <v>7.03</v>
       </c>
       <c r="O9" t="n">
-        <v>28.4</v>
+        <v>31.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2</v>
+        <v>0.8279</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-6.72</v>
+        <v>54.37</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2029</v>
+        <v>0.643</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.36</v>
+        <v>19.9</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2397</v>
+        <v>0.86</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1845</v>
+        <v>0.7403</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DFNS</t>
+          <t>HVII</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.12</v>
+        <v>3.37</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6</v>
+        <v>2.8</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1421,51 +1421,51 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-57.2</v>
+        <v>-5</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, -2.0pts)   Item 3.01 (delisting, -6) | 2026-08-17 8-K (material_event, +0.4pts)   Items: 8.01 (routine)</t>
+          <t>2026-08-24 8-K (material_event, +1.8pts)   Items: 5.07, 8.01 (routine) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>13.27</v>
+        <v>7.77</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="O10" t="n">
-        <v>42.1</v>
+        <v>28.7</v>
       </c>
       <c r="P10" t="n">
-        <v>11.7482</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-11.67</v>
+        <v>19.69</v>
       </c>
       <c r="S10" t="n">
-        <v>15.48</v>
+        <v>7.68</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>16.39</v>
+        <v>-1.16</v>
       </c>
       <c r="V10" t="n">
-        <v>26.75</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>11.01</v>
+        <v>6.09</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v/>
+        <v>3.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WVVIP</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1499,71 +1499,71 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v/>
+        <v>-15.9</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 8.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>5.42</v>
+        <v>3.66</v>
       </c>
       <c r="N11" t="n">
-        <v>18.87</v>
+        <v>4.52</v>
       </c>
       <c r="O11" t="n">
-        <v>89.3</v>
+        <v>27.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.75</v>
+        <v>3.835</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-50</v>
+        <v>4.78</v>
       </c>
       <c r="S11" t="n">
-        <v>17</v>
+        <v>3.7902</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>209.09</v>
+        <v>3.56</v>
       </c>
       <c r="V11" t="n">
-        <v>2.76</v>
+        <v>5.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BDRX</t>
+          <t>AMIX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1627,41 +1627,41 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.35</v>
+        <v>8.1</v>
       </c>
       <c r="N12" t="n">
-        <v>16.72</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>37.2</v>
+        <v>54.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>11.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-7.41</v>
+        <v>43.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.48</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>9.630000000000001</v>
+        <v>-1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>16.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1877</v>
+        <v>5.17</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1695,96 +1695,96 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>151.8</v>
+        <v>9.6</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)   Title: &gt;pmi20260814_8k.htm</t>
+          <t>2026-08-21 4 (insider_buy, +1.8pts)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>7.63</v>
+        <v>0.21</v>
       </c>
       <c r="N13" t="n">
-        <v>7.11</v>
+        <v>9.25</v>
       </c>
       <c r="O13" t="n">
-        <v>75.8</v>
+        <v>27.3</v>
       </c>
       <c r="P13" t="n">
-        <v>5.96</v>
+        <v>0.2</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-21.43</v>
+        <v>-2.58</v>
       </c>
       <c r="S13" t="n">
-        <v>6.04</v>
+        <v>0.2029</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-20.37</v>
+        <v>-1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0.2397</v>
       </c>
       <c r="W13" t="n">
-        <v>3.03</v>
+        <v>0.1845</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MCRP</t>
+          <t>DFNS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1793,82 +1793,82 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v/>
+        <v>-57.9</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-20 8-K (material_event, -2.0pts)   Item 3.01 (delisting, -6) | 2026-08-17 8-K (material_event, +0.4pts)   Items: 8.01 (routine)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +3, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>13.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.48</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>38.8</v>
+        <v>42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.36</v>
+        <v>11.7482</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>23.64</v>
+        <v>-10.44</v>
       </c>
       <c r="S14" t="n">
-        <v>1.105</v>
+        <v>15.48</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.45</v>
+        <v>18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>26.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>11.01</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1876,13 +1876,13 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CNTX</t>
+          <t>WVVIP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1921,41 +1921,41 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.43</v>
+        <v>5.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.98</v>
+        <v>18.93</v>
       </c>
       <c r="O15" t="n">
-        <v>33</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4798</v>
+        <v>2.75</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>12.16</v>
+        <v>-45.11</v>
       </c>
       <c r="S15" t="n">
-        <v>0.48</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>12.2</v>
+        <v>239.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0.524</v>
+        <v>2.76</v>
       </c>
       <c r="W15" t="n">
-        <v>0.465</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
@@ -1966,94 +1966,94 @@
         </is>
       </c>
       <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
         <v>1</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.8</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>176.1</v>
+        <v/>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, +0.6pts)   Items: 4.01, 4.02, 9.01 (routine)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.63</v>
+        <v>1.76</v>
       </c>
       <c r="N16" t="n">
-        <v>18.45</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>71.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2599</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-59.55</v>
+        <v>-7.69</v>
       </c>
       <c r="S16" t="n">
-        <v>0.26</v>
+        <v>1.61</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-59.53</v>
+        <v>-8.26</v>
       </c>
       <c r="V16" t="n">
-        <v>0.266</v>
+        <v>1.68</v>
       </c>
       <c r="W16" t="n">
-        <v>0.22</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
@@ -2078,22 +2078,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNYR</t>
+          <t>BDRX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-4.61</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2103,16 +2103,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-6.6</v>
+        <v/>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, -2.4pts)   Item 3.01 (delisting, -6)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2121,37 +2121,37 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.09</v>
+        <v>1.24</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>16.79</v>
       </c>
       <c r="O17" t="n">
-        <v>33.8</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1089</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="R17" t="n">
-        <v>15.61</v>
+        <v>1.63</v>
       </c>
       <c r="S17" t="n">
-        <v>0.082</v>
+        <v>1.48</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-12.95</v>
+        <v>20.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1587</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0912</v>
+        <v>1.1877</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
@@ -2162,39 +2162,39 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>-4</v>
@@ -2205,51 +2205,51 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>382</v>
+        <v>161.9</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, -0.6pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+          <t>2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)   Title: &gt;pmi20260814_8k.htm</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>7.93</v>
       </c>
       <c r="N18" t="n">
-        <v>9.27</v>
+        <v>7.4</v>
       </c>
       <c r="O18" t="n">
-        <v>79.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="P18" t="n">
-        <v>3.9123</v>
+        <v>5.96</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28.48</v>
+        <v>-24.62</v>
       </c>
       <c r="S18" t="n">
-        <v>3.73</v>
+        <v>6.04</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>22.5</v>
+        <v>-23.61</v>
       </c>
       <c r="V18" t="n">
-        <v>6.26</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4</v>
+        <v>3.03</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
@@ -2260,33 +2260,33 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>MCRP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -2299,20 +2299,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2321,37 +2317,37 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3.69</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>34.1</v>
+        <v>37.5</v>
       </c>
       <c r="P19" t="n">
-        <v>4.95</v>
+        <v>1.36</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>34.15</v>
+        <v>27.1</v>
       </c>
       <c r="S19" t="n">
-        <v>4.72</v>
+        <v>1.105</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>27.91</v>
+        <v>3.27</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>4.78</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
@@ -2362,15 +2358,607 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CNTX</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O20" t="n">
+        <v>34</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4798</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="X20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADCT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O21" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9601</v>
+      </c>
+      <c r="X21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NCPL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-18 8-K (material_event, +0.6pts)   Items: 4.01, 4.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N22" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="O22" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-58.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SNYR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-21 8-K (material_event, -2.4pts)   Item 3.01 (delisting, -6)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O23" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-11.64</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="X23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AB19" t="n">
+      <c r="AB23" t="n">
+        <v>-4.61</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E24" t="n">
         <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>526.8</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-18 8-K (material_event, -0.6pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>trend_alignment +1, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="O24" t="n">
+        <v>84</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.9123</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SHMD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="O25" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="X25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>-32</v>
       </c>
     </row>
   </sheetData>
@@ -2384,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2410,7 +2998,7 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="45" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
@@ -2614,22 +3202,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.75</v>
+        <v>10.41</v>
       </c>
       <c r="C2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="D2" t="n">
-        <v>75653328</v>
+        <v>73330552</v>
       </c>
       <c r="E2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H2" t="n">
         <v>0.46</v>
@@ -2638,7 +3226,7 @@
         <v>0.43</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="K2" t="n">
         <v>0.85</v>
@@ -2656,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-19.81</v>
+        <v>-17.35</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
@@ -2671,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-5.4</v>
+        <v>-2.49</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -2685,7 +3273,7 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>29.45</v>
+        <v>28.56</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -2707,23 +3295,23 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>-11.84</v>
+        <v>-11.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>33.34</v>
+        <v>32.13</v>
       </c>
       <c r="AG2" t="n">
-        <v>420.3</v>
+        <v>417.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.07</v>
+        <v>3.73</v>
       </c>
       <c r="AI2" t="n">
-        <v>17.43</v>
+        <v>17.09</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-11.84–$33.34 (ann. vol 420%) | ATR range: $4.07–$17.43</t>
+          <t>1-SD 3mo range: $-11.31–$32.13 (ann. vol 417%) | ATR range: $3.73–$17.09</t>
         </is>
       </c>
     </row>
@@ -2734,28 +3322,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.42</v>
+        <v>5.01</v>
       </c>
       <c r="C3" t="n">
-        <v>18.87</v>
+        <v>18.93</v>
       </c>
       <c r="D3" t="n">
-        <v>1772307</v>
+        <v>1737796</v>
       </c>
       <c r="E3" t="n">
-        <v>89.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
         <v>2.85</v>
       </c>
       <c r="I3" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="J3" t="n">
         <v>2.9</v>
@@ -2776,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-50</v>
+        <v>-45.11</v>
       </c>
       <c r="Q3" t="n">
         <v>2.76</v>
@@ -2791,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>209.09</v>
+        <v>239.32</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -2805,7 +3393,7 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -2827,23 +3415,23 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.56</v>
+        <v>6.82</v>
       </c>
       <c r="AG3" t="n">
-        <v>79.2</v>
+        <v>72.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3.04</v>
+        <v>-3.44</v>
       </c>
       <c r="AI3" t="n">
-        <v>13.87</v>
+        <v>13.46</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.27–$7.56 (ann. vol 79%) | ATR range: $-3.04–$13.87</t>
+          <t>1-SD 3mo range: $3.20–$6.82 (ann. vol 72%) | ATR range: $-3.44–$13.46</t>
         </is>
       </c>
     </row>
@@ -2854,16 +3442,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="C4" t="n">
-        <v>18.45</v>
+        <v>18.83</v>
       </c>
       <c r="D4" t="n">
-        <v>9204228</v>
+        <v>12257870</v>
       </c>
       <c r="E4" t="n">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="F4" t="n">
         <v>0.36</v>
@@ -2896,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-59.55</v>
+        <v>-58.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0.266</v>
@@ -2911,17 +3499,17 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-59.53</v>
+        <v>-58.4</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>6.79</v>
+        <v>6.65</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>6.8x vs 3.4x median — trading at premium</t>
+          <t>6.7x vs 6.7x median — in-line</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -2943,27 +3531,27 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>P/S 6.8x vs 3.4x median — trading at premium | P/B 0.2x vs 0.2x median — in-line | EV/EBITDA -0.4x vs 5.3x median — trading at discount</t>
+          <t>P/S 6.7x vs 6.7x median — in-line | P/B 0.2x vs 0.2x median — in-line | EV/EBITDA -0.4x vs -0.4x median — in-line</t>
         </is>
       </c>
       <c r="AE4" t="n">
         <v>0.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>193.1</v>
+        <v>193.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.02–$1.24 (ann. vol 193%) | ATR range: $0.00–$1.26</t>
+          <t>1-SD 3mo range: $0.02–$1.25 (ann. vol 194%) | ATR range: $-0.03–$1.30</t>
         </is>
       </c>
     </row>
@@ -2974,19 +3562,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="C5" t="n">
-        <v>16.72</v>
+        <v>16.79</v>
       </c>
       <c r="D5" t="n">
-        <v>1206683</v>
+        <v>1132656</v>
       </c>
       <c r="E5" t="n">
-        <v>37.2</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G5" t="n">
         <v>2.02</v>
@@ -3016,7 +3604,7 @@
         <v>848</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q5" t="n">
         <v>1.4</v>
@@ -3031,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>9.630000000000001</v>
+        <v>20.33</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
@@ -3049,7 +3637,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0x vs 0.5x median — trading at discount</t>
+          <t>0.0x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AA5" t="n">
@@ -3063,27 +3651,27 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>P/B 0.0x vs 0.5x median — trading at discount | EV/EBITDA 0.9x vs -0.3x median — trading at discount | Analyst target $10.29</t>
+          <t>P/B 0.0x vs 1.0x median — trading at discount | EV/EBITDA 0.9x vs -0.5x median — trading at discount | Analyst target $10.29</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>167.1</v>
+        <v>166.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.22–$2.48 (ann. vol 167%) | ATR range: $-0.10–$2.80</t>
+          <t>1-SD 3mo range: $0.21–$2.27 (ann. vol 167%) | ATR range: $-0.21–$2.69</t>
         </is>
       </c>
     </row>
@@ -3097,10 +3685,10 @@
         <v>0.18</v>
       </c>
       <c r="C6" t="n">
-        <v>11.49</v>
+        <v>11.56</v>
       </c>
       <c r="D6" t="n">
-        <v>1752415</v>
+        <v>1769662</v>
       </c>
       <c r="E6" t="n">
         <v>31.5</v>
@@ -3136,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>10.92</v>
+        <v>9.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.2349</v>
@@ -3151,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>15.28</v>
+        <v>13.55</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -3165,7 +3753,7 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -3214,28 +3802,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="C7" t="n">
-        <v>9.27</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>30134477</v>
+        <v>41127356</v>
       </c>
       <c r="E7" t="n">
-        <v>79.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="H7" t="n">
-        <v>18.03</v>
+        <v>18.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="J7" t="n">
         <v>11.49</v>
@@ -3256,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>28.48</v>
+        <v>-2.29</v>
       </c>
       <c r="Q7" t="n">
         <v>6.26</v>
@@ -3271,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>22.5</v>
+        <v>-6.84</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.68</v>
+        <v>22.54</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.7x vs 3.0x median — trading at discount</t>
+          <t>22.5x vs 22.5x median — in-line</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>-0.88</v>
+        <v>-1.17</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.9x vs -0.9x median — in-line</t>
+          <t>-1.2x vs -1.2x median — in-line</t>
         </is>
       </c>
       <c r="AA7" t="n">
@@ -3303,27 +3891,27 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>P/S 0.7x vs 3.0x median — trading at discount | P/B -0.9x vs -0.9x median — in-line</t>
+          <t>P/S 22.5x vs 22.5x median — in-line | P/B -1.2x vs -1.2x median — in-line</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>-0.2</v>
+        <v>-0.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.36</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>213</v>
+        <v>221.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.31</v>
+        <v>-0.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.47</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.20–$6.36 (ann. vol 213%) | ATR range: $-1.31–$7.47</t>
+          <t>1-SD 3mo range: $-0.44–$8.45 (ann. vol 222%) | ATR range: $-0.38–$8.39</t>
         </is>
       </c>
     </row>
@@ -3337,13 +3925,13 @@
         <v>0.21</v>
       </c>
       <c r="C8" t="n">
-        <v>8.58</v>
+        <v>9.25</v>
       </c>
       <c r="D8" t="n">
-        <v>767544</v>
+        <v>803994</v>
       </c>
       <c r="E8" t="n">
-        <v>28.4</v>
+        <v>27.3</v>
       </c>
       <c r="F8" t="n">
         <v>0.26</v>
@@ -3376,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.72</v>
+        <v>-2.58</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2397</v>
@@ -3391,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.36</v>
+        <v>-1.17</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -3405,11 +3993,11 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.4x vs 0.5x median — trading at discount</t>
+          <t>-0.3x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AA8" t="n">
@@ -3423,27 +4011,27 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>P/B -0.4x vs 0.5x median — trading at discount | EV/EBITDA -0.5x vs -0.3x median — trading at premium | Analyst target $1.43</t>
+          <t>P/B -0.3x vs 1.0x median — trading at discount | EV/EBITDA -0.5x vs -0.5x median — in-line | Analyst target $1.43</t>
         </is>
       </c>
       <c r="AE8" t="n">
         <v>0.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="AG8" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AI8" t="n">
         <v>0.47</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.10–$0.33 (ann. vol 106%) | ATR range: $-0.04–$0.47</t>
+          <t>1-SD 3mo range: $0.10–$0.32 (ann. vol 106%) | ATR range: $-0.05–$0.47</t>
         </is>
       </c>
     </row>
@@ -3454,28 +4042,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.63</v>
+        <v>7.93</v>
       </c>
       <c r="C9" t="n">
-        <v>7.11</v>
+        <v>7.4</v>
       </c>
       <c r="D9" t="n">
-        <v>21899887</v>
+        <v>23297570</v>
       </c>
       <c r="E9" t="n">
-        <v>75.8</v>
+        <v>76.5</v>
       </c>
       <c r="F9" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="H9" t="n">
         <v>2.08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J9" t="n">
         <v>1.49</v>
@@ -3496,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-21.43</v>
+        <v>-24.62</v>
       </c>
       <c r="Q9" t="n">
         <v>7.5</v>
@@ -3511,25 +4099,25 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-20.37</v>
+        <v>-23.61</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2.5x vs 2.5x median — in-line</t>
+          <t>2.6x vs 2.1x median — trading at premium</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>9.02</v>
+        <v>9.52</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.0x vs 0.5x median — trading at premium</t>
+          <t>9.5x vs 1.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA9" t="n">
@@ -3543,27 +4131,27 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>P/S 2.5x vs 2.5x median — in-line | P/B 9.0x vs 0.5x median — trading at premium | EV/EBITDA -0.9x vs -0.3x median — trading at premium</t>
+          <t>P/S 2.6x vs 2.1x median — trading at premium | P/B 9.5x vs 1.0x median — trading at premium | EV/EBITDA -0.9x vs -0.5x median — trading at premium</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>-19.38</v>
+        <v>-20.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>34.64</v>
+        <v>36.04</v>
       </c>
       <c r="AG9" t="n">
-        <v>708.1</v>
+        <v>708.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>14.44</v>
+        <v>14.75</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-19.38–$34.64 (ann. vol 708%) | ATR range: $0.82–$14.44</t>
+          <t>1-SD 3mo range: $-20.17–$36.04 (ann. vol 708%) | ATR range: $1.12–$14.75</t>
         </is>
       </c>
     </row>
@@ -3577,13 +4165,13 @@
         <v>0.54</v>
       </c>
       <c r="C10" t="n">
-        <v>6.54</v>
+        <v>7.03</v>
       </c>
       <c r="D10" t="n">
-        <v>503237</v>
+        <v>518822</v>
       </c>
       <c r="E10" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="F10" t="n">
         <v>0.73</v>
@@ -3592,7 +4180,7 @@
         <v>0.77</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
         <v>0.77</v>
@@ -3616,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>53.26</v>
+        <v>54.37</v>
       </c>
       <c r="Q10" t="n">
         <v>0.86</v>
@@ -3631,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>19.03</v>
+        <v>19.9</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -3641,7 +4229,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.1x vs 3.4x median — trading at discount</t>
+          <t>0.1x vs 6.7x median — trading at discount</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -3649,7 +4237,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.2x vs 0.2x median — trading at premium</t>
+          <t>0.2x vs 0.2x median — in-line</t>
         </is>
       </c>
       <c r="AA10" t="n">
@@ -3663,7 +4251,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 3.4x median — trading at discount | P/B 0.2x vs 0.2x median — trading at premium | EV/EBITDA 11.1x vs 5.3x median — trading at premium | Analyst target $3.06</t>
+          <t>P/S 0.1x vs 6.7x median — trading at discount | P/B 0.2x vs 0.2x median — in-line | EV/EBITDA 11.1x vs -0.4x median — trading at discount | Analyst target $3.06</t>
         </is>
       </c>
       <c r="AE10" t="n">
@@ -3673,17 +4261,17 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>100.7</v>
+        <v>101</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AI10" t="n">
         <v>1.12</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.27–$0.81 (ann. vol 101%) | ATR range: $-0.04–$1.12</t>
+          <t>1-SD 3mo range: $0.27–$0.81 (ann. vol 101%) | ATR range: $-0.05–$1.12</t>
         </is>
       </c>
     </row>
@@ -3694,16 +4282,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="C11" t="n">
-        <v>4.48</v>
+        <v>4.7</v>
       </c>
       <c r="D11" t="n">
-        <v>670270</v>
+        <v>661432</v>
       </c>
       <c r="E11" t="n">
-        <v>38.8</v>
+        <v>37.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.23</v>
@@ -3712,7 +4300,7 @@
         <v>1.47</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I11" t="n">
         <v>1.41</v>
@@ -3736,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>23.64</v>
+        <v>27.1</v>
       </c>
       <c r="Q11" t="n">
         <v>1.55</v>
@@ -3751,25 +4339,25 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.45</v>
+        <v>3.27</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>245.55</v>
+        <v>238.85</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>245.6x vs 3.0x median — trading at premium</t>
+          <t>238.9x vs 22.5x median — trading at premium</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>17.64</v>
+        <v>17.16</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.6x vs -0.9x median — trading at discount</t>
+          <t>17.2x vs -1.2x median — trading at discount</t>
         </is>
       </c>
       <c r="AA11" t="n">
@@ -3783,27 +4371,27 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>P/S 245.6x vs 3.0x median — trading at premium | P/B 17.6x vs -0.9x median — trading at discount | EV/EBITDA -1.3x vs -0.6x median — trading at premium | Analyst target $8.00</t>
+          <t>P/S 238.9x vs 22.5x median — trading at premium | P/B 17.2x vs -1.2x median — trading at discount | EV/EBITDA -1.3x vs -0.6x median — trading at premium | Analyst target $8.00</t>
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>128.4</v>
+        <v>128.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.39–$1.81 (ann. vol 128%) | ATR range: $-0.03–$2.23</t>
+          <t>1-SD 3mo range: $0.38–$1.76 (ann. vol 128%) | ATR range: $-0.06–$2.20</t>
         </is>
       </c>
     </row>
@@ -3814,28 +4402,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.51</v>
+        <v>3.66</v>
       </c>
       <c r="C12" t="n">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="D12" t="n">
-        <v>801670</v>
+        <v>845013</v>
       </c>
       <c r="E12" t="n">
-        <v>27.5</v>
+        <v>27.9</v>
       </c>
       <c r="F12" t="n">
-        <v>6.31</v>
+        <v>6.32</v>
       </c>
       <c r="G12" t="n">
-        <v>9.25</v>
+        <v>9.26</v>
       </c>
       <c r="H12" t="n">
-        <v>23.86</v>
+        <v>23.87</v>
       </c>
       <c r="I12" t="n">
-        <v>9.65</v>
+        <v>9.66</v>
       </c>
       <c r="J12" t="n">
         <v>28.93</v>
@@ -3856,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>9.27</v>
+        <v>4.78</v>
       </c>
       <c r="Q12" t="n">
         <v>5.15</v>
@@ -3871,25 +4459,25 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>3.56</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>3.0x vs 3.0x median — in-line</t>
+          <t>3.1x vs 22.5x median — trading at discount</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>-6.1</v>
+        <v>-6.37</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>-6.1x vs -0.9x median — trading at premium</t>
+          <t>-6.4x vs -1.2x median — trading at premium</t>
         </is>
       </c>
       <c r="AA12" t="n">
@@ -3903,27 +4491,27 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>P/S 3.0x vs 3.0x median — in-line | P/B -6.1x vs -0.9x median — trading at premium | EV/EBITDA 0.0x vs -0.6x median — trading at discount</t>
+          <t>P/S 3.1x vs 22.5x median — trading at discount | P/B -6.4x vs -1.2x median — trading at premium | EV/EBITDA 0.0x vs -0.6x median — trading at discount</t>
         </is>
       </c>
       <c r="AE12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.09</v>
+        <v>7.39</v>
       </c>
       <c r="AG12" t="n">
-        <v>204.1</v>
+        <v>204</v>
       </c>
       <c r="AH12" t="n">
-        <v>-4.77</v>
+        <v>-4.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.79</v>
+        <v>11.94</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.07–$7.09 (ann. vol 204%) | ATR range: $-4.77–$11.79</t>
+          <t>1-SD 3mo range: $-0.07–$7.39 (ann. vol 204%) | ATR range: $-4.62–$11.94</t>
         </is>
       </c>
     </row>
@@ -3934,19 +4522,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="C13" t="n">
-        <v>3.75</v>
+        <v>4.21</v>
       </c>
       <c r="D13" t="n">
-        <v>1839577</v>
+        <v>1882746</v>
       </c>
       <c r="E13" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="F13" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="G13" t="n">
         <v>5.02</v>
@@ -3955,7 +4543,7 @@
         <v>5.39</v>
       </c>
       <c r="I13" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
       <c r="J13" t="n">
         <v>6.09</v>
@@ -3976,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>34.15</v>
+        <v>35.62</v>
       </c>
       <c r="Q13" t="n">
         <v>5</v>
@@ -3991,25 +4579,25 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>27.91</v>
+        <v>29.32</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3.6x vs 1.8x median — trading at premium</t>
+          <t>3.6x vs 2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>-1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>-1.0x vs -0.4x median — trading at premium</t>
+          <t>-1.0x vs 0.4x median — trading at discount</t>
         </is>
       </c>
       <c r="AA13" t="n">
@@ -4023,65 +4611,65 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P/S 3.6x vs 1.8x median — trading at premium | P/B -1.0x vs -0.4x median — trading at premium | EV/EBITDA -104.6x vs -6.1x median — trading at premium</t>
+          <t>P/S 3.6x vs 2.7x median — trading at premium | P/B -1.0x vs 0.4x median — trading at discount | EV/EBITDA -104.6x vs -4.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF13" t="n">
-        <v>5.99</v>
+        <v>5.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>124.3</v>
+        <v>124.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.5</v>
+        <v>7.48</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.40–$5.99 (ann. vol 124%) | ATR range: $-0.12–$7.50</t>
+          <t>1-SD 3mo range: $1.39–$5.95 (ann. vol 124%) | ATR range: $-0.14–$7.48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CNTX</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="C14" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="D14" t="n">
-        <v>940802</v>
+        <v>1967789</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>25.3</v>
       </c>
       <c r="F14" t="n">
         <v>0.53</v>
       </c>
       <c r="G14" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="H14" t="n">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="J14" t="n">
-        <v>1.67</v>
+        <v>0.96</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4090,118 +4678,118 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4798</v>
+        <v/>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="P14" t="n">
-        <v>12.16</v>
+        <v/>
       </c>
       <c r="Q14" t="n">
-        <v>0.524</v>
+        <v/>
       </c>
       <c r="R14" t="n">
-        <v>0.465</v>
+        <v/>
       </c>
       <c r="S14" t="n">
-        <v>0.48</v>
+        <v>0.4813</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>12.2</v>
+        <v>24.98</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
       </c>
       <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1.0x vs 2.7x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2.1x vs 0.4x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="AB14" t="n">
         <v/>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>N/A — insufficient data</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1.0x vs 0.5x median — trading at premium</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>4.25</v>
-      </c>
       <c r="AC14" t="n">
-        <v/>
+        <v>7.75</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P/B 1.0x vs 0.5x median — trading at premium | EV/EBITDA -0.0x vs -0.3x median — trading at discount | Analyst target $4.25</t>
+          <t>P/S 1.0x vs 2.7x median — trading at discount | P/B 2.1x vs 0.4x median — trading at premium | EV/EBITDA -2.0x vs -4.0x median — trading at discount | Graham # $7.75</t>
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AG14" t="n">
-        <v>118.4</v>
+        <v>160.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.86</v>
+        <v>0.59</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.17–$0.68 (ann. vol 118%) | ATR range: $-0.01–$0.86</t>
+          <t>1-SD 3mo range: $0.08–$0.69 (ann. vol 161%) | ATR range: $0.18–$0.59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GPUS</t>
+          <t>CNTX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="C15" t="n">
-        <v>2.92</v>
+        <v>3.13</v>
       </c>
       <c r="D15" t="n">
-        <v>1894874</v>
+        <v>978511</v>
       </c>
       <c r="E15" t="n">
-        <v>24.7</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
         <v>0.53</v>
       </c>
       <c r="G15" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="H15" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="I15" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="J15" t="n">
-        <v>0.96</v>
+        <v>1.67</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4210,80 +4798,80 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v/>
+        <v>0.4798</v>
       </c>
       <c r="O15" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v/>
+        <v>8.75</v>
       </c>
       <c r="Q15" t="n">
-        <v/>
+        <v>0.524</v>
       </c>
       <c r="R15" t="n">
-        <v/>
+        <v>0.465</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4813</v>
+        <v>0.48</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>26.82</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v/>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>1.0x vs 1.8x median — trading at discount</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.1x vs -0.4x median — trading at discount</t>
+          <t>1.1x vs 1.0x median — in-line</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>-1.96</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC15" t="n">
         <v/>
       </c>
-      <c r="AC15" t="n">
-        <v>7.75</v>
-      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>P/S 1.0x vs 1.8x median — trading at discount | P/B 2.1x vs -0.4x median — trading at discount | EV/EBITDA -2.0x vs -6.1x median — trading at discount | Graham # $7.75</t>
+          <t>P/B 1.1x vs 1.0x median — in-line | EV/EBITDA -0.0x vs -0.5x median — trading at discount | Analyst target $4.25</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>161</v>
+        <v>118.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.07–$0.68 (ann. vol 161%) | ATR range: $0.17–$0.58</t>
+          <t>1-SD 3mo range: $0.18–$0.70 (ann. vol 118%) | ATR range: $0.01–$0.87</t>
         </is>
       </c>
     </row>
@@ -4297,13 +4885,13 @@
         <v>0.09</v>
       </c>
       <c r="C16" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="D16" t="n">
-        <v>1285208</v>
+        <v>1268465</v>
       </c>
       <c r="E16" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
       <c r="F16" t="n">
         <v>0.13</v>
@@ -4336,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15.61</v>
+        <v>17.35</v>
       </c>
       <c r="Q16" t="n">
         <v>0.1587</v>
@@ -4351,17 +4939,17 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-12.95</v>
+        <v>-11.64</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v/>
+        <v>0.05</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>0.0x vs 2.1x median — trading at discount</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -4369,7 +4957,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>-0.0x vs 0.5x median — trading at discount</t>
+          <t>-0.0x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AA16" t="n">
@@ -4383,7 +4971,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>P/B -0.0x vs 0.5x median — trading at discount | EV/EBITDA -2.7x vs -0.3x median — trading at premium | Analyst target $3.75</t>
+          <t>P/S 0.0x vs 2.1x median — trading at discount | P/B -0.0x vs 1.0x median — trading at discount | EV/EBITDA -2.7x vs -0.5x median — trading at premium | Analyst target $3.75</t>
         </is>
       </c>
       <c r="AE16" t="n">
@@ -4393,7 +4981,7 @@
         <v>0.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>107.3</v>
+        <v>107.5</v>
       </c>
       <c r="AH16" t="n">
         <v>-0.11</v>
@@ -4403,7 +4991,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.04–$0.14 (ann. vol 107%) | ATR range: $-0.11–$0.29</t>
+          <t>1-SD 3mo range: $0.04–$0.14 (ann. vol 108%) | ATR range: $-0.11–$0.29</t>
         </is>
       </c>
     </row>
@@ -4414,19 +5002,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.27</v>
+        <v>13.05</v>
       </c>
       <c r="C17" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="D17" t="n">
-        <v>47919073</v>
+        <v>47362693</v>
       </c>
       <c r="E17" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
-        <v>26.09</v>
+        <v>26.07</v>
       </c>
       <c r="G17" t="n">
         <v>19.63</v>
@@ -4435,7 +5023,7 @@
         <v>8.58</v>
       </c>
       <c r="I17" t="n">
-        <v>15.97</v>
+        <v>15.96</v>
       </c>
       <c r="J17" t="n">
         <v>5.76</v>
@@ -4456,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-11.67</v>
+        <v>-10.44</v>
       </c>
       <c r="Q17" t="n">
         <v>26.75</v>
@@ -4471,25 +5059,25 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>16.39</v>
+        <v>18</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>1.8x vs 1.8x median — in-line</t>
+          <t>1.7x vs 2.7x median — trading at discount</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>-0.4x vs -0.4x median — in-line</t>
+          <t>-0.4x vs 0.4x median — trading at discount</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -4503,27 +5091,27 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>P/S 1.8x vs 1.8x median — in-line | P/B -0.4x vs -0.4x median — in-line | EV/EBITDA -6.1x vs -6.1x median — in-line | Analyst target $108.75</t>
+          <t>P/S 1.7x vs 2.7x median — trading at discount | P/B -0.4x vs 0.4x median — trading at discount | EV/EBITDA -6.1x vs -4.0x median — trading at premium | Analyst target $108.75</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>-22.33</v>
+        <v>-21.96</v>
       </c>
       <c r="AF17" t="n">
-        <v>48.87</v>
+        <v>48.06</v>
       </c>
       <c r="AG17" t="n">
-        <v>536.6</v>
+        <v>536.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>-29.27</v>
+        <v>-29.49</v>
       </c>
       <c r="AI17" t="n">
-        <v>55.81</v>
+        <v>55.59</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-22.33–$48.87 (ann. vol 537%) | ATR range: $-29.27–$55.81</t>
+          <t>1-SD 3mo range: $-21.96–$48.06 (ann. vol 536%) | ATR range: $-29.49–$55.59</t>
         </is>
       </c>
     </row>
@@ -4534,22 +5122,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.56</v>
+        <v>7.77</v>
       </c>
       <c r="C18" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="D18" t="n">
-        <v>1139787</v>
+        <v>1174406</v>
       </c>
       <c r="E18" t="n">
-        <v>25.5</v>
+        <v>28.7</v>
       </c>
       <c r="F18" t="n">
-        <v>9.43</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="H18" t="n">
         <v>10.27</v>
@@ -4576,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>23.02</v>
+        <v>19.69</v>
       </c>
       <c r="Q18" t="n">
         <v>11</v>
@@ -4591,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.59</v>
+        <v>-1.16</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
@@ -4605,11 +5193,11 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>-18.31</v>
+        <v>-18.81</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>-18.3x vs 0.2x median — trading at discount</t>
+          <t>-18.8x vs 0.2x median — trading at discount</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -4623,27 +5211,27 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/B -18.3x vs 0.2x median — trading at discount | Analyst target $17.00</t>
+          <t>P/B -18.8x vs 0.2x median — trading at discount | Analyst target $17.00</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="AF18" t="n">
-        <v>9</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AG18" t="n">
-        <v>38.1</v>
+        <v>38.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="AI18" t="n">
-        <v>11.77</v>
+        <v>11.98</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $6.12–$9.00 (ann. vol 38%) | ATR range: $3.35–$11.77</t>
+          <t>1-SD 3mo range: $6.26–$9.28 (ann. vol 39%) | ATR range: $3.56–$11.98</t>
         </is>
       </c>
     </row>
@@ -4654,19 +5242,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="C19" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="D19" t="n">
-        <v>101410076</v>
+        <v>101694828</v>
       </c>
       <c r="E19" t="n">
         <v>54.4</v>
       </c>
       <c r="F19" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="G19" t="n">
         <v>6.86</v>
@@ -4696,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>44.36</v>
+        <v>43.3</v>
       </c>
       <c r="Q19" t="n">
         <v>16.41</v>
@@ -4711,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.87</v>
+        <v>-1.6</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
@@ -4725,11 +5313,11 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.4x vs 0.5x median — trading at premium</t>
+          <t>1.4x vs 1.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -4743,27 +5331,747 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>P/B 1.4x vs 0.5x median — trading at premium | EV/EBITDA -0.1x vs -0.3x median — trading at discount | Analyst target $58.80</t>
+          <t>P/B 1.4x vs 1.0x median — trading at premium | EV/EBITDA -0.1x vs -0.5x median — trading at discount | Analyst target $58.80</t>
         </is>
       </c>
       <c r="AE19" t="n">
         <v>-0.59</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.83</v>
+        <v>16.8</v>
       </c>
       <c r="AG19" t="n">
         <v>214.6</v>
       </c>
       <c r="AH19" t="n">
-        <v>-3.88</v>
+        <v>-3.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>20.12</v>
+        <v>20.1</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.59–$16.83 (ann. vol 215%) | ATR range: $-3.88–$20.12</t>
+          <t>1-SD 3mo range: $-0.59–$16.80 (ann. vol 215%) | ATR range: $-3.90–$20.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BMEA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2020511</v>
+      </c>
+      <c r="E20" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v/>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10.5x vs 1.0x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v/>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>P/B 10.5x vs 1.0x median — trading at premium | EV/EBITDA -1.5x vs -0.5x median — trading at premium | Analyst target $6.50</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.96–$2.56 (ann. vol 91%) | ATR range: $0.95–$2.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADCT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1370497</v>
+      </c>
+      <c r="E21" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.9601</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>1.6x vs 2.1x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>-0.5x vs 1.0x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v/>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>P/S 1.6x vs 2.1x median — trading at discount | P/B -0.5x vs 1.0x median — trading at discount | EV/EBITDA -3.7x vs -0.5x median — trading at premium | Analyst target $3.33</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.43–$1.52 (ann. vol 112%) | ATR range: $0.28–$1.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DTCX</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D22" t="n">
+        <v>557624</v>
+      </c>
+      <c r="E22" t="n">
+        <v>74</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.8201</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>12.5x vs 6.7x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1.5x vs 0.2x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>-15.05</v>
+      </c>
+      <c r="AB22" t="n">
+        <v/>
+      </c>
+      <c r="AC22" t="n">
+        <v/>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>P/S 12.5x vs 6.7x median — trading at premium | P/B 1.5x vs 0.2x median — trading at premium | EV/EBITDA -15.1x vs -0.4x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $1.26–$4.32 (ann. vol 109%) | ATR range: $1.47–$4.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9504150</v>
+      </c>
+      <c r="E23" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.6297</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-14</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.7254</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.6781</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>79.4x vs 2.7x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1.1x vs 0.4x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>P/S 79.4x vs 2.7x median — trading at premium | P/B 1.1x vs 0.4x median — trading at premium | EV/EBITDA -1.0x vs -4.0x median — trading at discount | Analyst target $2.00 | Graham # $1.63</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.81–$2.99 (ann. vol 114%) | ATR range: $0.97–$2.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TNXP</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6202657</v>
+      </c>
+      <c r="E24" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="J24" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="R24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>8.0x vs 2.1x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>0.8x vs 1.0x median — in-line</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v/>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>P/S 8.0x vs 2.1x median — trading at premium | P/B 0.8x vs 1.0x median — in-line | EV/EBITDA -0.2x vs -0.5x median — trading at discount | Analyst target $42.40</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>73</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $8.59–$18.45 (ann. vol 73%) | ATR range: $6.48–$20.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AVXL</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3212812</v>
+      </c>
+      <c r="E25" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.1564</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-11.59</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v/>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2.7x vs 1.0x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v/>
+      </c>
+      <c r="AB25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="n">
+        <v/>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>P/B 2.7x vs 1.0x median — trading at premium | Analyst target $20.00</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $1.88–$5.28 (ann. vol 95%) | ATR range: $2.05–$5.11</t>
         </is>
       </c>
     </row>
@@ -4778,7 +6086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5836,6 +7144,297 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DTCX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>8-K/A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0001493152-26-039796</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>form8-ka.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DTCX</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0001493152-26-039786</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>form8-k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0001213900-26-093255</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ea0303279-8k_richtech.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TNXP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0001999371-26-018494</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>xslF345X06/bagger-form4.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TNXP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v/>
+      </c>
+      <c r="F30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0001493152-26-039000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>form8-k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AVXL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0001731122-26-001143</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>e7897_8-k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AVXL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0001731122-26-001078</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>e7862_8k.htm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D2" t="n">
         <v>3.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>-4.5</v>
+        <v>-3.8</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="N2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="O2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" t="n">
         <v>2.8201</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>0.36</v>
       </c>
       <c r="S2" t="n">
         <v>2.91</v>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>4.3</v>
+        <v>3.56</v>
       </c>
       <c r="V2" t="n">
         <v>2.92</v>
@@ -688,21 +688,21 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v/>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TNXP</t>
+          <t>AVXL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.16</v>
+        <v>6.54</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -731,12 +731,12 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-24 4 (insider_buy, +2.7pts) | 2026-08-18 8-K (material_event, +0.3pts)   Item 5.02 (officer_departure, -1)</t>
+          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.4pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -745,37 +745,37 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>13.52</v>
+        <v>3.51</v>
       </c>
       <c r="N3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="O3" t="n">
-        <v>64.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="P3" t="n">
-        <v>12.75</v>
+        <v>3.1564</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-5.76</v>
+        <v>-10.2</v>
       </c>
       <c r="S3" t="n">
-        <v>12.44</v>
+        <v>3.33</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.06</v>
+        <v>-5.26</v>
       </c>
       <c r="V3" t="n">
-        <v>12.9</v>
+        <v>3.42</v>
       </c>
       <c r="W3" t="n">
-        <v>12.2</v>
+        <v>3.07</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
@@ -786,21 +786,21 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v/>
+        <v>6.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVXL</t>
+          <t>TNXP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,71 +809,71 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Moved</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.4pts)   Items: 7.01, 9.01 (routine)</t>
+          <t>2026-08-24 4 (insider_buy, +2.7pts) | 2026-08-18 8-K (material_event, +0.3pts)   Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3.58</v>
+        <v>13.6</v>
       </c>
       <c r="N4" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="O4" t="n">
-        <v>64.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1564</v>
+        <v>12.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-11.59</v>
+        <v>-6.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.33</v>
+        <v>12.44</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-6.72</v>
+        <v>-8.5</v>
       </c>
       <c r="V4" t="n">
-        <v>3.42</v>
+        <v>12.9</v>
       </c>
       <c r="W4" t="n">
-        <v>3.07</v>
+        <v>12.2</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v/>
+        <v>7.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FNGR</t>
+          <t>IFRX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -907,71 +907,71 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-41.6</v>
+        <v/>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 8.01, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.8pts)   Item 1.01 (entry_agreement, +3) | Item 2.03 (direct_obligation, -1) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)   Title: Entry into a Material Definitive Agreement.</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +4, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.18</v>
+        <v>2.15</v>
       </c>
       <c r="N5" t="n">
-        <v>11.56</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
-        <v>31.5</v>
+        <v>61.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0.196</v>
+        <v>1.9612</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>9.25</v>
+        <v>-8.99</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2037</v>
+        <v>2.1345</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>13.55</v>
+        <v>-0.95</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2349</v>
+        <v>2.12</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1951</v>
+        <v>1.9505</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>new</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.6</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GPUS</t>
+          <t>DHX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1005,71 +1005,71 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1.03</v>
       </c>
       <c r="F6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-17.7</v>
+        <v/>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-20 4/A (insider_buy, +1.5pts) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 7.01 (routine)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +4, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.38</v>
+        <v>4.42</v>
       </c>
       <c r="N6" t="n">
-        <v>3.16</v>
+        <v>1.54</v>
       </c>
       <c r="O6" t="n">
-        <v>25.3</v>
+        <v>61.9</v>
       </c>
       <c r="P6" t="n">
-        <v/>
+        <v>4.22</v>
       </c>
       <c r="Q6" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v/>
+        <v>-4.52</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4813</v>
+        <v>4.2265</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>24.98</v>
+        <v>-4.38</v>
       </c>
       <c r="V6" t="n">
-        <v/>
+        <v>4.2248</v>
       </c>
       <c r="W6" t="n">
-        <v/>
+        <v>4.11</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
@@ -1080,21 +1080,21 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>new</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.42</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRML</t>
+          <t>FNGR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1123,55 +1123,51 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>-41</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-25 4 (insider_buy, +3.0pts) | 2026-08-24 8-K (material_event, +1.8pts)   Items: 9.01 (routine) | 2026-08-24 424B5 (dilution_risk, -3.6pts)</t>
+          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 8.01, 9.01 (routine) | 2026-08-17 8-K (material_event, +0.8pts)   Item 1.01 (entry_agreement, +3) | Item 2.03 (direct_obligation, -1) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)   Title: Entry into a Material Definitive Agreement.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>trend_alignment +4, golden_cross +2, rsi_overbought -2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>10.41</v>
+        <v>0.18</v>
       </c>
       <c r="N7" t="n">
-        <v>0.28</v>
+        <v>11.6</v>
       </c>
       <c r="O7" t="n">
-        <v>99.09999999999999</v>
+        <v>31.7</v>
       </c>
       <c r="P7" t="n">
-        <v>8.619999999999999</v>
+        <v>0.196</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-17.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>10.17</v>
+        <v>0.2037</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.49</v>
+        <v>14.12</v>
       </c>
       <c r="V7" t="n">
-        <v>10.41</v>
+        <v>0.2349</v>
       </c>
       <c r="W7" t="n">
-        <v>8.119999999999999</v>
+        <v>0.1951</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1190,13 +1186,13 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1205,16 +1201,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.09</v>
+        <v>5.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1225,51 +1221,51 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, +1.0pts)   Item 5.02 (officer_departure, -1)</t>
+          <t>2026-08-20 4/A (insider_buy, +1.5pts) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 7.01 (routine)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.64</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
-        <v>59.5</v>
+        <v>26.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6297</v>
+        <v/>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="R8" t="n">
-        <v>-14</v>
+        <v/>
       </c>
       <c r="S8" t="n">
-        <v>1.6781</v>
+        <v>0.4813</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-11.45</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7254</v>
+        <v/>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v/>
       </c>
       <c r="X8" t="b">
         <v>1</v>
@@ -1280,21 +1276,21 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v/>
+        <v>5.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLQT</t>
+          <t>GRML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1303,17 +1299,17 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -1325,49 +1321,53 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)   Title: &gt;slqt-20260825</t>
+          <t>2026-08-25 4 (insider_buy, +3.0pts) | 2026-08-24 8-K (material_event, +1.8pts)   Items: 9.01 (routine) | 2026-08-24 424B5 (dilution_risk, -3.6pts)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +4, golden_cross +2, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.54</v>
+        <v>10.6</v>
       </c>
       <c r="N9" t="n">
-        <v>7.03</v>
+        <v>0.29</v>
       </c>
       <c r="O9" t="n">
-        <v>31.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8279</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>54.37</v>
+        <v>-18.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0.643</v>
+        <v>10.17</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>19.9</v>
+        <v>-3.61</v>
       </c>
       <c r="V9" t="n">
-        <v>0.86</v>
+        <v>10.41</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7403</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1386,31 +1386,31 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HVII</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.37</v>
+        <v>4.6</v>
       </c>
       <c r="D10" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1421,51 +1421,51 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-5</v>
+        <v>6.1</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, +1.8pts)   Items: 5.07, 8.01 (routine) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
+          <t>2026-08-17 4 (insider_buy, +0.6pts)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>7.77</v>
+        <v>11.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.34</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>28.7</v>
+        <v>69</v>
       </c>
       <c r="P10" t="n">
-        <v>9.300000000000001</v>
+        <v>10.74</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>19.69</v>
+        <v>-3.55</v>
       </c>
       <c r="S10" t="n">
-        <v>7.68</v>
+        <v>10.74</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.16</v>
+        <v>-3.55</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="W10" t="n">
-        <v>6.09</v>
+        <v>9.84</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
@@ -1476,39 +1476,39 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>new</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.29</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>HVII</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4.44</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="F11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1519,51 +1519,51 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-15.9</v>
+        <v>-3.2</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 8.01, 9.01 (routine)</t>
+          <t>2026-08-24 8-K (material_event, +1.8pts)   Items: 5.07, 8.01 (routine) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3.66</v>
+        <v>7.92</v>
       </c>
       <c r="N11" t="n">
-        <v>4.52</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>27.9</v>
+        <v>30.9</v>
       </c>
       <c r="P11" t="n">
-        <v>3.835</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.78</v>
+        <v>17.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7902</v>
+        <v>7.68</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.56</v>
+        <v>-3.03</v>
       </c>
       <c r="V11" t="n">
-        <v>5.15</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>3.7</v>
+        <v>6.09</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
@@ -1574,36 +1574,36 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMIX</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4.27</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1613,16 +1613,16 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-25 8-K (material_event, +1.0pts)   Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1631,37 +1631,37 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>8.1</v>
+        <v>1.88</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
-        <v>54.4</v>
+        <v>58.8</v>
       </c>
       <c r="P12" t="n">
-        <v>11.65</v>
+        <v>1.6297</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>43.3</v>
+        <v>-13.54</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>1.6781</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6</v>
+        <v>-10.98</v>
       </c>
       <c r="V12" t="n">
-        <v>16.41</v>
+        <v>1.7254</v>
       </c>
       <c r="W12" t="n">
-        <v>5.17</v>
+        <v>1.6</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
@@ -1676,35 +1676,35 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>SLQT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1715,51 +1715,51 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-21 4 (insider_buy, +1.8pts)</t>
+          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)   Title: &gt;slqt-20260825</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.25</v>
+        <v>7.2</v>
       </c>
       <c r="O13" t="n">
-        <v>27.3</v>
+        <v>31.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2</v>
+        <v>0.8279</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.58</v>
+        <v>52.89</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2029</v>
+        <v>0.643</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.17</v>
+        <v>18.74</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2397</v>
+        <v>0.86</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1845</v>
+        <v>0.7403</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DFNS</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.6</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1813,51 +1813,51 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-57.9</v>
+        <v>-16.6</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, -2.0pts)   Item 3.01 (delisting, -6) | 2026-08-17 8-K (material_event, +0.4pts)   Items: 8.01 (routine)</t>
+          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 8.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>13.05</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>4.58</v>
       </c>
       <c r="O14" t="n">
-        <v>42</v>
+        <v>27.8</v>
       </c>
       <c r="P14" t="n">
-        <v>11.7482</v>
+        <v>3.835</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-10.44</v>
+        <v>5.65</v>
       </c>
       <c r="S14" t="n">
-        <v>15.48</v>
+        <v>3.7902</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>18</v>
+        <v>4.41</v>
       </c>
       <c r="V14" t="n">
-        <v>26.75</v>
+        <v>5.15</v>
       </c>
       <c r="W14" t="n">
-        <v>11.01</v>
+        <v>3.7</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WVVIP</t>
+          <t>AMIX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1921,41 +1921,41 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>5.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>18.93</v>
+        <v>1.98</v>
       </c>
       <c r="O15" t="n">
-        <v>87.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.75</v>
+        <v>11.65</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-45.11</v>
+        <v>41.56</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>239.32</v>
+        <v>-2.79</v>
       </c>
       <c r="V15" t="n">
-        <v>2.76</v>
+        <v>16.41</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>5.17</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BMEA</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1989,71 +1989,71 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v/>
+        <v>-0.1</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 4 (insider_buy, +1.8pts)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.76</v>
+        <v>0.19</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>9.59</v>
       </c>
       <c r="O16" t="n">
-        <v>83.2</v>
+        <v>21.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.62</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-7.69</v>
+        <v>4.55</v>
       </c>
       <c r="S16" t="n">
-        <v>1.61</v>
+        <v>0.2029</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-8.26</v>
+        <v>6.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.68</v>
+        <v>0.2397</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>0.1845</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v/>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BDRX</t>
+          <t>DFNS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2087,71 +2087,71 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v/>
+        <v>-56.1</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-20 8-K (material_event, -2.0pts)   Item 3.01 (delisting, -6) | 2026-08-17 8-K (material_event, +0.4pts)   Items: 8.01 (routine)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +3, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.24</v>
+        <v>13.61</v>
       </c>
       <c r="N17" t="n">
-        <v>16.79</v>
+        <v>2.87</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>42.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>11.7482</v>
       </c>
       <c r="Q17" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>-13.84</v>
       </c>
       <c r="S17" t="n">
-        <v>1.48</v>
+        <v>15.48</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>20.33</v>
+        <v>13.52</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>26.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1877</v>
+        <v>11.01</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
@@ -2162,21 +2162,21 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>WVVIP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2185,82 +2185,82 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>161.9</v>
+        <v/>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)   Title: &gt;pmi20260814_8k.htm</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_overbought -2</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>7.93</v>
+        <v>5.21</v>
       </c>
       <c r="N18" t="n">
-        <v>7.4</v>
+        <v>18.94</v>
       </c>
       <c r="O18" t="n">
-        <v>76.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>5.96</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-24.62</v>
+        <v>-47.22</v>
       </c>
       <c r="S18" t="n">
-        <v>6.04</v>
+        <v>17</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-23.61</v>
+        <v>226.3</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>2.76</v>
       </c>
       <c r="W18" t="n">
-        <v>3.03</v>
+        <v>2.6</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MCRP</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2313,52 +2313,52 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.75</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>2.43</v>
       </c>
       <c r="O19" t="n">
-        <v>37.5</v>
+        <v>83.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>27.1</v>
+        <v>-7.43</v>
       </c>
       <c r="S19" t="n">
-        <v>1.105</v>
+        <v>1.61</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.27</v>
+        <v>-8</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CNTX</t>
+          <t>CTXR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2381,71 +2381,71 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v/>
+        <v>3.3</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 8-K (material_event, -2.4pts)   Item 3.01 (delisting, -6)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="N20" t="n">
-        <v>3.13</v>
+        <v>1.68</v>
       </c>
       <c r="O20" t="n">
-        <v>34</v>
+        <v>50.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4798</v>
+        <v>0.5851</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8.75</v>
+        <v>-5.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>8.789999999999999</v>
+        <v>-6.18</v>
       </c>
       <c r="V20" t="n">
-        <v>0.524</v>
+        <v>0.6449</v>
       </c>
       <c r="W20" t="n">
-        <v>0.465</v>
+        <v>0.5733</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
@@ -2456,21 +2456,21 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>new</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ADCT</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2482,177 +2482,177 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v/>
+        <v>199.3</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)   Title: &gt;pmi20260814_8k.htm</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.97</v>
+        <v>9.07</v>
       </c>
       <c r="N21" t="n">
-        <v>1.82</v>
+        <v>7.98</v>
       </c>
       <c r="O21" t="n">
-        <v>38.1</v>
+        <v>79</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9743000000000001</v>
+        <v>5.96</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.11</v>
+        <v>-34.61</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9792999999999999</v>
+        <v>6.04</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.63</v>
+        <v>-33.74</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9601</v>
+        <v>3.03</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>MCRP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>178.6</v>
+        <v/>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, +0.6pts)   Items: 4.01, 4.02, 9.01 (routine)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_mild_high +1</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>18.83</v>
+        <v>4.78</v>
       </c>
       <c r="O22" t="n">
-        <v>71.7</v>
+        <v>36.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2599</v>
+        <v>1.36</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-58.42</v>
+        <v>29.52</v>
       </c>
       <c r="S22" t="n">
-        <v>0.26</v>
+        <v>1.105</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-58.4</v>
+        <v>5.24</v>
       </c>
       <c r="V22" t="n">
-        <v>0.266</v>
+        <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>0.22</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2660,28 +2660,28 @@
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SNYR</t>
+          <t>CNTX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-4.69</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2691,16 +2691,16 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>-8.1</v>
+        <v/>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, -2.4pts)   Item 3.01 (delisting, -6)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2709,37 +2709,37 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.93</v>
+        <v>3.21</v>
       </c>
       <c r="O23" t="n">
-        <v>33.5</v>
+        <v>34.4</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1089</v>
+        <v>0.4798</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>17.35</v>
+        <v>7.48</v>
       </c>
       <c r="S23" t="n">
-        <v>0.082</v>
+        <v>0.48</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-11.64</v>
+        <v>7.53</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1587</v>
+        <v>0.524</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0912</v>
+        <v>0.465</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
@@ -2750,105 +2750,105 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>-4.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>ADCT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1.31</v>
       </c>
       <c r="F24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>526.8</v>
+        <v/>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, -0.6pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>4.01</v>
+        <v>0.97</v>
       </c>
       <c r="N24" t="n">
-        <v>9.779999999999999</v>
+        <v>1.97</v>
       </c>
       <c r="O24" t="n">
-        <v>84</v>
+        <v>37.8</v>
       </c>
       <c r="P24" t="n">
-        <v>3.9123</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.29</v>
+        <v>0.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.73</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.84</v>
+        <v>0.9</v>
       </c>
       <c r="V24" t="n">
-        <v>6.26</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>0.4</v>
+        <v>0.9601</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2871,93 +2871,681 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-32</v>
+        <v>-0.8</v>
       </c>
       <c r="D25" t="n">
-        <v>-16</v>
+        <v>0.6</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>172.9</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts)</t>
+          <t>2026-08-18 8-K (material_event, +0.6pts)   Items: 4.01, 4.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3.67</v>
+        <v>0.62</v>
       </c>
       <c r="N25" t="n">
-        <v>4.21</v>
+        <v>18.91</v>
       </c>
       <c r="O25" t="n">
-        <v>33.9</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>4.95</v>
+        <v>0.2599</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>35.62</v>
+        <v>-58.21</v>
       </c>
       <c r="S25" t="n">
-        <v>4.72</v>
+        <v>0.26</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>29.32</v>
+        <v>-58.19</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>0.266</v>
       </c>
       <c r="W25" t="n">
-        <v>4.78</v>
+        <v>0.22</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BDRX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v/>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N26" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="O26" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>848</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="X26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>falling</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OLOX</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O27" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.7597</v>
+      </c>
+      <c r="X27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-17 4 (insider_buy, +0.6pts) | 2026-08-17 4 (insider_buy, +0.6pts) | 2026-08-17 4 (insider_other, +0.0pts)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>trend_alignment +3, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O28" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="W28" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="X28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SNYR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-21 8-K (material_event, -2.4pts)   Item 3.01 (delisting, -6)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O29" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-11.73</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="X29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>falling</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>452.4</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-18 8-K (material_event, -0.6pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>trend_alignment +1, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="O30" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3.9123</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Z25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA25" t="inlineStr">
+      <c r="Z30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="AB25" t="n">
+      <c r="AB30" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SHMD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts) | 2026-08-25 424B3 (dilution_risk, -4.0pts)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="O31" t="n">
+        <v>32</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="X31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -2972,7 +3560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ25"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2997,7 +3585,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
     <col width="45" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="45" customWidth="1" min="26" max="26"/>
@@ -3202,22 +3790,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.41</v>
+        <v>10.6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="D2" t="n">
-        <v>73330552</v>
+        <v>74672445</v>
       </c>
       <c r="E2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H2" t="n">
         <v>0.46</v>
@@ -3244,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-17.35</v>
+        <v>-18.3</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
@@ -3259,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.49</v>
+        <v>-3.61</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -3273,7 +3861,7 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>28.56</v>
+        <v>28.91</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -3295,23 +3883,23 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>-11.31</v>
+        <v>-11.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>32.13</v>
+        <v>32.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>417.2</v>
+        <v>418.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.73</v>
+        <v>3.91</v>
       </c>
       <c r="AI2" t="n">
-        <v>17.09</v>
+        <v>17.28</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-11.31–$32.13 (ann. vol 417%) | ATR range: $3.73–$17.09</t>
+          <t>1-SD 3mo range: $-11.60–$32.79 (ann. vol 419%) | ATR range: $3.91–$17.28</t>
         </is>
       </c>
     </row>
@@ -3322,22 +3910,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.01</v>
+        <v>5.21</v>
       </c>
       <c r="C3" t="n">
-        <v>18.93</v>
+        <v>18.94</v>
       </c>
       <c r="D3" t="n">
-        <v>1737796</v>
+        <v>1830599</v>
       </c>
       <c r="E3" t="n">
-        <v>87.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="H3" t="n">
         <v>2.85</v>
@@ -3364,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-45.11</v>
+        <v>-47.22</v>
       </c>
       <c r="Q3" t="n">
         <v>2.76</v>
@@ -3379,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>239.32</v>
+        <v>226.3</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -3393,7 +3981,7 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -3415,23 +4003,23 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AF3" t="n">
-        <v>6.82</v>
+        <v>7.18</v>
       </c>
       <c r="AG3" t="n">
-        <v>72.2</v>
+        <v>75.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3.44</v>
+        <v>-3.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>13.46</v>
+        <v>13.66</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.20–$6.82 (ann. vol 72%) | ATR range: $-3.44–$13.46</t>
+          <t>1-SD 3mo range: $3.24–$7.18 (ann. vol 76%) | ATR range: $-3.24–$13.66</t>
         </is>
       </c>
     </row>
@@ -3442,16 +4030,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="C4" t="n">
-        <v>18.83</v>
+        <v>18.91</v>
       </c>
       <c r="D4" t="n">
-        <v>12257870</v>
+        <v>12928945</v>
       </c>
       <c r="E4" t="n">
-        <v>71.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F4" t="n">
         <v>0.36</v>
@@ -3484,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-58.42</v>
+        <v>-58.21</v>
       </c>
       <c r="Q4" t="n">
         <v>0.266</v>
@@ -3499,17 +4087,17 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-58.4</v>
+        <v>-58.19</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>6.65</v>
+        <v>6.58</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>6.7x vs 6.7x median — in-line</t>
+          <t>6.6x vs 6.6x median — in-line</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -3531,27 +4119,27 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>P/S 6.7x vs 6.7x median — in-line | P/B 0.2x vs 0.2x median — in-line | EV/EBITDA -0.4x vs -0.4x median — in-line</t>
+          <t>P/S 6.6x vs 6.6x median — in-line | P/B 0.2x vs 0.2x median — in-line | EV/EBITDA -0.4x vs -0.4x median — in-line</t>
         </is>
       </c>
       <c r="AE4" t="n">
         <v>0.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>193.6</v>
+        <v>192.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.02–$1.25 (ann. vol 194%) | ATR range: $-0.03–$1.30</t>
+          <t>1-SD 3mo range: $0.02–$1.22 (ann. vol 193%) | ATR range: $-0.04–$1.29</t>
         </is>
       </c>
     </row>
@@ -3562,16 +4150,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="C5" t="n">
-        <v>16.79</v>
+        <v>16.82</v>
       </c>
       <c r="D5" t="n">
-        <v>1132656</v>
+        <v>1121049</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="F5" t="n">
         <v>1.48</v>
@@ -3604,7 +4192,7 @@
         <v>848</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>1.4</v>
@@ -3619,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>20.33</v>
+        <v>18.4</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
@@ -3637,7 +4225,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0x vs 1.0x median — trading at discount</t>
+          <t>0.0x vs 1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA5" t="n">
@@ -3651,27 +4239,27 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>P/B 0.0x vs 1.0x median — trading at discount | EV/EBITDA 0.9x vs -0.5x median — trading at discount | Analyst target $10.29</t>
+          <t>P/B 0.0x vs 1.1x median — trading at discount | EV/EBITDA 0.9x vs -0.9x median — trading at discount | Analyst target $10.29</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AG5" t="n">
         <v>166.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.21–$2.27 (ann. vol 167%) | ATR range: $-0.21–$2.69</t>
+          <t>1-SD 3mo range: $0.20–$2.23 (ann. vol 167%) | ATR range: $-0.24–$2.67</t>
         </is>
       </c>
     </row>
@@ -3685,13 +4273,13 @@
         <v>0.18</v>
       </c>
       <c r="C6" t="n">
-        <v>11.56</v>
+        <v>11.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1769662</v>
+        <v>1795952</v>
       </c>
       <c r="E6" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="F6" t="n">
         <v>0.26</v>
@@ -3724,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>9.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>0.2349</v>
@@ -3739,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>13.55</v>
+        <v>14.12</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
@@ -3778,20 +4366,20 @@
         <v>0.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="AG6" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="AI6" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.08–$0.27 (ann. vol 108%) | ATR range: $-0.21–$0.56</t>
+          <t>1-SD 3mo range: $0.08–$0.28 (ann. vol 108%) | ATR range: $-0.20–$0.56</t>
         </is>
       </c>
     </row>
@@ -3802,28 +4390,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.01</v>
+        <v>3.53</v>
       </c>
       <c r="C7" t="n">
-        <v>9.779999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="D7" t="n">
-        <v>41127356</v>
+        <v>37633803</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H7" t="n">
-        <v>18.04</v>
+        <v>18.03</v>
       </c>
       <c r="I7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="J7" t="n">
         <v>11.49</v>
@@ -3844,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>6.26</v>
@@ -3859,25 +4447,25 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-6.84</v>
+        <v>4.19</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>22.54</v>
+        <v>0.79</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>22.5x vs 22.5x median — in-line</t>
+          <t>0.8x vs 2.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>-1.17</v>
+        <v>-1.03</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-1.2x vs -1.2x median — in-line</t>
+          <t>-1.0x vs 0.3x median — trading at discount</t>
         </is>
       </c>
       <c r="AA7" t="n">
@@ -3891,27 +4479,27 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>P/S 22.5x vs 22.5x median — in-line | P/B -1.2x vs -1.2x median — in-line</t>
+          <t>P/S 0.8x vs 2.3x median — trading at discount | P/B -1.0x vs 0.3x median — trading at discount</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>-0.44</v>
+        <v>-0.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.449999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="AG7" t="n">
-        <v>221.8</v>
+        <v>217.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.38</v>
+        <v>-0.86</v>
       </c>
       <c r="AI7" t="n">
-        <v>8.390000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.44–$8.45 (ann. vol 222%) | ATR range: $-0.38–$8.39</t>
+          <t>1-SD 3mo range: $-0.30–$7.36 (ann. vol 217%) | ATR range: $-0.86–$7.92</t>
         </is>
       </c>
     </row>
@@ -3922,16 +4510,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="C8" t="n">
-        <v>9.25</v>
+        <v>9.59</v>
       </c>
       <c r="D8" t="n">
-        <v>803994</v>
+        <v>757849</v>
       </c>
       <c r="E8" t="n">
-        <v>27.3</v>
+        <v>21.2</v>
       </c>
       <c r="F8" t="n">
         <v>0.26</v>
@@ -3964,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.58</v>
+        <v>4.55</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2397</v>
@@ -3979,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.17</v>
+        <v>6.06</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -3993,11 +4581,11 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>-0.35</v>
+        <v>-0.33</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.3x vs 1.0x median — trading at discount</t>
+          <t>-0.3x vs 1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA8" t="n">
@@ -4011,27 +4599,27 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>P/B -0.3x vs 1.0x median — trading at discount | EV/EBITDA -0.5x vs -0.5x median — in-line | Analyst target $1.43</t>
+          <t>P/B -0.3x vs 1.1x median — trading at discount | EV/EBITDA -0.5x vs -0.9x median — trading at discount | Analyst target $1.43</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.9</v>
+        <v>105.7</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.10–$0.32 (ann. vol 106%) | ATR range: $-0.05–$0.47</t>
+          <t>1-SD 3mo range: $0.09–$0.29 (ann. vol 106%) | ATR range: $-0.07–$0.45</t>
         </is>
       </c>
     </row>
@@ -4042,28 +4630,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.93</v>
+        <v>9.07</v>
       </c>
       <c r="C9" t="n">
-        <v>7.4</v>
+        <v>7.98</v>
       </c>
       <c r="D9" t="n">
-        <v>23297570</v>
+        <v>27913169</v>
       </c>
       <c r="E9" t="n">
-        <v>76.5</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="G9" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="J9" t="n">
         <v>1.49</v>
@@ -4084,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-24.62</v>
+        <v>-34.61</v>
       </c>
       <c r="Q9" t="n">
         <v>7.5</v>
@@ -4099,25 +4687,25 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-23.61</v>
+        <v>-33.74</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2.6x vs 2.1x median — trading at premium</t>
+          <t>3.0x vs 2.4x median — trading at premium</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>9.52</v>
+        <v>11.01</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.5x vs 1.0x median — trading at premium</t>
+          <t>11.0x vs 1.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA9" t="n">
@@ -4131,27 +4719,27 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>P/S 2.6x vs 2.1x median — trading at premium | P/B 9.5x vs 1.0x median — trading at premium | EV/EBITDA -0.9x vs -0.5x median — trading at premium</t>
+          <t>P/S 3.0x vs 2.4x median — trading at premium | P/B 11.0x vs 1.1x median — trading at premium | EV/EBITDA -0.9x vs -0.9x median — in-line</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>-20.17</v>
+        <v>-23.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>36.04</v>
+        <v>41.24</v>
       </c>
       <c r="AG9" t="n">
-        <v>708.3</v>
+        <v>709.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.12</v>
+        <v>2.26</v>
       </c>
       <c r="AI9" t="n">
-        <v>14.75</v>
+        <v>15.88</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-20.17–$36.04 (ann. vol 708%) | ATR range: $1.12–$14.75</t>
+          <t>1-SD 3mo range: $-23.10–$41.24 (ann. vol 709%) | ATR range: $2.26–$15.88</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4753,13 @@
         <v>0.54</v>
       </c>
       <c r="C10" t="n">
-        <v>7.03</v>
+        <v>7.2</v>
       </c>
       <c r="D10" t="n">
-        <v>518822</v>
+        <v>529214</v>
       </c>
       <c r="E10" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="F10" t="n">
         <v>0.73</v>
@@ -4180,7 +4768,7 @@
         <v>0.77</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
         <v>0.77</v>
@@ -4204,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>54.37</v>
+        <v>52.89</v>
       </c>
       <c r="Q10" t="n">
         <v>0.86</v>
@@ -4219,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>19.9</v>
+        <v>18.74</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -4229,7 +4817,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.1x vs 6.7x median — trading at discount</t>
+          <t>0.1x vs 6.6x median — trading at discount</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -4251,7 +4839,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 6.7x median — trading at discount | P/B 0.2x vs 0.2x median — in-line | EV/EBITDA 11.1x vs -0.4x median — trading at discount | Analyst target $3.06</t>
+          <t>P/S 0.1x vs 6.6x median — trading at discount | P/B 0.2x vs 0.2x median — in-line | EV/EBITDA 11.1x vs -0.4x median — trading at discount | Analyst target $3.06</t>
         </is>
       </c>
       <c r="AE10" t="n">
@@ -4261,17 +4849,17 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="AI10" t="n">
         <v>1.12</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.27–$0.81 (ann. vol 101%) | ATR range: $-0.05–$1.12</t>
+          <t>1-SD 3mo range: $0.27–$0.81 (ann. vol 101%) | ATR range: $-0.04–$1.12</t>
         </is>
       </c>
     </row>
@@ -4282,16 +4870,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="C11" t="n">
-        <v>4.7</v>
+        <v>4.78</v>
       </c>
       <c r="D11" t="n">
-        <v>661432</v>
+        <v>652301</v>
       </c>
       <c r="E11" t="n">
-        <v>37.5</v>
+        <v>36.7</v>
       </c>
       <c r="F11" t="n">
         <v>1.23</v>
@@ -4303,7 +4891,7 @@
         <v>1.99</v>
       </c>
       <c r="I11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>2.17</v>
@@ -4324,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>27.1</v>
+        <v>29.52</v>
       </c>
       <c r="Q11" t="n">
         <v>1.55</v>
@@ -4339,25 +4927,25 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.27</v>
+        <v>5.24</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>238.85</v>
+        <v>234.39</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>238.9x vs 22.5x median — trading at premium</t>
+          <t>234.4x vs 2.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>17.16</v>
+        <v>16.84</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.2x vs -1.2x median — trading at discount</t>
+          <t>16.8x vs 0.3x median — trading at premium</t>
         </is>
       </c>
       <c r="AA11" t="n">
@@ -4371,65 +4959,65 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>P/S 238.9x vs 22.5x median — trading at premium | P/B 17.2x vs -1.2x median — trading at discount | EV/EBITDA -1.3x vs -0.6x median — trading at premium | Analyst target $8.00</t>
+          <t>P/S 234.4x vs 2.3x median — trading at premium | P/B 16.8x vs 0.3x median — trading at premium | EV/EBITDA -1.3x vs 0.0x median — trading at discount | Analyst target $8.00</t>
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>128.5</v>
+        <v>128.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.38–$1.76 (ann. vol 128%) | ATR range: $-0.06–$2.20</t>
+          <t>1-SD 3mo range: $0.37–$1.73 (ann. vol 129%) | ATR range: $-0.08–$2.18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.66</v>
+        <v>3.44</v>
       </c>
       <c r="C12" t="n">
-        <v>4.52</v>
+        <v>4.77</v>
       </c>
       <c r="D12" t="n">
-        <v>845013</v>
+        <v>1829024</v>
       </c>
       <c r="E12" t="n">
-        <v>27.9</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>6.32</v>
+        <v>4.75</v>
       </c>
       <c r="G12" t="n">
-        <v>9.26</v>
+        <v>5.01</v>
       </c>
       <c r="H12" t="n">
-        <v>23.87</v>
+        <v>5.39</v>
       </c>
       <c r="I12" t="n">
-        <v>9.66</v>
+        <v>5.01</v>
       </c>
       <c r="J12" t="n">
-        <v>28.93</v>
+        <v>6.09</v>
       </c>
       <c r="K12" t="n">
-        <v>1.36</v>
+        <v>0.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -4438,50 +5026,50 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.835</v>
+        <v>4.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
         <v>4.78</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.7</v>
-      </c>
       <c r="S12" t="n">
-        <v>3.7902</v>
+        <v>4.72</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.56</v>
+        <v>37.21</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>3.1x vs 22.5x median — trading at discount</t>
+          <t>3.4x vs 1.8x median — trading at premium</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>-6.37</v>
+        <v>-0.96</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>-6.4x vs -1.2x median — trading at premium</t>
+          <t>-1.0x vs 0.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>0.03</v>
+        <v>-104.61</v>
       </c>
       <c r="AB12" t="n">
         <v/>
@@ -4491,65 +5079,65 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>P/S 3.1x vs 22.5x median — trading at discount | P/B -6.4x vs -1.2x median — trading at premium | EV/EBITDA 0.0x vs -0.6x median — trading at discount</t>
+          <t>P/S 3.4x vs 1.8x median — trading at premium | P/B -1.0x vs 0.1x median — trading at discount | EV/EBITDA -104.6x vs -2.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.39</v>
+        <v>5.61</v>
       </c>
       <c r="AG12" t="n">
-        <v>204</v>
+        <v>126.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>-4.62</v>
+        <v>-0.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.94</v>
+        <v>7.32</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.07–$7.39 (ann. vol 204%) | ATR range: $-4.62–$11.94</t>
+          <t>1-SD 3mo range: $1.27–$5.61 (ann. vol 126%) | ATR range: $-0.44–$7.32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="C13" t="n">
-        <v>4.21</v>
+        <v>4.58</v>
       </c>
       <c r="D13" t="n">
-        <v>1882746</v>
+        <v>841330</v>
       </c>
       <c r="E13" t="n">
-        <v>33.9</v>
+        <v>27.8</v>
       </c>
       <c r="F13" t="n">
-        <v>4.77</v>
+        <v>6.32</v>
       </c>
       <c r="G13" t="n">
-        <v>5.02</v>
+        <v>9.26</v>
       </c>
       <c r="H13" t="n">
-        <v>5.39</v>
+        <v>23.86</v>
       </c>
       <c r="I13" t="n">
-        <v>5.01</v>
+        <v>9.66</v>
       </c>
       <c r="J13" t="n">
-        <v>6.09</v>
+        <v>28.93</v>
       </c>
       <c r="K13" t="n">
-        <v>0.49</v>
+        <v>1.36</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -4558,50 +5146,50 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.95</v>
+        <v>3.835</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>35.62</v>
+        <v>5.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="R13" t="n">
-        <v>4.78</v>
+        <v>3.7</v>
       </c>
       <c r="S13" t="n">
-        <v>4.72</v>
+        <v>3.7902</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>29.32</v>
+        <v>4.41</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3.6x vs 2.7x median — trading at premium</t>
+          <t>3.1x vs 2.3x median — trading at premium</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>-1.02</v>
+        <v>-6.31</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>-1.0x vs 0.4x median — trading at discount</t>
+          <t>-6.3x vs 0.3x median — trading at discount</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>-104.61</v>
+        <v>0.03</v>
       </c>
       <c r="AB13" t="n">
         <v/>
@@ -4611,27 +5199,27 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P/S 3.6x vs 2.7x median — trading at premium | P/B -1.0x vs 0.4x median — trading at discount | EV/EBITDA -104.6x vs -4.0x median — trading at premium</t>
+          <t>P/S 3.1x vs 2.3x median — trading at premium | P/B -6.3x vs 0.3x median — trading at discount | EV/EBITDA 0.0x vs 0.0x median — in-line</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>1.39</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>5.95</v>
+        <v>7.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>124.4</v>
+        <v>204</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.14</v>
+        <v>-4.65</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.48</v>
+        <v>11.91</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.39–$5.95 (ann. vol 124%) | ATR range: $-0.14–$7.48</t>
+          <t>1-SD 3mo range: $-0.07–$7.33 (ann. vol 204%) | ATR range: $-4.65–$11.91</t>
         </is>
       </c>
     </row>
@@ -4642,16 +5230,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="C14" t="n">
-        <v>3.16</v>
+        <v>3.65</v>
       </c>
       <c r="D14" t="n">
-        <v>1967789</v>
+        <v>2094808</v>
       </c>
       <c r="E14" t="n">
-        <v>25.3</v>
+        <v>26.2</v>
       </c>
       <c r="F14" t="n">
         <v>0.53</v>
@@ -4699,29 +5287,29 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>24.98</v>
+        <v>20.9</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>1.0x vs 2.7x median — trading at discount</t>
+          <t>1.1x vs 1.8x median — trading at discount</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.1x vs 0.4x median — trading at premium</t>
+          <t>2.2x vs 0.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>-1.96</v>
+        <v>-2.9</v>
       </c>
       <c r="AB14" t="n">
         <v/>
@@ -4731,27 +5319,27 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P/S 1.0x vs 2.7x median — trading at discount | P/B 2.1x vs 0.4x median — trading at premium | EV/EBITDA -2.0x vs -4.0x median — trading at discount | Graham # $7.75</t>
+          <t>P/S 1.1x vs 1.8x median — trading at discount | P/B 2.2x vs 0.1x median — trading at premium | EV/EBITDA -2.9x vs -2.9x median — in-line | Graham # $7.75</t>
         </is>
       </c>
       <c r="AE14" t="n">
         <v>0.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AG14" t="n">
-        <v>160.7</v>
+        <v>160.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.08–$0.69 (ann. vol 161%) | ATR range: $0.18–$0.59</t>
+          <t>1-SD 3mo range: $0.08–$0.72 (ann. vol 160%) | ATR range: $0.19–$0.60</t>
         </is>
       </c>
     </row>
@@ -4762,16 +5350,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="C15" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="D15" t="n">
-        <v>978511</v>
+        <v>994694</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="F15" t="n">
         <v>0.53</v>
@@ -4804,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8.75</v>
+        <v>7.48</v>
       </c>
       <c r="Q15" t="n">
         <v>0.524</v>
@@ -4819,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>8.789999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -4833,11 +5421,11 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.1x vs 1.0x median — in-line</t>
+          <t>1.1x vs 1.1x median — in-line</t>
         </is>
       </c>
       <c r="AA15" t="n">
@@ -4851,27 +5439,27 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>P/B 1.1x vs 1.0x median — in-line | EV/EBITDA -0.0x vs -0.5x median — trading at discount | Analyst target $4.25</t>
+          <t>P/B 1.1x vs 1.1x median — in-line | EV/EBITDA -0.0x vs -0.9x median — trading at discount | Analyst target $4.25</t>
         </is>
       </c>
       <c r="AE15" t="n">
         <v>0.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>118.3</v>
+        <v>118.2</v>
       </c>
       <c r="AH15" t="n">
         <v>0.01</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.18–$0.70 (ann. vol 118%) | ATR range: $0.01–$0.87</t>
+          <t>1-SD 3mo range: $0.18–$0.71 (ann. vol 118%) | ATR range: $0.01–$0.88</t>
         </is>
       </c>
     </row>
@@ -4885,13 +5473,13 @@
         <v>0.09</v>
       </c>
       <c r="C16" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="D16" t="n">
-        <v>1268465</v>
+        <v>1244964</v>
       </c>
       <c r="E16" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="F16" t="n">
         <v>0.13</v>
@@ -4924,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>17.35</v>
+        <v>17.22</v>
       </c>
       <c r="Q16" t="n">
         <v>0.1587</v>
@@ -4939,17 +5527,17 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-11.64</v>
+        <v>-11.73</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.0x vs 2.1x median — trading at discount</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -4957,7 +5545,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>-0.0x vs 1.0x median — trading at discount</t>
+          <t>-0.0x vs 1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA16" t="n">
@@ -4971,7 +5559,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>P/S 0.0x vs 2.1x median — trading at discount | P/B -0.0x vs 1.0x median — trading at discount | EV/EBITDA -2.7x vs -0.5x median — trading at premium | Analyst target $3.75</t>
+          <t>P/B -0.0x vs 1.1x median — trading at discount | EV/EBITDA -2.7x vs -0.9x median — trading at premium | Analyst target $3.75</t>
         </is>
       </c>
       <c r="AE16" t="n">
@@ -4981,7 +5569,7 @@
         <v>0.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>107.5</v>
+        <v>107.7</v>
       </c>
       <c r="AH16" t="n">
         <v>-0.11</v>
@@ -5002,28 +5590,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.05</v>
+        <v>13.61</v>
       </c>
       <c r="C17" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="D17" t="n">
-        <v>47362693</v>
+        <v>49634885</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="F17" t="n">
-        <v>26.07</v>
+        <v>26.13</v>
       </c>
       <c r="G17" t="n">
-        <v>19.63</v>
+        <v>19.65</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
       </c>
       <c r="I17" t="n">
-        <v>15.96</v>
+        <v>15.97</v>
       </c>
       <c r="J17" t="n">
         <v>5.76</v>
@@ -5044,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-10.44</v>
+        <v>-13.84</v>
       </c>
       <c r="Q17" t="n">
         <v>26.75</v>
@@ -5059,25 +5647,25 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>18</v>
+        <v>13.52</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>1.7x vs 2.7x median — trading at discount</t>
+          <t>1.8x vs 1.8x median — in-line</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>-0.39</v>
+        <v>-0.41</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>-0.4x vs 0.4x median — trading at discount</t>
+          <t>-0.4x vs 0.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -5091,95 +5679,95 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>P/S 1.7x vs 2.7x median — trading at discount | P/B -0.4x vs 0.4x median — trading at discount | EV/EBITDA -6.1x vs -4.0x median — trading at premium | Analyst target $108.75</t>
+          <t>P/S 1.8x vs 1.8x median — in-line | P/B -0.4x vs 0.1x median — trading at discount | EV/EBITDA -6.1x vs -2.9x median — trading at premium | Analyst target $108.75</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>-21.96</v>
+        <v>-22.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>48.06</v>
+        <v>50.13</v>
       </c>
       <c r="AG17" t="n">
-        <v>536.5</v>
+        <v>536.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>-29.49</v>
+        <v>-28.93</v>
       </c>
       <c r="AI17" t="n">
-        <v>55.59</v>
+        <v>56.15</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-21.96–$48.06 (ann. vol 536%) | ATR range: $-29.49–$55.59</t>
+          <t>1-SD 3mo range: $-22.91–$50.13 (ann. vol 537%) | ATR range: $-28.93–$56.15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HVII</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.77</v>
+        <v>1.75</v>
       </c>
       <c r="C18" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="D18" t="n">
-        <v>1174406</v>
+        <v>2078473</v>
       </c>
       <c r="E18" t="n">
-        <v>28.7</v>
+        <v>83.2</v>
       </c>
       <c r="F18" t="n">
-        <v>9.449999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="G18" t="n">
-        <v>10.01</v>
+        <v>1.34</v>
       </c>
       <c r="H18" t="n">
-        <v>10.27</v>
+        <v>1.42</v>
       </c>
       <c r="I18" t="n">
-        <v>10.22</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>10.33</v>
+        <v>1.36</v>
       </c>
       <c r="K18" t="n">
-        <v>0.47</v>
+        <v>0.11</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>9.300000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>19.69</v>
+        <v>-7.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>1.68</v>
       </c>
       <c r="R18" t="n">
-        <v>6.09</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>7.68</v>
+        <v>1.61</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.16</v>
+        <v>-8</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
@@ -5193,113 +5781,113 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>-18.81</v>
+        <v>10.48</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>-18.8x vs 0.2x median — trading at discount</t>
+          <t>10.5x vs 1.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v/>
+        <v>-1.47</v>
       </c>
       <c r="AB18" t="n">
-        <v>17</v>
+        <v>6.5</v>
       </c>
       <c r="AC18" t="n">
         <v/>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/B -18.8x vs 0.2x median — trading at discount | Analyst target $17.00</t>
+          <t>P/B 10.5x vs 1.1x median — trading at premium | EV/EBITDA -1.5x vs -0.9x median — trading at premium | Analyst target $6.50</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>6.26</v>
+        <v>0.96</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.279999999999999</v>
+        <v>2.55</v>
       </c>
       <c r="AG18" t="n">
-        <v>38.8</v>
+        <v>90.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.56</v>
+        <v>0.93</v>
       </c>
       <c r="AI18" t="n">
-        <v>11.98</v>
+        <v>2.58</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $6.26–$9.28 (ann. vol 39%) | ATR range: $3.56–$11.98</t>
+          <t>1-SD 3mo range: $0.96–$2.55 (ann. vol 91%) | ATR range: $0.93–$2.58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMIX</t>
+          <t>HVII</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.1</v>
+        <v>7.92</v>
       </c>
       <c r="C19" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="D19" t="n">
-        <v>101694828</v>
+        <v>1200023</v>
       </c>
       <c r="E19" t="n">
-        <v>54.4</v>
+        <v>30.9</v>
       </c>
       <c r="F19" t="n">
-        <v>6.8</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>6.86</v>
+        <v>10.02</v>
       </c>
       <c r="H19" t="n">
-        <v>10.02</v>
+        <v>10.28</v>
       </c>
       <c r="I19" t="n">
-        <v>6.53</v>
+        <v>10.23</v>
       </c>
       <c r="J19" t="n">
-        <v>9.609999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="K19" t="n">
-        <v>1.91</v>
+        <v>0.47</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>11.65</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>43.3</v>
+        <v>17.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>16.41</v>
+        <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>5.17</v>
+        <v>6.09</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7.68</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6</v>
+        <v>-3.03</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
@@ -5313,405 +5901,405 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>-19.18</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.4x vs 1.0x median — trading at premium</t>
+          <t>-19.2x vs 0.2x median — trading at discount</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>-0.11</v>
+        <v/>
       </c>
       <c r="AB19" t="n">
-        <v>58.8</v>
+        <v>17</v>
       </c>
       <c r="AC19" t="n">
         <v/>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>P/B 1.4x vs 1.0x median — trading at premium | EV/EBITDA -0.1x vs -0.5x median — trading at discount | Analyst target $58.80</t>
+          <t>P/B -19.2x vs 0.2x median — trading at discount | Analyst target $17.00</t>
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>-0.59</v>
+        <v>6.36</v>
       </c>
       <c r="AF19" t="n">
-        <v>16.8</v>
+        <v>9.48</v>
       </c>
       <c r="AG19" t="n">
-        <v>214.6</v>
+        <v>39.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>-3.9</v>
+        <v>3.71</v>
       </c>
       <c r="AI19" t="n">
-        <v>20.1</v>
+        <v>12.13</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.59–$16.80 (ann. vol 215%) | ATR range: $-3.90–$20.10</t>
+          <t>1-SD 3mo range: $6.36–$9.48 (ann. vol 39%) | ATR range: $3.71–$12.13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BMEA</t>
+          <t>IFRX</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="C20" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="D20" t="n">
-        <v>2020511</v>
+        <v>1957477</v>
       </c>
       <c r="E20" t="n">
-        <v>83.2</v>
+        <v>61.7</v>
       </c>
       <c r="F20" t="n">
-        <v>1.37</v>
+        <v>1.99</v>
       </c>
       <c r="G20" t="n">
-        <v>1.34</v>
+        <v>1.94</v>
       </c>
       <c r="H20" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="J20" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.62</v>
+        <v>1.9612</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.69</v>
+        <v>-8.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.9505</v>
       </c>
       <c r="S20" t="n">
-        <v>1.61</v>
+        <v>2.1345</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.26</v>
+        <v>-0.95</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v/>
+        <v>-31440.31</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>-31440.3x vs 2.4x median — trading at discount</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>10.49</v>
+        <v>1.86</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.5x vs 1.0x median — trading at premium</t>
+          <t>1.9x vs 1.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>-1.47</v>
+        <v>-4.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.5</v>
+        <v>7.98</v>
       </c>
       <c r="AC20" t="n">
         <v/>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>P/B 10.5x vs 1.0x median — trading at premium | EV/EBITDA -1.5x vs -0.5x median — trading at premium | Analyst target $6.50</t>
+          <t>P/S -31440.3x vs 2.4x median — trading at discount | P/B 1.9x vs 1.1x median — trading at premium | EV/EBITDA -4.1x vs -0.9x median — trading at premium | Analyst target $7.98</t>
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.56</v>
+        <v>3.27</v>
       </c>
       <c r="AG20" t="n">
-        <v>90.8</v>
+        <v>103</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.95</v>
+        <v>1.16</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.96–$2.56 (ann. vol 91%) | ATR range: $0.95–$2.56</t>
+          <t>1-SD 3mo range: $1.04–$3.27 (ann. vol 103%) | ATR range: $1.16–$3.15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ADCT</t>
+          <t>AMIX</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.97</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="D21" t="n">
-        <v>1370497</v>
+        <v>103113296</v>
       </c>
       <c r="E21" t="n">
-        <v>38.1</v>
+        <v>54.7</v>
       </c>
       <c r="F21" t="n">
-        <v>1.07</v>
+        <v>6.81</v>
       </c>
       <c r="G21" t="n">
-        <v>1.37</v>
+        <v>6.86</v>
       </c>
       <c r="H21" t="n">
-        <v>2.59</v>
+        <v>10.02</v>
       </c>
       <c r="I21" t="n">
-        <v>1.14</v>
+        <v>6.53</v>
       </c>
       <c r="J21" t="n">
-        <v>3.08</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09</v>
+        <v>1.91</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9743000000000001</v>
+        <v>11.65</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.11</v>
+        <v>41.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.08</v>
+        <v>16.41</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9601</v>
+        <v>5.17</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9792999999999999</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.63</v>
+        <v>-2.79</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.56</v>
+        <v/>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.6x vs 2.1x median — trading at discount</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>-0.54</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>-0.5x vs 1.0x median — trading at discount</t>
+          <t>1.4x vs 1.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>-3.65</v>
+        <v>-0.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.33</v>
+        <v>58.8</v>
       </c>
       <c r="AC21" t="n">
         <v/>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>P/S 1.6x vs 2.1x median — trading at discount | P/B -0.5x vs 1.0x median — trading at discount | EV/EBITDA -3.7x vs -0.5x median — trading at premium | Analyst target $3.33</t>
+          <t>P/B 1.4x vs 1.1x median — trading at premium | EV/EBITDA -0.1x vs -0.9x median — trading at discount | Analyst target $58.80</t>
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>0.43</v>
+        <v>-0.61</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>17.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>111.9</v>
+        <v>214.8</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.28</v>
+        <v>-3.8</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.66</v>
+        <v>20.2</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.43–$1.52 (ann. vol 112%) | ATR range: $0.28–$1.66</t>
+          <t>1-SD 3mo range: $-0.61–$17.01 (ann. vol 215%) | ATR range: $-3.80–$20.20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>ADCT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.79</v>
+        <v>0.97</v>
       </c>
       <c r="C22" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="D22" t="n">
-        <v>557624</v>
+        <v>1377315</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>37.8</v>
       </c>
       <c r="F22" t="n">
-        <v>2.17</v>
+        <v>1.07</v>
       </c>
       <c r="G22" t="n">
-        <v>2.09</v>
+        <v>1.37</v>
       </c>
       <c r="H22" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="I22" t="n">
-        <v>2.01</v>
+        <v>1.14</v>
       </c>
       <c r="J22" t="n">
-        <v>2.51</v>
+        <v>3.08</v>
       </c>
       <c r="K22" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8201</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.92</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.99</v>
+        <v>0.9601</v>
       </c>
       <c r="S22" t="n">
-        <v>2.91</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="V22" t="b">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>12.49</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>12.5x vs 6.7x median — trading at premium</t>
+          <t>1.6x vs 2.4x median — trading at discount</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>-0.54</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.5x vs 0.2x median — trading at premium</t>
+          <t>-0.5x vs 1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>-15.05</v>
+        <v>-3.65</v>
       </c>
       <c r="AB22" t="n">
-        <v/>
+        <v>3.33</v>
       </c>
       <c r="AC22" t="n">
         <v/>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>P/S 12.5x vs 6.7x median — trading at premium | P/B 1.5x vs 0.2x median — trading at premium | EV/EBITDA -15.1x vs -0.4x median — trading at premium</t>
+          <t>P/S 1.6x vs 2.4x median — trading at discount | P/B -0.5x vs 1.1x median — trading at discount | EV/EBITDA -3.7x vs -0.9x median — trading at premium | Analyst target $3.33</t>
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>1.26</v>
+        <v>0.43</v>
       </c>
       <c r="AF22" t="n">
-        <v>4.32</v>
+        <v>1.51</v>
       </c>
       <c r="AG22" t="n">
-        <v>109.4</v>
+        <v>111.9</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>0.28</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.11</v>
+        <v>1.66</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.26–$4.32 (ann. vol 109%) | ATR range: $1.47–$4.11</t>
+          <t>1-SD 3mo range: $0.43–$1.51 (ann. vol 112%) | ATR range: $0.28–$1.66</t>
         </is>
       </c>
     </row>
@@ -5722,16 +6310,16 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="C23" t="n">
         <v>1.9</v>
       </c>
-      <c r="C23" t="n">
-        <v>1.64</v>
-      </c>
       <c r="D23" t="n">
-        <v>9504150</v>
+        <v>9540039</v>
       </c>
       <c r="E23" t="n">
-        <v>59.5</v>
+        <v>58.8</v>
       </c>
       <c r="F23" t="n">
         <v>1.68</v>
@@ -5764,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-14</v>
+        <v>-13.54</v>
       </c>
       <c r="Q23" t="n">
         <v>1.7254</v>
@@ -5779,25 +6367,25 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-11.45</v>
+        <v>-10.98</v>
       </c>
       <c r="V23" t="b">
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>79.36</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>79.4x vs 2.7x median — trading at premium</t>
+          <t>78.7x vs 1.8x median — trading at premium</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.1x vs 0.4x median — trading at premium</t>
+          <t>1.1x vs 0.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -5811,185 +6399,185 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>P/S 79.4x vs 2.7x median — trading at premium | P/B 1.1x vs 0.4x median — trading at premium | EV/EBITDA -1.0x vs -4.0x median — trading at discount | Analyst target $2.00 | Graham # $1.63</t>
+          <t>P/S 78.7x vs 1.8x median — trading at premium | P/B 1.1x vs 0.1x median — trading at premium | EV/EBITDA -1.0x vs -2.9x median — trading at discount | Analyst target $2.00 | Graham # $1.63</t>
         </is>
       </c>
       <c r="AE23" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>114.5</v>
+        <v>114.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.81–$2.99 (ann. vol 114%) | ATR range: $0.97–$2.83</t>
+          <t>1-SD 3mo range: $0.81–$2.96 (ann. vol 114%) | ATR range: $0.95–$2.81</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TNXP</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13.52</v>
+        <v>2.81</v>
       </c>
       <c r="C24" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="D24" t="n">
-        <v>6202657</v>
+        <v>562470</v>
       </c>
       <c r="E24" t="n">
-        <v>64.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="F24" t="n">
-        <v>12.2</v>
+        <v>2.17</v>
       </c>
       <c r="G24" t="n">
-        <v>12.06</v>
+        <v>2.09</v>
       </c>
       <c r="H24" t="n">
-        <v>15.48</v>
+        <v>2.69</v>
       </c>
       <c r="I24" t="n">
-        <v>11.86</v>
+        <v>2.01</v>
       </c>
       <c r="J24" t="n">
-        <v>14.24</v>
+        <v>2.51</v>
       </c>
       <c r="K24" t="n">
-        <v>0.84</v>
+        <v>0.17</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>12.75</v>
+        <v>2.8201</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.76</v>
+        <v>0.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>12.9</v>
+        <v>2.92</v>
       </c>
       <c r="R24" t="n">
-        <v>12.2</v>
+        <v>1.99</v>
       </c>
       <c r="S24" t="n">
-        <v>12.44</v>
+        <v>2.91</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.06</v>
+        <v>3.56</v>
       </c>
       <c r="V24" t="b">
         <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>7.97</v>
+        <v>12.58</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>8.0x vs 2.1x median — trading at premium</t>
+          <t>12.6x vs 6.6x median — trading at premium</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>0.85</v>
+        <v>1.49</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.8x vs 1.0x median — in-line</t>
+          <t>1.5x vs 0.2x median — trading at premium</t>
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>-0.24</v>
+        <v>-15.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>42.4</v>
+        <v/>
       </c>
       <c r="AC24" t="n">
         <v/>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>P/S 8.0x vs 2.1x median — trading at premium | P/B 0.8x vs 1.0x median — in-line | EV/EBITDA -0.2x vs -0.5x median — trading at discount | Analyst target $42.40</t>
+          <t>P/S 12.6x vs 6.6x median — trading at premium | P/B 1.5x vs 0.2x median — trading at premium | EV/EBITDA -15.1x vs -0.4x median — trading at premium</t>
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>8.59</v>
+        <v>1.27</v>
       </c>
       <c r="AF24" t="n">
-        <v>18.45</v>
+        <v>4.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>73</v>
+        <v>109.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>6.48</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" t="n">
-        <v>20.56</v>
+        <v>4.13</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $8.59–$18.45 (ann. vol 73%) | ATR range: $6.48–$20.56</t>
+          <t>1-SD 3mo range: $1.27–$4.35 (ann. vol 109%) | ATR range: $1.49–$4.13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AVXL</t>
+          <t>TNXP</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.58</v>
+        <v>13.6</v>
       </c>
       <c r="C25" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="D25" t="n">
-        <v>3212812</v>
+        <v>6282021</v>
       </c>
       <c r="E25" t="n">
-        <v>64.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>3.15</v>
+        <v>12.21</v>
       </c>
       <c r="G25" t="n">
-        <v>2.98</v>
+        <v>12.07</v>
       </c>
       <c r="H25" t="n">
-        <v>4.07</v>
+        <v>15.48</v>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>11.86</v>
       </c>
       <c r="J25" t="n">
-        <v>3.61</v>
+        <v>14.24</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2</v>
+        <v>0.84</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -5998,80 +6586,800 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1564</v>
+        <v>12.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-11.59</v>
+        <v>-6.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.42</v>
+        <v>12.9</v>
       </c>
       <c r="R25" t="n">
-        <v>3.07</v>
+        <v>12.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.33</v>
+        <v>12.44</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.72</v>
+        <v>-8.5</v>
       </c>
       <c r="V25" t="b">
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v/>
+        <v>8.01</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>8.0x vs 2.4x median — trading at premium</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2.7x vs 1.0x median — trading at premium</t>
+          <t>1.0x vs 1.1x median — in-line</t>
         </is>
       </c>
       <c r="AA25" t="n">
-        <v/>
+        <v>-0.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>20</v>
+        <v>42.4</v>
       </c>
       <c r="AC25" t="n">
         <v/>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>P/B 2.7x vs 1.0x median — trading at premium | Analyst target $20.00</t>
+          <t>P/S 8.0x vs 2.4x median — trading at premium | P/B 1.0x vs 1.1x median — in-line | EV/EBITDA -0.2x vs -0.9x median — trading at discount | Analyst target $42.40</t>
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AF25" t="n">
-        <v>5.28</v>
+        <v>18.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>95.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>6.55</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.11</v>
+        <v>20.64</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.88–$5.28 (ann. vol 95%) | ATR range: $2.05–$5.11</t>
+          <t>1-SD 3mo range: $8.63–$18.56 (ann. vol 73%) | ATR range: $6.55–$20.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CTXR</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D26" t="n">
+        <v>660848</v>
+      </c>
+      <c r="E26" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.5851</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-5.35</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.5733</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-6.18</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2.4x vs 2.4x median — in-line</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>0.3x vs 1.1x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v/>
+      </c>
+      <c r="AB26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v/>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>P/S 2.4x vs 2.4x median — in-line | P/B 0.3x vs 1.1x median — trading at discount | Analyst target $4.00</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.27–$0.97 (ann. vol 112%) | ATR range: $-0.01–$1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AVXL</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3156218</v>
+      </c>
+      <c r="E27" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.1564</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v/>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2.7x vs 1.1x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v/>
+      </c>
+      <c r="AB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="n">
+        <v/>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>P/B 2.7x vs 1.1x median — trading at premium | Analyst target $20.00</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $1.84–$5.17 (ann. vol 95%) | ATR range: $1.97–$5.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DHX</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1116949</v>
+      </c>
+      <c r="E28" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.2248</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.2265</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>1.5x vs 2.3x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>1.6x vs 0.3x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>P/S 1.5x vs 2.3x median — trading at discount | P/B 1.6x vs 0.3x median — trading at premium | EV/EBITDA 8.4x vs 0.0x median — trading at premium | Analyst target $6.75 | Graham # $1.36</t>
+        </is>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $2.80–$6.04 (ann. vol 73%) | ATR range: $1.74–$7.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7700111</v>
+      </c>
+      <c r="E29" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AC29" t="n">
+        <v/>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Analyst target $7.83</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $2.58–$9.64 (ann. vol 116%) | ATR range: $3.11–$9.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OLOX</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1605748</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="H30" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J30" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.7597</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>0.6x vs 1.8x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>0.1x vs 0.1x median — in-line</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="AB30" t="n">
+        <v/>
+      </c>
+      <c r="AC30" t="n">
+        <v>329.77</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>P/S 0.6x vs 1.8x median — trading at discount | P/B 0.1x vs 0.1x median — in-line | EV/EBITDA -2.5x vs -2.9x median — in-line | Graham # $329.77</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $-0.02–$2.95 (ann. vol 203%) | ATR range: $-2.82–$5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CRBP</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4874624</v>
+      </c>
+      <c r="E31" t="n">
+        <v>69</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="R31" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v/>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>2.0x vs 1.1x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="AC31" t="n">
+        <v/>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>P/B 2.0x vs 1.1x median — trading at premium | EV/EBITDA -0.9x vs -0.9x median — in-line | Analyst target $34.52</t>
+        </is>
+      </c>
+      <c r="AE31" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $6.56–$15.71 (ann. vol 82%) | ATR range: $6.29–$15.98</t>
         </is>
       </c>
     </row>
@@ -6086,7 +7394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6582,82 +7890,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Items: 5.03, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0001104659-26-099673</t>
+          <t>0001104659-26-100556</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>tm2623749d1_8k.htm</t>
+          <t>tm2623776d4_424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Items: 8.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0001104659-26-098592</t>
+          <t>0001104659-26-100555</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>tm2623548d1_8k.htm</t>
+          <t>tm2623776d3_424b3.htm</t>
         </is>
       </c>
     </row>
@@ -6689,12 +7989,12 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0001104659-26-100556</t>
+          <t>0001104659-26-100553</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>tm2623776d4_424b3.htm</t>
+          <t>tm2623776d2_424b3.htm</t>
         </is>
       </c>
     </row>
@@ -6726,86 +8026,94 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0001104659-26-100555</t>
+          <t>0001104659-26-100552</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>tm2623776d3_424b3.htm</t>
+          <t>tm2623776d1_424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Items: 5.03, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0001104659-26-100553</t>
+          <t>0001104659-26-099673</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>tm2623776d2_424b3.htm</t>
+          <t>tm2623749d1_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Items: 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0001104659-26-100552</t>
+          <t>0001104659-26-098592</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>tm2623776d1_424b3.htm</t>
+          <t>tm2623548d1_8k.htm</t>
         </is>
       </c>
     </row>
@@ -7147,17 +8455,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8-K/A</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7166,22 +8474,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Items: 2.02, 8.01, 9.01 (routine)</t>
+          <t>Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0001493152-26-039796</t>
+          <t>0001213900-26-093255</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>form8-ka.htm</t>
+          <t>ea0303279-8k_richtech.htm</t>
         </is>
       </c>
     </row>
@@ -7193,7 +8501,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>8-K/A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7211,25 +8519,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
+          <t>Items: 2.02, 8.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0001493152-26-039786</t>
+          <t>0001493152-26-039796</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>form8-ka.htm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7239,7 +8547,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -7248,22 +8556,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
+          <t>Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0001213900-26-093255</t>
+          <t>0001493152-26-039786</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ea0303279-8k_richtech.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
@@ -7356,7 +8664,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AVXL</t>
+          <t>CTXR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7366,7 +8674,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -7375,22 +8683,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
+          <t>Item 3.01 (delisting, -6)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0001731122-26-001143</t>
+          <t>0001213900-26-092604</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>e7897_8-k.htm</t>
+          <t>ea0302856-8k_citius.htm</t>
         </is>
       </c>
     </row>
@@ -7407,7 +8715,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -7420,18 +8728,227 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
+          <t>Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
+          <t>0001731122-26-001143</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>e7897_8-k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AVXL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>0001731122-26-001078</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>e7862_8k.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0001683168-26-006540</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0001683168-26-006538</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>insider_unknown</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0001683168-26-006530</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CRBP</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0001193125-26-354145</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>38.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7504</v>
+        <v>0.7605</v>
       </c>
       <c r="Q3" t="n">
         <v>9470</v>
       </c>
       <c r="R3" t="n">
-        <v>0.13</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
         <v>0.777</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -846,19 +846,19 @@
         <v>9.69</v>
       </c>
       <c r="N4" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="O4" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>8.841699999999999</v>
+        <v>9.84</v>
       </c>
       <c r="Q4" t="n">
         <v>5280</v>
       </c>
       <c r="R4" t="n">
-        <v>-7.51</v>
+        <v>2.93</v>
       </c>
       <c r="S4" t="n">
         <v>7.86</v>
@@ -870,7 +870,7 @@
         <v>-17.78</v>
       </c>
       <c r="V4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="W4" t="n">
         <v>7.03</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>65.8</v>
       </c>
       <c r="P7" t="n">
-        <v>13.66</v>
+        <v>13.73</v>
       </c>
       <c r="Q7" t="n">
         <v>65774</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="S7" t="n">
         <v>12.44</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -1238,19 +1238,19 @@
         <v>1.42</v>
       </c>
       <c r="N8" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
         <v>66.59999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3956</v>
+        <v>1.4653</v>
       </c>
       <c r="Q8" t="n">
         <v>5047</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.37</v>
+        <v>3.55</v>
       </c>
       <c r="S8" t="n">
         <v>1.32</v>
@@ -1262,7 +1262,7 @@
         <v>-6.71</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
         <v>1.24</v>
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,15 +1864,15 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,15 +2060,15 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -2126,13 +2126,13 @@
         <v>57.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.92</v>
+        <v>3.8726</v>
       </c>
       <c r="Q17" t="n">
         <v>5620</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.13</v>
+        <v>-1.34</v>
       </c>
       <c r="S17" t="n">
         <v>3.8915</v>
@@ -2147,7 +2147,7 @@
         <v>3.99</v>
       </c>
       <c r="W17" t="n">
-        <v>3.89</v>
+        <v>3.8726</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2316,19 +2316,19 @@
         <v>0.17</v>
       </c>
       <c r="N19" t="n">
-        <v>11.79</v>
+        <v>11.81</v>
       </c>
       <c r="O19" t="n">
         <v>30.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1686</v>
+        <v>0.17</v>
       </c>
       <c r="Q19" t="n">
         <v>74807</v>
       </c>
       <c r="R19" t="n">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="S19" t="n">
         <v>0.2037</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2414,19 +2414,19 @@
         <v>0.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="O20" t="n">
         <v>26.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0.398</v>
+        <v>0.3934</v>
       </c>
       <c r="Q20" t="n">
         <v>10218</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.53</v>
+        <v>-1.67</v>
       </c>
       <c r="S20" t="n">
         <v>0.4813</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2708,19 +2708,19 @@
         <v>1.97</v>
       </c>
       <c r="N23" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="O23" t="n">
         <v>61.8</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>1.9797</v>
       </c>
       <c r="Q23" t="n">
         <v>495485</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.25</v>
+        <v>0.24</v>
       </c>
       <c r="S23" t="n">
         <v>1.6781</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2910,13 +2910,13 @@
         <v>61.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.11</v>
+        <v>4.2701</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.12</v>
+        <v>4.02</v>
       </c>
       <c r="S25" t="n">
         <v>4.09</v>
@@ -2928,7 +2928,7 @@
         <v>-0.37</v>
       </c>
       <c r="V25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="W25" t="n">
         <v>4.01</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>81.90000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.55</v>
+        <v>4.4639</v>
       </c>
       <c r="Q26" t="n">
         <v>40316</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.55</v>
+        <v>-2.43</v>
       </c>
       <c r="S26" t="n">
         <v>4.11</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3110,13 +3110,13 @@
         <v>99</v>
       </c>
       <c r="P27" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>3033</v>
       </c>
       <c r="R27" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="S27" t="n">
         <v>10.17</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3300,19 +3300,19 @@
         <v>3.33</v>
       </c>
       <c r="N29" t="n">
-        <v>19</v>
+        <v>19.07</v>
       </c>
       <c r="O29" t="n">
         <v>73.2</v>
       </c>
       <c r="P29" t="n">
-        <v>6.23</v>
+        <v>4.32</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>87.08</v>
+        <v>29.72</v>
       </c>
       <c r="S29" t="n">
         <v>17</v>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3496,19 +3496,19 @@
         <v>0.55</v>
       </c>
       <c r="N31" t="n">
-        <v>8.609999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="O31" t="n">
         <v>32</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5897</v>
       </c>
       <c r="Q31" t="n">
         <v>49655</v>
       </c>
       <c r="R31" t="n">
-        <v>3.23</v>
+        <v>7.55</v>
       </c>
       <c r="S31" t="n">
         <v>0.643</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3730,15 +3730,15 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB33" t="n">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
@@ -3790,7 +3790,7 @@
         <v>3.92</v>
       </c>
       <c r="N34" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O34" t="n">
         <v>45.7</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3926,15 +3926,15 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4047,13 +4047,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="D37" t="n">
         <v>4.5</v>
       </c>
       <c r="E37" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -4084,19 +4084,19 @@
         <v>1.64</v>
       </c>
       <c r="N37" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="O37" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q37" t="n">
         <v>54639</v>
       </c>
       <c r="R37" t="n">
-        <v>-2.01</v>
+        <v>-3.23</v>
       </c>
       <c r="S37" t="n">
         <v>1.62</v>
@@ -4122,11 +4122,11 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -4188,13 +4188,13 @@
         <v>62.9</v>
       </c>
       <c r="P38" t="n">
-        <v>17.65</v>
+        <v>16.2273</v>
       </c>
       <c r="Q38" t="n">
         <v>16161</v>
       </c>
       <c r="R38" t="n">
-        <v>0.51</v>
+        <v>-7.59</v>
       </c>
       <c r="S38" t="n">
         <v>16.5</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="D40" t="n">
         <v>2.8</v>
       </c>
       <c r="E40" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="F40" t="n">
         <v>-1</v>
@@ -4378,19 +4378,19 @@
         <v>7.84</v>
       </c>
       <c r="N40" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
         <v>29.7</v>
       </c>
       <c r="P40" t="n">
-        <v>7.7</v>
+        <v>7.91</v>
       </c>
       <c r="Q40" t="n">
         <v>6127</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.53</v>
+        <v>1.15</v>
       </c>
       <c r="S40" t="n">
         <v>7.68</v>
@@ -4416,11 +4416,11 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -4476,19 +4476,19 @@
         <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>4.87</v>
+        <v>4.98</v>
       </c>
       <c r="O41" t="n">
         <v>28.1</v>
       </c>
       <c r="P41" t="n">
-        <v>3.9186</v>
+        <v>3.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>7895</v>
+        <v>45452</v>
       </c>
       <c r="R41" t="n">
-        <v>6.77</v>
+        <v>3.54</v>
       </c>
       <c r="S41" t="n">
         <v>3.7902</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -4574,19 +4574,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O42" t="n">
         <v>52.7</v>
       </c>
       <c r="P42" t="n">
-        <v>9.262</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q42" t="n">
         <v>6191</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>-0.33</v>
       </c>
       <c r="S42" t="n">
         <v>9.1</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4672,19 +4672,19 @@
         <v>7.19</v>
       </c>
       <c r="N43" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O43" t="n">
         <v>51.6</v>
       </c>
       <c r="P43" t="n">
-        <v>7.11</v>
+        <v>7.35</v>
       </c>
       <c r="Q43" t="n">
         <v>13347</v>
       </c>
       <c r="R43" t="n">
-        <v>-1.39</v>
+        <v>1.94</v>
       </c>
       <c r="S43" t="n">
         <v>8</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4972,13 +4972,13 @@
         <v>55.4</v>
       </c>
       <c r="P46" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>-2.41</v>
+        <v>0.27</v>
       </c>
       <c r="S46" t="n">
         <v>1.82</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5064,19 +5064,19 @@
         <v>0.21</v>
       </c>
       <c r="N47" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="O47" t="n">
         <v>27.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2159</v>
+        <v>0.2162</v>
       </c>
       <c r="Q47" t="n">
         <v>11695</v>
       </c>
       <c r="R47" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="S47" t="n">
         <v>0.2029</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -5554,7 +5554,7 @@
         <v>1.09</v>
       </c>
       <c r="N52" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="O52" t="n">
         <v>66.7</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -5652,19 +5652,19 @@
         <v>0.96</v>
       </c>
       <c r="N53" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O53" t="n">
         <v>42.7</v>
       </c>
       <c r="P53" t="n">
-        <v>0.9584</v>
+        <v>0.9506</v>
       </c>
       <c r="Q53" t="n">
         <v>95246</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.89</v>
       </c>
       <c r="S53" t="n">
         <v>0.8951</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>80.59999999999999</v>
       </c>
       <c r="P54" t="n">
-        <v>1.9729</v>
+        <v>1.9726</v>
       </c>
       <c r="Q54" t="n">
         <v>11650</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.86</v>
+        <v>-0.87</v>
       </c>
       <c r="S54" t="n">
         <v>1.9</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5952,13 +5952,13 @@
         <v>44.3</v>
       </c>
       <c r="P56" t="n">
-        <v>10.7114</v>
+        <v>10.73</v>
       </c>
       <c r="Q56" t="n">
         <v>7872</v>
       </c>
       <c r="R56" t="n">
-        <v>0.39</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S56" t="n">
         <v>10.74</v>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>13.04</v>
       </c>
       <c r="N57" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="O57" t="n">
         <v>42</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6244,19 +6244,19 @@
         <v>0.58</v>
       </c>
       <c r="N59" t="n">
-        <v>19.1</v>
+        <v>19.12</v>
       </c>
       <c r="O59" t="n">
         <v>69</v>
       </c>
       <c r="P59" t="n">
-        <v>0.5299</v>
+        <v>0.5382</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-7.81</v>
+        <v>-6.37</v>
       </c>
       <c r="S59" t="n">
         <v>0.26</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6342,19 +6342,19 @@
         <v>1.73</v>
       </c>
       <c r="N60" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="O60" t="n">
         <v>82.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1.7501</v>
+        <v>1.7503</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S60" t="n">
         <v>1.61</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6501,13 +6501,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="D62" t="n">
         <v>1.2</v>
       </c>
       <c r="E62" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6538,19 +6538,19 @@
         <v>0.2</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O62" t="n">
         <v>62.1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2019</v>
+        <v>0.2044</v>
       </c>
       <c r="Q62" t="n">
         <v>10241</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.66</v>
+        <v>-0.44</v>
       </c>
       <c r="S62" t="n">
         <v>0.178</v>
@@ -6576,11 +6576,11 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB62" t="n">
@@ -6642,13 +6642,13 @@
         <v>97</v>
       </c>
       <c r="P63" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="Q63" t="n">
         <v>3188</v>
       </c>
       <c r="R63" t="n">
-        <v>-2.04</v>
+        <v>-3.67</v>
       </c>
       <c r="S63" t="n">
         <v>3.15</v>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -6734,19 +6734,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="N64" t="n">
-        <v>10.43</v>
+        <v>10.47</v>
       </c>
       <c r="O64" t="n">
         <v>79.90000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>8.81</v>
+        <v>9.270799999999999</v>
       </c>
       <c r="Q64" t="n">
         <v>7560</v>
       </c>
       <c r="R64" t="n">
-        <v>-7.31</v>
+        <v>-2.46</v>
       </c>
       <c r="S64" t="n">
         <v>6.04</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -6832,19 +6832,19 @@
         <v>1.08</v>
       </c>
       <c r="N65" t="n">
-        <v>4.88</v>
+        <v>4.9</v>
       </c>
       <c r="O65" t="n">
         <v>37.9</v>
       </c>
       <c r="P65" t="n">
-        <v>1.0708</v>
+        <v>1.1</v>
       </c>
       <c r="Q65" t="n">
         <v>1200</v>
       </c>
       <c r="R65" t="n">
-        <v>-0.85</v>
+        <v>1.85</v>
       </c>
       <c r="S65" t="n">
         <v>1.105</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -6936,13 +6936,13 @@
         <v>33.6</v>
       </c>
       <c r="P66" t="n">
-        <v>0.4321</v>
+        <v>0.4343</v>
       </c>
       <c r="Q66" t="n">
         <v>49975</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.6</v>
+        <v>-0.09</v>
       </c>
       <c r="S66" t="n">
         <v>0.48</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>77.90000000000001</v>
       </c>
       <c r="P69" t="n">
-        <v>6.0462</v>
+        <v>6.05</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="S69" t="n">
         <v>5.85</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -7420,19 +7420,19 @@
         <v>1.18</v>
       </c>
       <c r="N71" t="n">
-        <v>16.94</v>
+        <v>16.96</v>
       </c>
       <c r="O71" t="n">
         <v>26.4</v>
       </c>
       <c r="P71" t="n">
-        <v>1.07</v>
+        <v>1.0607</v>
       </c>
       <c r="Q71" t="n">
         <v>848</v>
       </c>
       <c r="R71" t="n">
-        <v>-8.550000000000001</v>
+        <v>-9.34</v>
       </c>
       <c r="S71" t="n">
         <v>1.48</v>
@@ -7447,7 +7447,7 @@
         <v>1.4</v>
       </c>
       <c r="W71" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X71" t="b">
         <v>1</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="F73" t="n">
         <v>-1</v>
@@ -7616,19 +7616,19 @@
         <v>1.49</v>
       </c>
       <c r="N73" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O73" t="n">
         <v>17</v>
       </c>
       <c r="P73" t="n">
-        <v>1.46</v>
+        <v>1.4796</v>
       </c>
       <c r="Q73" t="n">
         <v>7426</v>
       </c>
       <c r="R73" t="n">
-        <v>-2.43</v>
+        <v>-1.12</v>
       </c>
       <c r="S73" t="n">
         <v>1.63</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -7677,13 +7677,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1.42</v>
+        <v>-1.43</v>
       </c>
       <c r="D74" t="n">
         <v>-0.3</v>
       </c>
       <c r="E74" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="F74" t="n">
         <v>3</v>
@@ -7714,19 +7714,19 @@
         <v>1.52</v>
       </c>
       <c r="N74" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="O74" t="n">
         <v>61.2</v>
       </c>
       <c r="P74" t="n">
-        <v>1.5003</v>
+        <v>1.51</v>
       </c>
       <c r="Q74" t="n">
         <v>543273</v>
       </c>
       <c r="R74" t="n">
-        <v>-1.3</v>
+        <v>-0.66</v>
       </c>
       <c r="S74" t="n">
         <v>1.33</v>
@@ -7752,11 +7752,11 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AB74" t="n">
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -7910,19 +7910,19 @@
         <v>0.1</v>
       </c>
       <c r="N76" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="O76" t="n">
         <v>34.9</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0939</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="Q76" t="n">
         <v>157511</v>
       </c>
       <c r="R76" t="n">
-        <v>-2.39</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0.082</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -8008,19 +8008,19 @@
         <v>3.88</v>
       </c>
       <c r="N77" t="n">
-        <v>10.52</v>
+        <v>10.65</v>
       </c>
       <c r="O77" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="P77" t="n">
-        <v>4.1681</v>
+        <v>5.85</v>
       </c>
       <c r="Q77" t="n">
         <v>25729</v>
       </c>
       <c r="R77" t="n">
-        <v>8.1</v>
+        <v>51.72</v>
       </c>
       <c r="S77" t="n">
         <v>3.73</v>
@@ -8032,7 +8032,7 @@
         <v>-3.26</v>
       </c>
       <c r="V77" t="n">
-        <v>6.26</v>
+        <v>6.49</v>
       </c>
       <c r="W77" t="n">
         <v>0.4</v>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8110,19 +8110,19 @@
         <v>3.42</v>
       </c>
       <c r="N78" t="n">
-        <v>5.98</v>
+        <v>6</v>
       </c>
       <c r="O78" t="n">
         <v>31.8</v>
       </c>
       <c r="P78" t="n">
-        <v>3.4007</v>
+        <v>3.39</v>
       </c>
       <c r="Q78" t="n">
         <v>27607</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.87</v>
       </c>
       <c r="S78" t="n">
         <v>4.72</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>68584569</v>
+        <v>68587163</v>
       </c>
       <c r="E2" t="n">
         <v>99</v>
@@ -8436,13 +8436,13 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>3033</v>
       </c>
       <c r="P2" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
@@ -8526,7 +8526,7 @@
         <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>5448101</v>
+        <v>5448245</v>
       </c>
       <c r="E3" t="n">
         <v>97</v>
@@ -8556,13 +8556,13 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="O3" t="n">
         <v>3188</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.04</v>
+        <v>-3.67</v>
       </c>
       <c r="Q3" t="n">
         <v>3.7192</v>
@@ -8643,10 +8643,10 @@
         <v>0.58</v>
       </c>
       <c r="C4" t="n">
-        <v>19.1</v>
+        <v>19.12</v>
       </c>
       <c r="D4" t="n">
-        <v>14651147</v>
+        <v>14905396</v>
       </c>
       <c r="E4" t="n">
         <v>69</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5299</v>
+        <v>0.5382</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.81</v>
+        <v>-6.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6899999999999999</v>
@@ -8763,10 +8763,10 @@
         <v>3.33</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>19.07</v>
       </c>
       <c r="D5" t="n">
-        <v>1237426</v>
+        <v>1331252</v>
       </c>
       <c r="E5" t="n">
         <v>73.2</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.23</v>
+        <v>4.32</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>87.08</v>
+        <v>29.72</v>
       </c>
       <c r="Q5" t="n">
         <v>6.88</v>
@@ -8883,10 +8883,10 @@
         <v>1.18</v>
       </c>
       <c r="C6" t="n">
-        <v>16.94</v>
+        <v>16.96</v>
       </c>
       <c r="D6" t="n">
-        <v>1129380</v>
+        <v>1139007</v>
       </c>
       <c r="E6" t="n">
         <v>26.4</v>
@@ -8916,19 +8916,19 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>1.0607</v>
       </c>
       <c r="O6" t="n">
         <v>848</v>
       </c>
       <c r="P6" t="n">
-        <v>-8.550000000000001</v>
+        <v>-9.34</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="S6" t="n">
         <v>1.48</v>
@@ -9003,10 +9003,10 @@
         <v>0.17</v>
       </c>
       <c r="C7" t="n">
-        <v>11.79</v>
+        <v>11.81</v>
       </c>
       <c r="D7" t="n">
-        <v>1756272</v>
+        <v>1759655</v>
       </c>
       <c r="E7" t="n">
         <v>30.9</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1686</v>
+        <v>0.17</v>
       </c>
       <c r="O7" t="n">
         <v>74807</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2349</v>
@@ -9123,10 +9123,10 @@
         <v>3.88</v>
       </c>
       <c r="C8" t="n">
-        <v>10.52</v>
+        <v>10.65</v>
       </c>
       <c r="D8" t="n">
-        <v>47187492</v>
+        <v>47842113</v>
       </c>
       <c r="E8" t="n">
         <v>83.59999999999999</v>
@@ -9156,16 +9156,16 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1681</v>
+        <v>5.85</v>
       </c>
       <c r="O8" t="n">
         <v>25729</v>
       </c>
       <c r="P8" t="n">
-        <v>8.1</v>
+        <v>51.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.26</v>
+        <v>6.49</v>
       </c>
       <c r="R8" t="n">
         <v>0.4</v>
@@ -9243,10 +9243,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>10.43</v>
+        <v>10.47</v>
       </c>
       <c r="D9" t="n">
-        <v>37416998</v>
+        <v>37582666</v>
       </c>
       <c r="E9" t="n">
         <v>79.90000000000001</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.81</v>
+        <v>9.270799999999999</v>
       </c>
       <c r="O9" t="n">
         <v>7560</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.31</v>
+        <v>-2.46</v>
       </c>
       <c r="Q9" t="n">
         <v>9.890000000000001</v>
@@ -9363,10 +9363,10 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="D10" t="n">
-        <v>856720</v>
+        <v>857963</v>
       </c>
       <c r="E10" t="n">
         <v>27.9</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2159</v>
+        <v>0.2162</v>
       </c>
       <c r="O10" t="n">
         <v>11695</v>
       </c>
       <c r="P10" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="Q10" t="n">
         <v>0.2397</v>
@@ -9603,10 +9603,10 @@
         <v>0.55</v>
       </c>
       <c r="C12" t="n">
-        <v>8.609999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>603829</v>
+        <v>604458</v>
       </c>
       <c r="E12" t="n">
         <v>32</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5897</v>
       </c>
       <c r="O12" t="n">
         <v>49655</v>
       </c>
       <c r="P12" t="n">
-        <v>3.23</v>
+        <v>7.55</v>
       </c>
       <c r="Q12" t="n">
         <v>0.86</v>
@@ -9726,7 +9726,7 @@
         <v>6.72</v>
       </c>
       <c r="D13" t="n">
-        <v>1062971</v>
+        <v>1063159</v>
       </c>
       <c r="E13" t="n">
         <v>48.4</v>
@@ -9843,10 +9843,10 @@
         <v>3.42</v>
       </c>
       <c r="C14" t="n">
-        <v>5.98</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1976201</v>
+        <v>1978890</v>
       </c>
       <c r="E14" t="n">
         <v>31.8</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4007</v>
+        <v>3.39</v>
       </c>
       <c r="O14" t="n">
         <v>27607</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.87</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
@@ -9956,38 +9956,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MCRP</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.08</v>
+        <v>3.7</v>
       </c>
       <c r="C15" t="n">
-        <v>4.88</v>
+        <v>4.98</v>
       </c>
       <c r="D15" t="n">
-        <v>724796</v>
+        <v>880564</v>
       </c>
       <c r="E15" t="n">
-        <v>37.9</v>
+        <v>28.1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.23</v>
+        <v>6.33</v>
       </c>
       <c r="G15" t="n">
-        <v>1.47</v>
+        <v>9.26</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>23.84</v>
       </c>
       <c r="I15" t="n">
-        <v>1.41</v>
+        <v>9.66</v>
       </c>
       <c r="J15" t="n">
-        <v>2.17</v>
+        <v>28.93</v>
       </c>
       <c r="K15" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -9996,118 +9996,118 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0708</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1200</v>
+        <v>45452</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.85</v>
+        <v>3.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>5.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.03</v>
+        <v>3.58</v>
       </c>
       <c r="S15" t="n">
-        <v>1.105</v>
+        <v>3.7902</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.31</v>
+        <v>3.28</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>241.09</v>
+        <v>3.16</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>241.1x vs 2.7x median — trading at premium</t>
+          <t>3.2x vs 2.7x median — in-line</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>17.32</v>
+        <v>-6.43</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17.3x vs 1.5x median — trading at premium</t>
+          <t>-6.4x vs 1.5x median — trading at discount</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>-1.28</v>
+        <v>0.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v/>
       </c>
       <c r="AC15" t="n">
         <v/>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>P/S 241.1x vs 2.7x median — trading at premium | P/B 17.3x vs 1.5x median — trading at premium | EV/EBITDA -1.3x vs -0.6x median — trading at premium | Analyst target $8.00</t>
+          <t>P/S 3.2x vs 2.7x median — in-line | P/B -6.4x vs 1.5x median — trading at discount | EV/EBITDA 0.0x vs -0.6x median — trading at discount</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>0.38</v>
+        <v>-0.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>7.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>128.7</v>
+        <v>204.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.05</v>
+        <v>-4.58</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.21</v>
+        <v>11.98</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.38–$1.78 (ann. vol 129%) | ATR range: $-0.05–$2.21</t>
+          <t>1-SD 3mo range: $-0.08–$7.48 (ann. vol 204%) | ATR range: $-4.58–$11.98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>MCRP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.7</v>
+        <v>1.08</v>
       </c>
       <c r="C16" t="n">
-        <v>4.87</v>
+        <v>4.9</v>
       </c>
       <c r="D16" t="n">
-        <v>873941</v>
+        <v>725777</v>
       </c>
       <c r="E16" t="n">
-        <v>28.1</v>
+        <v>37.9</v>
       </c>
       <c r="F16" t="n">
-        <v>6.33</v>
+        <v>1.23</v>
       </c>
       <c r="G16" t="n">
-        <v>9.26</v>
+        <v>1.47</v>
       </c>
       <c r="H16" t="n">
-        <v>23.84</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>9.66</v>
+        <v>1.41</v>
       </c>
       <c r="J16" t="n">
-        <v>28.93</v>
+        <v>2.17</v>
       </c>
       <c r="K16" t="n">
-        <v>1.36</v>
+        <v>0.15</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -10116,80 +10116,80 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9186</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>7895</v>
+        <v>1200</v>
       </c>
       <c r="P16" t="n">
-        <v>6.77</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.15</v>
+        <v>1.55</v>
       </c>
       <c r="R16" t="n">
-        <v>3.58</v>
+        <v>1.03</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7902</v>
+        <v>1.105</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.28</v>
+        <v>2.31</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>3.16</v>
+        <v>241.09</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>3.2x vs 2.7x median — in-line</t>
+          <t>241.1x vs 2.7x median — trading at premium</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>-6.43</v>
+        <v>17.32</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>-6.4x vs 1.5x median — trading at discount</t>
+          <t>17.3x vs 1.5x median — trading at premium</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>0.03</v>
+        <v>-1.28</v>
       </c>
       <c r="AB16" t="n">
-        <v/>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
         <v/>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>P/S 3.2x vs 2.7x median — in-line | P/B -6.4x vs 1.5x median — trading at discount | EV/EBITDA 0.0x vs -0.6x median — trading at discount</t>
+          <t>P/S 241.1x vs 2.7x median — trading at premium | P/B 17.3x vs 1.5x median — trading at premium | EV/EBITDA -1.3x vs -0.6x median — trading at premium | Analyst target $8.00</t>
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>-0.08</v>
+        <v>0.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>7.48</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>204.5</v>
+        <v>128.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>-4.58</v>
+        <v>-0.05</v>
       </c>
       <c r="AI16" t="n">
-        <v>11.98</v>
+        <v>2.21</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.08–$7.48 (ann. vol 204%) | ATR range: $-4.58–$11.98</t>
+          <t>1-SD 3mo range: $0.38–$1.78 (ann. vol 129%) | ATR range: $-0.05–$2.21</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
         <v>4.73</v>
       </c>
       <c r="D17" t="n">
-        <v>758850</v>
+        <v>758946</v>
       </c>
       <c r="E17" t="n">
         <v>58.4</v>
@@ -10323,10 +10323,10 @@
         <v>0.4</v>
       </c>
       <c r="C18" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="D18" t="n">
-        <v>2225181</v>
+        <v>2226932</v>
       </c>
       <c r="E18" t="n">
         <v>26.3</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.398</v>
+        <v>0.3934</v>
       </c>
       <c r="O18" t="n">
         <v>10218</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.53</v>
+        <v>-1.67</v>
       </c>
       <c r="Q18" t="n">
         <v>0.4038</v>
@@ -10443,10 +10443,10 @@
         <v>9.69</v>
       </c>
       <c r="C19" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="D19" t="n">
-        <v>913074</v>
+        <v>913599</v>
       </c>
       <c r="E19" t="n">
         <v>73.59999999999999</v>
@@ -10476,16 +10476,16 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8.841699999999999</v>
+        <v>9.84</v>
       </c>
       <c r="O19" t="n">
         <v>5280</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.51</v>
+        <v>2.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.699999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="R19" t="n">
         <v>7.03</v>
@@ -10566,7 +10566,7 @@
         <v>3.87</v>
       </c>
       <c r="D20" t="n">
-        <v>2473445</v>
+        <v>2473911</v>
       </c>
       <c r="E20" t="n">
         <v>71.90000000000001</v>
@@ -10686,7 +10686,7 @@
         <v>3.58</v>
       </c>
       <c r="D21" t="n">
-        <v>992871</v>
+        <v>992890</v>
       </c>
       <c r="E21" t="n">
         <v>33.6</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4321</v>
+        <v>0.4343</v>
       </c>
       <c r="O21" t="n">
         <v>49975</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6</v>
+        <v>-0.09</v>
       </c>
       <c r="Q21" t="n">
         <v>0.524</v>
@@ -10923,10 +10923,10 @@
         <v>1.73</v>
       </c>
       <c r="C23" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="D23" t="n">
-        <v>2187149</v>
+        <v>2188194</v>
       </c>
       <c r="E23" t="n">
         <v>82.5</v>
@@ -10956,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7501</v>
+        <v>1.7503</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q23" t="n">
         <v>1.76</v>
@@ -11046,7 +11046,7 @@
         <v>3.49</v>
       </c>
       <c r="D24" t="n">
-        <v>1300121</v>
+        <v>1300130</v>
       </c>
       <c r="E24" t="n">
         <v>44.3</v>
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.7114</v>
+        <v>10.73</v>
       </c>
       <c r="O24" t="n">
         <v>7872</v>
       </c>
       <c r="P24" t="n">
-        <v>0.39</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>10.74</v>
@@ -11163,10 +11163,10 @@
         <v>13.04</v>
       </c>
       <c r="C25" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="D25" t="n">
-        <v>49081616</v>
+        <v>49161822</v>
       </c>
       <c r="E25" t="n">
         <v>42</v>
@@ -11283,10 +11283,10 @@
         <v>1.97</v>
       </c>
       <c r="C26" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="D26" t="n">
-        <v>10730366</v>
+        <v>10738695</v>
       </c>
       <c r="E26" t="n">
         <v>61.8</v>
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.97</v>
+        <v>1.9797</v>
       </c>
       <c r="O26" t="n">
         <v>495485</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.25</v>
+        <v>0.24</v>
       </c>
       <c r="Q26" t="n">
         <v>1.99</v>
@@ -11403,10 +11403,10 @@
         <v>0.1</v>
       </c>
       <c r="C27" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="D27" t="n">
-        <v>1389839</v>
+        <v>1390365</v>
       </c>
       <c r="E27" t="n">
         <v>34.9</v>
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0939</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>157511</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.39</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1587</v>
@@ -11526,7 +11526,7 @@
         <v>2.94</v>
       </c>
       <c r="D28" t="n">
-        <v>756207</v>
+        <v>756212</v>
       </c>
       <c r="E28" t="n">
         <v>59.5</v>
@@ -11646,7 +11646,7 @@
         <v>2.73</v>
       </c>
       <c r="D29" t="n">
-        <v>5303379</v>
+        <v>5303551</v>
       </c>
       <c r="E29" t="n">
         <v>70.3</v>
@@ -11766,7 +11766,7 @@
         <v>2.66</v>
       </c>
       <c r="D30" t="n">
-        <v>1534825</v>
+        <v>1534889</v>
       </c>
       <c r="E30" t="n">
         <v>43.8</v>
@@ -12006,7 +12006,7 @@
         <v>2.6</v>
       </c>
       <c r="D32" t="n">
-        <v>3390851</v>
+        <v>3390869</v>
       </c>
       <c r="E32" t="n">
         <v>64.3</v>
@@ -12126,7 +12126,7 @@
         <v>2.47</v>
       </c>
       <c r="D33" t="n">
-        <v>568595</v>
+        <v>568642</v>
       </c>
       <c r="E33" t="n">
         <v>71.59999999999999</v>
@@ -12236,240 +12236,240 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HVII</t>
+          <t>RNXT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7.84</v>
+        <v>1.42</v>
       </c>
       <c r="C34" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="D34" t="n">
-        <v>1327745</v>
+        <v>748719</v>
       </c>
       <c r="E34" t="n">
-        <v>29.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>9.460000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="G34" t="n">
-        <v>10.01</v>
+        <v>1.06</v>
       </c>
       <c r="H34" t="n">
-        <v>10.27</v>
+        <v>0.98</v>
       </c>
       <c r="I34" t="n">
-        <v>10.22</v>
+        <v>1.01</v>
       </c>
       <c r="J34" t="n">
-        <v>10.33</v>
+        <v>0.95</v>
       </c>
       <c r="K34" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>7.7</v>
+        <v>1.4653</v>
       </c>
       <c r="O34" t="n">
-        <v>6127</v>
+        <v>5047</v>
       </c>
       <c r="P34" t="n">
-        <v>-1.53</v>
+        <v>3.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>1.47</v>
       </c>
       <c r="R34" t="n">
-        <v>6.09</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>7.68</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>-1.79</v>
+        <v>-6.71</v>
       </c>
       <c r="V34" t="b">
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v/>
+        <v>32.43</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>32.4x vs 3.0x median — trading at premium</t>
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>-18.98</v>
+        <v>7.14</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>-19.0x vs 0.8x median — trading at discount</t>
+          <t>7.1x vs 1.0x median — trading at premium</t>
         </is>
       </c>
       <c r="AA34" t="n">
-        <v/>
+        <v>-3.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AC34" t="n">
         <v/>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>P/B -19.0x vs 0.8x median — trading at discount | Analyst target $17.00</t>
+          <t>P/S 32.4x vs 3.0x median — trading at premium | P/B 7.1x vs 1.0x median — trading at premium | EV/EBITDA -3.6x vs -0.9x median — trading at premium | Analyst target $7.00</t>
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>6.31</v>
+        <v>0.84</v>
       </c>
       <c r="AF34" t="n">
-        <v>9.369999999999999</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>39.1</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.63</v>
+        <v>0.24</v>
       </c>
       <c r="AI34" t="n">
-        <v>12.05</v>
+        <v>2.6</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $6.31–$9.37 (ann. vol 39%) | ATR range: $3.63–$12.05</t>
+          <t>1-SD 3mo range: $0.84–$2.00 (ann. vol 82%) | ATR range: $0.24–$2.60</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RNXT</t>
+          <t>HVII</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.42</v>
+        <v>7.84</v>
       </c>
       <c r="C35" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="D35" t="n">
-        <v>747426</v>
+        <v>1329507</v>
       </c>
       <c r="E35" t="n">
-        <v>66.59999999999999</v>
+        <v>29.7</v>
       </c>
       <c r="F35" t="n">
-        <v>1.19</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>1.06</v>
+        <v>10.01</v>
       </c>
       <c r="H35" t="n">
-        <v>0.98</v>
+        <v>10.27</v>
       </c>
       <c r="I35" t="n">
-        <v>1.01</v>
+        <v>10.22</v>
       </c>
       <c r="J35" t="n">
-        <v>0.95</v>
+        <v>10.33</v>
       </c>
       <c r="K35" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.3956</v>
+        <v>7.91</v>
       </c>
       <c r="O35" t="n">
-        <v>5047</v>
+        <v>6127</v>
       </c>
       <c r="P35" t="n">
-        <v>-1.37</v>
+        <v>1.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="R35" t="n">
-        <v>1.24</v>
+        <v>6.09</v>
       </c>
       <c r="S35" t="n">
-        <v>1.32</v>
+        <v>7.68</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>-6.71</v>
+        <v>-1.79</v>
       </c>
       <c r="V35" t="b">
         <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>32.43</v>
+        <v/>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>32.4x vs 3.0x median — trading at premium</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>7.14</v>
+        <v>-18.98</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>7.1x vs 1.0x median — trading at premium</t>
+          <t>-19.0x vs 0.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>-3.63</v>
+        <v/>
       </c>
       <c r="AB35" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AC35" t="n">
         <v/>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>P/S 32.4x vs 3.0x median — trading at premium | P/B 7.1x vs 1.0x median — trading at premium | EV/EBITDA -3.6x vs -0.9x median — trading at premium | Analyst target $7.00</t>
+          <t>P/B -19.0x vs 0.8x median — trading at discount | Analyst target $17.00</t>
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>0.84</v>
+        <v>6.31</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AG35" t="n">
-        <v>82.40000000000001</v>
+        <v>39.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.24</v>
+        <v>3.63</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.6</v>
+        <v>12.05</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.84–$2.00 (ann. vol 82%) | ATR range: $0.24–$2.60</t>
+          <t>1-SD 3mo range: $6.31–$9.37 (ann. vol 39%) | ATR range: $3.63–$12.05</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
         <v>2.38</v>
       </c>
       <c r="D36" t="n">
-        <v>6552045</v>
+        <v>6553257</v>
       </c>
       <c r="E36" t="n">
         <v>65.8</v>
@@ -12516,13 +12516,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>13.66</v>
+        <v>13.73</v>
       </c>
       <c r="O36" t="n">
         <v>65774</v>
       </c>
       <c r="P36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="Q36" t="n">
         <v>13.9</v>
@@ -12606,7 +12606,7 @@
         <v>2.32</v>
       </c>
       <c r="D37" t="n">
-        <v>3745132</v>
+        <v>3745144</v>
       </c>
       <c r="E37" t="n">
         <v>67.09999999999999</v>
@@ -12726,7 +12726,7 @@
         <v>2.31</v>
       </c>
       <c r="D38" t="n">
-        <v>4682509</v>
+        <v>4682738</v>
       </c>
       <c r="E38" t="n">
         <v>81.90000000000001</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.55</v>
+        <v>4.4639</v>
       </c>
       <c r="O38" t="n">
         <v>40316</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.55</v>
+        <v>-2.43</v>
       </c>
       <c r="Q38" t="n">
         <v>4.589</v>
@@ -13083,10 +13083,10 @@
         <v>9.140000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="D41" t="n">
-        <v>4049731</v>
+        <v>4052706</v>
       </c>
       <c r="E41" t="n">
         <v>52.7</v>
@@ -13116,13 +13116,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>9.262</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>6191</v>
       </c>
       <c r="P41" t="n">
-        <v>1.33</v>
+        <v>-0.33</v>
       </c>
       <c r="Q41" t="n">
         <v>9.262</v>
@@ -13203,10 +13203,10 @@
         <v>7.19</v>
       </c>
       <c r="C42" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="D42" t="n">
-        <v>92257440</v>
+        <v>92298873</v>
       </c>
       <c r="E42" t="n">
         <v>51.6</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.11</v>
+        <v>7.35</v>
       </c>
       <c r="O42" t="n">
         <v>13347</v>
       </c>
       <c r="P42" t="n">
-        <v>-1.39</v>
+        <v>1.94</v>
       </c>
       <c r="Q42" t="n">
         <v>16.41</v>
@@ -13566,7 +13566,7 @@
         <v>2.14</v>
       </c>
       <c r="D45" t="n">
-        <v>7897102</v>
+        <v>7897547</v>
       </c>
       <c r="E45" t="n">
         <v>77.90000000000001</v>
@@ -13596,13 +13596,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6.0462</v>
+        <v>6.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="Q45" t="n">
         <v>6.12</v>
@@ -13686,7 +13686,7 @@
         <v>2.14</v>
       </c>
       <c r="D46" t="n">
-        <v>7391585</v>
+        <v>7391588</v>
       </c>
       <c r="E46" t="n">
         <v>38.8</v>
@@ -13923,10 +13923,10 @@
         <v>1.52</v>
       </c>
       <c r="C48" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="D48" t="n">
-        <v>11363687</v>
+        <v>11365903</v>
       </c>
       <c r="E48" t="n">
         <v>61.2</v>
@@ -13956,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.5003</v>
+        <v>1.51</v>
       </c>
       <c r="O48" t="n">
         <v>543273</v>
       </c>
       <c r="P48" t="n">
-        <v>-1.3</v>
+        <v>-0.66</v>
       </c>
       <c r="Q48" t="n">
         <v>1.525</v>
@@ -14046,7 +14046,7 @@
         <v>2.04</v>
       </c>
       <c r="D49" t="n">
-        <v>928797</v>
+        <v>928806</v>
       </c>
       <c r="E49" t="n">
         <v>71.90000000000001</v>
@@ -14156,38 +14156,38 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CTXR</t>
+          <t>UPXI</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6</v>
+        <v>1.09</v>
       </c>
       <c r="C50" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="D50" t="n">
-        <v>655145</v>
+        <v>2055952</v>
       </c>
       <c r="E50" t="n">
-        <v>48.7</v>
+        <v>66.7</v>
       </c>
       <c r="F50" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="G50" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H50" t="n">
-        <v>0.78</v>
+        <v>2.01</v>
       </c>
       <c r="I50" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="J50" t="n">
-        <v>0.78</v>
+        <v>1.42</v>
       </c>
       <c r="K50" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -14196,800 +14196,800 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6001</v>
+        <v>1.06</v>
       </c>
       <c r="O50" t="n">
-        <v>9914</v>
+        <v>13913</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.13</v>
+        <v>-2.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.6449</v>
+        <v>1.12</v>
       </c>
       <c r="R50" t="n">
-        <v>0.5733</v>
+        <v>0.88</v>
       </c>
       <c r="S50" t="n">
-        <v>0.58</v>
+        <v>1.0497</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>-3.48</v>
+        <v>-3.25</v>
       </c>
       <c r="V50" t="b">
         <v>1</v>
       </c>
       <c r="W50" t="n">
-        <v>2.33</v>
+        <v>3.06</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2.3x vs 3.0x median — trading at discount</t>
+          <t>3.1x vs 0.7x median — trading at premium</t>
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>0.25</v>
+        <v>-1.4</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.2x vs 1.0x median — trading at discount</t>
+          <t>-1.4x vs 0.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AA50" t="n">
-        <v/>
+        <v>-1.43</v>
       </c>
       <c r="AB50" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="AC50" t="n">
         <v/>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>P/S 2.3x vs 3.0x median — trading at discount | P/B 0.2x vs 1.0x median — trading at discount | Analyst target $4.00</t>
+          <t>P/S 3.1x vs 0.7x median — trading at premium | P/B -1.4x vs 0.8x median — trading at discount | EV/EBITDA -1.4x vs -1.4x median — in-line | Analyst target $1.30</t>
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>112.4</v>
+        <v>120.8</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.03</v>
+        <v>0.46</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.26–$0.94 (ann. vol 112%) | ATR range: $-0.03–$1.24</t>
+          <t>1-SD 3mo range: $0.43–$1.75 (ann. vol 121%) | ATR range: $0.46–$1.72</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CTXR</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.64</v>
+        <v>0.6</v>
       </c>
       <c r="C51" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="D51" t="n">
-        <v>9072066</v>
+        <v>655155</v>
       </c>
       <c r="E51" t="n">
-        <v>85.40000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="F51" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="G51" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="J51" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="K51" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.61</v>
+        <v>0.6001</v>
       </c>
       <c r="O51" t="n">
-        <v>54639</v>
+        <v>9914</v>
       </c>
       <c r="P51" t="n">
-        <v>-2.01</v>
+        <v>-0.13</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.8</v>
+        <v>0.6449</v>
       </c>
       <c r="R51" t="n">
-        <v>1.06</v>
+        <v>0.5733</v>
       </c>
       <c r="S51" t="n">
-        <v>1.62</v>
+        <v>0.58</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>-1.41</v>
+        <v>-3.48</v>
       </c>
       <c r="V51" t="b">
         <v>1</v>
       </c>
       <c r="W51" t="n">
-        <v/>
+        <v>2.33</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>2.3x vs 3.0x median — trading at discount</t>
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>1.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>1.3x vs 0.8x median — trading at premium</t>
+          <t>0.2x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AA51" t="n">
         <v/>
       </c>
       <c r="AB51" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.31</v>
+        <v/>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>P/B 1.3x vs 0.8x median — trading at premium | Analyst target $1.60 | Graham # $4.31</t>
+          <t>P/S 2.3x vs 3.0x median — trading at discount | P/B 0.2x vs 1.0x median — trading at discount | Analyst target $4.00</t>
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>-0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AF51" t="n">
-        <v>3.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AG51" t="n">
-        <v>235.3</v>
+        <v>112.4</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.31</v>
+        <v>-0.03</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.97</v>
+        <v>1.24</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.29–$3.57 (ann. vol 235%) | ATR range: $0.31–$2.97</t>
+          <t>1-SD 3mo range: $0.26–$0.94 (ann. vol 112%) | ATR range: $-0.03–$1.24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UPXI</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="C52" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="D52" t="n">
-        <v>2051435</v>
+        <v>9081798</v>
       </c>
       <c r="E52" t="n">
-        <v>66.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H52" t="n">
-        <v>2.01</v>
+        <v>0.8</v>
       </c>
       <c r="I52" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="J52" t="n">
-        <v>1.42</v>
+        <v>0.95</v>
       </c>
       <c r="K52" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
       <c r="N52" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O52" t="n">
+        <v>54639</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R52" t="n">
         <v>1.06</v>
       </c>
-      <c r="O52" t="n">
-        <v>13913</v>
-      </c>
-      <c r="P52" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.88</v>
-      </c>
       <c r="S52" t="n">
-        <v>1.0497</v>
+        <v>1.62</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>-3.25</v>
+        <v>-1.41</v>
       </c>
       <c r="V52" t="b">
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>3.06</v>
+        <v/>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>3.1x vs 0.7x median — trading at premium</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>-1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>-1.4x vs 0.8x median — trading at discount</t>
+          <t>1.3x vs 0.8x median — trading at premium</t>
         </is>
       </c>
       <c r="AA52" t="n">
-        <v>-1.43</v>
+        <v/>
       </c>
       <c r="AB52" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AC52" t="n">
-        <v/>
+        <v>4.31</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>P/S 3.1x vs 0.7x median — trading at premium | P/B -1.4x vs 0.8x median — trading at discount | EV/EBITDA -1.4x vs -1.4x median — in-line | Analyst target $1.30</t>
+          <t>P/B 1.3x vs 0.8x median — trading at premium | Analyst target $1.60 | Graham # $4.31</t>
         </is>
       </c>
       <c r="AE52" t="n">
-        <v>0.43</v>
+        <v>-0.29</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.75</v>
+        <v>3.57</v>
       </c>
       <c r="AG52" t="n">
-        <v>120.8</v>
+        <v>235.3</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.72</v>
+        <v>2.97</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.43–$1.75 (ann. vol 121%) | ATR range: $0.46–$1.72</t>
+          <t>1-SD 3mo range: $-0.29–$3.57 (ann. vol 235%) | ATR range: $0.31–$2.97</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BNED</t>
+          <t>GOSS</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12.61</v>
+        <v>0.2</v>
       </c>
       <c r="C53" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="D53" t="n">
-        <v>2320545</v>
+        <v>4862567</v>
       </c>
       <c r="E53" t="n">
-        <v>56.1</v>
+        <v>62.1</v>
       </c>
       <c r="F53" t="n">
-        <v>12.29</v>
+        <v>0.17</v>
       </c>
       <c r="G53" t="n">
-        <v>11.98</v>
+        <v>0.2</v>
       </c>
       <c r="H53" t="n">
-        <v>10.42</v>
+        <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>12.2</v>
+        <v>0.17</v>
       </c>
       <c r="J53" t="n">
-        <v>9.84</v>
+        <v>1.2</v>
       </c>
       <c r="K53" t="n">
-        <v>0.52</v>
+        <v>0.02</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>12.75</v>
+        <v>0.2044</v>
       </c>
       <c r="O53" t="n">
-        <v>37871</v>
+        <v>10241</v>
       </c>
       <c r="P53" t="n">
-        <v>0.71</v>
+        <v>-0.44</v>
       </c>
       <c r="Q53" t="n">
-        <v>12.75</v>
+        <v>0.2094</v>
       </c>
       <c r="R53" t="n">
-        <v>11.7</v>
+        <v>0.1508</v>
       </c>
       <c r="S53" t="n">
-        <v>12.4</v>
+        <v>0.178</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>-2.05</v>
+        <v>-13.3</v>
       </c>
       <c r="V53" t="b">
         <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>0.25</v>
+        <v>1.88</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>0.3x vs 0.3x median — trading at discount</t>
+          <t>1.9x vs 3.0x median — trading at discount</t>
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>1.47</v>
+        <v>-1.07</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1.5x vs 0.9x median — trading at premium</t>
+          <t>-1.1x vs 1.0x median — trading at discount</t>
         </is>
       </c>
       <c r="AA53" t="n">
-        <v>9.31</v>
+        <v>-0.43</v>
       </c>
       <c r="AB53" t="n">
-        <v>17.25</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
-        <v>9.710000000000001</v>
+        <v/>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>P/S 0.3x vs 0.3x median — trading at discount | P/B 1.5x vs 0.9x median — trading at premium | EV/EBITDA 9.3x vs 9.3x median — in-line | Analyst target $17.25 | Graham # $9.71</t>
+          <t>P/S 1.9x vs 3.0x median — trading at discount | P/B -1.1x vs 1.0x median — trading at discount | EV/EBITDA -0.4x vs -0.9x median — trading at discount | Analyst target $1.66</t>
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>8.68</v>
+        <v>-0</v>
       </c>
       <c r="AF53" t="n">
-        <v>16.54</v>
+        <v>0.41</v>
       </c>
       <c r="AG53" t="n">
-        <v>62.3</v>
+        <v>200.8</v>
       </c>
       <c r="AH53" t="n">
-        <v>9.01</v>
+        <v>0.06</v>
       </c>
       <c r="AI53" t="n">
-        <v>16.21</v>
+        <v>0.35</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $8.68–$16.54 (ann. vol 62%) | ATR range: $9.01–$16.21</t>
+          <t>1-SD 3mo range: $-0.00–$0.41 (ann. vol 201%) | ATR range: $0.06–$0.35</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GOSS</t>
+          <t>BNED</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2</v>
+        <v>12.61</v>
       </c>
       <c r="C54" t="n">
         <v>1.95</v>
       </c>
       <c r="D54" t="n">
-        <v>4856926</v>
+        <v>2320586</v>
       </c>
       <c r="E54" t="n">
-        <v>62.1</v>
+        <v>56.1</v>
       </c>
       <c r="F54" t="n">
-        <v>0.17</v>
+        <v>12.29</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2</v>
+        <v>11.98</v>
       </c>
       <c r="H54" t="n">
-        <v>0.92</v>
+        <v>10.42</v>
       </c>
       <c r="I54" t="n">
-        <v>0.17</v>
+        <v>12.2</v>
       </c>
       <c r="J54" t="n">
-        <v>1.2</v>
+        <v>9.84</v>
       </c>
       <c r="K54" t="n">
-        <v>0.02</v>
+        <v>0.52</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2019</v>
+        <v>12.75</v>
       </c>
       <c r="O54" t="n">
-        <v>10241</v>
+        <v>37871</v>
       </c>
       <c r="P54" t="n">
-        <v>-1.66</v>
+        <v>0.71</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.2094</v>
+        <v>12.75</v>
       </c>
       <c r="R54" t="n">
-        <v>0.1508</v>
+        <v>11.7</v>
       </c>
       <c r="S54" t="n">
-        <v>0.178</v>
+        <v>12.4</v>
       </c>
       <c r="T54" t="n">
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>-13.3</v>
+        <v>-2.05</v>
       </c>
       <c r="V54" t="b">
         <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>1.88</v>
+        <v>0.25</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>1.9x vs 3.0x median — trading at discount</t>
+          <t>0.3x vs 0.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>-1.07</v>
+        <v>1.47</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>-1.1x vs 1.0x median — trading at discount</t>
+          <t>1.5x vs 0.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AA54" t="n">
-        <v>-0.43</v>
+        <v>9.31</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.66</v>
+        <v>17.25</v>
       </c>
       <c r="AC54" t="n">
-        <v/>
+        <v>9.710000000000001</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>P/S 1.9x vs 3.0x median — trading at discount | P/B -1.1x vs 1.0x median — trading at discount | EV/EBITDA -0.4x vs -0.9x median — trading at discount | Analyst target $1.66</t>
+          <t>P/S 0.3x vs 0.3x median — trading at discount | P/B 1.5x vs 0.9x median — trading at premium | EV/EBITDA 9.3x vs 9.3x median — in-line | Analyst target $17.25 | Graham # $9.71</t>
         </is>
       </c>
       <c r="AE54" t="n">
-        <v>-0</v>
+        <v>8.68</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.41</v>
+        <v>16.54</v>
       </c>
       <c r="AG54" t="n">
-        <v>200.8</v>
+        <v>62.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.06</v>
+        <v>9.01</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.35</v>
+        <v>16.21</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.00–$0.41 (ann. vol 201%) | ATR range: $0.06–$0.35</t>
+          <t>1-SD 3mo range: $8.68–$16.54 (ann. vol 62%) | ATR range: $9.01–$16.21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STEX</t>
+          <t>FLWS</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.76</v>
+        <v>3.92</v>
       </c>
       <c r="C55" t="n">
         <v>1.95</v>
       </c>
       <c r="D55" t="n">
-        <v>731074</v>
+        <v>832441</v>
       </c>
       <c r="E55" t="n">
-        <v>45.3</v>
+        <v>45.7</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8100000000000001</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>0.87</v>
+        <v>3.98</v>
       </c>
       <c r="H55" t="n">
-        <v>1.95</v>
+        <v>4.08</v>
       </c>
       <c r="I55" t="n">
-        <v>0.83</v>
+        <v>3.92</v>
       </c>
       <c r="J55" t="n">
-        <v>2.01</v>
+        <v>3.84</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7569</v>
+        <v>3.901</v>
       </c>
       <c r="O55" t="n">
-        <v>9513</v>
+        <v>23267</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.41</v>
+        <v>-0.48</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.85</v>
+        <v>4.08</v>
       </c>
       <c r="R55" t="n">
-        <v>0.7311</v>
+        <v>3.88</v>
       </c>
       <c r="S55" t="n">
-        <v>0.7659</v>
+        <v>3.8225</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0.78</v>
+        <v>-2.49</v>
       </c>
       <c r="V55" t="b">
         <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>1169.23</v>
+        <v>0.16</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>1169.2x vs 9.4x median — trading at premium</t>
+          <t>0.2x vs 0.3x median — trading at discount</t>
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>0.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>0.3x vs 0.8x median — trading at discount</t>
+          <t>1.3x vs 0.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AA55" t="n">
-        <v>-0.79</v>
+        <v>-26.01</v>
       </c>
       <c r="AB55" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AC55" t="n">
         <v/>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>P/S 1169.2x vs 9.4x median — trading at premium | P/B 0.3x vs 0.8x median — trading at discount | EV/EBITDA -0.8x vs -0.8x median — in-line | Analyst target $4.00</t>
+          <t>P/S 0.2x vs 0.3x median — trading at discount | P/B 1.3x vs 0.9x median — trading at premium | EV/EBITDA -26.0x vs 9.3x median — trading at discount | Analyst target $5.50</t>
         </is>
       </c>
       <c r="AE55" t="n">
-        <v>0.3</v>
+        <v>2.42</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.22</v>
+        <v>5.42</v>
       </c>
       <c r="AG55" t="n">
-        <v>121.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.03</v>
+        <v>2.71</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.54</v>
+        <v>5.13</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.30–$1.22 (ann. vol 122%) | ATR range: $-0.03–$1.54</t>
+          <t>1-SD 3mo range: $2.42–$5.42 (ann. vol 77%) | ATR range: $2.71–$5.13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FLWS</t>
+          <t>STEX</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.92</v>
+        <v>0.76</v>
       </c>
       <c r="C56" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="D56" t="n">
-        <v>832044</v>
+        <v>731074</v>
       </c>
       <c r="E56" t="n">
-        <v>45.7</v>
+        <v>45.3</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>3.98</v>
+        <v>0.87</v>
       </c>
       <c r="H56" t="n">
-        <v>4.08</v>
+        <v>1.95</v>
       </c>
       <c r="I56" t="n">
-        <v>3.92</v>
+        <v>0.83</v>
       </c>
       <c r="J56" t="n">
-        <v>3.84</v>
+        <v>2.01</v>
       </c>
       <c r="K56" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.901</v>
+        <v>0.7569</v>
       </c>
       <c r="O56" t="n">
-        <v>23267</v>
+        <v>9513</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.48</v>
+        <v>-0.41</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.08</v>
+        <v>0.85</v>
       </c>
       <c r="R56" t="n">
-        <v>3.88</v>
+        <v>0.7311</v>
       </c>
       <c r="S56" t="n">
-        <v>3.8225</v>
+        <v>0.7659</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>-2.49</v>
+        <v>0.78</v>
       </c>
       <c r="V56" t="b">
         <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>0.16</v>
+        <v>1169.23</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>0.2x vs 0.3x median — trading at discount</t>
+          <t>1169.2x vs 9.4x median — trading at premium</t>
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>1.3</v>
+        <v>0.28</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>1.3x vs 0.9x median — trading at premium</t>
+          <t>0.3x vs 0.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AA56" t="n">
-        <v>-26.01</v>
+        <v>-0.79</v>
       </c>
       <c r="AB56" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AC56" t="n">
         <v/>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>P/S 0.2x vs 0.3x median — trading at discount | P/B 1.3x vs 0.9x median — trading at premium | EV/EBITDA -26.0x vs 9.3x median — trading at discount | Analyst target $5.50</t>
+          <t>P/S 1169.2x vs 9.4x median — trading at premium | P/B 0.3x vs 0.8x median — trading at discount | EV/EBITDA -0.8x vs -0.8x median — in-line | Analyst target $4.00</t>
         </is>
       </c>
       <c r="AE56" t="n">
-        <v>2.42</v>
+        <v>0.3</v>
       </c>
       <c r="AF56" t="n">
-        <v>5.42</v>
+        <v>1.22</v>
       </c>
       <c r="AG56" t="n">
-        <v>76.59999999999999</v>
+        <v>121.6</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.71</v>
+        <v>-0.03</v>
       </c>
       <c r="AI56" t="n">
-        <v>5.13</v>
+        <v>1.54</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.42–$5.42 (ann. vol 77%) | ATR range: $2.71–$5.13</t>
+          <t>1-SD 3mo range: $0.30–$1.22 (ann. vol 122%) | ATR range: $-0.03–$1.54</t>
         </is>
       </c>
     </row>
@@ -15006,7 +15006,7 @@
         <v>1.92</v>
       </c>
       <c r="D57" t="n">
-        <v>1169366</v>
+        <v>1169418</v>
       </c>
       <c r="E57" t="n">
         <v>75.90000000000001</v>
@@ -15246,7 +15246,7 @@
         <v>1.91</v>
       </c>
       <c r="D59" t="n">
-        <v>3000272</v>
+        <v>3000291</v>
       </c>
       <c r="E59" t="n">
         <v>59.2</v>
@@ -15486,7 +15486,7 @@
         <v>1.89</v>
       </c>
       <c r="D61" t="n">
-        <v>1456737</v>
+        <v>1456739</v>
       </c>
       <c r="E61" t="n">
         <v>67.8</v>
@@ -15723,10 +15723,10 @@
         <v>0.96</v>
       </c>
       <c r="C63" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="D63" t="n">
-        <v>5930917</v>
+        <v>5933662</v>
       </c>
       <c r="E63" t="n">
         <v>42.7</v>
@@ -15756,13 +15756,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.9584</v>
+        <v>0.9506</v>
       </c>
       <c r="O63" t="n">
         <v>95246</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.89</v>
       </c>
       <c r="Q63" t="n">
         <v>0.97</v>
@@ -15843,10 +15843,10 @@
         <v>1.49</v>
       </c>
       <c r="C64" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="D64" t="n">
-        <v>1664395</v>
+        <v>1664959</v>
       </c>
       <c r="E64" t="n">
         <v>17</v>
@@ -15876,13 +15876,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.46</v>
+        <v>1.4796</v>
       </c>
       <c r="O64" t="n">
         <v>7426</v>
       </c>
       <c r="P64" t="n">
-        <v>-2.43</v>
+        <v>-1.12</v>
       </c>
       <c r="Q64" t="n">
         <v>2.77</v>
@@ -15966,7 +15966,7 @@
         <v>1.73</v>
       </c>
       <c r="D65" t="n">
-        <v>3551151</v>
+        <v>3551154</v>
       </c>
       <c r="E65" t="n">
         <v>61.9</v>
@@ -15996,16 +15996,16 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.11</v>
+        <v>4.2701</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0.12</v>
+        <v>4.02</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="R65" t="n">
         <v>4.01</v>
@@ -16086,7 +16086,7 @@
         <v>1.69</v>
       </c>
       <c r="D66" t="n">
-        <v>2555377</v>
+        <v>2555432</v>
       </c>
       <c r="E66" t="n">
         <v>80.59999999999999</v>
@@ -16116,13 +16116,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.9729</v>
+        <v>1.9726</v>
       </c>
       <c r="O66" t="n">
         <v>11650</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.86</v>
+        <v>-0.87</v>
       </c>
       <c r="Q66" t="n">
         <v>2</v>
@@ -16206,7 +16206,7 @@
         <v>1.69</v>
       </c>
       <c r="D67" t="n">
-        <v>19310976</v>
+        <v>19311035</v>
       </c>
       <c r="E67" t="n">
         <v>54.5</v>
@@ -16566,7 +16566,7 @@
         <v>1.62</v>
       </c>
       <c r="D70" t="n">
-        <v>722584</v>
+        <v>722668</v>
       </c>
       <c r="E70" t="n">
         <v>38.9</v>
@@ -16596,13 +16596,13 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0.7504</v>
+        <v>0.7605</v>
       </c>
       <c r="O70" t="n">
         <v>9470</v>
       </c>
       <c r="P70" t="n">
-        <v>0.13</v>
+        <v>1.48</v>
       </c>
       <c r="Q70" t="n">
         <v>0.8671</v>
@@ -16686,7 +16686,7 @@
         <v>1.62</v>
       </c>
       <c r="D71" t="n">
-        <v>3977720</v>
+        <v>3978238</v>
       </c>
       <c r="E71" t="n">
         <v>62.9</v>
@@ -16716,13 +16716,13 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>17.65</v>
+        <v>16.2273</v>
       </c>
       <c r="O71" t="n">
         <v>16161</v>
       </c>
       <c r="P71" t="n">
-        <v>0.51</v>
+        <v>-7.59</v>
       </c>
       <c r="Q71" t="n">
         <v>17.65</v>
@@ -16806,7 +16806,7 @@
         <v>1.61</v>
       </c>
       <c r="D72" t="n">
-        <v>1351486</v>
+        <v>1351645</v>
       </c>
       <c r="E72" t="n">
         <v>67.59999999999999</v>
@@ -16926,7 +16926,7 @@
         <v>1.59</v>
       </c>
       <c r="D73" t="n">
-        <v>1937291</v>
+        <v>1937340</v>
       </c>
       <c r="E73" t="n">
         <v>64.40000000000001</v>
@@ -17166,7 +17166,7 @@
         <v>1.54</v>
       </c>
       <c r="D75" t="n">
-        <v>835090</v>
+        <v>835094</v>
       </c>
       <c r="E75" t="n">
         <v>63.2</v>
@@ -17406,7 +17406,7 @@
         <v>1.5</v>
       </c>
       <c r="D77" t="n">
-        <v>1250762</v>
+        <v>1250999</v>
       </c>
       <c r="E77" t="n">
         <v>55.4</v>
@@ -17436,13 +17436,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-2.41</v>
+        <v>0.27</v>
       </c>
       <c r="Q77" t="n">
         <v>1.8982</v>
@@ -17526,7 +17526,7 @@
         <v>1.5</v>
       </c>
       <c r="D78" t="n">
-        <v>1403282</v>
+        <v>1403439</v>
       </c>
       <c r="E78" t="n">
         <v>57.6</v>
@@ -17556,19 +17556,19 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.92</v>
+        <v>3.8726</v>
       </c>
       <c r="O78" t="n">
         <v>5620</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.13</v>
+        <v>-1.34</v>
       </c>
       <c r="Q78" t="n">
         <v>3.99</v>
       </c>
       <c r="R78" t="n">
-        <v>3.89</v>
+        <v>3.8726</v>
       </c>
       <c r="S78" t="n">
         <v>3.8915</v>
@@ -19501,7 +19501,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HVII</t>
+          <t>RNXT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -19524,13 +19524,13 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Items: 5.07, 8.01 (routine)</t>
+          <t>Items: 8.01 (routine)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0001493152-26-039917</t>
+          <t>0001493152-26-039472</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -19565,13 +19565,13 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
+          <t>Items: 5.07, 8.01 (routine)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0001493152-26-039511</t>
+          <t>0001493152-26-039917</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -19583,7 +19583,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RNXT</t>
+          <t>HVII</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -19606,13 +19606,13 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Items: 8.01 (routine)</t>
+          <t>Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0001493152-26-039472</t>
+          <t>0001493152-26-039511</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>38.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7605</v>
+        <v>0.7578</v>
       </c>
       <c r="Q3" t="n">
         <v>9470</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="S3" t="n">
         <v>0.777</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>73.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>9.84</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>5280</v>
       </c>
       <c r="R4" t="n">
-        <v>2.93</v>
+        <v>-3.77</v>
       </c>
       <c r="S4" t="n">
         <v>7.86</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>64.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.54</v>
+        <v>3.5401</v>
       </c>
       <c r="Q6" t="n">
         <v>60653</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1244,13 +1244,13 @@
         <v>66.59999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4653</v>
+        <v>1.42</v>
       </c>
       <c r="Q8" t="n">
         <v>5047</v>
       </c>
       <c r="R8" t="n">
-        <v>3.55</v>
+        <v>0.35</v>
       </c>
       <c r="S8" t="n">
         <v>1.32</v>
@@ -1276,15 +1276,15 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="9">
@@ -1342,13 +1342,13 @@
         <v>59.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3.8144</v>
+        <v>3.8371</v>
       </c>
       <c r="Q9" t="n">
         <v>10324</v>
       </c>
       <c r="R9" t="n">
-        <v>4.5</v>
+        <v>5.13</v>
       </c>
       <c r="S9" t="n">
         <v>3.72</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1734,13 +1734,13 @@
         <v>60.9</v>
       </c>
       <c r="P13" t="n">
-        <v>4.38</v>
+        <v>4.3495</v>
       </c>
       <c r="Q13" t="n">
         <v>9477</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.23</v>
+        <v>-0.92</v>
       </c>
       <c r="S13" t="n">
         <v>4.2265</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1832,13 +1832,13 @@
         <v>56.1</v>
       </c>
       <c r="P14" t="n">
-        <v>12.75</v>
+        <v>12.36</v>
       </c>
       <c r="Q14" t="n">
         <v>37871</v>
       </c>
       <c r="R14" t="n">
-        <v>0.71</v>
+        <v>-2.37</v>
       </c>
       <c r="S14" t="n">
         <v>12.4</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2224,13 +2224,13 @@
         <v>57</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
         <v>20696</v>
       </c>
       <c r="R18" t="n">
-        <v>0.46</v>
+        <v>-0.05</v>
       </c>
       <c r="S18" t="n">
         <v>1.9501</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2322,13 +2322,13 @@
         <v>30.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0.17</v>
+        <v>0.1808</v>
       </c>
       <c r="Q19" t="n">
         <v>74807</v>
       </c>
       <c r="R19" t="n">
-        <v>1.92</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="S19" t="n">
         <v>0.2037</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>26.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3934</v>
+        <v>0.3915</v>
       </c>
       <c r="Q20" t="n">
         <v>10218</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.67</v>
+        <v>-2.15</v>
       </c>
       <c r="S20" t="n">
         <v>0.4813</v>
@@ -2441,7 +2441,7 @@
         <v>0.4038</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3916</v>
+        <v>0.39</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2518,13 +2518,13 @@
         <v>70.3</v>
       </c>
       <c r="P21" t="n">
-        <v>11.15</v>
+        <v>11.3</v>
       </c>
       <c r="Q21" t="n">
         <v>25217</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.41</v>
+        <v>-0.09</v>
       </c>
       <c r="S21" t="n">
         <v>10.74</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2616,13 +2616,13 @@
         <v>71.90000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>2.42</v>
+        <v>2.3862</v>
       </c>
       <c r="Q22" t="n">
         <v>5717</v>
       </c>
       <c r="R22" t="n">
-        <v>-1.22</v>
+        <v>-2.6</v>
       </c>
       <c r="S22" t="n">
         <v>2.1345</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>61.8</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9797</v>
+        <v>1.9703</v>
       </c>
       <c r="Q23" t="n">
         <v>495485</v>
       </c>
       <c r="R23" t="n">
-        <v>0.24</v>
+        <v>-0.24</v>
       </c>
       <c r="S23" t="n">
         <v>1.6781</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2812,13 +2812,13 @@
         <v>71.90000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
         <v>20075</v>
       </c>
       <c r="R24" t="n">
-        <v>0.21</v>
+        <v>-1.05</v>
       </c>
       <c r="S24" t="n">
         <v>2.43</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2910,13 +2910,13 @@
         <v>61.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.2701</v>
+        <v>4.28</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.02</v>
+        <v>4.26</v>
       </c>
       <c r="S25" t="n">
         <v>4.09</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>81.90000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.4639</v>
+        <v>4.47</v>
       </c>
       <c r="Q26" t="n">
         <v>40316</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.43</v>
+        <v>-2.3</v>
       </c>
       <c r="S26" t="n">
         <v>4.11</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GRML</t>
+          <t>ELME</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3063,16 +3063,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4.6</v>
+        <v>4.03</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>1.03</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -3083,55 +3083,51 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-25 4 (insider_buy, +3.0pts) | 2026-08-24 8-K (material_event, +1.8pts)   Items: 9.01 (routine) | 2026-08-24 424B5 (dilution_risk, -3.6pts)</t>
+          <t>2026-08-20 8-K (material_event, +1.0pts)   Items: 8.01 (routine)   Title: &gt;elme-20260820</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>trend_alignment +4, golden_cross +2, rsi_overbought -2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>9.710000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="N27" t="n">
-        <v>0.34</v>
+        <v>1.54</v>
       </c>
       <c r="O27" t="n">
-        <v>99</v>
+        <v>63.2</v>
       </c>
       <c r="P27" t="n">
-        <v>9.949999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>3033</v>
+        <v>17989</v>
       </c>
       <c r="R27" t="n">
-        <v>2.79</v>
+        <v>-0.3</v>
       </c>
       <c r="S27" t="n">
-        <v>10.17</v>
+        <v>1.69</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>5.06</v>
+        <v>0.3</v>
       </c>
       <c r="V27" t="n">
-        <v>10.41</v>
+        <v>1.69</v>
       </c>
       <c r="W27" t="n">
-        <v>8.119999999999999</v>
+        <v>1.6106</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
@@ -3142,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3150,13 +3146,13 @@
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>4.6</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ELME</t>
+          <t>WVVIP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3165,71 +3161,71 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v/>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-20 8-K (material_event, +1.0pts)   Items: 8.01 (routine)   Title: &gt;elme-20260820</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1.69</v>
+        <v>3.33</v>
       </c>
       <c r="N28" t="n">
-        <v>1.54</v>
+        <v>19.07</v>
       </c>
       <c r="O28" t="n">
-        <v>63.2</v>
+        <v>73.2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.68</v>
+        <v>4.68</v>
       </c>
       <c r="Q28" t="n">
-        <v>17989</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.3</v>
+        <v>40.53</v>
       </c>
       <c r="S28" t="n">
-        <v>1.69</v>
+        <v>17</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3</v>
+        <v>410.48</v>
       </c>
       <c r="V28" t="n">
-        <v>1.69</v>
+        <v>6.88</v>
       </c>
       <c r="W28" t="n">
-        <v>1.6106</v>
+        <v>2.6</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
@@ -3240,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3248,13 +3244,13 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WVVIP</t>
+          <t>NHIC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3293,41 +3289,41 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_mild_high +1</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>3.33</v>
+        <v>10.63</v>
       </c>
       <c r="N29" t="n">
-        <v>19.07</v>
+        <v>9.25</v>
       </c>
       <c r="O29" t="n">
-        <v>73.2</v>
+        <v>41.1</v>
       </c>
       <c r="P29" t="n">
-        <v>4.32</v>
+        <v>10.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="R29" t="n">
-        <v>29.72</v>
+        <v>0.09</v>
       </c>
       <c r="S29" t="n">
-        <v>17</v>
+        <v>10.61</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>410.48</v>
+        <v>-0.09</v>
       </c>
       <c r="V29" t="n">
-        <v>6.88</v>
+        <v>10.7</v>
       </c>
       <c r="W29" t="n">
-        <v>2.6</v>
+        <v>10.61</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
@@ -3338,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3352,7 +3348,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NHIC</t>
+          <t>SLQT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3364,68 +3360,68 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)   Title: &gt;slqt-20260825</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>10.63</v>
+        <v>0.55</v>
       </c>
       <c r="N30" t="n">
-        <v>9.25</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>41.1</v>
+        <v>32</v>
       </c>
       <c r="P30" t="n">
-        <v>10.63</v>
+        <v>0.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>384</v>
+        <v>49655</v>
       </c>
       <c r="R30" t="n">
-        <v>0.09</v>
+        <v>3.96</v>
       </c>
       <c r="S30" t="n">
-        <v>10.61</v>
+        <v>0.643</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.09</v>
+        <v>17.27</v>
       </c>
       <c r="V30" t="n">
-        <v>10.7</v>
+        <v>0.86</v>
       </c>
       <c r="W30" t="n">
-        <v>10.61</v>
+        <v>0.5367</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
@@ -3436,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3450,7 +3446,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SLQT</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3462,68 +3458,68 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Late Entry</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, +2.0pts)   Items: 2.02, 9.01 (routine)   Title: &gt;slqt-20260825</t>
+          <t>2026-08-18 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +4, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.55</v>
+        <v>5.52</v>
       </c>
       <c r="N31" t="n">
-        <v>8.619999999999999</v>
+        <v>4.73</v>
       </c>
       <c r="O31" t="n">
-        <v>32</v>
+        <v>58.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0.5897</v>
+        <v>5.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>49655</v>
+        <v>70938</v>
       </c>
       <c r="R31" t="n">
-        <v>7.55</v>
+        <v>-0.36</v>
       </c>
       <c r="S31" t="n">
-        <v>0.643</v>
+        <v>5.64</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>17.27</v>
+        <v>1.81</v>
       </c>
       <c r="V31" t="n">
-        <v>0.86</v>
+        <v>5.65</v>
       </c>
       <c r="W31" t="n">
-        <v>0.5367</v>
+        <v>4.76</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
@@ -3534,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3548,7 +3544,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>IFN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3563,65 +3559,65 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Late Entry</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>15.2</v>
+        <v/>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-18 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts) | 2026-08-18 4 (insider_other, +0.0pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5.52</v>
+        <v>11.56</v>
       </c>
       <c r="N32" t="n">
-        <v>4.73</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
-        <v>58.4</v>
+        <v>61.6</v>
       </c>
       <c r="P32" t="n">
-        <v>5.52</v>
+        <v>11.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>70938</v>
+        <v>1350</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.36</v>
+        <v>-0</v>
       </c>
       <c r="S32" t="n">
-        <v>5.64</v>
+        <v>11.38</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.81</v>
+        <v>-1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>5.65</v>
+        <v>11.9</v>
       </c>
       <c r="W32" t="n">
-        <v>4.76</v>
+        <v>11.38</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
@@ -3632,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3646,7 +3642,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IFN</t>
+          <t>FLWS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3661,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -3689,37 +3685,37 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>11.56</v>
+        <v>3.92</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
-        <v>61.6</v>
+        <v>45.7</v>
       </c>
       <c r="P33" t="n">
-        <v>11.56</v>
+        <v>3.901</v>
       </c>
       <c r="Q33" t="n">
-        <v>1350</v>
+        <v>23267</v>
       </c>
       <c r="R33" t="n">
-        <v>-0</v>
+        <v>-0.48</v>
       </c>
       <c r="S33" t="n">
-        <v>11.38</v>
+        <v>3.8225</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-1.56</v>
+        <v>-2.49</v>
       </c>
       <c r="V33" t="n">
-        <v>11.9</v>
+        <v>4.08</v>
       </c>
       <c r="W33" t="n">
-        <v>11.38</v>
+        <v>3.88</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
@@ -3730,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3744,7 +3740,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FLWS</t>
+          <t>RIV</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3759,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
@@ -3787,37 +3783,37 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>3.92</v>
+        <v>11.09</v>
       </c>
       <c r="N34" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="O34" t="n">
-        <v>45.7</v>
+        <v>44.8</v>
       </c>
       <c r="P34" t="n">
-        <v>3.901</v>
+        <v>11.09</v>
       </c>
       <c r="Q34" t="n">
-        <v>23267</v>
+        <v>2424</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.48</v>
+        <v>0.23</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8225</v>
+        <v>11.05</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>-2.49</v>
+        <v>-0.14</v>
       </c>
       <c r="V34" t="n">
-        <v>4.08</v>
+        <v>11.09</v>
       </c>
       <c r="W34" t="n">
-        <v>3.88</v>
+        <v>10.95</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
@@ -3828,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3842,7 +3838,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RIV</t>
+          <t>NPWR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3857,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
@@ -3885,37 +3881,37 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>11.09</v>
+        <v>1.95</v>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="O35" t="n">
-        <v>44.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P35" t="n">
-        <v>11.09</v>
+        <v>1.963</v>
       </c>
       <c r="Q35" t="n">
-        <v>2424</v>
+        <v>40733</v>
       </c>
       <c r="R35" t="n">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="S35" t="n">
-        <v>11.05</v>
+        <v>2.0389</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.14</v>
+        <v>4.56</v>
       </c>
       <c r="V35" t="n">
-        <v>11.09</v>
+        <v>2.0397</v>
       </c>
       <c r="W35" t="n">
-        <v>10.95</v>
+        <v>1.5202</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
@@ -3926,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3940,80 +3936,80 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v/>
+        <v>103.7</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-24 4 (insider_buy, +2.7pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +1.8pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="N36" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="O36" t="n">
-        <v>64.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P36" t="n">
-        <v>1.963</v>
+        <v>1.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>40733</v>
+        <v>54639</v>
       </c>
       <c r="R36" t="n">
-        <v>0.67</v>
+        <v>-2.62</v>
       </c>
       <c r="S36" t="n">
-        <v>2.0389</v>
+        <v>1.62</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.56</v>
+        <v>-1.41</v>
       </c>
       <c r="V36" t="n">
-        <v>2.0397</v>
+        <v>1.8</v>
       </c>
       <c r="W36" t="n">
-        <v>1.5202</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
@@ -4024,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4032,13 +4028,13 @@
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4047,71 +4043,71 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.97</v>
+        <v>3.62</v>
       </c>
       <c r="D37" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="E37" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Late Entry</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>103.7</v>
+        <v>17.7</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-24 4 (insider_buy, +2.7pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-19 4 (insider_other, +0.0pts) | 2026-08-18 8-K (material_event, +1.8pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement</t>
+          <t>2026-08-20 4 (insider_buy, +1.5pts)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>trend_alignment +4, rsi_overbought -2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1.64</v>
+        <v>17.65</v>
       </c>
       <c r="N37" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="O37" t="n">
-        <v>85.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="P37" t="n">
-        <v>1.59</v>
+        <v>16.2273</v>
       </c>
       <c r="Q37" t="n">
-        <v>54639</v>
+        <v>16161</v>
       </c>
       <c r="R37" t="n">
-        <v>-3.23</v>
+        <v>-7.59</v>
       </c>
       <c r="S37" t="n">
-        <v>1.62</v>
+        <v>16.5</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>-1.41</v>
+        <v>-6.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.8</v>
+        <v>17.65</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>14.36</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
@@ -4122,21 +4118,21 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>3.91</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>STEX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4145,71 +4141,71 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="D38" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E38" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Late Entry</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>17.7</v>
+        <v>-9.1</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-20 4 (insider_buy, +1.5pts)</t>
+          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 2.02, 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>17.65</v>
+        <v>0.76</v>
       </c>
       <c r="N38" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="O38" t="n">
-        <v>62.9</v>
+        <v>45.3</v>
       </c>
       <c r="P38" t="n">
-        <v>16.2273</v>
+        <v>0.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>16161</v>
+        <v>9513</v>
       </c>
       <c r="R38" t="n">
-        <v>-7.59</v>
+        <v>-1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>16.5</v>
+        <v>0.7659</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>-6.04</v>
+        <v>0.78</v>
       </c>
       <c r="V38" t="n">
-        <v>17.65</v>
+        <v>0.85</v>
       </c>
       <c r="W38" t="n">
-        <v>14.36</v>
+        <v>0.7311</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
@@ -4220,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4228,13 +4224,13 @@
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STEX</t>
+          <t>HVII</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4243,16 +4239,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="D39" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -4263,51 +4259,51 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>-9.1</v>
+        <v>-4.2</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 2.02, 7.01, 9.01 (routine)</t>
+          <t>2026-08-24 8-K (material_event, +1.8pts)   Items: 5.07, 8.01 (routine) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +0, rsi_weak -1</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.76</v>
+        <v>7.84</v>
       </c>
       <c r="N39" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
-        <v>45.3</v>
+        <v>29.7</v>
       </c>
       <c r="P39" t="n">
-        <v>0.7569</v>
+        <v>7.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>9513</v>
+        <v>6127</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.41</v>
+        <v>1.02</v>
       </c>
       <c r="S39" t="n">
-        <v>0.7659</v>
+        <v>7.68</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0.78</v>
+        <v>-1.79</v>
       </c>
       <c r="V39" t="n">
-        <v>0.85</v>
+        <v>11</v>
       </c>
       <c r="W39" t="n">
-        <v>0.7311</v>
+        <v>6.09</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
@@ -4318,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4326,13 +4322,13 @@
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HVII</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4341,13 +4337,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>-1</v>
@@ -4361,12 +4357,12 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>-4.2</v>
+        <v>-14.9</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, +1.8pts)   Items: 5.07, 8.01 (routine) | 2026-08-20 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
+          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 8.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4375,37 +4371,37 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>7.84</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>4.98</v>
       </c>
       <c r="O40" t="n">
-        <v>29.7</v>
+        <v>28.1</v>
       </c>
       <c r="P40" t="n">
-        <v>7.91</v>
+        <v>3.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>6127</v>
+        <v>45452</v>
       </c>
       <c r="R40" t="n">
-        <v>1.15</v>
+        <v>4.63</v>
       </c>
       <c r="S40" t="n">
-        <v>7.68</v>
+        <v>3.7902</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>-1.79</v>
+        <v>3.28</v>
       </c>
       <c r="V40" t="n">
-        <v>11</v>
+        <v>5.15</v>
       </c>
       <c r="W40" t="n">
-        <v>6.09</v>
+        <v>3.58</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
@@ -4416,21 +4412,21 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>EVV</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4442,68 +4438,68 @@
         <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1.49</v>
       </c>
       <c r="F41" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>-14.9</v>
+        <v/>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.2pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.8pts)   Items: 8.01, 9.01 (routine)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>4.98</v>
+        <v>2.24</v>
       </c>
       <c r="O41" t="n">
-        <v>28.1</v>
+        <v>52.7</v>
       </c>
       <c r="P41" t="n">
-        <v>3.8</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>45452</v>
+        <v>6191</v>
       </c>
       <c r="R41" t="n">
-        <v>3.54</v>
+        <v>-0.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.7902</v>
+        <v>9.1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.28</v>
+        <v>-0.44</v>
       </c>
       <c r="V41" t="n">
-        <v>5.15</v>
+        <v>9.262</v>
       </c>
       <c r="W41" t="n">
-        <v>3.58</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
@@ -4514,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4528,7 +4524,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EVV</t>
+          <t>AMIX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4543,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -4571,37 +4567,37 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>9.140000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="N42" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="O42" t="n">
-        <v>52.7</v>
+        <v>51.6</v>
       </c>
       <c r="P42" t="n">
-        <v>9.109999999999999</v>
+        <v>7.2608</v>
       </c>
       <c r="Q42" t="n">
-        <v>6191</v>
+        <v>13347</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.33</v>
+        <v>0.7</v>
       </c>
       <c r="S42" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.44</v>
+        <v>10.96</v>
       </c>
       <c r="V42" t="n">
-        <v>9.262</v>
+        <v>16.41</v>
       </c>
       <c r="W42" t="n">
-        <v>9.039999999999999</v>
+        <v>5.17</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
@@ -4612,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4626,7 +4622,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMIX</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4641,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -4669,37 +4665,37 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>7.19</v>
+        <v>13.96</v>
       </c>
       <c r="N43" t="n">
-        <v>2.21</v>
+        <v>1.69</v>
       </c>
       <c r="O43" t="n">
-        <v>51.6</v>
+        <v>54.5</v>
       </c>
       <c r="P43" t="n">
-        <v>7.35</v>
+        <v>13.82</v>
       </c>
       <c r="Q43" t="n">
-        <v>13347</v>
+        <v>177376</v>
       </c>
       <c r="R43" t="n">
-        <v>1.94</v>
+        <v>-1.07</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>12.71</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>10.96</v>
+        <v>-9.02</v>
       </c>
       <c r="V43" t="n">
-        <v>16.41</v>
+        <v>14.8497</v>
       </c>
       <c r="W43" t="n">
-        <v>5.17</v>
+        <v>11.85</v>
       </c>
       <c r="X43" t="b">
         <v>1</v>
@@ -4710,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4724,7 +4720,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>DHY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4739,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -4767,37 +4763,37 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>13.96</v>
+        <v>1.73</v>
       </c>
       <c r="N44" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="O44" t="n">
-        <v>54.5</v>
+        <v>51</v>
       </c>
       <c r="P44" t="n">
-        <v>13.82</v>
+        <v>1.7207</v>
       </c>
       <c r="Q44" t="n">
-        <v>177376</v>
+        <v>16311</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.07</v>
+        <v>0.04</v>
       </c>
       <c r="S44" t="n">
-        <v>12.71</v>
+        <v>1.71</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>-9.02</v>
+        <v>-0.58</v>
       </c>
       <c r="V44" t="n">
-        <v>14.8497</v>
+        <v>1.74</v>
       </c>
       <c r="W44" t="n">
-        <v>11.85</v>
+        <v>1.7001</v>
       </c>
       <c r="X44" t="b">
         <v>1</v>
@@ -4808,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4822,7 +4818,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DHY</t>
+          <t>ENGN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4837,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
@@ -4865,37 +4861,37 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O45" t="n">
-        <v>51</v>
+        <v>55.4</v>
       </c>
       <c r="P45" t="n">
-        <v>1.7293</v>
+        <v>1.8797</v>
       </c>
       <c r="Q45" t="n">
-        <v>16311</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.54</v>
+        <v>0.79</v>
       </c>
       <c r="S45" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>-0.58</v>
+        <v>-2.41</v>
       </c>
       <c r="V45" t="n">
-        <v>1.74</v>
+        <v>1.8982</v>
       </c>
       <c r="W45" t="n">
-        <v>1.7001</v>
+        <v>1.754</v>
       </c>
       <c r="X45" t="b">
         <v>1</v>
@@ -4906,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4920,7 +4916,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENGN</t>
+          <t>GRML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4929,71 +4925,75 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v/>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-25 424B5 (dilution_risk, -4.0pts) | 2026-08-25 4 (insider_buy, +3.0pts) | 2026-08-24 8-K (material_event, +1.8pts)   Items: 9.01 (routine) | 2026-08-24 424B5 (dilution_risk, -3.6pts)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +4, golden_cross +2, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>1.87</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>1.5</v>
+        <v>0.34</v>
       </c>
       <c r="O46" t="n">
-        <v>55.4</v>
+        <v>99</v>
       </c>
       <c r="P46" t="n">
-        <v>1.87</v>
+        <v>7.2399</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3033</v>
       </c>
       <c r="R46" t="n">
-        <v>0.27</v>
+        <v>-25.21</v>
       </c>
       <c r="S46" t="n">
-        <v>1.82</v>
+        <v>10.17</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>-2.41</v>
+        <v>5.06</v>
       </c>
       <c r="V46" t="n">
-        <v>1.8982</v>
+        <v>10.41</v>
       </c>
       <c r="W46" t="n">
-        <v>1.754</v>
+        <v>6.68</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
@@ -5004,15 +5004,15 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="47">
@@ -5070,13 +5070,13 @@
         <v>27.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2162</v>
+        <v>0.2153</v>
       </c>
       <c r="Q47" t="n">
         <v>11695</v>
       </c>
       <c r="R47" t="n">
-        <v>0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="S47" t="n">
         <v>0.2029</v>
@@ -5088,7 +5088,7 @@
         <v>-5.89</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2397</v>
+        <v>0.24</v>
       </c>
       <c r="W47" t="n">
         <v>0.1845</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5168,13 +5168,13 @@
         <v>48.4</v>
       </c>
       <c r="P48" t="n">
-        <v>14.15</v>
+        <v>14.4125</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.14</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
         <v>14.01</v>
@@ -5186,7 +5186,7 @@
         <v>-0.85</v>
       </c>
       <c r="V48" t="n">
-        <v>14.38</v>
+        <v>14.4125</v>
       </c>
       <c r="W48" t="n">
         <v>13.84</v>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5266,13 +5266,13 @@
         <v>43.8</v>
       </c>
       <c r="P49" t="n">
-        <v>1.0303</v>
+        <v>1.04</v>
       </c>
       <c r="Q49" t="n">
         <v>126337</v>
       </c>
       <c r="R49" t="n">
-        <v>0.03</v>
+        <v>0.97</v>
       </c>
       <c r="S49" t="n">
         <v>0.9792999999999999</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5560,13 +5560,13 @@
         <v>66.7</v>
       </c>
       <c r="P52" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Q52" t="n">
         <v>13913</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.3</v>
+        <v>-3.23</v>
       </c>
       <c r="S52" t="n">
         <v>1.0497</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>80.59999999999999</v>
       </c>
       <c r="P54" t="n">
-        <v>1.9726</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
         <v>11650</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.87</v>
+        <v>0.5</v>
       </c>
       <c r="S54" t="n">
         <v>1.9</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6050,13 +6050,13 @@
         <v>42</v>
       </c>
       <c r="P57" t="n">
-        <v>12.64</v>
+        <v>12.5232</v>
       </c>
       <c r="Q57" t="n">
         <v>8737</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.29</v>
+        <v>-4.18</v>
       </c>
       <c r="S57" t="n">
         <v>15.48</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6250,13 +6250,13 @@
         <v>69</v>
       </c>
       <c r="P59" t="n">
-        <v>0.5382</v>
+        <v>0.506</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-6.37</v>
+        <v>-11.97</v>
       </c>
       <c r="S59" t="n">
         <v>0.26</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6348,13 +6348,13 @@
         <v>82.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1.7503</v>
+        <v>1.77</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.47</v>
+        <v>2.61</v>
       </c>
       <c r="S60" t="n">
         <v>1.61</v>
@@ -6366,7 +6366,7 @@
         <v>-6.67</v>
       </c>
       <c r="V60" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W60" t="n">
         <v>1.33</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6446,13 +6446,13 @@
         <v>75.90000000000001</v>
       </c>
       <c r="P61" t="n">
-        <v>2.6</v>
+        <v>2.5845</v>
       </c>
       <c r="Q61" t="n">
         <v>10529</v>
       </c>
       <c r="R61" t="n">
-        <v>1.56</v>
+        <v>0.96</v>
       </c>
       <c r="S61" t="n">
         <v>2.46</v>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         <v>62.1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2044</v>
+        <v>0.2091</v>
       </c>
       <c r="Q62" t="n">
         <v>10241</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.44</v>
+        <v>1.85</v>
       </c>
       <c r="S62" t="n">
         <v>0.178</v>
@@ -6562,7 +6562,7 @@
         <v>-13.3</v>
       </c>
       <c r="V62" t="n">
-        <v>0.2094</v>
+        <v>0.2104</v>
       </c>
       <c r="W62" t="n">
         <v>0.1508</v>
@@ -6576,15 +6576,15 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="63">
@@ -6642,13 +6642,13 @@
         <v>97</v>
       </c>
       <c r="P63" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="Q63" t="n">
         <v>3188</v>
       </c>
       <c r="R63" t="n">
-        <v>-3.67</v>
+        <v>-2.86</v>
       </c>
       <c r="S63" t="n">
         <v>3.15</v>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -6740,13 +6740,13 @@
         <v>79.90000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>9.270799999999999</v>
+        <v>8.773300000000001</v>
       </c>
       <c r="Q64" t="n">
         <v>7560</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.46</v>
+        <v>-7.7</v>
       </c>
       <c r="S64" t="n">
         <v>6.04</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -6838,13 +6838,13 @@
         <v>37.9</v>
       </c>
       <c r="P65" t="n">
-        <v>1.1</v>
+        <v>1.0773</v>
       </c>
       <c r="Q65" t="n">
         <v>1200</v>
       </c>
       <c r="R65" t="n">
-        <v>1.85</v>
+        <v>-0.25</v>
       </c>
       <c r="S65" t="n">
         <v>1.105</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>77.90000000000001</v>
       </c>
       <c r="P69" t="n">
-        <v>6.05</v>
+        <v>6.0139</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.08</v>
+        <v>-0.51</v>
       </c>
       <c r="S69" t="n">
         <v>5.85</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -7426,13 +7426,13 @@
         <v>26.4</v>
       </c>
       <c r="P71" t="n">
-        <v>1.0607</v>
+        <v>1.07</v>
       </c>
       <c r="Q71" t="n">
         <v>848</v>
       </c>
       <c r="R71" t="n">
-        <v>-9.34</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="S71" t="n">
         <v>1.48</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -7622,13 +7622,13 @@
         <v>17</v>
       </c>
       <c r="P73" t="n">
-        <v>1.4796</v>
+        <v>1.4898</v>
       </c>
       <c r="Q73" t="n">
         <v>7426</v>
       </c>
       <c r="R73" t="n">
-        <v>-1.12</v>
+        <v>-0.43</v>
       </c>
       <c r="S73" t="n">
         <v>1.63</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>61.2</v>
       </c>
       <c r="P74" t="n">
-        <v>1.51</v>
+        <v>1.5099</v>
       </c>
       <c r="Q74" t="n">
         <v>543273</v>
@@ -7752,15 +7752,15 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>-1.42</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="75">
@@ -7818,13 +7818,13 @@
         <v>67.8</v>
       </c>
       <c r="P75" t="n">
-        <v>3.41</v>
+        <v>3.3561</v>
       </c>
       <c r="Q75" t="n">
         <v>6435</v>
       </c>
       <c r="R75" t="n">
-        <v>0.15</v>
+        <v>-1.44</v>
       </c>
       <c r="S75" t="n">
         <v>3.4</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -7916,13 +7916,13 @@
         <v>34.9</v>
       </c>
       <c r="P76" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="Q76" t="n">
         <v>157511</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S76" t="n">
         <v>0.082</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -8014,13 +8014,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="P77" t="n">
-        <v>5.85</v>
+        <v>5.4201</v>
       </c>
       <c r="Q77" t="n">
         <v>25729</v>
       </c>
       <c r="R77" t="n">
-        <v>51.72</v>
+        <v>40.57</v>
       </c>
       <c r="S77" t="n">
         <v>3.73</v>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8116,13 +8116,13 @@
         <v>31.8</v>
       </c>
       <c r="P78" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="Q78" t="n">
         <v>27607</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.87</v>
+        <v>-0.58</v>
       </c>
       <c r="S78" t="n">
         <v>4.72</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8436,19 +8436,19 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>9.949999999999999</v>
+        <v>7.2399</v>
       </c>
       <c r="O2" t="n">
         <v>3033</v>
       </c>
       <c r="P2" t="n">
-        <v>2.79</v>
+        <v>-25.21</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
       </c>
       <c r="R2" t="n">
-        <v>8.119999999999999</v>
+        <v>6.68</v>
       </c>
       <c r="S2" t="n">
         <v>10.17</v>
@@ -8556,13 +8556,13 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="O3" t="n">
         <v>3188</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.67</v>
+        <v>-2.86</v>
       </c>
       <c r="Q3" t="n">
         <v>3.7192</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5382</v>
+        <v>0.506</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.37</v>
+        <v>-11.97</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6899999999999999</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.32</v>
+        <v>4.68</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>29.72</v>
+        <v>40.53</v>
       </c>
       <c r="Q5" t="n">
         <v>6.88</v>
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0607</v>
+        <v>1.07</v>
       </c>
       <c r="O6" t="n">
         <v>848</v>
       </c>
       <c r="P6" t="n">
-        <v>-9.34</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.17</v>
+        <v>0.1808</v>
       </c>
       <c r="O7" t="n">
         <v>74807</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2349</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.85</v>
+        <v>5.4201</v>
       </c>
       <c r="O8" t="n">
         <v>25729</v>
       </c>
       <c r="P8" t="n">
-        <v>51.72</v>
+        <v>40.57</v>
       </c>
       <c r="Q8" t="n">
         <v>6.49</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>9.270799999999999</v>
+        <v>8.773300000000001</v>
       </c>
       <c r="O9" t="n">
         <v>7560</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.46</v>
+        <v>-7.7</v>
       </c>
       <c r="Q9" t="n">
         <v>9.890000000000001</v>
@@ -9396,16 +9396,16 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2162</v>
+        <v>0.2153</v>
       </c>
       <c r="O10" t="n">
         <v>11695</v>
       </c>
       <c r="P10" t="n">
-        <v>0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2397</v>
+        <v>0.24</v>
       </c>
       <c r="R10" t="n">
         <v>0.1845</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5897</v>
+        <v>0.57</v>
       </c>
       <c r="O12" t="n">
         <v>49655</v>
       </c>
       <c r="P12" t="n">
-        <v>7.55</v>
+        <v>3.96</v>
       </c>
       <c r="Q12" t="n">
         <v>0.86</v>
@@ -9756,16 +9756,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>14.15</v>
+        <v>14.4125</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.14</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.38</v>
+        <v>14.4125</v>
       </c>
       <c r="R13" t="n">
         <v>13.84</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
         <v>27607</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.87</v>
+        <v>-0.58</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="O15" t="n">
         <v>45452</v>
       </c>
       <c r="P15" t="n">
-        <v>3.54</v>
+        <v>4.63</v>
       </c>
       <c r="Q15" t="n">
         <v>5.15</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.0773</v>
       </c>
       <c r="O16" t="n">
         <v>1200</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>-0.25</v>
       </c>
       <c r="Q16" t="n">
         <v>1.55</v>
@@ -10356,19 +10356,19 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3934</v>
+        <v>0.3915</v>
       </c>
       <c r="O18" t="n">
         <v>10218</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.67</v>
+        <v>-2.15</v>
       </c>
       <c r="Q18" t="n">
         <v>0.4038</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3916</v>
+        <v>0.39</v>
       </c>
       <c r="S18" t="n">
         <v>0.4813</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.84</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>5280</v>
       </c>
       <c r="P19" t="n">
-        <v>2.93</v>
+        <v>-3.77</v>
       </c>
       <c r="Q19" t="n">
         <v>9.84</v>
@@ -10596,13 +10596,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>2.3862</v>
       </c>
       <c r="O20" t="n">
         <v>5717</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.22</v>
+        <v>-2.6</v>
       </c>
       <c r="Q20" t="n">
         <v>2.46</v>
@@ -10956,16 +10956,16 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7503</v>
+        <v>1.77</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.47</v>
+        <v>2.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R23" t="n">
         <v>1.33</v>
@@ -11196,13 +11196,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>12.64</v>
+        <v>12.5232</v>
       </c>
       <c r="O25" t="n">
         <v>8737</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.29</v>
+        <v>-4.18</v>
       </c>
       <c r="Q25" t="n">
         <v>26.75</v>
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.9797</v>
+        <v>1.9703</v>
       </c>
       <c r="O26" t="n">
         <v>495485</v>
       </c>
       <c r="P26" t="n">
-        <v>0.24</v>
+        <v>-0.24</v>
       </c>
       <c r="Q26" t="n">
         <v>1.99</v>
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>157511</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1587</v>
@@ -11556,13 +11556,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8144</v>
+        <v>3.8371</v>
       </c>
       <c r="O28" t="n">
         <v>10324</v>
       </c>
       <c r="P28" t="n">
-        <v>4.5</v>
+        <v>5.13</v>
       </c>
       <c r="Q28" t="n">
         <v>3.89</v>
@@ -11676,13 +11676,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>11.15</v>
+        <v>11.3</v>
       </c>
       <c r="O29" t="n">
         <v>25217</v>
       </c>
       <c r="P29" t="n">
-        <v>-1.41</v>
+        <v>-0.09</v>
       </c>
       <c r="Q29" t="n">
         <v>11.37</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.0303</v>
+        <v>1.04</v>
       </c>
       <c r="O30" t="n">
         <v>126337</v>
       </c>
       <c r="P30" t="n">
-        <v>0.03</v>
+        <v>0.97</v>
       </c>
       <c r="Q30" t="n">
         <v>1.08</v>
@@ -12036,7 +12036,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.54</v>
+        <v>3.5401</v>
       </c>
       <c r="O32" t="n">
         <v>60653</v>
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.4653</v>
+        <v>1.42</v>
       </c>
       <c r="O34" t="n">
         <v>5047</v>
       </c>
       <c r="P34" t="n">
-        <v>3.55</v>
+        <v>0.35</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
@@ -12396,13 +12396,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="O35" t="n">
         <v>6127</v>
       </c>
       <c r="P35" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="Q35" t="n">
         <v>11</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4639</v>
+        <v>4.47</v>
       </c>
       <c r="O38" t="n">
         <v>40316</v>
       </c>
       <c r="P38" t="n">
-        <v>-2.43</v>
+        <v>-2.3</v>
       </c>
       <c r="Q38" t="n">
         <v>4.589</v>
@@ -12876,13 +12876,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
         <v>20075</v>
       </c>
       <c r="P39" t="n">
-        <v>0.21</v>
+        <v>-1.05</v>
       </c>
       <c r="Q39" t="n">
         <v>2.43</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.35</v>
+        <v>7.2608</v>
       </c>
       <c r="O42" t="n">
         <v>13347</v>
       </c>
       <c r="P42" t="n">
-        <v>1.94</v>
+        <v>0.7</v>
       </c>
       <c r="Q42" t="n">
         <v>16.41</v>
@@ -13596,13 +13596,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6.05</v>
+        <v>6.0139</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.08</v>
+        <v>-0.51</v>
       </c>
       <c r="Q45" t="n">
         <v>6.12</v>
@@ -13836,13 +13836,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.38</v>
+        <v>4.3495</v>
       </c>
       <c r="O47" t="n">
         <v>9477</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.23</v>
+        <v>-0.92</v>
       </c>
       <c r="Q47" t="n">
         <v>4.38</v>
@@ -13956,7 +13956,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.51</v>
+        <v>1.5099</v>
       </c>
       <c r="O48" t="n">
         <v>543273</v>
@@ -14196,13 +14196,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="O50" t="n">
         <v>13913</v>
       </c>
       <c r="P50" t="n">
-        <v>-2.3</v>
+        <v>-3.23</v>
       </c>
       <c r="Q50" t="n">
         <v>1.12</v>
@@ -14436,13 +14436,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O52" t="n">
         <v>54639</v>
       </c>
       <c r="P52" t="n">
-        <v>-3.23</v>
+        <v>-2.62</v>
       </c>
       <c r="Q52" t="n">
         <v>1.8</v>
@@ -14556,16 +14556,16 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2044</v>
+        <v>0.2091</v>
       </c>
       <c r="O53" t="n">
         <v>10241</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.44</v>
+        <v>1.85</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.2094</v>
+        <v>0.2104</v>
       </c>
       <c r="R53" t="n">
         <v>0.1508</v>
@@ -14676,13 +14676,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>12.75</v>
+        <v>12.36</v>
       </c>
       <c r="O54" t="n">
         <v>37871</v>
       </c>
       <c r="P54" t="n">
-        <v>0.71</v>
+        <v>-2.37</v>
       </c>
       <c r="Q54" t="n">
         <v>12.75</v>
@@ -14916,13 +14916,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0.7569</v>
+        <v>0.75</v>
       </c>
       <c r="O56" t="n">
         <v>9513</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.41</v>
+        <v>-1.32</v>
       </c>
       <c r="Q56" t="n">
         <v>0.85</v>
@@ -15036,13 +15036,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>2.5845</v>
       </c>
       <c r="O57" t="n">
         <v>10529</v>
       </c>
       <c r="P57" t="n">
-        <v>1.56</v>
+        <v>0.96</v>
       </c>
       <c r="Q57" t="n">
         <v>2.6</v>
@@ -15442,14 +15442,14 @@
         <v>47.67</v>
       </c>
       <c r="AB60" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AC60" t="n">
         <v/>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 0.7x median — trading at discount | P/B 0.7x vs 0.8x median — in-line | EV/EBITDA 47.7x vs -1.4x median — trading at discount | Analyst target $3.64</t>
+          <t>P/S 0.1x vs 0.7x median — trading at discount | P/B 0.7x vs 0.8x median — in-line | EV/EBITDA 47.7x vs -1.4x median — trading at discount | Analyst target $3.65</t>
         </is>
       </c>
       <c r="AE60" t="n">
@@ -15516,13 +15516,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.41</v>
+        <v>3.3561</v>
       </c>
       <c r="O61" t="n">
         <v>6435</v>
       </c>
       <c r="P61" t="n">
-        <v>0.15</v>
+        <v>-1.44</v>
       </c>
       <c r="Q61" t="n">
         <v>3.49</v>
@@ -15876,13 +15876,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.4796</v>
+        <v>1.4898</v>
       </c>
       <c r="O64" t="n">
         <v>7426</v>
       </c>
       <c r="P64" t="n">
-        <v>-1.12</v>
+        <v>-0.43</v>
       </c>
       <c r="Q64" t="n">
         <v>2.77</v>
@@ -15996,13 +15996,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.2701</v>
+        <v>4.28</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>4.02</v>
+        <v>4.26</v>
       </c>
       <c r="Q65" t="n">
         <v>4.3</v>
@@ -16116,13 +16116,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.9726</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
         <v>11650</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.87</v>
+        <v>0.5</v>
       </c>
       <c r="Q66" t="n">
         <v>2</v>
@@ -16356,13 +16356,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O68" t="n">
         <v>20696</v>
       </c>
       <c r="P68" t="n">
-        <v>0.46</v>
+        <v>-0.05</v>
       </c>
       <c r="Q68" t="n">
         <v>1.98</v>
@@ -16596,13 +16596,13 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0.7605</v>
+        <v>0.7578</v>
       </c>
       <c r="O70" t="n">
         <v>9470</v>
       </c>
       <c r="P70" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="Q70" t="n">
         <v>0.8671</v>
@@ -17316,13 +17316,13 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>1.7293</v>
+        <v>1.7207</v>
       </c>
       <c r="O76" t="n">
         <v>16311</v>
       </c>
       <c r="P76" t="n">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="Q76" t="n">
         <v>1.74</v>
@@ -17436,13 +17436,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1.87</v>
+        <v>1.8797</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.27</v>
+        <v>0.79</v>
       </c>
       <c r="Q77" t="n">
         <v>1.8982</v>
@@ -17644,7 +17644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17719,7 +17719,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -17729,13 +17729,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
-        </is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v/>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -17744,12 +17742,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0001213900-26-093307</t>
+          <t>0001213900-26-093597</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>xslF345X06/marketforms-73893.xml</t>
+          <t>ea0303382-424b5_green.htm</t>
         </is>
       </c>
     </row>
@@ -17761,39 +17759,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v/>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Items: 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0001213900-26-093122</t>
+          <t>0001213900-26-093307</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ea0303162-8k_greenland.htm</t>
+          <t>xslF345X06/marketforms-73893.xml</t>
         </is>
       </c>
     </row>
@@ -17805,7 +17801,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>424B5</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -17815,7 +17811,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -17824,64 +17820,67 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Items: 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0001213900-26-093106</t>
+          <t>0001213900-26-093122</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ea0303090-424b5_greenland.htm</t>
+          <t>ea0303162-8k_greenland.htm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GAME</t>
+          <t>GRML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v/>
       </c>
       <c r="F5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Item 3.03 (rights_modification, -1)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0001493152-26-039213</t>
+          <t>0001213900-26-093106</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>ea0303090-424b5_greenland.htm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>GAME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -17891,7 +17890,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -17904,13 +17903,13 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
+          <t>Item 3.03 (rights_modification, -1)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0001493152-26-040042</t>
+          <t>0001493152-26-039213</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -17932,7 +17931,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17941,17 +17940,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Items: 4.01, 4.02, 9.01 (routine)</t>
+          <t>Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0001493152-26-038853</t>
+          <t>0001493152-26-040042</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -17963,7 +17962,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FNGR</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -17973,7 +17972,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17986,13 +17985,13 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Items: 8.01, 9.01 (routine)</t>
+          <t>Items: 4.01, 4.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0001493152-26-039927</t>
+          <t>0001493152-26-038853</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -18014,7 +18013,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18023,21 +18022,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Item 1.01 (entry_agreement, +3) | Item 2.03 (direct_obligation, -1) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Entry into a Material Definitive Agreement.</t>
-        </is>
-      </c>
+          <t>Items: 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0001493152-26-038662</t>
+          <t>0001493152-26-039927</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -18049,7 +18044,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>FNGR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -18059,7 +18054,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18068,29 +18063,33 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Item 1.01 (entry_agreement, +3) | Item 2.03 (direct_obligation, -1) | Item 3.02 (unregistered_equity, -3) | Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Entry into a Material Definitive Agreement.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0001213900-26-091288</t>
+          <t>0001493152-26-038662</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ea0302597-8k_cidhold.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -18100,7 +18099,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18109,125 +18108,121 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>&gt;pmi20260814_8k.htm</t>
-        </is>
-      </c>
+          <t>Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0001437749-26-028585</t>
+          <t>0001213900-26-091288</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>pmi20260814_8k.htm</t>
+          <t>ea0302597-8k_cidhold.htm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&gt;pmi20260814_8k.htm</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0000935836-26-000440</t>
+          <t>0001437749-26-028585</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>xslF345X06/form4.xml</t>
+          <t>pmi20260814_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SLQT</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>&gt;slqt-20260825</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0001794783-26-000056</t>
+          <t>0000935836-26-000440</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>slqt-20260825.htm</t>
+          <t>xslF345X06/form4.xml</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>SLQT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -18237,22 +18232,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&gt;slqt-20260825</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0001104659-26-100556</t>
+          <t>0001794783-26-000056</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>tm2623776d4_424b3.htm</t>
+          <t>slqt-20260825.htm</t>
         </is>
       </c>
     </row>
@@ -18284,12 +18287,12 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0001104659-26-100555</t>
+          <t>0001104659-26-100556</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>tm2623776d3_424b3.htm</t>
+          <t>tm2623776d4_424b3.htm</t>
         </is>
       </c>
     </row>
@@ -18321,12 +18324,12 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0001104659-26-100553</t>
+          <t>0001104659-26-100555</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>tm2623776d2_424b3.htm</t>
+          <t>tm2623776d3_424b3.htm</t>
         </is>
       </c>
     </row>
@@ -18358,53 +18361,49 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0001104659-26-100552</t>
+          <t>0001104659-26-100553</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>tm2623776d1_424b3.htm</t>
+          <t>tm2623776d2_424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Items: 5.03, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0001104659-26-099673</t>
+          <t>0001104659-26-100552</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>tm2623749d1_8k.htm</t>
+          <t>tm2623776d1_424b3.htm</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18420,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18434,60 +18433,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Items: 8.01, 9.01 (routine)</t>
+          <t>Items: 5.03, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0001104659-26-098592</t>
+          <t>0001104659-26-099673</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>tm2623548d1_8k.htm</t>
+          <t>tm2623749d1_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>insider_other</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Items: 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0001628280-26-057569</t>
+          <t>0001104659-26-098592</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787062360.xml</t>
+          <t>tm2623548d1_8k.htm</t>
         </is>
       </c>
     </row>
@@ -18524,12 +18522,12 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0001628280-26-057567</t>
+          <t>0001628280-26-057569</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787062233.xml</t>
+          <t>xslF345X06/wk-form4_1787062360.xml</t>
         </is>
       </c>
     </row>
@@ -18566,12 +18564,12 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0001628280-26-057564</t>
+          <t>0001628280-26-057567</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787062147.xml</t>
+          <t>xslF345X06/wk-form4_1787062233.xml</t>
         </is>
       </c>
     </row>
@@ -18608,29 +18606,29 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0001628280-26-057562</t>
+          <t>0001628280-26-057564</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787062056.xml</t>
+          <t>xslF345X06/wk-form4_1787062147.xml</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GPUS</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4/A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -18640,7 +18638,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>insider_buy</t>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -18650,12 +18648,12 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0001214659-26-010677</t>
+          <t>0001628280-26-057562</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>xslF345X06/marketforms-73837.xml</t>
+          <t>xslF345X06/wk-form4_1787062056.xml</t>
         </is>
       </c>
     </row>
@@ -18667,7 +18665,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4/A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -18677,29 +18675,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v/>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Items: 5.03, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0001214659-26-010654</t>
+          <t>0001214659-26-010677</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>o842618k.htm</t>
+          <t>xslF345X06/marketforms-73837.xml</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18712,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18732,60 +18728,62 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Items: 7.01 (routine)</t>
+          <t>Items: 5.03, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0001214659-26-010619</t>
+          <t>0001214659-26-010654</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>hd8182618k.htm</t>
+          <t>o842618k.htm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EXOD</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v/>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Items: 7.01 (routine)</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0001628280-26-058738</t>
+          <t>0001214659-26-010619</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787614012.xml</t>
+          <t>hd8182618k.htm</t>
         </is>
       </c>
     </row>
@@ -18822,12 +18820,12 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0001628280-26-058732</t>
+          <t>0001628280-26-058738</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787612293.xml</t>
+          <t>xslF345X06/wk-form4_1787614012.xml</t>
         </is>
       </c>
     </row>
@@ -18864,12 +18862,12 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0001628280-26-058729</t>
+          <t>0001628280-26-058732</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787612159.xml</t>
+          <t>xslF345X06/wk-form4_1787612293.xml</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18894,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>insider_sell</t>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -18906,12 +18904,12 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0001628280-26-058580</t>
+          <t>0001628280-26-058729</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787594598.xml</t>
+          <t>xslF345X06/wk-form4_1787612159.xml</t>
         </is>
       </c>
     </row>
@@ -18928,7 +18926,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -18948,12 +18946,12 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0001628280-26-058233</t>
+          <t>0001628280-26-058580</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787255344.xml</t>
+          <t>xslF345X06/wk-form4_1787594598.xml</t>
         </is>
       </c>
     </row>
@@ -18970,7 +18968,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -18990,12 +18988,12 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0001628280-26-057929</t>
+          <t>0001628280-26-058233</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787169681.xml</t>
+          <t>xslF345X06/wk-form4_1787255344.xml</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19010,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19032,140 +19030,141 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0001628280-26-057239</t>
+          <t>0001628280-26-057929</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1786971403.xml</t>
+          <t>xslF345X06/wk-form4_1787169681.xml</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CEPO</t>
+          <t>EXOD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Item 1.01 (entry_agreement, +3) | Item 1.02 (termination_agreement, +1)</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>&amp;#160;Entry into a Material Definitive Agreement.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0001213900-26-092163</t>
+          <t>0001628280-26-057239</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ea0302895-8k_cantor1.htm</t>
+          <t>xslF345X06/wk-form4_1786971403.xml</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EFT</t>
+          <t>CEPO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>insider_sell</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Item 1.01 (entry_agreement, +3) | Item 1.02 (termination_agreement, +1)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>&amp;#160;Entry into a Material Definitive Agreement.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0001225208-26-007269</t>
+          <t>0001213900-26-092163</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>xslF345X06/doc4.xml</t>
+          <t>ea0302895-8k_cantor1.htm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DFNS</t>
+          <t>EFT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Item 3.01 (delisting, -6)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0001185185-26-003654</t>
+          <t>0001225208-26-007269</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>dfns8k082026.htm</t>
+          <t>xslF345X06/doc4.xml</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19181,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -19191,29 +19190,29 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Items: 8.01 (routine)</t>
+          <t>Item 3.01 (delisting, -6)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0001185185-26-003572</t>
+          <t>0001185185-26-003654</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>dfns8k081726.htm</t>
+          <t>dfns8k082026.htm</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>DFNS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -19223,7 +19222,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -19232,29 +19231,29 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
+          <t>Items: 8.01 (routine)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0001213900-26-093255</t>
+          <t>0001185185-26-003572</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ea0303279-8k_richtech.htm</t>
+          <t>dfns8k081726.htm</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SNYR</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -19264,7 +19263,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -19273,105 +19272,105 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Item 3.01 (delisting, -6)</t>
+          <t>Item 5.02 (officer_departure, -1)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0001213900-26-092335</t>
+          <t>0001213900-26-093255</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>ea0302944-8k_synergy.htm</t>
+          <t>ea0303279-8k_richtech.htm</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>SNYR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
+        <v>-6</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Item 3.01 (delisting, -6)</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0001193125-26-354145</t>
+          <t>0001213900-26-092335</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>ea0302944-8k_synergy.htm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AVXL</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0001731122-26-001143</t>
+          <t>0001193125-26-354145</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>e7897_8-k.htm</t>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19387,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -19401,35 +19400,35 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
+          <t>Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0001731122-26-001078</t>
+          <t>0001731122-26-001143</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>e7862_8k.htm</t>
+          <t>e7897_8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>AVXL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8-K/A</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -19442,18 +19441,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Items: 2.02, 8.01, 9.01 (routine)</t>
+          <t>Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0001493152-26-039796</t>
+          <t>0001731122-26-001078</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>form8-ka.htm</t>
+          <t>e7862_8k.htm</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19464,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>8-K/A</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -19483,25 +19482,25 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
+          <t>Items: 2.02, 8.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0001493152-26-039786</t>
+          <t>0001493152-26-039796</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>form8-ka.htm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RNXT</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19511,7 +19510,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -19524,13 +19523,13 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Items: 8.01 (routine)</t>
+          <t>Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0001493152-26-039472</t>
+          <t>0001493152-26-039786</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -19542,7 +19541,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HVII</t>
+          <t>RNXT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -19552,7 +19551,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -19565,13 +19564,13 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Items: 5.07, 8.01 (routine)</t>
+          <t>Items: 8.01 (routine)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0001493152-26-039917</t>
+          <t>0001493152-26-039472</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -19593,7 +19592,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -19606,13 +19605,13 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
+          <t>Items: 5.07, 8.01 (routine)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0001493152-26-039511</t>
+          <t>0001493152-26-039917</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -19624,42 +19623,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TNXP</t>
+          <t>HVII</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0001999371-26-018494</t>
+          <t>0001493152-26-039511</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>xslF345X06/bagger-form4.xml</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
@@ -19671,81 +19669,81 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v/>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
       </c>
       <c r="F49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0001493152-26-039000</t>
+          <t>0001999371-26-018494</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>xslF345X06/bagger-form4.xml</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>TNXP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v/>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0002061848-26-000003</t>
+          <t>0001493152-26-039000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787602480.xml</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
@@ -19762,7 +19760,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -19782,12 +19780,12 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0001225208-26-007275</t>
+          <t>0002061848-26-000003</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xslF345X06/doc4.xml</t>
+          <t>xslF345X06/wk-form4_1787602480.xml</t>
         </is>
       </c>
     </row>
@@ -19804,7 +19802,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -19814,7 +19812,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>insider_other</t>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -19824,7 +19822,7 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0001225208-26-007188</t>
+          <t>0001225208-26-007275</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -19846,7 +19844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -19856,7 +19854,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>insider_buy</t>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -19866,7 +19864,7 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0001225208-26-007140</t>
+          <t>0001225208-26-007188</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -19878,7 +19876,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -19908,12 +19906,12 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0001683168-26-006540</t>
+          <t>0001225208-26-007140</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>xslF345X06/doc4.xml</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19948,7 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0001683168-26-006538</t>
+          <t>0001683168-26-006540</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -19992,7 +19990,7 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0001683168-26-006530</t>
+          <t>0001683168-26-006538</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -20004,7 +20002,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -20014,7 +20012,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -20024,7 +20022,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>insider_sell</t>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -20034,95 +20032,95 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0001299130-26-000128</t>
+          <t>0001683168-26-006530</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787098653.xml</t>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CTXR</t>
+          <t>PACB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Item 3.01 (delisting, -6)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0001213900-26-092604</t>
+          <t>0001299130-26-000128</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>ea0302856-8k_citius.htm</t>
+          <t>xslF345X06/wk-form4_1787098653.xml</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CTXR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
+        <v>-6</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Item 3.01 (delisting, -6)</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0001104659-26-100330</t>
+          <t>0001213900-26-092604</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>xslF345X06/tm2623825-2_4seq1.xml</t>
+          <t>ea0302856-8k_citius.htm</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20137,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -20149,7 +20147,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>insider_other</t>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -20159,12 +20157,12 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0002092596-26-000002</t>
+          <t>0001104659-26-100330</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>xslF345X06/form4-08192026_100818.xml</t>
+          <t>xslF345X06/tm2623825-2_4seq1.xml</t>
         </is>
       </c>
     </row>
@@ -20201,12 +20199,12 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0001231919-26-000951</t>
+          <t>0002092596-26-000002</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>xslF345X06/form4-08192026_100822.xml</t>
+          <t>xslF345X06/form4-08192026_100818.xml</t>
         </is>
       </c>
     </row>
@@ -20218,50 +20216,44 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>material_event</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v/>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>insider_other</t>
+        </is>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Entry into a Material Definitive Agreement</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0001104659-26-098120</t>
+          <t>0001231919-26-000951</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>tm2623453d1_8k.htm</t>
+          <t>xslF345X06/form4-08192026_100822.xml</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GOSS</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -20271,7 +20263,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -20279,8 +20271,11 @@
           <t>material_event</t>
         </is>
       </c>
+      <c r="E63" t="n">
+        <v/>
+      </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -20289,24 +20284,24 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>&gt;goss-20260820</t>
+          <t>Entry into a Material Definitive Agreement</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0001728117-26-000077</t>
+          <t>0001104659-26-098120</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>goss-20260820.htm</t>
+          <t>tm2623453d1_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STEX</t>
+          <t>GOSS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -20329,67 +20324,70 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&gt;goss-20260820</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0001493152-26-039547</t>
+          <t>0001728117-26-000077</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>goss-20260820.htm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HYPD</t>
+          <t>STEX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>insider_other</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0001104659-26-098397</t>
+          <t>0001493152-26-039547</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>xslF345X06/tm2623434-1_4seq1.xml</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DOUG</t>
+          <t>HYPD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -20409,7 +20407,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>insider_buy</t>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -20419,12 +20417,12 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0002145258-26-000006</t>
+          <t>0001104659-26-098397</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787088247.xml</t>
+          <t>xslF345X06/tm2623434-1_4seq1.xml</t>
         </is>
       </c>
     </row>
@@ -20461,57 +20459,54 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0002145121-26-000006</t>
+          <t>0002145258-26-000006</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787088082.xml</t>
+          <t>xslF345X06/wk-form4_1787088247.xml</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BTAI</t>
+          <t>DOUG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Item 1.01 (entry_agreement, +3)</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Entry into a Material Definitive</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0001104659-26-100532</t>
+          <t>0002145121-26-000006</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>tm2623945d1_8k.htm</t>
+          <t>xslF345X06/wk-form4_1787088082.xml</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20523,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -20537,7 +20532,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -20546,81 +20541,89 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Entry into a Material Definitive Agreement.</t>
+          <t>Entry into a Material Definitive</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0001104659-26-099900</t>
+          <t>0001104659-26-100532</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>tm2623861d1_8k.htm</t>
+          <t>tm2623945d1_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>BTAI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Item 1.01 (entry_agreement, +3)</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Entry into a Material Definitive Agreement.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0001193125-26-359167</t>
+          <t>0001104659-26-099900</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>tm2623861d1_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BRR</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -20630,39 +20633,34 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0001493152-26-039145</t>
+          <t>0001193125-26-359167</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>form424b3.htm</t>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>BRR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>insider_sell</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -20672,55 +20670,97 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0001213900-26-092588</t>
+          <t>0001493152-26-039145</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>form424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>PAL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0001213900-26-092588</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>ELME</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>8-K</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>material_event</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>Items: 8.01 (routine)</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>&gt;elme-20260820</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>0000104894-26-000110</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>elme-20260820.htm</t>
         </is>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -656,13 +656,13 @@
         <v>61.9</v>
       </c>
       <c r="P2" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="Q2" t="n">
         <v>8295</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.19</v>
+        <v>-0.09</v>
       </c>
       <c r="S2" t="n">
         <v>10.79</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>38.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7578</v>
+        <v>0.75</v>
       </c>
       <c r="Q3" t="n">
         <v>9470</v>
       </c>
       <c r="R3" t="n">
-        <v>1.12</v>
+        <v>0.08</v>
       </c>
       <c r="S3" t="n">
         <v>0.777</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>73.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>5280</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.77</v>
+        <v>-1.05</v>
       </c>
       <c r="S4" t="n">
         <v>7.86</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1244,13 +1244,13 @@
         <v>66.59999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q8" t="n">
         <v>5047</v>
       </c>
       <c r="R8" t="n">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="S8" t="n">
         <v>1.32</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2322,13 +2322,13 @@
         <v>30.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1808</v>
+        <v>0.1785</v>
       </c>
       <c r="Q19" t="n">
         <v>74807</v>
       </c>
       <c r="R19" t="n">
-        <v>8.390000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="S19" t="n">
         <v>0.2037</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>26.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3915</v>
+        <v>0.39</v>
       </c>
       <c r="Q20" t="n">
         <v>10218</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.15</v>
+        <v>-2.52</v>
       </c>
       <c r="S20" t="n">
         <v>0.4813</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>61.8</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9703</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
         <v>495485</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.24</v>
+        <v>0.25</v>
       </c>
       <c r="S23" t="n">
         <v>1.6781</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2910,13 +2910,13 @@
         <v>61.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.28</v>
+        <v>4.176</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.26</v>
+        <v>1.73</v>
       </c>
       <c r="S25" t="n">
         <v>4.09</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>81.90000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.47</v>
+        <v>4.4611</v>
       </c>
       <c r="Q26" t="n">
         <v>40316</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.3</v>
+        <v>-2.49</v>
       </c>
       <c r="S26" t="n">
         <v>4.11</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3204,13 +3204,13 @@
         <v>73.2</v>
       </c>
       <c r="P28" t="n">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>40.53</v>
+        <v>26.42</v>
       </c>
       <c r="S28" t="n">
         <v>17</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3400,13 +3400,13 @@
         <v>32</v>
       </c>
       <c r="P30" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="Q30" t="n">
         <v>49655</v>
       </c>
       <c r="R30" t="n">
-        <v>3.96</v>
+        <v>7.61</v>
       </c>
       <c r="S30" t="n">
         <v>0.643</v>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3498,13 +3498,13 @@
         <v>58.4</v>
       </c>
       <c r="P31" t="n">
-        <v>5.52</v>
+        <v>5.65</v>
       </c>
       <c r="Q31" t="n">
         <v>70938</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.36</v>
+        <v>1.99</v>
       </c>
       <c r="S31" t="n">
         <v>5.64</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3988,13 +3988,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="P36" t="n">
-        <v>1.6</v>
+        <v>1.6097</v>
       </c>
       <c r="Q36" t="n">
         <v>54639</v>
       </c>
       <c r="R36" t="n">
-        <v>-2.62</v>
+        <v>-2.03</v>
       </c>
       <c r="S36" t="n">
         <v>1.62</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>29.7</v>
       </c>
       <c r="P39" t="n">
-        <v>7.9</v>
+        <v>7.7005</v>
       </c>
       <c r="Q39" t="n">
         <v>6127</v>
       </c>
       <c r="R39" t="n">
-        <v>1.02</v>
+        <v>-1.53</v>
       </c>
       <c r="S39" t="n">
         <v>7.68</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>28.1</v>
       </c>
       <c r="P40" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="Q40" t="n">
         <v>45452</v>
       </c>
       <c r="R40" t="n">
-        <v>4.63</v>
+        <v>3.81</v>
       </c>
       <c r="S40" t="n">
         <v>3.7902</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
         <v>52.7</v>
       </c>
       <c r="P41" t="n">
-        <v>9.109999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q41" t="n">
         <v>6191</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.33</v>
+        <v>-0.22</v>
       </c>
       <c r="S41" t="n">
         <v>9.1</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4576,13 +4576,13 @@
         <v>51.6</v>
       </c>
       <c r="P42" t="n">
-        <v>7.2608</v>
+        <v>7.2</v>
       </c>
       <c r="Q42" t="n">
         <v>13347</v>
       </c>
       <c r="R42" t="n">
-        <v>0.7</v>
+        <v>-0.14</v>
       </c>
       <c r="S42" t="n">
         <v>8</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>54.5</v>
       </c>
       <c r="P43" t="n">
-        <v>13.82</v>
+        <v>13.9</v>
       </c>
       <c r="Q43" t="n">
         <v>177376</v>
       </c>
       <c r="R43" t="n">
-        <v>-1.07</v>
+        <v>-0.5</v>
       </c>
       <c r="S43" t="n">
         <v>12.71</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4772,13 +4772,13 @@
         <v>51</v>
       </c>
       <c r="P44" t="n">
-        <v>1.7207</v>
+        <v>1.73</v>
       </c>
       <c r="Q44" t="n">
         <v>16311</v>
       </c>
       <c r="R44" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="S44" t="n">
         <v>1.71</v>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4972,13 +4972,13 @@
         <v>99</v>
       </c>
       <c r="P46" t="n">
-        <v>7.2399</v>
+        <v>7.5</v>
       </c>
       <c r="Q46" t="n">
         <v>3033</v>
       </c>
       <c r="R46" t="n">
-        <v>-25.21</v>
+        <v>-22.52</v>
       </c>
       <c r="S46" t="n">
         <v>10.17</v>
@@ -5004,15 +5004,15 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="47">
@@ -5070,13 +5070,13 @@
         <v>27.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2153</v>
+        <v>0.222</v>
       </c>
       <c r="Q47" t="n">
         <v>11695</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.14</v>
+        <v>2.97</v>
       </c>
       <c r="S47" t="n">
         <v>0.2029</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5266,13 +5266,13 @@
         <v>43.8</v>
       </c>
       <c r="P49" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Q49" t="n">
         <v>126337</v>
       </c>
       <c r="R49" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0.9792999999999999</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6050,13 +6050,13 @@
         <v>42</v>
       </c>
       <c r="P57" t="n">
-        <v>12.5232</v>
+        <v>12.85</v>
       </c>
       <c r="Q57" t="n">
         <v>8737</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.18</v>
+        <v>-1.68</v>
       </c>
       <c r="S57" t="n">
         <v>15.48</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6250,13 +6250,13 @@
         <v>69</v>
       </c>
       <c r="P59" t="n">
-        <v>0.506</v>
+        <v>0.4933</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-11.97</v>
+        <v>-14.18</v>
       </c>
       <c r="S59" t="n">
         <v>0.26</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6348,13 +6348,13 @@
         <v>82.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="S60" t="n">
         <v>1.61</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         <v>62.1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2091</v>
+        <v>0.2086</v>
       </c>
       <c r="Q62" t="n">
         <v>10241</v>
       </c>
       <c r="R62" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="S62" t="n">
         <v>0.178</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6642,13 +6642,13 @@
         <v>97</v>
       </c>
       <c r="P63" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="Q63" t="n">
         <v>3188</v>
       </c>
       <c r="R63" t="n">
-        <v>-2.86</v>
+        <v>-2.59</v>
       </c>
       <c r="S63" t="n">
         <v>3.15</v>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -6740,13 +6740,13 @@
         <v>79.90000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>8.773300000000001</v>
+        <v>8.958500000000001</v>
       </c>
       <c r="Q64" t="n">
         <v>7560</v>
       </c>
       <c r="R64" t="n">
-        <v>-7.7</v>
+        <v>-5.75</v>
       </c>
       <c r="S64" t="n">
         <v>6.04</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -6838,13 +6838,13 @@
         <v>37.9</v>
       </c>
       <c r="P65" t="n">
-        <v>1.0773</v>
+        <v>1.06</v>
       </c>
       <c r="Q65" t="n">
         <v>1200</v>
       </c>
       <c r="R65" t="n">
-        <v>-0.25</v>
+        <v>-1.85</v>
       </c>
       <c r="S65" t="n">
         <v>1.105</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -6936,13 +6936,13 @@
         <v>33.6</v>
       </c>
       <c r="P66" t="n">
-        <v>0.4343</v>
+        <v>0.4342</v>
       </c>
       <c r="Q66" t="n">
         <v>49975</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="S66" t="n">
         <v>0.48</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -7426,13 +7426,13 @@
         <v>26.4</v>
       </c>
       <c r="P71" t="n">
-        <v>1.07</v>
+        <v>1.0601</v>
       </c>
       <c r="Q71" t="n">
         <v>848</v>
       </c>
       <c r="R71" t="n">
-        <v>-8.550000000000001</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="S71" t="n">
         <v>1.48</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -7622,13 +7622,13 @@
         <v>17</v>
       </c>
       <c r="P73" t="n">
-        <v>1.4898</v>
+        <v>1.45</v>
       </c>
       <c r="Q73" t="n">
         <v>7426</v>
       </c>
       <c r="R73" t="n">
-        <v>-0.43</v>
+        <v>-3.09</v>
       </c>
       <c r="S73" t="n">
         <v>1.63</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -7720,13 +7720,13 @@
         <v>61.2</v>
       </c>
       <c r="P74" t="n">
-        <v>1.5099</v>
+        <v>1.5</v>
       </c>
       <c r="Q74" t="n">
         <v>543273</v>
       </c>
       <c r="R74" t="n">
-        <v>-0.66</v>
+        <v>-1.32</v>
       </c>
       <c r="S74" t="n">
         <v>1.33</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -7818,13 +7818,13 @@
         <v>67.8</v>
       </c>
       <c r="P75" t="n">
-        <v>3.3561</v>
+        <v>3.41</v>
       </c>
       <c r="Q75" t="n">
         <v>6435</v>
       </c>
       <c r="R75" t="n">
-        <v>-1.44</v>
+        <v>0.15</v>
       </c>
       <c r="S75" t="n">
         <v>3.4</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -7916,13 +7916,13 @@
         <v>34.9</v>
       </c>
       <c r="P76" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0968</v>
       </c>
       <c r="Q76" t="n">
         <v>157511</v>
       </c>
       <c r="R76" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="S76" t="n">
         <v>0.082</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -8014,13 +8014,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="P77" t="n">
-        <v>5.4201</v>
+        <v>5.3499</v>
       </c>
       <c r="Q77" t="n">
         <v>25729</v>
       </c>
       <c r="R77" t="n">
-        <v>40.57</v>
+        <v>38.75</v>
       </c>
       <c r="S77" t="n">
         <v>3.73</v>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8116,13 +8116,13 @@
         <v>31.8</v>
       </c>
       <c r="P78" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q78" t="n">
         <v>27607</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
       <c r="S78" t="n">
         <v>4.72</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8436,13 +8436,13 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>7.2399</v>
+        <v>7.5</v>
       </c>
       <c r="O2" t="n">
         <v>3033</v>
       </c>
       <c r="P2" t="n">
-        <v>-25.21</v>
+        <v>-22.52</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
@@ -8556,13 +8556,13 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="O3" t="n">
         <v>3188</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.86</v>
+        <v>-2.59</v>
       </c>
       <c r="Q3" t="n">
         <v>3.7192</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.506</v>
+        <v>0.4933</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-11.97</v>
+        <v>-14.18</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6899999999999999</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>40.53</v>
+        <v>26.42</v>
       </c>
       <c r="Q5" t="n">
         <v>6.88</v>
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>1.0601</v>
       </c>
       <c r="O6" t="n">
         <v>848</v>
       </c>
       <c r="P6" t="n">
-        <v>-8.550000000000001</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1808</v>
+        <v>0.1785</v>
       </c>
       <c r="O7" t="n">
         <v>74807</v>
       </c>
       <c r="P7" t="n">
-        <v>8.390000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2349</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.4201</v>
+        <v>5.3499</v>
       </c>
       <c r="O8" t="n">
         <v>25729</v>
       </c>
       <c r="P8" t="n">
-        <v>40.57</v>
+        <v>38.75</v>
       </c>
       <c r="Q8" t="n">
         <v>6.49</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.773300000000001</v>
+        <v>8.958500000000001</v>
       </c>
       <c r="O9" t="n">
         <v>7560</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.7</v>
+        <v>-5.75</v>
       </c>
       <c r="Q9" t="n">
         <v>9.890000000000001</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2153</v>
+        <v>0.222</v>
       </c>
       <c r="O10" t="n">
         <v>11695</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.14</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
         <v>0.24</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="O12" t="n">
         <v>49655</v>
       </c>
       <c r="P12" t="n">
-        <v>3.96</v>
+        <v>7.61</v>
       </c>
       <c r="Q12" t="n">
         <v>0.86</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="O14" t="n">
         <v>27607</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.58</v>
+        <v>1.17</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="O15" t="n">
         <v>45452</v>
       </c>
       <c r="P15" t="n">
-        <v>4.63</v>
+        <v>3.81</v>
       </c>
       <c r="Q15" t="n">
         <v>5.15</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0773</v>
+        <v>1.06</v>
       </c>
       <c r="O16" t="n">
         <v>1200</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.25</v>
+        <v>-1.85</v>
       </c>
       <c r="Q16" t="n">
         <v>1.55</v>
@@ -10236,13 +10236,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.52</v>
+        <v>5.65</v>
       </c>
       <c r="O17" t="n">
         <v>70938</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.36</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
         <v>5.65</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3915</v>
+        <v>0.39</v>
       </c>
       <c r="O18" t="n">
         <v>10218</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.15</v>
+        <v>-2.52</v>
       </c>
       <c r="Q18" t="n">
         <v>0.4038</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>5280</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.77</v>
+        <v>-1.05</v>
       </c>
       <c r="Q19" t="n">
         <v>9.84</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4343</v>
+        <v>0.4342</v>
       </c>
       <c r="O21" t="n">
         <v>49975</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="Q21" t="n">
         <v>0.524</v>
@@ -10836,13 +10836,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="O22" t="n">
         <v>8295</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.19</v>
+        <v>-0.09</v>
       </c>
       <c r="Q22" t="n">
         <v>10.828</v>
@@ -10956,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="Q23" t="n">
         <v>1.77</v>
@@ -11196,13 +11196,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>12.5232</v>
+        <v>12.85</v>
       </c>
       <c r="O25" t="n">
         <v>8737</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.18</v>
+        <v>-1.68</v>
       </c>
       <c r="Q25" t="n">
         <v>26.75</v>
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.9703</v>
+        <v>1.98</v>
       </c>
       <c r="O26" t="n">
         <v>495485</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.24</v>
+        <v>0.25</v>
       </c>
       <c r="Q26" t="n">
         <v>1.99</v>
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0968</v>
       </c>
       <c r="O27" t="n">
         <v>157511</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1587</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="O30" t="n">
         <v>126337</v>
       </c>
       <c r="P30" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>1.08</v>
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="O34" t="n">
         <v>5047</v>
       </c>
       <c r="P34" t="n">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
@@ -12396,13 +12396,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>7.9</v>
+        <v>7.7005</v>
       </c>
       <c r="O35" t="n">
         <v>6127</v>
       </c>
       <c r="P35" t="n">
-        <v>1.02</v>
+        <v>-1.53</v>
       </c>
       <c r="Q35" t="n">
         <v>11</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.47</v>
+        <v>4.4611</v>
       </c>
       <c r="O38" t="n">
         <v>40316</v>
       </c>
       <c r="P38" t="n">
-        <v>-2.3</v>
+        <v>-2.49</v>
       </c>
       <c r="Q38" t="n">
         <v>4.589</v>
@@ -13116,13 +13116,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>9.109999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>6191</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.33</v>
+        <v>-0.22</v>
       </c>
       <c r="Q41" t="n">
         <v>9.262</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.2608</v>
+        <v>7.2</v>
       </c>
       <c r="O42" t="n">
         <v>13347</v>
       </c>
       <c r="P42" t="n">
-        <v>0.7</v>
+        <v>-0.14</v>
       </c>
       <c r="Q42" t="n">
         <v>16.41</v>
@@ -13956,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.5099</v>
+        <v>1.5</v>
       </c>
       <c r="O48" t="n">
         <v>543273</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.66</v>
+        <v>-1.32</v>
       </c>
       <c r="Q48" t="n">
         <v>1.525</v>
@@ -14436,13 +14436,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.6</v>
+        <v>1.6097</v>
       </c>
       <c r="O52" t="n">
         <v>54639</v>
       </c>
       <c r="P52" t="n">
-        <v>-2.62</v>
+        <v>-2.03</v>
       </c>
       <c r="Q52" t="n">
         <v>1.8</v>
@@ -14556,13 +14556,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2091</v>
+        <v>0.2086</v>
       </c>
       <c r="O53" t="n">
         <v>10241</v>
       </c>
       <c r="P53" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="Q53" t="n">
         <v>0.2104</v>
@@ -15516,13 +15516,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.3561</v>
+        <v>3.41</v>
       </c>
       <c r="O61" t="n">
         <v>6435</v>
       </c>
       <c r="P61" t="n">
-        <v>-1.44</v>
+        <v>0.15</v>
       </c>
       <c r="Q61" t="n">
         <v>3.49</v>
@@ -15876,13 +15876,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.4898</v>
+        <v>1.45</v>
       </c>
       <c r="O64" t="n">
         <v>7426</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.43</v>
+        <v>-3.09</v>
       </c>
       <c r="Q64" t="n">
         <v>2.77</v>
@@ -15996,13 +15996,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.28</v>
+        <v>4.176</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>4.26</v>
+        <v>1.73</v>
       </c>
       <c r="Q65" t="n">
         <v>4.3</v>
@@ -16236,13 +16236,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>13.82</v>
+        <v>13.9</v>
       </c>
       <c r="O67" t="n">
         <v>177376</v>
       </c>
       <c r="P67" t="n">
-        <v>-1.07</v>
+        <v>-0.5</v>
       </c>
       <c r="Q67" t="n">
         <v>14.8497</v>
@@ -16596,13 +16596,13 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0.7578</v>
+        <v>0.75</v>
       </c>
       <c r="O70" t="n">
         <v>9470</v>
       </c>
       <c r="P70" t="n">
-        <v>1.12</v>
+        <v>0.08</v>
       </c>
       <c r="Q70" t="n">
         <v>0.8671</v>
@@ -17316,13 +17316,13 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>1.7207</v>
+        <v>1.73</v>
       </c>
       <c r="O76" t="n">
         <v>16311</v>
       </c>
       <c r="P76" t="n">
-        <v>0.04</v>
+        <v>0.58</v>
       </c>
       <c r="Q76" t="n">
         <v>1.74</v>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>38.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0.75</v>
+        <v>0.743</v>
       </c>
       <c r="Q3" t="n">
         <v>9470</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08</v>
+        <v>-0.85</v>
       </c>
       <c r="S3" t="n">
         <v>0.777</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>73.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" t="n">
         <v>5280</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.05</v>
+        <v>-0.63</v>
       </c>
       <c r="S4" t="n">
         <v>7.86</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         <v>64.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.5401</v>
+        <v>3.55</v>
       </c>
       <c r="Q6" t="n">
         <v>60653</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="S6" t="n">
         <v>3.33</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>65.8</v>
       </c>
       <c r="P7" t="n">
-        <v>13.73</v>
+        <v>13.5116</v>
       </c>
       <c r="Q7" t="n">
         <v>65774</v>
       </c>
       <c r="R7" t="n">
-        <v>0.59</v>
+        <v>-1.01</v>
       </c>
       <c r="S7" t="n">
         <v>12.44</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1244,13 +1244,13 @@
         <v>66.59999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" t="n">
         <v>5047</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.35</v>
+        <v>3.18</v>
       </c>
       <c r="S8" t="n">
         <v>1.32</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1342,13 +1342,13 @@
         <v>59.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3.8371</v>
+        <v>3.68</v>
       </c>
       <c r="Q9" t="n">
         <v>10324</v>
       </c>
       <c r="R9" t="n">
-        <v>5.13</v>
+        <v>0.82</v>
       </c>
       <c r="S9" t="n">
         <v>3.72</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1734,13 +1734,13 @@
         <v>60.9</v>
       </c>
       <c r="P13" t="n">
-        <v>4.3495</v>
+        <v>4.33</v>
       </c>
       <c r="Q13" t="n">
         <v>9477</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.92</v>
+        <v>-1.37</v>
       </c>
       <c r="S13" t="n">
         <v>4.2265</v>
@@ -1752,7 +1752,7 @@
         <v>-3.72</v>
       </c>
       <c r="V13" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="W13" t="n">
         <v>4.11</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2322,13 +2322,13 @@
         <v>30.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1785</v>
+        <v>0.1755</v>
       </c>
       <c r="Q19" t="n">
         <v>74807</v>
       </c>
       <c r="R19" t="n">
-        <v>7.01</v>
+        <v>5.22</v>
       </c>
       <c r="S19" t="n">
         <v>0.2037</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>26.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0.39</v>
+        <v>0.3921</v>
       </c>
       <c r="Q20" t="n">
         <v>10218</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.52</v>
+        <v>-2</v>
       </c>
       <c r="S20" t="n">
         <v>0.4813</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2616,13 +2616,13 @@
         <v>71.90000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3862</v>
+        <v>2.42</v>
       </c>
       <c r="Q22" t="n">
         <v>5717</v>
       </c>
       <c r="R22" t="n">
-        <v>-2.6</v>
+        <v>-1.22</v>
       </c>
       <c r="S22" t="n">
         <v>2.1345</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>61.8</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q23" t="n">
         <v>495485</v>
       </c>
       <c r="R23" t="n">
-        <v>0.25</v>
+        <v>0.76</v>
       </c>
       <c r="S23" t="n">
         <v>1.6781</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2910,13 +2910,13 @@
         <v>61.9</v>
       </c>
       <c r="P25" t="n">
-        <v>4.176</v>
+        <v>4.18</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="S25" t="n">
         <v>4.09</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>81.90000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.4611</v>
+        <v>4.4608</v>
       </c>
       <c r="Q26" t="n">
         <v>40316</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.49</v>
+        <v>-2.5</v>
       </c>
       <c r="S26" t="n">
         <v>4.11</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3204,13 +3204,13 @@
         <v>73.2</v>
       </c>
       <c r="P28" t="n">
-        <v>4.21</v>
+        <v>4.0597</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>26.42</v>
+        <v>21.91</v>
       </c>
       <c r="S28" t="n">
         <v>17</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3400,13 +3400,13 @@
         <v>32</v>
       </c>
       <c r="P30" t="n">
-        <v>0.59</v>
+        <v>0.5998</v>
       </c>
       <c r="Q30" t="n">
         <v>49655</v>
       </c>
       <c r="R30" t="n">
-        <v>7.61</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="S30" t="n">
         <v>0.643</v>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="P35" t="n">
-        <v>1.963</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
         <v>40733</v>
       </c>
       <c r="R35" t="n">
-        <v>0.67</v>
+        <v>-1.54</v>
       </c>
       <c r="S35" t="n">
         <v>2.0389</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3988,13 +3988,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="P36" t="n">
-        <v>1.6097</v>
+        <v>1.64</v>
       </c>
       <c r="Q36" t="n">
         <v>54639</v>
       </c>
       <c r="R36" t="n">
-        <v>-2.03</v>
+        <v>-0.19</v>
       </c>
       <c r="S36" t="n">
         <v>1.62</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>29.7</v>
       </c>
       <c r="P39" t="n">
-        <v>7.7005</v>
+        <v>7.65</v>
       </c>
       <c r="Q39" t="n">
         <v>6127</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.53</v>
+        <v>-2.17</v>
       </c>
       <c r="S39" t="n">
         <v>7.68</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>28.1</v>
       </c>
       <c r="P40" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="Q40" t="n">
         <v>45452</v>
       </c>
       <c r="R40" t="n">
-        <v>3.81</v>
+        <v>6.27</v>
       </c>
       <c r="S40" t="n">
         <v>3.7902</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4576,13 +4576,13 @@
         <v>51.6</v>
       </c>
       <c r="P42" t="n">
-        <v>7.2</v>
+        <v>7.05</v>
       </c>
       <c r="Q42" t="n">
         <v>13347</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.14</v>
+        <v>-2.22</v>
       </c>
       <c r="S42" t="n">
         <v>8</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4972,13 +4972,13 @@
         <v>99</v>
       </c>
       <c r="P46" t="n">
-        <v>7.5</v>
+        <v>6.97</v>
       </c>
       <c r="Q46" t="n">
         <v>3033</v>
       </c>
       <c r="R46" t="n">
-        <v>-22.52</v>
+        <v>-28</v>
       </c>
       <c r="S46" t="n">
         <v>10.17</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5070,13 +5070,13 @@
         <v>27.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0.222</v>
+        <v>0.2128</v>
       </c>
       <c r="Q47" t="n">
         <v>11695</v>
       </c>
       <c r="R47" t="n">
-        <v>2.97</v>
+        <v>-1.3</v>
       </c>
       <c r="S47" t="n">
         <v>0.2029</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5266,13 +5266,13 @@
         <v>43.8</v>
       </c>
       <c r="P49" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Q49" t="n">
         <v>126337</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S49" t="n">
         <v>0.9792999999999999</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5658,13 +5658,13 @@
         <v>42.7</v>
       </c>
       <c r="P53" t="n">
-        <v>0.9506</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="Q53" t="n">
         <v>95246</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.89</v>
+        <v>0.01</v>
       </c>
       <c r="S53" t="n">
         <v>0.8951</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5854,13 +5854,13 @@
         <v>49.4</v>
       </c>
       <c r="P55" t="n">
-        <v>1.73</v>
+        <v>1.7697</v>
       </c>
       <c r="Q55" t="n">
         <v>12359</v>
       </c>
       <c r="R55" t="n">
-        <v>1.76</v>
+        <v>4.1</v>
       </c>
       <c r="S55" t="n">
         <v>1.72</v>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6050,13 +6050,13 @@
         <v>42</v>
       </c>
       <c r="P57" t="n">
-        <v>12.85</v>
+        <v>12.84</v>
       </c>
       <c r="Q57" t="n">
         <v>8737</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.68</v>
+        <v>-1.76</v>
       </c>
       <c r="S57" t="n">
         <v>15.48</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6250,13 +6250,13 @@
         <v>69</v>
       </c>
       <c r="P59" t="n">
-        <v>0.4933</v>
+        <v>0.4665</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-14.18</v>
+        <v>-18.84</v>
       </c>
       <c r="S59" t="n">
         <v>0.26</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6348,13 +6348,13 @@
         <v>82.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1.75</v>
+        <v>1.7699</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="S60" t="n">
         <v>1.61</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6446,13 +6446,13 @@
         <v>75.90000000000001</v>
       </c>
       <c r="P61" t="n">
-        <v>2.5845</v>
+        <v>2.58</v>
       </c>
       <c r="Q61" t="n">
         <v>10529</v>
       </c>
       <c r="R61" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="S61" t="n">
         <v>2.46</v>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         <v>62.1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2086</v>
+        <v>0.2088</v>
       </c>
       <c r="Q62" t="n">
         <v>10241</v>
       </c>
       <c r="R62" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="S62" t="n">
         <v>0.178</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6642,13 +6642,13 @@
         <v>97</v>
       </c>
       <c r="P63" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="Q63" t="n">
         <v>3188</v>
       </c>
       <c r="R63" t="n">
-        <v>-2.59</v>
+        <v>-3.4</v>
       </c>
       <c r="S63" t="n">
         <v>3.15</v>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -6740,13 +6740,13 @@
         <v>79.90000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>8.958500000000001</v>
+        <v>9.0876</v>
       </c>
       <c r="Q64" t="n">
         <v>7560</v>
       </c>
       <c r="R64" t="n">
-        <v>-5.75</v>
+        <v>-4.39</v>
       </c>
       <c r="S64" t="n">
         <v>6.04</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -6838,13 +6838,13 @@
         <v>37.9</v>
       </c>
       <c r="P65" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q65" t="n">
         <v>1200</v>
       </c>
       <c r="R65" t="n">
-        <v>-1.85</v>
+        <v>-0.93</v>
       </c>
       <c r="S65" t="n">
         <v>1.105</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -6936,13 +6936,13 @@
         <v>33.6</v>
       </c>
       <c r="P66" t="n">
-        <v>0.4342</v>
+        <v>0.4343</v>
       </c>
       <c r="Q66" t="n">
         <v>49975</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="S66" t="n">
         <v>0.48</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -7034,13 +7034,13 @@
         <v>38.8</v>
       </c>
       <c r="P67" t="n">
-        <v>14.3</v>
+        <v>14.41</v>
       </c>
       <c r="Q67" t="n">
         <v>106295</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="S67" t="n">
         <v>15.42</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>77.90000000000001</v>
       </c>
       <c r="P69" t="n">
-        <v>6.0139</v>
+        <v>6.04</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>-0.51</v>
+        <v>-0.08</v>
       </c>
       <c r="S69" t="n">
         <v>5.85</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -7426,13 +7426,13 @@
         <v>26.4</v>
       </c>
       <c r="P71" t="n">
-        <v>1.0601</v>
+        <v>1.05</v>
       </c>
       <c r="Q71" t="n">
         <v>848</v>
       </c>
       <c r="R71" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.26</v>
       </c>
       <c r="S71" t="n">
         <v>1.48</v>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -7622,13 +7622,13 @@
         <v>17</v>
       </c>
       <c r="P73" t="n">
-        <v>1.45</v>
+        <v>1.4602</v>
       </c>
       <c r="Q73" t="n">
         <v>7426</v>
       </c>
       <c r="R73" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="S73" t="n">
         <v>1.63</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -7720,13 +7720,13 @@
         <v>61.2</v>
       </c>
       <c r="P74" t="n">
-        <v>1.5</v>
+        <v>1.5097</v>
       </c>
       <c r="Q74" t="n">
         <v>543273</v>
       </c>
       <c r="R74" t="n">
-        <v>-1.32</v>
+        <v>-0.68</v>
       </c>
       <c r="S74" t="n">
         <v>1.33</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -7916,13 +7916,13 @@
         <v>34.9</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0968</v>
+        <v>0.0961</v>
       </c>
       <c r="Q76" t="n">
         <v>157511</v>
       </c>
       <c r="R76" t="n">
-        <v>0.62</v>
+        <v>-0.1</v>
       </c>
       <c r="S76" t="n">
         <v>0.082</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -8014,13 +8014,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="P77" t="n">
-        <v>5.3499</v>
+        <v>5.45</v>
       </c>
       <c r="Q77" t="n">
         <v>25729</v>
       </c>
       <c r="R77" t="n">
-        <v>38.75</v>
+        <v>41.35</v>
       </c>
       <c r="S77" t="n">
         <v>3.73</v>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8116,13 +8116,13 @@
         <v>31.8</v>
       </c>
       <c r="P78" t="n">
-        <v>3.46</v>
+        <v>3.4193</v>
       </c>
       <c r="Q78" t="n">
         <v>27607</v>
       </c>
       <c r="R78" t="n">
-        <v>1.17</v>
+        <v>-0.02</v>
       </c>
       <c r="S78" t="n">
         <v>4.72</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8436,13 +8436,13 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>7.5</v>
+        <v>6.97</v>
       </c>
       <c r="O2" t="n">
         <v>3033</v>
       </c>
       <c r="P2" t="n">
-        <v>-22.52</v>
+        <v>-28</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
@@ -8556,13 +8556,13 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
         <v>3188</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.59</v>
+        <v>-3.4</v>
       </c>
       <c r="Q3" t="n">
         <v>3.7192</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4933</v>
+        <v>0.4665</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-14.18</v>
+        <v>-18.84</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6899999999999999</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.21</v>
+        <v>4.0597</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>26.42</v>
+        <v>21.91</v>
       </c>
       <c r="Q5" t="n">
         <v>6.88</v>
@@ -8916,13 +8916,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0601</v>
+        <v>1.05</v>
       </c>
       <c r="O6" t="n">
         <v>848</v>
       </c>
       <c r="P6" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1785</v>
+        <v>0.1755</v>
       </c>
       <c r="O7" t="n">
         <v>74807</v>
       </c>
       <c r="P7" t="n">
-        <v>7.01</v>
+        <v>5.22</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2349</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3499</v>
+        <v>5.45</v>
       </c>
       <c r="O8" t="n">
         <v>25729</v>
       </c>
       <c r="P8" t="n">
-        <v>38.75</v>
+        <v>41.35</v>
       </c>
       <c r="Q8" t="n">
         <v>6.49</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.958500000000001</v>
+        <v>9.0876</v>
       </c>
       <c r="O9" t="n">
         <v>7560</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.75</v>
+        <v>-4.39</v>
       </c>
       <c r="Q9" t="n">
         <v>9.890000000000001</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.222</v>
+        <v>0.2128</v>
       </c>
       <c r="O10" t="n">
         <v>11695</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>-1.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0.24</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.59</v>
+        <v>0.5998</v>
       </c>
       <c r="O12" t="n">
         <v>49655</v>
       </c>
       <c r="P12" t="n">
-        <v>7.61</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>0.86</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.46</v>
+        <v>3.4193</v>
       </c>
       <c r="O14" t="n">
         <v>27607</v>
       </c>
       <c r="P14" t="n">
-        <v>1.17</v>
+        <v>-0.02</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P/S 3.4x vs 1.4x median — trading at premium | P/B -1.0x vs 0.5x median — trading at discount | EV/EBITDA -104.6x vs -2.5x median — trading at premium</t>
+          <t>P/S 3.4x vs 1.4x median — trading at premium | P/B -1.0x vs 0.5x median — trading at discount | EV/EBITDA -104.6x vs -2.4x median — trading at premium</t>
         </is>
       </c>
       <c r="AE14" t="n">
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>45452</v>
       </c>
       <c r="P15" t="n">
-        <v>3.81</v>
+        <v>6.27</v>
       </c>
       <c r="Q15" t="n">
         <v>5.15</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="O16" t="n">
         <v>1200</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.85</v>
+        <v>-0.93</v>
       </c>
       <c r="Q16" t="n">
         <v>1.55</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.39</v>
+        <v>0.3921</v>
       </c>
       <c r="O18" t="n">
         <v>10218</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.52</v>
+        <v>-2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.4038</v>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/S 1.1x vs 1.4x median — trading at discount | P/B 2.2x vs 0.5x median — trading at premium | EV/EBITDA -2.9x vs -2.5x median — in-line | Graham # $7.75</t>
+          <t>P/S 1.1x vs 1.4x median — trading at discount | P/B 2.2x vs 0.5x median — trading at premium | EV/EBITDA -2.9x vs -2.4x median — in-line | Graham # $7.75</t>
         </is>
       </c>
       <c r="AE18" t="n">
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.460000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O19" t="n">
         <v>5280</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.05</v>
+        <v>-0.63</v>
       </c>
       <c r="Q19" t="n">
         <v>9.84</v>
@@ -10596,13 +10596,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3862</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
         <v>5717</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.6</v>
+        <v>-1.22</v>
       </c>
       <c r="Q20" t="n">
         <v>2.46</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4342</v>
+        <v>0.4343</v>
       </c>
       <c r="O21" t="n">
         <v>49975</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="Q21" t="n">
         <v>0.524</v>
@@ -10956,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>1.7699</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
         <v>1.77</v>
@@ -11196,13 +11196,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>12.85</v>
+        <v>12.84</v>
       </c>
       <c r="O25" t="n">
         <v>8737</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.68</v>
+        <v>-1.76</v>
       </c>
       <c r="Q25" t="n">
         <v>26.75</v>
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>P/S 1.7x vs 1.4x median — trading at premium | P/B -0.4x vs 0.5x median — trading at discount | EV/EBITDA -6.1x vs -2.5x median — trading at premium | Analyst target $108.75</t>
+          <t>P/S 1.7x vs 1.4x median — trading at premium | P/B -0.4x vs 0.5x median — trading at discount | EV/EBITDA -6.1x vs -2.4x median — trading at premium | Analyst target $108.75</t>
         </is>
       </c>
       <c r="AE25" t="n">
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O26" t="n">
         <v>495485</v>
       </c>
       <c r="P26" t="n">
-        <v>0.25</v>
+        <v>0.76</v>
       </c>
       <c r="Q26" t="n">
         <v>1.99</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>P/S 82.3x vs 1.4x median — trading at premium | P/B 1.2x vs 0.5x median — trading at premium | EV/EBITDA -1.0x vs -2.5x median — trading at discount | Analyst target $2.00 | Graham # $1.63</t>
+          <t>P/S 82.3x vs 1.4x median — trading at premium | P/B 1.2x vs 0.5x median — trading at premium | EV/EBITDA -1.0x vs -2.4x median — trading at discount | Analyst target $2.00 | Graham # $1.63</t>
         </is>
       </c>
       <c r="AE26" t="n">
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0968</v>
+        <v>0.0961</v>
       </c>
       <c r="O27" t="n">
         <v>157511</v>
       </c>
       <c r="P27" t="n">
-        <v>0.62</v>
+        <v>-0.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1587</v>
@@ -11556,13 +11556,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8371</v>
+        <v>3.68</v>
       </c>
       <c r="O28" t="n">
         <v>10324</v>
       </c>
       <c r="P28" t="n">
-        <v>5.13</v>
+        <v>0.82</v>
       </c>
       <c r="Q28" t="n">
         <v>3.89</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="O30" t="n">
         <v>126337</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
         <v>1.08</v>
@@ -12036,13 +12036,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5401</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>60653</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="Q32" t="n">
         <v>3.56</v>
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="O34" t="n">
         <v>5047</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.35</v>
+        <v>3.18</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
@@ -12396,13 +12396,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>7.7005</v>
+        <v>7.65</v>
       </c>
       <c r="O35" t="n">
         <v>6127</v>
       </c>
       <c r="P35" t="n">
-        <v>-1.53</v>
+        <v>-2.17</v>
       </c>
       <c r="Q35" t="n">
         <v>11</v>
@@ -12516,13 +12516,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>13.73</v>
+        <v>13.5116</v>
       </c>
       <c r="O36" t="n">
         <v>65774</v>
       </c>
       <c r="P36" t="n">
-        <v>0.59</v>
+        <v>-1.01</v>
       </c>
       <c r="Q36" t="n">
         <v>13.9</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4611</v>
+        <v>4.4608</v>
       </c>
       <c r="O38" t="n">
         <v>40316</v>
       </c>
       <c r="P38" t="n">
-        <v>-2.49</v>
+        <v>-2.5</v>
       </c>
       <c r="Q38" t="n">
         <v>4.589</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.2</v>
+        <v>7.05</v>
       </c>
       <c r="O42" t="n">
         <v>13347</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.14</v>
+        <v>-2.22</v>
       </c>
       <c r="Q42" t="n">
         <v>16.41</v>
@@ -13596,13 +13596,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6.0139</v>
+        <v>6.04</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.51</v>
+        <v>-0.08</v>
       </c>
       <c r="Q45" t="n">
         <v>6.12</v>
@@ -13716,13 +13716,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>14.3</v>
+        <v>14.41</v>
       </c>
       <c r="O46" t="n">
         <v>106295</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="Q46" t="n">
         <v>15.9</v>
@@ -13836,16 +13836,16 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3495</v>
+        <v>4.33</v>
       </c>
       <c r="O47" t="n">
         <v>9477</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.92</v>
+        <v>-1.37</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="R47" t="n">
         <v>4.11</v>
@@ -13956,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.5</v>
+        <v>1.5097</v>
       </c>
       <c r="O48" t="n">
         <v>543273</v>
       </c>
       <c r="P48" t="n">
-        <v>-1.32</v>
+        <v>-0.68</v>
       </c>
       <c r="Q48" t="n">
         <v>1.525</v>
@@ -14436,13 +14436,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.6097</v>
+        <v>1.64</v>
       </c>
       <c r="O52" t="n">
         <v>54639</v>
       </c>
       <c r="P52" t="n">
-        <v>-2.03</v>
+        <v>-0.19</v>
       </c>
       <c r="Q52" t="n">
         <v>1.8</v>
@@ -14556,13 +14556,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2086</v>
+        <v>0.2088</v>
       </c>
       <c r="O53" t="n">
         <v>10241</v>
       </c>
       <c r="P53" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q53" t="n">
         <v>0.2104</v>
@@ -15036,13 +15036,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.5845</v>
+        <v>2.58</v>
       </c>
       <c r="O57" t="n">
         <v>10529</v>
       </c>
       <c r="P57" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="Q57" t="n">
         <v>2.6</v>
@@ -15756,13 +15756,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.9506</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="O63" t="n">
         <v>95246</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.89</v>
+        <v>0.01</v>
       </c>
       <c r="Q63" t="n">
         <v>0.97</v>
@@ -15876,13 +15876,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.45</v>
+        <v>1.4602</v>
       </c>
       <c r="O64" t="n">
         <v>7426</v>
       </c>
       <c r="P64" t="n">
-        <v>-3.09</v>
+        <v>-2.41</v>
       </c>
       <c r="Q64" t="n">
         <v>2.77</v>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="AA64" t="n">
-        <v>-2.52</v>
+        <v>-2.44</v>
       </c>
       <c r="AB64" t="n">
         <v/>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>P/S 0.6x vs 1.4x median — trading at discount | P/B 0.1x vs 0.5x median — trading at discount | EV/EBITDA -2.5x vs -2.5x median — in-line | Graham # $329.77</t>
+          <t>P/S 0.6x vs 1.4x median — trading at discount | P/B 0.1x vs 0.5x median — trading at discount | EV/EBITDA -2.4x vs -2.4x median — in-line | Graham # $329.77</t>
         </is>
       </c>
       <c r="AE64" t="n">
@@ -15996,13 +15996,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.176</v>
+        <v>4.18</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q65" t="n">
         <v>4.3</v>
@@ -16476,13 +16476,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.73</v>
+        <v>1.7697</v>
       </c>
       <c r="O69" t="n">
         <v>12359</v>
       </c>
       <c r="P69" t="n">
-        <v>1.76</v>
+        <v>4.1</v>
       </c>
       <c r="Q69" t="n">
         <v>1.87</v>
@@ -16596,13 +16596,13 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0.75</v>
+        <v>0.743</v>
       </c>
       <c r="O70" t="n">
         <v>9470</v>
       </c>
       <c r="P70" t="n">
-        <v>0.08</v>
+        <v>-0.85</v>
       </c>
       <c r="Q70" t="n">
         <v>0.8671</v>
@@ -16956,13 +16956,13 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.963</v>
+        <v>1.92</v>
       </c>
       <c r="O73" t="n">
         <v>40733</v>
       </c>
       <c r="P73" t="n">
-        <v>0.67</v>
+        <v>-1.54</v>
       </c>
       <c r="Q73" t="n">
         <v>2.0397</v>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>P/B 2.1x vs 0.5x median — trading at premium | EV/EBITDA -0.6x vs -2.5x median — trading at discount | Analyst target $3.00</t>
+          <t>P/B 2.1x vs 0.5x median — trading at premium | EV/EBITDA -0.6x vs -2.4x median — trading at discount | Analyst target $3.00</t>
         </is>
       </c>
       <c r="AE73" t="n">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 1.4x median — trading at discount | P/B 0.5x vs 0.5x median — in-line | EV/EBITDA 9.1x vs -2.5x median — trading at discount | Analyst target $12.00</t>
+          <t>P/S 0.4x vs 1.4x median — trading at discount | P/B 0.5x vs 0.5x median — in-line | EV/EBITDA 9.1x vs -2.4x median — trading at discount | Analyst target $12.00</t>
         </is>
       </c>
       <c r="AE74" t="n">

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>38.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0.743</v>
+        <v>0.7605</v>
       </c>
       <c r="Q3" t="n">
         <v>9470</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.85</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
         <v>0.777</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>73.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>9.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>5280</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.63</v>
+        <v>-1.15</v>
       </c>
       <c r="S4" t="n">
         <v>7.86</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>65.8</v>
       </c>
       <c r="P7" t="n">
-        <v>13.5116</v>
+        <v>13.7</v>
       </c>
       <c r="Q7" t="n">
         <v>65774</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.01</v>
+        <v>0.37</v>
       </c>
       <c r="S7" t="n">
         <v>12.44</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1342,13 +1342,13 @@
         <v>59.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3.68</v>
+        <v>3.6859</v>
       </c>
       <c r="Q9" t="n">
         <v>10324</v>
       </c>
       <c r="R9" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="S9" t="n">
         <v>3.72</v>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1734,13 +1734,13 @@
         <v>60.9</v>
       </c>
       <c r="P13" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="Q13" t="n">
         <v>9477</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.37</v>
+        <v>-0.23</v>
       </c>
       <c r="S13" t="n">
         <v>4.2265</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2322,13 +2322,13 @@
         <v>30.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1755</v>
+        <v>0.171</v>
       </c>
       <c r="Q19" t="n">
         <v>74807</v>
       </c>
       <c r="R19" t="n">
-        <v>5.22</v>
+        <v>2.52</v>
       </c>
       <c r="S19" t="n">
         <v>0.2037</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>26.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3921</v>
+        <v>0.3969</v>
       </c>
       <c r="Q20" t="n">
         <v>10218</v>
       </c>
       <c r="R20" t="n">
-        <v>-2</v>
+        <v>-0.8</v>
       </c>
       <c r="S20" t="n">
         <v>0.4813</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>61.8</v>
       </c>
       <c r="P23" t="n">
-        <v>1.99</v>
+        <v>1.9899</v>
       </c>
       <c r="Q23" t="n">
         <v>495485</v>
       </c>
       <c r="R23" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="S23" t="n">
         <v>1.6781</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2812,13 +2812,13 @@
         <v>71.90000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
         <v>20075</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.05</v>
+        <v>-2.32</v>
       </c>
       <c r="S24" t="n">
         <v>2.43</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>81.90000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.4608</v>
+        <v>4.46</v>
       </c>
       <c r="Q26" t="n">
         <v>40316</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.5</v>
+        <v>-2.51</v>
       </c>
       <c r="S26" t="n">
         <v>4.11</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3204,13 +3204,13 @@
         <v>73.2</v>
       </c>
       <c r="P28" t="n">
-        <v>4.0597</v>
+        <v>4.48</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>21.91</v>
+        <v>34.53</v>
       </c>
       <c r="S28" t="n">
         <v>17</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3400,13 +3400,13 @@
         <v>32</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5998</v>
+        <v>0.5868</v>
       </c>
       <c r="Q30" t="n">
         <v>49655</v>
       </c>
       <c r="R30" t="n">
-        <v>9.390000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="S30" t="n">
         <v>0.643</v>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="P35" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q35" t="n">
         <v>40733</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.54</v>
+        <v>1.54</v>
       </c>
       <c r="S35" t="n">
         <v>2.0389</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>29.7</v>
       </c>
       <c r="P39" t="n">
-        <v>7.65</v>
+        <v>7.3</v>
       </c>
       <c r="Q39" t="n">
         <v>6127</v>
       </c>
       <c r="R39" t="n">
-        <v>-2.17</v>
+        <v>-6.65</v>
       </c>
       <c r="S39" t="n">
         <v>7.68</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>28.1</v>
       </c>
       <c r="P40" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="Q40" t="n">
         <v>45452</v>
       </c>
       <c r="R40" t="n">
-        <v>6.27</v>
+        <v>16.62</v>
       </c>
       <c r="S40" t="n">
         <v>3.7902</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4576,13 +4576,13 @@
         <v>51.6</v>
       </c>
       <c r="P42" t="n">
-        <v>7.05</v>
+        <v>6.81</v>
       </c>
       <c r="Q42" t="n">
         <v>13347</v>
       </c>
       <c r="R42" t="n">
-        <v>-2.22</v>
+        <v>-5.55</v>
       </c>
       <c r="S42" t="n">
         <v>8</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>54.5</v>
       </c>
       <c r="P43" t="n">
-        <v>13.9</v>
+        <v>13.9108</v>
       </c>
       <c r="Q43" t="n">
         <v>177376</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="S43" t="n">
         <v>12.71</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4972,13 +4972,13 @@
         <v>99</v>
       </c>
       <c r="P46" t="n">
-        <v>6.97</v>
+        <v>6.26</v>
       </c>
       <c r="Q46" t="n">
         <v>3033</v>
       </c>
       <c r="R46" t="n">
-        <v>-28</v>
+        <v>-35.33</v>
       </c>
       <c r="S46" t="n">
         <v>10.17</v>
@@ -4993,7 +4993,7 @@
         <v>10.41</v>
       </c>
       <c r="W46" t="n">
-        <v>6.68</v>
+        <v>6.26</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5070,13 +5070,13 @@
         <v>27.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2128</v>
+        <v>0.2096</v>
       </c>
       <c r="Q47" t="n">
         <v>11695</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.3</v>
+        <v>-2.78</v>
       </c>
       <c r="S47" t="n">
         <v>0.2029</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5168,13 +5168,13 @@
         <v>48.4</v>
       </c>
       <c r="P48" t="n">
-        <v>14.4125</v>
+        <v>14.4</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S48" t="n">
         <v>14.01</v>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5266,13 +5266,13 @@
         <v>43.8</v>
       </c>
       <c r="P49" t="n">
-        <v>1.05</v>
+        <v>1.0318</v>
       </c>
       <c r="Q49" t="n">
         <v>126337</v>
       </c>
       <c r="R49" t="n">
-        <v>1.94</v>
+        <v>0.17</v>
       </c>
       <c r="S49" t="n">
         <v>0.9792999999999999</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6050,13 +6050,13 @@
         <v>42</v>
       </c>
       <c r="P57" t="n">
-        <v>12.84</v>
+        <v>12.6</v>
       </c>
       <c r="Q57" t="n">
         <v>8737</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.76</v>
+        <v>-3.6</v>
       </c>
       <c r="S57" t="n">
         <v>15.48</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6250,13 +6250,13 @@
         <v>69</v>
       </c>
       <c r="P59" t="n">
-        <v>0.4665</v>
+        <v>0.4528</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-18.84</v>
+        <v>-21.22</v>
       </c>
       <c r="S59" t="n">
         <v>0.26</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6348,13 +6348,13 @@
         <v>82.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1.7699</v>
+        <v>1.7694</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="S60" t="n">
         <v>1.61</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         <v>62.1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2088</v>
+        <v>0.208</v>
       </c>
       <c r="Q62" t="n">
         <v>10241</v>
       </c>
       <c r="R62" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="S62" t="n">
         <v>0.178</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -6740,13 +6740,13 @@
         <v>79.90000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>9.0876</v>
+        <v>8.803100000000001</v>
       </c>
       <c r="Q64" t="n">
         <v>7560</v>
       </c>
       <c r="R64" t="n">
-        <v>-4.39</v>
+        <v>-7.38</v>
       </c>
       <c r="S64" t="n">
         <v>6.04</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -6838,13 +6838,13 @@
         <v>37.9</v>
       </c>
       <c r="P65" t="n">
-        <v>1.07</v>
+        <v>1.0799</v>
       </c>
       <c r="Q65" t="n">
         <v>1200</v>
       </c>
       <c r="R65" t="n">
-        <v>-0.93</v>
+        <v>-0.01</v>
       </c>
       <c r="S65" t="n">
         <v>1.105</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -6936,13 +6936,13 @@
         <v>33.6</v>
       </c>
       <c r="P66" t="n">
-        <v>0.4343</v>
+        <v>0.434</v>
       </c>
       <c r="Q66" t="n">
         <v>49975</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="S66" t="n">
         <v>0.48</v>
@@ -6957,7 +6957,7 @@
         <v>0.524</v>
       </c>
       <c r="W66" t="n">
-        <v>0.4293</v>
+        <v>0.4251</v>
       </c>
       <c r="X66" t="b">
         <v>1</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7132,13 +7132,13 @@
         <v>48.7</v>
       </c>
       <c r="P68" t="n">
-        <v>0.6001</v>
+        <v>0.6076</v>
       </c>
       <c r="Q68" t="n">
         <v>9914</v>
       </c>
       <c r="R68" t="n">
-        <v>-0.13</v>
+        <v>1.11</v>
       </c>
       <c r="S68" t="n">
         <v>0.58</v>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>77.90000000000001</v>
       </c>
       <c r="P69" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="S69" t="n">
         <v>5.85</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -7622,13 +7622,13 @@
         <v>17</v>
       </c>
       <c r="P73" t="n">
-        <v>1.4602</v>
+        <v>1.5</v>
       </c>
       <c r="Q73" t="n">
         <v>7426</v>
       </c>
       <c r="R73" t="n">
-        <v>-2.41</v>
+        <v>0.25</v>
       </c>
       <c r="S73" t="n">
         <v>1.63</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -7720,13 +7720,13 @@
         <v>61.2</v>
       </c>
       <c r="P74" t="n">
-        <v>1.5097</v>
+        <v>1.5</v>
       </c>
       <c r="Q74" t="n">
         <v>543273</v>
       </c>
       <c r="R74" t="n">
-        <v>-0.68</v>
+        <v>-1.32</v>
       </c>
       <c r="S74" t="n">
         <v>1.33</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -7916,13 +7916,13 @@
         <v>34.9</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0961</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="Q76" t="n">
         <v>157511</v>
       </c>
       <c r="R76" t="n">
-        <v>-0.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S76" t="n">
         <v>0.082</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -8014,13 +8014,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="P77" t="n">
-        <v>5.45</v>
+        <v>5.2797</v>
       </c>
       <c r="Q77" t="n">
         <v>25729</v>
       </c>
       <c r="R77" t="n">
-        <v>41.35</v>
+        <v>36.93</v>
       </c>
       <c r="S77" t="n">
         <v>3.73</v>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8116,13 +8116,13 @@
         <v>31.8</v>
       </c>
       <c r="P78" t="n">
-        <v>3.4193</v>
+        <v>3.43</v>
       </c>
       <c r="Q78" t="n">
         <v>27607</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.02</v>
+        <v>0.3</v>
       </c>
       <c r="S78" t="n">
         <v>4.72</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8436,19 +8436,19 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>6.97</v>
+        <v>6.26</v>
       </c>
       <c r="O2" t="n">
         <v>3033</v>
       </c>
       <c r="P2" t="n">
-        <v>-28</v>
+        <v>-35.33</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
       </c>
       <c r="R2" t="n">
-        <v>6.68</v>
+        <v>6.26</v>
       </c>
       <c r="S2" t="n">
         <v>10.17</v>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>-7.77</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="AB3" t="n">
         <v>11.33</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>P/S 0.8x vs 0.7x median — in-line | P/B 4.7x vs 0.8x median — trading at premium | EV/EBITDA -7.8x vs -1.4x median — trading at premium | Analyst target $11.33</t>
+          <t>P/S 0.8x vs 0.7x median — in-line | P/B 4.7x vs 0.8x median — trading at premium | EV/EBITDA -8.7x vs -1.4x median — trading at premium | Analyst target $11.33</t>
         </is>
       </c>
       <c r="AE3" t="n">
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4665</v>
+        <v>0.4528</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-18.84</v>
+        <v>-21.22</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6899999999999999</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.0597</v>
+        <v>4.48</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>21.91</v>
+        <v>34.53</v>
       </c>
       <c r="Q5" t="n">
         <v>6.88</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1755</v>
+        <v>0.171</v>
       </c>
       <c r="O7" t="n">
         <v>74807</v>
       </c>
       <c r="P7" t="n">
-        <v>5.22</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2349</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.45</v>
+        <v>5.2797</v>
       </c>
       <c r="O8" t="n">
         <v>25729</v>
       </c>
       <c r="P8" t="n">
-        <v>41.35</v>
+        <v>36.93</v>
       </c>
       <c r="Q8" t="n">
         <v>6.49</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>9.0876</v>
+        <v>8.803100000000001</v>
       </c>
       <c r="O9" t="n">
         <v>7560</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.39</v>
+        <v>-7.38</v>
       </c>
       <c r="Q9" t="n">
         <v>9.890000000000001</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2128</v>
+        <v>0.2096</v>
       </c>
       <c r="O10" t="n">
         <v>11695</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3</v>
+        <v>-2.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0.24</v>
@@ -9636,13 +9636,13 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5998</v>
+        <v>0.5868</v>
       </c>
       <c r="O12" t="n">
         <v>49655</v>
       </c>
       <c r="P12" t="n">
-        <v>9.390000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="Q12" t="n">
         <v>0.86</v>
@@ -9756,13 +9756,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>14.4125</v>
+        <v>14.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
         <v>14.4125</v>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>0.72</v>
+        <v>0.41</v>
       </c>
       <c r="AB13" t="n">
         <v>12.5</v>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P/S 1.6x vs 3.0x median — trading at discount | P/B 0.7x vs 1.0x median — trading at discount | EV/EBITDA 0.7x vs -0.9x median — trading at discount | Analyst target $12.50</t>
+          <t>P/S 1.6x vs 3.0x median — trading at discount | P/B 0.7x vs 1.0x median — trading at discount | EV/EBITDA 0.4x vs -0.9x median — trading at discount | Analyst target $12.50</t>
         </is>
       </c>
       <c r="AE13" t="n">
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4193</v>
+        <v>3.43</v>
       </c>
       <c r="O14" t="n">
         <v>27607</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.02</v>
+        <v>0.3</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P/S 3.4x vs 1.4x median — trading at premium | P/B -1.0x vs 0.5x median — trading at discount | EV/EBITDA -104.6x vs -2.4x median — trading at premium</t>
+          <t>P/S 3.4x vs 1.4x median — trading at premium | P/B -1.0x vs 0.5x median — trading at discount | EV/EBITDA -104.6x vs -2.9x median — trading at premium</t>
         </is>
       </c>
       <c r="AE14" t="n">
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>4.28</v>
       </c>
       <c r="O15" t="n">
         <v>45452</v>
       </c>
       <c r="P15" t="n">
-        <v>6.27</v>
+        <v>16.62</v>
       </c>
       <c r="Q15" t="n">
         <v>5.15</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.07</v>
+        <v>1.0799</v>
       </c>
       <c r="O16" t="n">
         <v>1200</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.93</v>
+        <v>-0.01</v>
       </c>
       <c r="Q16" t="n">
         <v>1.55</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3921</v>
+        <v>0.3969</v>
       </c>
       <c r="O18" t="n">
         <v>10218</v>
       </c>
       <c r="P18" t="n">
-        <v>-2</v>
+        <v>-0.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.4038</v>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/S 1.1x vs 1.4x median — trading at discount | P/B 2.2x vs 0.5x median — trading at premium | EV/EBITDA -2.9x vs -2.4x median — in-line | Graham # $7.75</t>
+          <t>P/S 1.1x vs 1.4x median — trading at discount | P/B 2.2x vs 0.5x median — trading at premium | EV/EBITDA -2.9x vs -2.9x median — in-line | Graham # $7.75</t>
         </is>
       </c>
       <c r="AE18" t="n">
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>5280</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.63</v>
+        <v>-1.15</v>
       </c>
       <c r="Q19" t="n">
         <v>9.84</v>
@@ -10716,19 +10716,19 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4343</v>
+        <v>0.434</v>
       </c>
       <c r="O21" t="n">
         <v>49975</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="Q21" t="n">
         <v>0.524</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4293</v>
+        <v>0.4251</v>
       </c>
       <c r="S21" t="n">
         <v>0.48</v>
@@ -10956,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7699</v>
+        <v>1.7694</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q23" t="n">
         <v>1.77</v>
@@ -10999,7 +10999,7 @@
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>-1.47</v>
+        <v>-1.65</v>
       </c>
       <c r="AB23" t="n">
         <v>6.5</v>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>P/B 10.4x vs 1.0x median — trading at premium | EV/EBITDA -1.5x vs -0.9x median — trading at premium | Analyst target $6.50</t>
+          <t>P/B 10.4x vs 1.0x median — trading at premium | EV/EBITDA -1.7x vs -0.9x median — trading at premium | Analyst target $6.50</t>
         </is>
       </c>
       <c r="AE23" t="n">
@@ -11196,13 +11196,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>12.84</v>
+        <v>12.6</v>
       </c>
       <c r="O25" t="n">
         <v>8737</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.76</v>
+        <v>-3.6</v>
       </c>
       <c r="Q25" t="n">
         <v>26.75</v>
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>P/S 1.7x vs 1.4x median — trading at premium | P/B -0.4x vs 0.5x median — trading at discount | EV/EBITDA -6.1x vs -2.4x median — trading at premium | Analyst target $108.75</t>
+          <t>P/S 1.7x vs 1.4x median — trading at premium | P/B -0.4x vs 0.5x median — trading at discount | EV/EBITDA -6.1x vs -2.9x median — trading at premium | Analyst target $108.75</t>
         </is>
       </c>
       <c r="AE25" t="n">
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.99</v>
+        <v>1.9899</v>
       </c>
       <c r="O26" t="n">
         <v>495485</v>
       </c>
       <c r="P26" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="Q26" t="n">
         <v>1.99</v>
@@ -11359,7 +11359,7 @@
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>-1</v>
+        <v>-4.06</v>
       </c>
       <c r="AB26" t="n">
         <v>2</v>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>P/S 82.3x vs 1.4x median — trading at premium | P/B 1.2x vs 0.5x median — trading at premium | EV/EBITDA -1.0x vs -2.4x median — trading at discount | Analyst target $2.00 | Graham # $1.63</t>
+          <t>P/S 82.3x vs 1.4x median — trading at premium | P/B 1.2x vs 0.5x median — trading at premium | EV/EBITDA -4.1x vs -2.9x median — trading at premium | Analyst target $2.00 | Graham # $1.63</t>
         </is>
       </c>
       <c r="AE26" t="n">
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0961</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>157511</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1587</v>
@@ -11556,13 +11556,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.68</v>
+        <v>3.6859</v>
       </c>
       <c r="O28" t="n">
         <v>10324</v>
       </c>
       <c r="P28" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="Q28" t="n">
         <v>3.89</v>
@@ -11796,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.05</v>
+        <v>1.0318</v>
       </c>
       <c r="O30" t="n">
         <v>126337</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>0.17</v>
       </c>
       <c r="Q30" t="n">
         <v>1.08</v>
@@ -12396,13 +12396,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>7.65</v>
+        <v>7.3</v>
       </c>
       <c r="O35" t="n">
         <v>6127</v>
       </c>
       <c r="P35" t="n">
-        <v>-2.17</v>
+        <v>-6.65</v>
       </c>
       <c r="Q35" t="n">
         <v>11</v>
@@ -12516,13 +12516,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>13.5116</v>
+        <v>13.7</v>
       </c>
       <c r="O36" t="n">
         <v>65774</v>
       </c>
       <c r="P36" t="n">
-        <v>-1.01</v>
+        <v>0.37</v>
       </c>
       <c r="Q36" t="n">
         <v>13.9</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4608</v>
+        <v>4.46</v>
       </c>
       <c r="O38" t="n">
         <v>40316</v>
       </c>
       <c r="P38" t="n">
-        <v>-2.5</v>
+        <v>-2.51</v>
       </c>
       <c r="Q38" t="n">
         <v>4.589</v>
@@ -12876,13 +12876,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="O39" t="n">
         <v>20075</v>
       </c>
       <c r="P39" t="n">
-        <v>-1.05</v>
+        <v>-2.32</v>
       </c>
       <c r="Q39" t="n">
         <v>2.43</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>7.05</v>
+        <v>6.81</v>
       </c>
       <c r="O42" t="n">
         <v>13347</v>
       </c>
       <c r="P42" t="n">
-        <v>-2.22</v>
+        <v>-5.55</v>
       </c>
       <c r="Q42" t="n">
         <v>16.41</v>
@@ -13596,13 +13596,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="Q45" t="n">
         <v>6.12</v>
@@ -13836,13 +13836,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="O47" t="n">
         <v>9477</v>
       </c>
       <c r="P47" t="n">
-        <v>-1.37</v>
+        <v>-0.23</v>
       </c>
       <c r="Q47" t="n">
         <v>4.42</v>
@@ -13956,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.5097</v>
+        <v>1.5</v>
       </c>
       <c r="O48" t="n">
         <v>543273</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.68</v>
+        <v>-1.32</v>
       </c>
       <c r="Q48" t="n">
         <v>1.525</v>
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="AA49" t="n">
-        <v>-3.98</v>
+        <v>-4.24</v>
       </c>
       <c r="AB49" t="n">
         <v>10</v>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>P/B 15.4x vs 1.0x median — trading at premium | EV/EBITDA -4.0x vs -0.9x median — trading at premium | Analyst target $10.00</t>
+          <t>P/B 15.4x vs 1.0x median — trading at premium | EV/EBITDA -4.2x vs -0.9x median — trading at premium | Analyst target $10.00</t>
         </is>
       </c>
       <c r="AE49" t="n">
@@ -14316,13 +14316,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6001</v>
+        <v>0.6076</v>
       </c>
       <c r="O51" t="n">
         <v>9914</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.13</v>
+        <v>1.11</v>
       </c>
       <c r="Q51" t="n">
         <v>0.6449</v>
@@ -14556,13 +14556,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2088</v>
+        <v>0.208</v>
       </c>
       <c r="O53" t="n">
         <v>10241</v>
       </c>
       <c r="P53" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="Q53" t="n">
         <v>0.2104</v>
@@ -15319,7 +15319,7 @@
         </is>
       </c>
       <c r="AA59" t="n">
-        <v>-7.49</v>
+        <v>-7.48</v>
       </c>
       <c r="AB59" t="n">
         <v>19.8</v>
@@ -15876,13 +15876,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.4602</v>
+        <v>1.5</v>
       </c>
       <c r="O64" t="n">
         <v>7426</v>
       </c>
       <c r="P64" t="n">
-        <v>-2.41</v>
+        <v>0.25</v>
       </c>
       <c r="Q64" t="n">
         <v>2.77</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>P/S 0.6x vs 1.4x median — trading at discount | P/B 0.1x vs 0.5x median — trading at discount | EV/EBITDA -2.4x vs -2.4x median — in-line | Graham # $329.77</t>
+          <t>P/S 0.6x vs 1.4x median — trading at discount | P/B 0.1x vs 0.5x median — trading at discount | EV/EBITDA -2.4x vs -2.9x median — in-line | Graham # $329.77</t>
         </is>
       </c>
       <c r="AE64" t="n">
@@ -16236,13 +16236,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>13.9</v>
+        <v>13.9108</v>
       </c>
       <c r="O67" t="n">
         <v>177376</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="Q67" t="n">
         <v>14.8497</v>
@@ -16596,13 +16596,13 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0.743</v>
+        <v>0.7605</v>
       </c>
       <c r="O70" t="n">
         <v>9470</v>
       </c>
       <c r="P70" t="n">
-        <v>-0.85</v>
+        <v>1.48</v>
       </c>
       <c r="Q70" t="n">
         <v>0.8671</v>
@@ -16956,13 +16956,13 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="O73" t="n">
         <v>40733</v>
       </c>
       <c r="P73" t="n">
-        <v>-1.54</v>
+        <v>1.54</v>
       </c>
       <c r="Q73" t="n">
         <v>2.0397</v>
@@ -16999,7 +16999,7 @@
         </is>
       </c>
       <c r="AA73" t="n">
-        <v>-0.57</v>
+        <v>-0.55</v>
       </c>
       <c r="AB73" t="n">
         <v>3</v>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>P/B 2.1x vs 0.5x median — trading at premium | EV/EBITDA -0.6x vs -2.4x median — trading at discount | Analyst target $3.00</t>
+          <t>P/B 2.1x vs 0.5x median — trading at premium | EV/EBITDA -0.6x vs -2.9x median — trading at discount | Analyst target $3.00</t>
         </is>
       </c>
       <c r="AE73" t="n">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 1.4x median — trading at discount | P/B 0.5x vs 0.5x median — in-line | EV/EBITDA 9.1x vs -2.4x median — trading at discount | Analyst target $12.00</t>
+          <t>P/S 0.4x vs 1.4x median — trading at discount | P/B 0.5x vs 0.5x median — in-line | EV/EBITDA 9.1x vs -2.9x median — trading at discount | Analyst target $12.00</t>
         </is>
       </c>
       <c r="AE74" t="n">

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         <v>38.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7605</v>
+        <v>0.75</v>
       </c>
       <c r="Q3" t="n">
         <v>9470</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>0.08</v>
       </c>
       <c r="S3" t="n">
         <v>0.777</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>73.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>5280</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.15</v>
+        <v>-1.78</v>
       </c>
       <c r="S4" t="n">
         <v>7.86</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1048,13 +1048,13 @@
         <v>64.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="Q6" t="n">
         <v>60653</v>
       </c>
       <c r="R6" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S6" t="n">
         <v>3.33</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1146,13 +1146,13 @@
         <v>65.8</v>
       </c>
       <c r="P7" t="n">
-        <v>13.7</v>
+        <v>13.52</v>
       </c>
       <c r="Q7" t="n">
         <v>65774</v>
       </c>
       <c r="R7" t="n">
-        <v>0.37</v>
+        <v>-0.95</v>
       </c>
       <c r="S7" t="n">
         <v>12.44</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1244,13 +1244,13 @@
         <v>66.59999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Q8" t="n">
         <v>5047</v>
       </c>
       <c r="R8" t="n">
-        <v>3.18</v>
+        <v>-1.77</v>
       </c>
       <c r="S8" t="n">
         <v>1.32</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2322,13 +2322,13 @@
         <v>30.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0.171</v>
+        <v>0.1666</v>
       </c>
       <c r="Q19" t="n">
         <v>74807</v>
       </c>
       <c r="R19" t="n">
-        <v>2.52</v>
+        <v>-0.12</v>
       </c>
       <c r="S19" t="n">
         <v>0.2037</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2420,13 +2420,13 @@
         <v>26.3</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3969</v>
+        <v>0.393</v>
       </c>
       <c r="Q20" t="n">
         <v>10218</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.8</v>
+        <v>-1.77</v>
       </c>
       <c r="S20" t="n">
         <v>0.4813</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2714,13 +2714,13 @@
         <v>61.8</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9899</v>
+        <v>1.9798</v>
       </c>
       <c r="Q23" t="n">
         <v>495485</v>
       </c>
       <c r="R23" t="n">
-        <v>0.75</v>
+        <v>0.24</v>
       </c>
       <c r="S23" t="n">
         <v>1.6781</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -2812,13 +2812,13 @@
         <v>71.90000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.3304</v>
       </c>
       <c r="Q24" t="n">
         <v>20075</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.32</v>
+        <v>-1.88</v>
       </c>
       <c r="S24" t="n">
         <v>2.43</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3008,13 +3008,13 @@
         <v>81.90000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="Q26" t="n">
         <v>40316</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.51</v>
+        <v>-1.86</v>
       </c>
       <c r="S26" t="n">
         <v>4.11</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3106,13 +3106,13 @@
         <v>63.2</v>
       </c>
       <c r="P27" t="n">
-        <v>1.68</v>
+        <v>1.6893</v>
       </c>
       <c r="Q27" t="n">
         <v>17989</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.3</v>
+        <v>0.26</v>
       </c>
       <c r="S27" t="n">
         <v>1.69</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3204,13 +3204,13 @@
         <v>73.2</v>
       </c>
       <c r="P28" t="n">
-        <v>4.48</v>
+        <v>4.26</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>34.53</v>
+        <v>27.92</v>
       </c>
       <c r="S28" t="n">
         <v>17</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3498,13 +3498,13 @@
         <v>58.4</v>
       </c>
       <c r="P31" t="n">
-        <v>5.65</v>
+        <v>5.79</v>
       </c>
       <c r="Q31" t="n">
         <v>70938</v>
       </c>
       <c r="R31" t="n">
-        <v>1.99</v>
+        <v>4.51</v>
       </c>
       <c r="S31" t="n">
         <v>5.64</v>
@@ -3516,7 +3516,7 @@
         <v>1.81</v>
       </c>
       <c r="V31" t="n">
-        <v>5.65</v>
+        <v>5.79</v>
       </c>
       <c r="W31" t="n">
         <v>4.76</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3890,13 +3890,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="P35" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
         <v>40733</v>
       </c>
       <c r="R35" t="n">
-        <v>1.54</v>
+        <v>-1.54</v>
       </c>
       <c r="S35" t="n">
         <v>2.0389</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -3988,13 +3988,13 @@
         <v>85.40000000000001</v>
       </c>
       <c r="P36" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q36" t="n">
         <v>54639</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.19</v>
+        <v>-2.01</v>
       </c>
       <c r="S36" t="n">
         <v>1.62</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4086,13 +4086,13 @@
         <v>62.9</v>
       </c>
       <c r="P37" t="n">
-        <v>16.2273</v>
+        <v>17.39</v>
       </c>
       <c r="Q37" t="n">
         <v>16161</v>
       </c>
       <c r="R37" t="n">
-        <v>-7.59</v>
+        <v>-0.97</v>
       </c>
       <c r="S37" t="n">
         <v>16.5</v>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4184,13 +4184,13 @@
         <v>45.3</v>
       </c>
       <c r="P38" t="n">
-        <v>0.75</v>
+        <v>0.7569</v>
       </c>
       <c r="Q38" t="n">
         <v>9513</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.32</v>
+        <v>-0.41</v>
       </c>
       <c r="S38" t="n">
         <v>0.7659</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         <v>29.7</v>
       </c>
       <c r="P39" t="n">
-        <v>7.3</v>
+        <v>7.51</v>
       </c>
       <c r="Q39" t="n">
         <v>6127</v>
       </c>
       <c r="R39" t="n">
-        <v>-6.65</v>
+        <v>-3.96</v>
       </c>
       <c r="S39" t="n">
         <v>7.68</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         <v>28.1</v>
       </c>
       <c r="P40" t="n">
-        <v>4.28</v>
+        <v>4.74</v>
       </c>
       <c r="Q40" t="n">
         <v>45452</v>
       </c>
       <c r="R40" t="n">
-        <v>16.62</v>
+        <v>29.16</v>
       </c>
       <c r="S40" t="n">
         <v>3.7902</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -4576,13 +4576,13 @@
         <v>51.6</v>
       </c>
       <c r="P42" t="n">
-        <v>6.81</v>
+        <v>6.73</v>
       </c>
       <c r="Q42" t="n">
         <v>13347</v>
       </c>
       <c r="R42" t="n">
-        <v>-5.55</v>
+        <v>-6.66</v>
       </c>
       <c r="S42" t="n">
         <v>8</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>54.5</v>
       </c>
       <c r="P43" t="n">
-        <v>13.9108</v>
+        <v>13.8687</v>
       </c>
       <c r="Q43" t="n">
         <v>177376</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.42</v>
+        <v>-0.73</v>
       </c>
       <c r="S43" t="n">
         <v>12.71</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -4870,13 +4870,13 @@
         <v>55.4</v>
       </c>
       <c r="P45" t="n">
-        <v>1.8797</v>
+        <v>1.86</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.79</v>
+        <v>-0.27</v>
       </c>
       <c r="S45" t="n">
         <v>1.82</v>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4972,13 +4972,13 @@
         <v>99</v>
       </c>
       <c r="P46" t="n">
-        <v>6.26</v>
+        <v>6.3982</v>
       </c>
       <c r="Q46" t="n">
         <v>3033</v>
       </c>
       <c r="R46" t="n">
-        <v>-35.33</v>
+        <v>-33.9</v>
       </c>
       <c r="S46" t="n">
         <v>10.17</v>
@@ -4993,7 +4993,7 @@
         <v>10.41</v>
       </c>
       <c r="W46" t="n">
-        <v>6.26</v>
+        <v>6.19</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5070,13 +5070,13 @@
         <v>27.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2096</v>
+        <v>0.2059</v>
       </c>
       <c r="Q47" t="n">
         <v>11695</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.78</v>
+        <v>-4.5</v>
       </c>
       <c r="S47" t="n">
         <v>0.2029</v>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5168,13 +5168,13 @@
         <v>48.4</v>
       </c>
       <c r="P48" t="n">
-        <v>14.4</v>
+        <v>14.45</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="S48" t="n">
         <v>14.01</v>
@@ -5186,7 +5186,7 @@
         <v>-0.85</v>
       </c>
       <c r="V48" t="n">
-        <v>14.4125</v>
+        <v>14.45</v>
       </c>
       <c r="W48" t="n">
         <v>13.84</v>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5364,13 +5364,13 @@
         <v>67.09999999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="Q50" t="n">
         <v>94874</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.36</v>
+        <v>-0.6</v>
       </c>
       <c r="S50" t="n">
         <v>3.88</v>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>-4.08</v>
       </c>
       <c r="V51" t="n">
-        <v>2.0899</v>
+        <v>2.1189</v>
       </c>
       <c r="W51" t="n">
         <v>1.7</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -5560,13 +5560,13 @@
         <v>66.7</v>
       </c>
       <c r="P52" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Q52" t="n">
         <v>13913</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.23</v>
+        <v>-0.46</v>
       </c>
       <c r="S52" t="n">
         <v>1.0497</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -5658,13 +5658,13 @@
         <v>42.7</v>
       </c>
       <c r="P53" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9585</v>
       </c>
       <c r="Q53" t="n">
         <v>95246</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="S53" t="n">
         <v>0.8951</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -5756,13 +5756,13 @@
         <v>80.59999999999999</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q54" t="n">
         <v>11650</v>
       </c>
       <c r="R54" t="n">
-        <v>0.5</v>
+        <v>-0</v>
       </c>
       <c r="S54" t="n">
         <v>1.9</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -5854,13 +5854,13 @@
         <v>49.4</v>
       </c>
       <c r="P55" t="n">
-        <v>1.7697</v>
+        <v>1.73</v>
       </c>
       <c r="Q55" t="n">
         <v>12359</v>
       </c>
       <c r="R55" t="n">
-        <v>4.1</v>
+        <v>1.76</v>
       </c>
       <c r="S55" t="n">
         <v>1.72</v>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -5952,13 +5952,13 @@
         <v>44.3</v>
       </c>
       <c r="P56" t="n">
-        <v>10.73</v>
+        <v>10.65</v>
       </c>
       <c r="Q56" t="n">
         <v>7872</v>
       </c>
       <c r="R56" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="S56" t="n">
         <v>10.74</v>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -6050,13 +6050,13 @@
         <v>42</v>
       </c>
       <c r="P57" t="n">
-        <v>12.6</v>
+        <v>12.5798</v>
       </c>
       <c r="Q57" t="n">
         <v>8737</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.6</v>
+        <v>-3.75</v>
       </c>
       <c r="S57" t="n">
         <v>15.48</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -6250,13 +6250,13 @@
         <v>69</v>
       </c>
       <c r="P59" t="n">
-        <v>0.4528</v>
+        <v>0.4615</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>-21.22</v>
+        <v>-19.71</v>
       </c>
       <c r="S59" t="n">
         <v>0.26</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -6348,13 +6348,13 @@
         <v>82.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1.7694</v>
+        <v>1.76</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.57</v>
+        <v>2.03</v>
       </c>
       <c r="S60" t="n">
         <v>1.61</v>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -6446,13 +6446,13 @@
         <v>75.90000000000001</v>
       </c>
       <c r="P61" t="n">
-        <v>2.58</v>
+        <v>2.531</v>
       </c>
       <c r="Q61" t="n">
         <v>10529</v>
       </c>
       <c r="R61" t="n">
-        <v>0.78</v>
+        <v>-1.13</v>
       </c>
       <c r="S61" t="n">
         <v>2.46</v>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -6544,13 +6544,13 @@
         <v>62.1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.208</v>
+        <v>0.2045</v>
       </c>
       <c r="Q62" t="n">
         <v>10241</v>
       </c>
       <c r="R62" t="n">
-        <v>1.32</v>
+        <v>-0.39</v>
       </c>
       <c r="S62" t="n">
         <v>0.178</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -6642,13 +6642,13 @@
         <v>97</v>
       </c>
       <c r="P63" t="n">
-        <v>3.55</v>
+        <v>3.5601</v>
       </c>
       <c r="Q63" t="n">
         <v>3188</v>
       </c>
       <c r="R63" t="n">
-        <v>-3.4</v>
+        <v>-3.13</v>
       </c>
       <c r="S63" t="n">
         <v>3.15</v>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -6740,13 +6740,13 @@
         <v>79.90000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>8.803100000000001</v>
+        <v>9.019500000000001</v>
       </c>
       <c r="Q64" t="n">
         <v>7560</v>
       </c>
       <c r="R64" t="n">
-        <v>-7.38</v>
+        <v>-5.11</v>
       </c>
       <c r="S64" t="n">
         <v>6.04</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -6838,13 +6838,13 @@
         <v>37.9</v>
       </c>
       <c r="P65" t="n">
-        <v>1.0799</v>
+        <v>1.06</v>
       </c>
       <c r="Q65" t="n">
         <v>1200</v>
       </c>
       <c r="R65" t="n">
-        <v>-0.01</v>
+        <v>-1.85</v>
       </c>
       <c r="S65" t="n">
         <v>1.105</v>
@@ -6870,7 +6870,7 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -6936,13 +6936,13 @@
         <v>33.6</v>
       </c>
       <c r="P66" t="n">
-        <v>0.434</v>
+        <v>0.43</v>
       </c>
       <c r="Q66" t="n">
         <v>49975</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.16</v>
+        <v>-1.08</v>
       </c>
       <c r="S66" t="n">
         <v>0.48</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -7132,13 +7132,13 @@
         <v>48.7</v>
       </c>
       <c r="P68" t="n">
-        <v>0.6076</v>
+        <v>0.6075</v>
       </c>
       <c r="Q68" t="n">
         <v>9914</v>
       </c>
       <c r="R68" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="S68" t="n">
         <v>0.58</v>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -7622,13 +7622,13 @@
         <v>17</v>
       </c>
       <c r="P73" t="n">
-        <v>1.5</v>
+        <v>1.4901</v>
       </c>
       <c r="Q73" t="n">
         <v>7426</v>
       </c>
       <c r="R73" t="n">
-        <v>0.25</v>
+        <v>-0.41</v>
       </c>
       <c r="S73" t="n">
         <v>1.63</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -7720,13 +7720,13 @@
         <v>61.2</v>
       </c>
       <c r="P74" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q74" t="n">
         <v>543273</v>
       </c>
       <c r="R74" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>1.33</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -7818,13 +7818,13 @@
         <v>67.8</v>
       </c>
       <c r="P75" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="Q75" t="n">
         <v>6435</v>
       </c>
       <c r="R75" t="n">
-        <v>0.15</v>
+        <v>-1.62</v>
       </c>
       <c r="S75" t="n">
         <v>3.4</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -7916,13 +7916,13 @@
         <v>34.9</v>
       </c>
       <c r="P76" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="Q76" t="n">
         <v>157511</v>
       </c>
       <c r="R76" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.21</v>
       </c>
       <c r="S76" t="n">
         <v>0.082</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -8014,13 +8014,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="P77" t="n">
-        <v>5.2797</v>
+        <v>5.3605</v>
       </c>
       <c r="Q77" t="n">
         <v>25729</v>
       </c>
       <c r="R77" t="n">
-        <v>36.93</v>
+        <v>39.02</v>
       </c>
       <c r="S77" t="n">
         <v>3.73</v>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -8116,13 +8116,13 @@
         <v>31.8</v>
       </c>
       <c r="P78" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="Q78" t="n">
         <v>27607</v>
       </c>
       <c r="R78" t="n">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="S78" t="n">
         <v>4.72</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -8436,19 +8436,19 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>6.26</v>
+        <v>6.3982</v>
       </c>
       <c r="O2" t="n">
         <v>3033</v>
       </c>
       <c r="P2" t="n">
-        <v>-35.33</v>
+        <v>-33.9</v>
       </c>
       <c r="Q2" t="n">
         <v>10.41</v>
       </c>
       <c r="R2" t="n">
-        <v>6.26</v>
+        <v>6.19</v>
       </c>
       <c r="S2" t="n">
         <v>10.17</v>
@@ -8556,13 +8556,13 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.5601</v>
       </c>
       <c r="O3" t="n">
         <v>3188</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.4</v>
+        <v>-3.13</v>
       </c>
       <c r="Q3" t="n">
         <v>3.7192</v>
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4528</v>
+        <v>0.4615</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-21.22</v>
+        <v>-19.71</v>
       </c>
       <c r="Q4" t="n">
         <v>0.6899999999999999</v>
@@ -8796,13 +8796,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.48</v>
+        <v>4.26</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>34.53</v>
+        <v>27.92</v>
       </c>
       <c r="Q5" t="n">
         <v>6.88</v>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.171</v>
+        <v>0.1666</v>
       </c>
       <c r="O7" t="n">
         <v>74807</v>
       </c>
       <c r="P7" t="n">
-        <v>2.52</v>
+        <v>-0.12</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2349</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2797</v>
+        <v>5.3605</v>
       </c>
       <c r="O8" t="n">
         <v>25729</v>
       </c>
       <c r="P8" t="n">
-        <v>36.93</v>
+        <v>39.02</v>
       </c>
       <c r="Q8" t="n">
         <v>6.49</v>
@@ -9276,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8.803100000000001</v>
+        <v>9.019500000000001</v>
       </c>
       <c r="O9" t="n">
         <v>7560</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.38</v>
+        <v>-5.11</v>
       </c>
       <c r="Q9" t="n">
         <v>9.890000000000001</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2096</v>
+        <v>0.2059</v>
       </c>
       <c r="O10" t="n">
         <v>11695</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.78</v>
+        <v>-4.5</v>
       </c>
       <c r="Q10" t="n">
         <v>0.24</v>
@@ -9756,16 +9756,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>14.4</v>
+        <v>14.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.4125</v>
+        <v>14.45</v>
       </c>
       <c r="R13" t="n">
         <v>13.84</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="O14" t="n">
         <v>27607</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
@@ -9996,13 +9996,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.28</v>
+        <v>4.74</v>
       </c>
       <c r="O15" t="n">
         <v>45452</v>
       </c>
       <c r="P15" t="n">
-        <v>16.62</v>
+        <v>29.16</v>
       </c>
       <c r="Q15" t="n">
         <v>5.15</v>
@@ -10116,13 +10116,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0799</v>
+        <v>1.06</v>
       </c>
       <c r="O16" t="n">
         <v>1200</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.01</v>
+        <v>-1.85</v>
       </c>
       <c r="Q16" t="n">
         <v>1.55</v>
@@ -10236,16 +10236,16 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.65</v>
+        <v>5.79</v>
       </c>
       <c r="O17" t="n">
         <v>70938</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>4.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.65</v>
+        <v>5.79</v>
       </c>
       <c r="R17" t="n">
         <v>4.76</v>
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3969</v>
+        <v>0.393</v>
       </c>
       <c r="O18" t="n">
         <v>10218</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.8</v>
+        <v>-1.77</v>
       </c>
       <c r="Q18" t="n">
         <v>0.4038</v>
@@ -10476,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9.449999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>5280</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.15</v>
+        <v>-1.78</v>
       </c>
       <c r="Q19" t="n">
         <v>9.84</v>
@@ -10716,13 +10716,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.434</v>
+        <v>0.43</v>
       </c>
       <c r="O21" t="n">
         <v>49975</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.16</v>
+        <v>-1.08</v>
       </c>
       <c r="Q21" t="n">
         <v>0.524</v>
@@ -10956,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7694</v>
+        <v>1.76</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.57</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
         <v>1.77</v>
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.73</v>
+        <v>10.65</v>
       </c>
       <c r="O24" t="n">
         <v>7872</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="Q24" t="n">
         <v>10.74</v>
@@ -11196,13 +11196,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>12.6</v>
+        <v>12.5798</v>
       </c>
       <c r="O25" t="n">
         <v>8737</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.6</v>
+        <v>-3.75</v>
       </c>
       <c r="Q25" t="n">
         <v>26.75</v>
@@ -11316,13 +11316,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.9899</v>
+        <v>1.9798</v>
       </c>
       <c r="O26" t="n">
         <v>495485</v>
       </c>
       <c r="P26" t="n">
-        <v>0.75</v>
+        <v>0.24</v>
       </c>
       <c r="Q26" t="n">
         <v>1.99</v>
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="O27" t="n">
         <v>157511</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.21</v>
       </c>
       <c r="Q27" t="n">
         <v>0.1587</v>
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>-3.65</v>
+        <v>-3.75</v>
       </c>
       <c r="AB30" t="n">
         <v>3.33</v>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>P/S 1.7x vs 3.0x median — trading at discount | P/B -0.6x vs 1.0x median — trading at discount | EV/EBITDA -3.7x vs -0.9x median — trading at premium | Analyst target $3.33</t>
+          <t>P/S 1.7x vs 3.0x median — trading at discount | P/B -0.6x vs 1.0x median — trading at discount | EV/EBITDA -3.8x vs -0.9x median — trading at premium | Analyst target $3.33</t>
         </is>
       </c>
       <c r="AE30" t="n">
@@ -12036,13 +12036,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="O32" t="n">
         <v>60653</v>
       </c>
       <c r="P32" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q32" t="n">
         <v>3.56</v>
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>-15.05</v>
+        <v>-13.39</v>
       </c>
       <c r="AB33" t="n">
         <v/>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>P/S 12.3x vs 9.4x median — trading at premium | P/B 1.5x vs 0.8x median — trading at premium | EV/EBITDA -15.1x vs -0.8x median — trading at premium</t>
+          <t>P/S 12.3x vs 9.4x median — trading at premium | P/B 1.5x vs 0.8x median — trading at premium | EV/EBITDA -13.4x vs -0.8x median — trading at premium</t>
         </is>
       </c>
       <c r="AE33" t="n">
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="O34" t="n">
         <v>5047</v>
       </c>
       <c r="P34" t="n">
-        <v>3.18</v>
+        <v>-1.77</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
@@ -12319,7 +12319,7 @@
         </is>
       </c>
       <c r="AA34" t="n">
-        <v>-3.63</v>
+        <v>-4.22</v>
       </c>
       <c r="AB34" t="n">
         <v>7</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>P/S 32.4x vs 3.0x median — trading at premium | P/B 7.1x vs 1.0x median — trading at premium | EV/EBITDA -3.6x vs -0.9x median — trading at premium | Analyst target $7.00</t>
+          <t>P/S 32.4x vs 3.0x median — trading at premium | P/B 7.1x vs 1.0x median — trading at premium | EV/EBITDA -4.2x vs -0.9x median — trading at premium | Analyst target $7.00</t>
         </is>
       </c>
       <c r="AE34" t="n">
@@ -12396,13 +12396,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>7.3</v>
+        <v>7.51</v>
       </c>
       <c r="O35" t="n">
         <v>6127</v>
       </c>
       <c r="P35" t="n">
-        <v>-6.65</v>
+        <v>-3.96</v>
       </c>
       <c r="Q35" t="n">
         <v>11</v>
@@ -12516,13 +12516,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>13.7</v>
+        <v>13.52</v>
       </c>
       <c r="O36" t="n">
         <v>65774</v>
       </c>
       <c r="P36" t="n">
-        <v>0.37</v>
+        <v>-0.95</v>
       </c>
       <c r="Q36" t="n">
         <v>13.9</v>
@@ -12636,13 +12636,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="O37" t="n">
         <v>94874</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.36</v>
+        <v>-0.6</v>
       </c>
       <c r="Q37" t="n">
         <v>4.14</v>
@@ -12679,7 +12679,7 @@
         </is>
       </c>
       <c r="AA37" t="n">
-        <v>-16.36</v>
+        <v>-17.54</v>
       </c>
       <c r="AB37" t="n">
         <v>10.33</v>
@@ -12756,13 +12756,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="O38" t="n">
         <v>40316</v>
       </c>
       <c r="P38" t="n">
-        <v>-2.51</v>
+        <v>-1.86</v>
       </c>
       <c r="Q38" t="n">
         <v>4.589</v>
@@ -12876,13 +12876,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.32</v>
+        <v>2.3304</v>
       </c>
       <c r="O39" t="n">
         <v>20075</v>
       </c>
       <c r="P39" t="n">
-        <v>-2.32</v>
+        <v>-1.88</v>
       </c>
       <c r="Q39" t="n">
         <v>2.43</v>
@@ -13236,13 +13236,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.81</v>
+        <v>6.73</v>
       </c>
       <c r="O42" t="n">
         <v>13347</v>
       </c>
       <c r="P42" t="n">
-        <v>-5.55</v>
+        <v>-6.66</v>
       </c>
       <c r="Q42" t="n">
         <v>16.41</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>51.95</v>
+        <v>54.27</v>
       </c>
       <c r="AB45" t="n">
         <v>7.83</v>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>P/S 8.4x vs 0.3x median — trading at premium | P/B 0.9x vs 0.9x median — in-line | EV/EBITDA 52.0x vs 9.3x median — trading at premium | Analyst target $7.83</t>
+          <t>P/S 8.4x vs 0.3x median — trading at premium | P/B 0.9x vs 0.9x median — in-line | EV/EBITDA 54.3x vs 9.4x median — trading at premium | Analyst target $7.83</t>
         </is>
       </c>
       <c r="AE45" t="n">
@@ -13759,7 +13759,7 @@
         </is>
       </c>
       <c r="AA46" t="n">
-        <v>6.93</v>
+        <v>6.56</v>
       </c>
       <c r="AB46" t="n">
         <v>22</v>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>P/S 0.3x vs 0.3x median — in-line | P/B 0.6x vs 0.9x median — trading at discount | EV/EBITDA 6.9x vs 9.3x median — trading at discount | Analyst target $22.00 | Graham # $27.45</t>
+          <t>P/S 0.3x vs 0.3x median — in-line | P/B 0.6x vs 0.9x median — trading at discount | EV/EBITDA 6.6x vs 9.4x median — trading at discount | Analyst target $22.00 | Graham # $27.45</t>
         </is>
       </c>
       <c r="AE46" t="n">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="AA47" t="n">
-        <v>8.449999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="AB47" t="n">
         <v>6.75</v>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>P/S 1.5x vs 2.7x median — trading at discount | P/B 1.6x vs 1.5x median — in-line | EV/EBITDA 8.4x vs -0.6x median — trading at discount | Analyst target $6.75 | Graham # $1.36</t>
+          <t>P/S 1.5x vs 2.7x median — trading at discount | P/B 1.6x vs 1.5x median — in-line | EV/EBITDA 8.7x vs -0.6x median — trading at discount | Analyst target $6.75 | Graham # $1.36</t>
         </is>
       </c>
       <c r="AE47" t="n">
@@ -13956,13 +13956,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O48" t="n">
         <v>543273</v>
       </c>
       <c r="P48" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>1.525</v>
@@ -14085,7 +14085,7 @@
         <v>-0.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.0899</v>
+        <v>2.1189</v>
       </c>
       <c r="R49" t="n">
         <v>1.7</v>
@@ -14196,13 +14196,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="O50" t="n">
         <v>13913</v>
       </c>
       <c r="P50" t="n">
-        <v>-3.23</v>
+        <v>-0.46</v>
       </c>
       <c r="Q50" t="n">
         <v>1.12</v>
@@ -14316,13 +14316,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6076</v>
+        <v>0.6075</v>
       </c>
       <c r="O51" t="n">
         <v>9914</v>
       </c>
       <c r="P51" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Q51" t="n">
         <v>0.6449</v>
@@ -14436,13 +14436,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O52" t="n">
         <v>54639</v>
       </c>
       <c r="P52" t="n">
-        <v>-0.19</v>
+        <v>-2.01</v>
       </c>
       <c r="Q52" t="n">
         <v>1.8</v>
@@ -14556,13 +14556,13 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.208</v>
+        <v>0.2045</v>
       </c>
       <c r="O53" t="n">
         <v>10241</v>
       </c>
       <c r="P53" t="n">
-        <v>1.32</v>
+        <v>-0.39</v>
       </c>
       <c r="Q53" t="n">
         <v>0.2104</v>
@@ -14719,7 +14719,7 @@
         </is>
       </c>
       <c r="AA54" t="n">
-        <v>9.31</v>
+        <v>9.41</v>
       </c>
       <c r="AB54" t="n">
         <v>17.25</v>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>P/S 0.3x vs 0.3x median — trading at discount | P/B 1.5x vs 0.9x median — trading at premium | EV/EBITDA 9.3x vs 9.3x median — in-line | Analyst target $17.25 | Graham # $9.71</t>
+          <t>P/S 0.3x vs 0.3x median — trading at discount | P/B 1.5x vs 0.9x median — trading at premium | EV/EBITDA 9.4x vs 9.4x median — in-line | Analyst target $17.25 | Graham # $9.71</t>
         </is>
       </c>
       <c r="AE54" t="n">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>P/S 0.2x vs 0.3x median — trading at discount | P/B 1.3x vs 0.9x median — trading at premium | EV/EBITDA -26.0x vs 9.3x median — trading at discount | Analyst target $5.50</t>
+          <t>P/S 0.2x vs 0.3x median — trading at discount | P/B 1.3x vs 0.9x median — trading at premium | EV/EBITDA -26.0x vs 9.4x median — trading at discount | Analyst target $5.50</t>
         </is>
       </c>
       <c r="AE55" t="n">
@@ -14916,13 +14916,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0.75</v>
+        <v>0.7569</v>
       </c>
       <c r="O56" t="n">
         <v>9513</v>
       </c>
       <c r="P56" t="n">
-        <v>-1.32</v>
+        <v>-0.41</v>
       </c>
       <c r="Q56" t="n">
         <v>0.85</v>
@@ -15036,13 +15036,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.58</v>
+        <v>2.531</v>
       </c>
       <c r="O57" t="n">
         <v>10529</v>
       </c>
       <c r="P57" t="n">
-        <v>0.78</v>
+        <v>-1.13</v>
       </c>
       <c r="Q57" t="n">
         <v>2.6</v>
@@ -15516,13 +15516,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="O61" t="n">
         <v>6435</v>
       </c>
       <c r="P61" t="n">
-        <v>0.15</v>
+        <v>-1.62</v>
       </c>
       <c r="Q61" t="n">
         <v>3.49</v>
@@ -15756,13 +15756,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9585</v>
       </c>
       <c r="O63" t="n">
         <v>95246</v>
       </c>
       <c r="P63" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="Q63" t="n">
         <v>0.97</v>
@@ -15876,13 +15876,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.5</v>
+        <v>1.4901</v>
       </c>
       <c r="O64" t="n">
         <v>7426</v>
       </c>
       <c r="P64" t="n">
-        <v>0.25</v>
+        <v>-0.41</v>
       </c>
       <c r="Q64" t="n">
         <v>2.77</v>
@@ -16116,13 +16116,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O66" t="n">
         <v>11650</v>
       </c>
       <c r="P66" t="n">
-        <v>0.5</v>
+        <v>-0</v>
       </c>
       <c r="Q66" t="n">
         <v>2</v>
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="AA66" t="n">
-        <v>-5.34</v>
+        <v>-5.79</v>
       </c>
       <c r="AB66" t="n">
         <v>7.91</v>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>P/B 13.3x vs 1.0x median — trading at premium | EV/EBITDA -5.3x vs -0.9x median — trading at premium | Analyst target $7.91</t>
+          <t>P/B 13.3x vs 1.0x median — trading at premium | EV/EBITDA -5.8x vs -0.9x median — trading at premium | Analyst target $7.91</t>
         </is>
       </c>
       <c r="AE66" t="n">
@@ -16236,13 +16236,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>13.9108</v>
+        <v>13.8687</v>
       </c>
       <c r="O67" t="n">
         <v>177376</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.42</v>
+        <v>-0.73</v>
       </c>
       <c r="Q67" t="n">
         <v>14.8497</v>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 0.3x median — in-line | P/B 0.7x vs 0.9x median — trading at discount | EV/EBITDA 10.7x vs 9.3x median — in-line | Analyst target $22.00 | Graham # $9.82</t>
+          <t>P/S 0.4x vs 0.3x median — in-line | P/B 0.7x vs 0.9x median — trading at discount | EV/EBITDA 10.7x vs 9.4x median — in-line | Analyst target $22.00 | Graham # $9.82</t>
         </is>
       </c>
       <c r="AE67" t="n">
@@ -16476,13 +16476,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.7697</v>
+        <v>1.73</v>
       </c>
       <c r="O69" t="n">
         <v>12359</v>
       </c>
       <c r="P69" t="n">
-        <v>4.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q69" t="n">
         <v>1.87</v>
@@ -16596,13 +16596,13 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0.7605</v>
+        <v>0.75</v>
       </c>
       <c r="O70" t="n">
         <v>9470</v>
       </c>
       <c r="P70" t="n">
-        <v>1.48</v>
+        <v>0.08</v>
       </c>
       <c r="Q70" t="n">
         <v>0.8671</v>
@@ -16716,13 +16716,13 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>16.2273</v>
+        <v>17.39</v>
       </c>
       <c r="O71" t="n">
         <v>16161</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.59</v>
+        <v>-0.97</v>
       </c>
       <c r="Q71" t="n">
         <v>17.65</v>
@@ -16956,13 +16956,13 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O73" t="n">
         <v>40733</v>
       </c>
       <c r="P73" t="n">
-        <v>1.54</v>
+        <v>-1.54</v>
       </c>
       <c r="Q73" t="n">
         <v>2.0397</v>
@@ -17196,13 +17196,13 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1.68</v>
+        <v>1.6893</v>
       </c>
       <c r="O75" t="n">
         <v>17989</v>
       </c>
       <c r="P75" t="n">
-        <v>-0.3</v>
+        <v>0.26</v>
       </c>
       <c r="Q75" t="n">
         <v>1.69</v>
@@ -17436,13 +17436,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1.8797</v>
+        <v>1.86</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.79</v>
+        <v>-0.27</v>
       </c>
       <c r="Q77" t="n">
         <v>1.8982</v>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30.4</v>
+        <v>32.4</v>
       </c>
       <c r="D2" t="n">
         <v>17.2</v>
@@ -622,7 +622,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>-4</v>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>45.2</v>
+        <v>30.2</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_overbought -2</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>8.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.26</v>
+        <v>4.57</v>
       </c>
       <c r="O2" t="n">
-        <v>76</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="P2" t="n">
         <v>6.58</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-26.89</v>
+        <v>-17.85</v>
       </c>
       <c r="S2" t="n">
         <v>6.251</v>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-30.54</v>
+        <v>-21.96</v>
       </c>
       <c r="V2" t="n">
         <v>8.619999999999999</v>
@@ -688,40 +688,40 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v/>
+        <v>30.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>OWLT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>5.74</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
@@ -731,94 +731,94 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-8</v>
+        <v>-0.8</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.0pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.6pts)   Items: 8.01, 9.01 (routine)</t>
+          <t>2026-08-21 4 (insider_buy, +1.5pts) | 2026-08-21 4 (insider_buy, +1.5pts)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>5.16</v>
       </c>
       <c r="N3" t="n">
-        <v>10.09</v>
+        <v>1.87</v>
       </c>
       <c r="O3" t="n">
-        <v>30.7</v>
+        <v>42.6</v>
       </c>
       <c r="P3" t="n">
-        <v>4.69</v>
+        <v>5.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>17.25</v>
+        <v>-0.19</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4276</v>
+        <v>5.28</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>10.69</v>
+        <v>2.33</v>
       </c>
       <c r="V3" t="n">
-        <v>5.15</v>
+        <v>5.88</v>
       </c>
       <c r="W3" t="n">
-        <v>3.58</v>
+        <v>5.08</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>new</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTCI</t>
+          <t>ELME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.24</v>
+        <v>4.16</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -829,55 +829,51 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-26 4 (insider_buy, +3.0pts) | 2026-08-18 424B3 (dilution_risk, -0.8pts)</t>
+          <t>2026-08-20 8-K (material_event, +0.8pts)   Items: 8.01 (routine)   Title: &gt;elme-20260820</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="N4" t="n">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="O4" t="n">
-        <v>35.9</v>
+        <v>59.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9807</v>
+        <v>1.6893</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-11.97</v>
+        <v>0.85</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.78</v>
+        <v>0.9</v>
       </c>
       <c r="V4" t="n">
-        <v>2.17</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
@@ -902,7 +898,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VVOS</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -911,10 +907,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -931,12 +927,12 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-12.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-21 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
+          <t>2026-08-21 8-K (material_event, +1.0pts)   Items: 5.03, 9.01 (routine) | 2026-08-19 8-K (material_event, +0.6pts)   Items: 8.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -945,62 +941,62 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.26</v>
+        <v>3.99</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>10.28</v>
       </c>
       <c r="O5" t="n">
-        <v>33.5</v>
+        <v>30.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2866</v>
+        <v>4.69</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>9.81</v>
+        <v>17.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2599</v>
+        <v>4.4276</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.42</v>
+        <v>10.83</v>
       </c>
       <c r="V5" t="n">
-        <v>0.31</v>
+        <v>5.15</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2652</v>
+        <v>3.58</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v/>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>FTCI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1009,13 +1005,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1029,7 +1025,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-9.699999999999999</v>
+        <v>-2.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1038,7 +1034,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-26 8-K (material_event, +2.0pts)   Items: 7.01, 9.01 (routine) | 2026-08-18 S-3 (dilution_risk, -0.8pts)</t>
+          <t>2026-08-26 4 (insider_buy, +3.0pts) | 2026-08-18 424B3 (dilution_risk, -0.8pts)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1047,37 +1043,37 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>2.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="O6" t="n">
-        <v>32.8</v>
+        <v>31.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9579</v>
+        <v>1.9807</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-10.89</v>
+        <v>-7.01</v>
       </c>
       <c r="S6" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.26</v>
+        <v>-0.47</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>2.17</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9407</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
@@ -1088,21 +1084,21 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v/>
+        <v>2.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RDIB</t>
+          <t>VMAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1111,7 +1107,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1120,7 +1116,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1141,41 +1137,41 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>13.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>19.56</v>
+        <v>6.07</v>
       </c>
       <c r="O7" t="n">
-        <v>83.5</v>
+        <v>46.6</v>
       </c>
       <c r="P7" t="n">
-        <v>9.6</v>
+        <v>7.287</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-27.33</v>
+        <v>-16.24</v>
       </c>
       <c r="S7" t="n">
-        <v>12.28</v>
+        <v>7.57</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-7.04</v>
+        <v>-12.99</v>
       </c>
       <c r="V7" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="W7" t="n">
-        <v>8.710000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
@@ -1200,7 +1196,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WVVIP</t>
+          <t>ENGN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1209,16 +1205,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1239,75 +1235,75 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3.66</v>
+        <v>1.94</v>
       </c>
       <c r="N8" t="n">
-        <v>5.52</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>78.7</v>
+        <v>60.2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>17.48</v>
+        <v>-3.88</v>
       </c>
       <c r="S8" t="n">
-        <v>4.3007</v>
+        <v>1.88</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>17.5</v>
+        <v>-2.84</v>
       </c>
       <c r="V8" t="n">
-        <v>6.88</v>
+        <v>1.8797</v>
       </c>
       <c r="W8" t="n">
-        <v>2.65</v>
+        <v>1.754</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>new</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>SBFM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1316,7 +1312,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1337,41 +1333,41 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.27</v>
+        <v>1.27</v>
       </c>
       <c r="N9" t="n">
-        <v>10.96</v>
+        <v>6.16</v>
       </c>
       <c r="O9" t="n">
-        <v>78.5</v>
+        <v>41.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1538</v>
+        <v>1.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>4879</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-43.48</v>
+        <v>-10.16</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2668</v>
+        <v>1.24</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.95</v>
+        <v>-3.12</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1618</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>0.146</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
@@ -1382,105 +1378,105 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v/>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OLOX</t>
+          <t>VVOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v/>
+        <v>-13</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-21 8-K (material_event, +1.0pts)   Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.49</v>
+        <v>0.26</v>
       </c>
       <c r="N10" t="n">
-        <v>6.06</v>
+        <v>3.89</v>
       </c>
       <c r="O10" t="n">
-        <v>17.2</v>
+        <v>33.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>0.2866</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.33</v>
+        <v>10.87</v>
       </c>
       <c r="S10" t="n">
-        <v>1.53</v>
+        <v>0.2599</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>0.54</v>
       </c>
       <c r="V10" t="n">
-        <v>2.77</v>
+        <v>0.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4099</v>
+        <v>0.2652</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1488,31 +1484,31 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBFM</t>
+          <t>ACTU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F11" t="n">
         <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1533,41 +1529,41 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +1, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="N11" t="n">
-        <v>5.55</v>
+        <v>2.91</v>
       </c>
       <c r="O11" t="n">
-        <v>27.5</v>
+        <v>69.8</v>
       </c>
       <c r="P11" t="n">
-        <v>1.15</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5.02</v>
+        <v>-4.68</v>
       </c>
       <c r="S11" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>13.24</v>
+        <v>-2.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.7799</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
@@ -1592,80 +1588,80 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TRUG</t>
+          <t>CRDL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-2.22</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-41.6</v>
+        <v/>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-24 8-K (material_event, +1.6pts)   Items: 7.01, 9.01 (routine) | 2026-08-21 8-K (material_event, -3.5pts)   Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3) | 2026-08-18 8-K (material_event, +0.4pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +4, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.64</v>
+        <v>2.26</v>
       </c>
       <c r="N12" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>37.6</v>
+        <v>85.7</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8298</v>
+        <v>1.9978</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>30.29</v>
+        <v>-11.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0.67</v>
+        <v>2.04</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5.2</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5675</v>
+        <v>1.82</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
@@ -1690,91 +1686,95 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-5.65</v>
+        <v>1.94</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>1.61</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>705.9</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
+        <v>-15.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, -0.4pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+          <t>2026-08-26 8-K (material_event, +2.0pts)   Items: 7.01, 9.01 (routine) | 2026-08-18 S-3 (dilution_risk, -0.8pts)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5.15</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>2.42</v>
       </c>
       <c r="O13" t="n">
-        <v>87.5</v>
+        <v>31.3</v>
       </c>
       <c r="P13" t="n">
-        <v>5.24</v>
+        <v>0.9579</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.02</v>
+        <v>-4.69</v>
       </c>
       <c r="S13" t="n">
-        <v>6.18</v>
+        <v>1.04</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>20.32</v>
+        <v>3.48</v>
       </c>
       <c r="V13" t="n">
-        <v>6.49</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4118</v>
+        <v>0.9407</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1782,86 +1782,86 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>-6.2</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MSS</t>
+          <t>RDIB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-6.6</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v/>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, -3.6pts)   Item 3.01 (delisting, -6) | 2026-08-21 4 (insider_sell, -0.5pts) | 2026-08-18 4 (insider_sell, -0.2pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.64</v>
+        <v>15.06</v>
       </c>
       <c r="N14" t="n">
-        <v>6.62</v>
+        <v>19.7</v>
       </c>
       <c r="O14" t="n">
-        <v>44.9</v>
+        <v>87.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.42</v>
+        <v>9.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-13.15</v>
+        <v>-36.02</v>
       </c>
       <c r="S14" t="n">
-        <v>2.03</v>
+        <v>12.28</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>24.16</v>
+        <v>-18.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7</v>
+        <v>9.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3461</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
@@ -1872,117 +1872,1097 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>WVVIP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>trend_alignment +3, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.3007</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BMEA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>trend_alignment +3, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O16" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BEEM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-19 8-K (material_event, +0.6pts)   Items: 2.02, 9.01 (routine)   Title: &gt;beem20260819_8k.htm</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-22.67</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.3424</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-21.95</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AZIO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O18" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.2052</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>trend_alignment +1, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="O19" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4879</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-45.63</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OLOX</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.4099</v>
+      </c>
+      <c r="X20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AIV</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O21" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TRUG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-24 8-K (material_event, +1.6pts)   Items: 7.01, 9.01 (routine) | 2026-08-21 8-K (material_event, -3.5pts)   Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3) | 2026-08-18 8-K (material_event, +0.4pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>trend_alignment +0</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="X22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>falling</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Late Entry — Priced In</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-18 8-K (material_event, -0.4pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>trend_alignment +1, rsi_overbought -2</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O23" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="X23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>falling</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>-5.65</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MSS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-25 8-K (material_event, -3.6pts)   Item 3.01 (delisting, -6) | 2026-08-21 4 (insider_sell, -0.5pts) | 2026-08-18 4 (insider_sell, -0.2pts)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="O24" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-11.24</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.3461</v>
+      </c>
+      <c r="X24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>-6.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>SHMD</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C25" t="n">
+        <v>-29.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="O25" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="X25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>falling</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
         <v>-26.82</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts)</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O15" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="X15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="Z15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>rising</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>-32</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2226,34 +3206,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.2</v>
+        <v>15.06</v>
       </c>
       <c r="C2" t="n">
-        <v>19.56</v>
+        <v>19.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3325480</v>
+        <v>5521843</v>
       </c>
       <c r="E2" t="n">
-        <v>83.5</v>
+        <v>87.2</v>
       </c>
       <c r="F2" t="n">
-        <v>9.33</v>
+        <v>9.51</v>
       </c>
       <c r="G2" t="n">
-        <v>9.08</v>
+        <v>9.16</v>
       </c>
       <c r="H2" t="n">
-        <v>10.1</v>
+        <v>10.12</v>
       </c>
       <c r="I2" t="n">
-        <v>8.869999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="J2" t="n">
-        <v>10.27</v>
+        <v>10.28</v>
       </c>
       <c r="K2" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -2268,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-27.33</v>
+        <v>-36.02</v>
       </c>
       <c r="Q2" t="n">
         <v>9.6</v>
@@ -2283,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-7.04</v>
+        <v>-18.16</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -2297,7 +3277,7 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>-12.95</v>
+        <v>-14.65</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -2319,23 +3299,23 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>7.76</v>
+        <v>8.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.64</v>
+        <v>21.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>82.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>8.59</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>17.81</v>
+        <v>21.58</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $7.76–$18.64 (ann. vol 82%) | ATR range: $8.59–$17.81</t>
+          <t>1-SD 3mo range: $8.40–$21.72 (ann. vol 88%) | ATR range: $8.54–$21.58</t>
         </is>
       </c>
     </row>
@@ -2346,19 +3326,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="C3" t="n">
-        <v>10.96</v>
+        <v>11.78</v>
       </c>
       <c r="D3" t="n">
-        <v>13926960</v>
+        <v>16069053</v>
       </c>
       <c r="E3" t="n">
-        <v>78.5</v>
+        <v>79.8</v>
       </c>
       <c r="F3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="G3" t="n">
         <v>0.17</v>
@@ -2388,7 +3368,7 @@
         <v>4879</v>
       </c>
       <c r="P3" t="n">
-        <v>-43.48</v>
+        <v>-45.63</v>
       </c>
       <c r="Q3" t="n">
         <v>0.1618</v>
@@ -2403,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.95</v>
+        <v>-5.69</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -2417,11 +3397,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>-12.36</v>
+        <v>-12.85</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-12.4x vs -0.4x median — trading at premium</t>
+          <t>-12.9x vs -0.4x median — trading at premium</t>
         </is>
       </c>
       <c r="AA3" t="n">
@@ -2435,27 +3415,27 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>P/S 0.5x vs 0.8x median — trading at discount | P/B -12.4x vs -0.4x median — trading at premium | EV/EBITDA 0.1x vs -1.4x median — trading at discount</t>
+          <t>P/S 0.5x vs 0.8x median — trading at discount | P/B -12.9x vs -0.4x median — trading at premium | EV/EBITDA 0.1x vs -1.4x median — trading at discount</t>
         </is>
       </c>
       <c r="AE3" t="n">
         <v>0.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>158.6</v>
+        <v>160.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.06–$0.49 (ann. vol 159%) | ATR range: $0.02–$0.53</t>
+          <t>1-SD 3mo range: $0.06–$0.51 (ann. vol 160%) | ATR range: $0.03–$0.54</t>
         </is>
       </c>
     </row>
@@ -2466,16 +3446,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="C4" t="n">
-        <v>10.09</v>
+        <v>10.28</v>
       </c>
       <c r="D4" t="n">
-        <v>1922967</v>
+        <v>1956997</v>
       </c>
       <c r="E4" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="F4" t="n">
         <v>6.11</v>
@@ -2508,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>17.25</v>
+        <v>17.4</v>
       </c>
       <c r="Q4" t="n">
         <v>5.15</v>
@@ -2523,25 +3503,25 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>10.69</v>
+        <v>10.83</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3.4x vs 3.4x median — in-line</t>
+          <t>3.4x vs 1.5x median — trading at premium</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>-6.96</v>
+        <v>-6.95</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.0x vs -1.5x median — trading at premium</t>
+          <t>-6.9x vs -1.3x median — trading at premium</t>
         </is>
       </c>
       <c r="AA4" t="n">
@@ -2555,27 +3535,27 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>P/S 3.4x vs 3.4x median — in-line | P/B -7.0x vs -1.5x median — trading at premium | EV/EBITDA 0.0x vs -0.6x median — trading at discount</t>
+          <t>P/S 3.4x vs 1.5x median — trading at premium | P/B -6.9x vs -1.3x median — trading at premium | EV/EBITDA 0.0x vs -1.2x median — trading at discount</t>
         </is>
       </c>
       <c r="AE4" t="n">
         <v>-0.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.08</v>
+        <v>8.06</v>
       </c>
       <c r="AG4" t="n">
         <v>204.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>-4.42</v>
+        <v>-4.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.08–$8.08 (ann. vol 204%) | ATR range: $-4.42–$12.42</t>
+          <t>1-SD 3mo range: $-0.08–$8.06 (ann. vol 204%) | ATR range: $-4.43–$12.41</t>
         </is>
       </c>
     </row>
@@ -2586,16 +3566,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="C5" t="n">
-        <v>6.62</v>
+        <v>6.72</v>
       </c>
       <c r="D5" t="n">
-        <v>9157798</v>
+        <v>8976158</v>
       </c>
       <c r="E5" t="n">
-        <v>44.9</v>
+        <v>43.6</v>
       </c>
       <c r="F5" t="n">
         <v>1.65</v>
@@ -2628,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-13.15</v>
+        <v>-11.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.7</v>
@@ -2643,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>24.16</v>
+        <v>26.88</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
@@ -2679,23 +3659,23 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>121.8</v>
+        <v>121.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.84</v>
+        <v>-0.89</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.64–$2.64 (ann. vol 122%) | ATR range: $-0.84–$4.12</t>
+          <t>1-SD 3mo range: $0.63–$2.56 (ann. vol 122%) | ATR range: $-0.89–$4.08</t>
         </is>
       </c>
     </row>
@@ -2706,19 +3686,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="C6" t="n">
-        <v>6.06</v>
+        <v>6.29</v>
       </c>
       <c r="D6" t="n">
-        <v>2397485</v>
+        <v>2567883</v>
       </c>
       <c r="E6" t="n">
-        <v>17.2</v>
+        <v>19.3</v>
       </c>
       <c r="F6" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
         <v>4.26</v>
@@ -2748,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.33</v>
+        <v>-4.46</v>
       </c>
       <c r="Q6" t="n">
         <v>2.77</v>
@@ -2763,17 +3743,17 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>-2.55</v>
       </c>
       <c r="V6" t="b">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.6x vs 0.8x median — trading at discount</t>
+          <t>0.6x vs 0.8x median — in-line</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -2795,27 +3775,27 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>P/S 0.6x vs 0.8x median — trading at discount | P/B 0.1x vs -0.4x median — trading at discount | EV/EBITDA -2.4x vs -1.4x median — trading at premium | Graham # $329.77</t>
+          <t>P/S 0.6x vs 0.8x median — in-line | P/B 0.1x vs -0.4x median — trading at discount | EV/EBITDA -2.4x vs -1.4x median — trading at premium | Graham # $329.77</t>
         </is>
       </c>
       <c r="AE6" t="n">
         <v>-0.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="AG6" t="n">
-        <v>202.4</v>
+        <v>202.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>-2.45</v>
+        <v>-2.37</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.43</v>
+        <v>5.51</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.02–$3.00 (ann. vol 202%) | ATR range: $-2.45–$5.43</t>
+          <t>1-SD 3mo range: $-0.02–$3.16 (ann. vol 202%) | ATR range: $-2.37–$5.51</t>
         </is>
       </c>
     </row>
@@ -2826,28 +3806,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="C7" t="n">
-        <v>5.55</v>
+        <v>6.16</v>
       </c>
       <c r="D7" t="n">
-        <v>1352253</v>
+        <v>1637335</v>
       </c>
       <c r="E7" t="n">
-        <v>27.5</v>
+        <v>41.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
         <v>7.14</v>
       </c>
       <c r="I7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="J7" t="n">
         <v>8.550000000000001</v>
@@ -2868,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5.02</v>
+        <v>-10.16</v>
       </c>
       <c r="Q7" t="n">
         <v>1.19</v>
@@ -2883,13 +3863,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>13.24</v>
+        <v>-3.12</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2897,11 +3877,11 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0x vs 0.0x median — in-line</t>
+          <t>0.0x vs 3.5x median — trading at discount</t>
         </is>
       </c>
       <c r="AA7" t="n">
@@ -2915,109 +3895,109 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 0.3x median — trading at discount | P/B 0.0x vs 0.0x median — in-line | EV/EBITDA 1.8x vs 0.0x median — trading at premium | Analyst target $56.00</t>
+          <t>P/S 0.1x vs 0.3x median — trading at discount | P/B 0.0x vs 3.5x median — trading at discount | EV/EBITDA 1.8x vs -0.8x median — trading at discount | Analyst target $56.00</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>126.7</v>
+        <v>127.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.40–$1.79 (ann. vol 127%) | ATR range: $0.25–$1.94</t>
+          <t>1-SD 3mo range: $0.46–$2.08 (ann. vol 127%) | ATR range: $0.38–$2.16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WVVIP</t>
+          <t>VMAR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.66</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>5.52</v>
+        <v>6.07</v>
       </c>
       <c r="D8" t="n">
-        <v>2126835</v>
+        <v>4192977</v>
       </c>
       <c r="E8" t="n">
-        <v>78.7</v>
+        <v>46.6</v>
       </c>
       <c r="F8" t="n">
-        <v>2.83</v>
+        <v>7.79</v>
       </c>
       <c r="G8" t="n">
-        <v>2.75</v>
+        <v>26.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.84</v>
+        <v>1095.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.72</v>
+        <v>11.94</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>744.9</v>
       </c>
       <c r="K8" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>7.287</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>17.48</v>
+        <v>-16.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.88</v>
+        <v>7.6</v>
       </c>
       <c r="R8" t="n">
-        <v>2.65</v>
+        <v>6.55</v>
       </c>
       <c r="S8" t="n">
-        <v>4.3007</v>
+        <v>7.57</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>17.5</v>
+        <v>-12.99</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v/>
+        <v>0.09</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>N/A — sector too small</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>0.84</v>
+        <v>0.26</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -3025,315 +4005,315 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>4789.15</v>
+        <v>-1.67</v>
       </c>
       <c r="AB8" t="n">
         <v/>
       </c>
       <c r="AC8" t="n">
-        <v>3.64</v>
+        <v/>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Graham # $3.64</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>2.9</v>
+        <v>0.52</v>
       </c>
       <c r="AF8" t="n">
-        <v>4.42</v>
+        <v>16.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>41.8</v>
+        <v>188.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>-5.28</v>
+        <v>-0.02</v>
       </c>
       <c r="AI8" t="n">
-        <v>12.6</v>
+        <v>17.42</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.90–$4.42 (ann. vol 42%) | ATR range: $-5.28–$12.60</t>
+          <t>1-SD 3mo range: $0.52–$16.88 (ann. vol 188%) | ATR range: $-0.02–$17.42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XPON</t>
+          <t>WVVIP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>3.72</v>
       </c>
       <c r="C9" t="n">
-        <v>4.26</v>
+        <v>5.9</v>
       </c>
       <c r="D9" t="n">
-        <v>62661739</v>
+        <v>2220297</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>4.57</v>
+        <v>2.83</v>
       </c>
       <c r="G9" t="n">
-        <v>4.69</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="n">
-        <v>8.18</v>
+        <v>2.84</v>
       </c>
       <c r="I9" t="n">
-        <v>4.41</v>
+        <v>2.72</v>
       </c>
       <c r="J9" t="n">
-        <v>8.130000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.58</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-26.89</v>
+        <v>15.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.619999999999999</v>
+        <v>6.88</v>
       </c>
       <c r="R9" t="n">
-        <v>3.41</v>
+        <v>2.65</v>
       </c>
       <c r="S9" t="n">
-        <v>6.251</v>
+        <v>4.3007</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-30.54</v>
+        <v>15.6</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v/>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1.0x vs 0.8x median — trading at premium</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>13.43</v>
+        <v>0.85</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.4x vs -0.4x median — trading at discount</t>
+          <t>N/A — sector too small</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>-0.38</v>
+        <v>4789.15</v>
       </c>
       <c r="AB9" t="n">
         <v/>
       </c>
       <c r="AC9" t="n">
-        <v/>
+        <v>3.64</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>P/S 1.0x vs 0.8x median — trading at premium | P/B 13.4x vs -0.4x median — trading at discount | EV/EBITDA -0.4x vs -1.4x median — trading at discount</t>
+          <t>Graham # $3.64</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>3.29</v>
+        <v>2.94</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.71</v>
+        <v>4.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>126.8</v>
+        <v>42.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1.13</v>
+        <v>-5.37</v>
       </c>
       <c r="AI9" t="n">
-        <v>19.13</v>
+        <v>12.81</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.29–$14.71 (ann. vol 127%) | ATR range: $-1.13–$19.13</t>
+          <t>1-SD 3mo range: $2.94–$4.50 (ann. vol 42%) | ATR range: $-5.37–$12.81</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VVOS</t>
+          <t>XPON</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.26</v>
+        <v>8.07</v>
       </c>
       <c r="C10" t="n">
-        <v>3.85</v>
+        <v>4.57</v>
       </c>
       <c r="D10" t="n">
-        <v>973005</v>
+        <v>57337999</v>
       </c>
       <c r="E10" t="n">
-        <v>33.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.32</v>
+        <v>4.48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.42</v>
+        <v>4.65</v>
       </c>
       <c r="H10" t="n">
-        <v>1.29</v>
+        <v>8.17</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>4.39</v>
       </c>
       <c r="J10" t="n">
-        <v>1.21</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04</v>
+        <v>1.23</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2866</v>
+        <v>6.58</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>9.81</v>
+        <v>-17.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.31</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2652</v>
+        <v>3.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2599</v>
+        <v>6.251</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.42</v>
+        <v>-21.96</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.25</v>
+        <v>0.93</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.3x vs 0.3x median — in-line</t>
+          <t>0.9x vs 0.8x median — in-line</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>0.85</v>
+        <v>11.99</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.9x vs 0.0x median — trading at premium</t>
+          <t>12.0x vs -0.4x median — trading at discount</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>-0.82</v>
+        <v>-0.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.12</v>
+        <v/>
       </c>
       <c r="AC10" t="n">
         <v/>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>P/S 0.3x vs 0.3x median — in-line | P/B 0.9x vs 0.0x median — trading at premium | EV/EBITDA -0.8x vs 0.0x median — trading at discount | Analyst target $2.12</t>
+          <t>P/S 0.9x vs 0.8x median — in-line | P/B 12.0x vs -0.4x median — trading at discount | EV/EBITDA -0.4x vs -1.4x median — trading at discount</t>
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>0.14</v>
+        <v>3.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.38</v>
+        <v>13.02</v>
       </c>
       <c r="AG10" t="n">
-        <v>94.2</v>
+        <v>122.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.01</v>
+        <v>-2.06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.53</v>
+        <v>18.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.14–$0.38 (ann. vol 94%) | ATR range: $-0.01–$0.53</t>
+          <t>1-SD 3mo range: $3.12–$13.02 (ann. vol 123%) | ATR range: $-2.06–$18.20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>VVOS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.98</v>
+        <v>0.26</v>
       </c>
       <c r="C11" t="n">
-        <v>2.69</v>
+        <v>3.89</v>
       </c>
       <c r="D11" t="n">
-        <v>1896339</v>
+        <v>966233</v>
       </c>
       <c r="E11" t="n">
-        <v>28.5</v>
+        <v>33.2</v>
       </c>
       <c r="F11" t="n">
-        <v>4.58</v>
+        <v>0.32</v>
       </c>
       <c r="G11" t="n">
-        <v>4.93</v>
+        <v>0.42</v>
       </c>
       <c r="H11" t="n">
-        <v>5.37</v>
+        <v>1.29</v>
       </c>
       <c r="I11" t="n">
-        <v>4.94</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>6.08</v>
+        <v>1.21</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3342,170 +4322,170 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>0.2866</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>14.52</v>
+        <v>10.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>0.31</v>
       </c>
       <c r="R11" t="n">
-        <v>3.39</v>
+        <v>0.2652</v>
       </c>
       <c r="S11" t="n">
-        <v>3.39</v>
+        <v>0.2599</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>13.85</v>
+        <v>0.54</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>2.91</v>
+        <v>0.25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2.9x vs 0.8x median — trading at premium</t>
+          <t>0.2x vs 0.3x median — in-line</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>-0.83</v>
+        <v>-3.08</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.8x vs -0.4x median — trading at premium</t>
+          <t>-3.1x vs 3.5x median — trading at discount</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>-80.87</v>
+        <v>-0.82</v>
       </c>
       <c r="AB11" t="n">
-        <v/>
+        <v>2.12</v>
       </c>
       <c r="AC11" t="n">
         <v/>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>P/S 2.9x vs 0.8x median — trading at premium | P/B -0.8x vs -0.4x median — trading at premium | EV/EBITDA -80.9x vs -1.4x median — trading at premium</t>
+          <t>P/S 0.2x vs 0.3x median — in-line | P/B -3.1x vs 3.5x median — trading at discount | EV/EBITDA -0.8x vs -0.8x median — in-line | Analyst target $2.12</t>
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>1.09</v>
+        <v>0.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>4.87</v>
+        <v>0.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>127</v>
+        <v>94.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.97</v>
+        <v>0.53</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.09–$4.87 (ann. vol 127%) | ATR range: $-1.01–$6.97</t>
+          <t>1-SD 3mo range: $0.14–$0.38 (ann. vol 94%) | ATR range: $-0.01–$0.53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.15</v>
+        <v>3.07</v>
       </c>
       <c r="C12" t="n">
-        <v>2.42</v>
+        <v>3.16</v>
       </c>
       <c r="D12" t="n">
-        <v>75211369</v>
+        <v>2007197</v>
       </c>
       <c r="E12" t="n">
-        <v>87.5</v>
+        <v>29.1</v>
       </c>
       <c r="F12" t="n">
-        <v>1.51</v>
+        <v>4.59</v>
       </c>
       <c r="G12" t="n">
-        <v>1.76</v>
+        <v>4.93</v>
       </c>
       <c r="H12" t="n">
-        <v>17.63</v>
+        <v>5.37</v>
       </c>
       <c r="I12" t="n">
-        <v>1.38</v>
+        <v>4.95</v>
       </c>
       <c r="J12" t="n">
-        <v>11.22</v>
+        <v>6.08</v>
       </c>
       <c r="K12" t="n">
-        <v>0.73</v>
+        <v>0.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.24</v>
+        <v>3.41</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>11.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.49</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4118</v>
+        <v>3.39</v>
       </c>
       <c r="S12" t="n">
-        <v>6.18</v>
+        <v>3.39</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>20.32</v>
+        <v>10.42</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>28.46</v>
+        <v>3.01</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>28.5x vs 3.4x median — trading at premium</t>
+          <t>3.0x vs 0.8x median — trading at premium</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>-1.49</v>
+        <v>-0.86</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>-1.5x vs -1.5x median — in-line</t>
+          <t>-0.9x vs -0.4x median — trading at premium</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v/>
+        <v>-80.87</v>
       </c>
       <c r="AB12" t="n">
         <v/>
@@ -3515,305 +4495,305 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>P/S 28.5x vs 3.4x median — trading at premium | P/B -1.5x vs -1.5x median — in-line</t>
+          <t>P/S 3.0x vs 0.8x median — trading at premium | P/B -0.9x vs -0.4x median — trading at premium | EV/EBITDA -80.9x vs -1.4x median — trading at premium</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>-0.58</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>10.88</v>
+        <v>5.01</v>
       </c>
       <c r="AG12" t="n">
-        <v>222.5</v>
+        <v>126.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.79</v>
+        <v>-0.92</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.09</v>
+        <v>7.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.58–$10.88 (ann. vol 222%) | ATR range: $-0.79–$11.09</t>
+          <t>1-SD 3mo range: $1.13–$5.01 (ann. vol 127%) | ATR range: $-0.92–$7.06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>ACTU</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.08</v>
+        <v>1.71</v>
       </c>
       <c r="C13" t="n">
-        <v>2.36</v>
+        <v>2.91</v>
       </c>
       <c r="D13" t="n">
-        <v>10364294</v>
+        <v>501188</v>
       </c>
       <c r="E13" t="n">
-        <v>32.8</v>
+        <v>69.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="G13" t="n">
-        <v>5.67</v>
+        <v>1.44</v>
       </c>
       <c r="H13" t="n">
-        <v>45.54</v>
+        <v>3.23</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="J13" t="n">
-        <v>44.52</v>
+        <v>3.47</v>
       </c>
       <c r="K13" t="n">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="b">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9579</v>
+        <v>1.63</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-10.89</v>
+        <v>-4.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.19</v>
+        <v>1.7799</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9407</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.26</v>
+        <v>-2.34</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.38</v>
+        <v/>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.4x vs 0.3x median — trading at premium</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>-0.3</v>
+        <v>41.71</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>-0.3x vs 0.0x median — trading at discount</t>
+          <t>41.7x vs 3.5x median — trading at premium</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>0.02</v>
+        <v/>
       </c>
       <c r="AB13" t="n">
-        <v/>
+        <v>10.01</v>
       </c>
       <c r="AC13" t="n">
         <v/>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 0.3x median — trading at premium | P/B -0.3x vs 0.0x median — trading at discount | EV/EBITDA 0.0x vs 0.0x median — in-line</t>
+          <t>P/B 41.7x vs 3.5x median — trading at premium | Analyst target $10.01</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>-0.01</v>
+        <v>0.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>201.8</v>
+        <v>100</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.01–$2.16 (ann. vol 202%) | ATR range: $0.12–$2.03</t>
+          <t>1-SD 3mo range: $0.85–$2.57 (ann. vol 100%) | ATR range: $0.42–$3.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRUG</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.64</v>
+        <v>4.45</v>
       </c>
       <c r="C14" t="n">
-        <v>2.22</v>
+        <v>2.69</v>
       </c>
       <c r="D14" t="n">
-        <v>4168888</v>
+        <v>65994316</v>
       </c>
       <c r="E14" t="n">
-        <v>37.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.92</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="H14" t="n">
-        <v>7.7</v>
+        <v>17.62</v>
       </c>
       <c r="I14" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="J14" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>5.24</v>
       </c>
-      <c r="K14" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.8298</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30.29</v>
+        <v>14.87</v>
       </c>
       <c r="Q14" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.01</v>
       </c>
-      <c r="R14" t="n">
-        <v>0.5675</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="V14" t="b">
-        <v>1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.06</v>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>1.0x vs 1.5x median — trading at discount</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>0.17</v>
+        <v>-1.33</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>-1.3x vs -1.3x median — in-line</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>0.36</v>
+        <v/>
       </c>
       <c r="AB14" t="n">
-        <v>6</v>
+        <v/>
       </c>
       <c r="AC14" t="n">
         <v/>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Analyst target $6.00</t>
+          <t>P/S 1.0x vs 1.5x median — trading at discount | P/B -1.3x vs -1.3x median — in-line</t>
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>0.17</v>
+        <v>-0.47</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.11</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AG14" t="n">
-        <v>147.1</v>
+        <v>221.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>-1.07</v>
+        <v>-1.49</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.34</v>
+        <v>10.39</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.17–$1.11 (ann. vol 147%) | ATR range: $-1.07–$2.34</t>
+          <t>1-SD 3mo range: $-0.47–$9.37 (ann. vol 221%) | ATR range: $-1.49–$10.39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FTCI</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="D15" t="n">
-        <v>528779</v>
+        <v>9723942</v>
       </c>
       <c r="E15" t="n">
-        <v>35.9</v>
+        <v>31.3</v>
       </c>
       <c r="F15" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="G15" t="n">
-        <v>3.33</v>
+        <v>5.67</v>
       </c>
       <c r="H15" t="n">
-        <v>5.39</v>
+        <v>45.54</v>
       </c>
       <c r="I15" t="n">
-        <v>3.66</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>6.46</v>
+        <v>44.52</v>
       </c>
       <c r="K15" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3822,80 +4802,1280 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9807</v>
+        <v>0.9579</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.97</v>
+        <v>-4.69</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.17</v>
+        <v>1.19</v>
       </c>
       <c r="R15" t="n">
-        <v>1.98</v>
+        <v>0.9407</v>
       </c>
       <c r="S15" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.78</v>
+        <v>3.48</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.4x vs 3.4x median — trading at discount</t>
+          <t>0.4x vs 0.3x median — in-line</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>-1.22</v>
+        <v>-0.28</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>-1.2x vs -1.5x median — in-line</t>
+          <t>-0.3x vs 3.5x median — trading at discount</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>-1.28</v>
+        <v>0.02</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.880000000000001</v>
+        <v/>
       </c>
       <c r="AC15" t="n">
         <v/>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 3.4x median — trading at discount | P/B -1.2x vs -1.5x median — in-line | EV/EBITDA -1.3x vs -0.6x median — trading at premium | Analyst target $8.88</t>
+          <t>P/S 0.4x vs 0.3x median — in-line | P/B -0.3x vs 3.5x median — trading at discount | EV/EBITDA 0.0x vs -0.8x median — trading at discount</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>-0.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="AG15" t="n">
-        <v>111.3</v>
+        <v>201.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.54</v>
+        <v>0.05</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.96</v>
+        <v>1.96</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.00–$3.50 (ann. vol 111%) | ATR range: $0.54–$3.96</t>
+          <t>1-SD 3mo range: $-0.01–$2.02 (ann. vol 201%) | ATR range: $0.05–$1.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TRUG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4245812</v>
+      </c>
+      <c r="E16" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v/>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Analyst target $6.00</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.17–$1.12 (ann. vol 147%) | ATR range: $-1.06–$2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AZIO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D17" t="n">
+        <v>698725</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.2052</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2.0x vs 1.5x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>-1.3x vs -1.3x median — in-line</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AB17" t="n">
+        <v/>
+      </c>
+      <c r="AC17" t="n">
+        <v/>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>P/S 2.0x vs 1.5x median — trading at premium | P/B -1.3x vs -1.3x median — in-line | EV/EBITDA -1.2x vs -1.2x median — in-line</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $-0.13–$2.41 (ann. vol 223%) | ATR range: $0.04–$2.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ELME</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D18" t="n">
+        <v>845288</v>
+      </c>
+      <c r="E18" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.6893</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v/>
+      </c>
+      <c r="AC18" t="n">
+        <v/>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $1.22–$2.13 (ann. vol 54%) | ATR range: $1.46–$1.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CRDL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3103458</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.9978</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-11.41</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v/>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15.1x vs 3.5x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>-5.79</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AC19" t="n">
+        <v/>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>P/B 15.1x vs 3.5x median — trading at premium | EV/EBITDA -5.8x vs -0.8x median — trading at premium | Analyst target $7.89</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>59</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $1.59–$2.92 (ann. vol 59%) | ATR range: $1.08–$3.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FTCI</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D20" t="n">
+        <v>515873</v>
+      </c>
+      <c r="E20" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.9807</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-7.01</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>0.3x vs 1.5x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>-1.2x vs -1.3x median — in-line</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AC20" t="n">
+        <v/>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>P/S 0.3x vs 1.5x median — trading at discount | P/B -1.2x vs -1.3x median — in-line | EV/EBITDA -1.3x vs -1.2x median — in-line | Analyst target $8.88</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.95–$3.31 (ann. vol 111%) | ATR range: $0.42–$3.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AIV</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2068226</v>
+      </c>
+      <c r="E21" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="AB21" t="n">
+        <v/>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Graham # $2.53</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $2.29–$2.78 (ann. vol 20%) | ATR range: $2.15–$2.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ENGN</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1385356</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.8797</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v/>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>0.5x vs 3.5x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AC22" t="n">
+        <v/>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>P/B 0.5x vs 3.5x median — trading at discount | EV/EBITDA 0.8x vs -0.8x median — trading at discount | Analyst target $3.29</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.13–$3.75 (ann. vol 186%) | ATR range: $1.32–$2.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OWLT</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1201962</v>
+      </c>
+      <c r="E23" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1.3x vs 0.3x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>6.4x vs 3.5x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>-19.39</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC23" t="n">
+        <v/>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>P/S 1.3x vs 0.3x median — trading at premium | P/B 6.4x vs 3.5x median — trading at premium | EV/EBITDA -19.4x vs -0.8x median — trading at premium | Analyst target $13.00</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $2.90–$7.42 (ann. vol 88%) | ATR range: $1.13–$9.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BMEA</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2424696</v>
+      </c>
+      <c r="E24" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v/>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>N/A — insufficient data</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10.7x vs 3.5x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>-1.65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v/>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>P/B 10.7x vs 3.5x median — trading at premium | EV/EBITDA -1.7x vs -0.8x median — trading at premium | Analyst target $6.50</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.98–$2.61 (ann. vol 91%) | ATR range: $0.91–$2.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BEEM</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3956754</v>
+      </c>
+      <c r="E25" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-22.67</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.3424</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-21.95</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>1.5x vs 1.5x median — in-line</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>1.9x vs -1.3x median — trading at discount</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v/>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>P/S 1.5x vs 1.5x median — in-line | P/B 1.9x vs -1.3x median — trading at discount | EV/EBITDA -2.3x vs -1.2x median — trading at premium | Analyst target $2.50</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $0.98–$2.50 (ann. vol 87%) | ATR range: $0.73–$2.75</t>
         </is>
       </c>
     </row>
@@ -3910,7 +6090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3922,7 +6102,7 @@
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4963,42 +7143,45 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FTCI</t>
+          <t>ELME</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Items: 8.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>&gt;elme-20260820</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0001193125-26-365940</t>
+          <t>0000104894-26-000110</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>elme-20260820.htm</t>
         </is>
       </c>
     </row>
@@ -5010,21 +7193,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v/>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -5033,12 +7218,181 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
+          <t>0001193125-26-365940</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FTCI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>424B3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v/>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>0001213900-26-091326</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>ea0302559-424b3_ftcsolar.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OWLT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0001416811-26-000004</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>xslF345X06/wk-form4_1787343101.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OWLT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0001213555-26-000004</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>xslF345X06/wk-form4_1787343096.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BEEM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>&gt;beem20260819_8k.htm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0001437749-26-028564</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>beem20260819_8k.htm</t>
         </is>
       </c>
     </row>

--- a/output/stage1_shortlist.xlsx
+++ b/output/stage1_shortlist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:AB52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -650,19 +650,19 @@
         <v>9.17</v>
       </c>
       <c r="N2" t="n">
-        <v>4.94</v>
+        <v>4.98</v>
       </c>
       <c r="O2" t="n">
         <v>76.40000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q2" t="n">
         <v>44632</v>
       </c>
       <c r="R2" t="n">
-        <v>-6.37</v>
+        <v>-3.51</v>
       </c>
       <c r="S2" t="n">
         <v>6.251</v>
@@ -674,7 +674,7 @@
         <v>-31.38</v>
       </c>
       <c r="V2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="W2" t="n">
         <v>3.41</v>
@@ -688,15 +688,15 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>32.4</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="3">
@@ -748,19 +748,19 @@
         <v>0.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="O3" t="n">
         <v>32.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2588</v>
+        <v>0.26</v>
       </c>
       <c r="Q3" t="n">
         <v>21127</v>
       </c>
       <c r="R3" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="S3" t="n">
         <v>0.2599</v>
@@ -786,15 +786,15 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -852,13 +852,13 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="Q4" t="n">
         <v>3310</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.73</v>
+        <v>1.1</v>
       </c>
       <c r="S4" t="n">
         <v>2.7174</v>
@@ -884,15 +884,15 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v/>
+        <v>7.29</v>
       </c>
     </row>
     <row r="5">
@@ -950,13 +950,13 @@
         <v>70.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="S5" t="n">
         <v>2.52</v>
@@ -982,15 +982,15 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="D6" t="n">
         <v>2.7</v>
@@ -1042,19 +1042,19 @@
         <v>15.17</v>
       </c>
       <c r="N6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
         <v>46</v>
       </c>
       <c r="P6" t="n">
-        <v>15.36</v>
+        <v>15.51</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="S6" t="n">
         <v>14.21</v>
@@ -1066,7 +1066,7 @@
         <v>-6.27</v>
       </c>
       <c r="V6" t="n">
-        <v>15.4534</v>
+        <v>15.51</v>
       </c>
       <c r="W6" t="n">
         <v>13.85</v>
@@ -1080,15 +1080,15 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v/>
+        <v>6.77</v>
       </c>
     </row>
     <row r="7">
@@ -1146,13 +1146,13 @@
         <v>42.6</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="Q7" t="n">
         <v>6082</v>
       </c>
       <c r="R7" t="n">
-        <v>2.14</v>
+        <v>-0.78</v>
       </c>
       <c r="S7" t="n">
         <v>5.28</v>
@@ -1178,15 +1178,15 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.74</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="8">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.27</v>
+        <v>6.64</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -1226,7 +1226,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-26 8-K (material_event, +2.0pts)   Items: 2.02, 7.01, 9.01 (routine)   Title: &gt;LANTRONIX, INC. 8-K</t>
+          <t>2026-08-26 4 (insider_other, +0.0pts) | 2026-08-26 8-K (material_event, +2.0pts)   Items: 2.02, 7.01, 9.01 (routine)   Title: &gt;LANTRONIX, INC. 8-K</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1238,19 +1238,19 @@
         <v>5.66</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
         <v>45.7</v>
       </c>
       <c r="P8" t="n">
-        <v>6.4</v>
+        <v>6.48</v>
       </c>
       <c r="Q8" t="n">
         <v>82681</v>
       </c>
       <c r="R8" t="n">
-        <v>12.97</v>
+        <v>14.39</v>
       </c>
       <c r="S8" t="n">
         <v>5.91</v>
@@ -1276,15 +1276,15 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v/>
+        <v>6.27</v>
       </c>
     </row>
     <row r="9">
@@ -1342,13 +1342,13 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>11.3</v>
+        <v>11.33</v>
       </c>
       <c r="Q9" t="n">
         <v>7930</v>
       </c>
       <c r="R9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="S9" t="n">
         <v>11.31</v>
@@ -1374,15 +1374,15 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v/>
+        <v>6.16</v>
       </c>
     </row>
     <row r="10">
@@ -1472,15 +1472,15 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1570,15 +1570,15 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1630,7 +1630,7 @@
         <v>4.97</v>
       </c>
       <c r="N12" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
         <v>54.3</v>
@@ -1668,15 +1668,15 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v/>
+        <v>5.39</v>
       </c>
     </row>
     <row r="13">
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -1728,19 +1728,19 @@
         <v>2.81</v>
       </c>
       <c r="N13" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O13" t="n">
         <v>51.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
         <v>12181</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.35</v>
+        <v>-0.71</v>
       </c>
       <c r="S13" t="n">
         <v>2.8139</v>
@@ -1755,7 +1755,7 @@
         <v>2.96</v>
       </c>
       <c r="W13" t="n">
-        <v>2.77</v>
+        <v>2.7625</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
@@ -1766,15 +1766,15 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1832,13 +1832,13 @@
         <v>69.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.42</v>
+        <v>2.4232</v>
       </c>
       <c r="Q14" t="n">
         <v>30117</v>
       </c>
       <c r="R14" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="S14" t="n">
         <v>2.45</v>
@@ -1850,7 +1850,7 @@
         <v>1.66</v>
       </c>
       <c r="V14" t="n">
-        <v>2.46</v>
+        <v>2.524</v>
       </c>
       <c r="W14" t="n">
         <v>1.9505</v>
@@ -1864,15 +1864,15 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1930,13 +1930,13 @@
         <v>75</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.5599</v>
       </c>
       <c r="Q15" t="n">
         <v>40931</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.59</v>
+        <v>-0.96</v>
       </c>
       <c r="S15" t="n">
         <v>1.48</v>
@@ -1962,15 +1962,15 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2028,31 +2028,31 @@
         <v>50</v>
       </c>
       <c r="P16" t="n">
-        <v>4.75</v>
+        <v/>
       </c>
       <c r="Q16" t="n">
-        <v>2199</v>
+        <v/>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="S16" t="n">
-        <v>4.77</v>
+        <v/>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="U16" t="n">
-        <v>0.42</v>
+        <v/>
       </c>
       <c r="V16" t="n">
-        <v>4.77</v>
+        <v/>
       </c>
       <c r="W16" t="n">
-        <v>4.74</v>
+        <v/>
       </c>
       <c r="X16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -2060,15 +2060,15 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -2126,13 +2126,13 @@
         <v>58</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
         <v>15976</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1.69</v>
@@ -2158,15 +2158,15 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4.16</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="18">
@@ -2256,15 +2256,15 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2322,13 +2322,13 @@
         <v>52.4</v>
       </c>
       <c r="P19" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.13</v>
+        <v>0.4</v>
       </c>
       <c r="S19" t="n">
         <v>3.7</v>
@@ -2354,15 +2354,15 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2424,13 +2424,13 @@
         <v>37.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2821</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
         <v>6377</v>
       </c>
       <c r="R20" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="S20" t="n">
         <v>2.12</v>
@@ -2456,15 +2456,15 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2554,15 +2554,15 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2620,13 +2620,13 @@
         <v>58.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q22" t="n">
         <v>8735</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
         <v>1.26</v>
@@ -2652,15 +2652,15 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -2718,13 +2718,13 @@
         <v>56</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
         <v>335914</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.54</v>
+        <v>1.09</v>
       </c>
       <c r="S23" t="n">
         <v>1.94</v>
@@ -2750,15 +2750,15 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v/>
+        <v>3.96</v>
       </c>
     </row>
     <row r="24">
@@ -2810,19 +2810,19 @@
         <v>4.22</v>
       </c>
       <c r="N24" t="n">
-        <v>10.17</v>
+        <v>10.19</v>
       </c>
       <c r="O24" t="n">
         <v>32.5</v>
       </c>
       <c r="P24" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="Q24" t="n">
         <v>43924</v>
       </c>
       <c r="R24" t="n">
-        <v>-6.18</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="S24" t="n">
         <v>4.4276</v>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CAMP</t>
+          <t>VMAR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2871,71 +2871,71 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>-9.699999999999999</v>
+        <v/>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-21 4 (insider_sell, -0.5pts) | 2026-08-19 4 (insider_sell, -0.3pts)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>1.55</v>
+        <v>6.75</v>
       </c>
       <c r="O25" t="n">
-        <v>48.3</v>
+        <v>49.8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.2</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>11412</v>
+        <v>4938</v>
       </c>
       <c r="R25" t="n">
-        <v>0.36</v>
+        <v>-4.92</v>
       </c>
       <c r="S25" t="n">
-        <v>4.53</v>
+        <v>7.57</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8.24</v>
+        <v>-18.6</v>
       </c>
       <c r="V25" t="n">
-        <v>4.55</v>
+        <v>9.65</v>
       </c>
       <c r="W25" t="n">
-        <v>4.2</v>
+        <v>6.55</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
@@ -2946,21 +2946,21 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB25" t="n">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VMAR</t>
+          <t>ENGN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -3003,37 +3003,37 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>9.300000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="N26" t="n">
-        <v>6.72</v>
+        <v>2.49</v>
       </c>
       <c r="O26" t="n">
-        <v>49.8</v>
+        <v>60.8</v>
       </c>
       <c r="P26" t="n">
-        <v>9.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>4938</v>
+        <v>35514</v>
       </c>
       <c r="R26" t="n">
-        <v>1.08</v>
+        <v>-2.31</v>
       </c>
       <c r="S26" t="n">
-        <v>7.57</v>
+        <v>1.88</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>-18.6</v>
+        <v>-3.34</v>
       </c>
       <c r="V26" t="n">
-        <v>9.65</v>
+        <v>1.95</v>
       </c>
       <c r="W26" t="n">
-        <v>6.55</v>
+        <v>1.754</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENGN</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.66</v>
+        <v>1.15</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -3097,41 +3097,41 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1.95</v>
+        <v>10.36</v>
       </c>
       <c r="N27" t="n">
-        <v>2.49</v>
+        <v>1.72</v>
       </c>
       <c r="O27" t="n">
-        <v>60.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>10.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>35514</v>
+        <v>94516</v>
       </c>
       <c r="R27" t="n">
-        <v>0.26</v>
+        <v>-0.87</v>
       </c>
       <c r="S27" t="n">
-        <v>1.88</v>
+        <v>10.2</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.34</v>
+        <v>-1.73</v>
       </c>
       <c r="V27" t="n">
-        <v>1.95</v>
+        <v>10.46</v>
       </c>
       <c r="W27" t="n">
-        <v>1.754</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
@@ -3156,7 +3156,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -3195,41 +3195,41 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>10.36</v>
+        <v>4.03</v>
       </c>
       <c r="N28" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="O28" t="n">
-        <v>67.09999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="P28" t="n">
-        <v>10.36</v>
+        <v>4.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>94516</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.19</v>
+        <v>0.12</v>
       </c>
       <c r="S28" t="n">
-        <v>10.2</v>
+        <v>4.11</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.73</v>
+        <v>2.11</v>
       </c>
       <c r="V28" t="n">
-        <v>10.46</v>
+        <v>4.14</v>
       </c>
       <c r="W28" t="n">
-        <v>9.949999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
@@ -3240,21 +3240,21 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB28" t="n">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>GORO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -3297,37 +3297,37 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>4.03</v>
+        <v>3.56</v>
       </c>
       <c r="N29" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="O29" t="n">
-        <v>63.3</v>
+        <v>60.3</v>
       </c>
       <c r="P29" t="n">
-        <v>4.03</v>
+        <v>3.61</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>14859</v>
       </c>
       <c r="R29" t="n">
-        <v>0.12</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.11</v>
+        <v>6.74</v>
       </c>
       <c r="V29" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="W29" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB29" t="n">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GORO</t>
+          <t>NERV</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -3391,41 +3391,41 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3.56</v>
+        <v>5.43</v>
       </c>
       <c r="N30" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O30" t="n">
-        <v>60.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>3.5899</v>
+        <v>5.43</v>
       </c>
       <c r="Q30" t="n">
-        <v>14859</v>
+        <v>15915</v>
       </c>
       <c r="R30" t="n">
-        <v>0.84</v>
+        <v>-0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.8</v>
+        <v>4.9696</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>6.74</v>
+        <v>-8.48</v>
       </c>
       <c r="V30" t="n">
-        <v>3.88</v>
+        <v>5.43</v>
       </c>
       <c r="W30" t="n">
-        <v>3</v>
+        <v>4.79</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
@@ -3436,21 +3436,21 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB30" t="n">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NERV</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -3489,41 +3489,41 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>trend_alignment +2, rsi_mild_high +1</t>
+          <t>trend_alignment +1, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5.43</v>
+        <v>5.72</v>
       </c>
       <c r="N31" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O31" t="n">
-        <v>67.40000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="P31" t="n">
-        <v>5.43</v>
+        <v>5.4901</v>
       </c>
       <c r="Q31" t="n">
-        <v>15915</v>
+        <v>66540</v>
       </c>
       <c r="R31" t="n">
-        <v>-0</v>
+        <v>-3.85</v>
       </c>
       <c r="S31" t="n">
-        <v>4.9696</v>
+        <v>5.55</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>-8.48</v>
+        <v>-2.8</v>
       </c>
       <c r="V31" t="n">
-        <v>5.43</v>
+        <v>5.87</v>
       </c>
       <c r="W31" t="n">
-        <v>4.79</v>
+        <v>5.44</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB31" t="n">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>CAMP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3557,71 +3557,71 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="E32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v/>
+        <v>-9.699999999999999</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-26 4 (insider_sell, -1.0pts) | 2026-08-21 4 (insider_sell, -0.5pts) | 2026-08-19 4 (insider_sell, -0.3pts)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_sweet_spot +2</t>
+          <t>trend_alignment +2, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5.72</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="O32" t="n">
-        <v>44.1</v>
+        <v>48.3</v>
       </c>
       <c r="P32" t="n">
-        <v>5.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>66540</v>
+        <v>11412</v>
       </c>
       <c r="R32" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="S32" t="n">
-        <v>5.55</v>
+        <v>4.53</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>-2.8</v>
+        <v>8.24</v>
       </c>
       <c r="V32" t="n">
-        <v>5.87</v>
+        <v>4.55</v>
       </c>
       <c r="W32" t="n">
-        <v>5.44</v>
+        <v>4.2</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
@@ -3632,15 +3632,15 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AB32" t="n">
-        <v/>
+        <v>3.17</v>
       </c>
     </row>
     <row r="33">
@@ -3698,13 +3698,13 @@
         <v>71.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.7092</v>
+        <v>1.74</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-3.91</v>
+        <v>-2.18</v>
       </c>
       <c r="S33" t="n">
         <v>1.67</v>
@@ -3716,7 +3716,7 @@
         <v>-6.12</v>
       </c>
       <c r="V33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W33" t="n">
         <v>1.18</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -3790,19 +3790,19 @@
         <v>2.14</v>
       </c>
       <c r="N34" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="O34" t="n">
         <v>83.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1662</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
         <v>16850</v>
       </c>
       <c r="R34" t="n">
-        <v>1.46</v>
+        <v>3.04</v>
       </c>
       <c r="S34" t="n">
         <v>2.04</v>
@@ -3814,7 +3814,7 @@
         <v>-4.45</v>
       </c>
       <c r="V34" t="n">
-        <v>2.1662</v>
+        <v>2.24</v>
       </c>
       <c r="W34" t="n">
         <v>1.82</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -3894,13 +3894,13 @@
         <v>45.1</v>
       </c>
       <c r="P35" t="n">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="Q35" t="n">
         <v>50357</v>
       </c>
       <c r="R35" t="n">
-        <v>-0</v>
+        <v>1.79</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -3926,21 +3926,21 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3949,16 +3949,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="D36" t="n">
-        <v>1.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E36" t="n">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>-15.1</v>
+        <v>-25.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3978,46 +3978,46 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-26 8-K (material_event, +2.0pts)   Items: 7.01, 9.01 (routine) | 2026-08-18 S-3 (dilution_risk, -0.8pts)</t>
+          <t>2026-08-21 424B3 (dilution_risk, -2.0pts) | 2026-08-21 8-K (material_event, +3.0pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement. | 2026-08-20 424B3 (dilution_risk, -1.6pts) | 2026-08-17 8-K (material_event, +0.2pts)   Items: 2.02, 9.01 (routine)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>trend_alignment +0</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="O36" t="n">
-        <v>31.5</v>
+        <v>42</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9953</v>
+        <v>4.14</v>
       </c>
       <c r="Q36" t="n">
-        <v>10629</v>
+        <v>2325</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.47</v>
+        <v>3.24</v>
       </c>
       <c r="S36" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>24.69</v>
       </c>
       <c r="V36" t="n">
-        <v>1.19</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0.9407</v>
+        <v>3.95</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>1.94</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>RDIB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4051,75 +4051,71 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.51</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-21 424B3 (dilution_risk, -2.0pts) | 2026-08-21 8-K (material_event, +3.0pts)   Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)   Title: Entry into a Material Definitive Agreement. | 2026-08-20 424B3 (dilution_risk, -1.6pts) | 2026-08-17 8-K (material_event, +0.2pts)   Items: 2.02, 9.01 (routine)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +3, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>3.98</v>
+        <v>15.38</v>
       </c>
       <c r="N37" t="n">
-        <v>1.85</v>
+        <v>19.74</v>
       </c>
       <c r="O37" t="n">
-        <v>42</v>
+        <v>87.7</v>
       </c>
       <c r="P37" t="n">
-        <v>4.1</v>
+        <v>14.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>2325</v>
+        <v>3809186</v>
       </c>
       <c r="R37" t="n">
-        <v>2.24</v>
+        <v>-5.3</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>12.28</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>24.69</v>
+        <v>-20.62</v>
       </c>
       <c r="V37" t="n">
-        <v>6.5</v>
+        <v>16.78</v>
       </c>
       <c r="W37" t="n">
-        <v>3.95</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
@@ -4130,21 +4126,21 @@
         </is>
       </c>
       <c r="Z37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
         <v>1</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="AB37" t="n">
-        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RDIB</t>
+          <t>WVVIP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4187,48 +4183,48 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>15.38</v>
+        <v>4.15</v>
       </c>
       <c r="N38" t="n">
-        <v>19.74</v>
+        <v>5.91</v>
       </c>
       <c r="O38" t="n">
-        <v>87.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="P38" t="n">
-        <v>14.16</v>
+        <v>3.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>3493</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>-8.470000000000001</v>
+        <v>-7.71</v>
       </c>
       <c r="S38" t="n">
-        <v>12.28</v>
+        <v>4.3007</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>-20.62</v>
+        <v>3.64</v>
       </c>
       <c r="V38" t="n">
-        <v>16.78</v>
+        <v>6.88</v>
       </c>
       <c r="W38" t="n">
-        <v>8.710000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4242,7 +4238,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WVVIP</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4257,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -4285,48 +4281,48 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>4.15</v>
+        <v>1.71</v>
       </c>
       <c r="N39" t="n">
-        <v>5.9</v>
+        <v>2.28</v>
       </c>
       <c r="O39" t="n">
-        <v>83.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="P39" t="n">
-        <v>4.09</v>
+        <v>1.6908</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.44</v>
+        <v>-0.54</v>
       </c>
       <c r="S39" t="n">
-        <v>4.3007</v>
+        <v>1.74</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3.64</v>
+        <v>2.35</v>
       </c>
       <c r="V39" t="n">
-        <v>6.88</v>
+        <v>1.77</v>
       </c>
       <c r="W39" t="n">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -4340,7 +4336,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BMEA</t>
+          <t>BEEM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4349,71 +4345,71 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E40" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v/>
+        <v>41.3</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>2026-08-19 8-K (material_event, +0.6pts)   Items: 2.02, 9.01 (routine)   Title: &gt;beem20260819_8k.htm</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_overbought -2</t>
+          <t>trend_alignment +3, rsi_mild_high +1</t>
         </is>
       </c>
       <c r="M40" t="n">
         <v>1.71</v>
       </c>
       <c r="N40" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="O40" t="n">
-        <v>79.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="P40" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="R40" t="n">
-        <v>0.59</v>
+        <v>-1.73</v>
       </c>
       <c r="S40" t="n">
-        <v>1.74</v>
+        <v>1.3424</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.35</v>
+        <v>-22.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="W40" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
@@ -4424,7 +4420,7 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -4432,13 +4428,13 @@
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BEEM</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4447,71 +4443,75 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6</v>
+        <v>-3.2</v>
       </c>
       <c r="E41" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Moved</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J41" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-19 8-K (material_event, +0.6pts)   Items: 2.02, 9.01 (routine)   Title: &gt;beem20260819_8k.htm</t>
+          <t>2026-08-24 S-1/A (dilution_risk, -3.2pts)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>trend_alignment +3, rsi_mild_high +1</t>
+          <t>trend_alignment +3, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>1.71</v>
+        <v>4.04</v>
       </c>
       <c r="N41" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O41" t="n">
-        <v>73.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="P41" t="n">
-        <v>1.69</v>
+        <v>4.023</v>
       </c>
       <c r="Q41" t="n">
-        <v>747</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>-2.31</v>
+        <v>-0.42</v>
       </c>
       <c r="S41" t="n">
-        <v>1.3424</v>
+        <v>4.1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>-22.4</v>
+        <v>1.49</v>
       </c>
       <c r="V41" t="n">
-        <v>1.72</v>
+        <v>4.23</v>
       </c>
       <c r="W41" t="n">
-        <v>1.32</v>
+        <v>3.3549</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
@@ -4522,15 +4522,15 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>new</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>0.6</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -4582,19 +4582,19 @@
         <v>1.24</v>
       </c>
       <c r="N42" t="n">
-        <v>6.81</v>
+        <v>6.83</v>
       </c>
       <c r="O42" t="n">
         <v>39</v>
       </c>
       <c r="P42" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Q42" t="n">
         <v>4258</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="S42" t="n">
         <v>1.24</v>
@@ -4606,7 +4606,7 @@
         <v>-0.8</v>
       </c>
       <c r="V42" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W42" t="n">
         <v>1.1</v>
@@ -4620,15 +4620,15 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>falling</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4686,13 +4686,13 @@
         <v>34.8</v>
       </c>
       <c r="P43" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.2</v>
+        <v>-0.66</v>
       </c>
       <c r="S43" t="n">
         <v>1.2052</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -4784,13 +4784,13 @@
         <v>38.5</v>
       </c>
       <c r="P44" t="n">
-        <v>0.9117</v>
+        <v>0.8969</v>
       </c>
       <c r="Q44" t="n">
         <v>125903</v>
       </c>
       <c r="R44" t="n">
-        <v>0.48</v>
+        <v>-1.15</v>
       </c>
       <c r="S44" t="n">
         <v>0.9321</v>
@@ -4816,15 +4816,15 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4876,19 +4876,19 @@
         <v>0.24</v>
       </c>
       <c r="N45" t="n">
-        <v>12.36</v>
+        <v>12.43</v>
       </c>
       <c r="O45" t="n">
         <v>75.09999999999999</v>
       </c>
       <c r="P45" t="n">
-        <v>0.2172</v>
+        <v>0.2001</v>
       </c>
       <c r="Q45" t="n">
         <v>215103246</v>
       </c>
       <c r="R45" t="n">
-        <v>-11.35</v>
+        <v>-18.33</v>
       </c>
       <c r="S45" t="n">
         <v>0.2668</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -4974,19 +4974,19 @@
         <v>1.48</v>
       </c>
       <c r="N46" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="O46" t="n">
         <v>17</v>
       </c>
       <c r="P46" t="n">
-        <v>1.4998</v>
+        <v>1.48</v>
       </c>
       <c r="Q46" t="n">
         <v>12385</v>
       </c>
       <c r="R46" t="n">
-        <v>4.15</v>
+        <v>2.78</v>
       </c>
       <c r="S46" t="n">
         <v>1.53</v>
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5078,13 +5078,13 @@
         <v>28.8</v>
       </c>
       <c r="P47" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="Q47" t="n">
         <v>97956</v>
       </c>
       <c r="R47" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="S47" t="n">
         <v>2.58</v>
@@ -5099,7 +5099,7 @@
         <v>2.62</v>
       </c>
       <c r="W47" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="X47" t="b">
         <v>1</v>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-2.17</v>
+        <v>-2.18</v>
       </c>
       <c r="D48" t="n">
         <v>-1.5</v>
@@ -5170,19 +5170,19 @@
         <v>0.66</v>
       </c>
       <c r="N48" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="O48" t="n">
         <v>38.5</v>
       </c>
       <c r="P48" t="n">
-        <v>0.6335</v>
+        <v>0.62</v>
       </c>
       <c r="Q48" t="n">
         <v>14755</v>
       </c>
       <c r="R48" t="n">
-        <v>-4.54</v>
+        <v>-6.57</v>
       </c>
       <c r="S48" t="n">
         <v>0.67</v>
@@ -5208,21 +5208,21 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>-2.3</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5231,82 +5231,86 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-5.8</v>
+        <v>-4.65</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4</v>
+        <v>-2.8</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="F49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Late Entry — Priced In</t>
+          <t>Early</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>705.9</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>-15.1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-18 8-K (material_event, -0.4pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
+          <t>2026-08-26 424B3 (dilution_risk, -4.0pts) | 2026-08-26 8-K (material_event, +2.0pts)   Items: 7.01, 9.01 (routine) | 2026-08-18 S-3 (dilution_risk, -0.8pts)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>trend_alignment +1, rsi_overbought -2</t>
+          <t>trend_alignment +0</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>5.15</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="O49" t="n">
-        <v>87.5</v>
+        <v>31.5</v>
       </c>
       <c r="P49" t="n">
-        <v>6.3982</v>
+        <v>0.9885</v>
       </c>
       <c r="Q49" t="n">
-        <v>8731</v>
+        <v>10629</v>
       </c>
       <c r="R49" t="n">
-        <v>24.24</v>
+        <v>-1.15</v>
       </c>
       <c r="S49" t="n">
-        <v>6.18</v>
+        <v>1.04</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="V49" t="n">
-        <v>7.2</v>
+        <v>1.19</v>
       </c>
       <c r="W49" t="n">
-        <v>0.4118</v>
+        <v>0.9407</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -5314,13 +5318,13 @@
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>-5.72</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MSS</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5329,96 +5333,96 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-6.2</v>
+        <v>-5.8</v>
       </c>
       <c r="D50" t="n">
-        <v>-4.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E50" t="n">
         <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Late Entry — Priced In</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>705.9</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-25 8-K (material_event, -3.6pts)   Item 3.01 (delisting, -6) | 2026-08-21 4 (insider_sell, -0.5pts) | 2026-08-18 4 (insider_other, +0.0pts)</t>
+          <t>2026-08-18 8-K (material_event, -0.4pts)   Item 3.01 (delisting, -6) | Item 2.04 (price_trigger, +2)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_sweet_spot +2</t>
+          <t>trend_alignment +1, rsi_overbought -2</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1.63</v>
+        <v>5.15</v>
       </c>
       <c r="N50" t="n">
-        <v>6.86</v>
+        <v>3.23</v>
       </c>
       <c r="O50" t="n">
-        <v>44.7</v>
+        <v>87.5</v>
       </c>
       <c r="P50" t="n">
-        <v>1.5996</v>
+        <v>5.6281</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>8731</v>
       </c>
       <c r="R50" t="n">
-        <v>-2.46</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S50" t="n">
-        <v>2.03</v>
+        <v>6.18</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>23.78</v>
+        <v>20</v>
       </c>
       <c r="V50" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="W50" t="n">
-        <v>1.3461</v>
+        <v>0.4118</v>
       </c>
       <c r="X50" t="b">
         <v>1</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>rising</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>-6.6</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>MSS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5427,16 +5431,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-29.8</v>
+        <v>-6.6</v>
       </c>
       <c r="D51" t="n">
-        <v>-14.4</v>
+        <v>-4.3</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -5447,73 +5451,171 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>dilution_risk</t>
-        </is>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts)</t>
+          <t>2026-08-25 8-K (material_event, -3.6pts)   Item 3.01 (delisting, -6) | 2026-08-21 4 (insider_sell, -0.5pts) | 2026-08-18 4 (insider_sell, -0.2pts)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>trend_alignment +0, rsi_weak -1</t>
+          <t>trend_alignment +0, rsi_sweet_spot +2</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>3.17</v>
+        <v>1.63</v>
       </c>
       <c r="N51" t="n">
-        <v>3.9</v>
+        <v>6.87</v>
       </c>
       <c r="O51" t="n">
-        <v>29.8</v>
+        <v>44.7</v>
       </c>
       <c r="P51" t="n">
-        <v>3.17</v>
+        <v>1.56</v>
       </c>
       <c r="Q51" t="n">
-        <v>23169</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.31</v>
+        <v>-4.88</v>
       </c>
       <c r="S51" t="n">
-        <v>3.39</v>
+        <v>2.03</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>6.6</v>
+        <v>23.78</v>
       </c>
       <c r="V51" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="W51" t="n">
-        <v>3.17</v>
+        <v>1.3461</v>
       </c>
       <c r="X51" t="b">
         <v>1</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>falling</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SHMD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-29.8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>dilution_risk</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts) | 2026-08-25 424B3 (dilution_risk, -3.6pts)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>trend_alignment +0, rsi_weak -1</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O52" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3.249</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>23169</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X52" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Z51" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA51" t="inlineStr">
+      <c r="Z52" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>stable</t>
         </is>
       </c>
-      <c r="AB51" t="n">
+      <c r="AB52" t="n">
         <v>-29.8</v>
       </c>
     </row>
@@ -5528,7 +5630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ51"/>
+  <dimension ref="A1:AJ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5764,7 +5866,7 @@
         <v>0.82</v>
       </c>
       <c r="D2" t="n">
-        <v>5371904</v>
+        <v>5371914</v>
       </c>
       <c r="E2" t="n">
         <v>70.09999999999999</v>
@@ -5794,13 +5896,13 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>11.3</v>
+        <v>11.33</v>
       </c>
       <c r="O2" t="n">
         <v>7930</v>
       </c>
       <c r="P2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="Q2" t="n">
         <v>11.37</v>
@@ -5884,7 +5986,7 @@
         <v>0.33</v>
       </c>
       <c r="D3" t="n">
-        <v>2362644</v>
+        <v>2362650</v>
       </c>
       <c r="E3" t="n">
         <v>70.2</v>
@@ -5914,13 +6016,13 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="Q3" t="n">
         <v>2.51</v>
@@ -6004,7 +6106,7 @@
         <v>19.74</v>
       </c>
       <c r="D4" t="n">
-        <v>6545177</v>
+        <v>6598656</v>
       </c>
       <c r="E4" t="n">
         <v>87.7</v>
@@ -6034,13 +6136,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>14.16</v>
+        <v>14.65</v>
       </c>
       <c r="O4" t="n">
-        <v>3493</v>
+        <v>3809186</v>
       </c>
       <c r="P4" t="n">
-        <v>-8.470000000000001</v>
+        <v>-5.3</v>
       </c>
       <c r="Q4" t="n">
         <v>16.78</v>
@@ -6121,10 +6223,10 @@
         <v>0.24</v>
       </c>
       <c r="C5" t="n">
-        <v>12.36</v>
+        <v>12.43</v>
       </c>
       <c r="D5" t="n">
-        <v>14786521</v>
+        <v>14918041</v>
       </c>
       <c r="E5" t="n">
         <v>75.09999999999999</v>
@@ -6154,13 +6256,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2172</v>
+        <v>0.2001</v>
       </c>
       <c r="O5" t="n">
         <v>215103246</v>
       </c>
       <c r="P5" t="n">
-        <v>-11.35</v>
+        <v>-18.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0.2657</v>
@@ -6241,10 +6343,10 @@
         <v>4.22</v>
       </c>
       <c r="C6" t="n">
-        <v>10.17</v>
+        <v>10.19</v>
       </c>
       <c r="D6" t="n">
-        <v>2183719</v>
+        <v>2189856</v>
       </c>
       <c r="E6" t="n">
         <v>32.5</v>
@@ -6274,13 +6376,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>43924</v>
       </c>
       <c r="P6" t="n">
-        <v>-6.18</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>5.15</v>
@@ -6317,7 +6419,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -6327,7 +6429,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>P/S 3.6x vs 1.8x median — trading at premium | P/B -7.3x vs 0.1x median — trading at discount | EV/EBITDA 0.0x vs -1.2x median — trading at discount</t>
+          <t>P/S 3.6x vs 1.8x median — trading at premium | P/B -7.3x vs 0.1x median — trading at discount | EV/EBITDA 0.0x vs -1.3x median — trading at discount</t>
         </is>
       </c>
       <c r="AE6" t="n">
@@ -6364,7 +6466,7 @@
         <v>7.91</v>
       </c>
       <c r="D7" t="n">
-        <v>739365</v>
+        <v>739664</v>
       </c>
       <c r="E7" t="n">
         <v>71.5</v>
@@ -6394,16 +6496,16 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7092</v>
+        <v>1.74</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.91</v>
+        <v>-2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -6481,10 +6583,10 @@
         <v>1.63</v>
       </c>
       <c r="C8" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="D8" t="n">
-        <v>9270793</v>
+        <v>9278297</v>
       </c>
       <c r="E8" t="n">
         <v>44.7</v>
@@ -6514,13 +6616,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5996</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.46</v>
+        <v>-4.88</v>
       </c>
       <c r="Q8" t="n">
         <v>1.7</v>
@@ -6557,7 +6659,7 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>-5.5</v>
+        <v>-5.51</v>
       </c>
       <c r="AB8" t="n">
         <v>162.5</v>
@@ -6601,10 +6703,10 @@
         <v>1.24</v>
       </c>
       <c r="C9" t="n">
-        <v>6.81</v>
+        <v>6.83</v>
       </c>
       <c r="D9" t="n">
-        <v>1677225</v>
+        <v>1679545</v>
       </c>
       <c r="E9" t="n">
         <v>39</v>
@@ -6634,16 +6736,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
         <v>4258</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="R9" t="n">
         <v>1.1</v>
@@ -6677,7 +6779,7 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AB9" t="n">
         <v>56</v>
@@ -6721,10 +6823,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>6.72</v>
+        <v>6.75</v>
       </c>
       <c r="D10" t="n">
-        <v>4701327</v>
+        <v>4709769</v>
       </c>
       <c r="E10" t="n">
         <v>49.8</v>
@@ -6754,13 +6856,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>9.4</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>4938</v>
       </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>-4.92</v>
       </c>
       <c r="Q10" t="n">
         <v>9.65</v>
@@ -6797,7 +6899,7 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>-1.67</v>
+        <v>-1.71</v>
       </c>
       <c r="AB10" t="n">
         <v/>
@@ -6841,10 +6943,10 @@
         <v>1.48</v>
       </c>
       <c r="C11" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="D11" t="n">
-        <v>2464905</v>
+        <v>2468030</v>
       </c>
       <c r="E11" t="n">
         <v>17</v>
@@ -6874,13 +6976,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4998</v>
+        <v>1.48</v>
       </c>
       <c r="O11" t="n">
         <v>12385</v>
       </c>
       <c r="P11" t="n">
-        <v>4.15</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>2.77</v>
@@ -7081,10 +7183,10 @@
         <v>4.15</v>
       </c>
       <c r="C13" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="D13" t="n">
-        <v>2533885</v>
+        <v>2537079</v>
       </c>
       <c r="E13" t="n">
         <v>83.59999999999999</v>
@@ -7114,13 +7216,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.44</v>
+        <v>-7.71</v>
       </c>
       <c r="Q13" t="n">
         <v>6.88</v>
@@ -7157,7 +7259,7 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>4789.15</v>
+        <v>5005.44</v>
       </c>
       <c r="AB13" t="n">
         <v/>
@@ -7180,14 +7282,14 @@
         <v>46.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>-4.95</v>
+        <v>-4.94</v>
       </c>
       <c r="AI13" t="n">
-        <v>13.25</v>
+        <v>13.24</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.19–$5.11 (ann. vol 46%) | ATR range: $-4.95–$13.25</t>
+          <t>1-SD 3mo range: $3.19–$5.11 (ann. vol 46%) | ATR range: $-4.94–$13.24</t>
         </is>
       </c>
     </row>
@@ -7201,10 +7303,10 @@
         <v>9.17</v>
       </c>
       <c r="C14" t="n">
-        <v>4.94</v>
+        <v>4.98</v>
       </c>
       <c r="D14" t="n">
-        <v>67095581</v>
+        <v>67255209</v>
       </c>
       <c r="E14" t="n">
         <v>76.40000000000001</v>
@@ -7234,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>8.529999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O14" t="n">
         <v>44632</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.37</v>
+        <v>-3.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="R14" t="n">
         <v>3.41</v>
@@ -7277,7 +7379,7 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>-0.38</v>
+        <v>-0.71</v>
       </c>
       <c r="AB14" t="n">
         <v/>
@@ -7287,7 +7389,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>P/S 1.1x vs 1.4x median — trading at discount | P/B 13.7x vs 0.6x median — trading at premium | EV/EBITDA -0.4x vs -3.2x median — trading at discount</t>
+          <t>P/S 1.1x vs 1.4x median — trading at discount | P/B 13.7x vs 0.6x median — trading at premium | EV/EBITDA -0.7x vs -3.2x median — trading at discount</t>
         </is>
       </c>
       <c r="AE14" t="n">
@@ -7441,10 +7543,10 @@
         <v>0.25</v>
       </c>
       <c r="C16" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="D16" t="n">
-        <v>954471</v>
+        <v>954874</v>
       </c>
       <c r="E16" t="n">
         <v>32.6</v>
@@ -7474,13 +7576,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2588</v>
+        <v>0.26</v>
       </c>
       <c r="O16" t="n">
         <v>21127</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
         <v>0.31</v>
@@ -7517,7 +7619,7 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>-0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AB16" t="n">
         <v>2.12</v>
@@ -7564,7 +7666,7 @@
         <v>3.9</v>
       </c>
       <c r="D17" t="n">
-        <v>2172849</v>
+        <v>2172899</v>
       </c>
       <c r="E17" t="n">
         <v>29.8</v>
@@ -7594,19 +7696,19 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.17</v>
+        <v>3.249</v>
       </c>
       <c r="O17" t="n">
         <v>23169</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.31</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
         <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="S17" t="n">
         <v>3.39</v>
@@ -7637,7 +7739,7 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>-80.87</v>
+        <v>-76.72</v>
       </c>
       <c r="AB17" t="n">
         <v/>
@@ -7647,7 +7749,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>P/S 3.1x vs 1.4x median — trading at premium | P/B -0.9x vs 0.6x median — trading at discount | EV/EBITDA -80.9x vs -3.2x median — trading at premium</t>
+          <t>P/S 3.1x vs 1.4x median — trading at premium | P/B -0.9x vs 0.6x median — trading at discount | EV/EBITDA -76.7x vs -3.2x median — trading at premium</t>
         </is>
       </c>
       <c r="AE17" t="n">
@@ -7674,360 +7776,360 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DOMO</t>
+          <t>DAIC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.78</v>
+        <v>5.15</v>
       </c>
       <c r="C18" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="D18" t="n">
-        <v>3379584</v>
+        <v>79669692</v>
       </c>
       <c r="E18" t="n">
-        <v>52.4</v>
+        <v>87.5</v>
       </c>
       <c r="F18" t="n">
-        <v>3.76</v>
+        <v>1.51</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65</v>
+        <v>1.76</v>
       </c>
       <c r="H18" t="n">
-        <v>5.88</v>
+        <v>17.75</v>
       </c>
       <c r="I18" t="n">
-        <v>3.44</v>
+        <v>1.38</v>
       </c>
       <c r="J18" t="n">
-        <v>5.23</v>
+        <v>11.22</v>
       </c>
       <c r="K18" t="n">
-        <v>0.19</v>
+        <v>0.73</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.78</v>
+        <v>5.6281</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>8731</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.13</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8658</v>
+        <v>7.2</v>
       </c>
       <c r="R18" t="n">
-        <v>3.7003</v>
+        <v>0.4118</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>6.18</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.25</v>
+        <v>20</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.6x vs 1.8x median — trading at discount</t>
+          <t>1.1x vs 1.8x median — trading at discount</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>-0.92</v>
+        <v>-1.49</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>-0.9x vs 0.1x median — trading at discount</t>
+          <t>-1.5x vs 0.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>-9.32</v>
+        <v/>
       </c>
       <c r="AB18" t="n">
-        <v>3.93</v>
+        <v/>
       </c>
       <c r="AC18" t="n">
         <v/>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>P/S 0.6x vs 1.8x median — trading at discount | P/B -0.9x vs 0.1x median — trading at discount | EV/EBITDA -9.3x vs -1.2x median — trading at premium | Analyst target $3.93</t>
+          <t>P/S 1.1x vs 1.8x median — trading at discount | P/B -1.5x vs 0.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>-0.59</v>
       </c>
       <c r="AF18" t="n">
-        <v>5.73</v>
+        <v>10.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>103.1</v>
+        <v>223</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.78</v>
+        <v>-0.79</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.78</v>
+        <v>11.09</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.83–$5.73 (ann. vol 103%) | ATR range: $2.78–$4.78</t>
+          <t>1-SD 3mo range: $-0.59–$10.89 (ann. vol 223%) | ATR range: $-0.79–$11.09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CRDL</t>
+          <t>DOMO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.14</v>
+        <v>3.78</v>
       </c>
       <c r="C19" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="D19" t="n">
-        <v>3114771</v>
+        <v>3379590</v>
       </c>
       <c r="E19" t="n">
-        <v>83.8</v>
+        <v>52.4</v>
       </c>
       <c r="F19" t="n">
-        <v>1.69</v>
+        <v>3.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.45</v>
+        <v>3.65</v>
       </c>
       <c r="H19" t="n">
-        <v>1.23</v>
+        <v>5.88</v>
       </c>
       <c r="I19" t="n">
-        <v>1.32</v>
+        <v>3.44</v>
       </c>
       <c r="J19" t="n">
-        <v>1.17</v>
+        <v>5.23</v>
       </c>
       <c r="K19" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.1662</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
-        <v>16850</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.46</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1662</v>
+        <v>3.8658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.82</v>
+        <v>3.7003</v>
       </c>
       <c r="S19" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.45</v>
+        <v>-2.25</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v/>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>0.6x vs 1.8x median — trading at discount</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>14.31</v>
+        <v>-0.92</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14.3x vs 1.7x median — trading at premium</t>
+          <t>-0.9x vs 0.1x median — trading at discount</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>-5.79</v>
+        <v>-9.32</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.89</v>
+        <v>3.93</v>
       </c>
       <c r="AC19" t="n">
         <v/>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>P/B 14.3x vs 1.7x median — trading at premium | EV/EBITDA -5.8x vs -1.7x median — trading at premium | Analyst target $7.89</t>
+          <t>P/S 0.6x vs 1.8x median — trading at discount | P/B -0.9x vs 0.1x median — trading at discount | EV/EBITDA -9.3x vs -1.3x median — trading at premium | Analyst target $3.93</t>
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.76</v>
+        <v>5.73</v>
       </c>
       <c r="AG19" t="n">
-        <v>58.3</v>
+        <v>103.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.95</v>
+        <v>2.78</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.33</v>
+        <v>4.78</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.52–$2.76 (ann. vol 58%) | ATR range: $0.95–$3.33</t>
+          <t>1-SD 3mo range: $1.83–$5.73 (ann. vol 103%) | ATR range: $2.78–$4.78</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CRDL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.15</v>
+        <v>2.14</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="D20" t="n">
-        <v>78628449</v>
+        <v>3115357</v>
       </c>
       <c r="E20" t="n">
-        <v>87.5</v>
+        <v>83.8</v>
       </c>
       <c r="F20" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="G20" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="n">
-        <v>17.75</v>
+        <v>1.23</v>
       </c>
       <c r="I20" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="J20" t="n">
-        <v>11.22</v>
+        <v>1.17</v>
       </c>
       <c r="K20" t="n">
-        <v>0.73</v>
+        <v>0.13</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3982</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>8731</v>
+        <v>16850</v>
       </c>
       <c r="P20" t="n">
-        <v>24.24</v>
+        <v>3.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.2</v>
+        <v>2.24</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4118</v>
+        <v>1.82</v>
       </c>
       <c r="S20" t="n">
-        <v>6.18</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>20</v>
+        <v>-4.45</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v/>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>1.1x vs 1.8x median — trading at discount</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>-1.49</v>
+        <v>14.31</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>-1.5x vs 0.1x median — trading at discount</t>
+          <t>14.3x vs 1.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v/>
+        <v>-5.79</v>
       </c>
       <c r="AB20" t="n">
-        <v/>
+        <v>7.89</v>
       </c>
       <c r="AC20" t="n">
         <v/>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>P/S 1.1x vs 1.8x median — trading at discount | P/B -1.5x vs 0.1x median — trading at discount</t>
+          <t>P/B 14.3x vs 1.7x median — trading at premium | EV/EBITDA -5.8x vs -1.7x median — trading at premium | Analyst target $7.89</t>
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>-0.59</v>
+        <v>1.52</v>
       </c>
       <c r="AF20" t="n">
-        <v>10.89</v>
+        <v>2.76</v>
       </c>
       <c r="AG20" t="n">
-        <v>223</v>
+        <v>58.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.79</v>
+        <v>0.95</v>
       </c>
       <c r="AI20" t="n">
-        <v>11.09</v>
+        <v>3.33</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.59–$10.89 (ann. vol 223%) | ATR range: $-0.79–$11.09</t>
+          <t>1-SD 3mo range: $1.52–$2.76 (ann. vol 58%) | ATR range: $0.95–$3.33</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8146,7 @@
         <v>2.73</v>
       </c>
       <c r="D21" t="n">
-        <v>575470</v>
+        <v>575519</v>
       </c>
       <c r="E21" t="n">
         <v>37.2</v>
@@ -8074,13 +8176,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2821</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
         <v>6377</v>
       </c>
       <c r="P21" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
         <v>2.3</v>
@@ -8117,7 +8219,7 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>-1.28</v>
+        <v>-1.42</v>
       </c>
       <c r="AB21" t="n">
         <v>8.880000000000001</v>
@@ -8127,7 +8229,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 1.8x median — trading at discount | P/B -1.2x vs 0.1x median — trading at discount | EV/EBITDA -1.3x vs -1.2x median — in-line | Analyst target $8.88</t>
+          <t>P/S 0.4x vs 1.8x median — trading at discount | P/B -1.2x vs 0.1x median — trading at discount | EV/EBITDA -1.4x vs -1.3x median — in-line | Analyst target $8.88</t>
         </is>
       </c>
       <c r="AE21" t="n">
@@ -8154,480 +8256,480 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AIV</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.53</v>
+        <v>5.66</v>
       </c>
       <c r="C22" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="D22" t="n">
-        <v>2133221</v>
+        <v>4446018</v>
       </c>
       <c r="E22" t="n">
-        <v>28.8</v>
+        <v>45.7</v>
       </c>
       <c r="F22" t="n">
-        <v>2.63</v>
+        <v>5.91</v>
       </c>
       <c r="G22" t="n">
-        <v>2.71</v>
+        <v>5.92</v>
       </c>
       <c r="H22" t="n">
-        <v>2.86</v>
+        <v>5.77</v>
       </c>
       <c r="I22" t="n">
-        <v>2.74</v>
+        <v>5.76</v>
       </c>
       <c r="J22" t="n">
-        <v>2.91</v>
+        <v>5.98</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05</v>
+        <v>0.37</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>6.48</v>
       </c>
       <c r="O22" t="n">
-        <v>97956</v>
+        <v>82681</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2</v>
+        <v>14.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>6.7997</v>
       </c>
       <c r="R22" t="n">
-        <v>2.53</v>
+        <v>5.66</v>
       </c>
       <c r="S22" t="n">
-        <v>2.58</v>
+        <v>5.91</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.18</v>
+        <v>4.32</v>
       </c>
       <c r="V22" t="b">
         <v>1</v>
       </c>
       <c r="W22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2.1x vs 1.8x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>3.0x vs 0.1x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>-134.43</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AC22" t="n">
+        <v/>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>P/S 2.1x vs 1.8x median — trading at premium | P/B 3.0x vs 0.1x median — trading at premium | EV/EBITDA -134.4x vs -1.3x median — trading at premium | Analyst target $10.33</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.82</v>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2.8x vs 2.0x median — trading at premium</t>
-        </is>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>1.0x vs 0.6x median — trading at premium</t>
-        </is>
-      </c>
-      <c r="AA22" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="AB22" t="n">
-        <v/>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>P/S 2.8x vs 2.0x median — trading at premium | P/B 1.0x vs 0.6x median — trading at premium | EV/EBITDA 78.6x vs 18.4x median — trading at premium | Graham # $2.53</t>
-        </is>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AI22" t="n">
-        <v>2.92</v>
+        <v>8.5</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.28–$2.78 (ann. vol 20%) | ATR range: $2.14–$2.92</t>
+          <t>1-SD 3mo range: $3.48–$7.84 (ann. vol 77%) | ATR range: $2.82–$8.50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENGN</t>
+          <t>AIV</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="C23" t="n">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="D23" t="n">
-        <v>1427775</v>
+        <v>2133222</v>
       </c>
       <c r="E23" t="n">
-        <v>60.8</v>
+        <v>28.8</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="G23" t="n">
-        <v>2.07</v>
+        <v>2.71</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>2.74</v>
       </c>
       <c r="J23" t="n">
-        <v>5.85</v>
+        <v>2.91</v>
       </c>
       <c r="K23" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="O23" t="n">
-        <v>35514</v>
+        <v>97956</v>
       </c>
       <c r="P23" t="n">
-        <v>0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.754</v>
+        <v>2.52</v>
       </c>
       <c r="S23" t="n">
-        <v>1.88</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.34</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="b">
         <v>1</v>
       </c>
       <c r="W23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2.8x vs 2.0x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1.0x vs 0.6x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="AB23" t="n">
         <v/>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>N/A — insufficient data</t>
-        </is>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>0.5x vs 1.7x median — trading at discount</t>
-        </is>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.29</v>
-      </c>
       <c r="AC23" t="n">
-        <v/>
+        <v>2.53</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>P/B 0.5x vs 1.7x median — trading at discount | EV/EBITDA 0.8x vs -1.7x median — trading at discount | Analyst target $3.29</t>
+          <t>P/S 2.8x vs 2.0x median — trading at premium | P/B 1.0x vs 0.6x median — trading at premium | EV/EBITDA 78.1x vs 18.4x median — trading at premium | Graham # $2.53</t>
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>0.13</v>
+        <v>2.28</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.77</v>
+        <v>2.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>186.5</v>
+        <v>19.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.57</v>
+        <v>2.92</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.13–$3.77 (ann. vol 186%) | ATR range: $1.33–$2.57</t>
+          <t>1-SD 3mo range: $2.28–$2.78 (ann. vol 20%) | ATR range: $2.14–$2.92</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>ENGN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="C24" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="D24" t="n">
-        <v>9803464</v>
+        <v>1428144</v>
       </c>
       <c r="E24" t="n">
-        <v>31.5</v>
+        <v>60.8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="G24" t="n">
-        <v>5.67</v>
+        <v>2.07</v>
       </c>
       <c r="H24" t="n">
-        <v>45.4</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>44.52</v>
+        <v>5.85</v>
       </c>
       <c r="K24" t="n">
-        <v>0.39</v>
+        <v>0.09</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.9953</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>10629</v>
+        <v>35514</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.47</v>
+        <v>-2.31</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.19</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9407</v>
+        <v>1.754</v>
       </c>
       <c r="S24" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>-3.34</v>
       </c>
       <c r="V24" t="b">
         <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0.36</v>
+        <v/>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.4x vs 1.1x median — trading at discount</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>-0.28</v>
+        <v>0.51</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>-0.3x vs 1.7x median — trading at discount</t>
+          <t>0.5x vs 1.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>0.02</v>
+        <v>0.72</v>
       </c>
       <c r="AB24" t="n">
-        <v/>
+        <v>3.29</v>
       </c>
       <c r="AC24" t="n">
         <v/>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>P/S 0.4x vs 1.1x median — trading at discount | P/B -0.3x vs 1.7x median — trading at discount | EV/EBITDA 0.0x vs -1.7x median — trading at discount</t>
+          <t>P/B 0.5x vs 1.7x median — trading at discount | EV/EBITDA 0.7x vs -1.7x median — trading at discount | Analyst target $3.29</t>
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.03</v>
+        <v>3.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>201.9</v>
+        <v>186.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.06</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.96</v>
+        <v>2.57</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.01–$2.03 (ann. vol 202%) | ATR range: $0.06–$1.96</t>
+          <t>1-SD 3mo range: $0.13–$3.77 (ann. vol 186%) | ATR range: $1.33–$2.57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.66</v>
+        <v>1.01</v>
       </c>
       <c r="C25" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="D25" t="n">
-        <v>4374487</v>
+        <v>9809561</v>
       </c>
       <c r="E25" t="n">
-        <v>45.7</v>
+        <v>31.5</v>
       </c>
       <c r="F25" t="n">
-        <v>5.91</v>
+        <v>1.57</v>
       </c>
       <c r="G25" t="n">
-        <v>5.92</v>
+        <v>5.67</v>
       </c>
       <c r="H25" t="n">
-        <v>5.77</v>
+        <v>45.4</v>
       </c>
       <c r="I25" t="n">
-        <v>5.76</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
-        <v>5.98</v>
+        <v>44.52</v>
       </c>
       <c r="K25" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.4</v>
+        <v>0.9885</v>
       </c>
       <c r="O25" t="n">
-        <v>82681</v>
+        <v>10629</v>
       </c>
       <c r="P25" t="n">
-        <v>12.97</v>
+        <v>-1.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.7997</v>
+        <v>1.19</v>
       </c>
       <c r="R25" t="n">
-        <v>5.66</v>
+        <v>0.9407</v>
       </c>
       <c r="S25" t="n">
-        <v>5.91</v>
+        <v>1.04</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="V25" t="b">
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>2.13</v>
+        <v>0.36</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2.1x vs 1.8x median — trading at premium</t>
+          <t>0.4x vs 1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>3.03</v>
+        <v>-0.28</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3.0x vs 0.1x median — trading at premium</t>
+          <t>-0.3x vs 1.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>-139.33</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.33</v>
+        <v/>
       </c>
       <c r="AC25" t="n">
         <v/>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>P/S 2.1x vs 1.8x median — trading at premium | P/B 3.0x vs 0.1x median — trading at premium | EV/EBITDA -139.3x vs -1.2x median — trading at premium | Analyst target $10.33</t>
+          <t>P/S 0.4x vs 1.1x median — trading at discount | P/B -0.3x vs 1.7x median — trading at discount | EV/EBITDA 0.0x vs -1.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>3.48</v>
+        <v>-0.01</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.84</v>
+        <v>2.03</v>
       </c>
       <c r="AG25" t="n">
-        <v>76.90000000000001</v>
+        <v>201.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.82</v>
+        <v>0.06</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.5</v>
+        <v>1.96</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.48–$7.84 (ann. vol 77%) | ATR range: $2.82–$8.50</t>
+          <t>1-SD 3mo range: $-0.01–$2.03 (ann. vol 202%) | ATR range: $0.06–$1.96</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8746,7 @@
         <v>2.4</v>
       </c>
       <c r="D26" t="n">
-        <v>728710</v>
+        <v>728769</v>
       </c>
       <c r="E26" t="n">
         <v>34.8</v>
@@ -8674,13 +8776,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2</v>
+        <v>-0.66</v>
       </c>
       <c r="Q26" t="n">
         <v>1.23</v>
@@ -8727,7 +8829,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>P/S 2.1x vs 1.8x median — in-line | P/B -1.3x vs 0.1x median — trading at discount | EV/EBITDA -1.2x vs -1.2x median — in-line</t>
+          <t>P/S 2.1x vs 1.8x median — in-line | P/B -1.3x vs 0.1x median — trading at discount | EV/EBITDA -1.2x vs -1.3x median — in-line</t>
         </is>
       </c>
       <c r="AE26" t="n">
@@ -8764,7 +8866,7 @@
         <v>2.38</v>
       </c>
       <c r="D27" t="n">
-        <v>852892</v>
+        <v>852894</v>
       </c>
       <c r="E27" t="n">
         <v>58</v>
@@ -8794,13 +8896,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O27" t="n">
         <v>15976</v>
       </c>
       <c r="P27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>1.69</v>
@@ -8837,7 +8939,7 @@
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>10.5</v>
+        <v>10.48</v>
       </c>
       <c r="AB27" t="n">
         <v/>
@@ -8881,10 +8983,10 @@
         <v>2.81</v>
       </c>
       <c r="C28" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="D28" t="n">
-        <v>894938</v>
+        <v>895191</v>
       </c>
       <c r="E28" t="n">
         <v>51.2</v>
@@ -8914,19 +9016,19 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>12181</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.35</v>
+        <v>-0.71</v>
       </c>
       <c r="Q28" t="n">
         <v>2.96</v>
       </c>
       <c r="R28" t="n">
-        <v>2.77</v>
+        <v>2.7625</v>
       </c>
       <c r="S28" t="n">
         <v>2.8139</v>
@@ -8957,7 +9059,7 @@
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>12.17</v>
+        <v>12.02</v>
       </c>
       <c r="AB28" t="n">
         <v>3.5</v>
@@ -8967,7 +9069,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>P/S 1.2x vs 2.0x median — trading at discount | P/B 0.3x vs 0.6x median — trading at discount | EV/EBITDA 12.2x vs 18.4x median — trading at discount | Analyst target $3.50</t>
+          <t>P/S 1.2x vs 2.0x median — trading at discount | P/B 0.3x vs 0.6x median — trading at discount | EV/EBITDA 12.0x vs 18.4x median — trading at discount | Analyst target $3.50</t>
         </is>
       </c>
       <c r="AE28" t="n">
@@ -9004,7 +9106,7 @@
         <v>2.35</v>
       </c>
       <c r="D29" t="n">
-        <v>1234753</v>
+        <v>1234810</v>
       </c>
       <c r="E29" t="n">
         <v>42.6</v>
@@ -9034,13 +9136,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="O29" t="n">
         <v>6082</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>-0.78</v>
       </c>
       <c r="Q29" t="n">
         <v>5.88</v>
@@ -9077,7 +9179,7 @@
         </is>
       </c>
       <c r="AA29" t="n">
-        <v>-19.39</v>
+        <v>-19.24</v>
       </c>
       <c r="AB29" t="n">
         <v>13</v>
@@ -9087,7 +9189,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>P/S 1.3x vs 1.1x median — in-line | P/B 6.4x vs 1.7x median — trading at premium | EV/EBITDA -19.4x vs -1.7x median — trading at premium | Analyst target $13.00</t>
+          <t>P/S 1.3x vs 1.1x median — in-line | P/B 6.4x vs 1.7x median — trading at premium | EV/EBITDA -19.2x vs -1.7x median — trading at premium | Analyst target $13.00</t>
         </is>
       </c>
       <c r="AE29" t="n">
@@ -9121,10 +9223,10 @@
         <v>4.97</v>
       </c>
       <c r="C30" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="D30" t="n">
-        <v>975142</v>
+        <v>975248</v>
       </c>
       <c r="E30" t="n">
         <v>54.3</v>
@@ -9197,7 +9299,7 @@
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="AB30" t="n">
         <v>20</v>
@@ -9207,7 +9309,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>P/S 0.7x vs 1.8x median — trading at discount | P/B 1.2x vs 0.1x median — trading at premium | EV/EBITDA -0.2x vs -1.2x median — trading at discount | Analyst target $20.00 | Graham # $93.54</t>
+          <t>P/S 0.7x vs 1.8x median — trading at discount | P/B 1.2x vs 0.1x median — trading at premium | EV/EBITDA -0.2x vs -1.3x median — trading at discount | Analyst target $20.00 | Graham # $93.54</t>
         </is>
       </c>
       <c r="AE30" t="n">
@@ -9244,7 +9346,7 @@
         <v>2.28</v>
       </c>
       <c r="D31" t="n">
-        <v>2408206</v>
+        <v>2408498</v>
       </c>
       <c r="E31" t="n">
         <v>79.8</v>
@@ -9274,13 +9376,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.71</v>
+        <v>1.6908</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.59</v>
+        <v>-0.54</v>
       </c>
       <c r="Q31" t="n">
         <v>1.77</v>
@@ -9361,10 +9463,10 @@
         <v>0.66</v>
       </c>
       <c r="C32" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="D32" t="n">
-        <v>4831064</v>
+        <v>4833438</v>
       </c>
       <c r="E32" t="n">
         <v>38.5</v>
@@ -9394,13 +9496,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6335</v>
+        <v>0.62</v>
       </c>
       <c r="O32" t="n">
         <v>14755</v>
       </c>
       <c r="P32" t="n">
-        <v>-4.54</v>
+        <v>-6.57</v>
       </c>
       <c r="Q32" t="n">
         <v>1.01</v>
@@ -9484,7 +9586,7 @@
         <v>2.12</v>
       </c>
       <c r="D33" t="n">
-        <v>2415483</v>
+        <v>2415699</v>
       </c>
       <c r="E33" t="n">
         <v>54.2</v>
@@ -9557,7 +9659,7 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>9.41</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB33" t="n">
         <v>17.25</v>
@@ -9594,68 +9696,68 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TARA</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="C34" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="D34" t="n">
-        <v>1411667</v>
+        <v>578819</v>
       </c>
       <c r="E34" t="n">
-        <v>45.1</v>
+        <v>58.3</v>
       </c>
       <c r="F34" t="n">
-        <v>3.96</v>
+        <v>3.63</v>
       </c>
       <c r="G34" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.023</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.3549</v>
+      </c>
+      <c r="S34" t="n">
         <v>4.1</v>
       </c>
-      <c r="H34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="J34" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="b">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="O34" t="n">
-        <v>50357</v>
-      </c>
-      <c r="P34" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="V34" t="b">
         <v>1</v>
@@ -9669,83 +9771,83 @@
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>1.43</v>
+        <v/>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1.4x vs 1.7x median — in-line</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="AA34" t="n">
-        <v>-1.24</v>
+        <v/>
       </c>
       <c r="AB34" t="n">
-        <v>25.71</v>
+        <v/>
       </c>
       <c r="AC34" t="n">
         <v/>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>P/B 1.4x vs 1.7x median — in-line | EV/EBITDA -1.2x vs -1.7x median — trading at discount | Analyst target $25.71</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF34" t="n">
-        <v>5.44</v>
+        <v>6.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>78.3</v>
+        <v>133.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.66</v>
+        <v>0.42</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.16</v>
+        <v>7.66</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.38–$5.44 (ann. vol 78%) | ATR range: $2.66–$5.16</t>
+          <t>1-SD 3mo range: $1.35–$6.73 (ann. vol 133%) | ATR range: $0.42–$7.66</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AKBA</t>
+          <t>TARA</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.91</v>
+        <v>3.91</v>
       </c>
       <c r="C35" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="D35" t="n">
-        <v>6158932</v>
+        <v>1411755</v>
       </c>
       <c r="E35" t="n">
-        <v>38.5</v>
+        <v>45.1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.98</v>
+        <v>3.96</v>
       </c>
       <c r="G35" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="H35" t="n">
-        <v>1.45</v>
+        <v>4.6</v>
       </c>
       <c r="I35" t="n">
-        <v>1.14</v>
+        <v>4.02</v>
       </c>
       <c r="J35" t="n">
-        <v>1.32</v>
+        <v>5.18</v>
       </c>
       <c r="K35" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9754,598 +9856,598 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0.9117</v>
+        <v>3.98</v>
       </c>
       <c r="O35" t="n">
-        <v>125903</v>
+        <v>50357</v>
       </c>
       <c r="P35" t="n">
-        <v>0.48</v>
+        <v>1.79</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.97</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>0.8911</v>
+        <v>3.85</v>
       </c>
       <c r="S35" t="n">
-        <v>0.9321</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="V35" t="b">
         <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.15</v>
+        <v/>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>1.1x vs 1.1x median — in-line</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>9.85</v>
+        <v>1.43</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9.9x vs 1.7x median — trading at premium</t>
+          <t>1.4x vs 1.7x median — in-line</t>
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>-71.98</v>
+        <v>-1.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.8</v>
+        <v>25.71</v>
       </c>
       <c r="AC35" t="n">
         <v/>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>P/S 1.1x vs 1.1x median — in-line | P/B 9.9x vs 1.7x median — trading at premium | EV/EBITDA -72.0x vs -1.7x median — trading at premium | Analyst target $3.80</t>
+          <t>P/B 1.4x vs 1.7x median — in-line | EV/EBITDA -1.2x vs -1.7x median — trading at discount | Analyst target $25.71</t>
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>0.53</v>
+        <v>2.38</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.28</v>
+        <v>5.44</v>
       </c>
       <c r="AG35" t="n">
-        <v>82.8</v>
+        <v>78.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.46</v>
+        <v>2.66</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.35</v>
+        <v>5.16</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.53–$1.28 (ann. vol 83%) | ATR range: $0.46–$1.35</t>
+          <t>1-SD 3mo range: $2.38–$5.44 (ann. vol 78%) | ATR range: $2.66–$5.16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BEEM</t>
+          <t>AKBA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.71</v>
+        <v>0.91</v>
       </c>
       <c r="C36" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="D36" t="n">
-        <v>4010032</v>
+        <v>6159124</v>
       </c>
       <c r="E36" t="n">
-        <v>73.09999999999999</v>
+        <v>38.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1.28</v>
+        <v>0.98</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="H36" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="I36" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="J36" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="K36" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.69</v>
+        <v>0.8969</v>
       </c>
       <c r="O36" t="n">
-        <v>747</v>
+        <v>125903</v>
       </c>
       <c r="P36" t="n">
-        <v>-2.31</v>
+        <v>-1.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.72</v>
+        <v>0.97</v>
       </c>
       <c r="R36" t="n">
-        <v>1.32</v>
+        <v>0.8911</v>
       </c>
       <c r="S36" t="n">
-        <v>1.3424</v>
+        <v>0.9321</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-22.4</v>
+        <v>2.73</v>
       </c>
       <c r="V36" t="b">
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>1.4x vs 1.8x median — in-line</t>
+          <t>1.1x vs 1.1x median — in-line</t>
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>1.88</v>
+        <v>9.85</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>1.9x vs 0.1x median — trading at premium</t>
+          <t>9.9x vs 1.7x median — trading at premium</t>
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>-2.27</v>
+        <v>-68.63</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC36" t="n">
         <v/>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>P/S 1.4x vs 1.8x median — in-line | P/B 1.9x vs 0.1x median — trading at premium | EV/EBITDA -2.3x vs -1.2x median — trading at premium | Analyst target $2.50</t>
+          <t>P/S 1.1x vs 1.1x median — in-line | P/B 9.9x vs 1.7x median — trading at premium | EV/EBITDA -68.6x vs -1.7x median — trading at premium | Analyst target $3.80</t>
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.45</v>
+        <v>1.28</v>
       </c>
       <c r="AG36" t="n">
-        <v>86.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.72</v>
+        <v>1.35</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.97–$2.45 (ann. vol 87%) | ATR range: $0.70–$2.72</t>
+          <t>1-SD 3mo range: $0.53–$1.28 (ann. vol 83%) | ATR range: $0.46–$1.35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RXST</t>
+          <t>BEEM</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6.38</v>
+        <v>1.71</v>
       </c>
       <c r="C37" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="D37" t="n">
-        <v>5540884</v>
+        <v>4012658</v>
       </c>
       <c r="E37" t="n">
-        <v>54.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>6.28</v>
+        <v>1.28</v>
       </c>
       <c r="G37" t="n">
-        <v>6.03</v>
+        <v>1.25</v>
       </c>
       <c r="H37" t="n">
-        <v>6.98</v>
+        <v>1.6</v>
       </c>
       <c r="I37" t="n">
-        <v>5.73</v>
+        <v>1.19</v>
       </c>
       <c r="J37" t="n">
-        <v>7.66</v>
+        <v>1.52</v>
       </c>
       <c r="K37" t="n">
-        <v>0.39</v>
+        <v>0.12</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6.38</v>
+        <v>1.7</v>
       </c>
       <c r="O37" t="n">
-        <v>32062</v>
+        <v>747</v>
       </c>
       <c r="P37" t="n">
-        <v>-0</v>
+        <v>-1.73</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.4</v>
+        <v>1.72</v>
       </c>
       <c r="R37" t="n">
-        <v>6.09</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>6.19</v>
+        <v>1.3424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>-2.98</v>
+        <v>-22.4</v>
       </c>
       <c r="V37" t="b">
         <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2.1x vs 1.1x median — trading at premium</t>
+          <t>1.4x vs 1.8x median — in-line</t>
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1.0x vs 1.7x median — trading at discount</t>
+          <t>1.9x vs 0.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA37" t="n">
-        <v>-1.32</v>
+        <v>-2.27</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.79</v>
+        <v>2.5</v>
       </c>
       <c r="AC37" t="n">
         <v/>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>P/S 2.1x vs 1.1x median — trading at premium | P/B 1.0x vs 1.7x median — trading at discount | EV/EBITDA -1.3x vs -1.7x median — trading at discount | Analyst target $7.79</t>
+          <t>P/S 1.4x vs 1.8x median — in-line | P/B 1.9x vs 0.1x median — trading at premium | EV/EBITDA -2.3x vs -1.3x median — trading at premium | Analyst target $2.50</t>
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>4.36</v>
+        <v>0.97</v>
       </c>
       <c r="AF37" t="n">
-        <v>8.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG37" t="n">
-        <v>63.4</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.35</v>
+        <v>0.7</v>
       </c>
       <c r="AI37" t="n">
-        <v>9.41</v>
+        <v>2.72</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $4.36–$8.40 (ann. vol 63%) | ATR range: $3.35–$9.41</t>
+          <t>1-SD 3mo range: $0.97–$2.45 (ann. vol 87%) | ATR range: $0.70–$2.72</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>RXST</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.98</v>
+        <v>6.38</v>
       </c>
       <c r="C38" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="D38" t="n">
-        <v>672535</v>
+        <v>5540884</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>54.7</v>
       </c>
       <c r="F38" t="n">
-        <v>4.92</v>
+        <v>6.28</v>
       </c>
       <c r="G38" t="n">
-        <v>4.98</v>
+        <v>6.03</v>
       </c>
       <c r="H38" t="n">
-        <v>6.48</v>
+        <v>6.98</v>
       </c>
       <c r="I38" t="n">
-        <v>4.88</v>
+        <v>5.73</v>
       </c>
       <c r="J38" t="n">
-        <v>6.2</v>
+        <v>7.66</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.1</v>
+        <v>6.38</v>
       </c>
       <c r="O38" t="n">
-        <v>2325</v>
+        <v>32062</v>
       </c>
       <c r="P38" t="n">
-        <v>2.24</v>
+        <v>-0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="R38" t="n">
-        <v>3.95</v>
+        <v>6.09</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6.19</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>24.69</v>
+        <v>-2.98</v>
       </c>
       <c r="V38" t="b">
         <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>18.82</v>
+        <v>2.08</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>18.8x vs 1.8x median — trading at premium</t>
+          <t>2.1x vs 1.1x median — trading at premium</t>
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>8.74</v>
+        <v>1.01</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>8.7x vs 0.1x median — trading at premium</t>
+          <t>1.0x vs 1.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA38" t="n">
-        <v/>
+        <v>-1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v/>
+        <v>7.79</v>
       </c>
       <c r="AC38" t="n">
         <v/>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>P/S 18.8x vs 1.8x median — trading at premium | P/B 8.7x vs 0.1x median — trading at premium</t>
+          <t>P/S 2.1x vs 1.1x median — trading at premium | P/B 1.0x vs 1.7x median — trading at discount | EV/EBITDA -1.3x vs -1.7x median — trading at discount | Analyst target $7.79</t>
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>-0.38</v>
+        <v>4.36</v>
       </c>
       <c r="AF38" t="n">
-        <v>8.35</v>
+        <v>8.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>219.2</v>
+        <v>63.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>-1.32</v>
+        <v>3.35</v>
       </c>
       <c r="AI38" t="n">
-        <v>9.289999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $-0.38–$8.35 (ann. vol 219%) | ATR range: $-1.32–$9.29</t>
+          <t>1-SD 3mo range: $4.36–$8.40 (ann. vol 63%) | ATR range: $3.35–$9.41</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.36</v>
+        <v>3.98</v>
       </c>
       <c r="C39" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="D39" t="n">
-        <v>5028608</v>
+        <v>672849</v>
       </c>
       <c r="E39" t="n">
-        <v>67.09999999999999</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
-        <v>9.970000000000001</v>
+        <v>4.92</v>
       </c>
       <c r="G39" t="n">
-        <v>9.92</v>
+        <v>4.98</v>
       </c>
       <c r="H39" t="n">
-        <v>10.29</v>
+        <v>6.48</v>
       </c>
       <c r="I39" t="n">
-        <v>9.73</v>
+        <v>4.88</v>
       </c>
       <c r="J39" t="n">
-        <v>10.41</v>
+        <v>6.2</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>10.36</v>
+        <v>4.14</v>
       </c>
       <c r="O39" t="n">
-        <v>94516</v>
+        <v>2325</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.19</v>
+        <v>3.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.46</v>
+        <v>6.5</v>
       </c>
       <c r="R39" t="n">
-        <v>9.949999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="S39" t="n">
-        <v>10.2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>-1.73</v>
+        <v>24.69</v>
       </c>
       <c r="V39" t="b">
         <v>1</v>
       </c>
       <c r="W39" t="n">
-        <v>8.91</v>
+        <v>18.82</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>8.9x vs 2.0x median — trading at premium</t>
+          <t>18.8x vs 1.8x median — trading at premium</t>
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>0.98</v>
+        <v>8.74</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>1.0x vs 0.6x median — trading at premium</t>
+          <t>8.7x vs 0.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA39" t="n">
-        <v>24.7</v>
+        <v/>
       </c>
       <c r="AB39" t="n">
-        <v>10.5</v>
+        <v/>
       </c>
       <c r="AC39" t="n">
-        <v>11.03</v>
+        <v/>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>P/S 8.9x vs 2.0x median — trading at premium | P/B 1.0x vs 0.6x median — trading at premium | EV/EBITDA 24.7x vs 18.4x median — trading at premium | Analyst target $10.50 | Graham # $11.03</t>
+          <t>P/S 18.8x vs 1.8x median — trading at premium | P/B 8.7x vs 0.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>9.19</v>
+        <v>-0.38</v>
       </c>
       <c r="AF39" t="n">
-        <v>11.53</v>
+        <v>8.35</v>
       </c>
       <c r="AG39" t="n">
-        <v>22.6</v>
+        <v>219.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>8.82</v>
+        <v>-1.32</v>
       </c>
       <c r="AI39" t="n">
-        <v>11.9</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $9.19–$11.53 (ann. vol 23%) | ATR range: $8.82–$11.90</t>
+          <t>1-SD 3mo range: $-0.38–$8.35 (ann. vol 219%) | ATR range: $-1.32–$9.29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SKYX</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.25</v>
+        <v>10.36</v>
       </c>
       <c r="C40" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="D40" t="n">
-        <v>1120255</v>
+        <v>5028608</v>
       </c>
       <c r="E40" t="n">
-        <v>58.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>1.17</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>1.16</v>
+        <v>9.92</v>
       </c>
       <c r="H40" t="n">
-        <v>1.35</v>
+        <v>10.29</v>
       </c>
       <c r="I40" t="n">
-        <v>1.14</v>
+        <v>9.73</v>
       </c>
       <c r="J40" t="n">
-        <v>1.59</v>
+        <v>10.41</v>
       </c>
       <c r="K40" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="L40" t="n">
         <v>2</v>
@@ -10354,358 +10456,358 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.26</v>
+        <v>10.29</v>
       </c>
       <c r="O40" t="n">
-        <v>8735</v>
+        <v>94516</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4</v>
+        <v>-0.87</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.29</v>
+        <v>10.46</v>
       </c>
       <c r="R40" t="n">
-        <v>1.1</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S40" t="n">
-        <v>1.26</v>
+        <v>10.2</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0.4</v>
+        <v>-1.73</v>
       </c>
       <c r="V40" t="b">
         <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>1.76</v>
+        <v>8.91</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>1.8x vs 1.4x median — trading at premium</t>
+          <t>8.9x vs 2.0x median — trading at premium</t>
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>14.88</v>
+        <v>0.98</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14.9x vs 0.6x median — trading at premium</t>
+          <t>1.0x vs 0.6x median — trading at premium</t>
         </is>
       </c>
       <c r="AA40" t="n">
-        <v>-7.15</v>
+        <v>24.7</v>
       </c>
       <c r="AB40" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AC40" t="n">
-        <v/>
+        <v>11.03</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>P/S 1.8x vs 1.4x median — trading at premium | P/B 14.9x vs 0.6x median — trading at premium | EV/EBITDA -7.2x vs -3.2x median — trading at premium | Analyst target $4.00</t>
+          <t>P/S 8.9x vs 2.0x median — trading at premium | P/B 1.0x vs 0.6x median — trading at premium | EV/EBITDA 24.7x vs 18.4x median — trading at premium | Analyst target $10.50 | Graham # $11.03</t>
         </is>
       </c>
       <c r="AE40" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.81</v>
+        <v>11.53</v>
       </c>
       <c r="AG40" t="n">
-        <v>89.2</v>
+        <v>22.6</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.64</v>
+        <v>8.82</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.86</v>
+        <v>11.9</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.69–$1.81 (ann. vol 89%) | ATR range: $0.64–$1.86</t>
+          <t>1-SD 3mo range: $9.19–$11.53 (ann. vol 23%) | ATR range: $8.82–$11.90</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IFRX</t>
+          <t>SKYX</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="C41" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="D41" t="n">
-        <v>2531358</v>
+        <v>1120359</v>
       </c>
       <c r="E41" t="n">
-        <v>69.3</v>
+        <v>58.3</v>
       </c>
       <c r="F41" t="n">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="G41" t="n">
-        <v>1.97</v>
+        <v>1.16</v>
       </c>
       <c r="H41" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="I41" t="n">
-        <v>1.96</v>
+        <v>1.14</v>
       </c>
       <c r="J41" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="K41" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>1.27</v>
       </c>
       <c r="O41" t="n">
-        <v>30117</v>
+        <v>8735</v>
       </c>
       <c r="P41" t="n">
-        <v>0.41</v>
+        <v>1.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="R41" t="n">
-        <v>1.9505</v>
+        <v>1.1</v>
       </c>
       <c r="S41" t="n">
-        <v>2.45</v>
+        <v>1.26</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.66</v>
+        <v>0.4</v>
       </c>
       <c r="V41" t="b">
         <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>-35306.52</v>
+        <v>1.76</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>-35306.5x vs 1.1x median — trading at discount</t>
+          <t>1.8x vs 1.4x median — trading at premium</t>
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>2.09</v>
+        <v>14.88</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2.1x vs 1.7x median — in-line</t>
+          <t>14.9x vs 0.6x median — trading at premium</t>
         </is>
       </c>
       <c r="AA41" t="n">
-        <v>-5.75</v>
+        <v>-7.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>7.96</v>
+        <v>4</v>
       </c>
       <c r="AC41" t="n">
         <v/>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>P/S -35306.5x vs 1.1x median — trading at discount | P/B 2.1x vs 1.7x median — in-line | EV/EBITDA -5.7x vs -1.7x median — trading at premium | Analyst target $7.96</t>
+          <t>P/S 1.8x vs 1.4x median — trading at premium | P/B 14.9x vs 0.6x median — trading at premium | EV/EBITDA -7.2x vs -3.2x median — trading at premium | Analyst target $4.00</t>
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>1.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF41" t="n">
-        <v>3.68</v>
+        <v>1.81</v>
       </c>
       <c r="AG41" t="n">
-        <v>104.4</v>
+        <v>89.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.24</v>
+        <v>0.64</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.6</v>
+        <v>1.86</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.16–$3.68 (ann. vol 104%) | ATR range: $1.24–$3.60</t>
+          <t>1-SD 3mo range: $0.69–$1.81 (ann. vol 89%) | ATR range: $0.64–$1.86</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>IFRX</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="C42" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="D42" t="n">
-        <v>10404119</v>
+        <v>2531419</v>
       </c>
       <c r="E42" t="n">
-        <v>56</v>
+        <v>69.3</v>
       </c>
       <c r="F42" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="G42" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="H42" t="n">
-        <v>2.53</v>
+        <v>1.62</v>
       </c>
       <c r="I42" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="J42" t="n">
-        <v>2.69</v>
+        <v>1.48</v>
       </c>
       <c r="K42" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.83</v>
+        <v>2.4232</v>
       </c>
       <c r="O42" t="n">
-        <v>335914</v>
+        <v>30117</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.54</v>
+        <v>0.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>2.524</v>
       </c>
       <c r="R42" t="n">
-        <v>1.6</v>
+        <v>1.9505</v>
       </c>
       <c r="S42" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>5.43</v>
+        <v>1.66</v>
       </c>
       <c r="V42" t="b">
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>77.28</v>
+        <v>-35306.52</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>77.3x vs 1.4x median — trading at premium</t>
+          <t>-35306.5x vs 1.1x median — trading at discount</t>
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>1.09</v>
+        <v>2.09</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1.1x vs 0.6x median — trading at premium</t>
+          <t>2.1x vs 1.7x median — in-line</t>
         </is>
       </c>
       <c r="AA42" t="n">
-        <v>-4.06</v>
+        <v>-5.58</v>
       </c>
       <c r="AB42" t="n">
-        <v>2</v>
+        <v>7.97</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.63</v>
+        <v/>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>P/S 77.3x vs 1.4x median — trading at premium | P/B 1.1x vs 0.6x median — trading at premium | EV/EBITDA -4.1x vs -3.2x median — trading at premium | Analyst target $2.00 | Graham # $1.63</t>
+          <t>P/S -35306.5x vs 1.1x median — trading at discount | P/B 2.1x vs 1.7x median — in-line | EV/EBITDA -5.6x vs -1.7x median — trading at premium | Analyst target $7.97</t>
         </is>
       </c>
       <c r="AE42" t="n">
-        <v>0.82</v>
+        <v>1.16</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="AG42" t="n">
-        <v>111.8</v>
+        <v>104.4</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.83</v>
+        <v>1.24</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.82–$2.88 (ann. vol 112%) | ATR range: $0.83–$2.87</t>
+          <t>1-SD 3mo range: $1.16–$3.68 (ann. vol 104%) | ATR range: $1.24–$3.60</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4.03</v>
+        <v>1.85</v>
       </c>
       <c r="C43" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="D43" t="n">
-        <v>3233100</v>
+        <v>10405483</v>
       </c>
       <c r="E43" t="n">
-        <v>63.3</v>
+        <v>56</v>
       </c>
       <c r="F43" t="n">
-        <v>3.56</v>
+        <v>1.7</v>
       </c>
       <c r="G43" t="n">
-        <v>3.67</v>
+        <v>1.82</v>
       </c>
       <c r="H43" t="n">
-        <v>4.3</v>
+        <v>2.53</v>
       </c>
       <c r="I43" t="n">
-        <v>3.62</v>
+        <v>1.74</v>
       </c>
       <c r="J43" t="n">
-        <v>4.77</v>
+        <v>2.69</v>
       </c>
       <c r="K43" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -10714,154 +10816,154 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.03</v>
+        <v>1.86</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>335914</v>
       </c>
       <c r="P43" t="n">
-        <v>0.12</v>
+        <v>1.09</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.14</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>3.55</v>
+        <v>1.6</v>
       </c>
       <c r="S43" t="n">
-        <v>4.11</v>
+        <v>1.94</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.11</v>
+        <v>5.43</v>
       </c>
       <c r="V43" t="b">
         <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>28.81</v>
+        <v>77.28</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>77.3x vs 1.4x median — trading at premium</t>
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>73.27</v>
+        <v>1.09</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>1.1x vs 0.6x median — trading at premium</t>
         </is>
       </c>
       <c r="AA43" t="n">
-        <v>-17.54</v>
+        <v>-4.06</v>
       </c>
       <c r="AB43" t="n">
-        <v>10.33</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="n">
-        <v/>
+        <v>1.63</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Analyst target $10.33</t>
+          <t>P/S 77.3x vs 1.4x median — trading at premium | P/B 1.1x vs 0.6x median — trading at premium | EV/EBITDA -4.1x vs -3.2x median — trading at premium | Analyst target $2.00 | Graham # $1.63</t>
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>2.72</v>
+        <v>0.82</v>
       </c>
       <c r="AF43" t="n">
-        <v>5.34</v>
+        <v>2.88</v>
       </c>
       <c r="AG43" t="n">
-        <v>64.90000000000001</v>
+        <v>111.8</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.12</v>
+        <v>0.83</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.94</v>
+        <v>2.87</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $2.72–$5.34 (ann. vol 65%) | ATR range: $2.12–$5.94</t>
+          <t>1-SD 3mo range: $0.82–$2.88 (ann. vol 112%) | ATR range: $0.83–$2.87</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C44" t="n">
         <v>1.58</v>
       </c>
-      <c r="C44" t="n">
-        <v>1.55</v>
-      </c>
       <c r="D44" t="n">
-        <v>2091976</v>
+        <v>3233115</v>
       </c>
       <c r="E44" t="n">
-        <v>75</v>
+        <v>63.3</v>
       </c>
       <c r="F44" t="n">
-        <v>1.37</v>
+        <v>3.56</v>
       </c>
       <c r="G44" t="n">
-        <v>1.25</v>
+        <v>3.67</v>
       </c>
       <c r="H44" t="n">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="I44" t="n">
-        <v>1.23</v>
+        <v>3.62</v>
       </c>
       <c r="J44" t="n">
-        <v>1.05</v>
+        <v>4.77</v>
       </c>
       <c r="K44" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.55</v>
+        <v>4.03</v>
       </c>
       <c r="O44" t="n">
-        <v>40931</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-1.59</v>
+        <v>0.12</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.58</v>
+        <v>4.14</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>3.55</v>
       </c>
       <c r="S44" t="n">
-        <v>1.48</v>
+        <v>4.11</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>-6.03</v>
+        <v>2.11</v>
       </c>
       <c r="V44" t="b">
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>13.1</v>
+        <v>28.81</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -10869,7 +10971,7 @@
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>2.24</v>
+        <v>73.27</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -10877,75 +10979,75 @@
         </is>
       </c>
       <c r="AA44" t="n">
-        <v>-10.88</v>
+        <v>-17.54</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.75</v>
+        <v>10.33</v>
       </c>
       <c r="AC44" t="n">
         <v/>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Analyst target $2.75</t>
+          <t>Analyst target $10.33</t>
         </is>
       </c>
       <c r="AE44" t="n">
-        <v>0.99</v>
+        <v>2.72</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.17</v>
+        <v>5.34</v>
       </c>
       <c r="AG44" t="n">
-        <v>74.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.76</v>
+        <v>2.12</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.4</v>
+        <v>5.94</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $0.99–$2.17 (ann. vol 74%) | ATR range: $0.76–$2.40</t>
+          <t>1-SD 3mo range: $2.72–$5.34 (ann. vol 65%) | ATR range: $2.12–$5.94</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CAMP</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4.2</v>
+        <v>15.17</v>
       </c>
       <c r="C45" t="n">
         <v>1.55</v>
       </c>
       <c r="D45" t="n">
-        <v>988701</v>
+        <v>7025829</v>
       </c>
       <c r="E45" t="n">
-        <v>48.3</v>
+        <v>46</v>
       </c>
       <c r="F45" t="n">
-        <v>4.35</v>
+        <v>15.52</v>
       </c>
       <c r="G45" t="n">
-        <v>4.22</v>
+        <v>16.68</v>
       </c>
       <c r="H45" t="n">
-        <v>4.05</v>
+        <v>15.09</v>
       </c>
       <c r="I45" t="n">
-        <v>4.13</v>
+        <v>17.36</v>
       </c>
       <c r="J45" t="n">
-        <v>4.48</v>
+        <v>15.04</v>
       </c>
       <c r="K45" t="n">
-        <v>0.44</v>
+        <v>1.21</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -10954,410 +11056,410 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.2</v>
+        <v>15.51</v>
       </c>
       <c r="O45" t="n">
-        <v>11412</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.36</v>
+        <v>2.31</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.55</v>
+        <v>15.51</v>
       </c>
       <c r="R45" t="n">
-        <v>4.2</v>
+        <v>13.85</v>
       </c>
       <c r="S45" t="n">
-        <v>4.53</v>
+        <v>14.21</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>8.24</v>
+        <v>-6.27</v>
       </c>
       <c r="V45" t="b">
         <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>62.52</v>
+        <v>3.25</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>62.5x vs 1.1x median — trading at premium</t>
+          <t>3.3x vs 1.8x median — trading at premium</t>
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>-323.08</v>
+        <v>2.3</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>-323.1x vs 1.7x median — trading at discount</t>
+          <t>2.3x vs 0.1x median — trading at premium</t>
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>-3.86</v>
+        <v>21.84</v>
       </c>
       <c r="AB45" t="n">
-        <v>9.92</v>
+        <v>22</v>
       </c>
       <c r="AC45" t="n">
-        <v/>
+        <v>6.33</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>P/S 62.5x vs 1.1x median — trading at premium | P/B -323.1x vs 1.7x median — trading at discount | EV/EBITDA -3.9x vs -1.7x median — trading at premium | Analyst target $9.92</t>
+          <t>P/S 3.3x vs 1.8x median — trading at premium | P/B 2.3x vs 0.1x median — trading at premium | EV/EBITDA 21.8x vs -1.3x median — trading at discount | Analyst target $22.00 | Graham # $6.33</t>
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>1.73</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="AF45" t="n">
-        <v>6.67</v>
+        <v>22.3</v>
       </c>
       <c r="AG45" t="n">
-        <v>117.4</v>
+        <v>94</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.51</v>
+        <v>6.86</v>
       </c>
       <c r="AI45" t="n">
-        <v>7.89</v>
+        <v>23.48</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.73–$6.67 (ann. vol 117%) | ATR range: $0.51–$7.89</t>
+          <t>1-SD 3mo range: $8.04–$22.30 (ann. vol 94%) | ATR range: $6.86–$23.48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ASYS</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.17</v>
+        <v>1.58</v>
       </c>
       <c r="C46" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="D46" t="n">
-        <v>7024507</v>
+        <v>2092335</v>
       </c>
       <c r="E46" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="F46" t="n">
-        <v>15.52</v>
+        <v>1.37</v>
       </c>
       <c r="G46" t="n">
-        <v>16.68</v>
+        <v>1.25</v>
       </c>
       <c r="H46" t="n">
-        <v>15.09</v>
+        <v>1.11</v>
       </c>
       <c r="I46" t="n">
-        <v>17.36</v>
+        <v>1.23</v>
       </c>
       <c r="J46" t="n">
-        <v>15.04</v>
+        <v>1.05</v>
       </c>
       <c r="K46" t="n">
-        <v>1.21</v>
+        <v>0.09</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>15.36</v>
+        <v>1.5599</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>40931</v>
       </c>
       <c r="P46" t="n">
-        <v>1.32</v>
+        <v>-0.96</v>
       </c>
       <c r="Q46" t="n">
-        <v>15.4534</v>
+        <v>1.58</v>
       </c>
       <c r="R46" t="n">
-        <v>13.85</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>14.21</v>
+        <v>1.48</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>-6.27</v>
+        <v>-6.03</v>
       </c>
       <c r="V46" t="b">
         <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>3.25</v>
+        <v>13.1</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>3.3x vs 1.8x median — trading at premium</t>
+          <t>N/A — sector too small</t>
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>2.3x vs 0.1x median — trading at premium</t>
+          <t>N/A — sector too small</t>
         </is>
       </c>
       <c r="AA46" t="n">
-        <v>20.08</v>
+        <v>-10.88</v>
       </c>
       <c r="AB46" t="n">
-        <v>22</v>
+        <v>2.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.33</v>
+        <v/>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>P/S 3.3x vs 1.8x median — trading at premium | P/B 2.3x vs 0.1x median — trading at premium | EV/EBITDA 20.1x vs -1.2x median — trading at discount | Analyst target $22.00 | Graham # $6.33</t>
+          <t>Analyst target $2.75</t>
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>8.039999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="AF46" t="n">
-        <v>22.3</v>
+        <v>2.17</v>
       </c>
       <c r="AG46" t="n">
-        <v>94</v>
+        <v>74.2</v>
       </c>
       <c r="AH46" t="n">
-        <v>6.86</v>
+        <v>0.76</v>
       </c>
       <c r="AI46" t="n">
-        <v>23.48</v>
+        <v>2.4</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $8.04–$22.30 (ann. vol 94%) | ATR range: $6.86–$23.48</t>
+          <t>1-SD 3mo range: $0.99–$2.17 (ann. vol 74%) | ATR range: $0.76–$2.40</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>CAMP</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.71</v>
+        <v>4.2</v>
       </c>
       <c r="C47" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="D47" t="n">
-        <v>599498</v>
+        <v>988701</v>
       </c>
       <c r="E47" t="n">
-        <v>70.09999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="F47" t="n">
-        <v>2.22</v>
+        <v>4.35</v>
       </c>
       <c r="G47" t="n">
-        <v>2.11</v>
+        <v>4.22</v>
       </c>
       <c r="H47" t="n">
-        <v>2.63</v>
+        <v>4.05</v>
       </c>
       <c r="I47" t="n">
-        <v>2.02</v>
+        <v>4.13</v>
       </c>
       <c r="J47" t="n">
-        <v>2.51</v>
+        <v>4.48</v>
       </c>
       <c r="K47" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.71</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
-        <v>3310</v>
+        <v>11412</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.73</v>
+        <v>0.36</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.92</v>
+        <v>4.55</v>
       </c>
       <c r="R47" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="S47" t="n">
-        <v>2.7174</v>
+        <v>4.53</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.46</v>
+        <v>8.24</v>
       </c>
       <c r="V47" t="b">
         <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>12.13</v>
+        <v>62.52</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>12.1x vs 12.1x median — in-line</t>
+          <t>62.5x vs 1.1x median — trading at premium</t>
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>1.44</v>
+        <v>-323.08</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>1.4x vs -15.7x median — trading at discount</t>
+          <t>-323.1x vs 1.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA47" t="n">
-        <v>-13.39</v>
+        <v>-3.55</v>
       </c>
       <c r="AB47" t="n">
-        <v/>
+        <v>9.92</v>
       </c>
       <c r="AC47" t="n">
         <v/>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>P/S 12.1x vs 12.1x median — in-line | P/B 1.4x vs -15.7x median — trading at discount | EV/EBITDA -13.4x vs -13.4x median — in-line</t>
+          <t>P/S 62.5x vs 1.1x median — trading at premium | P/B -323.1x vs 1.7x median — trading at discount | EV/EBITDA -3.6x vs -1.7x median — trading at premium | Analyst target $9.92</t>
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="AF47" t="n">
-        <v>4.19</v>
+        <v>6.67</v>
       </c>
       <c r="AG47" t="n">
-        <v>109</v>
+        <v>117.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.28</v>
+        <v>0.51</v>
       </c>
       <c r="AI47" t="n">
-        <v>4.14</v>
+        <v>7.89</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.23–$4.19 (ann. vol 109%) | ATR range: $1.28–$4.14</t>
+          <t>1-SD 3mo range: $1.73–$6.67 (ann. vol 117%) | ATR range: $0.51–$7.89</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GORO</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3.56</v>
+        <v>2.71</v>
       </c>
       <c r="C48" t="n">
         <v>1.54</v>
       </c>
       <c r="D48" t="n">
-        <v>4942718</v>
+        <v>599498</v>
       </c>
       <c r="E48" t="n">
-        <v>60.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>3.02</v>
+        <v>2.22</v>
       </c>
       <c r="G48" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="H48" t="n">
-        <v>3.79</v>
+        <v>2.63</v>
       </c>
       <c r="I48" t="n">
-        <v>3.46</v>
+        <v>2.02</v>
       </c>
       <c r="J48" t="n">
-        <v>4.08</v>
+        <v>2.51</v>
       </c>
       <c r="K48" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.5899</v>
+        <v>2.76</v>
       </c>
       <c r="O48" t="n">
-        <v>14859</v>
+        <v>3310</v>
       </c>
       <c r="P48" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.88</v>
+        <v>2.92</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="S48" t="n">
-        <v>3.8</v>
+        <v>2.7174</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>6.74</v>
+        <v>-0.46</v>
       </c>
       <c r="V48" t="b">
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>6.78</v>
+        <v>12.13</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>12.1x vs 12.1x median — in-line</t>
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>-43.95</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>N/A — sector too small</t>
+          <t>1.4x vs -15.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA48" t="n">
-        <v>557.26</v>
+        <v>-13.39</v>
       </c>
       <c r="AB48" t="n">
         <v/>
@@ -11367,385 +11469,505 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>N/A — insufficient data</t>
+          <t>P/S 12.1x vs 12.1x median — in-line | P/B 1.4x vs -15.7x median — trading at discount | EV/EBITDA -13.4x vs -13.4x median — in-line</t>
         </is>
       </c>
       <c r="AE48" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AF48" t="n">
-        <v>5.22</v>
+        <v>4.19</v>
       </c>
       <c r="AG48" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AI48" t="n">
-        <v>6.03</v>
+        <v>4.14</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.90–$5.22 (ann. vol 93%) | ATR range: $1.09–$6.03</t>
+          <t>1-SD 3mo range: $1.23–$4.19 (ann. vol 109%) | ATR range: $1.28–$4.14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NERV</t>
+          <t>GORO</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.43</v>
+        <v>3.56</v>
       </c>
       <c r="C49" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="D49" t="n">
-        <v>1362215</v>
+        <v>4943300</v>
       </c>
       <c r="E49" t="n">
-        <v>67.40000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="F49" t="n">
-        <v>4.62</v>
+        <v>3.02</v>
       </c>
       <c r="G49" t="n">
-        <v>4.62</v>
+        <v>3.3</v>
       </c>
       <c r="H49" t="n">
-        <v>4.68</v>
+        <v>3.79</v>
       </c>
       <c r="I49" t="n">
-        <v>4.49</v>
+        <v>3.46</v>
       </c>
       <c r="J49" t="n">
-        <v>5.05</v>
+        <v>4.08</v>
       </c>
       <c r="K49" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>5.43</v>
+        <v>3.61</v>
       </c>
       <c r="O49" t="n">
-        <v>15915</v>
+        <v>14859</v>
       </c>
       <c r="P49" t="n">
-        <v>-0</v>
+        <v>1.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.43</v>
+        <v>3.88</v>
       </c>
       <c r="R49" t="n">
-        <v>4.79</v>
+        <v>3</v>
       </c>
       <c r="S49" t="n">
-        <v>4.9696</v>
+        <v>3.8</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>-8.48</v>
+        <v>6.74</v>
       </c>
       <c r="V49" t="b">
         <v>1</v>
       </c>
       <c r="W49" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="Y49" t="n">
+        <v>-43.95</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>N/A — sector too small</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>557.26</v>
+      </c>
+      <c r="AB49" t="n">
         <v/>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>N/A — insufficient data</t>
-        </is>
-      </c>
-      <c r="Y49" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>-1.2x vs 1.7x median — trading at discount</t>
-        </is>
-      </c>
-      <c r="AA49" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>10.33</v>
       </c>
       <c r="AC49" t="n">
         <v/>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>P/B -1.2x vs 1.7x median — trading at discount | EV/EBITDA -6.7x vs -1.7x median — trading at premium | Analyst target $10.33</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="AE49" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AF49" t="n">
-        <v>8.92</v>
+        <v>5.22</v>
       </c>
       <c r="AG49" t="n">
-        <v>128.5</v>
+        <v>93</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="AI49" t="n">
-        <v>8.699999999999999</v>
+        <v>6.03</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $1.94–$8.92 (ann. vol 128%) | ATR range: $2.16–$8.70</t>
+          <t>1-SD 3mo range: $1.90–$5.22 (ann. vol 93%) | ATR range: $1.09–$6.03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DBI</t>
+          <t>NERV</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5.72</v>
+        <v>5.43</v>
       </c>
       <c r="C50" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="D50" t="n">
-        <v>2229006</v>
+        <v>1362402</v>
       </c>
       <c r="E50" t="n">
-        <v>44.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>5.96</v>
+        <v>4.62</v>
       </c>
       <c r="G50" t="n">
-        <v>6.13</v>
+        <v>4.62</v>
       </c>
       <c r="H50" t="n">
-        <v>6.02</v>
+        <v>4.68</v>
       </c>
       <c r="I50" t="n">
-        <v>5.94</v>
+        <v>4.49</v>
       </c>
       <c r="J50" t="n">
-        <v>6.39</v>
+        <v>5.05</v>
       </c>
       <c r="K50" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5.72</v>
+        <v>5.43</v>
       </c>
       <c r="O50" t="n">
-        <v>66540</v>
+        <v>15915</v>
       </c>
       <c r="P50" t="n">
-        <v>0.18</v>
+        <v>-0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.87</v>
+        <v>5.43</v>
       </c>
       <c r="R50" t="n">
-        <v>5.44</v>
+        <v>4.79</v>
       </c>
       <c r="S50" t="n">
-        <v>5.55</v>
+        <v>4.9696</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>-2.8</v>
+        <v>-8.48</v>
       </c>
       <c r="V50" t="b">
         <v>1</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>0.1x vs 0.1x median — in-line</t>
+          <t>N/A — insufficient data</t>
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>1.03</v>
+        <v>-1.2</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>1.0x vs 0.7x median — trading at premium</t>
+          <t>-1.2x vs 1.7x median — trading at discount</t>
         </is>
       </c>
       <c r="AA50" t="n">
-        <v>10.97</v>
+        <v>-7.28</v>
       </c>
       <c r="AB50" t="n">
-        <v>7.75</v>
+        <v>10.33</v>
       </c>
       <c r="AC50" t="n">
-        <v>5.23</v>
+        <v/>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>P/S 0.1x vs 0.1x median — in-line | P/B 1.0x vs 0.7x median — trading at premium | EV/EBITDA 11.0x vs 4.9x median — trading at premium | Analyst target $7.75 | Graham # $5.23</t>
+          <t>P/B -1.2x vs 1.7x median — trading at discount | EV/EBITDA -7.3x vs -1.7x median — trading at premium | Analyst target $10.33</t>
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>3.38</v>
+        <v>1.94</v>
       </c>
       <c r="AF50" t="n">
-        <v>8.06</v>
+        <v>8.92</v>
       </c>
       <c r="AG50" t="n">
-        <v>81.90000000000001</v>
+        <v>128.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.51</v>
+        <v>2.16</v>
       </c>
       <c r="AI50" t="n">
-        <v>7.93</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>1-SD 3mo range: $3.38–$8.06 (ann. vol 82%) | ATR range: $3.51–$7.93</t>
+          <t>1-SD 3mo range: $1.94–$8.92 (ann. vol 128%) | ATR range: $2.16–$8.70</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JQC</t>
+          <t>DBI</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4.75</v>
+        <v>5.72</v>
       </c>
       <c r="C51" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="D51" t="n">
-        <v>2898397</v>
+        <v>2229006</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>44.1</v>
       </c>
       <c r="F51" t="n">
-        <v>4.76</v>
+        <v>5.96</v>
       </c>
       <c r="G51" t="n">
-        <v>4.73</v>
+        <v>6.13</v>
       </c>
       <c r="H51" t="n">
-        <v>4.69</v>
+        <v>6.02</v>
       </c>
       <c r="I51" t="n">
-        <v>4.73</v>
+        <v>5.94</v>
       </c>
       <c r="J51" t="n">
-        <v>4.66</v>
+        <v>6.39</v>
       </c>
       <c r="K51" t="n">
-        <v>0.04</v>
+        <v>0.31</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.75</v>
+        <v>5.4901</v>
       </c>
       <c r="O51" t="n">
-        <v>2199</v>
+        <v>66540</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.77</v>
+        <v>5.87</v>
       </c>
       <c r="R51" t="n">
-        <v>4.74</v>
+        <v>5.44</v>
       </c>
       <c r="S51" t="n">
-        <v>4.77</v>
+        <v>5.55</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0.42</v>
+        <v>-2.8</v>
       </c>
       <c r="V51" t="b">
         <v>1</v>
       </c>
       <c r="W51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>0.1x vs 0.1x median — in-line</t>
+        </is>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>1.0x vs 0.7x median — trading at premium</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>P/S 0.1x vs 0.1x median — in-line | P/B 1.0x vs 0.7x median — trading at premium | EV/EBITDA 11.0x vs 4.9x median — trading at premium | Analyst target $7.75 | Graham # $5.23</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>1-SD 3mo range: $3.38–$8.06 (ann. vol 82%) | ATR range: $3.51–$7.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JQC</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2898397</v>
+      </c>
+      <c r="E52" t="n">
+        <v>50</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
         <v/>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="O52" t="n">
+        <v/>
+      </c>
+      <c r="P52" t="n">
+        <v/>
+      </c>
+      <c r="Q52" t="n">
+        <v/>
+      </c>
+      <c r="R52" t="n">
+        <v/>
+      </c>
+      <c r="S52" t="n">
+        <v/>
+      </c>
+      <c r="T52" t="n">
+        <v/>
+      </c>
+      <c r="U52" t="n">
+        <v/>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v/>
+      </c>
+      <c r="X52" t="inlineStr">
         <is>
           <t>N/A — insufficient data</t>
         </is>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y52" t="n">
         <v>0.86</v>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>0.9x vs -15.7x median — trading at discount</t>
         </is>
       </c>
-      <c r="AA51" t="n">
+      <c r="AA52" t="n">
         <v/>
       </c>
-      <c r="AB51" t="n">
+      <c r="AB52" t="n">
         <v/>
       </c>
-      <c r="AC51" t="n">
+      <c r="AC52" t="n">
         <v>5.88</v>
       </c>
-      <c r="AD51" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>P/B 0.9x vs -15.7x median — trading at discount | Graham # $5.88</t>
         </is>
       </c>
-      <c r="AE51" t="n">
+      <c r="AE52" t="n">
         <v>4.49</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AF52" t="n">
         <v>5.01</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AG52" t="n">
         <v>11.1</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AH52" t="n">
         <v>4.47</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AI52" t="n">
         <v>5.03</v>
       </c>
-      <c r="AJ51" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>1-SD 3mo range: $4.49–$5.01 (ann. vol 11%) | ATR range: $4.47–$5.03</t>
         </is>
@@ -11762,7 +11984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12062,7 +12284,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>insider_unknown</t>
+          <t>insider_sell</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -12783,12 +13005,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12798,75 +13020,87 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>insider_other</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0001140361-26-034367</t>
+          <t>0001683168-26-006737</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ef20081099_8k.htm</t>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S-3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
-        </is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v/>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>&gt;LANTRONIX, INC. 8-K</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0001140361-26-033577</t>
+          <t>0001683168-26-006732</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ny20080465x1_s3.htm</t>
+          <t>lantronix_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12876,37 +13110,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Items: 2.02, 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>&gt;LANTRONIX, INC. 8-K</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0001683168-26-006732</t>
+          <t>0001140361-26-034472</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>lantronix_8k.htm</t>
+          <t>ny20080465x2_424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ELME</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12916,7 +13142,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -12929,49 +13155,40 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Items: 8.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>&gt;elme-20260820</t>
-        </is>
-      </c>
+          <t>Items: 7.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0000104894-26-000110</t>
+          <t>0001140361-26-034367</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>elme-20260820.htm</t>
+          <t>ef20081099_8k.htm</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OWLT</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>S-3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -12981,143 +13198,148 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0001416811-26-000004</t>
+          <t>0001140361-26-033577</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787343101.xml</t>
+          <t>ny20080465x1_s3.htm</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OWLT</t>
+          <t>ELME</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Items: 8.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>&gt;elme-20260820</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0001213555-26-000004</t>
+          <t>0000104894-26-000110</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787343096.xml</t>
+          <t>elme-20260820.htm</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CSAI</t>
+          <t>OWLT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Item 3.01 (delisting, -6)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0001683168-26-006505</t>
+          <t>0001416811-26-000004</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>cloud_8k.htm</t>
+          <t>xslF345X06/wk-form4_1787343101.xml</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRUG</t>
+          <t>OWLT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Items: 7.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0001493152-26-039904</t>
+          <t>0001213555-26-000004</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>xslF345X06/wk-form4_1787343096.xml</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRUG</t>
+          <t>CSAI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -13127,7 +13349,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13136,22 +13358,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3)</t>
+          <t>Item 3.01 (delisting, -6)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0001493152-26-039727</t>
+          <t>0001683168-26-006505</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>cloud_8k.htm</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13390,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13181,13 +13403,13 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+          <t>Items: 7.01, 9.01 (routine)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0001493152-26-038904</t>
+          <t>0001493152-26-039904</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -13199,7 +13421,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BEEM</t>
+          <t>TRUG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -13209,7 +13431,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13218,145 +13440,145 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>&gt;beem20260819_8k.htm</t>
-        </is>
-      </c>
+          <t>Item 3.01 (delisting, -6) | Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0001437749-26-028564</t>
+          <t>0001493152-26-039727</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>beem20260819_8k.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>TRUG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0001493152-26-039581</t>
+          <t>0001493152-26-038904</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>form424b3.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>S-1/A</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Entry into a Material Definitive Agreement.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0001493152-26-039579</t>
+          <t>0001104659-26-100274</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>tm2615795d8_s1a.htm</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>BEEM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>424B3</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>dilution_risk</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&gt;beem20260819_8k.htm</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0001493152-26-039468</t>
+          <t>0001437749-26-028564</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>form424b3.htm</t>
+          <t>beem20260819_8k.htm</t>
         </is>
       </c>
     </row>
@@ -13368,43 +13590,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0001493152-26-038656</t>
+          <t>0001493152-26-039581</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>form8-k.htm</t>
+          <t>form424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -13414,7 +13632,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -13423,49 +13641,48 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Item 5.02 (officer_departure, -1)</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Item 1.01 (entry_agreement, +3) | Item 3.02 (unregistered_equity, -3)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Entry into a Material Definitive Agreement.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0001213900-26-093255</t>
+          <t>0001493152-26-039579</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ea0303279-8k_richtech.htm</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CAMP</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>424B3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>insider_sell</t>
+          <t>dilution_risk</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -13475,66 +13692,65 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0001598549-26-000007</t>
+          <t>0001493152-26-039468</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>xslF345X06/form4-08212026_080827.xml</t>
+          <t>form424b3.htm</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CAMP</t>
+          <t>AMCI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>insider_sell</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0001628280-26-058107</t>
+          <t>0001493152-26-038656</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>xslF345X06/wk-form4_1787186763.xml</t>
+          <t>form8-k.htm</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASYS</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8-K</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13544,107 +13760,274 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>insider_transaction</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>insider_buy</t>
+          <t>material_event</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Item 5.02 (officer_departure, -1)</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0002136935-26-000004</t>
+          <t>0001213900-26-093255</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>xslF345X06/ownership.xml</t>
+          <t>ea0303279-8k_richtech.htm</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8-K/A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>insider_buy</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Items: 2.02, 8.01, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0001493152-26-039796</t>
+          <t>0002136935-26-000004</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>form8-ka.htm</t>
+          <t>xslF345X06/ownership.xml</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>CAMP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8-K</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>material_event</t>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Items: 2.02, 9.01 (routine)</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
+          <t>0001598549-26-000009</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>xslF345X06/form4-08262026_080835.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CAMP</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0001598549-26-000007</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>xslF345X06/form4-08212026_080827.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CAMP</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>insider_transaction</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>insider_sell</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0001628280-26-058107</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>xslF345X06/wk-form4_1787186763.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DTCX</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>8-K/A</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 8.01, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0001493152-26-039796</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>form8-ka.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DTCX</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>8-K</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>material_event</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Items: 2.02, 9.01 (routine)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>0001493152-26-039786</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>form8-k.htm</t>
         </is>
